--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rba7c9d05ef384aea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R69053c984aef47ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R8cf30965075a4dab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-29新剧推荐" sheetId="4" r:id="R6cc1e64f16c04b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R6f074949ae1e4959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R6f8f2987ca4041ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Re20f34620c4c4a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rba43e63550604361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-29新剧推荐" sheetId="4" r:id="R14636510ab0e4bd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R521d8c2313f24aba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,25 +348,23 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>占院风波</x:v>
+        <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="E2" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>现实反转</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="n">
-        <x:v>4289</x:v>
-      </x:c>
+        <x:v>年代怀旧 / 种田囤货</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -374,7 +372,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
+        <x:v>占院风波</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
         <x:v>16</x:v>
@@ -386,11 +384,13 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="str"/>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="n">
+        <x:v>4289</x:v>
+      </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -398,25 +398,23 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>收租老汉</x:v>
+        <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>121</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E4" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>种田囤货</x:v>
-      </x:c>
-      <x:c r="G4" s="11" t="n">
-        <x:v>8368</x:v>
-      </x:c>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -424,25 +422,23 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>包子里的真心</x:v>
+        <x:v>灶下煤之自由篇</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E5" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
-      </x:c>
-      <x:c r="G5" s="11" t="n">
-        <x:v>7514</x:v>
-      </x:c>
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -450,22 +446,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>天灾囤货录，善恶见人心</x:v>
+        <x:v>包子里的真心</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>种田囤货 / 现实反转</x:v>
+        <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>852</x:v>
+        <x:v>7514</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
@@ -476,23 +472,25 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>1977山猎重生，我以余生偿前错</x:v>
+        <x:v>天灾囤货录，善恶见人心</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>375</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E7" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="str"/>
+        <x:v>种田囤货 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="n">
+        <x:v>852</x:v>
+      </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -500,23 +498,25 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>灶下煤之自由篇</x:v>
+        <x:v>收租老汉</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
         <x:v>种田囤货</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="str"/>
+      <x:c r="G8" s="11" t="n">
+        <x:v>8368</x:v>
+      </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -572,25 +572,23 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>垃圾桶里的寻人启事</x:v>
+        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E11" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="n">
-        <x:v>4442</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str"/>
       <x:c r="H11" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -598,23 +596,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
+        <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E12" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="str"/>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="n">
+        <x:v>4442</x:v>
+      </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -622,23 +622,23 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>山王传奇</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E13" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str"/>
       <x:c r="H13" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -646,23 +646,23 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>山王传奇</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -670,25 +670,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>谁说纨绔不能当状元</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="E15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>785</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
+        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -696,25 +696,23 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>谁说纨绔不能当状元</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>788</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E16" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="n">
-        <x:v>572</x:v>
-      </x:c>
+        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="str"/>
       <x:c r="H16" s="10" t="str">
-        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -722,25 +720,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>重生归来，四小姐她不装了</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E17" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>371</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -748,23 +746,23 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
-        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G18" s="11" t="str"/>
       <x:c r="H18" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -772,23 +770,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>重生归来，四小姐她不装了</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="str"/>
+      <x:c r="G19" s="11" t="n">
+        <x:v>371</x:v>
+      </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -820,23 +820,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E21" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="n">
+        <x:v>1834</x:v>
+      </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -844,23 +846,23 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>孤城照山河第一季</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>185</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25</x:v>
+        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -868,23 +870,23 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>孤城照山河第一季</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E23" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -892,25 +894,23 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>我将恩人一家捡回村</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E24" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G24" s="11" t="n">
-        <x:v>1834</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -918,25 +918,23 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>爷爷不请七遍不动筷</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E25" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="n">
-        <x:v>490</x:v>
-      </x:c>
+        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-18、2026-08-26</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -944,23 +942,23 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>悍妻替嫁，从前说</x:v>
+        <x:v>商场收回档口我成了全城的供应商</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E26" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>2026-08-10、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19</x:v>
+        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1018,25 +1016,25 @@
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="10" t="str">
-        <x:v>垃圾桶里捡来的状元郎</x:v>
+        <x:v>糯糯下山，师兄们都慌了</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>青椒剪辑</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1045,25 +1043,25 @@
       </x:c>
       <x:c r="B3" s="11"/>
       <x:c r="C3" s="10" t="str">
-        <x:v>锦绣新生1</x:v>
+        <x:v>玄门归来：十年婚约</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>九仙说漫</x:v>
+        <x:v>大公鸡剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1072,25 +1070,25 @@
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="10" t="str">
-        <x:v>红烛错缘，另寻良人</x:v>
+        <x:v>冒充我的网恋骗局</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>忆梦剧场</x:v>
+        <x:v>光影动画</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1099,25 +1097,25 @@
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="10" t="str">
-        <x:v>床底下的人</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>独影剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1126,25 +1124,25 @@
       </x:c>
       <x:c r="B6" s="11"/>
       <x:c r="C6" s="10" t="str">
-        <x:v>同志，你不配与我为敌</x:v>
+        <x:v>山沟里救下一条白龙</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>旺旺动画</x:v>
+        <x:v>小何故事会</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1153,25 +1151,25 @@
       </x:c>
       <x:c r="B7" s="11"/>
       <x:c r="C7" s="10" t="str">
-        <x:v>洪武苟长生第一季</x:v>
+        <x:v>藏拙十八年，千金归来掀风云</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>256</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
-        <x:v>一号剧场</x:v>
+        <x:v>魔力大剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1180,25 +1178,25 @@
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="10" t="str">
-        <x:v>断腿父王别慌，福星多多来啦！</x:v>
+        <x:v>谁说纨绔不能当状元第二季</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>星界秘漫</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1207,25 +1205,25 @@
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="10" t="str">
-        <x:v>我用骨髓换了个妹妹</x:v>
+        <x:v>错付奔向归途</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>小罗剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1234,25 +1232,25 @@
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="10" t="str">
-        <x:v>岭南归途</x:v>
+        <x:v>八零悍妇：女汉子逆袭记</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>漫剧场小管家</x:v>
+        <x:v>大宝动画</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1261,25 +1259,25 @@
       </x:c>
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="10" t="str">
-        <x:v>十块钱，我成了全校焦点</x:v>
+        <x:v>重回台风夜，我让她悔不当初</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>西米漫</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1288,25 +1286,25 @@
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="10" t="str">
-        <x:v>小福星驾到，通通闪开第一季</x:v>
+        <x:v>婚后计划</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>漫有戏剧场</x:v>
+        <x:v>草莓漫漫</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1315,25 +1313,25 @@
       </x:c>
       <x:c r="B13" s="11"/>
       <x:c r="C13" s="10" t="str">
-        <x:v>不向恶意妥协</x:v>
+        <x:v>萌宝神助攻，前妻不好哄</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈 / 婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>小小动画</x:v>
+        <x:v>拓拓逆袭剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1342,25 +1340,25 @@
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="10" t="str">
-        <x:v>重回八一从打猎开始发家第二季</x:v>
+        <x:v>我只想找死，却被奉为九州战神了</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>128</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
-        <x:v>年代怀旧 / 逆袭打脸</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>水滴文化</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1369,16 +1367,16 @@
       </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="10" t="str">
-        <x:v>错岸</x:v>
+        <x:v>听泉打捞王</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -1387,7 +1385,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>灰鲸剧场</x:v>
+        <x:v>泡姐漫屋</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1396,25 +1394,25 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="10" t="str">
-        <x:v>神医奶团：妙手扶爹</x:v>
+        <x:v>我在夜市摆摊成王</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>家庭伦理 / 萌宝治愈 / 战神异能</x:v>
+        <x:v>都市职场 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>小良短剧</x:v>
+        <x:v>张小曼</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1423,25 +1421,25 @@
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="10" t="str">
-        <x:v>领导拿我会员卡做人情</x:v>
+        <x:v>实习教出金牌班，家长要换班主任</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>壹琚影视</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1450,16 +1448,16 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="10" t="str">
-        <x:v>说好废柴大师兄，你成师妹严父了第一季</x:v>
+        <x:v>无限进化：从矿泉水开始称霸末日</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>127</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -1468,7 +1466,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
-        <x:v>暴躁的老少女</x:v>
+        <x:v>奇树剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1477,25 +1475,25 @@
       </x:c>
       <x:c r="B19" s="11"/>
       <x:c r="C19" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>被房车堵住的生死路</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>116</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>猛犸象短剧</x:v>
+        <x:v>二妞.影视</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1504,25 +1502,25 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="10" t="str">
-        <x:v>快闪开，我家公主来了</x:v>
+        <x:v>我的保镖身份不简单</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>148</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>樱桃追剧</x:v>
+        <x:v>伯爵剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1531,25 +1529,25 @@
       </x:c>
       <x:c r="B21" s="11"/>
       <x:c r="C21" s="10" t="str">
-        <x:v>渠水照见人心善恶</x:v>
+        <x:v>暴雨那天，全村看清了谁的砖是真的</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
-        <x:v>二三ONE.1</x:v>
+        <x:v>星梦短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1558,25 +1556,25 @@
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="10" t="str">
-        <x:v>分家那天，我要了一间破屋</x:v>
+        <x:v>退婚那天，他们嫌弃我爸收废品</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>卜卜漫剧</x:v>
+        <x:v>云起剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1585,25 +1583,25 @@
       </x:c>
       <x:c r="B23" s="11"/>
       <x:c r="C23" s="10" t="str">
-        <x:v>边界微光</x:v>
+        <x:v>签完离婚协议，我摊牌了</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场 / 婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>维维动画</x:v>
+        <x:v>小小动漫🔥</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1612,25 +1610,25 @@
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="10" t="str">
-        <x:v>不朽仙秦！第二季</x:v>
+        <x:v>风过牧野逢晚晴</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>189</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H24" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>虾仁白白</x:v>
+        <x:v>杭鹿二姐爱看剧</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1639,25 +1637,25 @@
       </x:c>
       <x:c r="B25" s="11"/>
       <x:c r="C25" s="10" t="str">
-        <x:v>晏晏总角时时安</x:v>
+        <x:v>回来那天，我成了钟点工</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
-        <x:v>寻光推剧</x:v>
+        <x:v>熊猫热剧</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1666,25 +1664,25 @@
       </x:c>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="10" t="str">
-        <x:v>我自风雨来</x:v>
+        <x:v>度淼入年</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>104</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>夜月山庄</x:v>
+        <x:v>安夏剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1693,25 +1691,25 @@
       </x:c>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="10" t="str">
-        <x:v>落子换良人</x:v>
+        <x:v>唯有暖阳照寒夜</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>枕边剧场</x:v>
+        <x:v>苞米花剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1720,25 +1718,25 @@
       </x:c>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="10" t="str">
-        <x:v>你是我的意外惊喜</x:v>
+        <x:v>卷王师妹不讲武德</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>103</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>元气剧场</x:v>
+        <x:v>光影</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1747,25 +1745,25 @@
       </x:c>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="10" t="str">
-        <x:v>锦绣芳华：乔兰书重生记</x:v>
+        <x:v>云端旧梦：分手四年傅机长失控了</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H29" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>别离剧场</x:v>
+        <x:v>小小动画</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1774,52 +1772,52 @@
       </x:c>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="10" t="str">
-        <x:v>就差你签字</x:v>
+        <x:v>开局拜仙尊为师杂灵根小师妹气运超强的</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
-        <x:v>灵魂漫谈</x:v>
+        <x:v>垂钓剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="10" t="str">
-        <x:v>一瓶水，让我看清亲生女儿</x:v>
+        <x:v>住三个月，住成了婚房</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>大表妹吖</x:v>
+        <x:v>小 淇</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1828,25 +1826,25 @@
       </x:c>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="10" t="str">
-        <x:v>扮废三年，年会当天我不演了</x:v>
+        <x:v>一瓶水，让我看清亲生女儿</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>大表妹吖</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1855,25 +1853,25 @@
       </x:c>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="10" t="str">
-        <x:v>我能在海里呼吸</x:v>
+        <x:v>重生六七：赶山狩猎养全家</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
-        <x:v>墨杨</x:v>
+        <x:v>铁柱动画</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1882,25 +1880,25 @@
       </x:c>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="10" t="str">
-        <x:v>末世重生：我不做圣母第一季</x:v>
+        <x:v>扮废三年，年会当天我不演了</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>170</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>至尊爽剧社</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1909,25 +1907,25 @@
       </x:c>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="10" t="str">
-        <x:v>重生六七：赶山狩猎养全家</x:v>
+        <x:v>我能在海里呼吸</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
-        <x:v>铁柱动画</x:v>
+        <x:v>墨杨</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1936,25 +1934,25 @@
       </x:c>
       <x:c r="B36" s="11"/>
       <x:c r="C36" s="10" t="str">
-        <x:v>修真一刹那，人间十三年</x:v>
+        <x:v>神医奶团：妙手扶爹</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>动漫放映机</x:v>
+        <x:v>小良短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1963,25 +1961,349 @@
       </x:c>
       <x:c r="B37" s="11"/>
       <x:c r="C37" s="10" t="str">
-        <x:v>越界：男友不许姐姐喝冰啤酒</x:v>
+        <x:v>红烛错缘，另寻良人</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H37" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="I37" s="10" t="str">
+        <x:v>忆梦剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B38" s="11"/>
+      <x:c r="C38" s="10" t="str">
+        <x:v>不向恶意妥协</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G38" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H37" s="10" t="str">
+      <x:c r="H38" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I38" s="10" t="str">
+        <x:v>小小动画</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B39" s="11"/>
+      <x:c r="C39" s="10" t="str">
+        <x:v>垃圾桶里捡来的状元郎</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G39" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H39" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="I39" s="10" t="str">
+        <x:v>东山啊</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B40" s="11"/>
+      <x:c r="C40" s="10" t="str">
+        <x:v>小福星驾到，通通闪开第一季</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G40" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H40" s="10" t="str">
+        <x:v>萌宝治愈</x:v>
+      </x:c>
+      <x:c r="I40" s="10" t="str">
+        <x:v>漫有戏剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B41" s="11"/>
+      <x:c r="C41" s="10" t="str">
+        <x:v>分家那天，我要了一间破屋</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G41" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H41" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I41" s="10" t="str">
+        <x:v>卜卜漫剧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B42" s="11"/>
+      <x:c r="C42" s="10" t="str">
+        <x:v>重回八一从打猎开始发家第二季</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G42" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="H42" s="10" t="str">
+        <x:v>年代怀旧 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="I42" s="10" t="str">
+        <x:v>水滴文化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B43" s="11"/>
+      <x:c r="C43" s="10" t="str">
+        <x:v>错岸</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G43" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H43" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I43" s="10" t="str">
+        <x:v>灰鲸剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B44" s="11"/>
+      <x:c r="C44" s="10" t="str">
+        <x:v>渠水照见人心善恶</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G44" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H44" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="I44" s="10" t="str">
+        <x:v>二三ONE.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B45" s="11"/>
+      <x:c r="C45" s="10" t="str">
+        <x:v>我用骨髓换了个妹妹</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G45" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="H45" s="10" t="str">
         <x:v>家庭伦理</x:v>
       </x:c>
-      <x:c r="I37" s="10" t="str">
-        <x:v>雪球动漫</x:v>
+      <x:c r="I45" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B46" s="11"/>
+      <x:c r="C46" s="10" t="str">
+        <x:v>床底下的人</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G46" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="H46" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I46" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B47" s="11"/>
+      <x:c r="C47" s="10" t="str">
+        <x:v>锦绣芳华：乔兰书重生记</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G47" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H47" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I47" s="10" t="str">
+        <x:v>别离剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B48" s="11"/>
+      <x:c r="C48" s="10" t="str">
+        <x:v>拂衣震九州</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G48" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H48" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I48" s="10" t="str">
+        <x:v>猛犸象短剧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B49" s="11"/>
+      <x:c r="C49" s="10" t="str">
+        <x:v>断腿父王别慌，福星多多来啦！</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G49" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H49" s="10" t="str">
+        <x:v>萌宝治愈</x:v>
+      </x:c>
+      <x:c r="I49" s="10" t="str">
+        <x:v>星界秘漫</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2038,7 +2360,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
-        <x:v>收租老汉</x:v>
+        <x:v>包子里的真心</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
         <x:v>7</x:v>
@@ -2050,16 +2372,16 @@
         <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>121</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H2" s="11" t="n">
-        <x:v>8368</x:v>
+        <x:v>7514</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；8月消耗8,368元居前；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2067,7 +2389,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>包子里的真心</x:v>
+        <x:v>天灾囤货录，善恶见人心</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
         <x:v>7</x:v>
@@ -2079,16 +2401,16 @@
         <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>7514</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；8月消耗7,514元居前；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2096,7 +2418,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>天灾囤货录，善恶见人心</x:v>
+        <x:v>收租老汉</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
         <x:v>7</x:v>
@@ -2108,16 +2430,16 @@
         <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>852</x:v>
+        <x:v>8368</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2144,7 +2466,7 @@
       </x:c>
       <x:c r="H5" s="11" t="str"/>
       <x:c r="I5" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计14次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计14次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2152,7 +2474,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>垃圾桶里的寻人启事</x:v>
+        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
         <x:v>7</x:v>
@@ -2161,19 +2483,17 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="n">
-        <x:v>4442</x:v>
-      </x:c>
+      <x:c r="H6" s="11" t="str"/>
       <x:c r="I6" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；8月消耗4,442元居前；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2181,26 +2501,28 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="str"/>
+      <x:c r="H7" s="11" t="n">
+        <x:v>4442</x:v>
+      </x:c>
       <x:c r="I7" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2208,26 +2530,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>云岭藏金，真心为聘</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str"/>
       <x:c r="I8" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2235,26 +2557,26 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2262,26 +2584,26 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>魔力情谊之我一个人来的</x:v>
+        <x:v>孤城照山河第一季</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str"/>
       <x:c r="I10" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计10次，起量能力已被验证；185集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2289,26 +2611,26 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>我哥四个全是宠妹狂魔</x:v>
+        <x:v>云岭藏金，真心为聘</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜7次、累计7次，起量能力已被验证；仿真人制作；100集长剧集；题材契合爆款主线（婚姻情感）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2316,26 +2638,26 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
+        <x:v>魔力情谊之我一个人来的</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜6次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2343,26 +2665,26 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜6次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2370,26 +2692,26 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜6次、累计10次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计12次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2397,26 +2719,26 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>悍妻替嫁，从前说</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计11次，起量能力已被验证；56集长剧集；题材契合爆款主线（种田囤货 / 美食治愈 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2424,26 +2746,26 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>三百块的信任，九十万的真相</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计10次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2451,26 +2773,26 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>九二年，他塞给我五百块</x:v>
+        <x:v>悍妻替嫁，从前说</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str"/>
       <x:c r="I17" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2478,26 +2800,26 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>守着灶台，守住本心</x:v>
+        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；52集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2505,10 +2827,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>我被嫁给瘸腿猎户，饥荒年顿顿吃肉吃到撑</x:v>
+        <x:v>三百块的信任，九十万的真相</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>7</x:v>
@@ -2517,14 +2839,14 @@
         <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计7次，起量能力已被验证；经典3D制作；131集长剧集；题材契合爆款主线（婚姻情感 / 美食治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2532,26 +2854,26 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>199的排场，48万的账</x:v>
+        <x:v>我哥四个全是宠妹狂魔</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；100集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2562,7 +2884,7 @@
         <x:v>大力幼崽到处捡爹</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>6</x:v>
@@ -2578,7 +2900,7 @@
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2586,10 +2908,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>疯娘翻身，穿越宠崽</x:v>
+        <x:v>馋哭！陆总该吃饭了</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>6</x:v>
@@ -2598,14 +2920,14 @@
         <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计6次，起量能力已被验证；200集长剧集；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 现实反转）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；98集长剧集；题材契合爆款主线（美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2613,26 +2935,26 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>被总经理针对后，我只按菜单做菜</x:v>
+        <x:v>分家只给破枪，我听兽语富全屯</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场 / 美食治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2640,26 +2962,26 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>馋哭！陆总该吃饭了</x:v>
+        <x:v>这个姨娘不一般</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；98集长剧集；题材契合爆款主线（美食治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2667,26 +2989,26 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>一塘清水鉴人心</x:v>
+        <x:v>重回千禧我靠赶海养活家人</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计8次，起量能力已被验证；183集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2694,26 +3016,26 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>半熟沦陷</x:v>
+        <x:v>九二年，他塞给我五百块</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计5次，起量能力已被验证；68集长剧集；题材契合爆款主线（婚姻情感）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2721,26 +3043,26 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>小火归山</x:v>
+        <x:v>199的排场，48万的账</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计5次，起量能力已被验证；50集长剧集；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2748,26 +3070,26 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>恶妇翻身一锅烟火养全家第一季</x:v>
+        <x:v>疯娘翻身，穿越宠崽</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>174</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计5次，起量能力已被验证；174集长剧集；题材契合爆款主线（逆袭打脸）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；200集长剧集；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2775,26 +3097,26 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>青云入世这个神医会功夫</x:v>
+        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>146</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；146集长剧集；题材契合爆款主线（婚姻情感 / 战神异能）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2802,26 +3124,26 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>青礁潮起，鲛人归</x:v>
+        <x:v>被总经理针对后，我只按菜单做菜</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜5次、累计5次，起量能力已被验证；51集长剧集；题材契合爆款主线（战神异能）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2829,26 +3151,26 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>分家只给破枪，我听兽语富全屯</x:v>
+        <x:v>一塘清水鉴人心</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-15</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2856,26 +3178,26 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>这个姨娘不一般</x:v>
+        <x:v>寒庭有犬鸣</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计5次，起量能力已被验证；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2883,26 +3205,26 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>傅总，您的三岁小债主上门了</x:v>
+        <x:v>青云入世这个神医会功夫</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；97集长剧集；题材契合爆款主线（萌宝治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；146集长剧集；题材契合爆款主线（婚姻情感 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2910,26 +3232,26 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
+        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>119</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str"/>
       <x:c r="I34" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2937,28 +3259,26 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>这杯奶茶你请不起</x:v>
+        <x:v>八零之老妈在厂长家当后妈</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H35" s="11" t="n">
-        <x:v>6078</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H35" s="11" t="str"/>
       <x:c r="I35" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；60集长剧集；题材契合爆款主线（都市职场 / 美食治愈）；8月消耗6,078元居前；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2966,26 +3286,26 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>八零媳妇富农家</x:v>
+        <x:v>守着灶台，守住本心</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>105</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str"/>
       <x:c r="I36" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计5次，起量能力已被验证；105集长剧集；题材契合爆款主线（年代怀旧）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；52集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2993,26 +3313,26 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>寒庭有犬鸣</x:v>
+        <x:v>傅总，您的三岁小债主上门了</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E37" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计5次，起量能力已被验证；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；97集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3020,26 +3340,26 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>赶海救下小龙女，成群鱼虾网里钻</x:v>
+        <x:v>傻女重生记，睁眼后盖房发家</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str"/>
       <x:c r="I38" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；95集长剧集；题材契合爆款主线（种田囤货 / 战神异能）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3047,26 +3367,26 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>别人养鱼，我养水</x:v>
+        <x:v>八零媳妇富农家</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G39" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str"/>
       <x:c r="I39" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；62集长剧集；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；105集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3074,26 +3394,26 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>团宠农家小奶包</x:v>
+        <x:v>半熟沦陷</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G40" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str"/>
       <x:c r="I40" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；135集长剧集；题材契合爆款主线（婚姻情感）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3101,26 +3421,26 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>我的车间不养闲人</x:v>
+        <x:v>小火归山</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
         <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G41" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str"/>
       <x:c r="I41" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3128,26 +3448,26 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>携手八零，与君同赴山河</x:v>
+        <x:v>恶妇翻身一锅烟火养全家第一季</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-15</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G42" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H42" s="11" t="str"/>
       <x:c r="I42" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；124集长剧集；题材契合爆款主线（年代怀旧 / 古装宫廷）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；174集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3155,26 +3475,26 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>旧爱难哄：贺医生请自重</x:v>
+        <x:v>我家成了别人的婚房</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E43" s="11" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G43" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H43" s="11" t="str"/>
       <x:c r="I43" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；题材契合爆款主线（年代怀旧 / 婚姻情感）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；71集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -3182,26 +3502,26 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>满宝进山闻香，山货全归我家</x:v>
+        <x:v>我的订婚宴上，闯进来两个要饭的</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E44" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>203</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G44" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H44" s="11" t="str"/>
       <x:c r="I44" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；203集长剧集；题材契合爆款主线（种田囤货）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -3209,26 +3529,26 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>满朝文武等开饭</x:v>
+        <x:v>青礁潮起，鲛人归</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G45" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H45" s="11" t="str"/>
       <x:c r="I45" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；题材契合爆款主线（美食治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；51集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -3236,7 +3556,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>灵泉姑娘，分家后富甲一方第一季</x:v>
+        <x:v>别人养鱼，我养水</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>4</x:v>
@@ -3248,14 +3568,14 @@
         <x:v>2026-08-15</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>152</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G46" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H46" s="11" t="str"/>
       <x:c r="I46" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；152集长剧集；题材契合爆款主线（种田囤货）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；62集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3263,7 +3583,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>萌宝岁岁：两界穿梭建桃源</x:v>
+        <x:v>我的车间不养闲人</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>4</x:v>
@@ -3272,17 +3592,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E47" s="11" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G47" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H47" s="11" t="str"/>
       <x:c r="I47" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；88集长剧集；题材契合爆款主线（萌宝治愈）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -3290,7 +3610,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>蒙眼望断江南雪</x:v>
+        <x:v>携手八零，与君同赴山河</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>4</x:v>
@@ -3299,17 +3619,44 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E48" s="11" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G48" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H48" s="11" t="str"/>
       <x:c r="I48" s="10" t="str">
-        <x:v>8-10~8-16两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（古装宫廷）；已冷却约一周，复投窗口开启</x:v>
+        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；124集长剧集；题材契合爆款主线（年代怀旧 / 古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" s="10" t="str">
+        <x:v>灵泉姑娘，分家后富甲一方第一季</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="str">
+        <x:v>2026-08-15</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G49" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H49" s="11" t="str"/>
+      <x:c r="I49" s="10" t="str">
+        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；152集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4302,10 +4649,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>309</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>42.8%</x:v>
+        <x:v>43.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4313,10 +4660,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>222</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>30.7%</x:v>
+        <x:v>30.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4324,7 +4671,7 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>191</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>26.5%</x:v>
@@ -4351,10 +4698,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>12.2%</x:v>
+        <x:v>12%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4362,10 +4709,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>324</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>45.1%</x:v>
+        <x:v>45%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4373,10 +4720,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>11.5%</x:v>
+        <x:v>11.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4384,10 +4731,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>223</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>31%</x:v>
+        <x:v>31.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -4411,10 +4758,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>275</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>38.1%</x:v>
+        <x:v>38.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4422,10 +4769,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>18.7%</x:v>
+        <x:v>18.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4433,10 +4780,10 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>11.5%</x:v>
+        <x:v>11.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4444,7 +4791,7 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>10.1%</x:v>
@@ -4455,10 +4802,10 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>9.3%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4466,10 +4813,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.3%</x:v>
+        <x:v>8.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4477,10 +4824,10 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>7.3%</x:v>
+        <x:v>7.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4491,7 +4838,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>6.6%</x:v>
+        <x:v>6.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4499,10 +4846,10 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>5.4%</x:v>
+        <x:v>5.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4510,10 +4857,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>4.8%</x:v>
+        <x:v>5.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -4537,10 +4884,10 @@
         <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4548,10 +4895,10 @@
         <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4570,10 +4917,10 @@
         <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4592,10 +4939,10 @@
         <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4603,10 +4950,10 @@
         <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4614,10 +4961,10 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4625,10 +4972,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>1.4%</x:v>
+        <x:v>1.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4636,10 +4983,10 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>2.2%</x:v>
+        <x:v>2.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4647,10 +4994,10 @@
         <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>3.6%</x:v>
+        <x:v>4.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4658,10 +5005,10 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>5.4%</x:v>
+        <x:v>6.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4669,10 +5016,10 @@
         <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>6.9%</x:v>
+        <x:v>4.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4680,7 +5027,7 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
         <x:v>8.2%</x:v>
@@ -4691,10 +5038,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>16.6%</x:v>
+        <x:v>17.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -4702,10 +5049,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>374</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>51.8%</x:v>
+        <x:v>51.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="22" customHeight="1">
@@ -4729,10 +5076,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>712</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>98.6%</x:v>
+        <x:v>98.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -4795,7 +5142,7 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
         <x:v>5</x:v>
@@ -4804,16 +5151,16 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="B58" s="11" t="n">
         <x:v>4</x:v>
@@ -4822,7 +5169,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
         <x:v>4</x:v>
@@ -4831,7 +5178,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
         <x:v>4</x:v>
@@ -4840,7 +5187,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>取瘾书屋</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
         <x:v>4</x:v>
@@ -4849,7 +5196,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>清风短剧场</x:v>
+        <x:v>取瘾书屋</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
         <x:v>4</x:v>
@@ -4858,7 +5205,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>暖星追剧</x:v>
+        <x:v>清风短剧场</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
         <x:v>4</x:v>
@@ -4867,16 +5214,16 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>暖星追剧</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C64" s="11" t="str"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>一张不够花</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
         <x:v>3</x:v>
@@ -4885,7 +5232,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
         <x:v>3</x:v>
@@ -4894,7 +5241,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
         <x:v>3</x:v>
@@ -4903,7 +5250,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
         <x:v>3</x:v>
@@ -4912,7 +5259,7 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>不兜</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
         <x:v>3</x:v>
@@ -4992,7 +5339,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>战神/异能</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
         <x:v>6</x:v>
@@ -5003,7 +5350,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>6</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R6f8f2987ca4041ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Re20f34620c4c4a56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rba43e63550604361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-29新剧推荐" sheetId="4" r:id="R14636510ab0e4bd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R521d8c2313f24aba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R33a8e59118684aa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R7b78767691404af3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R66a8758a82af444c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Re2118d41c5a34391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R43df41bccec84b4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3669,13 +3669,14 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="70" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="70" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -3683,24 +3684,27 @@
         <x:v>排名</x:v>
       </x:c>
       <x:c r="B1" t="str">
+        <x:v>预计上线</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
         <x:v>剧名</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="D1" t="str">
         <x:v>集数</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="E1" t="str">
         <x:v>制作风格</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="F1" t="str">
         <x:v>主题分类</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="G1" t="str">
         <x:v>发布账号</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="H1" t="str">
         <x:v>推荐依据</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="I1" t="str">
         <x:v>综合评分</x:v>
       </x:c>
     </x:row>
@@ -3708,25 +3712,28 @@
       <x:c r="A2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B2" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
         <x:v>假面恋人：三十八万撕开两年恋爱骗局</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="n">
+      <x:c r="D2" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
+      <x:c r="E2" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
         <x:v>婚姻情感 / 美食治愈 / 现实反转</x:v>
       </x:c>
-      <x:c r="F2" s="10" t="str">
+      <x:c r="G2" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="str">
+      <x:c r="H2" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H2" s="11" t="n">
+      <x:c r="I2" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3734,25 +3741,28 @@
       <x:c r="A3" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="10" t="str">
+      <x:c r="B3" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
         <x:v>婚内骗局，我彻底粉碎前夫阴谋</x:v>
       </x:c>
-      <x:c r="C3" s="11" t="n">
+      <x:c r="D3" s="11" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E3" s="10" t="str">
+      <x:c r="E3" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
         <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
-      <x:c r="F3" s="10" t="str">
+      <x:c r="G3" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G3" s="10" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；84集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H3" s="11" t="n">
+      <x:c r="I3" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3760,25 +3770,28 @@
       <x:c r="A4" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="str">
+      <x:c r="B4" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
         <x:v>闺蜜的谎言</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="n">
+      <x:c r="D4" s="11" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E4" s="10" t="str">
+      <x:c r="E4" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
         <x:v>现实反转</x:v>
       </x:c>
-      <x:c r="F4" s="10" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="str">
+      <x:c r="H4" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H4" s="11" t="n">
+      <x:c r="I4" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3786,25 +3799,28 @@
       <x:c r="A5" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="10" t="str">
+      <x:c r="B5" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
         <x:v>一场蜜月，撕毁了我的婚姻</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="D5" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="str">
+      <x:c r="E5" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H5" s="11" t="n">
+      <x:c r="I5" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3812,25 +3828,28 @@
       <x:c r="A6" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="10" t="str">
+      <x:c r="B6" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
         <x:v>一庭兰香旧人归</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="D6" s="11" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E6" s="10" t="str">
+      <x:c r="E6" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="str">
         <x:v>年代怀旧</x:v>
       </x:c>
-      <x:c r="F6" s="10" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>西瑶短剧</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="str">
+      <x:c r="H6" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="n">
+      <x:c r="I6" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3838,25 +3857,28 @@
       <x:c r="A7" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="str">
+      <x:c r="B7" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
         <x:v>姐姐不是提款机</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="D7" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E7" s="10" t="str">
+      <x:c r="E7" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="str">
         <x:v>家庭伦理</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="n">
+      <x:c r="I7" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3864,25 +3886,28 @@
       <x:c r="A8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="10" t="str">
+      <x:c r="B8" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
         <x:v>婚礼当天，我拆穿了小姑子的假陪嫁房</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="D8" s="11" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E8" s="10" t="str">
+      <x:c r="E8" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="F8" s="10" t="str">
+      <x:c r="G8" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="str">
+      <x:c r="H8" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="n">
+      <x:c r="I8" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3890,25 +3915,28 @@
       <x:c r="A9" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="10" t="str">
+      <x:c r="B9" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
         <x:v>归来吧，妈妈</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="n">
+      <x:c r="D9" s="11" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E9" s="10" t="str">
+      <x:c r="E9" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
         <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="F9" s="10" t="str">
+      <x:c r="G9" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="str">
+      <x:c r="H9" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="n">
+      <x:c r="I9" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3916,25 +3944,28 @@
       <x:c r="A10" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="10" t="str">
+      <x:c r="B10" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
         <x:v>情深不知晚</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="n">
+      <x:c r="D10" s="11" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E10" s="10" t="str">
+      <x:c r="E10" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="F10" s="10" t="str">
+      <x:c r="G10" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="str">
+      <x:c r="H10" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H10" s="11" t="n">
+      <x:c r="I10" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3942,25 +3973,28 @@
       <x:c r="A11" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="10" t="str">
+      <x:c r="B11" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
         <x:v>我养了三年的保姆，想夺走我的一切</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="n">
+      <x:c r="D11" s="11" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E11" s="10" t="str">
+      <x:c r="E11" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="str">
         <x:v>家庭伦理</x:v>
       </x:c>
-      <x:c r="F11" s="10" t="str">
+      <x:c r="G11" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G11" s="10" t="str">
+      <x:c r="H11" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H11" s="11" t="n">
+      <x:c r="I11" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3968,25 +4002,28 @@
       <x:c r="A12" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="10" t="str">
+      <x:c r="B12" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
         <x:v>我用一场退婚，换回了整个人生</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="n">
+      <x:c r="D12" s="11" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E12" s="10" t="str">
+      <x:c r="E12" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="F12" s="10" t="str">
+      <x:c r="G12" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="str">
+      <x:c r="H12" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；68集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H12" s="11" t="n">
+      <x:c r="I12" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3994,25 +4031,28 @@
       <x:c r="A13" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B13" s="10" t="str">
+      <x:c r="B13" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
         <x:v>我的座位，恕不奉陪</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="n">
+      <x:c r="D13" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E13" s="10" t="str">
+      <x:c r="E13" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="str">
         <x:v>都市职场</x:v>
       </x:c>
-      <x:c r="F13" s="10" t="str">
+      <x:c r="G13" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="G13" s="10" t="str">
+      <x:c r="H13" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="H13" s="11" t="n">
+      <x:c r="I13" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4020,25 +4060,28 @@
       <x:c r="A14" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="10" t="str">
+      <x:c r="B14" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
         <x:v>逆袭之通天财眼第7季</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="n">
+      <x:c r="D14" s="11" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E14" s="10" t="str">
+      <x:c r="E14" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
-      <x:c r="F14" s="10" t="str">
+      <x:c r="G14" s="10" t="str">
         <x:v>丽娟影视</x:v>
       </x:c>
-      <x:c r="G14" s="10" t="str">
+      <x:c r="H14" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；100集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="n">
+      <x:c r="I14" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4046,25 +4089,28 @@
       <x:c r="A15" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B15" s="10" t="str">
+      <x:c r="B15" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
         <x:v>重生为蛇，投喂女帝反哺成龙第二季</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="n">
+      <x:c r="D15" s="11" t="n">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E15" s="10" t="str">
+      <x:c r="E15" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="str">
         <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
-      <x:c r="F15" s="10" t="str">
+      <x:c r="G15" s="10" t="str">
         <x:v>鲸喜漫剧🐳</x:v>
       </x:c>
-      <x:c r="G15" s="10" t="str">
+      <x:c r="H15" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H15" s="11" t="n">
+      <x:c r="I15" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4072,25 +4118,28 @@
       <x:c r="A16" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="10" t="str">
+      <x:c r="B16" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
         <x:v>重生猎户：杜鹃赶山屯满粮第二季</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="n">
+      <x:c r="D16" s="11" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E16" s="10" t="str">
+      <x:c r="E16" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F16" s="10" t="str">
         <x:v>种田囤货</x:v>
       </x:c>
-      <x:c r="F16" s="10" t="str">
+      <x:c r="G16" s="10" t="str">
         <x:v>朝霞看剧</x:v>
       </x:c>
-      <x:c r="G16" s="10" t="str">
+      <x:c r="H16" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；118集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H16" s="11" t="n">
+      <x:c r="I16" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4098,25 +4147,28 @@
       <x:c r="A17" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B17" s="10" t="str">
+      <x:c r="B17" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
         <x:v>食香记：从一坛腌萝卜开始逆袭第一季完整版</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="n">
+      <x:c r="D17" s="11" t="n">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E17" s="10" t="str">
+      <x:c r="E17" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F17" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
-      <x:c r="F17" s="10" t="str">
+      <x:c r="G17" s="10" t="str">
         <x:v>上官格格</x:v>
       </x:c>
-      <x:c r="G17" s="10" t="str">
+      <x:c r="H17" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；161集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H17" s="11" t="n">
+      <x:c r="I17" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4124,25 +4176,28 @@
       <x:c r="A18" s="11" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B18" s="10" t="str">
+      <x:c r="B18" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
         <x:v>不死帝师上界篇第一季</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="n">
+      <x:c r="D18" s="11" t="n">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E18" s="10" t="str">
+      <x:c r="E18" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="F18" s="10" t="str">
+      <x:c r="G18" s="10" t="str">
         <x:v>龙小五剧场</x:v>
       </x:c>
-      <x:c r="G18" s="10" t="str">
+      <x:c r="H18" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；74集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H18" s="11" t="n">
+      <x:c r="I18" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4150,25 +4205,28 @@
       <x:c r="A19" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B19" s="10" t="str">
+      <x:c r="B19" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
         <x:v>五千块起家！卡车司机的逆袭人生</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="n">
+      <x:c r="D19" s="11" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E19" s="10" t="str">
+      <x:c r="E19" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="str">
         <x:v>都市职场 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="F19" s="10" t="str">
+      <x:c r="G19" s="10" t="str">
         <x:v>骏乐夜航船AIGC剧场</x:v>
       </x:c>
-      <x:c r="G19" s="10" t="str">
+      <x:c r="H19" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「骏乐夜航船AIGC剧场」</x:v>
       </x:c>
-      <x:c r="H19" s="11" t="n">
+      <x:c r="I19" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4176,25 +4234,28 @@
       <x:c r="A20" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B20" s="10" t="str">
+      <x:c r="B20" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
         <x:v>从前说：七零佳媳渡风尘第一季</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="n">
+      <x:c r="D20" s="11" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E20" s="10" t="str">
+      <x:c r="E20" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F20" s="10" t="str">
         <x:v>年代怀旧</x:v>
       </x:c>
-      <x:c r="F20" s="10" t="str">
+      <x:c r="G20" s="10" t="str">
         <x:v>排尚漫屋</x:v>
       </x:c>
-      <x:c r="G20" s="10" t="str">
+      <x:c r="H20" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H20" s="11" t="n">
+      <x:c r="I20" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4202,25 +4263,28 @@
       <x:c r="A21" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B21" s="10" t="str">
+      <x:c r="B21" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
         <x:v>从捡个仙子做老婆开始，凡血踏九天第二季</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="n">
+      <x:c r="D21" s="11" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E21" s="10" t="str">
+      <x:c r="E21" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F21" s="10" t="str">
         <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
-      <x:c r="F21" s="10" t="str">
+      <x:c r="G21" s="10" t="str">
         <x:v>云腾剧场</x:v>
       </x:c>
-      <x:c r="G21" s="10" t="str">
+      <x:c r="H21" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；95集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H21" s="11" t="n">
+      <x:c r="I21" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4228,25 +4292,28 @@
       <x:c r="A22" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B22" s="10" t="str">
+      <x:c r="B22" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
         <x:v>仙姝重回：我和魔尊带着宗门上大分第三季</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="n">
+      <x:c r="D22" s="11" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D22" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E22" s="10" t="str">
+      <x:c r="E22" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F22" s="10" t="str">
         <x:v>年代怀旧 / 古装宫廷 / 战神异能</x:v>
       </x:c>
-      <x:c r="F22" s="10" t="str">
+      <x:c r="G22" s="10" t="str">
         <x:v>西子是个演员</x:v>
       </x:c>
-      <x:c r="G22" s="10" t="str">
+      <x:c r="H22" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧 / 古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H22" s="11" t="n">
+      <x:c r="I22" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4254,25 +4321,28 @@
       <x:c r="A23" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B23" s="10" t="str">
+      <x:c r="B23" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
         <x:v>公路求生卡进了古代，柳姨娘癫狂极了第三季</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="n">
+      <x:c r="D23" s="11" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E23" s="10" t="str">
+      <x:c r="E23" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F23" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="F23" s="10" t="str">
+      <x:c r="G23" s="10" t="str">
         <x:v>澜溪剧场</x:v>
       </x:c>
-      <x:c r="G23" s="10" t="str">
+      <x:c r="H23" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H23" s="11" t="n">
+      <x:c r="I23" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4280,25 +4350,28 @@
       <x:c r="A24" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B24" s="10" t="str">
+      <x:c r="B24" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
         <x:v>凤栖为臣，女扮男装搞基建第一季</x:v>
       </x:c>
-      <x:c r="C24" s="11" t="n">
+      <x:c r="D24" s="11" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D24" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E24" s="10" t="str">
+      <x:c r="E24" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F24" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="F24" s="10" t="str">
+      <x:c r="G24" s="10" t="str">
         <x:v>文心动漫</x:v>
       </x:c>
-      <x:c r="G24" s="10" t="str">
+      <x:c r="H24" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H24" s="11" t="n">
+      <x:c r="I24" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4306,25 +4379,28 @@
       <x:c r="A25" s="11" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B25" s="10" t="str">
+      <x:c r="B25" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
         <x:v>刘一祖的故事之逆袭</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="n">
+      <x:c r="D25" s="11" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D25" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E25" s="10" t="str">
+      <x:c r="E25" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F25" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
-      <x:c r="F25" s="10" t="str">
+      <x:c r="G25" s="10" t="str">
         <x:v>彩云动画</x:v>
       </x:c>
-      <x:c r="G25" s="10" t="str">
+      <x:c r="H25" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「彩云动画」</x:v>
       </x:c>
-      <x:c r="H25" s="11" t="n">
+      <x:c r="I25" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4332,25 +4408,28 @@
       <x:c r="A26" s="11" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B26" s="10" t="str">
+      <x:c r="B26" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
         <x:v>刚毕业，离婚逆袭系统就来了</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="n">
+      <x:c r="D26" s="11" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D26" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E26" s="10" t="str">
+      <x:c r="E26" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F26" s="10" t="str">
         <x:v>婚姻情感 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
-      <x:c r="F26" s="10" t="str">
+      <x:c r="G26" s="10" t="str">
         <x:v>灯下漫剧</x:v>
       </x:c>
-      <x:c r="G26" s="10" t="str">
+      <x:c r="H26" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 战神异能）；发布账号「灯下漫剧」</x:v>
       </x:c>
-      <x:c r="H26" s="11" t="n">
+      <x:c r="I26" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4358,25 +4437,28 @@
       <x:c r="A27" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B27" s="10" t="str">
+      <x:c r="B27" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
         <x:v>合伙人老婆夺我权我反手收购公司</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="n">
+      <x:c r="D27" s="11" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E27" s="10" t="str">
+      <x:c r="E27" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F27" s="10" t="str">
         <x:v>都市职场 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="F27" s="10" t="str">
+      <x:c r="G27" s="10" t="str">
         <x:v>优文疯漫</x:v>
       </x:c>
-      <x:c r="G27" s="10" t="str">
+      <x:c r="H27" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「优文疯漫」</x:v>
       </x:c>
-      <x:c r="H27" s="11" t="n">
+      <x:c r="I27" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4384,25 +4466,28 @@
       <x:c r="A28" s="11" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B28" s="10" t="str">
+      <x:c r="B28" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
         <x:v>商先生，婚后请热恋第三季</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="n">
+      <x:c r="D28" s="11" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D28" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E28" s="10" t="str">
+      <x:c r="E28" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F28" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="F28" s="10" t="str">
+      <x:c r="G28" s="10" t="str">
         <x:v>智帧剧场</x:v>
       </x:c>
-      <x:c r="G28" s="10" t="str">
+      <x:c r="H28" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H28" s="11" t="n">
+      <x:c r="I28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4410,25 +4495,28 @@
       <x:c r="A29" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B29" s="10" t="str">
+      <x:c r="B29" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
         <x:v>姑妈供我成状元，我用一生报她恩第一季</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="n">
+      <x:c r="D29" s="11" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D29" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E29" s="10" t="str">
+      <x:c r="E29" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F29" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="F29" s="10" t="str">
+      <x:c r="G29" s="10" t="str">
         <x:v>灵漫好剧</x:v>
       </x:c>
-      <x:c r="G29" s="10" t="str">
+      <x:c r="H29" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H29" s="11" t="n">
+      <x:c r="I29" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4436,25 +4524,28 @@
       <x:c r="A30" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B30" s="10" t="str">
+      <x:c r="B30" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
         <x:v>宠物急诊：自带病症词条天眼第一季</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="n">
+      <x:c r="D30" s="11" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D30" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E30" s="10" t="str">
+      <x:c r="E30" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F30" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="F30" s="10" t="str">
+      <x:c r="G30" s="10" t="str">
         <x:v>灵漫剧场</x:v>
       </x:c>
-      <x:c r="G30" s="10" t="str">
+      <x:c r="H30" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H30" s="11" t="n">
+      <x:c r="I30" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4462,25 +4553,28 @@
       <x:c r="A31" s="11" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B31" s="10" t="str">
+      <x:c r="B31" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
         <x:v>导航里的秘密！</x:v>
       </x:c>
-      <x:c r="C31" s="11" t="n">
+      <x:c r="D31" s="11" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D31" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E31" s="10" t="str">
+      <x:c r="E31" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F31" s="10" t="str">
         <x:v>现实反转</x:v>
       </x:c>
-      <x:c r="F31" s="10" t="str">
+      <x:c r="G31" s="10" t="str">
         <x:v>梦启剧场</x:v>
       </x:c>
-      <x:c r="G31" s="10" t="str">
+      <x:c r="H31" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「梦启剧场」</x:v>
       </x:c>
-      <x:c r="H31" s="11" t="n">
+      <x:c r="I31" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4488,25 +4582,28 @@
       <x:c r="A32" s="11" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B32" s="10" t="str">
+      <x:c r="B32" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
         <x:v>彩运照人心第三季</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="n">
+      <x:c r="D32" s="11" t="n">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D32" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E32" s="10" t="str">
+      <x:c r="E32" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F32" s="10" t="str">
         <x:v>现实反转</x:v>
       </x:c>
-      <x:c r="F32" s="10" t="str">
+      <x:c r="G32" s="10" t="str">
         <x:v>云间漫剧-丸子</x:v>
       </x:c>
-      <x:c r="G32" s="10" t="str">
+      <x:c r="H32" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；121集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H32" s="11" t="n">
+      <x:c r="I32" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4514,25 +4611,28 @@
       <x:c r="A33" s="11" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B33" s="10" t="str">
+      <x:c r="B33" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
         <x:v>穿成团宠后我靠读心逆袭</x:v>
       </x:c>
-      <x:c r="C33" s="11" t="n">
+      <x:c r="D33" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D33" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E33" s="10" t="str">
+      <x:c r="E33" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F33" s="10" t="str">
         <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="F33" s="10" t="str">
+      <x:c r="G33" s="10" t="str">
         <x:v>星梦好剧</x:v>
       </x:c>
-      <x:c r="G33" s="10" t="str">
+      <x:c r="H33" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
       </x:c>
-      <x:c r="H33" s="11" t="n">
+      <x:c r="I33" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4540,25 +4640,28 @@
       <x:c r="A34" s="11" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B34" s="10" t="str">
+      <x:c r="B34" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
         <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
       </x:c>
-      <x:c r="C34" s="11" t="n">
+      <x:c r="D34" s="11" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D34" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E34" s="10" t="str">
+      <x:c r="E34" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F34" s="10" t="str">
         <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
-      <x:c r="F34" s="10" t="str">
+      <x:c r="G34" s="10" t="str">
         <x:v>陈柯</x:v>
       </x:c>
-      <x:c r="G34" s="10" t="str">
+      <x:c r="H34" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H34" s="11" t="n">
+      <x:c r="I34" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4566,25 +4669,28 @@
       <x:c r="A35" s="11" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B35" s="10" t="str">
+      <x:c r="B35" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
         <x:v>藏在婚姻里的谎言</x:v>
       </x:c>
-      <x:c r="C35" s="11" t="n">
+      <x:c r="D35" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D35" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="E35" s="10" t="str">
+      <x:c r="E35" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F35" s="10" t="str">
         <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
-      <x:c r="F35" s="10" t="str">
+      <x:c r="G35" s="10" t="str">
         <x:v>九鲤动漫</x:v>
       </x:c>
-      <x:c r="G35" s="10" t="str">
+      <x:c r="H35" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
       </x:c>
-      <x:c r="H35" s="11" t="n">
+      <x:c r="I35" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4592,26 +4698,522 @@
       <x:c r="A36" s="11" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B36" s="10" t="str">
+      <x:c r="B36" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C36" s="10" t="str">
         <x:v>让你守边塞，你用汉堡养兵？第二季江南篇</x:v>
       </x:c>
-      <x:c r="C36" s="11" t="n">
+      <x:c r="D36" s="11" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D36" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="E36" s="10" t="str">
+      <x:c r="E36" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F36" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="F36" s="10" t="str">
+      <x:c r="G36" s="10" t="str">
         <x:v>浮绘剧场</x:v>
       </x:c>
-      <x:c r="G36" s="10" t="str">
+      <x:c r="H36" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="H36" s="11" t="n">
+      <x:c r="I36" s="11" t="n">
         <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C37" s="10" t="str">
+        <x:v>撞破婚约骗局</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F37" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G37" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H37" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I37" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C38" s="10" t="str">
+        <x:v>下山归来，影后向我求婚第二季</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F38" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G38" s="10" t="str">
+        <x:v>漫文</x:v>
+      </x:c>
+      <x:c r="H38" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；79集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I38" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C39" s="10" t="str">
+        <x:v>免费荠菜见人心</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F39" s="10" t="str">
+        <x:v>美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G39" s="10" t="str">
+        <x:v>闪闪动漫社</x:v>
+      </x:c>
+      <x:c r="H39" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「闪闪动漫社」</x:v>
+      </x:c>
+      <x:c r="I39" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C40" s="10" t="str">
+        <x:v>毁我清白，我反手指认皇帝</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F40" s="10" t="str">
+        <x:v>古装宫廷 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G40" s="10" t="str">
+        <x:v>卿读剧场</x:v>
+      </x:c>
+      <x:c r="H40" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「卿读剧场」</x:v>
+      </x:c>
+      <x:c r="I40" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C41" s="10" t="str">
+        <x:v>丁克二十载，我摊牌了</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F41" s="10" t="str">
+        <x:v>都市职场 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G41" s="10" t="str">
+        <x:v>次元佳思剧场</x:v>
+      </x:c>
+      <x:c r="H41" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「次元佳思剧场」</x:v>
+      </x:c>
+      <x:c r="I41" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="str">
+        <x:v>万界杂货铺：我靠倒卖物资赢麻了</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F42" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G42" s="10" t="str">
+        <x:v>青禾短剧</x:v>
+      </x:c>
+      <x:c r="H42" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；发布账号「青禾短剧」</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>双生麒麟，神君爹爹傲娇娘</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F43" s="10" t="str">
+        <x:v>家庭伦理 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G43" s="10" t="str">
+        <x:v>新美漫剧场</x:v>
+      </x:c>
+      <x:c r="H43" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能）；发布账号「新美漫剧场」</x:v>
+      </x:c>
+      <x:c r="I43" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C44" s="10" t="str">
+        <x:v>捐躯失踪十八年，归来女儿去世了</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F44" s="10" t="str">
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G44" s="10" t="str">
+        <x:v>凛冬短剧</x:v>
+      </x:c>
+      <x:c r="H44" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「凛冬短剧」</x:v>
+      </x:c>
+      <x:c r="I44" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="str">
+        <x:v>觉醒神级听劝系统，我成专听建议的校长</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F45" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G45" s="10" t="str">
+        <x:v>红豆剧场</x:v>
+      </x:c>
+      <x:c r="H45" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；80集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「红豆剧场」</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>退婚后我成了女帝</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F46" s="10" t="str">
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G46" s="10" t="str">
+        <x:v>次元心动剧场</x:v>
+      </x:c>
+      <x:c r="H46" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；55集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；发布账号「次元心动剧场」</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C47" s="10" t="str">
+        <x:v>1980：我重生后护她余生</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F47" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G47" s="10" t="str">
+        <x:v>阳光微剧</x:v>
+      </x:c>
+      <x:c r="H47" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材待验证；发布账号「阳光微剧」</x:v>
+      </x:c>
+      <x:c r="I47" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B48" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C48" s="10" t="str">
+        <x:v>一担米嫁哑郎，他开口那天我哭了</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F48" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G48" s="10" t="str">
+        <x:v>漫恋小剧场</x:v>
+      </x:c>
+      <x:c r="H48" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；45集，中等长度；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「漫恋小剧场」</x:v>
+      </x:c>
+      <x:c r="I48" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B49" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C49" s="10" t="str">
+        <x:v>乖囡寻爹记</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F49" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G49" s="10" t="str">
+        <x:v>漫语剧场</x:v>
+      </x:c>
+      <x:c r="H49" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；46集，中等长度；题材契合爆款主线（家庭伦理）；发布账号「漫语剧场」</x:v>
+      </x:c>
+      <x:c r="I49" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B50" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C50" s="10" t="str">
+        <x:v>山谷灵珠录第三季</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F50" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G50" s="10" t="str">
+        <x:v>漫文传媒</x:v>
+      </x:c>
+      <x:c r="H50" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；69集长剧集，符合起量主力区间；题材待验证；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I50" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B51" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C51" s="10" t="str">
+        <x:v>大促当天，我预言了一场爆炸</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F51" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G51" s="10" t="str">
+        <x:v>月光短剧</x:v>
+      </x:c>
+      <x:c r="H51" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材待验证；发布账号「月光短剧」</x:v>
+      </x:c>
+      <x:c r="I51" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B52" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C52" s="10" t="str">
+        <x:v>盐弈</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F52" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G52" s="10" t="str">
+        <x:v>凛冬短剧</x:v>
+      </x:c>
+      <x:c r="H52" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材待验证；发布账号「凛冬短剧」</x:v>
+      </x:c>
+      <x:c r="I52" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B53" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C53" s="10" t="str">
+        <x:v>九世相寻</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="F53" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G53" s="10" t="str">
+        <x:v>恐龙粑粑小百科</x:v>
+      </x:c>
+      <x:c r="H53" s="10" t="str">
+        <x:v>83集长剧集，符合起量主力区间；题材待验证；发布账号「恐龙粑粑小百科」</x:v>
+      </x:c>
+      <x:c r="I53" s="11" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R33a8e59118684aa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R7b78767691404af3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R66a8758a82af444c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Re2118d41c5a34391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R43df41bccec84b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R947e49fda88f4ff3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R101504ce5c5a4f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Red9f3820c4ab4deb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rdea2ff9143594056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R213265113bc143f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -351,7 +351,7 @@
         <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>375</x:v>
@@ -364,7 +364,7 @@
       </x:c>
       <x:c r="G2" s="11" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -375,7 +375,7 @@
         <x:v>占院风波</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
         <x:v>66</x:v>
@@ -390,7 +390,7 @@
         <x:v>4289</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -401,7 +401,7 @@
         <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
         <x:v>66</x:v>
@@ -414,7 +414,7 @@
       </x:c>
       <x:c r="G4" s="11" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -425,7 +425,7 @@
         <x:v>灶下煤之自由篇</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>82</x:v>
@@ -438,7 +438,7 @@
       </x:c>
       <x:c r="G5" s="11" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -524,23 +524,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E9" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str"/>
       <x:c r="H9" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -548,23 +548,23 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>重回八零，赶山狩猎养妻女</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str"/>
       <x:c r="H10" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -596,25 +596,23 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>垃圾桶里的寻人启事</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="n">
-        <x:v>4442</x:v>
-      </x:c>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str"/>
       <x:c r="H12" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -622,23 +620,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>山王传奇</x:v>
+        <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="str"/>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="n">
+        <x:v>4442</x:v>
+      </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -646,23 +646,23 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>山王传奇</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E14" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -673,7 +673,7 @@
         <x:v>谁说纨绔不能当状元</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>788</x:v>
@@ -688,7 +688,7 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28</x:v>
+        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -696,23 +696,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>重生归来，四小姐她不装了</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="str"/>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="n">
+        <x:v>371</x:v>
+      </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -720,25 +722,23 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E17" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -746,23 +746,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G18" s="11" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -770,25 +772,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>重生归来，四小姐她不装了</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E19" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>371</x:v>
+        <x:v>1834</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -796,23 +798,23 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>孤城照山河第一季</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E20" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str"/>
       <x:c r="H20" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-22</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -820,25 +822,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E21" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="n">
-        <x:v>1834</x:v>
-      </x:c>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="str"/>
       <x:c r="H21" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -846,23 +846,23 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>我将恩人一家捡回村</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E22" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -870,23 +870,23 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>孤城照山河第一季</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>185</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E23" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -894,23 +894,23 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>我将恩人一家捡回村</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E24" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-22</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -918,23 +918,23 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23</x:v>
+        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -942,23 +942,23 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>商场收回档口我成了全城的供应商</x:v>
+        <x:v>半梦半醒半清欢</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E26" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1016,25 +1016,25 @@
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="10" t="str">
-        <x:v>糯糯下山，师兄们都慌了</x:v>
+        <x:v>鉴宝天瞳</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>青椒剪辑</x:v>
+        <x:v>知我动画</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1043,26 +1043,22 @@
       </x:c>
       <x:c r="B3" s="11"/>
       <x:c r="C3" s="10" t="str">
-        <x:v>玄门归来：十年婚约</x:v>
+        <x:v>暮年大帝，再战诸天</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="n">
-        <x:v>190</x:v>
-      </x:c>
+      <x:c r="F3" s="11" t="str"/>
       <x:c r="G3" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="I3" s="10" t="str">
-        <x:v>大公鸡剧场</x:v>
-      </x:c>
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -1070,26 +1066,22 @@
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="10" t="str">
-        <x:v>冒充我的网恋骗局</x:v>
+        <x:v>满院亲戚全是上古大妖第二季</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="n">
-        <x:v>46</x:v>
-      </x:c>
+      <x:c r="F4" s="11" t="str"/>
       <x:c r="G4" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
-      </x:c>
-      <x:c r="I4" s="10" t="str">
-        <x:v>光影动画</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -1097,25 +1089,25 @@
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>换师尊后她转修无情道，全宗门跪了</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>独影剧场</x:v>
+        <x:v>笙笙动画</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1124,25 +1116,25 @@
       </x:c>
       <x:c r="B6" s="11"/>
       <x:c r="C6" s="10" t="str">
-        <x:v>山沟里救下一条白龙</x:v>
+        <x:v>指尖的童话</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>小何故事会</x:v>
+        <x:v>宅男剧社</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1151,26 +1143,22 @@
       </x:c>
       <x:c r="B7" s="11"/>
       <x:c r="C7" s="10" t="str">
-        <x:v>藏拙十八年，千金归来掀风云</x:v>
+        <x:v>你管这叫灾星首富家都旺翻了！</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
+      <x:c r="F7" s="11" t="str"/>
       <x:c r="G7" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="I7" s="10" t="str">
-        <x:v>魔力大剧场</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -1178,16 +1166,16 @@
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="10" t="str">
-        <x:v>谁说纨绔不能当状元第二季</x:v>
+        <x:v>特工王妃扛着王爷去流放</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>316</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -1196,7 +1184,7 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>小酒动画</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1205,25 +1193,25 @@
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="10" t="str">
-        <x:v>错付奔向归途</x:v>
+        <x:v>蹭饭一年，她们终于吃不起了</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>小罗剧场</x:v>
+        <x:v>云景动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1232,26 +1220,22 @@
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="10" t="str">
-        <x:v>八零悍妇：女汉子逆袭记</x:v>
+        <x:v>孤城照山河第二季</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="n">
-        <x:v>138</x:v>
-      </x:c>
+      <x:c r="F10" s="11" t="str"/>
       <x:c r="G10" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>年代怀旧 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="I10" s="10" t="str">
-        <x:v>大宝动画</x:v>
-      </x:c>
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -1259,25 +1243,25 @@
       </x:c>
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="10" t="str">
-        <x:v>重回台风夜，我让她悔不当初</x:v>
+        <x:v>规章冷厨心</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>小白动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1286,25 +1270,25 @@
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="10" t="str">
-        <x:v>婚后计划</x:v>
+        <x:v>丈母娘百万招婿，我的冰山老婆</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>草莓漫漫</x:v>
+        <x:v>星界Ai</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1313,25 +1297,25 @@
       </x:c>
       <x:c r="B13" s="11"/>
       <x:c r="C13" s="10" t="str">
-        <x:v>萌宝神助攻，前妻不好哄</x:v>
+        <x:v>无冕之根</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>萌宝治愈 / 婚姻情感 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>拓拓逆袭剧场</x:v>
+        <x:v>影留</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1340,25 +1324,25 @@
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="10" t="str">
-        <x:v>我只想找死，却被奉为九州战神了</x:v>
+        <x:v>坝上少年</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>852</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>萱萱短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1367,25 +1351,25 @@
       </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="10" t="str">
-        <x:v>听泉打捞王</x:v>
+        <x:v>萌宝幼崽大作战</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>147</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>泡姐漫屋</x:v>
+        <x:v>南风知意</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1394,25 +1378,25 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="10" t="str">
-        <x:v>我在夜市摆摊成王</x:v>
+        <x:v>穿越东北，我靠打猎养活三个外甥女</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>都市职场 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>张小曼</x:v>
+        <x:v>飞行轻舟剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1421,25 +1405,25 @@
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="10" t="str">
-        <x:v>实习教出金牌班，家长要换班主任</x:v>
+        <x:v>台风过境时</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1448,25 +1432,25 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="10" t="str">
-        <x:v>无限进化：从矿泉水开始称霸末日</x:v>
+        <x:v>黑塔：从超忆症开始成神</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
-        <x:v>奇树剧场</x:v>
+        <x:v>菠萝漫</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1475,25 +1459,25 @@
       </x:c>
       <x:c r="B19" s="11"/>
       <x:c r="C19" s="10" t="str">
-        <x:v>被房车堵住的生死路</x:v>
+        <x:v>流放厨娘，我靠美食绝地翻盘！</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>二妞.影视</x:v>
+        <x:v>延晨的动漫窝</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1502,25 +1486,25 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="10" t="str">
-        <x:v>我的保镖身份不简单</x:v>
+        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 婚姻情感</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>伯爵剧场</x:v>
+        <x:v>神文视界</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1529,25 +1513,25 @@
       </x:c>
       <x:c r="B21" s="11"/>
       <x:c r="C21" s="10" t="str">
-        <x:v>暴雨那天，全村看清了谁的砖是真的</x:v>
+        <x:v>杨巧替嫁残疾英雄，婆家宠我青云志</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
-        <x:v>星梦短剧</x:v>
+        <x:v>游世剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1556,26 +1540,22 @@
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="10" t="str">
-        <x:v>退婚那天，他们嫌弃我爸收废品</x:v>
+        <x:v>福运：逃荒种田农家团宠小奶包</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="n">
-        <x:v>79</x:v>
-      </x:c>
+      <x:c r="F22" s="11" t="str"/>
       <x:c r="G22" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="I22" s="10" t="str">
-        <x:v>云起剧场</x:v>
-      </x:c>
+        <x:v>种田囤货 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -1583,25 +1563,25 @@
       </x:c>
       <x:c r="B23" s="11"/>
       <x:c r="C23" s="10" t="str">
-        <x:v>签完离婚协议，我摊牌了</x:v>
+        <x:v>饭局生变，我偏要把账算清</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感 / 逆袭打脸</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>小小动漫🔥</x:v>
+        <x:v>不兜</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1610,25 +1590,25 @@
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="10" t="str">
-        <x:v>风过牧野逢晚晴</x:v>
+        <x:v>青山不忘</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H24" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>杭鹿二姐爱看剧</x:v>
+        <x:v>漫漫天星</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1637,25 +1617,25 @@
       </x:c>
       <x:c r="B25" s="11"/>
       <x:c r="C25" s="10" t="str">
-        <x:v>回来那天，我成了钟点工</x:v>
+        <x:v>怪力少女和她的病弱娇夫</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
-        <x:v>熊猫热剧</x:v>
+        <x:v>剧赞影视</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1664,25 +1644,25 @@
       </x:c>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="10" t="str">
-        <x:v>度淼入年</x:v>
+        <x:v>错爱沉霜</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>153</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>安夏剧场</x:v>
+        <x:v>灰鲸剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1691,25 +1671,25 @@
       </x:c>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="10" t="str">
-        <x:v>唯有暖阳照寒夜</x:v>
+        <x:v>替嫁残疾英雄婆家宠我青云志</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>苞米花剧场</x:v>
+        <x:v>觅影剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1718,25 +1698,25 @@
       </x:c>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="10" t="str">
-        <x:v>卷王师妹不讲武德</x:v>
+        <x:v>重回八零，赶山狩猎养妻女日记</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>光影</x:v>
+        <x:v>小迷动画</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1745,25 +1725,25 @@
       </x:c>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="10" t="str">
-        <x:v>云端旧梦：分手四年傅机长失控了</x:v>
+        <x:v>让我开早餐店，我下午才营业</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H29" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>小小动画</x:v>
+        <x:v>天圆漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1772,26 +1752,22 @@
       </x:c>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="10" t="str">
-        <x:v>开局拜仙尊为师杂灵根小师妹气运超强的</x:v>
+        <x:v>一村人养一个神第二季</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="n">
-        <x:v>150</x:v>
-      </x:c>
+      <x:c r="F30" s="11" t="str"/>
       <x:c r="G30" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
-      </x:c>
-      <x:c r="I30" s="10" t="str">
-        <x:v>垂钓剧场</x:v>
-      </x:c>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="I30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
@@ -1799,25 +1775,25 @@
       </x:c>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="10" t="str">
-        <x:v>住三个月，住成了婚房</x:v>
+        <x:v>一百块的安稳</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>小 淇</x:v>
+        <x:v>琥珀漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1826,25 +1802,25 @@
       </x:c>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="10" t="str">
-        <x:v>一瓶水，让我看清亲生女儿</x:v>
+        <x:v>分家那天，我要了一间破屋</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>大表妹吖</x:v>
+        <x:v>卜卜漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1853,25 +1829,25 @@
       </x:c>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="10" t="str">
-        <x:v>重生六七：赶山狩猎养全家</x:v>
+        <x:v>断腿父王别慌，福星多多来啦！</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
-        <x:v>铁柱动画</x:v>
+        <x:v>星界秘漫</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1880,25 +1856,25 @@
       </x:c>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="10" t="str">
-        <x:v>扮废三年，年会当天我不演了</x:v>
+        <x:v>拂衣震九州</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
-        <x:v>至尊爽剧社</x:v>
+        <x:v>猛犸象短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1907,25 +1883,25 @@
       </x:c>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="10" t="str">
-        <x:v>我能在海里呼吸</x:v>
+        <x:v>神医奶团：妙手扶爹</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
-        <x:v>墨杨</x:v>
+        <x:v>小良短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1934,25 +1910,25 @@
       </x:c>
       <x:c r="B36" s="11"/>
       <x:c r="C36" s="10" t="str">
-        <x:v>神医奶团：妙手扶爹</x:v>
+        <x:v>山下是绝路，山上是生门</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>家庭伦理 / 萌宝治愈 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>小良短剧</x:v>
+        <x:v>独影剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1961,25 +1937,25 @@
       </x:c>
       <x:c r="B37" s="11"/>
       <x:c r="C37" s="10" t="str">
-        <x:v>红烛错缘，另寻良人</x:v>
+        <x:v>糯糯下山，师兄们都慌了</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H37" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>忆梦剧场</x:v>
+        <x:v>青椒剪辑</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1988,25 +1964,25 @@
       </x:c>
       <x:c r="B38" s="11"/>
       <x:c r="C38" s="10" t="str">
-        <x:v>不向恶意妥协</x:v>
+        <x:v>心肝颤：双宝助攻复婚记</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H38" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
-        <x:v>小小动画</x:v>
+        <x:v>西施玩家</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2015,25 +1991,25 @@
       </x:c>
       <x:c r="B39" s="11"/>
       <x:c r="C39" s="10" t="str">
-        <x:v>垃圾桶里捡来的状元郎</x:v>
+        <x:v>风过牧野逢晚晴</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G39" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>杭鹿二姐爱看剧</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2042,25 +2018,25 @@
       </x:c>
       <x:c r="B40" s="11"/>
       <x:c r="C40" s="10" t="str">
-        <x:v>小福星驾到，通通闪开第一季</x:v>
+        <x:v>山沟里救下一条白龙</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>140</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G40" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
-        <x:v>漫有戏剧场</x:v>
+        <x:v>小何故事会</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2069,7 +2045,7 @@
       </x:c>
       <x:c r="B41" s="11"/>
       <x:c r="C41" s="10" t="str">
-        <x:v>分家那天，我要了一间破屋</x:v>
+        <x:v>晏晏总角时时安</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
         <x:v>2026-08-27</x:v>
@@ -2078,16 +2054,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G41" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str">
-        <x:v>卜卜漫剧</x:v>
+        <x:v>寻光推剧</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2096,16 +2072,16 @@
       </x:c>
       <x:c r="B42" s="11"/>
       <x:c r="C42" s="10" t="str">
-        <x:v>重回八一从打猎开始发家第二季</x:v>
+        <x:v>八零悍妇：女汉子逆袭记</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>128</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G42" s="10" t="str">
         <x:v>仿真人</x:v>
@@ -2114,7 +2090,7 @@
         <x:v>年代怀旧 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str">
-        <x:v>水滴文化</x:v>
+        <x:v>大宝动画</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2123,16 +2099,16 @@
       </x:c>
       <x:c r="B43" s="11"/>
       <x:c r="C43" s="10" t="str">
-        <x:v>错岸</x:v>
+        <x:v>听泉打捞王</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G43" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -2141,7 +2117,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str">
-        <x:v>灰鲸剧场</x:v>
+        <x:v>泡姐漫屋</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2150,25 +2126,25 @@
       </x:c>
       <x:c r="B44" s="11"/>
       <x:c r="C44" s="10" t="str">
-        <x:v>渠水照见人心善恶</x:v>
+        <x:v>实习教出金牌班，家长要换班主任</x:v>
       </x:c>
       <x:c r="D44" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G44" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H44" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str">
-        <x:v>二三ONE.1</x:v>
+        <x:v>长风剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2177,25 +2153,25 @@
       </x:c>
       <x:c r="B45" s="11"/>
       <x:c r="C45" s="10" t="str">
-        <x:v>我用骨髓换了个妹妹</x:v>
+        <x:v>谁说纨绔不能当状元第二季</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G45" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H45" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -2204,25 +2180,25 @@
       </x:c>
       <x:c r="B46" s="11"/>
       <x:c r="C46" s="10" t="str">
-        <x:v>床底下的人</x:v>
+        <x:v>我只想找死，却被奉为九州战神了</x:v>
       </x:c>
       <x:c r="D46" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="G46" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H46" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I46" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -2231,25 +2207,25 @@
       </x:c>
       <x:c r="B47" s="11"/>
       <x:c r="C47" s="10" t="str">
-        <x:v>锦绣芳华：乔兰书重生记</x:v>
+        <x:v>被房车堵住的生死路</x:v>
       </x:c>
       <x:c r="D47" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G47" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H47" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str">
-        <x:v>别离剧场</x:v>
+        <x:v>二妞.影视</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -2258,25 +2234,25 @@
       </x:c>
       <x:c r="B48" s="11"/>
       <x:c r="C48" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>开局拜仙尊为师杂灵根小师妹气运超强的</x:v>
       </x:c>
       <x:c r="D48" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>116</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G48" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H48" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str">
-        <x:v>猛犸象短剧</x:v>
+        <x:v>垂钓剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -2285,25 +2261,106 @@
       </x:c>
       <x:c r="B49" s="11"/>
       <x:c r="C49" s="10" t="str">
-        <x:v>断腿父王别慌，福星多多来啦！</x:v>
+        <x:v>玄门归来：十年婚约</x:v>
       </x:c>
       <x:c r="D49" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G49" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="H49" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="I49" s="10" t="str">
+        <x:v>大公鸡剧场</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B50" s="11"/>
+      <x:c r="C50" s="10" t="str">
+        <x:v>重回台风夜，我让她悔不当初</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G50" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H49" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
-      </x:c>
-      <x:c r="I49" s="10" t="str">
-        <x:v>星界秘漫</x:v>
+      <x:c r="H50" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="I50" s="10" t="str">
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B51" s="11"/>
+      <x:c r="C51" s="10" t="str">
+        <x:v>我在夜市摆摊成王</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G51" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H51" s="10" t="str">
+        <x:v>都市职场 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="I51" s="10" t="str">
+        <x:v>张小曼</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B52" s="11"/>
+      <x:c r="C52" s="10" t="str">
+        <x:v>别惹真千金，她手遮半边天</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="str">
+        <x:v>2026-08-28</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G52" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H52" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I52" s="10" t="str">
+        <x:v>剧鲸小剧场</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2381,7 +2438,7 @@
         <x:v>7514</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2410,7 +2467,7 @@
         <x:v>852</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2439,7 +2496,7 @@
         <x:v>8368</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2447,7 +2504,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>重回八零，赶山狩猎养妻女</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
         <x:v>7</x:v>
@@ -2456,17 +2513,17 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str"/>
       <x:c r="I5" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计14次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2493,7 +2550,7 @@
       </x:c>
       <x:c r="H6" s="11" t="str"/>
       <x:c r="I6" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2522,7 +2579,7 @@
         <x:v>4442</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2530,7 +2587,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>7</x:v>
@@ -2539,17 +2596,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="str"/>
+      <x:c r="H8" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2557,26 +2616,26 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2584,7 +2643,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>孤城照山河第一季</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
         <x:v>7</x:v>
@@ -2593,17 +2652,17 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>185</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str"/>
       <x:c r="I10" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计10次，起量能力已被验证；185集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2611,26 +2670,26 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>云岭藏金，真心为聘</x:v>
+        <x:v>悍妻替嫁，从前说</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜7次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2638,26 +2697,26 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>魔力情谊之我一个人来的</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计11次，起量能力已被验证；56集长剧集；题材契合爆款主线（种田囤货 / 美食治愈 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2665,26 +2724,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>爷爷不请七遍不动筷</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="n">
+        <x:v>490</x:v>
+      </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计9次，起量能力已被验证；仿真人制作；50集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2692,26 +2753,26 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>云岭藏金，真心为聘</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计12次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2719,26 +2780,26 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>分家只给破枪，我听兽语富全屯</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计11次，起量能力已被验证；56集长剧集；题材契合爆款主线（种田囤货 / 美食治愈 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2746,26 +2807,26 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>魔力情谊之我一个人来的</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计10次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2773,26 +2834,26 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>悍妻替嫁，从前说</x:v>
+        <x:v>三百块的信任，九十万的真相</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str"/>
       <x:c r="I17" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2800,26 +2861,26 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
+        <x:v>九二年，他塞给我五百块</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2827,26 +2888,26 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>三百块的信任，九十万的真相</x:v>
+        <x:v>大力幼崽到处捡爹</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2854,26 +2915,26 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>我哥四个全是宠妹狂魔</x:v>
+        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；100集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2881,26 +2942,26 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>大力幼崽到处捡爹</x:v>
+        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2908,26 +2969,26 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>馋哭！陆总该吃饭了</x:v>
+        <x:v>这个姨娘不一般</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；98集长剧集；题材契合爆款主线（美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2935,7 +2996,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>分家只给破枪，我听兽语富全屯</x:v>
+        <x:v>重回千禧我靠赶海养活家人</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>5</x:v>
@@ -2944,17 +3005,17 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；183集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2962,26 +3023,26 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>这个姨娘不一般</x:v>
+        <x:v>八零之老妈在厂长家当后妈</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2989,26 +3050,26 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>重回千禧我靠赶海养活家人</x:v>
+        <x:v>我哥四个全是宠妹狂魔</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>183</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计8次，起量能力已被验证；183集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；100集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3016,26 +3077,26 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>九二年，他塞给我五百块</x:v>
+        <x:v>199的排场，48万的账</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3043,7 +3104,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>199的排场，48万的账</x:v>
+        <x:v>傻女重生记，睁眼后盖房发家</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>5</x:v>
@@ -3052,17 +3113,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3070,7 +3131,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>疯娘翻身，穿越宠崽</x:v>
+        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>5</x:v>
@@ -3079,17 +3140,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；200集长剧集；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3097,7 +3158,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
+        <x:v>馋哭！陆总该吃饭了</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>5</x:v>
@@ -3106,17 +3167,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>119</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；98集长剧集；题材契合爆款主线（美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3124,26 +3185,26 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>被总经理针对后，我只按菜单做菜</x:v>
+        <x:v>八零媳妇富农家</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计5次，起量能力已被验证；105集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3151,7 +3212,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>一塘清水鉴人心</x:v>
+        <x:v>寒庭有犬鸣</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
         <x:v>5</x:v>
@@ -3160,17 +3221,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计5次，起量能力已被验证；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3178,7 +3239,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>寒庭有犬鸣</x:v>
+        <x:v>青云入世这个神医会功夫</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
         <x:v>5</x:v>
@@ -3187,17 +3248,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计5次，起量能力已被验证；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；146集长剧集；题材契合爆款主线（婚姻情感 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3205,26 +3266,26 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>青云入世这个神医会功夫</x:v>
+        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>146</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；146集长剧集；题材契合爆款主线（婚姻情感 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3232,26 +3293,26 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
+        <x:v>守着灶台，守住本心</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str"/>
       <x:c r="I34" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；52集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3259,26 +3320,26 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>八零之老妈在厂长家当后妈</x:v>
+        <x:v>傅总，您的三岁小债主上门了</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>156</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str"/>
       <x:c r="I35" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；97集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3286,26 +3347,26 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>守着灶台，守住本心</x:v>
+        <x:v>撞大运后我在县城买了个院</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str"/>
       <x:c r="I36" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；52集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；120集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3313,7 +3374,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>傅总，您的三岁小债主上门了</x:v>
+        <x:v>疯娘翻身，穿越宠崽</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>4</x:v>
@@ -3322,17 +3383,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E37" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；97集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；200集长剧集；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3340,7 +3401,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>傻女重生记，睁眼后盖房发家</x:v>
+        <x:v>离婚那天我多了个董事长妈妈</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>4</x:v>
@@ -3349,17 +3410,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str"/>
       <x:c r="I38" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3367,26 +3428,26 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>八零媳妇富农家</x:v>
+        <x:v>被总经理针对后，我只按菜单做菜</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>105</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G39" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str"/>
       <x:c r="I39" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；105集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3394,7 +3455,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>半熟沦陷</x:v>
+        <x:v>一塘清水鉴人心</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>4</x:v>
@@ -3403,17 +3464,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-15</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G40" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str"/>
       <x:c r="I40" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3421,7 +3482,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>小火归山</x:v>
+        <x:v>我家成了别人的婚房</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>4</x:v>
@@ -3430,17 +3491,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G41" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str"/>
       <x:c r="I41" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；71集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3448,7 +3509,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>恶妇翻身一锅烟火养全家第一季</x:v>
+        <x:v>我的订婚宴上，闯进来两个要饭的</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>4</x:v>
@@ -3457,17 +3518,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>174</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G42" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H42" s="11" t="str"/>
       <x:c r="I42" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；174集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3475,7 +3536,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>我家成了别人的婚房</x:v>
+        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>4</x:v>
@@ -3484,17 +3545,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E43" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G43" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H43" s="11" t="str"/>
       <x:c r="I43" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；71集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -3502,26 +3563,26 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>我的订婚宴上，闯进来两个要饭的</x:v>
+        <x:v>八零：苏念荷的故事</x:v>
       </x:c>
       <x:c r="C44" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E44" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G44" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H44" s="11" t="str"/>
       <x:c r="I44" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；123集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -3529,26 +3590,26 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>青礁潮起，鲛人归</x:v>
+        <x:v>情起屋檐下</x:v>
       </x:c>
       <x:c r="C45" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G45" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H45" s="11" t="str"/>
       <x:c r="I45" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计5次，起量能力已被验证；51集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；66集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -3556,7 +3617,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>别人养鱼，我养水</x:v>
+        <x:v>我的车间不养闲人</x:v>
       </x:c>
       <x:c r="C46" s="11" t="n">
         <x:v>4</x:v>
@@ -3565,17 +3626,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E46" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G46" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H46" s="11" t="str"/>
       <x:c r="I46" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；62集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3583,7 +3644,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>我的车间不养闲人</x:v>
+        <x:v>携手八零，与君同赴山河</x:v>
       </x:c>
       <x:c r="C47" s="11" t="n">
         <x:v>4</x:v>
@@ -3595,14 +3656,14 @@
         <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G47" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H47" s="11" t="str"/>
       <x:c r="I47" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；124集长剧集；题材契合爆款主线（年代怀旧 / 古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -3610,7 +3671,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>携手八零，与君同赴山河</x:v>
+        <x:v>灵泉姑娘，分家后富甲一方第一季</x:v>
       </x:c>
       <x:c r="C48" s="11" t="n">
         <x:v>4</x:v>
@@ -3619,17 +3680,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E48" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-15</x:v>
       </x:c>
       <x:c r="F48" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G48" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H48" s="11" t="str"/>
       <x:c r="I48" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；124集长剧集；题材契合爆款主线（年代怀旧 / 古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；152集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -3637,7 +3698,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>灵泉姑娘，分家后富甲一方第一季</x:v>
+        <x:v>老婆每月给别人一万五，离婚时她后悔了</x:v>
       </x:c>
       <x:c r="C49" s="11" t="n">
         <x:v>4</x:v>
@@ -3646,17 +3707,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E49" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
-        <x:v>152</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G49" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H49" s="11" t="str"/>
       <x:c r="I49" s="10" t="str">
-        <x:v>8-11~8-17两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；152集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；113集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5251,10 +5312,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>324</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>43.1%</x:v>
+        <x:v>42.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5262,10 +5323,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>229</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>30.5%</x:v>
+        <x:v>30.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5273,7 +5334,7 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>199</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>26.5%</x:v>
@@ -5300,7 +5361,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>12%</x:v>
@@ -5311,10 +5372,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>337</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>45%</x:v>
+        <x:v>44.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5322,7 +5383,7 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>11.6%</x:v>
@@ -5333,10 +5394,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>234</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>31.2%</x:v>
+        <x:v>31.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -5360,10 +5421,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>289</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>38.4%</x:v>
+        <x:v>38.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -5371,10 +5432,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>142</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>18.9%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -5382,10 +5443,10 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>11.3%</x:v>
+        <x:v>11.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5393,10 +5454,10 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>10.1%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -5404,7 +5465,7 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
         <x:v>9.0%</x:v>
@@ -5415,10 +5476,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.4%</x:v>
+        <x:v>8.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5426,10 +5487,10 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>7.2%</x:v>
+        <x:v>7.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5437,10 +5498,10 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>6.4%</x:v>
+        <x:v>6.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5448,10 +5509,10 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>5.5%</x:v>
+        <x:v>5.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -5459,10 +5520,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>5.2%</x:v>
+        <x:v>5.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -5483,7 +5544,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
         <x:v>4</x:v>
@@ -5497,10 +5558,10 @@
         <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -5508,10 +5569,10 @@
         <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -5519,169 +5580,169 @@
         <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>1.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>2.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>1.6%</x:v>
+        <x:v>2.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>2.4%</x:v>
+        <x:v>3.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>4.3%</x:v>
+        <x:v>5.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>6.3%</x:v>
+        <x:v>4.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>4.5%</x:v>
+        <x:v>7.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>8.2%</x:v>
+        <x:v>18.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>17.3%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="10" t="str">
-        <x:v>上榜1次</x:v>
-      </x:c>
-      <x:c r="B44" s="11" t="n">
-        <x:v>388</x:v>
-      </x:c>
-      <x:c r="C44" s="11" t="str">
-        <x:v>51.6%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="22" customHeight="1">
-      <x:c r="A46" s="14" t="str">
+        <x:v>51.1%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="24" customHeight="1">
-      <x:c r="A47" s="5" t="str">
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B47" t="str">
+      <x:c r="B46" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C47" t="str">
+      <x:c r="C46" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="10" t="str">
+        <x:v>CP自营</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="n">
+        <x:v>777</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>98.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>CP自营</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>742</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>98.7%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -5692,59 +5753,57 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>番茄原创</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>0.4%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="10" t="str">
-        <x:v>番茄原创</x:v>
-      </x:c>
-      <x:c r="B51" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C51" s="11" t="str">
         <x:v>0.3%</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="22" customHeight="1">
-      <x:c r="A53" s="14" t="str">
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="14" t="str">
         <x:v>发布抖音号TOP15</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="24" customHeight="1">
-      <x:c r="A54" s="5" t="str">
+    <x:row r="53" ht="24" customHeight="1">
+      <x:c r="A53" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B54" t="str">
+      <x:c r="B53" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C54" t="str">
+      <x:c r="C53" t="str">
         <x:v>占比</x:v>
       </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="B54" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C54" s="11" t="str"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B55" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C55" s="11" t="str"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
         <x:v>5</x:v>
@@ -5753,10 +5812,10 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str"/>
     </x:row>
@@ -5771,7 +5830,7 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>不兜</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
         <x:v>4</x:v>
@@ -5852,91 +5911,93 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str"/>
     </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
-      </x:c>
-      <x:c r="B69" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C69" s="11" t="str"/>
-    </x:row>
-    <x:row r="71" ht="22" customHeight="1">
-      <x:c r="A71" s="14" t="str">
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="24" customHeight="1">
-      <x:c r="A72" s="5" t="str">
+    <x:row r="71" ht="24" customHeight="1">
+      <x:c r="A71" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B72" t="str">
+      <x:c r="B71" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C72" t="str">
+      <x:c r="C71" t="str">
         <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="10" t="str">
+        <x:v>婚姻/情感</x:v>
+      </x:c>
+      <x:c r="B72" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C72" s="11" t="str">
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B73" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
-        <x:v>19.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>6.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -5952,23 +6013,12 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
-        <x:v>6.0%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="B80" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C80" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -5978,9 +6028,9 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A46:C46"/>
-    <x:mergeCell ref="A53:C53"/>
-    <x:mergeCell ref="A71:C71"/>
+    <x:mergeCell ref="A45:C45"/>
+    <x:mergeCell ref="A52:C52"/>
+    <x:mergeCell ref="A70:C70"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R947e49fda88f4ff3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R101504ce5c5a4f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Red9f3820c4ab4deb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rdea2ff9143594056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R213265113bc143f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R096e8703a99f49da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R7d19ce326cb44128"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rbdbb5a389aaf4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="R45c2a698e9ce40e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R0e5ff133878d4ab0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -351,7 +351,7 @@
         <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>375</x:v>
@@ -364,7 +364,7 @@
       </x:c>
       <x:c r="G2" s="11" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -375,7 +375,7 @@
         <x:v>占院风波</x:v>
       </x:c>
       <x:c r="C3" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
         <x:v>66</x:v>
@@ -390,7 +390,7 @@
         <x:v>4289</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -401,7 +401,7 @@
         <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
       </x:c>
       <x:c r="C4" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
         <x:v>66</x:v>
@@ -414,7 +414,7 @@
       </x:c>
       <x:c r="G4" s="11" t="str"/>
       <x:c r="H4" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -425,7 +425,7 @@
         <x:v>灶下煤之自由篇</x:v>
       </x:c>
       <x:c r="C5" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>82</x:v>
@@ -438,7 +438,7 @@
       </x:c>
       <x:c r="G5" s="11" t="str"/>
       <x:c r="H5" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -524,23 +524,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>重回八零，赶山狩猎养妻女</x:v>
+        <x:v>谁说纨绔不能当状元</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="E9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="str"/>
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="n">
+        <x:v>572</x:v>
+      </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29</x:v>
+        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -548,23 +550,23 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E10" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str"/>
       <x:c r="H10" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -572,23 +574,23 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str"/>
       <x:c r="H11" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -596,23 +598,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>重生归来，四小姐她不装了</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E12" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="str"/>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="n">
+        <x:v>371</x:v>
+      </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -620,25 +624,23 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>垃圾桶里的寻人启事</x:v>
+        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E13" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="n">
-        <x:v>4442</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str"/>
       <x:c r="H13" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -646,23 +648,23 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>山王传奇</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -670,25 +672,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>谁说纨绔不能当状元</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>788</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>572</x:v>
+        <x:v>1834</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -696,25 +698,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>重生归来，四小姐她不装了</x:v>
+        <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E16" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>371</x:v>
+        <x:v>4442</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -722,23 +724,23 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>孤城照山河第一季</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E17" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
-        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G17" s="11" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25、2026-08-28、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -746,13 +748,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>山王传奇</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E18" s="10" t="str">
         <x:v>未标注</x:v>
@@ -760,11 +762,9 @@
       <x:c r="F18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+      <x:c r="G18" s="11" t="str"/>
       <x:c r="H18" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
+        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -772,25 +772,23 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>我将恩人一家捡回村</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E19" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G19" s="11" t="n">
-        <x:v>1834</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="str"/>
       <x:c r="H19" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -798,23 +796,23 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>孤城照山河第一季</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>185</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E20" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F20" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G20" s="11" t="str"/>
       <x:c r="H20" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25、2026-08-28</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -822,23 +820,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E21" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -846,23 +846,23 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>我将恩人一家捡回村</x:v>
+        <x:v>半梦半醒半清欢</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E22" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -870,23 +870,23 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>商场收回档口我成了全城的供应商</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G23" s="11" t="str"/>
       <x:c r="H23" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29</x:v>
+        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -894,23 +894,23 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E24" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G24" s="11" t="str"/>
       <x:c r="H24" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-22</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -918,23 +918,23 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E25" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -942,23 +942,23 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>半梦半醒半清欢</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E26" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1016,26 +1016,22 @@
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="10" t="str">
-        <x:v>鉴宝天瞳</x:v>
+        <x:v>方寸宅院见公道</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="n">
-        <x:v>128</x:v>
-      </x:c>
+      <x:c r="F2" s="11" t="str"/>
       <x:c r="G2" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>知我动画</x:v>
-      </x:c>
+      <x:c r="I2" s="10" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -1043,22 +1039,26 @@
       </x:c>
       <x:c r="B3" s="11"/>
       <x:c r="C3" s="10" t="str">
-        <x:v>暮年大帝，再战诸天</x:v>
+        <x:v>卖鱼大叔，请多指教</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="str"/>
+      <x:c r="F3" s="11" t="n">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="I3" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="str">
+        <x:v>久久剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -1066,10 +1066,10 @@
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="10" t="str">
-        <x:v>满院亲戚全是上古大妖第二季</x:v>
+        <x:v>燃栀：栀子花开恰逢少年</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>1</x:v>
@@ -1089,26 +1089,22 @@
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="10" t="str">
-        <x:v>换师尊后她转修无情道，全宗门跪了</x:v>
+        <x:v>父爱护女归家</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="n">
-        <x:v>174</x:v>
-      </x:c>
+      <x:c r="F5" s="11" t="str"/>
       <x:c r="G5" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="str">
-        <x:v>笙笙动画</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -1116,16 +1112,16 @@
       </x:c>
       <x:c r="B6" s="11"/>
       <x:c r="C6" s="10" t="str">
-        <x:v>指尖的童话</x:v>
+        <x:v>小公爷道，老子可是何美丽的男人呀第一季</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>113</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -1134,7 +1130,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>宅男剧社</x:v>
+        <x:v>亦辰动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1143,22 +1139,26 @@
       </x:c>
       <x:c r="B7" s="11"/>
       <x:c r="C7" s="10" t="str">
-        <x:v>你管这叫灾星首富家都旺翻了！</x:v>
+        <x:v>重生摊牌身份，众人惊了</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="str"/>
+      <x:c r="F7" s="11" t="n">
+        <x:v>139</x:v>
+      </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I7" s="10" t="str"/>
+        <x:v>都市职场 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="str">
+        <x:v>小清书漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -1166,26 +1166,22 @@
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="10" t="str">
-        <x:v>特工王妃扛着王爷去流放</x:v>
+        <x:v>一顾见晚星</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="n">
-        <x:v>116</x:v>
-      </x:c>
+      <x:c r="F8" s="11" t="str"/>
       <x:c r="G8" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="I8" s="10" t="str">
-        <x:v>小酒动画</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -1193,26 +1189,22 @@
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="10" t="str">
-        <x:v>蹭饭一年，她们终于吃不起了</x:v>
+        <x:v>前妻逼我献血，我转身离开</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
-        <x:v>32</x:v>
-      </x:c>
+      <x:c r="F9" s="11" t="str"/>
       <x:c r="G9" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="I9" s="10" t="str">
-        <x:v>云景动漫剧场</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="I9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -1220,22 +1212,26 @@
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="10" t="str">
-        <x:v>孤城照山河第二季</x:v>
+        <x:v>妈妈的天下第一好</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="str"/>
+      <x:c r="F10" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="I10" s="10" t="str"/>
+        <x:v>家庭伦理 / 古装宫廷</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str">
+        <x:v>萌星看剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -1243,26 +1239,22 @@
       </x:c>
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="10" t="str">
-        <x:v>规章冷厨心</x:v>
+        <x:v>办公室的顺手人情</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
+      <x:c r="F11" s="11" t="str"/>
       <x:c r="G11" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="I11" s="10" t="str">
-        <x:v>小白动漫</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -1270,26 +1262,22 @@
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="10" t="str">
-        <x:v>丈母娘百万招婿，我的冰山老婆</x:v>
+        <x:v>恩与仇之间的距离</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="n">
-        <x:v>68</x:v>
-      </x:c>
+      <x:c r="F12" s="11" t="str"/>
       <x:c r="G12" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I12" s="10" t="str">
-        <x:v>星界Ai</x:v>
-      </x:c>
+      <x:c r="I12" s="10" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -1297,26 +1285,22 @@
       </x:c>
       <x:c r="B13" s="11"/>
       <x:c r="C13" s="10" t="str">
-        <x:v>无冕之根</x:v>
+        <x:v>被女神抛弃：我却在荒岛吃香喝辣</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="n">
-        <x:v>689</x:v>
-      </x:c>
+      <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I13" s="10" t="str">
-        <x:v>影留</x:v>
-      </x:c>
+        <x:v>美食治愈 / 战神异能</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -1324,16 +1308,16 @@
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="10" t="str">
-        <x:v>坝上少年</x:v>
+        <x:v>执笔春红</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
         <x:v>仿真人</x:v>
@@ -1342,7 +1326,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>萱萱短剧</x:v>
+        <x:v>小尘剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1351,26 +1335,22 @@
       </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="10" t="str">
-        <x:v>萌宝幼崽大作战</x:v>
+        <x:v>卯卯入帅府，全家乐开花第二季</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="n">
-        <x:v>142</x:v>
-      </x:c>
+      <x:c r="F15" s="11" t="str"/>
       <x:c r="G15" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
-      </x:c>
-      <x:c r="I15" s="10" t="str">
-        <x:v>南风知意</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -1378,26 +1358,22 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="10" t="str">
-        <x:v>穿越东北，我靠打猎养活三个外甥女</x:v>
+        <x:v>我拿五万去扶贫，男友家却有三片海</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="n">
-        <x:v>88</x:v>
-      </x:c>
+      <x:c r="F16" s="11" t="str"/>
       <x:c r="G16" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I16" s="10" t="str">
-        <x:v>飞行轻舟剧场</x:v>
-      </x:c>
+      <x:c r="I16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -1405,25 +1381,25 @@
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="10" t="str">
-        <x:v>台风过境时</x:v>
+        <x:v>全家偷听我心声后，假千金慌了</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>阿晚漫馆</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1432,26 +1408,22 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="10" t="str">
-        <x:v>黑塔：从超忆症开始成神</x:v>
+        <x:v>相亲当天，未婚妻的男助理抢我车位</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="n">
-        <x:v>139</x:v>
-      </x:c>
+      <x:c r="F18" s="11" t="str"/>
       <x:c r="G18" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="I18" s="10" t="str">
-        <x:v>菠萝漫</x:v>
-      </x:c>
+        <x:v>都市职场 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="I18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -1459,26 +1431,22 @@
       </x:c>
       <x:c r="B19" s="11"/>
       <x:c r="C19" s="10" t="str">
-        <x:v>流放厨娘，我靠美食绝地翻盘！</x:v>
+        <x:v>百万房车，被室友擅用当婚车</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="n">
-        <x:v>205</x:v>
-      </x:c>
+      <x:c r="F19" s="11" t="str"/>
       <x:c r="G19" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="I19" s="10" t="str">
-        <x:v>延晨的动漫窝</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -1486,26 +1454,22 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="10" t="str">
-        <x:v>重回82：我成山君契约万兽打猎宠妻</x:v>
+        <x:v>十八次返岗申请</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="n">
-        <x:v>80</x:v>
-      </x:c>
+      <x:c r="F20" s="11" t="str"/>
       <x:c r="G20" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
-        <x:v>年代怀旧 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="I20" s="10" t="str">
-        <x:v>神文视界</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -1513,26 +1477,22 @@
       </x:c>
       <x:c r="B21" s="11"/>
       <x:c r="C21" s="10" t="str">
-        <x:v>杨巧替嫁残疾英雄，婆家宠我青云志</x:v>
+        <x:v>重回太子遇险时，我把救命之功让给嫡姐</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="n">
-        <x:v>143</x:v>
-      </x:c>
+      <x:c r="F21" s="11" t="str"/>
       <x:c r="G21" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感 / 现实反转</x:v>
-      </x:c>
-      <x:c r="I21" s="10" t="str">
-        <x:v>游世剧场</x:v>
-      </x:c>
+        <x:v>年代怀旧 / 古装宫廷</x:v>
+      </x:c>
+      <x:c r="I21" s="10" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -1540,22 +1500,26 @@
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="10" t="str">
-        <x:v>福运：逃荒种田农家团宠小奶包</x:v>
+        <x:v>出渊狂龙</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="str"/>
+      <x:c r="F22" s="11" t="n">
+        <x:v>132</x:v>
+      </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>种田囤货 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="I22" s="10" t="str"/>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="str">
+        <x:v>幻想九月剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -1563,26 +1527,22 @@
       </x:c>
       <x:c r="B23" s="11"/>
       <x:c r="C23" s="10" t="str">
-        <x:v>饭局生变，我偏要把账算清</x:v>
+        <x:v>不赴旧约：她的人生重新开场</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="n">
-        <x:v>54</x:v>
-      </x:c>
+      <x:c r="F23" s="11" t="str"/>
       <x:c r="G23" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
-      </x:c>
-      <x:c r="I23" s="10" t="str">
-        <x:v>不兜</x:v>
-      </x:c>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="I23" s="10" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
@@ -1590,16 +1550,16 @@
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="10" t="str">
-        <x:v>青山不忘</x:v>
+        <x:v>麦浪风云</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -1608,157 +1568,149 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>漫漫天星</x:v>
+        <x:v>南辞说漫</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B25" s="11"/>
       <x:c r="C25" s="10" t="str">
-        <x:v>怪力少女和她的病弱娇夫</x:v>
+        <x:v>你管这叫灾星首富家都旺翻了！</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="n">
-        <x:v>84</x:v>
-      </x:c>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str"/>
       <x:c r="G25" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="I25" s="10" t="str">
-        <x:v>剧赞影视</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="10" t="str">
-        <x:v>错爱沉霜</x:v>
+        <x:v>蹭饭一年，她们终于吃不起了</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H26" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>灰鲸剧场</x:v>
+        <x:v>云景动漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="10" t="str">
-        <x:v>替嫁残疾英雄婆家宠我青云志</x:v>
+        <x:v>丈母娘百万招婿，我的冰山老婆</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>123</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>觅影剧场</x:v>
+        <x:v>星界Ai</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="10" t="str">
-        <x:v>重回八零，赶山狩猎养妻女日记</x:v>
+        <x:v>一村人养一个神第二季</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="n">
-        <x:v>128</x:v>
-      </x:c>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str"/>
       <x:c r="G28" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="I28" s="10" t="str">
-        <x:v>小迷动画</x:v>
-      </x:c>
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="I28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="10" t="str">
-        <x:v>让我开早餐店，我下午才营业</x:v>
+        <x:v>无冕之根</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H29" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>天圆漫剧</x:v>
+        <x:v>影留</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="10" t="str">
-        <x:v>一村人养一个神第二季</x:v>
+        <x:v>神女归途</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str"/>
       <x:c r="G30" s="10" t="str">
@@ -1771,30 +1723,26 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="10" t="str">
-        <x:v>一百块的安稳</x:v>
+        <x:v>福宝治愈全世界，家有萌娃岁岁安第二季</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="n">
-        <x:v>49</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str"/>
       <x:c r="G31" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I31" s="10" t="str">
-        <x:v>琥珀漫剧</x:v>
-      </x:c>
+        <x:v>萌宝治愈</x:v>
+      </x:c>
+      <x:c r="I31" s="10" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
@@ -1802,25 +1750,25 @@
       </x:c>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="10" t="str">
-        <x:v>分家那天，我要了一间破屋</x:v>
+        <x:v>月子第一天，婆婆离世了</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>卜卜漫剧</x:v>
+        <x:v>锋芒映剧</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1829,26 +1777,22 @@
       </x:c>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="10" t="str">
-        <x:v>断腿父王别慌，福星多多来啦！</x:v>
+        <x:v>铺子空了，房东慌了</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="n">
-        <x:v>70</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str"/>
       <x:c r="G33" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
-      </x:c>
-      <x:c r="I33" s="10" t="str">
-        <x:v>星界秘漫</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I33" s="10" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="11" t="str">
@@ -1856,25 +1800,25 @@
       </x:c>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="10" t="str">
-        <x:v>拂衣震九州</x:v>
+        <x:v>王府小祖宗，捡啥啥是宝</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
-        <x:v>猛犸象短剧</x:v>
+        <x:v>诗婳-君懿看剧</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1883,26 +1827,22 @@
       </x:c>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="10" t="str">
-        <x:v>神医奶团：妙手扶爹</x:v>
+        <x:v>八零：盒饭女王从小摊开始</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="n">
-        <x:v>135</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str"/>
       <x:c r="G35" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>家庭伦理 / 萌宝治愈 / 战神异能</x:v>
-      </x:c>
-      <x:c r="I35" s="10" t="str">
-        <x:v>小良短剧</x:v>
-      </x:c>
+        <x:v>年代怀旧 / 都市职场 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="I35" s="10" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
@@ -1910,26 +1850,22 @@
       </x:c>
       <x:c r="B36" s="11"/>
       <x:c r="C36" s="10" t="str">
-        <x:v>山下是绝路，山上是生门</x:v>
+        <x:v>择日复婚</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="n">
-        <x:v>99</x:v>
-      </x:c>
+      <x:c r="F36" s="11" t="str"/>
       <x:c r="G36" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I36" s="10" t="str">
-        <x:v>独影剧场</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="I36" s="10" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="11" t="str">
@@ -1937,25 +1873,25 @@
       </x:c>
       <x:c r="B37" s="11"/>
       <x:c r="C37" s="10" t="str">
-        <x:v>糯糯下山，师兄们都慌了</x:v>
+        <x:v>寒门嫡女：携空间护母妹谋生计</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H37" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>青椒剪辑</x:v>
+        <x:v>喵喵说书</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1964,25 +1900,25 @@
       </x:c>
       <x:c r="B38" s="11"/>
       <x:c r="C38" s="10" t="str">
-        <x:v>心肝颤：双宝助攻复婚记</x:v>
+        <x:v>杨巧替嫁残疾英雄，婆家宠我青云志</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>123</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H38" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理 / 婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
-        <x:v>西施玩家</x:v>
+        <x:v>游世剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1991,26 +1927,22 @@
       </x:c>
       <x:c r="B39" s="11"/>
       <x:c r="C39" s="10" t="str">
-        <x:v>风过牧野逢晚晴</x:v>
+        <x:v>我在急诊室摸鱼，全院跪求出手！</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="n">
-        <x:v>77</x:v>
-      </x:c>
+      <x:c r="F39" s="11" t="str"/>
       <x:c r="G39" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I39" s="10" t="str">
-        <x:v>杭鹿二姐爱看剧</x:v>
-      </x:c>
+      <x:c r="I39" s="10" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="11" t="str">
@@ -2018,26 +1950,22 @@
       </x:c>
       <x:c r="B40" s="11"/>
       <x:c r="C40" s="10" t="str">
-        <x:v>山沟里救下一条白龙</x:v>
+        <x:v>大婚当天，前任坐在我的婚床</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F40" s="11" t="n">
-        <x:v>83</x:v>
-      </x:c>
+      <x:c r="F40" s="11" t="str"/>
       <x:c r="G40" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="I40" s="10" t="str">
-        <x:v>小何故事会</x:v>
-      </x:c>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="I40" s="10" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="11" t="str">
@@ -2045,26 +1973,22 @@
       </x:c>
       <x:c r="B41" s="11"/>
       <x:c r="C41" s="10" t="str">
-        <x:v>晏晏总角时时安</x:v>
+        <x:v>云程赴佳期，一屋欢闹伴韶光</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F41" s="11" t="n">
-        <x:v>62</x:v>
-      </x:c>
+      <x:c r="F41" s="11" t="str"/>
       <x:c r="G41" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I41" s="10" t="str">
-        <x:v>寻光推剧</x:v>
-      </x:c>
+      <x:c r="I41" s="10" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="11" t="str">
@@ -2072,25 +1996,25 @@
       </x:c>
       <x:c r="B42" s="11"/>
       <x:c r="C42" s="10" t="str">
-        <x:v>八零悍妇：女汉子逆袭记</x:v>
+        <x:v>我家后山藏真龙</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>138</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G42" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H42" s="10" t="str">
-        <x:v>年代怀旧 / 逆袭打脸</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str">
-        <x:v>大宝动画</x:v>
+        <x:v>剧鲸剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2099,25 +2023,25 @@
       </x:c>
       <x:c r="B43" s="11"/>
       <x:c r="C43" s="10" t="str">
-        <x:v>听泉打捞王</x:v>
+        <x:v>穿成凡虎，我吞噬成神</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>147</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G43" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H43" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str">
-        <x:v>泡姐漫屋</x:v>
+        <x:v>寒冰剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2126,16 +2050,16 @@
       </x:c>
       <x:c r="B44" s="11"/>
       <x:c r="C44" s="10" t="str">
-        <x:v>实习教出金牌班，家长要换班主任</x:v>
+        <x:v>我大华第一逍遥王</x:v>
       </x:c>
       <x:c r="D44" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G44" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -2144,7 +2068,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str">
-        <x:v>长风剧场</x:v>
+        <x:v>口水显眼包</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2153,25 +2077,25 @@
       </x:c>
       <x:c r="B45" s="11"/>
       <x:c r="C45" s="10" t="str">
-        <x:v>谁说纨绔不能当状元第二季</x:v>
+        <x:v>团宠驾到：督军府的满级小锦鲤</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>316</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G45" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H45" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>每日沙雕速递</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -2180,26 +2104,22 @@
       </x:c>
       <x:c r="B46" s="11"/>
       <x:c r="C46" s="10" t="str">
-        <x:v>我只想找死，却被奉为九州战神了</x:v>
+        <x:v>小小力量大，从家属院开始当家</x:v>
       </x:c>
       <x:c r="D46" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F46" s="11" t="n">
-        <x:v>852</x:v>
-      </x:c>
+      <x:c r="F46" s="11" t="str"/>
       <x:c r="G46" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H46" s="10" t="str">
-        <x:v>战神异能</x:v>
-      </x:c>
-      <x:c r="I46" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I46" s="10" t="str"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="11" t="str">
@@ -2207,161 +2127,22 @@
       </x:c>
       <x:c r="B47" s="11"/>
       <x:c r="C47" s="10" t="str">
-        <x:v>被房车堵住的生死路</x:v>
+        <x:v>手打人间味</x:v>
       </x:c>
       <x:c r="D47" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F47" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
+      <x:c r="F47" s="11" t="str"/>
       <x:c r="G47" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H47" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I47" s="10" t="str">
-        <x:v>二妞.影视</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B48" s="11"/>
-      <x:c r="C48" s="10" t="str">
-        <x:v>开局拜仙尊为师杂灵根小师妹气运超强的</x:v>
-      </x:c>
-      <x:c r="D48" s="11" t="str">
-        <x:v>2026-08-28</x:v>
-      </x:c>
-      <x:c r="E48" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F48" s="11" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G48" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H48" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
-      </x:c>
-      <x:c r="I48" s="10" t="str">
-        <x:v>垂钓剧场</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B49" s="11"/>
-      <x:c r="C49" s="10" t="str">
-        <x:v>玄门归来：十年婚约</x:v>
-      </x:c>
-      <x:c r="D49" s="11" t="str">
-        <x:v>2026-08-28</x:v>
-      </x:c>
-      <x:c r="E49" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F49" s="11" t="n">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="G49" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H49" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="I49" s="10" t="str">
-        <x:v>大公鸡剧场</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B50" s="11"/>
-      <x:c r="C50" s="10" t="str">
-        <x:v>重回台风夜，我让她悔不当初</x:v>
-      </x:c>
-      <x:c r="D50" s="11" t="str">
-        <x:v>2026-08-28</x:v>
-      </x:c>
-      <x:c r="E50" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F50" s="11" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G50" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H50" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="I50" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B51" s="11"/>
-      <x:c r="C51" s="10" t="str">
-        <x:v>我在夜市摆摊成王</x:v>
-      </x:c>
-      <x:c r="D51" s="11" t="str">
-        <x:v>2026-08-28</x:v>
-      </x:c>
-      <x:c r="E51" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F51" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G51" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H51" s="10" t="str">
-        <x:v>都市职场 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="I51" s="10" t="str">
-        <x:v>张小曼</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B52" s="11"/>
-      <x:c r="C52" s="10" t="str">
-        <x:v>别惹真千金，她手遮半边天</x:v>
-      </x:c>
-      <x:c r="D52" s="11" t="str">
-        <x:v>2026-08-28</x:v>
-      </x:c>
-      <x:c r="E52" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F52" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G52" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H52" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I52" s="10" t="str">
-        <x:v>剧鲸小剧场</x:v>
-      </x:c>
+      <x:c r="I47" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2438,7 +2219,7 @@
         <x:v>7514</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2467,7 +2248,7 @@
         <x:v>852</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2496,7 +2277,7 @@
         <x:v>8368</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2523,7 +2304,7 @@
       </x:c>
       <x:c r="H5" s="11" t="str"/>
       <x:c r="I5" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2550,7 +2331,7 @@
       </x:c>
       <x:c r="H6" s="11" t="str"/>
       <x:c r="I6" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2558,28 +2339,26 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>垃圾桶里的寻人启事</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="n">
-        <x:v>4442</x:v>
-      </x:c>
+      <x:c r="H7" s="11" t="str"/>
       <x:c r="I7" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2587,28 +2366,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>我妈装穷来认我</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str"/>
       <x:c r="I8" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2616,26 +2393,26 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>分家只给破枪，我听兽语富全屯</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
         <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2643,26 +2420,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
       <x:c r="C10" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="n">
+        <x:v>4442</x:v>
+      </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜6次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2670,26 +2449,26 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>悍妻替嫁，从前说</x:v>
+        <x:v>山王传奇</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜7次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜6次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2697,26 +2476,26 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计11次，起量能力已被验证；56集长剧集；题材契合爆款主线（种田囤货 / 美食治愈 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜6次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2724,7 +2503,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>爷爷不请七遍不动筷</x:v>
+        <x:v>悍妻替嫁，从前说</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>6</x:v>
@@ -2733,19 +2512,17 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="n">
-        <x:v>490</x:v>
-      </x:c>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计9次，起量能力已被验证；仿真人制作；50集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2753,7 +2530,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>云岭藏金，真心为聘</x:v>
+        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>6</x:v>
@@ -2762,17 +2539,17 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2780,26 +2557,26 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>分家只给破枪，我听兽语富全屯</x:v>
+        <x:v>八零之老妈在厂长家当后妈</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜6次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2807,26 +2584,26 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>魔力情谊之我一个人来的</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2834,26 +2611,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>三百块的信任，九十万的真相</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2861,26 +2640,26 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>九二年，他塞给我五百块</x:v>
+        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2888,26 +2667,26 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>大力幼崽到处捡爹</x:v>
+        <x:v>九二年，他塞给我五百块</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2915,26 +2694,26 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
+        <x:v>这门婚我不嫁了</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计7次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2942,26 +2721,26 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
+        <x:v>逆流年代：从1970开始种田养家</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；110集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2969,26 +2748,26 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>这个姨娘不一般</x:v>
+        <x:v>傻女重生记，睁眼后盖房发家</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2996,26 +2775,26 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>重回千禧我靠赶海养活家人</x:v>
+        <x:v>离婚那天我多了个董事长妈妈</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>183</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计8次，起量能力已被验证；183集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3023,26 +2802,26 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>八零之老妈在厂长家当后妈</x:v>
+        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>156</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3050,26 +2829,26 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>我哥四个全是宠妹狂魔</x:v>
+        <x:v>芯骨藏锋</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；100集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜5次、累计5次，起量能力已被验证；仿真人制作；52集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3077,26 +2856,26 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>199的排场，48万的账</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计10次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3104,26 +2883,26 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>傻女重生记，睁眼后盖房发家</x:v>
+        <x:v>暴雪见人心</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3131,26 +2910,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
+        <x:v>爷爷不请七遍不动筷</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>119</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="n">
+        <x:v>490</x:v>
+      </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计9次，起量能力已被验证；仿真人制作；50集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3158,26 +2939,26 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>馋哭！陆总该吃饭了</x:v>
+        <x:v>云岭藏金，真心为聘</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
         <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；98集长剧集；题材契合爆款主线（美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3185,26 +2966,26 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>八零媳妇富农家</x:v>
+        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>105</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计5次，起量能力已被验证；105集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3212,26 +2993,26 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>寒庭有犬鸣</x:v>
+        <x:v>这个姨娘不一般</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计5次，起量能力已被验证；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3239,26 +3020,26 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>青云入世这个神医会功夫</x:v>
+        <x:v>魔力情谊之我一个人来的</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>146</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；146集长剧集；题材契合爆款主线（婚姻情感 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3266,26 +3047,26 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
+        <x:v>三百块的信任，九十万的真相</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3293,26 +3074,26 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>守着灶台，守住本心</x:v>
+        <x:v>199的排场，48万的账</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str"/>
       <x:c r="I34" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；52集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3320,7 +3101,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>傅总，您的三岁小债主上门了</x:v>
+        <x:v>大力幼崽到处捡爹</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
@@ -3329,17 +3110,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str"/>
       <x:c r="I35" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；97集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3366,7 +3147,7 @@
       </x:c>
       <x:c r="H36" s="11" t="str"/>
       <x:c r="I36" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；120集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计6次，起量能力已被验证；120集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3374,26 +3155,26 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>疯娘翻身，穿越宠崽</x:v>
+        <x:v>一墙之隔的求救声</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E37" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；200集长剧集；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；88集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3401,26 +3182,26 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>离婚那天我多了个董事长妈妈</x:v>
+        <x:v>寒庭有犬鸣</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str"/>
       <x:c r="I38" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3428,26 +3209,26 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>被总经理针对后，我只按菜单做菜</x:v>
+        <x:v>捡到小蛇，我养出龙崽</x:v>
       </x:c>
       <x:c r="C39" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G39" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str"/>
       <x:c r="I39" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；61集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3455,7 +3236,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>一塘清水鉴人心</x:v>
+        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>4</x:v>
@@ -3464,17 +3245,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>2026-08-15</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G40" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str"/>
       <x:c r="I40" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3482,26 +3263,26 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>我家成了别人的婚房</x:v>
+        <x:v>一辆旧中巴奔向新生活</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G41" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str"/>
       <x:c r="I41" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；71集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计4次，起量能力已被验证；82集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3509,26 +3290,26 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>我的订婚宴上，闯进来两个要饭的</x:v>
+        <x:v>情起屋檐下</x:v>
       </x:c>
       <x:c r="C42" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D42" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="G42" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H42" s="11" t="str"/>
       <x:c r="I42" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计4次，起量能力已被验证；66集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3536,188 +3317,26 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
+        <x:v>老婆每月给别人一万五，离婚时她后悔了</x:v>
       </x:c>
       <x:c r="C43" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D43" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E43" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G43" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H43" s="11" t="str"/>
       <x:c r="I43" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="11" t="n">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B44" s="10" t="str">
-        <x:v>八零：苏念荷的故事</x:v>
-      </x:c>
-      <x:c r="C44" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D44" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E44" s="11" t="str">
-        <x:v>2026-08-18</x:v>
-      </x:c>
-      <x:c r="F44" s="11" t="n">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G44" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H44" s="11" t="str"/>
-      <x:c r="I44" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；123集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="11" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B45" s="10" t="str">
-        <x:v>情起屋檐下</x:v>
-      </x:c>
-      <x:c r="C45" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D45" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E45" s="11" t="str">
-        <x:v>2026-08-18</x:v>
-      </x:c>
-      <x:c r="F45" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G45" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H45" s="11" t="str"/>
-      <x:c r="I45" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；66集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="11" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B46" s="10" t="str">
-        <x:v>我的车间不养闲人</x:v>
-      </x:c>
-      <x:c r="C46" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D46" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E46" s="11" t="str">
-        <x:v>2026-08-16</x:v>
-      </x:c>
-      <x:c r="F46" s="11" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G46" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H46" s="11" t="str"/>
-      <x:c r="I46" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="11" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B47" s="10" t="str">
-        <x:v>携手八零，与君同赴山河</x:v>
-      </x:c>
-      <x:c r="C47" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D47" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E47" s="11" t="str">
-        <x:v>2026-08-16</x:v>
-      </x:c>
-      <x:c r="F47" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G47" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H47" s="11" t="str"/>
-      <x:c r="I47" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；124集长剧集；题材契合爆款主线（年代怀旧 / 古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="11" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B48" s="10" t="str">
-        <x:v>灵泉姑娘，分家后富甲一方第一季</x:v>
-      </x:c>
-      <x:c r="C48" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D48" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E48" s="11" t="str">
-        <x:v>2026-08-15</x:v>
-      </x:c>
-      <x:c r="F48" s="11" t="n">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G48" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H48" s="11" t="str"/>
-      <x:c r="I48" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；152集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="11" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B49" s="10" t="str">
-        <x:v>老婆每月给别人一万五，离婚时她后悔了</x:v>
-      </x:c>
-      <x:c r="C49" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D49" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E49" s="11" t="str">
-        <x:v>2026-08-18</x:v>
-      </x:c>
-      <x:c r="F49" s="11" t="n">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G49" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H49" s="11" t="str"/>
-      <x:c r="I49" s="10" t="str">
-        <x:v>8-12~8-18两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；113集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-14~8-20两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；113集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4676,22 +4295,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>穿成团宠后我靠读心逆袭</x:v>
+        <x:v>拒绝996，我成为赶海大佬了第三季</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F33" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>种田囤货 / 都市职场</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
-        <x:v>星梦好剧</x:v>
+        <x:v>亦辰动漫</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
+        <x:v>123集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 都市职场）；续季/系列续作，有前作热度背书；发布账号「亦辰动漫」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I33" s="11" t="n">
         <x:v>7</x:v>
@@ -4705,22 +4324,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
+        <x:v>穿成团宠后我靠读心逆袭</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F34" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
-        <x:v>陈柯</x:v>
+        <x:v>星梦好剧</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
       </x:c>
       <x:c r="I34" s="11" t="n">
         <x:v>7</x:v>
@@ -4734,22 +4353,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>藏在婚姻里的谎言</x:v>
+        <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F35" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
+        <x:v>陈柯</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I35" s="11" t="n">
         <x:v>7</x:v>
@@ -4763,22 +4382,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>让你守边塞，你用汉堡养兵？第二季江南篇</x:v>
+        <x:v>藏在婚姻里的谎言</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F36" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
-        <x:v>浮绘剧场</x:v>
+        <x:v>九鲤动漫</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="I36" s="11" t="n">
         <x:v>7</x:v>
@@ -5312,10 +4931,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>339</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>42.7%</x:v>
+        <x:v>41.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5323,10 +4942,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>244</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>30.8%</x:v>
+        <x:v>32.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5334,10 +4953,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>210</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>26.5%</x:v>
+        <x:v>25.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -5361,7 +4980,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>12%</x:v>
@@ -5372,10 +4991,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>348</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>44.4%</x:v>
+        <x:v>44.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5383,10 +5002,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>11.6%</x:v>
+        <x:v>11.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5394,10 +5013,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>250</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>31.9%</x:v>
+        <x:v>32.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -5421,10 +5040,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>307</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>38.7%</x:v>
+        <x:v>39.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -5432,10 +5051,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>19.0%</x:v>
+        <x:v>18.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -5443,10 +5062,10 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>11.2%</x:v>
+        <x:v>11.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5454,7 +5073,7 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>10.0%</x:v>
@@ -5465,10 +5084,10 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -5476,10 +5095,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.3%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5490,7 +5109,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>7.4%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5498,10 +5117,10 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>6.6%</x:v>
+        <x:v>6.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5509,7 +5128,7 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
         <x:v>5.3%</x:v>
@@ -5520,10 +5139,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>5.0%</x:v>
+        <x:v>4.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -5544,293 +5163,297 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>1.0%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>2.4%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>2.4%</x:v>
+        <x:v>1.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>3.9%</x:v>
+        <x:v>2.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>5.0%</x:v>
+        <x:v>1.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>4.9%</x:v>
+        <x:v>4.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>7.7%</x:v>
+        <x:v>4.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>147</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>18.5%</x:v>
+        <x:v>5.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
+        <x:v>上榜3次</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>8.2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="10" t="str">
+        <x:v>上榜2次</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C44" s="11" t="str">
+        <x:v>19.4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="10" t="str">
         <x:v>上榜1次</x:v>
       </x:c>
-      <x:c r="B43" s="11" t="n">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="C43" s="11" t="str">
-        <x:v>51.1%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="22" customHeight="1">
-      <x:c r="A45" s="14" t="str">
+      <x:c r="B45" s="11" t="n">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>49.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="24" customHeight="1">
-      <x:c r="A46" s="5" t="str">
+    <x:row r="48" ht="24" customHeight="1">
+      <x:c r="A48" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B46" t="str">
+      <x:c r="B48" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C46" t="str">
+      <x:c r="C48" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="10" t="str">
-        <x:v>CP自营</x:v>
-      </x:c>
-      <x:c r="B47" s="11" t="n">
-        <x:v>777</x:v>
-      </x:c>
-      <x:c r="C47" s="11" t="str">
-        <x:v>98.0%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="B48" s="11" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C48" s="11" t="str">
-        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>94.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="B50" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="str">
+        <x:v>5.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="10" t="str">
+        <x:v>CP托管</x:v>
+      </x:c>
+      <x:c r="B51" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="10" t="str">
         <x:v>番茄原创</x:v>
       </x:c>
-      <x:c r="B50" s="11" t="n">
+      <x:c r="B52" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C50" s="11" t="str">
-        <x:v>0.3%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="22" customHeight="1">
-      <x:c r="A52" s="14" t="str">
+      <x:c r="C52" s="11" t="str">
+        <x:v>0.2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="14" t="str">
         <x:v>发布抖音号TOP15</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="24" customHeight="1">
-      <x:c r="A53" s="5" t="str">
+    <x:row r="55" ht="24" customHeight="1">
+      <x:c r="A55" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B53" t="str">
+      <x:c r="B55" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C53" t="str">
+      <x:c r="C55" t="str">
         <x:v>占比</x:v>
       </x:c>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="B54" s="11" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C54" s="11" t="str"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
-      </x:c>
-      <x:c r="B55" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C55" s="11" t="str"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B56" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C56" s="11" t="str"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B57" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C57" s="11" t="str"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B58" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C58" s="11" t="str"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="str">
-        <x:v>不兜</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
         <x:v>4</x:v>
@@ -5839,7 +5462,7 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
         <x:v>4</x:v>
@@ -5848,7 +5471,7 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>不兜</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
         <x:v>4</x:v>
@@ -5857,7 +5480,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>取瘾书屋</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
         <x:v>4</x:v>
@@ -5866,7 +5489,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>清风短剧场</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
         <x:v>4</x:v>
@@ -5875,7 +5498,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
-        <x:v>暖星追剧</x:v>
+        <x:v>取瘾书屋</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
         <x:v>4</x:v>
@@ -5884,141 +5507,159 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>清风短剧场</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C65" s="11" t="str"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>亦辰动漫</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C66" s="11" t="str"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>暖星追剧</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>一张不够花</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str"/>
     </x:row>
-    <x:row r="70" ht="22" customHeight="1">
-      <x:c r="A70" s="14" t="str">
+    <x:row r="69">
+      <x:c r="A69" s="10" t="str">
+        <x:v>渲渲动画</x:v>
+      </x:c>
+      <x:c r="B69" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C69" s="11" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="10" t="str">
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
+      <x:c r="B70" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C70" s="11" t="str"/>
+    </x:row>
+    <x:row r="72" ht="22" customHeight="1">
+      <x:c r="A72" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="24" customHeight="1">
-      <x:c r="A71" s="5" t="str">
+    <x:row r="73" ht="24" customHeight="1">
+      <x:c r="A73" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B71" t="str">
+      <x:c r="B73" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C71" t="str">
+      <x:c r="C73" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
-      </x:c>
-      <x:c r="B72" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C72" s="11" t="str">
-        <x:v>19.0%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
-      </x:c>
-      <x:c r="B73" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C73" s="11" t="str">
-        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B74" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C74" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B75" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C75" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
+        <x:v>现实反转/人性</x:v>
+      </x:c>
+      <x:c r="B79" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C79" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B80" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C80" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B79" s="11" t="n">
+      <x:c r="B81" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C79" s="11" t="str">
+      <x:c r="C81" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -6028,9 +5669,9 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A45:C45"/>
-    <x:mergeCell ref="A52:C52"/>
-    <x:mergeCell ref="A70:C70"/>
+    <x:mergeCell ref="A47:C47"/>
+    <x:mergeCell ref="A54:C54"/>
+    <x:mergeCell ref="A72:C72"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R096e8703a99f49da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R7d19ce326cb44128"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rbdbb5a389aaf4bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="R45c2a698e9ce40e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R0e5ff133878d4ab0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rd78a46e4dcaa454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Ra8cbc6ffd48546af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R9d1a555caeec411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rb2f92ac69cd142ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="Rdc11083628be4c36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1024,14 +1024,18 @@
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="str"/>
+      <x:c r="F2" s="11" t="n">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="G2" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str"/>
+      <x:c r="I2" s="10" t="str">
+        <x:v>豆豆动漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -1074,14 +1078,18 @@
       <x:c r="E4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="str"/>
+      <x:c r="F4" s="11" t="n">
+        <x:v>108</x:v>
+      </x:c>
       <x:c r="G4" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I4" s="10" t="str"/>
+      <x:c r="I4" s="10" t="str">
+        <x:v>AI漫剧老六</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -1097,14 +1105,18 @@
       <x:c r="E5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="str"/>
+      <x:c r="F5" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
       <x:c r="G5" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="str"/>
+      <x:c r="I5" s="10" t="str">
+        <x:v>丽佳漫剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -1174,14 +1186,18 @@
       <x:c r="E8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="str"/>
+      <x:c r="F8" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I8" s="10" t="str"/>
+      <x:c r="I8" s="10" t="str">
+        <x:v>三针剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -1197,14 +1213,18 @@
       <x:c r="E9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="str"/>
+      <x:c r="F9" s="11" t="n">
+        <x:v>104</x:v>
+      </x:c>
       <x:c r="G9" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I9" s="10" t="str"/>
+      <x:c r="I9" s="10" t="str">
+        <x:v>榴莲漫剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -1247,14 +1267,18 @@
       <x:c r="E11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="str"/>
+      <x:c r="F11" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I11" s="10" t="str"/>
+      <x:c r="I11" s="10" t="str">
+        <x:v>小 淇</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -1270,14 +1294,18 @@
       <x:c r="E12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="str"/>
+      <x:c r="F12" s="11" t="n">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="G12" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I12" s="10" t="str"/>
+      <x:c r="I12" s="10" t="str">
+        <x:v>艾微动画剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -1293,14 +1321,18 @@
       <x:c r="E13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="str"/>
+      <x:c r="F13" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
         <x:v>美食治愈 / 战神异能</x:v>
       </x:c>
-      <x:c r="I13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str">
+        <x:v>麋鹿漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -1343,14 +1375,18 @@
       <x:c r="E15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="str"/>
+      <x:c r="F15" s="11" t="n">
+        <x:v>106</x:v>
+      </x:c>
       <x:c r="G15" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I15" s="10" t="str"/>
+      <x:c r="I15" s="10" t="str">
+        <x:v>念⭐️念</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -1366,14 +1402,18 @@
       <x:c r="E16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="str"/>
+      <x:c r="F16" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="G16" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I16" s="10" t="str"/>
+      <x:c r="I16" s="10" t="str">
+        <x:v>小菲菲动画</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -1416,14 +1456,18 @@
       <x:c r="E18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="str"/>
+      <x:c r="F18" s="11" t="n">
+        <x:v>76</x:v>
+      </x:c>
       <x:c r="G18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
         <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
-      <x:c r="I18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str">
+        <x:v>小丘剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -1439,14 +1483,18 @@
       <x:c r="E19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="str"/>
+      <x:c r="F19" s="11" t="n">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I19" s="10" t="str"/>
+      <x:c r="I19" s="10" t="str">
+        <x:v>小牛文馆</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -1462,14 +1510,18 @@
       <x:c r="E20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="str"/>
+      <x:c r="F20" s="11" t="n">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="G20" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I20" s="10" t="str"/>
+      <x:c r="I20" s="10" t="str">
+        <x:v>星禾与众剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -1485,14 +1537,18 @@
       <x:c r="E21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="str"/>
+      <x:c r="F21" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
         <x:v>年代怀旧 / 古装宫廷</x:v>
       </x:c>
-      <x:c r="I21" s="10" t="str"/>
+      <x:c r="I21" s="10" t="str">
+        <x:v>墨雨星河</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -1535,14 +1591,18 @@
       <x:c r="E23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="str"/>
+      <x:c r="F23" s="11" t="n">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
         <x:v>年代怀旧</x:v>
       </x:c>
-      <x:c r="I23" s="10" t="str"/>
+      <x:c r="I23" s="10" t="str">
+        <x:v>喵喵说书</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
@@ -1585,14 +1645,18 @@
       <x:c r="E25" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="str"/>
+      <x:c r="F25" s="11" t="n">
+        <x:v>139</x:v>
+      </x:c>
       <x:c r="G25" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I25" s="10" t="str"/>
+      <x:c r="I25" s="10" t="str">
+        <x:v>尘埃漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -1662,14 +1726,18 @@
       <x:c r="E28" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F28" s="11" t="str"/>
+      <x:c r="F28" s="11" t="n">
+        <x:v>93</x:v>
+      </x:c>
       <x:c r="G28" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
         <x:v>战神异能</x:v>
       </x:c>
-      <x:c r="I28" s="10" t="str"/>
+      <x:c r="I28" s="10" t="str">
+        <x:v>木偶说漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
@@ -1712,14 +1780,18 @@
       <x:c r="E30" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="str"/>
+      <x:c r="F30" s="11" t="n">
+        <x:v>169</x:v>
+      </x:c>
       <x:c r="G30" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
         <x:v>战神异能</x:v>
       </x:c>
-      <x:c r="I30" s="10" t="str"/>
+      <x:c r="I30" s="10" t="str">
+        <x:v>河虾动漫</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
@@ -1735,14 +1807,18 @@
       <x:c r="E31" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F31" s="11" t="str"/>
+      <x:c r="F31" s="11" t="n">
+        <x:v>168</x:v>
+      </x:c>
       <x:c r="G31" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
         <x:v>萌宝治愈</x:v>
       </x:c>
-      <x:c r="I31" s="10" t="str"/>
+      <x:c r="I31" s="10" t="str">
+        <x:v>紫怡漫剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
@@ -1785,14 +1861,18 @@
       <x:c r="E33" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F33" s="11" t="str"/>
+      <x:c r="F33" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="G33" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I33" s="10" t="str"/>
+      <x:c r="I33" s="10" t="str">
+        <x:v>林帧漫剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="11" t="str">
@@ -1835,14 +1915,18 @@
       <x:c r="E35" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F35" s="11" t="str"/>
+      <x:c r="F35" s="11" t="n">
+        <x:v>133</x:v>
+      </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
         <x:v>年代怀旧 / 都市职场 / 美食治愈</x:v>
       </x:c>
-      <x:c r="I35" s="10" t="str"/>
+      <x:c r="I35" s="10" t="str">
+        <x:v>东瓜剧场</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
@@ -1858,14 +1942,18 @@
       <x:c r="E36" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="str"/>
+      <x:c r="F36" s="11" t="n">
+        <x:v>153</x:v>
+      </x:c>
       <x:c r="G36" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I36" s="10" t="str"/>
+      <x:c r="I36" s="10" t="str">
+        <x:v>森森动画</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="11" t="str">
@@ -1935,14 +2023,18 @@
       <x:c r="E39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="str"/>
+      <x:c r="F39" s="11" t="n">
+        <x:v>130</x:v>
+      </x:c>
       <x:c r="G39" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I39" s="10" t="str"/>
+      <x:c r="I39" s="10" t="str">
+        <x:v>追更漫剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="11" t="str">
@@ -1958,14 +2050,18 @@
       <x:c r="E40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F40" s="11" t="str"/>
+      <x:c r="F40" s="11" t="n">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="G40" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I40" s="10" t="str"/>
+      <x:c r="I40" s="10" t="str">
+        <x:v>星漫世界</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="11" t="str">
@@ -1981,14 +2077,18 @@
       <x:c r="E41" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F41" s="11" t="str"/>
+      <x:c r="F41" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
       <x:c r="G41" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I41" s="10" t="str"/>
+      <x:c r="I41" s="10" t="str">
+        <x:v>咕咕漫剧</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="11" t="str">
@@ -2112,14 +2212,18 @@
       <x:c r="E46" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F46" s="11" t="str"/>
+      <x:c r="F46" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
       <x:c r="G46" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H46" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I46" s="10" t="str"/>
+      <x:c r="I46" s="10" t="str">
+        <x:v>绿豆儿</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="11" t="str">
@@ -2135,14 +2239,18 @@
       <x:c r="E47" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F47" s="11" t="str"/>
+      <x:c r="F47" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="G47" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H47" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I47" s="10" t="str"/>
+      <x:c r="I47" s="10" t="str">
+        <x:v>在下七七</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4931,10 +5039,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>349</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>41.4%</x:v>
+        <x:v>43.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4942,10 +5050,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>277</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>32.8%</x:v>
+        <x:v>30.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4953,10 +5061,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>25.8%</x:v>
+        <x:v>26.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -4980,7 +5088,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>12%</x:v>
@@ -4991,10 +5099,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>355</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>44.3%</x:v>
+        <x:v>43.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5002,7 +5110,7 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>11.5%</x:v>
@@ -5013,10 +5121,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>258</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>32.2%</x:v>
+        <x:v>32.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -5369,32 +5477,32 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B49" s="11" t="n">
-        <x:v>795</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="C49" s="11" t="str">
-        <x:v>94.2%</x:v>
+        <x:v>98.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP托管</x:v>
       </x:c>
       <x:c r="B50" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C50" s="11" t="str">
-        <x:v>5.0%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -5480,7 +5588,7 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>喵喵说书</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
         <x:v>4</x:v>
@@ -5489,7 +5597,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
         <x:v>4</x:v>
@@ -5498,7 +5606,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
-        <x:v>取瘾书屋</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
         <x:v>4</x:v>
@@ -5507,7 +5615,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
-        <x:v>清风短剧场</x:v>
+        <x:v>取瘾书屋</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
         <x:v>4</x:v>
@@ -5516,7 +5624,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
-        <x:v>亦辰动漫</x:v>
+        <x:v>清风短剧场</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
         <x:v>4</x:v>
@@ -5525,7 +5633,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>暖星追剧</x:v>
+        <x:v>亦辰动漫</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
         <x:v>4</x:v>
@@ -5534,16 +5642,16 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>暖星追剧</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>一张不够花</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
         <x:v>3</x:v>
@@ -5552,7 +5660,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
         <x:v>3</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rd78a46e4dcaa454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Ra8cbc6ffd48546af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R9d1a555caeec411b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rb2f92ac69cd142ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="Rdc11083628be4c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R7af60343d1784954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Rd36cd6c9959e4197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rd84a15d38a534840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="R9dd6dd9c2baa4c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R1a08fcf374cf48a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -351,7 +351,7 @@
         <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>375</x:v>
@@ -364,7 +364,7 @@
       </x:c>
       <x:c r="G2" s="11" t="str"/>
       <x:c r="H2" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -446,25 +446,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>包子里的真心</x:v>
+        <x:v>谁说纨绔不能当状元</x:v>
       </x:c>
       <x:c r="C6" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="E6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>7514</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
+        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -472,22 +472,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>天灾囤货录，善恶见人心</x:v>
+        <x:v>包子里的真心</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>种田囤货 / 现实反转</x:v>
+        <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>852</x:v>
+        <x:v>7514</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
@@ -498,22 +498,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>收租老汉</x:v>
+        <x:v>天灾囤货录，善恶见人心</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>121</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E8" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>种田囤货 / 现实反转</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>8368</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
@@ -524,25 +524,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>谁说纨绔不能当状元</x:v>
+        <x:v>收租老汉</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>788</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E9" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>572</x:v>
+        <x:v>8368</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -574,23 +574,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E11" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="n">
+        <x:v>1834</x:v>
+      </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -598,25 +600,23 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>重生归来，四小姐她不装了</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="n">
-        <x:v>371</x:v>
-      </x:c>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str"/>
       <x:c r="H12" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -624,23 +624,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
+        <x:v>重生归来，四小姐她不装了</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E13" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="str"/>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="n">
+        <x:v>371</x:v>
+      </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -648,23 +650,23 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E14" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str"/>
       <x:c r="H14" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -672,25 +674,23 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E15" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="n">
-        <x:v>1834</x:v>
-      </x:c>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="str"/>
       <x:c r="H15" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -820,25 +820,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>半梦半醒半清欢</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+      <x:c r="G21" s="11" t="str"/>
       <x:c r="H21" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -846,23 +844,23 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>半梦半醒半清欢</x:v>
+        <x:v>商场收回档口我成了全城的供应商</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E22" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G22" s="11" t="str"/>
       <x:c r="H22" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -870,23 +868,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>商场收回档口我成了全城的供应商</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C23" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E23" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>都市职场</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -918,23 +918,23 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
       </x:c>
       <x:c r="C25" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E25" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="G25" s="11" t="str"/>
       <x:c r="H25" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -942,23 +942,23 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E26" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
       </x:c>
       <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-22</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1016,25 +1016,25 @@
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="10" t="str">
-        <x:v>方寸宅院见公道</x:v>
+        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G2" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>豆豆动漫</x:v>
+        <x:v>暖夏短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1043,25 +1043,25 @@
       </x:c>
       <x:c r="B3" s="11"/>
       <x:c r="C3" s="10" t="str">
-        <x:v>卖鱼大叔，请多指教</x:v>
+        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G3" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>久久剧场</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1070,25 +1070,25 @@
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="10" t="str">
-        <x:v>燃栀：栀子花开恰逢少年</x:v>
+        <x:v>大婚当日立规矩，这婚我不结了</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>AI漫剧老六</x:v>
+        <x:v>云影漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1097,25 +1097,25 @@
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="10" t="str">
-        <x:v>父爱护女归家</x:v>
+        <x:v>假千金归来，全家后悔莫及</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>丽佳漫剧场</x:v>
+        <x:v>小桃红动画</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1124,25 +1124,25 @@
       </x:c>
       <x:c r="B6" s="11"/>
       <x:c r="C6" s="10" t="str">
-        <x:v>小公爷道，老子可是何美丽的男人呀第一季</x:v>
+        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
-        <x:v>121</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>亦辰动漫</x:v>
+        <x:v>漫漫画丫头</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1151,25 +1151,25 @@
       </x:c>
       <x:c r="B7" s="11"/>
       <x:c r="C7" s="10" t="str">
-        <x:v>重生摊牌身份，众人惊了</x:v>
+        <x:v>和媳妇离家出走，享受幸福人生</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>139</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>都市职场 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
-        <x:v>小清书漫</x:v>
+        <x:v>小尘剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1178,25 +1178,25 @@
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="10" t="str">
-        <x:v>一顾见晚星</x:v>
+        <x:v>闻心：京华稚园录</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>三针剧场</x:v>
+        <x:v>阿云剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1205,25 +1205,25 @@
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="10" t="str">
-        <x:v>前妻逼我献血，我转身离开</x:v>
+        <x:v>猪场风起</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>104</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>榴莲漫剧</x:v>
+        <x:v>栗子说漫</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1232,25 +1232,25 @@
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="10" t="str">
-        <x:v>妈妈的天下第一好</x:v>
+        <x:v>胡同走出的真少爷</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>家庭伦理 / 古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>萌星看剧</x:v>
+        <x:v>二里清风</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1259,25 +1259,25 @@
       </x:c>
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="10" t="str">
-        <x:v>办公室的顺手人情</x:v>
+        <x:v>赘婿逆袭：我的亿万人生</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>小 淇</x:v>
+        <x:v>清欢古风剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1286,25 +1286,25 @@
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="10" t="str">
-        <x:v>恩与仇之间的距离</x:v>
+        <x:v>我住帐篷那天，整个豪宅区慌了</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>艾微动画剧场</x:v>
+        <x:v>95漫画</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1313,25 +1313,25 @@
       </x:c>
       <x:c r="B13" s="11"/>
       <x:c r="C13" s="10" t="str">
-        <x:v>被女神抛弃：我却在荒岛吃香喝辣</x:v>
+        <x:v>万界轮回，我有亿万神话词条加身</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>美食治愈 / 战神异能</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>麋鹿漫</x:v>
+        <x:v>云间漫剧-零七</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1340,25 +1340,25 @@
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="10" t="str">
-        <x:v>执笔春红</x:v>
+        <x:v>姐姐不买单我慌了</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>小尘剧场</x:v>
+        <x:v>表妹剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1367,16 +1367,16 @@
       </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="10" t="str">
-        <x:v>卯卯入帅府，全家乐开花第二季</x:v>
+        <x:v>烟火与匠心</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>106</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
         <x:v>未标注</x:v>
@@ -1385,7 +1385,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>念⭐️念</x:v>
+        <x:v>馆长玉先生剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1394,16 +1394,16 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="10" t="str">
-        <x:v>我拿五万去扶贫，男友家却有三片海</x:v>
+        <x:v>她契约的都是星际大佬</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
         <x:v>未标注</x:v>
@@ -1412,7 +1412,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>小菲菲动画</x:v>
+        <x:v>阅友动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1421,25 +1421,25 @@
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="10" t="str">
-        <x:v>全家偷听我心声后，假千金慌了</x:v>
+        <x:v>空间雷异能：废墟求生录</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>阿晚漫馆</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1448,25 +1448,25 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="10" t="str">
-        <x:v>相亲当天，未婚妻的男助理抢我车位</x:v>
+        <x:v>跨物种相亲，我连夜扛着冰山跑路</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
-        <x:v>小丘剧场</x:v>
+        <x:v>菁禾</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1475,25 +1475,25 @@
       </x:c>
       <x:c r="B19" s="11"/>
       <x:c r="C19" s="10" t="str">
-        <x:v>百万房车，被室友擅用当婚车</x:v>
+        <x:v>疯丫头与花薄少：六宝助功</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>小牛文馆</x:v>
+        <x:v>AI梦</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1502,25 +1502,25 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="10" t="str">
-        <x:v>十八次返岗申请</x:v>
+        <x:v>礼金局中局</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>星禾与众剧场</x:v>
+        <x:v>AI 风华</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1529,25 +1529,25 @@
       </x:c>
       <x:c r="B21" s="11"/>
       <x:c r="C21" s="10" t="str">
-        <x:v>重回太子遇险时，我把救命之功让给嫡姐</x:v>
+        <x:v>看我赶山养家第三季两情相悦</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>年代怀旧 / 古装宫廷</x:v>
+        <x:v>种田囤货 / 婚姻情感</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
-        <x:v>墨雨星河</x:v>
+        <x:v>知夏短剧</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1556,25 +1556,25 @@
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="10" t="str">
-        <x:v>出渊狂龙</x:v>
+        <x:v>颠婆穿书：我在年代文里当德华</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>132</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>幻想九月剧场</x:v>
+        <x:v>武汉卡看漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1583,25 +1583,25 @@
       </x:c>
       <x:c r="B23" s="11"/>
       <x:c r="C23" s="10" t="str">
-        <x:v>不赴旧约：她的人生重新开场</x:v>
+        <x:v>八零姊妹破局新生</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>年代怀旧 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>喵喵说书</x:v>
+        <x:v>朝夕影堂</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1610,79 +1610,75 @@
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="10" t="str">
-        <x:v>麦浪风云</x:v>
+        <x:v>比武招亲，我竟成了女王爷的夫婿</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>南辞说漫</x:v>
+        <x:v>诺威剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B25" s="11"/>
       <x:c r="C25" s="10" t="str">
-        <x:v>你管这叫灾星首富家都旺翻了！</x:v>
+        <x:v>清风不渡旧时寒</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="n">
-        <x:v>139</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str"/>
       <x:c r="G25" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I25" s="10" t="str">
-        <x:v>尘埃漫</x:v>
-      </x:c>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="I25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="10" t="str">
-        <x:v>蹭饭一年，她们终于吃不起了</x:v>
+        <x:v>灶边的规矩</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>32</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H26" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>云景动漫剧场</x:v>
+        <x:v>空白漫</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1691,25 +1687,25 @@
       </x:c>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="10" t="str">
-        <x:v>丈母娘百万招婿，我的冰山老婆</x:v>
+        <x:v>神女归途</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>星界Ai</x:v>
+        <x:v>河虾动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1718,25 +1714,25 @@
       </x:c>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="10" t="str">
-        <x:v>一村人养一个神第二季</x:v>
+        <x:v>团宠驾到：督军府的满级小锦鲤</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>93</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>木偶说漫</x:v>
+        <x:v>每日沙雕速递</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1745,16 +1741,16 @@
       </x:c>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="10" t="str">
-        <x:v>无冕之根</x:v>
+        <x:v>我大华第一逍遥王</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>689</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -1763,7 +1759,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>影留</x:v>
+        <x:v>口水显眼包</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1772,25 +1768,25 @@
       </x:c>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="10" t="str">
-        <x:v>神女归途</x:v>
+        <x:v>月子第一天，婆婆离世了</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>169</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
-        <x:v>河虾动漫</x:v>
+        <x:v>锋芒映剧</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1799,25 +1795,25 @@
       </x:c>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="10" t="str">
-        <x:v>福宝治愈全世界，家有萌娃岁岁安第二季</x:v>
+        <x:v>择日复婚</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>紫怡漫剧场</x:v>
+        <x:v>森森动画</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1826,25 +1822,25 @@
       </x:c>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="10" t="str">
-        <x:v>月子第一天，婆婆离世了</x:v>
+        <x:v>王府小祖宗，捡啥啥是宝</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>锋芒映剧</x:v>
+        <x:v>诗婳-君懿看剧</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1859,7 +1855,7 @@
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>55</x:v>
@@ -1880,25 +1876,25 @@
       </x:c>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="10" t="str">
-        <x:v>王府小祖宗，捡啥啥是宝</x:v>
+        <x:v>我在急诊室摸鱼，全院跪求出手！</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
-        <x:v>诗婳-君懿看剧</x:v>
+        <x:v>追更漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1907,25 +1903,25 @@
       </x:c>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="10" t="str">
-        <x:v>八零：盒饭女王从小摊开始</x:v>
+        <x:v>小小力量大，从家属院开始当家</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>年代怀旧 / 都市职场 / 美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
-        <x:v>东瓜剧场</x:v>
+        <x:v>绿豆儿</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1934,25 +1930,25 @@
       </x:c>
       <x:c r="B36" s="11"/>
       <x:c r="C36" s="10" t="str">
-        <x:v>择日复婚</x:v>
+        <x:v>八零：盒饭女王从小摊开始</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>153</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>年代怀旧 / 都市职场 / 美食治愈</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>森森动画</x:v>
+        <x:v>东瓜剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1961,25 +1957,25 @@
       </x:c>
       <x:c r="B37" s="11"/>
       <x:c r="C37" s="10" t="str">
-        <x:v>寒门嫡女：携空间护母妹谋生计</x:v>
+        <x:v>大婚当天，前任坐在我的婚床</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>173</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H37" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>喵喵说书</x:v>
+        <x:v>星漫世界</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1988,25 +1984,25 @@
       </x:c>
       <x:c r="B38" s="11"/>
       <x:c r="C38" s="10" t="str">
-        <x:v>杨巧替嫁残疾英雄，婆家宠我青云志</x:v>
+        <x:v>福宝治愈全世界，家有萌娃岁岁安第二季</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>143</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H38" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感 / 现实反转</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
-        <x:v>游世剧场</x:v>
+        <x:v>紫怡漫剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2015,25 +2011,25 @@
       </x:c>
       <x:c r="B39" s="11"/>
       <x:c r="C39" s="10" t="str">
-        <x:v>我在急诊室摸鱼，全院跪求出手！</x:v>
+        <x:v>方寸宅院见公道</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G39" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
-        <x:v>追更漫剧</x:v>
+        <x:v>豆豆动漫</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2042,25 +2038,25 @@
       </x:c>
       <x:c r="B40" s="11"/>
       <x:c r="C40" s="10" t="str">
-        <x:v>大婚当天，前任坐在我的婚床</x:v>
+        <x:v>重生摊牌身份，众人惊了</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G40" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>都市职场 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>小清书漫</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2069,25 +2065,25 @@
       </x:c>
       <x:c r="B41" s="11"/>
       <x:c r="C41" s="10" t="str">
-        <x:v>云程赴佳期，一屋欢闹伴韶光</x:v>
+        <x:v>我拿五万去扶贫，男友家却有三片海</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G41" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str">
-        <x:v>咕咕漫剧</x:v>
+        <x:v>小菲菲动画</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2096,25 +2092,25 @@
       </x:c>
       <x:c r="B42" s="11"/>
       <x:c r="C42" s="10" t="str">
-        <x:v>我家后山藏真龙</x:v>
+        <x:v>恩与仇之间的距离</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G42" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H42" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str">
-        <x:v>剧鲸剧场</x:v>
+        <x:v>艾微动画剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2123,25 +2119,25 @@
       </x:c>
       <x:c r="B43" s="11"/>
       <x:c r="C43" s="10" t="str">
-        <x:v>穿成凡虎，我吞噬成神</x:v>
+        <x:v>前妻逼我献血，我转身离开</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G43" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H43" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str">
-        <x:v>寒冰剧场</x:v>
+        <x:v>榴莲漫剧</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2150,25 +2146,25 @@
       </x:c>
       <x:c r="B44" s="11"/>
       <x:c r="C44" s="10" t="str">
-        <x:v>我大华第一逍遥王</x:v>
+        <x:v>一顾见晚星</x:v>
       </x:c>
       <x:c r="D44" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
-        <x:v>510</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G44" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H44" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str">
-        <x:v>口水显眼包</x:v>
+        <x:v>三针剧场</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2177,7 +2173,7 @@
       </x:c>
       <x:c r="B45" s="11"/>
       <x:c r="C45" s="10" t="str">
-        <x:v>团宠驾到：督军府的满级小锦鲤</x:v>
+        <x:v>相亲坐错桌，陆总他追着不放</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
         <x:v>2026-08-30</x:v>
@@ -2186,16 +2182,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
-        <x:v>254</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G45" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H45" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str">
-        <x:v>每日沙雕速递</x:v>
+        <x:v>喵琪琪追剧</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -2204,52 +2200,25 @@
       </x:c>
       <x:c r="B46" s="11"/>
       <x:c r="C46" s="10" t="str">
-        <x:v>小小力量大，从家属院开始当家</x:v>
+        <x:v>相亲当天，未婚妻的男助理抢我车位</x:v>
       </x:c>
       <x:c r="D46" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F46" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G46" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H46" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
       <x:c r="I46" s="10" t="str">
-        <x:v>绿豆儿</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B47" s="11"/>
-      <x:c r="C47" s="10" t="str">
-        <x:v>手打人间味</x:v>
-      </x:c>
-      <x:c r="D47" s="11" t="str">
-        <x:v>2026-08-30</x:v>
-      </x:c>
-      <x:c r="E47" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F47" s="11" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G47" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H47" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I47" s="10" t="str">
-        <x:v>在下七七</x:v>
+        <x:v>小丘剧场</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2327,7 +2296,7 @@
         <x:v>7514</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2356,7 +2325,7 @@
         <x:v>852</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2385,7 +2354,7 @@
         <x:v>8368</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2412,7 +2381,7 @@
       </x:c>
       <x:c r="H5" s="11" t="str"/>
       <x:c r="I5" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2439,7 +2408,7 @@
       </x:c>
       <x:c r="H6" s="11" t="str"/>
       <x:c r="I6" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2447,26 +2416,26 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>山王传奇</x:v>
       </x:c>
       <x:c r="C7" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
-        <x:v>136</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str"/>
       <x:c r="I7" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜7次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2474,26 +2443,26 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>我妈装穷来认我</x:v>
+        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
       </x:c>
       <x:c r="C8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str"/>
       <x:c r="I8" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2501,26 +2470,26 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>分家只给破枪，我听兽语富全屯</x:v>
+        <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
       <x:c r="C9" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str"/>
       <x:c r="I9" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜6次、累计15次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2549,7 +2518,7 @@
         <x:v>4442</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜6次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜6次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2557,26 +2526,26 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>山王传奇</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C11" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜6次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜6次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2584,26 +2553,26 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>我妈装穷来认我</x:v>
       </x:c>
       <x:c r="C12" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str"/>
       <x:c r="I12" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜6次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2611,26 +2580,26 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>悍妻替嫁，从前说</x:v>
+        <x:v>分家只给破枪，我听兽语富全屯</x:v>
       </x:c>
       <x:c r="C13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2638,26 +2607,26 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
+        <x:v>这门婚我不嫁了</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2665,7 +2634,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>八零之老妈在厂长家当后妈</x:v>
+        <x:v>逆流年代：从1970开始种田养家</x:v>
       </x:c>
       <x:c r="C15" s="11" t="n">
         <x:v>6</x:v>
@@ -2674,17 +2643,17 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
-        <x:v>156</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜6次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；110集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2692,26 +2661,26 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C16" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2719,28 +2688,26 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C17" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="str"/>
       <x:c r="I17" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计10次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2748,26 +2715,26 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
+        <x:v>悍妻替嫁，从前说</x:v>
       </x:c>
       <x:c r="C18" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2775,26 +2742,26 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>九二年，他塞给我五百块</x:v>
+        <x:v>暴雪见人心</x:v>
       </x:c>
       <x:c r="C19" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2802,26 +2769,26 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>这门婚我不嫁了</x:v>
+        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
       </x:c>
       <x:c r="C20" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计7次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2829,7 +2796,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>逆流年代：从1970开始种田养家</x:v>
+        <x:v>八零之老妈在厂长家当后妈</x:v>
       </x:c>
       <x:c r="C21" s="11" t="n">
         <x:v>5</x:v>
@@ -2838,17 +2805,17 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
-        <x:v>110</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；110集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2856,7 +2823,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>傻女重生记，睁眼后盖房发家</x:v>
+        <x:v>激活美食治愈系统,我靠摆摊火遍了整座城市</x:v>
       </x:c>
       <x:c r="C22" s="11" t="n">
         <x:v>5</x:v>
@@ -2865,17 +2832,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；177集长剧集；题材契合爆款主线（都市职场 / 美食治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2902,7 +2869,7 @@
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2910,26 +2877,26 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
+        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
       </x:c>
       <x:c r="C24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
-        <x:v>119</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2956,7 +2923,7 @@
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜5次、累计5次，起量能力已被验证；仿真人制作；52集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜5次、累计5次，起量能力已被验证；仿真人制作；52集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2964,26 +2931,26 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C26" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计10次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2991,26 +2958,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>暴雪见人心</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C27" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="G27" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="H27" s="11" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H27" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3018,28 +2987,26 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>爷爷不请七遍不动筷</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C28" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G28" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H28" s="11" t="n">
-        <x:v>490</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计9次，起量能力已被验证；仿真人制作；50集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计11次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3047,7 +3014,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>云岭藏金，真心为聘</x:v>
+        <x:v>这个姨娘不一般</x:v>
       </x:c>
       <x:c r="C29" s="11" t="n">
         <x:v>4</x:v>
@@ -3056,17 +3023,17 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G29" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str"/>
       <x:c r="I29" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3074,7 +3041,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
+        <x:v>重生凛冬跟随囤货</x:v>
       </x:c>
       <x:c r="C30" s="11" t="n">
         <x:v>4</x:v>
@@ -3083,17 +3050,17 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G30" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计8次，起量能力已被验证；81集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3101,26 +3068,26 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>这个姨娘不一般</x:v>
+        <x:v>九二年，他塞给我五百块</x:v>
       </x:c>
       <x:c r="C31" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G31" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3128,26 +3095,26 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>魔力情谊之我一个人来的</x:v>
+        <x:v>傻女重生记，睁眼后盖房发家</x:v>
       </x:c>
       <x:c r="C32" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G32" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3155,26 +3122,26 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>三百块的信任，九十万的真相</x:v>
+        <x:v>医风秩序线</x:v>
       </x:c>
       <x:c r="C33" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；89集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3182,7 +3149,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>199的排场，48万的账</x:v>
+        <x:v>各生归途</x:v>
       </x:c>
       <x:c r="C34" s="11" t="n">
         <x:v>4</x:v>
@@ -3191,17 +3158,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str"/>
       <x:c r="I34" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；82集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3209,7 +3176,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>大力幼崽到处捡爹</x:v>
+        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
       </x:c>
       <x:c r="C35" s="11" t="n">
         <x:v>4</x:v>
@@ -3218,17 +3185,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str"/>
       <x:c r="I35" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3236,26 +3203,26 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>撞大运后我在县城买了个院</x:v>
+        <x:v>一墙之隔的求救声</x:v>
       </x:c>
       <x:c r="C36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str"/>
       <x:c r="I36" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计6次，起量能力已被验证；120集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；88集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3263,7 +3230,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>一墙之隔的求救声</x:v>
+        <x:v>五福临门，八方报喜</x:v>
       </x:c>
       <x:c r="C37" s="11" t="n">
         <x:v>4</x:v>
@@ -3275,14 +3242,14 @@
         <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G37" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str"/>
       <x:c r="I37" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；88集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3290,7 +3257,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>寒庭有犬鸣</x:v>
+        <x:v>大唐：我真没想当国舅爷啊</x:v>
       </x:c>
       <x:c r="C38" s="11" t="n">
         <x:v>4</x:v>
@@ -3299,17 +3266,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G38" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str"/>
       <x:c r="I38" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；71集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3336,7 +3303,7 @@
       </x:c>
       <x:c r="H39" s="11" t="str"/>
       <x:c r="I39" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；61集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；61集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3344,26 +3311,26 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
+        <x:v>一辆旧中巴奔向新生活</x:v>
       </x:c>
       <x:c r="C40" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G40" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str"/>
       <x:c r="I40" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计4次，起量能力已被验证；82集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3371,7 +3338,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>一辆旧中巴奔向新生活</x:v>
+        <x:v>老婆每月给别人一万五，离婚时她后悔了</x:v>
       </x:c>
       <x:c r="C41" s="11" t="n">
         <x:v>4</x:v>
@@ -3380,71 +3347,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
-        <x:v>82</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G41" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str"/>
       <x:c r="I41" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计4次，起量能力已被验证；82集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="11" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B42" s="10" t="str">
-        <x:v>情起屋檐下</x:v>
-      </x:c>
-      <x:c r="C42" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D42" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="str">
-        <x:v>2026-08-18</x:v>
-      </x:c>
-      <x:c r="F42" s="11" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G42" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="H42" s="11" t="str"/>
-      <x:c r="I42" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计4次，起量能力已被验证；66集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="11" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B43" s="10" t="str">
-        <x:v>老婆每月给别人一万五，离婚时她后悔了</x:v>
-      </x:c>
-      <x:c r="C43" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D43" s="11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E43" s="11" t="str">
-        <x:v>2026-08-18</x:v>
-      </x:c>
-      <x:c r="F43" s="11" t="n">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G43" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H43" s="11" t="str"/>
-      <x:c r="I43" s="10" t="str">
-        <x:v>8-14~8-20两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；113集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-15~8-21两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；113集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4403,22 +4316,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>拒绝996，我成为赶海大佬了第三季</x:v>
+        <x:v>穿成团宠后我靠读心逆袭</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>123</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F33" s="10" t="str">
-        <x:v>种田囤货 / 都市职场</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G33" s="10" t="str">
-        <x:v>亦辰动漫</x:v>
+        <x:v>星梦好剧</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
-        <x:v>123集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 都市职场）；续季/系列续作，有前作热度背书；发布账号「亦辰动漫」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
       </x:c>
       <x:c r="I33" s="11" t="n">
         <x:v>7</x:v>
@@ -4432,22 +4345,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>穿成团宠后我靠读心逆袭</x:v>
+        <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F34" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G34" s="10" t="str">
-        <x:v>星梦好剧</x:v>
+        <x:v>陈柯</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I34" s="11" t="n">
         <x:v>7</x:v>
@@ -4461,22 +4374,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
+        <x:v>藏在婚姻里的谎言</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
-        <x:v>200</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F35" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="G35" s="10" t="str">
-        <x:v>陈柯</x:v>
+        <x:v>九鲤动漫</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="I35" s="11" t="n">
         <x:v>7</x:v>
@@ -4490,22 +4403,22 @@
         <x:v>08·29</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>藏在婚姻里的谎言</x:v>
+        <x:v>让你守边塞，你用汉堡养兵？第二季江南篇</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F36" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G36" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
+        <x:v>浮绘剧场</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I36" s="11" t="n">
         <x:v>7</x:v>
@@ -5039,10 +4952,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>367</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>43.5%</x:v>
+        <x:v>43.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -5050,10 +4963,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>256</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>30.3%</x:v>
+        <x:v>30.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5061,10 +4974,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>221</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>26.2%</x:v>
+        <x:v>26.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -5088,10 +5001,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>12%</x:v>
+        <x:v>12.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5099,10 +5012,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>367</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>43.6%</x:v>
+        <x:v>43.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5110,10 +5023,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>11.5%</x:v>
+        <x:v>11.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5121,10 +5034,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>275</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>32.7%</x:v>
+        <x:v>32.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -5148,10 +5061,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>333</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>39.5%</x:v>
+        <x:v>39.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -5159,7 +5072,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>159</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>18.8%</x:v>
@@ -5170,10 +5083,10 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>11.0%</x:v>
+        <x:v>10.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5181,32 +5094,32 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>10.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>8.8%</x:v>
+        <x:v>8.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="10" t="str">
-        <x:v>战神/异能/爽文</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.8%</x:v>
+        <x:v>8.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5214,7 +5127,7 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
         <x:v>7.0%</x:v>
@@ -5225,10 +5138,10 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>6.4%</x:v>
+        <x:v>6.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5236,7 +5149,7 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
         <x:v>5.3%</x:v>
@@ -5247,10 +5160,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>4.9%</x:v>
+        <x:v>5.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -5271,324 +5184,328 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>上榜19次</x:v>
+        <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>1.4%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>2.5%</x:v>
+        <x:v>1.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>1.5%</x:v>
+        <x:v>1.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>4.4%</x:v>
+        <x:v>2.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>4.0%</x:v>
+        <x:v>1.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>5.7%</x:v>
+        <x:v>4.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>8.2%</x:v>
+        <x:v>4.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>164</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>19.4%</x:v>
+        <x:v>5.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
+        <x:v>上榜3次</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>9.2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="10" t="str">
+        <x:v>上榜2次</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="str">
+        <x:v>17.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="10" t="str">
         <x:v>上榜1次</x:v>
       </x:c>
-      <x:c r="B45" s="11" t="n">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="C45" s="11" t="str">
-        <x:v>49.3%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="22" customHeight="1">
-      <x:c r="A47" s="14" t="str">
+      <x:c r="B47" s="11" t="n">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>49.7%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="24" customHeight="1">
-      <x:c r="A48" s="5" t="str">
+    <x:row r="50" ht="24" customHeight="1">
+      <x:c r="A50" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B48" t="str">
+      <x:c r="B50" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C48" t="str">
+      <x:c r="C50" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="10" t="str">
-        <x:v>CP自营</x:v>
-      </x:c>
-      <x:c r="B49" s="11" t="n">
-        <x:v>834</x:v>
-      </x:c>
-      <x:c r="C49" s="11" t="str">
-        <x:v>98.8%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="10" t="str">
-        <x:v>CP托管</x:v>
-      </x:c>
-      <x:c r="B50" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C50" s="11" t="str">
-        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>98.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
+        <x:v>CP托管</x:v>
+      </x:c>
+      <x:c r="B52" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C52" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="B53" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="10" t="str">
         <x:v>番茄原创</x:v>
       </x:c>
-      <x:c r="B52" s="11" t="n">
+      <x:c r="B54" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C52" s="11" t="str">
+      <x:c r="C54" s="11" t="str">
         <x:v>0.2%</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="22" customHeight="1">
-      <x:c r="A54" s="14" t="str">
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="14" t="str">
         <x:v>发布抖音号TOP15</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="24" customHeight="1">
-      <x:c r="A55" s="5" t="str">
+    <x:row r="57" ht="24" customHeight="1">
+      <x:c r="A57" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B55" t="str">
+      <x:c r="B57" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C55" t="str">
+      <x:c r="C57" t="str">
         <x:v>占比</x:v>
       </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="B56" s="11" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C56" s="11" t="str"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
-      </x:c>
-      <x:c r="B57" s="11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C57" s="11" t="str"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B58" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C58" s="11" t="str"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C59" s="11" t="str"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>不兜</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>喵喵说书</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
         <x:v>4</x:v>
@@ -5597,7 +5514,7 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
         <x:v>4</x:v>
@@ -5606,7 +5523,7 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
         <x:v>4</x:v>
@@ -5615,7 +5532,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
-        <x:v>取瘾书屋</x:v>
+        <x:v>不兜</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
         <x:v>4</x:v>
@@ -5624,7 +5541,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
-        <x:v>清风短剧场</x:v>
+        <x:v>喵喵说书</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
         <x:v>4</x:v>
@@ -5633,7 +5550,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>亦辰动漫</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
         <x:v>4</x:v>
@@ -5642,7 +5559,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>暖星追剧</x:v>
+        <x:v>取瘾书屋</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
         <x:v>4</x:v>
@@ -5651,123 +5568,141 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>清风短剧场</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>亦辰动漫</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C70" s="11" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="10" t="str">
+        <x:v>暖星追剧</x:v>
+      </x:c>
+      <x:c r="B71" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C71" s="11" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="10" t="str">
+        <x:v>一张不够花</x:v>
+      </x:c>
+      <x:c r="B72" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C70" s="11" t="str"/>
-    </x:row>
-    <x:row r="72" ht="22" customHeight="1">
-      <x:c r="A72" s="14" t="str">
+      <x:c r="C72" s="11" t="str"/>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="24" customHeight="1">
-      <x:c r="A73" s="5" t="str">
+    <x:row r="75" ht="24" customHeight="1">
+      <x:c r="A75" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B73" t="str">
+      <x:c r="B75" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C73" t="str">
+      <x:c r="C75" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
-      </x:c>
-      <x:c r="B74" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C74" s="11" t="str">
-        <x:v>19.0%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
-      </x:c>
-      <x:c r="B75" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C75" s="11" t="str">
-        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
+        <x:v>现实反转/人性</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C81" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B82" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C82" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B81" s="11" t="n">
+      <x:c r="B83" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C81" s="11" t="str">
+      <x:c r="C83" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -5777,9 +5712,9 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A47:C47"/>
-    <x:mergeCell ref="A54:C54"/>
-    <x:mergeCell ref="A72:C72"/>
+    <x:mergeCell ref="A49:C49"/>
+    <x:mergeCell ref="A56:C56"/>
+    <x:mergeCell ref="A74:C74"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R7af60343d1784954"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Rd36cd6c9959e4197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rd84a15d38a534840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="R9dd6dd9c2baa4c1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R1a08fcf374cf48a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rc1514b873a3c43b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Rc880ef7e66ba46f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R34579a5661544d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rc743ae3db9d648ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="Re70cf5785f834409"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -309,12 +309,13 @@
   <x:cols>
     <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -325,21 +326,24 @@
         <x:v>剧名</x:v>
       </x:c>
       <x:c r="C1" t="str">
+        <x:v>预计上线</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
         <x:v>上榜次数</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="E1" t="str">
         <x:v>集数</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="F1" t="str">
         <x:v>制作风格</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="G1" t="str">
         <x:v>主题分类</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="H1" t="str">
         <x:v>8月消耗(元)</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="I1" t="str">
         <x:v>上榜日期</x:v>
       </x:c>
     </x:row>
@@ -350,20 +354,23 @@
       <x:c r="B2" s="10" t="str">
         <x:v>1977山猎重生，我以余生偿前错</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="n">
+      <x:c r="C2" s="11" t="str">
+        <x:v>08-10 20:00</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
+      <x:c r="E2" s="10" t="n">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="E2" s="10" t="str">
+      <x:c r="F2" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F2" s="10" t="str">
+      <x:c r="G2" s="10" t="str">
         <x:v>年代怀旧 / 种田囤货</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str"/>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="H2" s="11" t="str"/>
+      <x:c r="I2" s="10" t="str">
         <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
@@ -374,22 +381,25 @@
       <x:c r="B3" s="10" t="str">
         <x:v>占院风波</x:v>
       </x:c>
-      <x:c r="C3" s="11" t="n">
+      <x:c r="C3" s="11" t="str">
+        <x:v>08-08 17:00</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="n">
+      <x:c r="E3" s="10" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E3" s="10" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F3" s="10" t="str">
+      <x:c r="G3" s="10" t="str">
         <x:v>现实反转</x:v>
       </x:c>
-      <x:c r="G3" s="11" t="n">
+      <x:c r="H3" s="11" t="n">
         <x:v>4289</x:v>
       </x:c>
-      <x:c r="H3" s="10" t="str">
+      <x:c r="I3" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
@@ -400,20 +410,23 @@
       <x:c r="B4" s="10" t="str">
         <x:v>婆婆要我上交工资卡，我反手只留两千</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="n">
+      <x:c r="C4" s="11" t="str">
+        <x:v>08-09 11:00</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="n">
+      <x:c r="E4" s="10" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E4" s="10" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F4" s="10" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="G4" s="11" t="str"/>
-      <x:c r="H4" s="10" t="str">
+      <x:c r="H4" s="11" t="str"/>
+      <x:c r="I4" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
@@ -424,20 +437,23 @@
       <x:c r="B5" s="10" t="str">
         <x:v>灶下煤之自由篇</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="11" t="str">
+        <x:v>08-11 16:40</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
+      <x:c r="E5" s="10" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>种田囤货</x:v>
       </x:c>
-      <x:c r="G5" s="11" t="str"/>
-      <x:c r="H5" s="10" t="str">
+      <x:c r="H5" s="11" t="str"/>
+      <x:c r="I5" s="10" t="str">
         <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
       </x:c>
     </x:row>
@@ -448,22 +464,25 @@
       <x:c r="B6" s="10" t="str">
         <x:v>谁说纨绔不能当状元</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="11" t="str">
+        <x:v>08-14 09:00</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
+      <x:c r="E6" s="10" t="n">
         <x:v>788</x:v>
       </x:c>
-      <x:c r="E6" s="10" t="str">
+      <x:c r="F6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F6" s="10" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="n">
+      <x:c r="H6" s="11" t="n">
         <x:v>572</x:v>
       </x:c>
-      <x:c r="H6" s="10" t="str">
+      <x:c r="I6" s="10" t="str">
         <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
@@ -474,22 +493,25 @@
       <x:c r="B7" s="10" t="str">
         <x:v>包子里的真心</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="11" t="str">
+        <x:v>08-07 17:29</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="n">
+      <x:c r="E7" s="10" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="n">
+      <x:c r="H7" s="11" t="n">
         <x:v>7514</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="str">
+      <x:c r="I7" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
       </x:c>
     </x:row>
@@ -500,22 +522,25 @@
       <x:c r="B8" s="10" t="str">
         <x:v>天灾囤货录，善恶见人心</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="C8" s="11" t="str">
+        <x:v>08-10 16:30</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="n">
+      <x:c r="E8" s="10" t="n">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="E8" s="10" t="str">
+      <x:c r="F8" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F8" s="10" t="str">
+      <x:c r="G8" s="10" t="str">
         <x:v>种田囤货 / 现实反转</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="n">
+      <x:c r="H8" s="11" t="n">
         <x:v>852</x:v>
       </x:c>
-      <x:c r="H8" s="10" t="str">
+      <x:c r="I8" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
       </x:c>
     </x:row>
@@ -526,22 +551,25 @@
       <x:c r="B9" s="10" t="str">
         <x:v>收租老汉</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="n">
+      <x:c r="C9" s="11" t="str">
+        <x:v>08-10 06:00</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="n">
+      <x:c r="E9" s="10" t="n">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="E9" s="10" t="str">
+      <x:c r="F9" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F9" s="10" t="str">
+      <x:c r="G9" s="10" t="str">
         <x:v>种田囤货</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="n">
+      <x:c r="H9" s="11" t="n">
         <x:v>8368</x:v>
       </x:c>
-      <x:c r="H9" s="10" t="str">
+      <x:c r="I9" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
       </x:c>
     </x:row>
@@ -552,20 +580,23 @@
       <x:c r="B10" s="10" t="str">
         <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="n">
+      <x:c r="C10" s="11" t="str">
+        <x:v>07-17 18:30</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="n">
+      <x:c r="E10" s="10" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="E10" s="10" t="str">
+      <x:c r="F10" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F10" s="10" t="str">
+      <x:c r="G10" s="10" t="str">
         <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="str"/>
-      <x:c r="H10" s="10" t="str">
+      <x:c r="H10" s="11" t="str"/>
+      <x:c r="I10" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29</x:v>
       </x:c>
     </x:row>
@@ -576,22 +607,25 @@
       <x:c r="B11" s="10" t="str">
         <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="n">
+      <x:c r="C11" s="11" t="str">
+        <x:v>06-29 17:30</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="n">
+      <x:c r="E11" s="10" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E11" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="F11" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="n">
+      <x:c r="H11" s="11" t="n">
         <x:v>1834</x:v>
       </x:c>
-      <x:c r="H11" s="10" t="str">
+      <x:c r="I11" s="10" t="str">
         <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
@@ -602,20 +636,23 @@
       <x:c r="B12" s="10" t="str">
         <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="n">
+      <x:c r="C12" s="11" t="str">
+        <x:v>08-10 15:00</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="n">
+      <x:c r="E12" s="10" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E12" s="10" t="str">
+      <x:c r="F12" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F12" s="10" t="str">
+      <x:c r="G12" s="10" t="str">
         <x:v>年代怀旧</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="str"/>
-      <x:c r="H12" s="10" t="str">
+      <x:c r="H12" s="11" t="str"/>
+      <x:c r="I12" s="10" t="str">
         <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
@@ -626,22 +663,25 @@
       <x:c r="B13" s="10" t="str">
         <x:v>重生归来，四小姐她不装了</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="n">
+      <x:c r="C13" s="11" t="str">
+        <x:v>07-31 00:30</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="n">
+      <x:c r="E13" s="10" t="n">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="E13" s="10" t="str">
+      <x:c r="F13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F13" s="10" t="str">
+      <x:c r="G13" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="n">
+      <x:c r="H13" s="11" t="n">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="H13" s="10" t="str">
+      <x:c r="I13" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
       </x:c>
     </x:row>
@@ -652,20 +692,23 @@
       <x:c r="B14" s="10" t="str">
         <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="n">
+      <x:c r="C14" s="11" t="str">
+        <x:v>08-11 08:00</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="n">
+      <x:c r="E14" s="10" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E14" s="10" t="str">
+      <x:c r="F14" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F14" s="10" t="str">
+      <x:c r="G14" s="10" t="str">
         <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="str"/>
-      <x:c r="H14" s="10" t="str">
+      <x:c r="H14" s="11" t="str"/>
+      <x:c r="I14" s="10" t="str">
         <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
       </x:c>
     </x:row>
@@ -676,20 +719,23 @@
       <x:c r="B15" s="10" t="str">
         <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="n">
+      <x:c r="C15" s="11" t="str">
+        <x:v>08-11 00:26</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="n">
+      <x:c r="E15" s="10" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E15" s="10" t="str">
+      <x:c r="F15" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F15" s="10" t="str">
+      <x:c r="G15" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="str"/>
-      <x:c r="H15" s="10" t="str">
+      <x:c r="H15" s="11" t="str"/>
+      <x:c r="I15" s="10" t="str">
         <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
       </x:c>
     </x:row>
@@ -700,22 +746,25 @@
       <x:c r="B16" s="10" t="str">
         <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="n">
+      <x:c r="C16" s="11" t="str">
+        <x:v>08-08 18:00</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="n">
+      <x:c r="E16" s="10" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E16" s="10" t="str">
+      <x:c r="F16" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F16" s="10" t="str">
+      <x:c r="G16" s="10" t="str">
         <x:v>年代怀旧</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="n">
+      <x:c r="H16" s="11" t="n">
         <x:v>4442</x:v>
       </x:c>
-      <x:c r="H16" s="10" t="str">
+      <x:c r="I16" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
       </x:c>
     </x:row>
@@ -726,20 +775,23 @@
       <x:c r="B17" s="10" t="str">
         <x:v>孤城照山河第一季</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="n">
+      <x:c r="C17" s="11" t="str">
+        <x:v>08-10 17:13</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="n">
+      <x:c r="E17" s="10" t="n">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="E17" s="10" t="str">
+      <x:c r="F17" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F17" s="10" t="str">
+      <x:c r="G17" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="str"/>
-      <x:c r="H17" s="10" t="str">
+      <x:c r="H17" s="11" t="str"/>
+      <x:c r="I17" s="10" t="str">
         <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25、2026-08-28、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
@@ -750,20 +802,23 @@
       <x:c r="B18" s="10" t="str">
         <x:v>山王传奇</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="n">
+      <x:c r="C18" s="11" t="str">
+        <x:v>08-15 10:00</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="n">
+      <x:c r="E18" s="10" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="E18" s="10" t="str">
+      <x:c r="F18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F18" s="10" t="str">
+      <x:c r="G18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="str"/>
-      <x:c r="H18" s="10" t="str">
+      <x:c r="H18" s="11" t="str"/>
+      <x:c r="I18" s="10" t="str">
         <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
       </x:c>
     </x:row>
@@ -774,20 +829,23 @@
       <x:c r="B19" s="10" t="str">
         <x:v>我将恩人一家捡回村</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="n">
+      <x:c r="C19" s="11" t="str">
+        <x:v>08-13 10:00</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="n">
+      <x:c r="E19" s="10" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E19" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="F19" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="str">
         <x:v>家庭伦理</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="str"/>
-      <x:c r="H19" s="10" t="str">
+      <x:c r="H19" s="11" t="str"/>
+      <x:c r="I19" s="10" t="str">
         <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
@@ -798,20 +856,23 @@
       <x:c r="B20" s="10" t="str">
         <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="n">
+      <x:c r="C20" s="11" t="str">
+        <x:v>06-30 18:00</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="n">
+      <x:c r="E20" s="10" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E20" s="10" t="str">
+      <x:c r="F20" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F20" s="10" t="str">
+      <x:c r="G20" s="10" t="str">
         <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="str"/>
-      <x:c r="H20" s="10" t="str">
+      <x:c r="H20" s="11" t="str"/>
+      <x:c r="I20" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
       </x:c>
     </x:row>
@@ -822,20 +883,23 @@
       <x:c r="B21" s="10" t="str">
         <x:v>半梦半醒半清欢</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="n">
+      <x:c r="C21" s="11" t="str">
+        <x:v>07-20 10:00</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="n">
+      <x:c r="E21" s="10" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E21" s="10" t="str">
+      <x:c r="F21" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F21" s="10" t="str">
+      <x:c r="G21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="str"/>
-      <x:c r="H21" s="10" t="str">
+      <x:c r="H21" s="11" t="str"/>
+      <x:c r="I21" s="10" t="str">
         <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
@@ -846,20 +910,23 @@
       <x:c r="B22" s="10" t="str">
         <x:v>商场收回档口我成了全城的供应商</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="n">
+      <x:c r="C22" s="11" t="str">
+        <x:v>08-19 20:22</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D22" s="11" t="n">
+      <x:c r="E22" s="10" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E22" s="10" t="str">
+      <x:c r="F22" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="F22" s="10" t="str">
+      <x:c r="G22" s="10" t="str">
         <x:v>都市职场</x:v>
       </x:c>
-      <x:c r="G22" s="11" t="str"/>
-      <x:c r="H22" s="10" t="str">
+      <x:c r="H22" s="11" t="str"/>
+      <x:c r="I22" s="10" t="str">
         <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
@@ -870,22 +937,25 @@
       <x:c r="B23" s="10" t="str">
         <x:v>余生逢玉伴心安</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="n">
+      <x:c r="C23" s="11" t="str">
+        <x:v>07-13 14:00</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="n">
+      <x:c r="E23" s="10" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="E23" s="10" t="str">
+      <x:c r="F23" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F23" s="10" t="str">
+      <x:c r="G23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="n">
+      <x:c r="H23" s="11" t="n">
         <x:v>785</x:v>
       </x:c>
-      <x:c r="H23" s="10" t="str">
+      <x:c r="I23" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
       </x:c>
     </x:row>
@@ -896,20 +966,23 @@
       <x:c r="B24" s="10" t="str">
         <x:v>小溪的逆袭第一季</x:v>
       </x:c>
-      <x:c r="C24" s="11" t="n">
+      <x:c r="C24" s="11" t="str">
+        <x:v>08-10 09:00</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D24" s="11" t="n">
+      <x:c r="E24" s="10" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="E24" s="10" t="str">
+      <x:c r="F24" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F24" s="10" t="str">
+      <x:c r="G24" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
-      <x:c r="G24" s="11" t="str"/>
-      <x:c r="H24" s="10" t="str">
+      <x:c r="H24" s="11" t="str"/>
+      <x:c r="I24" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
       </x:c>
     </x:row>
@@ -920,20 +993,23 @@
       <x:c r="B25" s="10" t="str">
         <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="n">
+      <x:c r="C25" s="11" t="str">
+        <x:v>08-21 10:00</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D25" s="11" t="n">
+      <x:c r="E25" s="10" t="n">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="E25" s="10" t="str">
+      <x:c r="F25" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F25" s="10" t="str">
+      <x:c r="G25" s="10" t="str">
         <x:v>萌宝治愈</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="str"/>
-      <x:c r="H25" s="10" t="str">
+      <x:c r="H25" s="11" t="str"/>
+      <x:c r="I25" s="10" t="str">
         <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
@@ -944,20 +1020,23 @@
       <x:c r="B26" s="10" t="str">
         <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="n">
+      <x:c r="C26" s="11" t="str">
+        <x:v>07-20 14:00</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D26" s="11" t="n">
+      <x:c r="E26" s="10" t="n">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="E26" s="10" t="str">
+      <x:c r="F26" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="F26" s="10" t="str">
+      <x:c r="G26" s="10" t="str">
         <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="str"/>
-      <x:c r="H26" s="10" t="str">
+      <x:c r="H26" s="11" t="str"/>
+      <x:c r="I26" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29</x:v>
       </x:c>
     </x:row>
@@ -974,11 +1053,12 @@
     <x:col min="2" max="2" width="7" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -995,18 +1075,21 @@
         <x:v>首次上榜</x:v>
       </x:c>
       <x:c r="E1" t="str">
+        <x:v>预计上线</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
         <x:v>上榜次数</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="G1" t="str">
         <x:v>集数</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="H1" t="str">
         <x:v>制作风格</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="I1" t="str">
         <x:v>主题分类</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="J1" t="str">
         <x:v>发布账号</x:v>
       </x:c>
     </x:row>
@@ -1021,19 +1104,22 @@
       <x:c r="D2" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E2" s="11" t="n">
+      <x:c r="E2" s="11" t="str">
+        <x:v>07-27 11:00</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="n">
+      <x:c r="G2" s="11" t="n">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="str">
+      <x:c r="H2" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="I2" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
+      <x:c r="J2" s="10" t="str">
         <x:v>暖夏短剧</x:v>
       </x:c>
     </x:row>
@@ -1048,19 +1134,22 @@
       <x:c r="D3" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E3" s="11" t="n">
+      <x:c r="E3" s="11" t="str">
+        <x:v>08-31 20:00</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="n">
+      <x:c r="G3" s="11" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G3" s="10" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H3" s="10" t="str">
+      <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I3" s="10" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>马克动漫</x:v>
       </x:c>
     </x:row>
@@ -1075,19 +1164,22 @@
       <x:c r="D4" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E4" s="11" t="n">
+      <x:c r="E4" s="11" t="str">
+        <x:v>08-31 17:00</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="n">
+      <x:c r="G4" s="11" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H4" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I4" s="10" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>云影漫剧</x:v>
       </x:c>
     </x:row>
@@ -1102,19 +1194,22 @@
       <x:c r="D5" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="n">
+      <x:c r="E5" s="11" t="str">
+        <x:v>08-30 18:42</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="n">
+      <x:c r="G5" s="11" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="str">
+      <x:c r="I5" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="str">
+      <x:c r="J5" s="10" t="str">
         <x:v>小桃红动画</x:v>
       </x:c>
     </x:row>
@@ -1129,19 +1224,22 @@
       <x:c r="D6" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="n">
+      <x:c r="E6" s="11" t="str">
+        <x:v>08-29 16:15</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
+      <x:c r="G6" s="11" t="n">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="str">
+      <x:c r="H6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H6" s="10" t="str">
+      <x:c r="I6" s="10" t="str">
         <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
       </x:c>
-      <x:c r="I6" s="10" t="str">
+      <x:c r="J6" s="10" t="str">
         <x:v>漫漫画丫头</x:v>
       </x:c>
     </x:row>
@@ -1156,19 +1254,22 @@
       <x:c r="D7" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="n">
+      <x:c r="E7" s="11" t="str">
+        <x:v>08-31 15:58</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="n">
+      <x:c r="G7" s="11" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="str">
+      <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="str">
+      <x:c r="J7" s="10" t="str">
         <x:v>小尘剧场</x:v>
       </x:c>
     </x:row>
@@ -1183,19 +1284,22 @@
       <x:c r="D8" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="n">
+      <x:c r="E8" s="11" t="str">
+        <x:v>08-31 19:00</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="n">
+      <x:c r="G8" s="11" t="n">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="str">
+      <x:c r="H8" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H8" s="10" t="str">
+      <x:c r="I8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I8" s="10" t="str">
+      <x:c r="J8" s="10" t="str">
         <x:v>阿云剧场</x:v>
       </x:c>
     </x:row>
@@ -1210,19 +1314,22 @@
       <x:c r="D9" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="n">
+      <x:c r="E9" s="11" t="str">
+        <x:v>08-28 21:37</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
+      <x:c r="G9" s="11" t="n">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="str">
+      <x:c r="H9" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H9" s="10" t="str">
+      <x:c r="I9" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I9" s="10" t="str">
+      <x:c r="J9" s="10" t="str">
         <x:v>栗子说漫</x:v>
       </x:c>
     </x:row>
@@ -1237,19 +1344,22 @@
       <x:c r="D10" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="n">
+      <x:c r="E10" s="11" t="str">
+        <x:v>08-29 11:03</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="n">
+      <x:c r="G10" s="11" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H10" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I10" s="10" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>二里清风</x:v>
       </x:c>
     </x:row>
@@ -1264,19 +1374,22 @@
       <x:c r="D11" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="n">
+      <x:c r="E11" s="11" t="str">
+        <x:v>08-31 11:45</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="n">
+      <x:c r="G11" s="11" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G11" s="10" t="str">
+      <x:c r="H11" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H11" s="10" t="str">
+      <x:c r="I11" s="10" t="str">
         <x:v>古装宫廷 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="I11" s="10" t="str">
+      <x:c r="J11" s="10" t="str">
         <x:v>清欢古风剧场</x:v>
       </x:c>
     </x:row>
@@ -1291,19 +1404,22 @@
       <x:c r="D12" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="n">
+      <x:c r="E12" s="11" t="str">
+        <x:v>08-31 11:00</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="n">
+      <x:c r="G12" s="11" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="str">
+      <x:c r="H12" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H12" s="10" t="str">
+      <x:c r="I12" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I12" s="10" t="str">
+      <x:c r="J12" s="10" t="str">
         <x:v>95漫画</x:v>
       </x:c>
     </x:row>
@@ -1318,19 +1434,22 @@
       <x:c r="D13" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="n">
+      <x:c r="E13" s="11" t="str">
+        <x:v>08-31 13:17</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="n">
+      <x:c r="G13" s="11" t="n">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G13" s="10" t="str">
+      <x:c r="H13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H13" s="10" t="str">
+      <x:c r="I13" s="10" t="str">
         <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
-      <x:c r="I13" s="10" t="str">
+      <x:c r="J13" s="10" t="str">
         <x:v>云间漫剧-零七</x:v>
       </x:c>
     </x:row>
@@ -1345,19 +1464,22 @@
       <x:c r="D14" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="n">
+      <x:c r="E14" s="11" t="str">
+        <x:v>08-31 19:10</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="n">
+      <x:c r="G14" s="11" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G14" s="10" t="str">
+      <x:c r="H14" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H14" s="10" t="str">
+      <x:c r="I14" s="10" t="str">
         <x:v>家庭伦理</x:v>
       </x:c>
-      <x:c r="I14" s="10" t="str">
+      <x:c r="J14" s="10" t="str">
         <x:v>表妹剧场</x:v>
       </x:c>
     </x:row>
@@ -1372,19 +1494,22 @@
       <x:c r="D15" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="n">
+      <x:c r="E15" s="11" t="str">
+        <x:v>08-31 20:07</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="n">
+      <x:c r="G15" s="11" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G15" s="10" t="str">
+      <x:c r="H15" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H15" s="10" t="str">
+      <x:c r="I15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I15" s="10" t="str">
+      <x:c r="J15" s="10" t="str">
         <x:v>馆长玉先生剧场</x:v>
       </x:c>
     </x:row>
@@ -1399,19 +1524,22 @@
       <x:c r="D16" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="n">
+      <x:c r="E16" s="11" t="str">
+        <x:v>08-31 10:00</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="n">
+      <x:c r="G16" s="11" t="n">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G16" s="10" t="str">
+      <x:c r="H16" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H16" s="10" t="str">
+      <x:c r="I16" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I16" s="10" t="str">
+      <x:c r="J16" s="10" t="str">
         <x:v>阅友动漫</x:v>
       </x:c>
     </x:row>
@@ -1426,19 +1554,22 @@
       <x:c r="D17" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="n">
+      <x:c r="E17" s="11" t="str">
+        <x:v>08-31 20:00</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="n">
+      <x:c r="G17" s="11" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G17" s="10" t="str">
+      <x:c r="H17" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H17" s="10" t="str">
+      <x:c r="I17" s="10" t="str">
         <x:v>战神异能</x:v>
       </x:c>
-      <x:c r="I17" s="10" t="str">
+      <x:c r="J17" s="10" t="str">
         <x:v>渲渲动画</x:v>
       </x:c>
     </x:row>
@@ -1453,19 +1584,22 @@
       <x:c r="D18" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="n">
+      <x:c r="E18" s="11" t="str">
+        <x:v>08-30 15:07</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="n">
+      <x:c r="G18" s="11" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G18" s="10" t="str">
+      <x:c r="H18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H18" s="10" t="str">
+      <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I18" s="10" t="str">
+      <x:c r="J18" s="10" t="str">
         <x:v>菁禾</x:v>
       </x:c>
     </x:row>
@@ -1480,19 +1614,22 @@
       <x:c r="D19" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="n">
+      <x:c r="E19" s="11" t="str">
+        <x:v>08-28 19:07</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="n">
+      <x:c r="G19" s="11" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G19" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H19" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="str">
         <x:v>现实反转</x:v>
       </x:c>
-      <x:c r="I19" s="10" t="str">
+      <x:c r="J19" s="10" t="str">
         <x:v>AI梦</x:v>
       </x:c>
     </x:row>
@@ -1507,19 +1644,22 @@
       <x:c r="D20" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="n">
+      <x:c r="E20" s="11" t="str">
+        <x:v>08-29 11:00</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="n">
+      <x:c r="G20" s="11" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G20" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H20" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I20" s="10" t="str">
+      <x:c r="J20" s="10" t="str">
         <x:v>AI 风华</x:v>
       </x:c>
     </x:row>
@@ -1534,19 +1674,22 @@
       <x:c r="D21" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="n">
+      <x:c r="E21" s="11" t="str">
+        <x:v>08-16 11:00</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="n">
+      <x:c r="G21" s="11" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="G21" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H21" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I21" s="10" t="str">
         <x:v>种田囤货 / 婚姻情感</x:v>
       </x:c>
-      <x:c r="I21" s="10" t="str">
+      <x:c r="J21" s="10" t="str">
         <x:v>知夏短剧</x:v>
       </x:c>
     </x:row>
@@ -1561,19 +1704,22 @@
       <x:c r="D22" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="n">
+      <x:c r="E22" s="11" t="str">
+        <x:v>09-01 00:06</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="n">
+      <x:c r="G22" s="11" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G22" s="10" t="str">
+      <x:c r="H22" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H22" s="10" t="str">
+      <x:c r="I22" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I22" s="10" t="str">
+      <x:c r="J22" s="10" t="str">
         <x:v>武汉卡看漫剧场</x:v>
       </x:c>
     </x:row>
@@ -1588,19 +1734,22 @@
       <x:c r="D23" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="n">
+      <x:c r="E23" s="11" t="str">
+        <x:v>08-29 10:00</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="n">
+      <x:c r="G23" s="11" t="n">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G23" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H23" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I23" s="10" t="str">
         <x:v>年代怀旧 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="I23" s="10" t="str">
+      <x:c r="J23" s="10" t="str">
         <x:v>朝夕影堂</x:v>
       </x:c>
     </x:row>
@@ -1615,19 +1764,22 @@
       <x:c r="D24" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="n">
+      <x:c r="E24" s="11" t="str">
+        <x:v>08-30 07:10</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F24" s="11" t="n">
+      <x:c r="G24" s="11" t="n">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="G24" s="10" t="str">
+      <x:c r="H24" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H24" s="10" t="str">
+      <x:c r="I24" s="10" t="str">
         <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
-      <x:c r="I24" s="10" t="str">
+      <x:c r="J24" s="10" t="str">
         <x:v>诺威剧场</x:v>
       </x:c>
     </x:row>
@@ -1642,17 +1794,18 @@
       <x:c r="D25" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="n">
+      <x:c r="E25" s="11" t="str"/>
+      <x:c r="F25" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="str"/>
-      <x:c r="G25" s="10" t="str">
+      <x:c r="G25" s="11" t="str"/>
+      <x:c r="H25" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H25" s="10" t="str">
+      <x:c r="I25" s="10" t="str">
         <x:v>年代怀旧</x:v>
       </x:c>
-      <x:c r="I25" s="10" t="str"/>
+      <x:c r="J25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -1665,19 +1818,22 @@
       <x:c r="D26" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="n">
+      <x:c r="E26" s="11" t="str">
+        <x:v>08-30 16:31</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F26" s="11" t="n">
+      <x:c r="G26" s="11" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G26" s="10" t="str">
+      <x:c r="H26" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H26" s="10" t="str">
+      <x:c r="I26" s="10" t="str">
         <x:v>种田囤货</x:v>
       </x:c>
-      <x:c r="I26" s="10" t="str">
+      <x:c r="J26" s="10" t="str">
         <x:v>空白漫</x:v>
       </x:c>
     </x:row>
@@ -1692,19 +1848,22 @@
       <x:c r="D27" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="n">
+      <x:c r="E27" s="11" t="str">
+        <x:v>08-29 19:20</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="n">
+      <x:c r="G27" s="11" t="n">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G27" s="10" t="str">
+      <x:c r="H27" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H27" s="10" t="str">
+      <x:c r="I27" s="10" t="str">
         <x:v>战神异能</x:v>
       </x:c>
-      <x:c r="I27" s="10" t="str">
+      <x:c r="J27" s="10" t="str">
         <x:v>河虾动漫</x:v>
       </x:c>
     </x:row>
@@ -1719,19 +1878,22 @@
       <x:c r="D28" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="n">
+      <x:c r="E28" s="11" t="str">
+        <x:v>08-26 10:00</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F28" s="11" t="n">
+      <x:c r="G28" s="11" t="n">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G28" s="10" t="str">
+      <x:c r="H28" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H28" s="10" t="str">
+      <x:c r="I28" s="10" t="str">
         <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
-      <x:c r="I28" s="10" t="str">
+      <x:c r="J28" s="10" t="str">
         <x:v>每日沙雕速递</x:v>
       </x:c>
     </x:row>
@@ -1746,19 +1908,22 @@
       <x:c r="D29" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="n">
+      <x:c r="E29" s="11" t="str">
+        <x:v>08-21 19:24</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="n">
+      <x:c r="G29" s="11" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="G29" s="10" t="str">
+      <x:c r="H29" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H29" s="10" t="str">
+      <x:c r="I29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I29" s="10" t="str">
+      <x:c r="J29" s="10" t="str">
         <x:v>口水显眼包</x:v>
       </x:c>
     </x:row>
@@ -1773,19 +1938,22 @@
       <x:c r="D30" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="n">
+      <x:c r="E30" s="11" t="str">
+        <x:v>08-28 17:55</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="n">
+      <x:c r="G30" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G30" s="10" t="str">
+      <x:c r="H30" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H30" s="10" t="str">
+      <x:c r="I30" s="10" t="str">
         <x:v>家庭伦理</x:v>
       </x:c>
-      <x:c r="I30" s="10" t="str">
+      <x:c r="J30" s="10" t="str">
         <x:v>锋芒映剧</x:v>
       </x:c>
     </x:row>
@@ -1800,19 +1968,22 @@
       <x:c r="D31" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E31" s="11" t="n">
+      <x:c r="E31" s="11" t="str">
+        <x:v>08-29 20:30</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F31" s="11" t="n">
+      <x:c r="G31" s="11" t="n">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G31" s="10" t="str">
+      <x:c r="H31" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H31" s="10" t="str">
+      <x:c r="I31" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I31" s="10" t="str">
+      <x:c r="J31" s="10" t="str">
         <x:v>森森动画</x:v>
       </x:c>
     </x:row>
@@ -1827,19 +1998,22 @@
       <x:c r="D32" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E32" s="11" t="n">
+      <x:c r="E32" s="11" t="str">
+        <x:v>08-29 10:00</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F32" s="11" t="n">
+      <x:c r="G32" s="11" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G32" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H32" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I32" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
-      <x:c r="I32" s="10" t="str">
+      <x:c r="J32" s="10" t="str">
         <x:v>诗婳-君懿看剧</x:v>
       </x:c>
     </x:row>
@@ -1854,19 +2028,22 @@
       <x:c r="D33" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E33" s="11" t="n">
+      <x:c r="E33" s="11" t="str">
+        <x:v>08-29 16:49</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F33" s="11" t="n">
+      <x:c r="G33" s="11" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G33" s="10" t="str">
+      <x:c r="H33" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H33" s="10" t="str">
+      <x:c r="I33" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I33" s="10" t="str">
+      <x:c r="J33" s="10" t="str">
         <x:v>林帧漫剧</x:v>
       </x:c>
     </x:row>
@@ -1881,19 +2058,22 @@
       <x:c r="D34" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E34" s="11" t="n">
+      <x:c r="E34" s="11" t="str">
+        <x:v>08-29 18:00</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F34" s="11" t="n">
+      <x:c r="G34" s="11" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="G34" s="10" t="str">
+      <x:c r="H34" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H34" s="10" t="str">
+      <x:c r="I34" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I34" s="10" t="str">
+      <x:c r="J34" s="10" t="str">
         <x:v>追更漫剧</x:v>
       </x:c>
     </x:row>
@@ -1908,19 +2088,22 @@
       <x:c r="D35" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E35" s="11" t="n">
+      <x:c r="E35" s="11" t="str">
+        <x:v>08-29 16:13</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F35" s="11" t="n">
+      <x:c r="G35" s="11" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G35" s="10" t="str">
+      <x:c r="H35" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H35" s="10" t="str">
+      <x:c r="I35" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I35" s="10" t="str">
+      <x:c r="J35" s="10" t="str">
         <x:v>绿豆儿</x:v>
       </x:c>
     </x:row>
@@ -1935,19 +2118,22 @@
       <x:c r="D36" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E36" s="11" t="n">
+      <x:c r="E36" s="11" t="str">
+        <x:v>08-30 10:00</x:v>
+      </x:c>
+      <x:c r="F36" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="n">
+      <x:c r="G36" s="11" t="n">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="G36" s="10" t="str">
+      <x:c r="H36" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H36" s="10" t="str">
+      <x:c r="I36" s="10" t="str">
         <x:v>年代怀旧 / 都市职场 / 美食治愈</x:v>
       </x:c>
-      <x:c r="I36" s="10" t="str">
+      <x:c r="J36" s="10" t="str">
         <x:v>东瓜剧场</x:v>
       </x:c>
     </x:row>
@@ -1962,19 +2148,22 @@
       <x:c r="D37" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="n">
+      <x:c r="E37" s="11" t="str">
+        <x:v>08-30 00:45</x:v>
+      </x:c>
+      <x:c r="F37" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F37" s="11" t="n">
+      <x:c r="G37" s="11" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G37" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H37" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I37" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I37" s="10" t="str">
+      <x:c r="J37" s="10" t="str">
         <x:v>星漫世界</x:v>
       </x:c>
     </x:row>
@@ -1989,19 +2178,22 @@
       <x:c r="D38" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="n">
+      <x:c r="E38" s="11" t="str">
+        <x:v>08-29 20:00</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F38" s="11" t="n">
+      <x:c r="G38" s="11" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G38" s="10" t="str">
+      <x:c r="H38" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H38" s="10" t="str">
+      <x:c r="I38" s="10" t="str">
         <x:v>萌宝治愈</x:v>
       </x:c>
-      <x:c r="I38" s="10" t="str">
+      <x:c r="J38" s="10" t="str">
         <x:v>紫怡漫剧场</x:v>
       </x:c>
     </x:row>
@@ -2016,19 +2208,22 @@
       <x:c r="D39" s="11" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
-      <x:c r="E39" s="11" t="n">
+      <x:c r="E39" s="11" t="str">
+        <x:v>08-30 10:00</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="n">
+      <x:c r="G39" s="11" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G39" s="10" t="str">
+      <x:c r="H39" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H39" s="10" t="str">
+      <x:c r="I39" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I39" s="10" t="str">
+      <x:c r="J39" s="10" t="str">
         <x:v>豆豆动漫</x:v>
       </x:c>
     </x:row>
@@ -2043,19 +2238,22 @@
       <x:c r="D40" s="11" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
-      <x:c r="E40" s="11" t="n">
+      <x:c r="E40" s="11" t="str">
+        <x:v>08-29 18:00</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F40" s="11" t="n">
+      <x:c r="G40" s="11" t="n">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G40" s="10" t="str">
+      <x:c r="H40" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H40" s="10" t="str">
+      <x:c r="I40" s="10" t="str">
         <x:v>都市职场 / 逆袭打脸</x:v>
       </x:c>
-      <x:c r="I40" s="10" t="str">
+      <x:c r="J40" s="10" t="str">
         <x:v>小清书漫</x:v>
       </x:c>
     </x:row>
@@ -2070,19 +2268,22 @@
       <x:c r="D41" s="11" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
-      <x:c r="E41" s="11" t="n">
+      <x:c r="E41" s="11" t="str">
+        <x:v>08-30 17:30</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F41" s="11" t="n">
+      <x:c r="G41" s="11" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G41" s="10" t="str">
+      <x:c r="H41" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H41" s="10" t="str">
+      <x:c r="I41" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I41" s="10" t="str">
+      <x:c r="J41" s="10" t="str">
         <x:v>小菲菲动画</x:v>
       </x:c>
     </x:row>
@@ -2097,19 +2298,22 @@
       <x:c r="D42" s="11" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
-      <x:c r="E42" s="11" t="n">
+      <x:c r="E42" s="11" t="str">
+        <x:v>08-29 19:57</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F42" s="11" t="n">
+      <x:c r="G42" s="11" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G42" s="10" t="str">
+      <x:c r="H42" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H42" s="10" t="str">
+      <x:c r="I42" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I42" s="10" t="str">
+      <x:c r="J42" s="10" t="str">
         <x:v>艾微动画剧场</x:v>
       </x:c>
     </x:row>
@@ -2124,19 +2328,22 @@
       <x:c r="D43" s="11" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
-      <x:c r="E43" s="11" t="n">
+      <x:c r="E43" s="11" t="str">
+        <x:v>08-30 16:50</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F43" s="11" t="n">
+      <x:c r="G43" s="11" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G43" s="10" t="str">
+      <x:c r="H43" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H43" s="10" t="str">
+      <x:c r="I43" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="I43" s="10" t="str">
+      <x:c r="J43" s="10" t="str">
         <x:v>榴莲漫剧</x:v>
       </x:c>
     </x:row>
@@ -2151,19 +2358,22 @@
       <x:c r="D44" s="11" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
-      <x:c r="E44" s="11" t="n">
+      <x:c r="E44" s="11" t="str">
+        <x:v>08-30 20:07</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F44" s="11" t="n">
+      <x:c r="G44" s="11" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G44" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H44" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I44" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I44" s="10" t="str">
+      <x:c r="J44" s="10" t="str">
         <x:v>三针剧场</x:v>
       </x:c>
     </x:row>
@@ -2178,19 +2388,22 @@
       <x:c r="D45" s="11" t="str">
         <x:v>2026-08-30</x:v>
       </x:c>
-      <x:c r="E45" s="11" t="n">
+      <x:c r="E45" s="11" t="str">
+        <x:v>08-26 11:28</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F45" s="11" t="n">
+      <x:c r="G45" s="11" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G45" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
       <x:c r="H45" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I45" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="I45" s="10" t="str">
+      <x:c r="J45" s="10" t="str">
         <x:v>喵琪琪追剧</x:v>
       </x:c>
     </x:row>
@@ -2205,19 +2418,22 @@
       <x:c r="D46" s="11" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
-      <x:c r="E46" s="11" t="n">
+      <x:c r="E46" s="11" t="str">
+        <x:v>08-30 12:50</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F46" s="11" t="n">
+      <x:c r="G46" s="11" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G46" s="10" t="str">
+      <x:c r="H46" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H46" s="10" t="str">
+      <x:c r="I46" s="10" t="str">
         <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
-      <x:c r="I46" s="10" t="str">
+      <x:c r="J46" s="10" t="str">
         <x:v>小丘剧场</x:v>
       </x:c>
     </x:row>
@@ -2232,13 +2448,14 @@
   <x:cols>
     <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="70" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -2249,24 +2466,27 @@
         <x:v>剧名</x:v>
       </x:c>
       <x:c r="C1" t="str">
+        <x:v>预计上线</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
         <x:v>两周前上榜次数</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="E1" t="str">
         <x:v>累计上榜</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="F1" t="str">
         <x:v>最近上榜</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="G1" t="str">
         <x:v>集数</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="H1" t="str">
         <x:v>制作风格</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="I1" t="str">
         <x:v>8月消耗(元)</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="J1" t="str">
         <x:v>选剧依据</x:v>
       </x:c>
     </x:row>
@@ -2277,25 +2497,28 @@
       <x:c r="B2" s="10" t="str">
         <x:v>包子里的真心</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="n">
+      <x:c r="C2" s="11" t="str">
+        <x:v>08-07 17:29</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
+      <x:c r="E2" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E2" s="11" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="n">
+      <x:c r="G2" s="10" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="str">
+      <x:c r="H2" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H2" s="11" t="n">
+      <x:c r="I2" s="11" t="n">
         <x:v>7514</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
+      <x:c r="J2" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2306,25 +2529,28 @@
       <x:c r="B3" s="10" t="str">
         <x:v>天灾囤货录，善恶见人心</x:v>
       </x:c>
-      <x:c r="C3" s="11" t="n">
+      <x:c r="C3" s="11" t="str">
+        <x:v>08-10 16:30</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="n">
+      <x:c r="E3" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E3" s="11" t="str">
+      <x:c r="F3" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="n">
+      <x:c r="G3" s="10" t="n">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="G3" s="10" t="str">
+      <x:c r="H3" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H3" s="11" t="n">
+      <x:c r="I3" s="11" t="n">
         <x:v>852</x:v>
       </x:c>
-      <x:c r="I3" s="10" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2335,25 +2561,28 @@
       <x:c r="B4" s="10" t="str">
         <x:v>收租老汉</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="n">
+      <x:c r="C4" s="11" t="str">
+        <x:v>08-10 06:00</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="n">
+      <x:c r="E4" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E4" s="11" t="str">
+      <x:c r="F4" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="n">
+      <x:c r="G4" s="10" t="n">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="str">
+      <x:c r="H4" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H4" s="11" t="n">
+      <x:c r="I4" s="11" t="n">
         <x:v>8368</x:v>
       </x:c>
-      <x:c r="I4" s="10" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2364,23 +2593,26 @@
       <x:c r="B5" s="10" t="str">
         <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="11" t="str">
+        <x:v>08-10 15:00</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
+      <x:c r="E5" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="str">
+      <x:c r="F5" s="11" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="n">
+      <x:c r="G5" s="10" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="str">
+      <x:c r="H5" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H5" s="11" t="str"/>
-      <x:c r="I5" s="10" t="str">
+      <x:c r="I5" s="11" t="str"/>
+      <x:c r="J5" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2391,23 +2623,26 @@
       <x:c r="B6" s="10" t="str">
         <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="11" t="str">
+        <x:v>08-11 08:00</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
+      <x:c r="E6" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="str">
+      <x:c r="F6" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
+      <x:c r="G6" s="10" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="str">
+      <x:c r="H6" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="str"/>
-      <x:c r="I6" s="10" t="str">
+      <x:c r="I6" s="11" t="str"/>
+      <x:c r="J6" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2418,23 +2653,26 @@
       <x:c r="B7" s="10" t="str">
         <x:v>山王传奇</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="11" t="str">
+        <x:v>08-15 10:00</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="n">
+      <x:c r="E7" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="str">
+      <x:c r="F7" s="11" t="str">
         <x:v>2026-08-28</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="n">
+      <x:c r="G7" s="10" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="str">
+      <x:c r="H7" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="str"/>
-      <x:c r="I7" s="10" t="str">
+      <x:c r="I7" s="11" t="str"/>
+      <x:c r="J7" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜7次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2445,23 +2683,26 @@
       <x:c r="B8" s="10" t="str">
         <x:v>天生怪力女主，被傅家捧在心尖</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="C8" s="11" t="str">
+        <x:v>08-12 15:35</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="n">
+      <x:c r="E8" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str">
+      <x:c r="F8" s="11" t="str">
         <x:v>2026-08-21</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="n">
+      <x:c r="G8" s="10" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="str">
+      <x:c r="H8" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="str"/>
-      <x:c r="I8" s="10" t="str">
+      <x:c r="I8" s="11" t="str"/>
+      <x:c r="J8" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2472,23 +2713,26 @@
       <x:c r="B9" s="10" t="str">
         <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="n">
+      <x:c r="C9" s="11" t="str">
+        <x:v>07-17 18:30</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="n">
+      <x:c r="E9" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="str">
+      <x:c r="F9" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
+      <x:c r="G9" s="10" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="str">
+      <x:c r="H9" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H9" s="11" t="str"/>
-      <x:c r="I9" s="10" t="str">
+      <x:c r="I9" s="11" t="str"/>
+      <x:c r="J9" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜6次、累计15次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2499,25 +2743,28 @@
       <x:c r="B10" s="10" t="str">
         <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="n">
+      <x:c r="C10" s="11" t="str">
+        <x:v>08-08 18:00</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="n">
+      <x:c r="E10" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="str">
+      <x:c r="F10" s="11" t="str">
         <x:v>2026-08-23</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="n">
+      <x:c r="G10" s="10" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="str">
+      <x:c r="H10" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H10" s="11" t="n">
+      <x:c r="I10" s="11" t="n">
         <x:v>4442</x:v>
       </x:c>
-      <x:c r="I10" s="10" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜6次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2528,23 +2775,26 @@
       <x:c r="B11" s="10" t="str">
         <x:v>小溪的逆袭第一季</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="n">
+      <x:c r="C11" s="11" t="str">
+        <x:v>08-10 09:00</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="n">
+      <x:c r="E11" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="str">
+      <x:c r="F11" s="11" t="str">
         <x:v>2026-08-20</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="n">
+      <x:c r="G11" s="10" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G11" s="10" t="str">
+      <x:c r="H11" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H11" s="11" t="str"/>
-      <x:c r="I11" s="10" t="str">
+      <x:c r="I11" s="11" t="str"/>
+      <x:c r="J11" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜6次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2555,23 +2805,26 @@
       <x:c r="B12" s="10" t="str">
         <x:v>我妈装穷来认我</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="n">
+      <x:c r="C12" s="11" t="str">
+        <x:v>08-14 10:00</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="n">
+      <x:c r="E12" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="str">
+      <x:c r="F12" s="11" t="str">
         <x:v>2026-08-27</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="n">
+      <x:c r="G12" s="10" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="str">
+      <x:c r="H12" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H12" s="11" t="str"/>
-      <x:c r="I12" s="10" t="str">
+      <x:c r="I12" s="11" t="str"/>
+      <x:c r="J12" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2582,23 +2835,26 @@
       <x:c r="B13" s="10" t="str">
         <x:v>分家只给破枪，我听兽语富全屯</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="n">
+      <x:c r="C13" s="11" t="str">
+        <x:v>08-13 09:02</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="n">
+      <x:c r="E13" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="str">
+      <x:c r="F13" s="11" t="str">
         <x:v>2026-08-20</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="n">
+      <x:c r="G13" s="10" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G13" s="10" t="str">
+      <x:c r="H13" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H13" s="11" t="str"/>
-      <x:c r="I13" s="10" t="str">
+      <x:c r="I13" s="11" t="str"/>
+      <x:c r="J13" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2609,23 +2865,26 @@
       <x:c r="B14" s="10" t="str">
         <x:v>这门婚我不嫁了</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="n">
+      <x:c r="C14" s="11" t="str">
+        <x:v>08-15 09:00</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="n">
+      <x:c r="E14" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="str">
+      <x:c r="F14" s="11" t="str">
         <x:v>2026-08-28</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="n">
+      <x:c r="G14" s="10" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G14" s="10" t="str">
+      <x:c r="H14" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H14" s="11" t="str"/>
-      <x:c r="I14" s="10" t="str">
+      <x:c r="I14" s="11" t="str"/>
+      <x:c r="J14" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2636,23 +2895,26 @@
       <x:c r="B15" s="10" t="str">
         <x:v>逆流年代：从1970开始种田养家</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="n">
+      <x:c r="C15" s="11" t="str">
+        <x:v>08-15 10:00</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="n">
+      <x:c r="E15" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="str">
+      <x:c r="F15" s="11" t="str">
         <x:v>2026-08-22</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="n">
+      <x:c r="G15" s="10" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G15" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H15" s="11" t="str"/>
-      <x:c r="I15" s="10" t="str">
+      <x:c r="H15" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str"/>
+      <x:c r="J15" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；110集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2663,23 +2925,26 @@
       <x:c r="B16" s="10" t="str">
         <x:v>一盏灯暖赶路人</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="n">
+      <x:c r="C16" s="11" t="str">
+        <x:v>08-10 21:16</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="n">
+      <x:c r="E16" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="str">
+      <x:c r="F16" s="11" t="str">
         <x:v>2026-08-22</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="n">
+      <x:c r="G16" s="10" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G16" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="str"/>
-      <x:c r="I16" s="10" t="str">
+      <x:c r="H16" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str"/>
+      <x:c r="J16" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2690,23 +2955,26 @@
       <x:c r="B17" s="10" t="str">
         <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="n">
+      <x:c r="C17" s="11" t="str">
+        <x:v>08-17 09:38</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="n">
+      <x:c r="E17" s="11" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="str">
+      <x:c r="F17" s="11" t="str">
         <x:v>2026-08-27</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="n">
+      <x:c r="G17" s="10" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G17" s="10" t="str">
+      <x:c r="H17" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H17" s="11" t="str"/>
-      <x:c r="I17" s="10" t="str">
+      <x:c r="I17" s="11" t="str"/>
+      <x:c r="J17" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计10次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2717,23 +2985,26 @@
       <x:c r="B18" s="10" t="str">
         <x:v>悍妻替嫁，从前说</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="n">
+      <x:c r="C18" s="11" t="str">
+        <x:v>08-06 11:00</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="n">
+      <x:c r="E18" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="str">
+      <x:c r="F18" s="11" t="str">
         <x:v>2026-08-19</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="n">
+      <x:c r="G18" s="10" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G18" s="10" t="str">
+      <x:c r="H18" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H18" s="11" t="str"/>
-      <x:c r="I18" s="10" t="str">
+      <x:c r="I18" s="11" t="str"/>
+      <x:c r="J18" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2744,23 +3015,26 @@
       <x:c r="B19" s="10" t="str">
         <x:v>暴雪见人心</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="n">
+      <x:c r="C19" s="11" t="str">
+        <x:v>08-16 08:21</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="n">
+      <x:c r="E19" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="str">
+      <x:c r="F19" s="11" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="n">
+      <x:c r="G19" s="10" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G19" s="10" t="str">
+      <x:c r="H19" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H19" s="11" t="str"/>
-      <x:c r="I19" s="10" t="str">
+      <x:c r="I19" s="11" t="str"/>
+      <x:c r="J19" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2771,23 +3045,26 @@
       <x:c r="B20" s="10" t="str">
         <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="n">
+      <x:c r="C20" s="11" t="str">
+        <x:v>08-11 10:41</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="n">
+      <x:c r="E20" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="str">
+      <x:c r="F20" s="11" t="str">
         <x:v>2026-08-22</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="n">
+      <x:c r="G20" s="10" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G20" s="10" t="str">
+      <x:c r="H20" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H20" s="11" t="str"/>
-      <x:c r="I20" s="10" t="str">
+      <x:c r="I20" s="11" t="str"/>
+      <x:c r="J20" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2798,23 +3075,26 @@
       <x:c r="B21" s="10" t="str">
         <x:v>八零之老妈在厂长家当后妈</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="n">
+      <x:c r="C21" s="11" t="str">
+        <x:v>08-14 09:08</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D21" s="11" t="n">
+      <x:c r="E21" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E21" s="11" t="str">
+      <x:c r="F21" s="11" t="str">
         <x:v>2026-08-23</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="n">
+      <x:c r="G21" s="10" t="n">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G21" s="10" t="str">
+      <x:c r="H21" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H21" s="11" t="str"/>
-      <x:c r="I21" s="10" t="str">
+      <x:c r="I21" s="11" t="str"/>
+      <x:c r="J21" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2825,23 +3105,26 @@
       <x:c r="B22" s="10" t="str">
         <x:v>激活美食治愈系统,我靠摆摊火遍了整座城市</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="n">
+      <x:c r="C22" s="11" t="str">
+        <x:v>08-14 17:00</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D22" s="11" t="n">
+      <x:c r="E22" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="str">
+      <x:c r="F22" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="n">
+      <x:c r="G22" s="10" t="n">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G22" s="10" t="str">
+      <x:c r="H22" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H22" s="11" t="str"/>
-      <x:c r="I22" s="10" t="str">
+      <x:c r="I22" s="11" t="str"/>
+      <x:c r="J22" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；177集长剧集；题材契合爆款主线（都市职场 / 美食治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2852,23 +3135,26 @@
       <x:c r="B23" s="10" t="str">
         <x:v>离婚那天我多了个董事长妈妈</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="n">
+      <x:c r="C23" s="11" t="str">
+        <x:v>07-24 00:06</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D23" s="11" t="n">
+      <x:c r="E23" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E23" s="11" t="str">
+      <x:c r="F23" s="11" t="str">
         <x:v>2026-08-19</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="n">
+      <x:c r="G23" s="10" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G23" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H23" s="11" t="str"/>
-      <x:c r="I23" s="10" t="str">
+      <x:c r="H23" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="str"/>
+      <x:c r="J23" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2879,23 +3165,26 @@
       <x:c r="B24" s="10" t="str">
         <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
       </x:c>
-      <x:c r="C24" s="11" t="n">
-        <x:v>5</x:v>
+      <x:c r="C24" s="11" t="str">
+        <x:v>08-15 12:00</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E24" s="11" t="str">
+      <x:c r="E24" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
         <x:v>2026-08-21</x:v>
       </x:c>
-      <x:c r="F24" s="11" t="n">
+      <x:c r="G24" s="10" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G24" s="10" t="str">
+      <x:c r="H24" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H24" s="11" t="str"/>
-      <x:c r="I24" s="10" t="str">
+      <x:c r="I24" s="11" t="str"/>
+      <x:c r="J24" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2906,23 +3195,26 @@
       <x:c r="B25" s="10" t="str">
         <x:v>芯骨藏锋</x:v>
       </x:c>
-      <x:c r="C25" s="11" t="n">
-        <x:v>5</x:v>
+      <x:c r="C25" s="11" t="str">
+        <x:v>08-15 05:58</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="str">
+      <x:c r="E25" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
         <x:v>2026-08-20</x:v>
       </x:c>
-      <x:c r="F25" s="11" t="n">
+      <x:c r="G25" s="10" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G25" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="str"/>
-      <x:c r="I25" s="10" t="str">
+      <x:c r="H25" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="str"/>
+      <x:c r="J25" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜5次、累计5次，起量能力已被验证；仿真人制作；52集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -2933,23 +3225,26 @@
       <x:c r="B26" s="10" t="str">
         <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
-      <x:c r="C26" s="11" t="n">
+      <x:c r="C26" s="11" t="str">
+        <x:v>08-11 00:26</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D26" s="11" t="n">
+      <x:c r="E26" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="str">
+      <x:c r="F26" s="11" t="str">
         <x:v>2026-08-28</x:v>
       </x:c>
-      <x:c r="F26" s="11" t="n">
+      <x:c r="G26" s="10" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G26" s="10" t="str">
+      <x:c r="H26" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H26" s="11" t="str"/>
-      <x:c r="I26" s="10" t="str">
+      <x:c r="I26" s="11" t="str"/>
+      <x:c r="J26" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2960,25 +3255,28 @@
       <x:c r="B27" s="10" t="str">
         <x:v>余生逢玉伴心安</x:v>
       </x:c>
-      <x:c r="C27" s="11" t="n">
+      <x:c r="C27" s="11" t="str">
+        <x:v>07-13 14:00</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D27" s="11" t="n">
+      <x:c r="E27" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E27" s="11" t="str">
+      <x:c r="F27" s="11" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
-      <x:c r="F27" s="11" t="n">
+      <x:c r="G27" s="10" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G27" s="10" t="str">
+      <x:c r="H27" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H27" s="11" t="n">
+      <x:c r="I27" s="11" t="n">
         <x:v>785</x:v>
       </x:c>
-      <x:c r="I27" s="10" t="str">
+      <x:c r="J27" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -2989,23 +3287,26 @@
       <x:c r="B28" s="10" t="str">
         <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
-      <x:c r="C28" s="11" t="n">
+      <x:c r="C28" s="11" t="str">
+        <x:v>07-20 14:00</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="11" t="n">
+      <x:c r="E28" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="str">
+      <x:c r="F28" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
-      <x:c r="F28" s="11" t="n">
+      <x:c r="G28" s="10" t="n">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="G28" s="10" t="str">
+      <x:c r="H28" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H28" s="11" t="str"/>
-      <x:c r="I28" s="10" t="str">
+      <x:c r="I28" s="11" t="str"/>
+      <x:c r="J28" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计11次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -3016,23 +3317,26 @@
       <x:c r="B29" s="10" t="str">
         <x:v>这个姨娘不一般</x:v>
       </x:c>
-      <x:c r="C29" s="11" t="n">
+      <x:c r="C29" s="11" t="str">
+        <x:v>07-12 11:00</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D29" s="11" t="n">
+      <x:c r="E29" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="str">
+      <x:c r="F29" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
-      <x:c r="F29" s="11" t="n">
+      <x:c r="G29" s="10" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G29" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H29" s="11" t="str"/>
-      <x:c r="I29" s="10" t="str">
+      <x:c r="H29" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I29" s="11" t="str"/>
+      <x:c r="J29" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3043,23 +3347,26 @@
       <x:c r="B30" s="10" t="str">
         <x:v>重生凛冬跟随囤货</x:v>
       </x:c>
-      <x:c r="C30" s="11" t="n">
+      <x:c r="C30" s="11" t="str">
+        <x:v>08-16 13:16</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D30" s="11" t="n">
+      <x:c r="E30" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E30" s="11" t="str">
+      <x:c r="F30" s="11" t="str">
         <x:v>2026-08-29</x:v>
       </x:c>
-      <x:c r="F30" s="11" t="n">
+      <x:c r="G30" s="10" t="n">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G30" s="10" t="str">
+      <x:c r="H30" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H30" s="11" t="str"/>
-      <x:c r="I30" s="10" t="str">
+      <x:c r="I30" s="11" t="str"/>
+      <x:c r="J30" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计8次，起量能力已被验证；81集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -3070,23 +3377,26 @@
       <x:c r="B31" s="10" t="str">
         <x:v>九二年，他塞给我五百块</x:v>
       </x:c>
-      <x:c r="C31" s="11" t="n">
+      <x:c r="C31" s="11" t="str">
+        <x:v>08-09 13:57</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="11" t="n">
+      <x:c r="E31" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E31" s="11" t="str">
+      <x:c r="F31" s="11" t="str">
         <x:v>2026-08-18</x:v>
       </x:c>
-      <x:c r="F31" s="11" t="n">
+      <x:c r="G31" s="10" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G31" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H31" s="11" t="str"/>
-      <x:c r="I31" s="10" t="str">
+      <x:c r="H31" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I31" s="11" t="str"/>
+      <x:c r="J31" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3097,23 +3407,26 @@
       <x:c r="B32" s="10" t="str">
         <x:v>傻女重生记，睁眼后盖房发家</x:v>
       </x:c>
-      <x:c r="C32" s="11" t="n">
+      <x:c r="C32" s="11" t="str">
+        <x:v>07-10 17:00</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D32" s="11" t="n">
+      <x:c r="E32" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E32" s="11" t="str">
+      <x:c r="F32" s="11" t="str">
         <x:v>2026-08-23</x:v>
       </x:c>
-      <x:c r="F32" s="11" t="n">
+      <x:c r="G32" s="10" t="n">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G32" s="10" t="str">
+      <x:c r="H32" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H32" s="11" t="str"/>
-      <x:c r="I32" s="10" t="str">
+      <x:c r="I32" s="11" t="str"/>
+      <x:c r="J32" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3124,23 +3437,26 @@
       <x:c r="B33" s="10" t="str">
         <x:v>医风秩序线</x:v>
       </x:c>
-      <x:c r="C33" s="11" t="n">
+      <x:c r="C33" s="11" t="str">
+        <x:v>08-17 11:00</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="11" t="n">
+      <x:c r="E33" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E33" s="11" t="str">
+      <x:c r="F33" s="11" t="str">
         <x:v>2026-08-23</x:v>
       </x:c>
-      <x:c r="F33" s="11" t="n">
+      <x:c r="G33" s="10" t="n">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G33" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H33" s="11" t="str"/>
-      <x:c r="I33" s="10" t="str">
+      <x:c r="H33" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I33" s="11" t="str"/>
+      <x:c r="J33" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；89集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3151,23 +3467,26 @@
       <x:c r="B34" s="10" t="str">
         <x:v>各生归途</x:v>
       </x:c>
-      <x:c r="C34" s="11" t="n">
+      <x:c r="C34" s="11" t="str">
+        <x:v>08-17 17:50</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D34" s="11" t="n">
+      <x:c r="E34" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E34" s="11" t="str">
+      <x:c r="F34" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
-      <x:c r="F34" s="11" t="n">
+      <x:c r="G34" s="10" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G34" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H34" s="11" t="str"/>
-      <x:c r="I34" s="10" t="str">
+      <x:c r="H34" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I34" s="11" t="str"/>
+      <x:c r="J34" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；82集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3178,23 +3497,26 @@
       <x:c r="B35" s="10" t="str">
         <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
       </x:c>
-      <x:c r="C35" s="11" t="n">
+      <x:c r="C35" s="11" t="str">
+        <x:v>08-13 06:00</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D35" s="11" t="n">
+      <x:c r="E35" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E35" s="11" t="str">
+      <x:c r="F35" s="11" t="str">
         <x:v>2026-08-19</x:v>
       </x:c>
-      <x:c r="F35" s="11" t="n">
+      <x:c r="G35" s="10" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G35" s="10" t="str">
+      <x:c r="H35" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H35" s="11" t="str"/>
-      <x:c r="I35" s="10" t="str">
+      <x:c r="I35" s="11" t="str"/>
+      <x:c r="J35" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3205,23 +3527,26 @@
       <x:c r="B36" s="10" t="str">
         <x:v>一墙之隔的求救声</x:v>
       </x:c>
-      <x:c r="C36" s="11" t="n">
+      <x:c r="C36" s="11" t="str">
+        <x:v>08-15 09:18</x:v>
+      </x:c>
+      <x:c r="D36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D36" s="11" t="n">
+      <x:c r="E36" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E36" s="11" t="str">
+      <x:c r="F36" s="11" t="str">
         <x:v>2026-08-22</x:v>
       </x:c>
-      <x:c r="F36" s="11" t="n">
+      <x:c r="G36" s="10" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G36" s="10" t="str">
+      <x:c r="H36" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H36" s="11" t="str"/>
-      <x:c r="I36" s="10" t="str">
+      <x:c r="I36" s="11" t="str"/>
+      <x:c r="J36" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；88集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3232,23 +3557,26 @@
       <x:c r="B37" s="10" t="str">
         <x:v>五福临门，八方报喜</x:v>
       </x:c>
-      <x:c r="C37" s="11" t="n">
+      <x:c r="C37" s="11" t="str">
+        <x:v>08-17 10:18</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D37" s="11" t="n">
+      <x:c r="E37" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E37" s="11" t="str">
+      <x:c r="F37" s="11" t="str">
         <x:v>2026-08-22</x:v>
       </x:c>
-      <x:c r="F37" s="11" t="n">
+      <x:c r="G37" s="10" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G37" s="10" t="str">
+      <x:c r="H37" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H37" s="11" t="str"/>
-      <x:c r="I37" s="10" t="str">
+      <x:c r="I37" s="11" t="str"/>
+      <x:c r="J37" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3259,23 +3587,26 @@
       <x:c r="B38" s="10" t="str">
         <x:v>大唐：我真没想当国舅爷啊</x:v>
       </x:c>
-      <x:c r="C38" s="11" t="n">
+      <x:c r="C38" s="11" t="str">
+        <x:v>08-14 16:04</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D38" s="11" t="n">
+      <x:c r="E38" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="str">
+      <x:c r="F38" s="11" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
-      <x:c r="F38" s="11" t="n">
+      <x:c r="G38" s="10" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G38" s="10" t="str">
+      <x:c r="H38" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="H38" s="11" t="str"/>
-      <x:c r="I38" s="10" t="str">
+      <x:c r="I38" s="11" t="str"/>
+      <x:c r="J38" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；71集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
@@ -3286,23 +3617,26 @@
       <x:c r="B39" s="10" t="str">
         <x:v>捡到小蛇，我养出龙崽</x:v>
       </x:c>
-      <x:c r="C39" s="11" t="n">
+      <x:c r="C39" s="11" t="str">
+        <x:v>08-08 10:08</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D39" s="11" t="n">
+      <x:c r="E39" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E39" s="11" t="str">
+      <x:c r="F39" s="11" t="str">
         <x:v>2026-08-21</x:v>
       </x:c>
-      <x:c r="F39" s="11" t="n">
+      <x:c r="G39" s="10" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G39" s="10" t="str">
+      <x:c r="H39" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H39" s="11" t="str"/>
-      <x:c r="I39" s="10" t="str">
+      <x:c r="I39" s="11" t="str"/>
+      <x:c r="J39" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；61集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3313,23 +3647,26 @@
       <x:c r="B40" s="10" t="str">
         <x:v>一辆旧中巴奔向新生活</x:v>
       </x:c>
-      <x:c r="C40" s="11" t="n">
-        <x:v>4</x:v>
+      <x:c r="C40" s="11" t="str">
+        <x:v>08-14 15:00</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E40" s="11" t="str">
+      <x:c r="E40" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
         <x:v>2026-08-20</x:v>
       </x:c>
-      <x:c r="F40" s="11" t="n">
+      <x:c r="G40" s="10" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G40" s="10" t="str">
+      <x:c r="H40" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="H40" s="11" t="str"/>
-      <x:c r="I40" s="10" t="str">
+      <x:c r="I40" s="11" t="str"/>
+      <x:c r="J40" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计4次，起量能力已被验证；82集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
@@ -3340,23 +3677,26 @@
       <x:c r="B41" s="10" t="str">
         <x:v>老婆每月给别人一万五，离婚时她后悔了</x:v>
       </x:c>
-      <x:c r="C41" s="11" t="n">
-        <x:v>4</x:v>
+      <x:c r="C41" s="11" t="str">
+        <x:v>08-14 10:00</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E41" s="11" t="str">
+      <x:c r="E41" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
         <x:v>2026-08-18</x:v>
       </x:c>
-      <x:c r="F41" s="11" t="n">
+      <x:c r="G41" s="10" t="n">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G41" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="H41" s="11" t="str"/>
-      <x:c r="I41" s="10" t="str">
+      <x:c r="H41" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I41" s="11" t="str"/>
+      <x:c r="J41" s="10" t="str">
         <x:v>8-15~8-21两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；113集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rc1514b873a3c43b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Rc880ef7e66ba46f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R34579a5661544d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rc743ae3db9d648ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="Re70cf5785f834409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rbd0b699cd0a2417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R2e56e295b9a6440f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R5f6e5cd11bb44d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rd57e58139e154983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R1cb6c2a47ba24163"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5257,6 +5257,1166 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B54" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C54" s="10" t="str">
+        <x:v>绝地重生：揭穿闺蜜虚伪的面具</x:v>
+      </x:c>
+      <x:c r="D54" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E54" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F54" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str">
+        <x:v>不兜</x:v>
+      </x:c>
+      <x:c r="H54" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「不兜」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I54" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B55" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="str">
+        <x:v>丈夫坑娃，我绝不认输</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F55" s="10" t="str">
+        <x:v>萌宝治愈 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G55" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H55" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I55" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B56" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C56" s="10" t="str">
+        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
+      </x:c>
+      <x:c r="D56" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F56" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G56" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H56" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I56" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B57" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C57" s="10" t="str">
+        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
+      </x:c>
+      <x:c r="D57" s="11" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E57" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F57" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G57" s="10" t="str">
+        <x:v>初八漫剧</x:v>
+      </x:c>
+      <x:c r="H57" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I57" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B58" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C58" s="10" t="str">
+        <x:v>同频心动</x:v>
+      </x:c>
+      <x:c r="D58" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E58" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F58" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H58" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I58" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B59" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C59" s="10" t="str">
+        <x:v>婚礼前夜，我换了新郎</x:v>
+      </x:c>
+      <x:c r="D59" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E59" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F59" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G59" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H59" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I59" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B60" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C60" s="10" t="str">
+        <x:v>玻璃钻戒终结七年错爱</x:v>
+      </x:c>
+      <x:c r="D60" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E60" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F60" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G60" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H60" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I60" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B61" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C61" s="10" t="str">
+        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F61" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G61" s="10" t="str">
+        <x:v>保温虾虾</x:v>
+      </x:c>
+      <x:c r="H61" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
+      </x:c>
+      <x:c r="I61" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B62" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C62" s="10" t="str">
+        <x:v>下午的早餐店第五季</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E62" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F62" s="10" t="str">
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="G62" s="10" t="str">
+        <x:v>盐系少女社</x:v>
+      </x:c>
+      <x:c r="H62" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I62" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B63" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C63" s="10" t="str">
+        <x:v>不朽仙秦！第三季</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="E63" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F63" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G63" s="10" t="str">
+        <x:v>虾仁白白</x:v>
+      </x:c>
+      <x:c r="H63" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I63" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B64" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C64" s="10" t="str">
+        <x:v>五十保姆觉醒，遗产见人心</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E64" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F64" s="10" t="str">
+        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G64" s="10" t="str">
+        <x:v>剑心动漫</x:v>
+      </x:c>
+      <x:c r="H64" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
+      </x:c>
+      <x:c r="I64" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B65" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C65" s="10" t="str">
+        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F65" s="10" t="str">
+        <x:v>美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G65" s="10" t="str">
+        <x:v>晟樊影视</x:v>
+      </x:c>
+      <x:c r="H65" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
+      </x:c>
+      <x:c r="I65" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B66" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C66" s="10" t="str">
+        <x:v>全民御兽：神级鉴兽师第二季</x:v>
+      </x:c>
+      <x:c r="D66" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E66" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F66" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G66" s="10" t="str">
+        <x:v>漫川动漫剧场</x:v>
+      </x:c>
+      <x:c r="H66" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I66" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B67" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C67" s="10" t="str">
+        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F67" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G67" s="10" t="str">
+        <x:v>竹蜻蜓剧场</x:v>
+      </x:c>
+      <x:c r="H67" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I67" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B68" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C68" s="10" t="str">
+        <x:v>农场萌宠！第六季</x:v>
+      </x:c>
+      <x:c r="D68" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E68" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F68" s="10" t="str">
+        <x:v>种田囤货 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G68" s="10" t="str">
+        <x:v>惜惜动漫</x:v>
+      </x:c>
+      <x:c r="H68" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I68" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B69" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C69" s="10" t="str">
+        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F69" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G69" s="10" t="str">
+        <x:v>枕月漫影</x:v>
+      </x:c>
+      <x:c r="H69" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I69" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B70" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C70" s="10" t="str">
+        <x:v>利益照见人心</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E70" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F70" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G70" s="10" t="str">
+        <x:v>天天爱看剧</x:v>
+      </x:c>
+      <x:c r="H70" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
+      </x:c>
+      <x:c r="I70" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B71" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C71" s="10" t="str">
+        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E71" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F71" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G71" s="10" t="str">
+        <x:v>月亮与孤岛</x:v>
+      </x:c>
+      <x:c r="H71" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I71" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B72" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C72" s="10" t="str">
+        <x:v>剑定山河第一季</x:v>
+      </x:c>
+      <x:c r="D72" s="11" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E72" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F72" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G72" s="10" t="str">
+        <x:v>捷捷动漫馆</x:v>
+      </x:c>
+      <x:c r="H72" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I72" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B73" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C73" s="10" t="str">
+        <x:v>反向养老：从出卖孙女到宠冠全村2</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F73" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G73" s="10" t="str">
+        <x:v>灵梦剧场</x:v>
+      </x:c>
+      <x:c r="H73" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I73" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B74" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="str">
+        <x:v>一张照片传遍公司群我却因此重生了</x:v>
+      </x:c>
+      <x:c r="D74" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E74" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F74" s="10" t="str">
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="G74" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H74" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I74" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B75" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C75" s="10" t="str">
+        <x:v>一纸通知书，丈夫托我赴前程</x:v>
+      </x:c>
+      <x:c r="D75" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E75" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F75" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G75" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H75" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I75" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B76" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C76" s="10" t="str">
+        <x:v>一顿饭算清</x:v>
+      </x:c>
+      <x:c r="D76" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E76" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F76" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="G76" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H76" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I76" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B77" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C77" s="10" t="str">
+        <x:v>一顿香锅断前缘</x:v>
+      </x:c>
+      <x:c r="D77" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E77" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F77" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G77" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H77" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I77" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B78" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C78" s="10" t="str">
+        <x:v>仙尊归来，四大家族慌了</x:v>
+      </x:c>
+      <x:c r="D78" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E78" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F78" s="10" t="str">
+        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G78" s="10" t="str">
+        <x:v>西瑶短剧</x:v>
+      </x:c>
+      <x:c r="H78" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I78" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B79" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C79" s="10" t="str">
+        <x:v>嫁妆被抢那天我亮明了身份</x:v>
+      </x:c>
+      <x:c r="D79" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E79" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F79" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H79" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I79" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B80" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C80" s="10" t="str">
+        <x:v>带男友回大山继承家产</x:v>
+      </x:c>
+      <x:c r="D80" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E80" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F80" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G80" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H80" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I80" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C81" s="10" t="str">
+        <x:v>末世，带着修改器重生，我无敌了2</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F81" s="10" t="str">
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G81" s="10" t="str">
+        <x:v>机甲熊</x:v>
+      </x:c>
+      <x:c r="H81" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I81" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B82" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C82" s="10" t="str">
+        <x:v>错写红封，终断婚约</x:v>
+      </x:c>
+      <x:c r="D82" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E82" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F82" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G82" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H82" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I82" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C83" s="10" t="str">
+        <x:v>一井见人心</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F83" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G83" s="10" t="str">
+        <x:v>云间予安</x:v>
+      </x:c>
+      <x:c r="H83" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
+      </x:c>
+      <x:c r="I83" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B84" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C84" s="10" t="str">
+        <x:v>一渠清水见人心</x:v>
+      </x:c>
+      <x:c r="D84" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E84" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F84" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G84" s="10" t="str">
+        <x:v>心痕剧场</x:v>
+      </x:c>
+      <x:c r="H84" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
+      </x:c>
+      <x:c r="I84" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C85" s="10" t="str">
+        <x:v>七天照见人心</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F85" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G85" s="10" t="str">
+        <x:v>倩倩短剧</x:v>
+      </x:c>
+      <x:c r="H85" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
+      </x:c>
+      <x:c r="I85" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B86" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C86" s="10" t="str">
+        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
+      </x:c>
+      <x:c r="D86" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E86" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F86" s="10" t="str">
+        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="G86" s="10" t="str">
+        <x:v>溪溪剧场</x:v>
+      </x:c>
+      <x:c r="H86" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I86" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B87" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C87" s="10" t="str">
+        <x:v>假面羁绊：极客先生的秘密</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F87" s="10" t="str">
+        <x:v>美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G87" s="10" t="str">
+        <x:v>北极熊短剧</x:v>
+      </x:c>
+      <x:c r="H87" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
+      </x:c>
+      <x:c r="I87" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B88" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C88" s="10" t="str">
+        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
+      </x:c>
+      <x:c r="D88" s="11" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E88" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F88" s="10" t="str">
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G88" s="10" t="str">
+        <x:v>浪客剧场</x:v>
+      </x:c>
+      <x:c r="H88" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
+      </x:c>
+      <x:c r="I88" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B89" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C89" s="10" t="str">
+        <x:v>农村兽神第五季</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F89" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G89" s="10" t="str">
+        <x:v>每日欢乐漫剧</x:v>
+      </x:c>
+      <x:c r="H89" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I89" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B90" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C90" s="10" t="str">
+        <x:v>匠心逆袭：我为行业立规矩</x:v>
+      </x:c>
+      <x:c r="D90" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E90" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F90" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G90" s="10" t="str">
+        <x:v>五碗说漫</x:v>
+      </x:c>
+      <x:c r="H90" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
+      </x:c>
+      <x:c r="I90" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B91" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C91" s="10" t="str">
+        <x:v>囤货逆袭大佬末世之归途</x:v>
+      </x:c>
+      <x:c r="D91" s="11" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E91" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F91" s="10" t="str">
+        <x:v>种田囤货 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G91" s="10" t="str">
+        <x:v>逐梦剧场</x:v>
+      </x:c>
+      <x:c r="H91" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
+      </x:c>
+      <x:c r="I91" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B92" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C92" s="10" t="str">
+        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
+      </x:c>
+      <x:c r="D92" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E92" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F92" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G92" s="10" t="str">
+        <x:v>小奶团动画</x:v>
+      </x:c>
+      <x:c r="H92" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I92" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B93" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C93" s="10" t="str">
+        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
+      </x:c>
+      <x:c r="D93" s="11" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F93" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G93" s="10" t="str">
+        <x:v>闲人一坤</x:v>
+      </x:c>
+      <x:c r="H93" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I93" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rbd0b699cd0a2417c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R2e56e295b9a6440f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R5f6e5cd11bb44d4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rd57e58139e154983"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R1cb6c2a47ba24163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R5e1c1e69e2e54a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Re1f0f13e24044c43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Raacb2d2c3961425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rafba5a3e438846db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R506c94072991440d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5265,22 +5265,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>绝地重生：揭穿闺蜜虚伪的面具</x:v>
+        <x:v>重生归来，我把爸爸捧上神坛</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>家庭伦理 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G54" s="10" t="str">
-        <x:v>不兜</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「不兜」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸 / 战神异能）；发布账号「闪闪动漫社」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I54" s="11" t="n">
         <x:v>9</x:v>
@@ -5294,22 +5294,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>丈夫坑娃，我绝不认输</x:v>
+        <x:v>1977山猎重生，我以余生偿前错第三季</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>萌宝治愈 / 婚姻情感</x:v>
+        <x:v>年代怀旧 / 种田囤货</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；307集，集数偏短/超长需关注；题材契合爆款主线（年代怀旧 / 种田囤货）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I55" s="11" t="n">
         <x:v>8</x:v>
@@ -5323,22 +5323,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
+        <x:v>丈夫坑娃，我绝不认输</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F56" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>萌宝治愈 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I56" s="11" t="n">
         <x:v>8</x:v>
@@ -5352,22 +5352,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
+        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>107</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
-        <x:v>初八漫剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I57" s="11" t="n">
         <x:v>8</x:v>
@@ -5381,22 +5381,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>同频心动</x:v>
+        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G58" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>初八漫剧</x:v>
       </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I58" s="11" t="n">
         <x:v>8</x:v>
@@ -5410,10 +5410,10 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>婚礼前夜，我换了新郎</x:v>
+        <x:v>同频心动</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -5425,7 +5425,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I59" s="11" t="n">
         <x:v>8</x:v>
@@ -5439,10 +5439,10 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>玻璃钻戒终结七年错爱</x:v>
+        <x:v>婚礼前夜，我换了新郎</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -5454,7 +5454,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I60" s="11" t="n">
         <x:v>8</x:v>
@@ -5468,25 +5468,25 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
+        <x:v>玻璃钻戒终结七年错爱</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>保温虾虾</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I61" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -5497,22 +5497,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>下午的早餐店第五季</x:v>
+        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>盐系少女社</x:v>
+        <x:v>保温虾虾</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
       </x:c>
       <x:c r="I62" s="11" t="n">
         <x:v>7</x:v>
@@ -5526,22 +5526,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>不朽仙秦！第三季</x:v>
+        <x:v>下午的早餐店第五季</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>190</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
-        <x:v>虾仁白白</x:v>
+        <x:v>盐系少女社</x:v>
       </x:c>
       <x:c r="H63" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I63" s="11" t="n">
         <x:v>7</x:v>
@@ -5555,22 +5555,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>五十保姆觉醒，遗产见人心</x:v>
+        <x:v>不朽仙秦！第三季</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
-        <x:v>剑心动漫</x:v>
+        <x:v>虾仁白白</x:v>
       </x:c>
       <x:c r="H64" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I64" s="11" t="n">
         <x:v>7</x:v>
@@ -5584,22 +5584,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
+        <x:v>五十保姆觉醒，遗产见人心</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
-        <x:v>晟樊影视</x:v>
+        <x:v>剑心动漫</x:v>
       </x:c>
       <x:c r="H65" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
       </x:c>
       <x:c r="I65" s="11" t="n">
         <x:v>7</x:v>
@@ -5613,22 +5613,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>全民御兽：神级鉴兽师第二季</x:v>
+        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
-        <x:v>漫川动漫剧场</x:v>
+        <x:v>晟樊影视</x:v>
       </x:c>
       <x:c r="H66" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
       </x:c>
       <x:c r="I66" s="11" t="n">
         <x:v>7</x:v>
@@ -5642,10 +5642,10 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
+        <x:v>全民御兽：神级鉴兽师第二季</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -5654,10 +5654,10 @@
         <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
-        <x:v>竹蜻蜓剧场</x:v>
+        <x:v>漫川动漫剧场</x:v>
       </x:c>
       <x:c r="H67" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I67" s="11" t="n">
         <x:v>7</x:v>
@@ -5671,22 +5671,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>农场萌宠！第六季</x:v>
+        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>种田囤货 / 婚姻情感</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>惜惜动漫</x:v>
+        <x:v>竹蜻蜓剧场</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I68" s="11" t="n">
         <x:v>7</x:v>
@@ -5700,22 +5700,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
+        <x:v>农场萌宠！第六季</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>种田囤货 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>枕月漫影</x:v>
+        <x:v>惜惜动漫</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I69" s="11" t="n">
         <x:v>7</x:v>
@@ -5729,22 +5729,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>利益照见人心</x:v>
+        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>天天爱看剧</x:v>
+        <x:v>枕月漫影</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I70" s="11" t="n">
         <x:v>7</x:v>
@@ -5758,22 +5758,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
+        <x:v>利益照见人心</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G71" s="10" t="str">
-        <x:v>月亮与孤岛</x:v>
+        <x:v>天天爱看剧</x:v>
       </x:c>
       <x:c r="H71" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
       </x:c>
       <x:c r="I71" s="11" t="n">
         <x:v>7</x:v>
@@ -5787,22 +5787,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>剑定山河第一季</x:v>
+        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>捷捷动漫馆</x:v>
+        <x:v>月亮与孤岛</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I72" s="11" t="n">
         <x:v>7</x:v>
@@ -5816,22 +5816,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>反向养老：从出卖孙女到宠冠全村2</x:v>
+        <x:v>剑定山河第一季</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F73" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
+        <x:v>捷捷动漫馆</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I73" s="11" t="n">
         <x:v>7</x:v>
@@ -5961,22 +5961,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>仙尊归来，四大家族慌了</x:v>
+        <x:v>嫁妆被抢那天我亮明了身份</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I78" s="11" t="n">
         <x:v>8</x:v>
@@ -5990,22 +5990,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>嫁妆被抢那天我亮明了身份</x:v>
+        <x:v>带男友回大山继承家产</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="G79" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H79" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I79" s="11" t="n">
         <x:v>8</x:v>
@@ -6019,22 +6019,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>带男友回大山继承家产</x:v>
+        <x:v>末世，带着修改器重生，我无敌了2</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>机甲熊</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I80" s="11" t="n">
         <x:v>8</x:v>
@@ -6048,22 +6048,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>末世，带着修改器重生，我无敌了2</x:v>
+        <x:v>错写红封，终断婚约</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>机甲熊</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I81" s="11" t="n">
         <x:v>8</x:v>
@@ -6077,25 +6077,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>错写红封，终断婚约</x:v>
+        <x:v>一井见人心</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>云间予安</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
       </x:c>
       <x:c r="I82" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -6106,10 +6106,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>一井见人心</x:v>
+        <x:v>一渠清水见人心</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -6118,10 +6118,10 @@
         <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>云间予安</x:v>
+        <x:v>心痕剧场</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
       </x:c>
       <x:c r="I83" s="11" t="n">
         <x:v>7</x:v>
@@ -6135,10 +6135,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>一渠清水见人心</x:v>
+        <x:v>七天照见人心</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -6147,10 +6147,10 @@
         <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>心痕剧场</x:v>
+        <x:v>倩倩短剧</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
       </x:c>
       <x:c r="I84" s="11" t="n">
         <x:v>7</x:v>
@@ -6164,22 +6164,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>七天照见人心</x:v>
+        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>倩倩短剧</x:v>
+        <x:v>溪溪剧场</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I85" s="11" t="n">
         <x:v>7</x:v>
@@ -6193,22 +6193,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
+        <x:v>假面羁绊：极客先生的秘密</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>溪溪剧场</x:v>
+        <x:v>北极熊短剧</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
       </x:c>
       <x:c r="I86" s="11" t="n">
         <x:v>7</x:v>
@@ -6222,22 +6222,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>假面羁绊：极客先生的秘密</x:v>
+        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>北极熊短剧</x:v>
+        <x:v>浪客剧场</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
       </x:c>
       <x:c r="I87" s="11" t="n">
         <x:v>7</x:v>
@@ -6251,22 +6251,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
+        <x:v>农村兽神第五季</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>浪客剧场</x:v>
+        <x:v>每日欢乐漫剧</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I88" s="11" t="n">
         <x:v>7</x:v>
@@ -6280,22 +6280,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>农村兽神第五季</x:v>
+        <x:v>匠心逆袭：我为行业立规矩</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F89" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>每日欢乐漫剧</x:v>
+        <x:v>五碗说漫</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
       </x:c>
       <x:c r="I89" s="11" t="n">
         <x:v>7</x:v>
@@ -6309,22 +6309,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>匠心逆袭：我为行业立规矩</x:v>
+        <x:v>囤货逆袭大佬末世之归途</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>种田囤货 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>五碗说漫</x:v>
+        <x:v>逐梦剧场</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
       </x:c>
       <x:c r="I90" s="11" t="n">
         <x:v>7</x:v>
@@ -6338,22 +6338,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>囤货逆袭大佬末世之归途</x:v>
+        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>种田囤货 / 逆袭打脸</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>逐梦剧场</x:v>
+        <x:v>小奶团动画</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I91" s="11" t="n">
         <x:v>7</x:v>
@@ -6367,22 +6367,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
+        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>小奶团动画</x:v>
+        <x:v>闲人一坤</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I92" s="11" t="n">
         <x:v>7</x:v>
@@ -6396,22 +6396,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
+        <x:v>家庭主妇的逆袭：亲手送他入狱</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>闲人一坤</x:v>
+        <x:v>九鲤动漫</x:v>
       </x:c>
       <x:c r="H93" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="I93" s="11" t="n">
         <x:v>7</x:v>
@@ -6969,10 +6969,10 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B58" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C58" s="11" t="str"/>
     </x:row>
@@ -6981,124 +6981,124 @@
         <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C59" s="11" t="str"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C63" s="11" t="str"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C64" s="11" t="str"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
-        <x:v>不兜</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C65" s="11" t="str"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
-        <x:v>喵喵说书</x:v>
+        <x:v>咕咚剧场</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C66" s="11" t="str"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>一样漫剧</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>取瘾书屋</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>清风短剧场</x:v>
+        <x:v>一张不够花</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>亦辰动漫</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>暖星追剧</x:v>
+        <x:v>星漫剧场</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>周八宝</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str"/>
     </x:row>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R5e1c1e69e2e54a84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="Re1f0f13e24044c43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Raacb2d2c3961425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rafba5a3e438846db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R506c94072991440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rba14812b53cd4251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R0cddf7f6268c4fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rba47a54fd6424dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rccc5623ea6994ead"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R47bc235260644752"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5265,22 +5265,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>重生归来，我把爸爸捧上神坛</x:v>
+        <x:v>绝地重生：揭穿闺蜜虚伪的面具</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸 / 战神异能</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G54" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>不兜</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸 / 战神异能）；发布账号「闪闪动漫社」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「不兜」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I54" s="11" t="n">
         <x:v>9</x:v>
@@ -5294,22 +5294,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>1977山猎重生，我以余生偿前错第三季</x:v>
+        <x:v>丈夫坑娃，我绝不认输</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>307</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
+        <x:v>萌宝治愈 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；307集，集数偏短/超长需关注；题材契合爆款主线（年代怀旧 / 种田囤货）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I55" s="11" t="n">
         <x:v>8</x:v>
@@ -5323,22 +5323,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>丈夫坑娃，我绝不认输</x:v>
+        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F56" s="10" t="str">
-        <x:v>萌宝治愈 / 婚姻情感</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I56" s="11" t="n">
         <x:v>8</x:v>
@@ -5352,22 +5352,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
+        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>初八漫剧</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I57" s="11" t="n">
         <x:v>8</x:v>
@@ -5381,22 +5381,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
+        <x:v>同频心动</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>107</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G58" s="10" t="str">
-        <x:v>初八漫剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I58" s="11" t="n">
         <x:v>8</x:v>
@@ -5410,10 +5410,10 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>同频心动</x:v>
+        <x:v>婚礼前夜，我换了新郎</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -5425,7 +5425,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I59" s="11" t="n">
         <x:v>8</x:v>
@@ -5439,10 +5439,10 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>婚礼前夜，我换了新郎</x:v>
+        <x:v>玻璃钻戒终结七年错爱</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -5454,7 +5454,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I60" s="11" t="n">
         <x:v>8</x:v>
@@ -5468,25 +5468,25 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>玻璃钻戒终结七年错爱</x:v>
+        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>保温虾虾</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
       </x:c>
       <x:c r="I61" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -5497,22 +5497,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
+        <x:v>下午的早餐店第五季</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>保温虾虾</x:v>
+        <x:v>盐系少女社</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I62" s="11" t="n">
         <x:v>7</x:v>
@@ -5526,22 +5526,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>下午的早餐店第五季</x:v>
+        <x:v>不朽仙秦！第三季</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
-        <x:v>盐系少女社</x:v>
+        <x:v>虾仁白白</x:v>
       </x:c>
       <x:c r="H63" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I63" s="11" t="n">
         <x:v>7</x:v>
@@ -5555,22 +5555,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>不朽仙秦！第三季</x:v>
+        <x:v>五十保姆觉醒，遗产见人心</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>190</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
-        <x:v>虾仁白白</x:v>
+        <x:v>剑心动漫</x:v>
       </x:c>
       <x:c r="H64" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
       </x:c>
       <x:c r="I64" s="11" t="n">
         <x:v>7</x:v>
@@ -5584,22 +5584,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>五十保姆觉醒，遗产见人心</x:v>
+        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
-        <x:v>剑心动漫</x:v>
+        <x:v>晟樊影视</x:v>
       </x:c>
       <x:c r="H65" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
       </x:c>
       <x:c r="I65" s="11" t="n">
         <x:v>7</x:v>
@@ -5613,22 +5613,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
+        <x:v>全民御兽：神级鉴兽师第二季</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
-        <x:v>晟樊影视</x:v>
+        <x:v>漫川动漫剧场</x:v>
       </x:c>
       <x:c r="H66" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I66" s="11" t="n">
         <x:v>7</x:v>
@@ -5642,10 +5642,10 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>全民御兽：神级鉴兽师第二季</x:v>
+        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
         <x:v>经典3D</x:v>
@@ -5654,10 +5654,10 @@
         <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
-        <x:v>漫川动漫剧场</x:v>
+        <x:v>竹蜻蜓剧场</x:v>
       </x:c>
       <x:c r="H67" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I67" s="11" t="n">
         <x:v>7</x:v>
@@ -5671,22 +5671,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
+        <x:v>农场萌宠！第六季</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>种田囤货 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>竹蜻蜓剧场</x:v>
+        <x:v>惜惜动漫</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I68" s="11" t="n">
         <x:v>7</x:v>
@@ -5700,22 +5700,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>农场萌宠！第六季</x:v>
+        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>种田囤货 / 婚姻情感</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>惜惜动漫</x:v>
+        <x:v>枕月漫影</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I69" s="11" t="n">
         <x:v>7</x:v>
@@ -5729,22 +5729,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
+        <x:v>利益照见人心</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>枕月漫影</x:v>
+        <x:v>天天爱看剧</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
       </x:c>
       <x:c r="I70" s="11" t="n">
         <x:v>7</x:v>
@@ -5758,22 +5758,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>利益照见人心</x:v>
+        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G71" s="10" t="str">
-        <x:v>天天爱看剧</x:v>
+        <x:v>月亮与孤岛</x:v>
       </x:c>
       <x:c r="H71" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I71" s="11" t="n">
         <x:v>7</x:v>
@@ -5787,22 +5787,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
+        <x:v>剑定山河第一季</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>月亮与孤岛</x:v>
+        <x:v>捷捷动漫馆</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I72" s="11" t="n">
         <x:v>7</x:v>
@@ -5816,22 +5816,22 @@
         <x:v>09·02</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>剑定山河第一季</x:v>
+        <x:v>反向养老：从出卖孙女到宠冠全村2</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F73" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>捷捷动漫馆</x:v>
+        <x:v>灵梦剧场</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I73" s="11" t="n">
         <x:v>7</x:v>
@@ -5961,22 +5961,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>嫁妆被抢那天我亮明了身份</x:v>
+        <x:v>仙尊归来，四大家族慌了</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I78" s="11" t="n">
         <x:v>8</x:v>
@@ -5990,22 +5990,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>带男友回大山继承家产</x:v>
+        <x:v>嫁妆被抢那天我亮明了身份</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G79" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H79" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I79" s="11" t="n">
         <x:v>8</x:v>
@@ -6019,22 +6019,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>末世，带着修改器重生，我无敌了2</x:v>
+        <x:v>带男友回大山继承家产</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>机甲熊</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I80" s="11" t="n">
         <x:v>8</x:v>
@@ -6048,22 +6048,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>错写红封，终断婚约</x:v>
+        <x:v>末世，带着修改器重生，我无敌了2</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>机甲熊</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I81" s="11" t="n">
         <x:v>8</x:v>
@@ -6077,25 +6077,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>一井见人心</x:v>
+        <x:v>错写红封，终断婚约</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>云间予安</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
       <x:c r="I82" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -6106,10 +6106,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>一渠清水见人心</x:v>
+        <x:v>一井见人心</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -6118,10 +6118,10 @@
         <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>心痕剧场</x:v>
+        <x:v>云间予安</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
       </x:c>
       <x:c r="I83" s="11" t="n">
         <x:v>7</x:v>
@@ -6135,10 +6135,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>七天照见人心</x:v>
+        <x:v>一渠清水见人心</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>仿真人</x:v>
@@ -6147,10 +6147,10 @@
         <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>倩倩短剧</x:v>
+        <x:v>心痕剧场</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
       </x:c>
       <x:c r="I84" s="11" t="n">
         <x:v>7</x:v>
@@ -6164,22 +6164,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
+        <x:v>七天照见人心</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>溪溪剧场</x:v>
+        <x:v>倩倩短剧</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
       </x:c>
       <x:c r="I85" s="11" t="n">
         <x:v>7</x:v>
@@ -6193,22 +6193,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>假面羁绊：极客先生的秘密</x:v>
+        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>北极熊短剧</x:v>
+        <x:v>溪溪剧场</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I86" s="11" t="n">
         <x:v>7</x:v>
@@ -6222,22 +6222,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
+        <x:v>假面羁绊：极客先生的秘密</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>浪客剧场</x:v>
+        <x:v>北极熊短剧</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
       </x:c>
       <x:c r="I87" s="11" t="n">
         <x:v>7</x:v>
@@ -6251,22 +6251,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>农村兽神第五季</x:v>
+        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>每日欢乐漫剧</x:v>
+        <x:v>浪客剧场</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
       </x:c>
       <x:c r="I88" s="11" t="n">
         <x:v>7</x:v>
@@ -6280,22 +6280,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>匠心逆袭：我为行业立规矩</x:v>
+        <x:v>农村兽神第五季</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F89" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>五碗说漫</x:v>
+        <x:v>每日欢乐漫剧</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I89" s="11" t="n">
         <x:v>7</x:v>
@@ -6309,22 +6309,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>囤货逆袭大佬末世之归途</x:v>
+        <x:v>匠心逆袭：我为行业立规矩</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>种田囤货 / 逆袭打脸</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>逐梦剧场</x:v>
+        <x:v>五碗说漫</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
       </x:c>
       <x:c r="I90" s="11" t="n">
         <x:v>7</x:v>
@@ -6338,22 +6338,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
+        <x:v>囤货逆袭大佬末世之归途</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>种田囤货 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>小奶团动画</x:v>
+        <x:v>逐梦剧场</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
       </x:c>
       <x:c r="I91" s="11" t="n">
         <x:v>7</x:v>
@@ -6367,22 +6367,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
+        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>闲人一坤</x:v>
+        <x:v>小奶团动画</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I92" s="11" t="n">
         <x:v>7</x:v>
@@ -6396,22 +6396,22 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>家庭主妇的逆袭：亲手送他入狱</x:v>
+        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
+        <x:v>闲人一坤</x:v>
       </x:c>
       <x:c r="H93" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「九鲤动漫」</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
       <x:c r="I93" s="11" t="n">
         <x:v>7</x:v>
@@ -6953,7 +6953,7 @@
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
       <x:c r="A56" s="14" t="str">
-        <x:v>发布抖音号TOP15</x:v>
+        <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
@@ -6974,7 +6974,9 @@
       <x:c r="B58" s="11" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C58" s="11" t="str"/>
+      <x:c r="C58" s="11" t="str">
+        <x:v>1.5%</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="str">
@@ -6983,7 +6985,9 @@
       <x:c r="B59" s="11" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C59" s="11" t="str"/>
+      <x:c r="C59" s="11" t="str">
+        <x:v>1.3%</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
@@ -6992,7 +6996,9 @@
       <x:c r="B60" s="11" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C60" s="11" t="str"/>
+      <x:c r="C60" s="11" t="str">
+        <x:v>1%</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
@@ -7001,7 +7007,9 @@
       <x:c r="B61" s="11" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C61" s="11" t="str"/>
+      <x:c r="C61" s="11" t="str">
+        <x:v>0.9%</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
@@ -7010,7 +7018,9 @@
       <x:c r="B62" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C62" s="11" t="str"/>
+      <x:c r="C62" s="11" t="str">
+        <x:v>0.9%</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
@@ -7019,7 +7029,9 @@
       <x:c r="B63" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C63" s="11" t="str"/>
+      <x:c r="C63" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
@@ -7028,7 +7040,9 @@
       <x:c r="B64" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C64" s="11" t="str"/>
+      <x:c r="C64" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
@@ -7037,7 +7051,9 @@
       <x:c r="B65" s="11" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C65" s="11" t="str"/>
+      <x:c r="C65" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
@@ -7046,7 +7062,9 @@
       <x:c r="B66" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C66" s="11" t="str"/>
+      <x:c r="C66" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
@@ -7055,7 +7073,9 @@
       <x:c r="B67" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C67" s="11" t="str"/>
+      <x:c r="C67" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
@@ -7064,7 +7084,9 @@
       <x:c r="B68" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C68" s="11" t="str"/>
+      <x:c r="C68" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
@@ -7073,7 +7095,9 @@
       <x:c r="B69" s="11" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C69" s="11" t="str"/>
+      <x:c r="C69" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
@@ -7082,7 +7106,9 @@
       <x:c r="B70" s="11" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C70" s="11" t="str"/>
+      <x:c r="C70" s="11" t="str">
+        <x:v>0.8%</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
@@ -7091,7 +7117,9 @@
       <x:c r="B71" s="11" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C71" s="11" t="str"/>
+      <x:c r="C71" s="11" t="str">
+        <x:v>0.7%</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="str">
@@ -7100,11 +7128,13 @@
       <x:c r="B72" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C72" s="11" t="str"/>
+      <x:c r="C72" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="22" customHeight="1">
       <x:c r="A74" s="14" t="str">
-        <x:v>付费榜主题分布</x:v>
+        <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="24" customHeight="1">
@@ -7120,89 +7150,270 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B76" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
-        <x:v>19.0%</x:v>
+        <x:v>1.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C81" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="B82" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C82" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="10" t="str">
+        <x:v>不兜</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C83" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="10" t="str">
+        <x:v>喵喵说书</x:v>
+      </x:c>
+      <x:c r="B84" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C84" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="10" t="str">
+        <x:v>星屿漫剧场</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C85" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="10" t="str">
+        <x:v>取瘾书屋</x:v>
+      </x:c>
+      <x:c r="B86" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C86" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="10" t="str">
+        <x:v>清风短剧场</x:v>
+      </x:c>
+      <x:c r="B87" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C87" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="10" t="str">
+        <x:v>亦辰动漫</x:v>
+      </x:c>
+      <x:c r="B88" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C88" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="10" t="str">
+        <x:v>暖星追剧</x:v>
+      </x:c>
+      <x:c r="B89" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C89" s="11" t="str">
+        <x:v>0.5%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="10" t="str">
+        <x:v>一张不够花</x:v>
+      </x:c>
+      <x:c r="B90" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C90" s="11" t="str">
+        <x:v>0.3%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="14" t="str">
+        <x:v>付费榜主题分布</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="24" customHeight="1">
+      <x:c r="A93" s="5" t="str">
+        <x:v>项目</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>占比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="10" t="str">
+        <x:v>婚姻/情感</x:v>
+      </x:c>
+      <x:c r="B94" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C94" s="11" t="str">
+        <x:v>19.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="10" t="str">
+        <x:v>家庭伦理/萌宝</x:v>
+      </x:c>
+      <x:c r="B95" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C95" s="11" t="str">
+        <x:v>15.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="B96" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C96" s="11" t="str">
+        <x:v>10.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="10" t="str">
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="B97" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C97" s="11" t="str">
+        <x:v>9.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="10" t="str">
+        <x:v>年代怀旧/种田</x:v>
+      </x:c>
+      <x:c r="B98" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C98" s="11" t="str">
+        <x:v>7.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="10" t="str">
+        <x:v>现实反转/人性</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C99" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B100" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C100" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B83" s="11" t="n">
+      <x:c r="B101" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C83" s="11" t="str">
+      <x:c r="C101" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -7215,6 +7426,7 @@
     <x:mergeCell ref="A49:C49"/>
     <x:mergeCell ref="A56:C56"/>
     <x:mergeCell ref="A74:C74"/>
+    <x:mergeCell ref="A92:C92"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="Rba14812b53cd4251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R0cddf7f6268c4fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rba47a54fd6424dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐" sheetId="4" r:id="Rccc5623ea6994ead"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="5" r:id="R47bc235260644752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R776378a53aed45bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R11279ae6184e43c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rda704d3dd7e34f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Rbad9c0615d0c43cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R23d57fc4ee194f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R1c90b87023e14f02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5280,7 +5281,7 @@
         <x:v>不兜</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「不兜」曾产出榜单常客</x:v>
+        <x:v>经典3D制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「不兜」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I54" s="11" t="n">
         <x:v>9</x:v>
@@ -5309,7 +5310,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I55" s="11" t="n">
         <x:v>8</x:v>
@@ -5338,7 +5339,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I56" s="11" t="n">
         <x:v>8</x:v>
@@ -5396,7 +5397,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I58" s="11" t="n">
         <x:v>8</x:v>
@@ -5425,7 +5426,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I59" s="11" t="n">
         <x:v>8</x:v>
@@ -5454,7 +5455,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I60" s="11" t="n">
         <x:v>8</x:v>
@@ -5860,7 +5861,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H74" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I74" s="11" t="n">
         <x:v>9</x:v>
@@ -5889,7 +5890,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H75" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I75" s="11" t="n">
         <x:v>8</x:v>
@@ -5918,7 +5919,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H76" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I76" s="11" t="n">
         <x:v>8</x:v>
@@ -5947,7 +5948,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H77" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I77" s="11" t="n">
         <x:v>8</x:v>
@@ -5976,7 +5977,7 @@
         <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；发布账号「西瑶短剧」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I78" s="11" t="n">
         <x:v>8</x:v>
@@ -6005,7 +6006,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H79" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I79" s="11" t="n">
         <x:v>8</x:v>
@@ -6034,7 +6035,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I80" s="11" t="n">
         <x:v>8</x:v>
@@ -6092,7 +6093,7 @@
         <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
       </x:c>
       <x:c r="I82" s="11" t="n">
         <x:v>8</x:v>
@@ -6423,6 +6424,2723 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="70" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>预计上线</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>剧名</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>集数</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>制作风格</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>主题分类</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>发布账号</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>推荐依据</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>综合评分</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>假面恋人：三十八万撕开两年恋爱骗局</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
+        <x:v>婚姻情感 / 美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>婚内骗局，我彻底粉碎前夫阴谋</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；84集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>闺蜜的谎言</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>一场蜜月，撕毁了我的婚姻</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C6" s="10" t="str">
+        <x:v>一庭兰香旧人归</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="G6" s="10" t="str">
+        <x:v>西瑶短剧</x:v>
+      </x:c>
+      <x:c r="H6" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>姐姐不是提款机</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="str">
+        <x:v>婚礼当天，我拆穿了小姑子的假陪嫁房</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G8" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H8" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="str">
+        <x:v>归来吧，妈妈</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="str">
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H9" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>情深不知晚</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H10" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="str">
+        <x:v>我养了三年的保姆，想夺走我的一切</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H11" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="str">
+        <x:v>我用一场退婚，换回了整个人生</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G12" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；68集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="str">
+        <x:v>我的座位，恕不奉陪</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="str">
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="G13" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H13" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="str">
+        <x:v>逆袭之通天财眼第7季</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G14" s="10" t="str">
+        <x:v>丽娟影视</x:v>
+      </x:c>
+      <x:c r="H14" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；100集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="str">
+        <x:v>重生为蛇，投喂女帝反哺成龙第二季</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G15" s="10" t="str">
+        <x:v>鲸喜漫剧🐳</x:v>
+      </x:c>
+      <x:c r="H15" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="str">
+        <x:v>重生猎户：杜鹃赶山屯满粮第二季</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F16" s="10" t="str">
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="str">
+        <x:v>朝霞看剧</x:v>
+      </x:c>
+      <x:c r="H16" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；118集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="str">
+        <x:v>食香记：从一坛腌萝卜开始逆袭第一季完整版</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F17" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="str">
+        <x:v>上官格格</x:v>
+      </x:c>
+      <x:c r="H17" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；161集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C18" s="10" t="str">
+        <x:v>不死帝师上界篇第一季</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G18" s="10" t="str">
+        <x:v>龙小五剧场</x:v>
+      </x:c>
+      <x:c r="H18" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；74集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C19" s="10" t="str">
+        <x:v>五千块起家！卡车司机的逆袭人生</x:v>
+      </x:c>
+      <x:c r="D19" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F19" s="10" t="str">
+        <x:v>都市职场 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="str">
+        <x:v>骏乐夜航船AIGC剧场</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「骏乐夜航船AIGC剧场」</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="str">
+        <x:v>从前说：七零佳媳渡风尘第一季</x:v>
+      </x:c>
+      <x:c r="D20" s="11" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F20" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="G20" s="10" t="str">
+        <x:v>排尚漫屋</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C21" s="10" t="str">
+        <x:v>从捡个仙子做老婆开始，凡血踏九天第二季</x:v>
+      </x:c>
+      <x:c r="D21" s="11" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F21" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G21" s="10" t="str">
+        <x:v>云腾剧场</x:v>
+      </x:c>
+      <x:c r="H21" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；95集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C22" s="10" t="str">
+        <x:v>仙姝重回：我和魔尊带着宗门上大分第三季</x:v>
+      </x:c>
+      <x:c r="D22" s="11" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F22" s="10" t="str">
+        <x:v>年代怀旧 / 古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G22" s="10" t="str">
+        <x:v>西子是个演员</x:v>
+      </x:c>
+      <x:c r="H22" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧 / 古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="11" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C23" s="10" t="str">
+        <x:v>公路求生卡进了古代，柳姨娘癫狂极了第三季</x:v>
+      </x:c>
+      <x:c r="D23" s="11" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F23" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G23" s="10" t="str">
+        <x:v>澜溪剧场</x:v>
+      </x:c>
+      <x:c r="H23" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="11" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>凤栖为臣，女扮男装搞基建第一季</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F24" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G24" s="10" t="str">
+        <x:v>文心动漫</x:v>
+      </x:c>
+      <x:c r="H24" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I24" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="11" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C25" s="10" t="str">
+        <x:v>刘一祖的故事之逆袭</x:v>
+      </x:c>
+      <x:c r="D25" s="11" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F25" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G25" s="10" t="str">
+        <x:v>彩云动画</x:v>
+      </x:c>
+      <x:c r="H25" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「彩云动画」</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C26" s="10" t="str">
+        <x:v>刚毕业，离婚逆袭系统就来了</x:v>
+      </x:c>
+      <x:c r="D26" s="11" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F26" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G26" s="10" t="str">
+        <x:v>灯下漫剧</x:v>
+      </x:c>
+      <x:c r="H26" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 战神异能）；发布账号「灯下漫剧」</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="11" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C27" s="10" t="str">
+        <x:v>合伙人老婆夺我权我反手收购公司</x:v>
+      </x:c>
+      <x:c r="D27" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F27" s="10" t="str">
+        <x:v>都市职场 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G27" s="10" t="str">
+        <x:v>优文疯漫</x:v>
+      </x:c>
+      <x:c r="H27" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「优文疯漫」</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="11" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="str">
+        <x:v>商先生，婚后请热恋第三季</x:v>
+      </x:c>
+      <x:c r="D28" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F28" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G28" s="10" t="str">
+        <x:v>智帧剧场</x:v>
+      </x:c>
+      <x:c r="H28" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I28" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="11" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C29" s="10" t="str">
+        <x:v>姑妈供我成状元，我用一生报她恩第一季</x:v>
+      </x:c>
+      <x:c r="D29" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F29" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G29" s="10" t="str">
+        <x:v>灵漫好剧</x:v>
+      </x:c>
+      <x:c r="H29" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I29" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="11" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C30" s="10" t="str">
+        <x:v>宠物急诊：自带病症词条天眼第一季</x:v>
+      </x:c>
+      <x:c r="D30" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F30" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G30" s="10" t="str">
+        <x:v>灵漫剧场</x:v>
+      </x:c>
+      <x:c r="H30" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I30" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="11" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>导航里的秘密！</x:v>
+      </x:c>
+      <x:c r="D31" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F31" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G31" s="10" t="str">
+        <x:v>梦启剧场</x:v>
+      </x:c>
+      <x:c r="H31" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「梦启剧场」</x:v>
+      </x:c>
+      <x:c r="I31" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="11" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>彩运照人心第三季</x:v>
+      </x:c>
+      <x:c r="D32" s="11" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F32" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G32" s="10" t="str">
+        <x:v>云间漫剧-丸子</x:v>
+      </x:c>
+      <x:c r="H32" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；121集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I32" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="11" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C33" s="10" t="str">
+        <x:v>穿成团宠后我靠读心逆袭</x:v>
+      </x:c>
+      <x:c r="D33" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F33" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G33" s="10" t="str">
+        <x:v>星梦好剧</x:v>
+      </x:c>
+      <x:c r="H33" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
+      </x:c>
+      <x:c r="I33" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="11" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C34" s="10" t="str">
+        <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
+      </x:c>
+      <x:c r="D34" s="11" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F34" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G34" s="10" t="str">
+        <x:v>陈柯</x:v>
+      </x:c>
+      <x:c r="H34" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I34" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="11" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="str">
+        <x:v>藏在婚姻里的谎言</x:v>
+      </x:c>
+      <x:c r="D35" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F35" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G35" s="10" t="str">
+        <x:v>九鲤动漫</x:v>
+      </x:c>
+      <x:c r="H35" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
+      </x:c>
+      <x:c r="I35" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="11" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="str">
+        <x:v>08·29</x:v>
+      </x:c>
+      <x:c r="C36" s="10" t="str">
+        <x:v>让你守边塞，你用汉堡养兵？第二季江南篇</x:v>
+      </x:c>
+      <x:c r="D36" s="11" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F36" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G36" s="10" t="str">
+        <x:v>浮绘剧场</x:v>
+      </x:c>
+      <x:c r="H36" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I36" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C37" s="10" t="str">
+        <x:v>撞破婚约骗局</x:v>
+      </x:c>
+      <x:c r="D37" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F37" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G37" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H37" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
+      </x:c>
+      <x:c r="I37" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C38" s="10" t="str">
+        <x:v>下山归来，影后向我求婚第二季</x:v>
+      </x:c>
+      <x:c r="D38" s="11" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F38" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G38" s="10" t="str">
+        <x:v>漫文</x:v>
+      </x:c>
+      <x:c r="H38" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；79集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I38" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C39" s="10" t="str">
+        <x:v>免费荠菜见人心</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F39" s="10" t="str">
+        <x:v>美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G39" s="10" t="str">
+        <x:v>闪闪动漫社</x:v>
+      </x:c>
+      <x:c r="H39" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「闪闪动漫社」</x:v>
+      </x:c>
+      <x:c r="I39" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C40" s="10" t="str">
+        <x:v>毁我清白，我反手指认皇帝</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E40" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F40" s="10" t="str">
+        <x:v>古装宫廷 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G40" s="10" t="str">
+        <x:v>卿读剧场</x:v>
+      </x:c>
+      <x:c r="H40" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「卿读剧场」</x:v>
+      </x:c>
+      <x:c r="I40" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B41" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C41" s="10" t="str">
+        <x:v>丁克二十载，我摊牌了</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F41" s="10" t="str">
+        <x:v>都市职场 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G41" s="10" t="str">
+        <x:v>次元佳思剧场</x:v>
+      </x:c>
+      <x:c r="H41" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「次元佳思剧场」</x:v>
+      </x:c>
+      <x:c r="I41" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B42" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C42" s="10" t="str">
+        <x:v>万界杂货铺：我靠倒卖物资赢麻了</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F42" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G42" s="10" t="str">
+        <x:v>青禾短剧</x:v>
+      </x:c>
+      <x:c r="H42" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；发布账号「青禾短剧」</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B43" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C43" s="10" t="str">
+        <x:v>双生麒麟，神君爹爹傲娇娘</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F43" s="10" t="str">
+        <x:v>家庭伦理 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G43" s="10" t="str">
+        <x:v>新美漫剧场</x:v>
+      </x:c>
+      <x:c r="H43" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能）；发布账号「新美漫剧场」</x:v>
+      </x:c>
+      <x:c r="I43" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B44" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C44" s="10" t="str">
+        <x:v>捐躯失踪十八年，归来女儿去世了</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F44" s="10" t="str">
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G44" s="10" t="str">
+        <x:v>凛冬短剧</x:v>
+      </x:c>
+      <x:c r="H44" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「凛冬短剧」</x:v>
+      </x:c>
+      <x:c r="I44" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B45" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="str">
+        <x:v>觉醒神级听劝系统，我成专听建议的校长</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F45" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G45" s="10" t="str">
+        <x:v>红豆剧场</x:v>
+      </x:c>
+      <x:c r="H45" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；80集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「红豆剧场」</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B46" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C46" s="10" t="str">
+        <x:v>退婚后我成了女帝</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F46" s="10" t="str">
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G46" s="10" t="str">
+        <x:v>次元心动剧场</x:v>
+      </x:c>
+      <x:c r="H46" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；55集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；发布账号「次元心动剧场」</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C47" s="10" t="str">
+        <x:v>1980：我重生后护她余生</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F47" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G47" s="10" t="str">
+        <x:v>阳光微剧</x:v>
+      </x:c>
+      <x:c r="H47" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材待验证；发布账号「阳光微剧」</x:v>
+      </x:c>
+      <x:c r="I47" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B48" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C48" s="10" t="str">
+        <x:v>一担米嫁哑郎，他开口那天我哭了</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F48" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G48" s="10" t="str">
+        <x:v>漫恋小剧场</x:v>
+      </x:c>
+      <x:c r="H48" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；45集，中等长度；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「漫恋小剧场」</x:v>
+      </x:c>
+      <x:c r="I48" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B49" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C49" s="10" t="str">
+        <x:v>乖囡寻爹记</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F49" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G49" s="10" t="str">
+        <x:v>漫语剧场</x:v>
+      </x:c>
+      <x:c r="H49" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；46集，中等长度；题材契合爆款主线（家庭伦理）；发布账号「漫语剧场」</x:v>
+      </x:c>
+      <x:c r="I49" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B50" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C50" s="10" t="str">
+        <x:v>山谷灵珠录第三季</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F50" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G50" s="10" t="str">
+        <x:v>漫文传媒</x:v>
+      </x:c>
+      <x:c r="H50" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；69集长剧集，符合起量主力区间；题材待验证；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I50" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B51" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C51" s="10" t="str">
+        <x:v>大促当天，我预言了一场爆炸</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F51" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G51" s="10" t="str">
+        <x:v>月光短剧</x:v>
+      </x:c>
+      <x:c r="H51" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材待验证；发布账号「月光短剧」</x:v>
+      </x:c>
+      <x:c r="I51" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B52" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C52" s="10" t="str">
+        <x:v>盐弈</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F52" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G52" s="10" t="str">
+        <x:v>凛冬短剧</x:v>
+      </x:c>
+      <x:c r="H52" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材待验证；发布账号「凛冬短剧」</x:v>
+      </x:c>
+      <x:c r="I52" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B53" s="11" t="str">
+        <x:v>08·30</x:v>
+      </x:c>
+      <x:c r="C53" s="10" t="str">
+        <x:v>九世相寻</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="F53" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G53" s="10" t="str">
+        <x:v>恐龙粑粑小百科</x:v>
+      </x:c>
+      <x:c r="H53" s="10" t="str">
+        <x:v>83集长剧集，符合起量主力区间；题材待验证；发布账号「恐龙粑粑小百科」</x:v>
+      </x:c>
+      <x:c r="I53" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B54" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C54" s="10" t="str">
+        <x:v>重生归来，我把爸爸捧上神坛</x:v>
+      </x:c>
+      <x:c r="D54" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E54" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F54" s="10" t="str">
+        <x:v>家庭伦理 / 逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str">
+        <x:v>闪闪动漫社</x:v>
+      </x:c>
+      <x:c r="H54" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸 / 战神异能）；发布账号「闪闪动漫社」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I54" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B55" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="str">
+        <x:v>1977山猎重生，我以余生偿前错第三季</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F55" s="10" t="str">
+        <x:v>年代怀旧 / 种田囤货</x:v>
+      </x:c>
+      <x:c r="G55" s="10" t="str">
+        <x:v>茉冉漫影</x:v>
+      </x:c>
+      <x:c r="H55" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；307集，集数偏短/超长需关注；题材契合爆款主线（年代怀旧 / 种田囤货）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I55" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B56" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C56" s="10" t="str">
+        <x:v>丈夫坑娃，我绝不认输</x:v>
+      </x:c>
+      <x:c r="D56" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E56" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F56" s="10" t="str">
+        <x:v>萌宝治愈 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G56" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H56" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I56" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B57" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C57" s="10" t="str">
+        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
+      </x:c>
+      <x:c r="D57" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E57" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F57" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G57" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H57" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I57" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B58" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C58" s="10" t="str">
+        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
+      </x:c>
+      <x:c r="D58" s="11" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E58" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F58" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str">
+        <x:v>初八漫剧</x:v>
+      </x:c>
+      <x:c r="H58" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I58" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B59" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C59" s="10" t="str">
+        <x:v>同频心动</x:v>
+      </x:c>
+      <x:c r="D59" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E59" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F59" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G59" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H59" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I59" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B60" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C60" s="10" t="str">
+        <x:v>婚礼前夜，我换了新郎</x:v>
+      </x:c>
+      <x:c r="D60" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E60" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F60" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G60" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H60" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I60" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B61" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C61" s="10" t="str">
+        <x:v>玻璃钻戒终结七年错爱</x:v>
+      </x:c>
+      <x:c r="D61" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E61" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F61" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G61" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H61" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I61" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B62" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C62" s="10" t="str">
+        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
+      </x:c>
+      <x:c r="D62" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E62" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F62" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G62" s="10" t="str">
+        <x:v>保温虾虾</x:v>
+      </x:c>
+      <x:c r="H62" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
+      </x:c>
+      <x:c r="I62" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B63" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C63" s="10" t="str">
+        <x:v>下午的早餐店第五季</x:v>
+      </x:c>
+      <x:c r="D63" s="11" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E63" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F63" s="10" t="str">
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="G63" s="10" t="str">
+        <x:v>盐系少女社</x:v>
+      </x:c>
+      <x:c r="H63" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I63" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B64" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C64" s="10" t="str">
+        <x:v>不朽仙秦！第三季</x:v>
+      </x:c>
+      <x:c r="D64" s="11" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="E64" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F64" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G64" s="10" t="str">
+        <x:v>虾仁白白</x:v>
+      </x:c>
+      <x:c r="H64" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I64" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B65" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C65" s="10" t="str">
+        <x:v>五十保姆觉醒，遗产见人心</x:v>
+      </x:c>
+      <x:c r="D65" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E65" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F65" s="10" t="str">
+        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G65" s="10" t="str">
+        <x:v>剑心动漫</x:v>
+      </x:c>
+      <x:c r="H65" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
+      </x:c>
+      <x:c r="I65" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B66" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C66" s="10" t="str">
+        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
+      </x:c>
+      <x:c r="D66" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E66" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F66" s="10" t="str">
+        <x:v>美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G66" s="10" t="str">
+        <x:v>晟樊影视</x:v>
+      </x:c>
+      <x:c r="H66" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
+      </x:c>
+      <x:c r="I66" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B67" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C67" s="10" t="str">
+        <x:v>全民御兽：神级鉴兽师第二季</x:v>
+      </x:c>
+      <x:c r="D67" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E67" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F67" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G67" s="10" t="str">
+        <x:v>漫川动漫剧场</x:v>
+      </x:c>
+      <x:c r="H67" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I67" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B68" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C68" s="10" t="str">
+        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
+      </x:c>
+      <x:c r="D68" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E68" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F68" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G68" s="10" t="str">
+        <x:v>竹蜻蜓剧场</x:v>
+      </x:c>
+      <x:c r="H68" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I68" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B69" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C69" s="10" t="str">
+        <x:v>农场萌宠！第六季</x:v>
+      </x:c>
+      <x:c r="D69" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E69" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F69" s="10" t="str">
+        <x:v>种田囤货 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G69" s="10" t="str">
+        <x:v>惜惜动漫</x:v>
+      </x:c>
+      <x:c r="H69" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I69" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B70" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C70" s="10" t="str">
+        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
+      </x:c>
+      <x:c r="D70" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E70" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F70" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G70" s="10" t="str">
+        <x:v>枕月漫影</x:v>
+      </x:c>
+      <x:c r="H70" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I70" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B71" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C71" s="10" t="str">
+        <x:v>利益照见人心</x:v>
+      </x:c>
+      <x:c r="D71" s="11" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E71" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F71" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G71" s="10" t="str">
+        <x:v>天天爱看剧</x:v>
+      </x:c>
+      <x:c r="H71" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
+      </x:c>
+      <x:c r="I71" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B72" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C72" s="10" t="str">
+        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
+      </x:c>
+      <x:c r="D72" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E72" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F72" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G72" s="10" t="str">
+        <x:v>月亮与孤岛</x:v>
+      </x:c>
+      <x:c r="H72" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I72" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B73" s="11" t="str">
+        <x:v>09·02</x:v>
+      </x:c>
+      <x:c r="C73" s="10" t="str">
+        <x:v>剑定山河第一季</x:v>
+      </x:c>
+      <x:c r="D73" s="11" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E73" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F73" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G73" s="10" t="str">
+        <x:v>捷捷动漫馆</x:v>
+      </x:c>
+      <x:c r="H73" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I73" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B74" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="str">
+        <x:v>一张照片传遍公司群我却因此重生了</x:v>
+      </x:c>
+      <x:c r="D74" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E74" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F74" s="10" t="str">
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="G74" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H74" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I74" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B75" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C75" s="10" t="str">
+        <x:v>一纸通知书，丈夫托我赴前程</x:v>
+      </x:c>
+      <x:c r="D75" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E75" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F75" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G75" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H75" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I75" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B76" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C76" s="10" t="str">
+        <x:v>一顿饭算清</x:v>
+      </x:c>
+      <x:c r="D76" s="11" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E76" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F76" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="G76" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H76" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I76" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B77" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C77" s="10" t="str">
+        <x:v>一顿香锅断前缘</x:v>
+      </x:c>
+      <x:c r="D77" s="11" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E77" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F77" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G77" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H77" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I77" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B78" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C78" s="10" t="str">
+        <x:v>嫁妆被抢那天我亮明了身份</x:v>
+      </x:c>
+      <x:c r="D78" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E78" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F78" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G78" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H78" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I78" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B79" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C79" s="10" t="str">
+        <x:v>带男友回大山继承家产</x:v>
+      </x:c>
+      <x:c r="D79" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E79" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F79" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H79" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I79" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B80" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C80" s="10" t="str">
+        <x:v>末世，带着修改器重生，我无敌了2</x:v>
+      </x:c>
+      <x:c r="D80" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E80" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F80" s="10" t="str">
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G80" s="10" t="str">
+        <x:v>机甲熊</x:v>
+      </x:c>
+      <x:c r="H80" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I80" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B81" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C81" s="10" t="str">
+        <x:v>错写红封，终断婚约</x:v>
+      </x:c>
+      <x:c r="D81" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E81" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F81" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G81" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H81" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="I81" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B82" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C82" s="10" t="str">
+        <x:v>一井见人心</x:v>
+      </x:c>
+      <x:c r="D82" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E82" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F82" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G82" s="10" t="str">
+        <x:v>云间予安</x:v>
+      </x:c>
+      <x:c r="H82" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
+      </x:c>
+      <x:c r="I82" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B83" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C83" s="10" t="str">
+        <x:v>一渠清水见人心</x:v>
+      </x:c>
+      <x:c r="D83" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E83" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F83" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G83" s="10" t="str">
+        <x:v>心痕剧场</x:v>
+      </x:c>
+      <x:c r="H83" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
+      </x:c>
+      <x:c r="I83" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B84" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C84" s="10" t="str">
+        <x:v>七天照见人心</x:v>
+      </x:c>
+      <x:c r="D84" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E84" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F84" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G84" s="10" t="str">
+        <x:v>倩倩短剧</x:v>
+      </x:c>
+      <x:c r="H84" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
+      </x:c>
+      <x:c r="I84" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B85" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C85" s="10" t="str">
+        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
+      </x:c>
+      <x:c r="D85" s="11" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E85" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F85" s="10" t="str">
+        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="G85" s="10" t="str">
+        <x:v>溪溪剧场</x:v>
+      </x:c>
+      <x:c r="H85" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I85" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B86" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C86" s="10" t="str">
+        <x:v>假面羁绊：极客先生的秘密</x:v>
+      </x:c>
+      <x:c r="D86" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E86" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F86" s="10" t="str">
+        <x:v>美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G86" s="10" t="str">
+        <x:v>北极熊短剧</x:v>
+      </x:c>
+      <x:c r="H86" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
+      </x:c>
+      <x:c r="I86" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B87" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C87" s="10" t="str">
+        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
+      </x:c>
+      <x:c r="D87" s="11" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E87" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F87" s="10" t="str">
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G87" s="10" t="str">
+        <x:v>浪客剧场</x:v>
+      </x:c>
+      <x:c r="H87" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
+      </x:c>
+      <x:c r="I87" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B88" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C88" s="10" t="str">
+        <x:v>农村兽神第五季</x:v>
+      </x:c>
+      <x:c r="D88" s="11" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E88" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F88" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G88" s="10" t="str">
+        <x:v>每日欢乐漫剧</x:v>
+      </x:c>
+      <x:c r="H88" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I88" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B89" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C89" s="10" t="str">
+        <x:v>匠心逆袭：我为行业立规矩</x:v>
+      </x:c>
+      <x:c r="D89" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E89" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F89" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G89" s="10" t="str">
+        <x:v>五碗说漫</x:v>
+      </x:c>
+      <x:c r="H89" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
+      </x:c>
+      <x:c r="I89" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B90" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C90" s="10" t="str">
+        <x:v>囤货逆袭大佬末世之归途</x:v>
+      </x:c>
+      <x:c r="D90" s="11" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E90" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F90" s="10" t="str">
+        <x:v>种田囤货 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G90" s="10" t="str">
+        <x:v>逐梦剧场</x:v>
+      </x:c>
+      <x:c r="H90" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
+      </x:c>
+      <x:c r="I90" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B91" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C91" s="10" t="str">
+        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
+      </x:c>
+      <x:c r="D91" s="11" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E91" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="F91" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G91" s="10" t="str">
+        <x:v>小奶团动画</x:v>
+      </x:c>
+      <x:c r="H91" s="10" t="str">
+        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I91" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B92" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C92" s="10" t="str">
+        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
+      </x:c>
+      <x:c r="D92" s="11" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E92" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F92" s="10" t="str">
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G92" s="10" t="str">
+        <x:v>闲人一坤</x:v>
+      </x:c>
+      <x:c r="H92" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
+      </x:c>
+      <x:c r="I92" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B93" s="11" t="str">
+        <x:v>09·03</x:v>
+      </x:c>
+      <x:c r="C93" s="10" t="str">
+        <x:v>家庭主妇的逆袭：亲手送他入狱</x:v>
+      </x:c>
+      <x:c r="D93" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="F93" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G93" s="10" t="str">
+        <x:v>九鲤动漫</x:v>
+      </x:c>
+      <x:c r="H93" s="10" t="str">
+        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「九鲤动漫」</x:v>
+      </x:c>
+      <x:c r="I93" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R776378a53aed45bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R11279ae6184e43c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rda704d3dd7e34f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Rbad9c0615d0c43cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R23d57fc4ee194f2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R1c90b87023e14f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R5c81280e1e464689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R185a7586c3ec4143"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R2ab6c17dc3ab41eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R9247f74579db41a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R8b3a454492c24903"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="Rc55ad0f341b04510"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1060,6 +1060,7 @@
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="50" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -1093,6 +1094,9 @@
       <x:c r="J1" t="str">
         <x:v>发布账号</x:v>
       </x:c>
+      <x:c r="K1" t="str">
+        <x:v>简介</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -1123,6 +1127,7 @@
       <x:c r="J2" s="10" t="str">
         <x:v>暖夏短剧</x:v>
       </x:c>
+      <x:c r="K2" s="10" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -1153,6 +1158,7 @@
       <x:c r="J3" s="10" t="str">
         <x:v>马克动漫</x:v>
       </x:c>
+      <x:c r="K3" s="10" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -1183,6 +1189,7 @@
       <x:c r="J4" s="10" t="str">
         <x:v>云影漫剧</x:v>
       </x:c>
+      <x:c r="K4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -1213,6 +1220,7 @@
       <x:c r="J5" s="10" t="str">
         <x:v>小桃红动画</x:v>
       </x:c>
+      <x:c r="K5" s="10" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -1243,6 +1251,7 @@
       <x:c r="J6" s="10" t="str">
         <x:v>漫漫画丫头</x:v>
       </x:c>
+      <x:c r="K6" s="10" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -1273,6 +1282,7 @@
       <x:c r="J7" s="10" t="str">
         <x:v>小尘剧场</x:v>
       </x:c>
+      <x:c r="K7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -1303,6 +1313,7 @@
       <x:c r="J8" s="10" t="str">
         <x:v>阿云剧场</x:v>
       </x:c>
+      <x:c r="K8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -1333,6 +1344,7 @@
       <x:c r="J9" s="10" t="str">
         <x:v>栗子说漫</x:v>
       </x:c>
+      <x:c r="K9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -1363,6 +1375,7 @@
       <x:c r="J10" s="10" t="str">
         <x:v>二里清风</x:v>
       </x:c>
+      <x:c r="K10" s="10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -1393,6 +1406,7 @@
       <x:c r="J11" s="10" t="str">
         <x:v>清欢古风剧场</x:v>
       </x:c>
+      <x:c r="K11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -1423,6 +1437,7 @@
       <x:c r="J12" s="10" t="str">
         <x:v>95漫画</x:v>
       </x:c>
+      <x:c r="K12" s="10" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -1453,6 +1468,7 @@
       <x:c r="J13" s="10" t="str">
         <x:v>云间漫剧-零七</x:v>
       </x:c>
+      <x:c r="K13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -1483,6 +1499,7 @@
       <x:c r="J14" s="10" t="str">
         <x:v>表妹剧场</x:v>
       </x:c>
+      <x:c r="K14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -1513,6 +1530,7 @@
       <x:c r="J15" s="10" t="str">
         <x:v>馆长玉先生剧场</x:v>
       </x:c>
+      <x:c r="K15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -1543,6 +1561,7 @@
       <x:c r="J16" s="10" t="str">
         <x:v>阅友动漫</x:v>
       </x:c>
+      <x:c r="K16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -1573,6 +1592,7 @@
       <x:c r="J17" s="10" t="str">
         <x:v>渲渲动画</x:v>
       </x:c>
+      <x:c r="K17" s="10" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
@@ -1603,6 +1623,7 @@
       <x:c r="J18" s="10" t="str">
         <x:v>菁禾</x:v>
       </x:c>
+      <x:c r="K18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -1633,6 +1654,7 @@
       <x:c r="J19" s="10" t="str">
         <x:v>AI梦</x:v>
       </x:c>
+      <x:c r="K19" s="10" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -1663,6 +1685,7 @@
       <x:c r="J20" s="10" t="str">
         <x:v>AI 风华</x:v>
       </x:c>
+      <x:c r="K20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -1693,6 +1716,7 @@
       <x:c r="J21" s="10" t="str">
         <x:v>知夏短剧</x:v>
       </x:c>
+      <x:c r="K21" s="10" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -1723,6 +1747,7 @@
       <x:c r="J22" s="10" t="str">
         <x:v>武汉卡看漫剧场</x:v>
       </x:c>
+      <x:c r="K22" s="10" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -1753,6 +1778,7 @@
       <x:c r="J23" s="10" t="str">
         <x:v>朝夕影堂</x:v>
       </x:c>
+      <x:c r="K23" s="10" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
@@ -1783,6 +1809,7 @@
       <x:c r="J24" s="10" t="str">
         <x:v>诺威剧场</x:v>
       </x:c>
+      <x:c r="K24" s="10" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
@@ -1795,18 +1822,25 @@
       <x:c r="D25" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="E25" s="11" t="str"/>
+      <x:c r="E25" s="11" t="str">
+        <x:v>08-31 09:58</x:v>
+      </x:c>
       <x:c r="F25" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G25" s="11" t="str"/>
+      <x:c r="G25" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="H25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>年代怀旧</x:v>
       </x:c>
-      <x:c r="J25" s="10" t="str"/>
+      <x:c r="J25" s="10" t="str">
+        <x:v>蜜糖次元社</x:v>
+      </x:c>
+      <x:c r="K25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -1837,6 +1871,7 @@
       <x:c r="J26" s="10" t="str">
         <x:v>空白漫</x:v>
       </x:c>
+      <x:c r="K26" s="10" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
@@ -1867,6 +1902,7 @@
       <x:c r="J27" s="10" t="str">
         <x:v>河虾动漫</x:v>
       </x:c>
+      <x:c r="K27" s="10" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
@@ -1897,6 +1933,7 @@
       <x:c r="J28" s="10" t="str">
         <x:v>每日沙雕速递</x:v>
       </x:c>
+      <x:c r="K28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
@@ -1927,6 +1964,7 @@
       <x:c r="J29" s="10" t="str">
         <x:v>口水显眼包</x:v>
       </x:c>
+      <x:c r="K29" s="10" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="str">
@@ -1957,6 +1995,7 @@
       <x:c r="J30" s="10" t="str">
         <x:v>锋芒映剧</x:v>
       </x:c>
+      <x:c r="K30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
@@ -1987,6 +2026,7 @@
       <x:c r="J31" s="10" t="str">
         <x:v>森森动画</x:v>
       </x:c>
+      <x:c r="K31" s="10" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
@@ -2017,6 +2057,7 @@
       <x:c r="J32" s="10" t="str">
         <x:v>诗婳-君懿看剧</x:v>
       </x:c>
+      <x:c r="K32" s="10" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="11" t="str">
@@ -2047,6 +2088,7 @@
       <x:c r="J33" s="10" t="str">
         <x:v>林帧漫剧</x:v>
       </x:c>
+      <x:c r="K33" s="10" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="11" t="str">
@@ -2077,6 +2119,7 @@
       <x:c r="J34" s="10" t="str">
         <x:v>追更漫剧</x:v>
       </x:c>
+      <x:c r="K34" s="10" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="11" t="str">
@@ -2107,6 +2150,7 @@
       <x:c r="J35" s="10" t="str">
         <x:v>绿豆儿</x:v>
       </x:c>
+      <x:c r="K35" s="10" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
@@ -2137,6 +2181,7 @@
       <x:c r="J36" s="10" t="str">
         <x:v>东瓜剧场</x:v>
       </x:c>
+      <x:c r="K36" s="10" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="11" t="str">
@@ -2167,6 +2212,7 @@
       <x:c r="J37" s="10" t="str">
         <x:v>星漫世界</x:v>
       </x:c>
+      <x:c r="K37" s="10" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="11" t="str">
@@ -2197,6 +2243,7 @@
       <x:c r="J38" s="10" t="str">
         <x:v>紫怡漫剧场</x:v>
       </x:c>
+      <x:c r="K38" s="10" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="11" t="str">
@@ -2227,6 +2274,7 @@
       <x:c r="J39" s="10" t="str">
         <x:v>豆豆动漫</x:v>
       </x:c>
+      <x:c r="K39" s="10" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="11" t="str">
@@ -2257,6 +2305,7 @@
       <x:c r="J40" s="10" t="str">
         <x:v>小清书漫</x:v>
       </x:c>
+      <x:c r="K40" s="10" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="11" t="str">
@@ -2287,6 +2336,7 @@
       <x:c r="J41" s="10" t="str">
         <x:v>小菲菲动画</x:v>
       </x:c>
+      <x:c r="K41" s="10" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="11" t="str">
@@ -2317,6 +2367,7 @@
       <x:c r="J42" s="10" t="str">
         <x:v>艾微动画剧场</x:v>
       </x:c>
+      <x:c r="K42" s="10" t="str"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="11" t="str">
@@ -2347,6 +2398,7 @@
       <x:c r="J43" s="10" t="str">
         <x:v>榴莲漫剧</x:v>
       </x:c>
+      <x:c r="K43" s="10" t="str"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="11" t="str">
@@ -2377,6 +2429,7 @@
       <x:c r="J44" s="10" t="str">
         <x:v>三针剧场</x:v>
       </x:c>
+      <x:c r="K44" s="10" t="str"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="11" t="str">
@@ -2407,6 +2460,7 @@
       <x:c r="J45" s="10" t="str">
         <x:v>喵琪琪追剧</x:v>
       </x:c>
+      <x:c r="K45" s="10" t="str"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="11" t="str">
@@ -2437,6 +2491,7 @@
       <x:c r="J46" s="10" t="str">
         <x:v>小丘剧场</x:v>
       </x:c>
+      <x:c r="K46" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3717,8 +3772,9 @@
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="70" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="50" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="70" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -3744,9 +3800,12 @@
         <x:v>发布账号</x:v>
       </x:c>
       <x:c r="H1" t="str">
+        <x:v>简介</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
         <x:v>推荐依据</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="J1" t="str">
         <x:v>综合评分</x:v>
       </x:c>
     </x:row>
@@ -3772,10 +3831,11 @@
       <x:c r="G2" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="H2" s="10" t="str"/>
+      <x:c r="I2" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I2" s="11" t="n">
+      <x:c r="J2" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3801,10 +3861,11 @@
       <x:c r="G3" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H3" s="10" t="str">
+      <x:c r="H3" s="10" t="str"/>
+      <x:c r="I3" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；84集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="n">
+      <x:c r="J3" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3830,10 +3891,11 @@
       <x:c r="G4" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H4" s="10" t="str">
+      <x:c r="H4" s="10" t="str"/>
+      <x:c r="I4" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="n">
+      <x:c r="J4" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -3859,10 +3921,11 @@
       <x:c r="G5" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="str">
+      <x:c r="H5" s="10" t="str"/>
+      <x:c r="I5" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="n">
+      <x:c r="J5" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3888,10 +3951,11 @@
       <x:c r="G6" s="10" t="str">
         <x:v>西瑶短剧</x:v>
       </x:c>
-      <x:c r="H6" s="10" t="str">
+      <x:c r="H6" s="10" t="str"/>
+      <x:c r="I6" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="n">
+      <x:c r="J6" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3917,10 +3981,11 @@
       <x:c r="G7" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="str">
+      <x:c r="H7" s="10" t="str"/>
+      <x:c r="I7" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="n">
+      <x:c r="J7" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3946,10 +4011,11 @@
       <x:c r="G8" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H8" s="10" t="str">
+      <x:c r="H8" s="10" t="str"/>
+      <x:c r="I8" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I8" s="11" t="n">
+      <x:c r="J8" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -3975,10 +4041,11 @@
       <x:c r="G9" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H9" s="10" t="str">
+      <x:c r="H9" s="10" t="str"/>
+      <x:c r="I9" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4004,10 +4071,11 @@
       <x:c r="G10" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H10" s="10" t="str">
+      <x:c r="H10" s="10" t="str"/>
+      <x:c r="I10" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="n">
+      <x:c r="J10" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4033,10 +4101,11 @@
       <x:c r="G11" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H11" s="10" t="str">
+      <x:c r="H11" s="10" t="str"/>
+      <x:c r="I11" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I11" s="11" t="n">
+      <x:c r="J11" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4062,10 +4131,11 @@
       <x:c r="G12" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H12" s="10" t="str">
+      <x:c r="H12" s="10" t="str"/>
+      <x:c r="I12" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；68集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I12" s="11" t="n">
+      <x:c r="J12" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4091,10 +4161,11 @@
       <x:c r="G13" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H13" s="10" t="str">
+      <x:c r="H13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="n">
+      <x:c r="J13" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4120,10 +4191,11 @@
       <x:c r="G14" s="10" t="str">
         <x:v>丽娟影视</x:v>
       </x:c>
-      <x:c r="H14" s="10" t="str">
+      <x:c r="H14" s="10" t="str"/>
+      <x:c r="I14" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；100集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="n">
+      <x:c r="J14" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4149,10 +4221,11 @@
       <x:c r="G15" s="10" t="str">
         <x:v>鲸喜漫剧🐳</x:v>
       </x:c>
-      <x:c r="H15" s="10" t="str">
+      <x:c r="H15" s="10" t="str"/>
+      <x:c r="I15" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="n">
+      <x:c r="J15" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4178,10 +4251,11 @@
       <x:c r="G16" s="10" t="str">
         <x:v>朝霞看剧</x:v>
       </x:c>
-      <x:c r="H16" s="10" t="str">
+      <x:c r="H16" s="10" t="str"/>
+      <x:c r="I16" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；118集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="n">
+      <x:c r="J16" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4207,10 +4281,11 @@
       <x:c r="G17" s="10" t="str">
         <x:v>上官格格</x:v>
       </x:c>
-      <x:c r="H17" s="10" t="str">
+      <x:c r="H17" s="10" t="str"/>
+      <x:c r="I17" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；161集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I17" s="11" t="n">
+      <x:c r="J17" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -4236,10 +4311,11 @@
       <x:c r="G18" s="10" t="str">
         <x:v>龙小五剧场</x:v>
       </x:c>
-      <x:c r="H18" s="10" t="str">
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；74集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I18" s="11" t="n">
+      <x:c r="J18" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4265,10 +4341,11 @@
       <x:c r="G19" s="10" t="str">
         <x:v>骏乐夜航船AIGC剧场</x:v>
       </x:c>
-      <x:c r="H19" s="10" t="str">
+      <x:c r="H19" s="10" t="str"/>
+      <x:c r="I19" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「骏乐夜航船AIGC剧场」</x:v>
       </x:c>
-      <x:c r="I19" s="11" t="n">
+      <x:c r="J19" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4294,10 +4371,11 @@
       <x:c r="G20" s="10" t="str">
         <x:v>排尚漫屋</x:v>
       </x:c>
-      <x:c r="H20" s="10" t="str">
+      <x:c r="H20" s="10" t="str"/>
+      <x:c r="I20" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I20" s="11" t="n">
+      <x:c r="J20" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4323,10 +4401,11 @@
       <x:c r="G21" s="10" t="str">
         <x:v>云腾剧场</x:v>
       </x:c>
-      <x:c r="H21" s="10" t="str">
+      <x:c r="H21" s="10" t="str"/>
+      <x:c r="I21" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；95集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="n">
+      <x:c r="J21" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4352,10 +4431,11 @@
       <x:c r="G22" s="10" t="str">
         <x:v>西子是个演员</x:v>
       </x:c>
-      <x:c r="H22" s="10" t="str">
+      <x:c r="H22" s="10" t="str"/>
+      <x:c r="I22" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧 / 古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I22" s="11" t="n">
+      <x:c r="J22" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4381,10 +4461,11 @@
       <x:c r="G23" s="10" t="str">
         <x:v>澜溪剧场</x:v>
       </x:c>
-      <x:c r="H23" s="10" t="str">
+      <x:c r="H23" s="10" t="str"/>
+      <x:c r="I23" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I23" s="11" t="n">
+      <x:c r="J23" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4410,10 +4491,11 @@
       <x:c r="G24" s="10" t="str">
         <x:v>文心动漫</x:v>
       </x:c>
-      <x:c r="H24" s="10" t="str">
+      <x:c r="H24" s="10" t="str"/>
+      <x:c r="I24" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I24" s="11" t="n">
+      <x:c r="J24" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4439,10 +4521,11 @@
       <x:c r="G25" s="10" t="str">
         <x:v>彩云动画</x:v>
       </x:c>
-      <x:c r="H25" s="10" t="str">
+      <x:c r="H25" s="10" t="str"/>
+      <x:c r="I25" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「彩云动画」</x:v>
       </x:c>
-      <x:c r="I25" s="11" t="n">
+      <x:c r="J25" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4468,10 +4551,11 @@
       <x:c r="G26" s="10" t="str">
         <x:v>灯下漫剧</x:v>
       </x:c>
-      <x:c r="H26" s="10" t="str">
+      <x:c r="H26" s="10" t="str"/>
+      <x:c r="I26" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 战神异能）；发布账号「灯下漫剧」</x:v>
       </x:c>
-      <x:c r="I26" s="11" t="n">
+      <x:c r="J26" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4497,10 +4581,11 @@
       <x:c r="G27" s="10" t="str">
         <x:v>优文疯漫</x:v>
       </x:c>
-      <x:c r="H27" s="10" t="str">
+      <x:c r="H27" s="10" t="str"/>
+      <x:c r="I27" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「优文疯漫」</x:v>
       </x:c>
-      <x:c r="I27" s="11" t="n">
+      <x:c r="J27" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4526,10 +4611,11 @@
       <x:c r="G28" s="10" t="str">
         <x:v>智帧剧场</x:v>
       </x:c>
-      <x:c r="H28" s="10" t="str">
+      <x:c r="H28" s="10" t="str"/>
+      <x:c r="I28" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I28" s="11" t="n">
+      <x:c r="J28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4555,10 +4641,11 @@
       <x:c r="G29" s="10" t="str">
         <x:v>灵漫好剧</x:v>
       </x:c>
-      <x:c r="H29" s="10" t="str">
+      <x:c r="H29" s="10" t="str"/>
+      <x:c r="I29" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I29" s="11" t="n">
+      <x:c r="J29" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4584,10 +4671,11 @@
       <x:c r="G30" s="10" t="str">
         <x:v>灵漫剧场</x:v>
       </x:c>
-      <x:c r="H30" s="10" t="str">
+      <x:c r="H30" s="10" t="str"/>
+      <x:c r="I30" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I30" s="11" t="n">
+      <x:c r="J30" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4613,10 +4701,11 @@
       <x:c r="G31" s="10" t="str">
         <x:v>梦启剧场</x:v>
       </x:c>
-      <x:c r="H31" s="10" t="str">
+      <x:c r="H31" s="10" t="str"/>
+      <x:c r="I31" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「梦启剧场」</x:v>
       </x:c>
-      <x:c r="I31" s="11" t="n">
+      <x:c r="J31" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4642,10 +4731,11 @@
       <x:c r="G32" s="10" t="str">
         <x:v>云间漫剧-丸子</x:v>
       </x:c>
-      <x:c r="H32" s="10" t="str">
+      <x:c r="H32" s="10" t="str"/>
+      <x:c r="I32" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；121集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I32" s="11" t="n">
+      <x:c r="J32" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4671,10 +4761,11 @@
       <x:c r="G33" s="10" t="str">
         <x:v>星梦好剧</x:v>
       </x:c>
-      <x:c r="H33" s="10" t="str">
+      <x:c r="H33" s="10" t="str"/>
+      <x:c r="I33" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
       </x:c>
-      <x:c r="I33" s="11" t="n">
+      <x:c r="J33" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4700,10 +4791,11 @@
       <x:c r="G34" s="10" t="str">
         <x:v>陈柯</x:v>
       </x:c>
-      <x:c r="H34" s="10" t="str">
+      <x:c r="H34" s="10" t="str"/>
+      <x:c r="I34" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I34" s="11" t="n">
+      <x:c r="J34" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4729,10 +4821,11 @@
       <x:c r="G35" s="10" t="str">
         <x:v>九鲤动漫</x:v>
       </x:c>
-      <x:c r="H35" s="10" t="str">
+      <x:c r="H35" s="10" t="str"/>
+      <x:c r="I35" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
       </x:c>
-      <x:c r="I35" s="11" t="n">
+      <x:c r="J35" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4758,10 +4851,11 @@
       <x:c r="G36" s="10" t="str">
         <x:v>浮绘剧场</x:v>
       </x:c>
-      <x:c r="H36" s="10" t="str">
+      <x:c r="H36" s="10" t="str"/>
+      <x:c r="I36" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I36" s="11" t="n">
+      <x:c r="J36" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4787,10 +4881,11 @@
       <x:c r="G37" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H37" s="10" t="str">
+      <x:c r="H37" s="10" t="str"/>
+      <x:c r="I37" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I37" s="11" t="n">
+      <x:c r="J37" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -4816,10 +4911,11 @@
       <x:c r="G38" s="10" t="str">
         <x:v>漫文</x:v>
       </x:c>
-      <x:c r="H38" s="10" t="str">
+      <x:c r="H38" s="10" t="str"/>
+      <x:c r="I38" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；79集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I38" s="11" t="n">
+      <x:c r="J38" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4845,10 +4941,11 @@
       <x:c r="G39" s="10" t="str">
         <x:v>闪闪动漫社</x:v>
       </x:c>
-      <x:c r="H39" s="10" t="str">
+      <x:c r="H39" s="10" t="str"/>
+      <x:c r="I39" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「闪闪动漫社」</x:v>
       </x:c>
-      <x:c r="I39" s="11" t="n">
+      <x:c r="J39" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4874,10 +4971,11 @@
       <x:c r="G40" s="10" t="str">
         <x:v>卿读剧场</x:v>
       </x:c>
-      <x:c r="H40" s="10" t="str">
+      <x:c r="H40" s="10" t="str"/>
+      <x:c r="I40" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「卿读剧场」</x:v>
       </x:c>
-      <x:c r="I40" s="11" t="n">
+      <x:c r="J40" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4903,10 +5001,11 @@
       <x:c r="G41" s="10" t="str">
         <x:v>次元佳思剧场</x:v>
       </x:c>
-      <x:c r="H41" s="10" t="str">
+      <x:c r="H41" s="10" t="str"/>
+      <x:c r="I41" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「次元佳思剧场」</x:v>
       </x:c>
-      <x:c r="I41" s="11" t="n">
+      <x:c r="J41" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4932,10 +5031,11 @@
       <x:c r="G42" s="10" t="str">
         <x:v>青禾短剧</x:v>
       </x:c>
-      <x:c r="H42" s="10" t="str">
+      <x:c r="H42" s="10" t="str"/>
+      <x:c r="I42" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；发布账号「青禾短剧」</x:v>
       </x:c>
-      <x:c r="I42" s="11" t="n">
+      <x:c r="J42" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4961,10 +5061,11 @@
       <x:c r="G43" s="10" t="str">
         <x:v>新美漫剧场</x:v>
       </x:c>
-      <x:c r="H43" s="10" t="str">
+      <x:c r="H43" s="10" t="str"/>
+      <x:c r="I43" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能）；发布账号「新美漫剧场」</x:v>
       </x:c>
-      <x:c r="I43" s="11" t="n">
+      <x:c r="J43" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -4990,10 +5091,11 @@
       <x:c r="G44" s="10" t="str">
         <x:v>凛冬短剧</x:v>
       </x:c>
-      <x:c r="H44" s="10" t="str">
+      <x:c r="H44" s="10" t="str"/>
+      <x:c r="I44" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「凛冬短剧」</x:v>
       </x:c>
-      <x:c r="I44" s="11" t="n">
+      <x:c r="J44" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5019,10 +5121,11 @@
       <x:c r="G45" s="10" t="str">
         <x:v>红豆剧场</x:v>
       </x:c>
-      <x:c r="H45" s="10" t="str">
+      <x:c r="H45" s="10" t="str"/>
+      <x:c r="I45" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；80集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「红豆剧场」</x:v>
       </x:c>
-      <x:c r="I45" s="11" t="n">
+      <x:c r="J45" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5048,10 +5151,11 @@
       <x:c r="G46" s="10" t="str">
         <x:v>次元心动剧场</x:v>
       </x:c>
-      <x:c r="H46" s="10" t="str">
+      <x:c r="H46" s="10" t="str"/>
+      <x:c r="I46" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；55集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；发布账号「次元心动剧场」</x:v>
       </x:c>
-      <x:c r="I46" s="11" t="n">
+      <x:c r="J46" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5077,10 +5181,11 @@
       <x:c r="G47" s="10" t="str">
         <x:v>阳光微剧</x:v>
       </x:c>
-      <x:c r="H47" s="10" t="str">
+      <x:c r="H47" s="10" t="str"/>
+      <x:c r="I47" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材待验证；发布账号「阳光微剧」</x:v>
       </x:c>
-      <x:c r="I47" s="11" t="n">
+      <x:c r="J47" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5106,10 +5211,11 @@
       <x:c r="G48" s="10" t="str">
         <x:v>漫恋小剧场</x:v>
       </x:c>
-      <x:c r="H48" s="10" t="str">
+      <x:c r="H48" s="10" t="str"/>
+      <x:c r="I48" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；45集，中等长度；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「漫恋小剧场」</x:v>
       </x:c>
-      <x:c r="I48" s="11" t="n">
+      <x:c r="J48" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5135,10 +5241,11 @@
       <x:c r="G49" s="10" t="str">
         <x:v>漫语剧场</x:v>
       </x:c>
-      <x:c r="H49" s="10" t="str">
+      <x:c r="H49" s="10" t="str"/>
+      <x:c r="I49" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；46集，中等长度；题材契合爆款主线（家庭伦理）；发布账号「漫语剧场」</x:v>
       </x:c>
-      <x:c r="I49" s="11" t="n">
+      <x:c r="J49" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5164,10 +5271,11 @@
       <x:c r="G50" s="10" t="str">
         <x:v>漫文传媒</x:v>
       </x:c>
-      <x:c r="H50" s="10" t="str">
+      <x:c r="H50" s="10" t="str"/>
+      <x:c r="I50" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；69集长剧集，符合起量主力区间；题材待验证；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I50" s="11" t="n">
+      <x:c r="J50" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -5193,10 +5301,11 @@
       <x:c r="G51" s="10" t="str">
         <x:v>月光短剧</x:v>
       </x:c>
-      <x:c r="H51" s="10" t="str">
+      <x:c r="H51" s="10" t="str"/>
+      <x:c r="I51" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材待验证；发布账号「月光短剧」</x:v>
       </x:c>
-      <x:c r="I51" s="11" t="n">
+      <x:c r="J51" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -5222,10 +5331,11 @@
       <x:c r="G52" s="10" t="str">
         <x:v>凛冬短剧</x:v>
       </x:c>
-      <x:c r="H52" s="10" t="str">
+      <x:c r="H52" s="10" t="str"/>
+      <x:c r="I52" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材待验证；发布账号「凛冬短剧」</x:v>
       </x:c>
-      <x:c r="I52" s="11" t="n">
+      <x:c r="J52" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -5251,10 +5361,11 @@
       <x:c r="G53" s="10" t="str">
         <x:v>恐龙粑粑小百科</x:v>
       </x:c>
-      <x:c r="H53" s="10" t="str">
+      <x:c r="H53" s="10" t="str"/>
+      <x:c r="I53" s="10" t="str">
         <x:v>83集长剧集，符合起量主力区间；题材待验证；发布账号「恐龙粑粑小百科」</x:v>
       </x:c>
-      <x:c r="I53" s="11" t="n">
+      <x:c r="J53" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -5263,28 +5374,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B54" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>绝地重生：揭穿闺蜜虚伪的面具</x:v>
+        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
-      <x:c r="G54" s="10" t="str">
-        <x:v>不兜</x:v>
-      </x:c>
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str"/>
       <x:c r="H54" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「不兜」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I54" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
+      </x:c>
+      <x:c r="I54" s="10" t="str">
+        <x:v>57集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J54" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -5292,28 +5404,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B55" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>丈夫坑娃，我绝不认输</x:v>
+        <x:v>重生：回到1983当富翁之路第一季</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>萌宝治愈 / 婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>阿水漫画</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I55" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>上市公司执行总裁周于峰意外重回1983年。面对尚未改善的家庭关系、生活拮据的弟弟妹妹，以及处处充满机遇与挑战的时代环境。凭借多年积累的商业经验与判断力，周于峰从小生意做起，在坚守原则与规则的同时抓住时代机遇，一步步改善家人的生活，也重新审视婚姻与亲情。在改革浪潮中，他与身边的人共同成长，用一次次选择改变人生轨迹，走出属于自己的创业之路。</x:v>
+      </x:c>
+      <x:c r="I55" s="10" t="str">
+        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「阿水漫画」</x:v>
+      </x:c>
+      <x:c r="J55" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -5321,28 +5436,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
+        <x:v>1970重生岁岁，不负韶华</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F56" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>星文文化</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I56" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
+      </x:c>
+      <x:c r="I56" s="10" t="str">
+        <x:v>86集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「星文文化」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J56" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -5350,28 +5468,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B57" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
+        <x:v>全校笑我铁匠，我反手锻剑娘</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>107</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>古装宫廷 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
-        <x:v>初八漫剧</x:v>
+        <x:v>榴莲漫剧</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I57" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>故事讲述英雄遗孤陆渊在转职仪式上觉醒最低级生活职业“铁匠”，遭受众人嘲笑，却意外激活隐藏职业“神级器灵师”。他以锻造之力创造出拥有灵智的强大器灵，一路打造剑娘、刀灵、盾灵，凭借隐藏实力横扫秘境、打破纪录、反击天才与权贵，从被轻视的废物铁匠成长为震撼世界的顶级强者。</x:v>
+      </x:c>
+      <x:c r="I57" s="10" t="str">
+        <x:v>142集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「榴莲漫剧」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J57" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -5379,28 +5500,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>同频心动</x:v>
+        <x:v>八十年代：铁娘子的缝纫机逆袭路</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G58" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>漫剧场小管家</x:v>
       </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I58" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>八十年代改革开放初期，金枝丈夫去世后，一直与婆家同住，带着女儿过日子。面对婆家的偏心与冷眼，她从不低头，靠着一手裁缝好手艺，从走街串巷给人缝补做起。一针一线，把日子缝得踏实。从为人代工到盘下门面，金枝凭手中针线和不认输的劲头，挣出尊严，也闯出了属于自己的裁缝铺子与人生。</x:v>
+      </x:c>
+      <x:c r="I58" s="10" t="str">
+        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「漫剧场小管家」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J58" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -5408,28 +5532,31 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B59" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>婚礼前夜，我换了新郎</x:v>
+        <x:v>反派大佬成了女儿奴第一季</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>戏众生</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I59" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>为了糖果奖励，薄珠珠接下系统任务，要让薄宴州认下自己。她顺着纸箱空降薄氏集团。薄宴州十分抗拒，故意逗弄珠珠。可糖果的吸引力让薄珠珠不肯放弃，折返回来状况百出，系统疯狂报错，薄宴州看着古灵精怪的小团子满心审视。</x:v>
+      </x:c>
+      <x:c r="I59" s="10" t="str">
+        <x:v>144集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；续季/系列续作，有前作热度背书；发布账号「戏众生」</x:v>
+      </x:c>
+      <x:c r="J59" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -5437,28 +5564,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>玻璃钻戒终结七年错爱</x:v>
+        <x:v>后娘逆袭</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>1649世界</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I60" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
+      </x:c>
+      <x:c r="I60" s="10" t="str">
+        <x:v>74集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「1649世界」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J60" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -5466,28 +5596,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B61" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
+        <x:v>带着仓库回七零第一季</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>保温虾虾</x:v>
+        <x:v>无极动画</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
-      </x:c>
-      <x:c r="I61" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>1976年，沈牧野含恨重生，回到与周翠兰离婚当天。他凭穿越而来的现代仓库和前世厨艺进入钢铁厂食堂，从被刁难到凭西餐接待外宾一战成名。他先救下二姐母女，再治大姐的腿、还三姐的债，把家人一个个从苦日子里拉出来。期间，厂办秘书苏婉清一次次替他解围，两人在烟火与患难中越走越近。最后全家搬进厂区小院，枣树下，悸动暗生。</x:v>
+      </x:c>
+      <x:c r="I61" s="10" t="str">
+        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「无极动画」</x:v>
+      </x:c>
+      <x:c r="J61" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -5495,28 +5628,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B62" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>下午的早餐店第五季</x:v>
+        <x:v>异能赶海：从失业到海洋女王第二季</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>盐系少女社</x:v>
+        <x:v>每日沙雕推荐</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I62" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>北漂失意的苏蕴舟回乡后，觉醒能看透水下的特殊能力，靠收获珍贵海产快速积累财富，买下独栋别墅，改善全家生活。她救下遭遇意外的少年陆星辰，结识商界的霍铮，二人从试探发展为合作伙伴。苏蕴舟从容应对前男友、同学带来的人际纠葛。家里日子蒸蒸日上，父亲开办海产加工坊。苏蕴舟将一批珍珠交由霍氏处理，收到拍卖会邀约，在与大海相伴的日子里，完成自我成长与人生蜕变。</x:v>
+      </x:c>
+      <x:c r="I62" s="10" t="str">
+        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+      </x:c>
+      <x:c r="J62" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -5524,28 +5660,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B63" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>不朽仙秦！第三季</x:v>
+        <x:v>彩运照人心，第一季</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>190</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
-        <x:v>虾仁白白</x:v>
+        <x:v>文之江影视</x:v>
       </x:c>
       <x:c r="H63" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I63" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>胡帕喜中巨额彩票，领奖当天却惨遭相恋四年的女友分手，昔日温情瞬间化为泡影。他斩断过往纠葛，毅然离职，奔赴郑州探望勤工俭学的妹妹，也因此结识了善良坚韧的梁池，两人渐生情愫。清明返乡，他冷眼看透势利亲戚的虚伪嘴脸，手握财富却选择低调行事，一心照料家人。在这冷暖交织的人情世故里，他褪去浮华，终与梁池携手，收获了一份纯粹真挚的缘分。</x:v>
+      </x:c>
+      <x:c r="I63" s="10" t="str">
+        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书；发布账号「文之江影视」</x:v>
+      </x:c>
+      <x:c r="J63" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -5553,28 +5692,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B64" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>五十保姆觉醒，遗产见人心</x:v>
+        <x:v>恋上心通第一季</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
-        <x:v>剑心动漫</x:v>
+        <x:v>益阳动漫</x:v>
       </x:c>
       <x:c r="H64" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
-      </x:c>
-      <x:c r="I64" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>快穿大佬叶聆刚退休就穿成恋综恶毒原配，绑定系统后惩罚竟全劈在冷漠老公谢淮舟身上，还附带感官通感！为了保命，高岭之花谢淮舟当众崩人设抢牵手、爆金币、求贴贴，全网惊呆说好的塑料夫妻呢？叶聆反骨杀疯恋综，手撕绿茶、暴揍前任、扫地出门全家奇葩。</x:v>
+      </x:c>
+      <x:c r="I64" s="10" t="str">
+        <x:v>129集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「益阳动漫」</x:v>
+      </x:c>
+      <x:c r="J64" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -5582,28 +5724,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B65" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
+        <x:v>收租精神小妹！第二季</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
-        <x:v>晟樊影视</x:v>
+        <x:v>心悦漫剪</x:v>
       </x:c>
       <x:c r="H65" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
-      </x:c>
-      <x:c r="I65" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>大厂十年，一朝被裁。林野拿着两百万补偿金回到县城，全款买了套别墅，只想安静活着。系统不让。收租万倍返还系统已激活。他盯着空荡荡的五个房间，开始琢磨怎么找租客。第一个上门的，是三个流浪到江城的精神小妹。从这天起，他的别墅再也没安静过。精神小妹、落魄富二代、跑路网红，各路奇人排着队住进来。</x:v>
+      </x:c>
+      <x:c r="I65" s="10" t="str">
+        <x:v>124集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「心悦漫剪」</x:v>
+      </x:c>
+      <x:c r="J65" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -5611,28 +5756,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>全民御兽：神级鉴兽师第二季</x:v>
+        <x:v>无心攀比，假千金重生后成团宠了</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
-        <x:v>漫川动漫剧场</x:v>
+        <x:v>鲸跃AI剧场</x:v>
       </x:c>
       <x:c r="H66" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I66" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
+      </x:c>
+      <x:c r="I66" s="10" t="str">
+        <x:v>100集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「鲸跃AI剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J66" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -5640,28 +5788,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
+        <x:v>死对头校花竟是我网恋女友第二季</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
-        <x:v>竹蜻蜓剧场</x:v>
+        <x:v>长鹿漫漫</x:v>
       </x:c>
       <x:c r="H67" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I67" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>网络里的温柔陪伴，与现实中的针锋相对形成奇妙反差。相识四年，他们一直是彼此最熟悉的网友，却从未想过对方就在身边。从最初的误会，到一次次相处中逐渐卸下防备，两人慢慢发现彼此不为人知的温柔一面。当四年网聊终于迎来奔现，他们才发现，那个一直陪伴自己的人，竟是现实中最意想不到的存在。一场甜蜜、欢乐又充满惊喜的青春恋爱，就此开始。</x:v>
+      </x:c>
+      <x:c r="I67" s="10" t="str">
+        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「长鹿漫漫」</x:v>
+      </x:c>
+      <x:c r="J67" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -5669,28 +5820,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>农场萌宠！第六季</x:v>
+        <x:v>浴火重生，我撕碎前夫的美梦</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>种田囤货 / 婚姻情感</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>惜惜动漫</x:v>
+        <x:v>云阅真人漫剧</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I68" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>家庭主妇林晚遭丈夫陈世杰与情人苏曼背叛，更被设计坠崖毁容。死里逃生后，她继承遗产、改头换面，以资本新贵身份重返陈世杰身边，步步引他暴露贪婪与罪行。最终真相大白，林晚在顾言守护下夺回属于她的一切，迎来新生。</x:v>
+      </x:c>
+      <x:c r="I68" s="10" t="str">
+        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「云阅真人漫剧」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J68" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -5698,28 +5852,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B69" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
+        <x:v>破窑洞飞出金凤凰第一季</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>枕月漫影</x:v>
+        <x:v>定边同城帮</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I69" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>李根出身贫寒，大学时与富家女苏婉晴相恋，却在订婚宴上被当众退婚羞辱。他落魄返乡，在荒山上发现野生酸枣的商机，立志创业。从承包荒山、改土育苗，到历经暴雨毁林、父亲病倒、资金断裂等重重打击，他凭一股不服输的韧劲咬牙坚持。在贵人相助和全村人的支持下，他成功将荒山变成千亩枣园，成立合作社，带领黄土坡村脱贫致富。事业有成后，他赢得真诚爱情，拒绝资本诱惑，创办农业大学，用一生诠释了什么是坚守初心，扎根土地。</x:v>
+      </x:c>
+      <x:c r="I69" s="10" t="str">
+        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「定边同城帮」</x:v>
+      </x:c>
+      <x:c r="J69" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -5727,28 +5884,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B70" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>利益照见人心</x:v>
+        <x:v>纨绔穿越古代成就百万诗仙第一季</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>天天爱看剧</x:v>
+        <x:v>咪漫剧场</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
-      </x:c>
-      <x:c r="I70" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>现代纨绔魂穿贞观十年，成为军神李靖之孙李景安。开局揭皇榜医治长孙皇后，凭抄录千古诗词惊艳长安，诗会碾压对手一战封神。解锁硝石制冰、马蹄铁等黑科技搅动朝堂。一边当摆烂纨绔，一边搅动大唐风云，周旋世家权贵，邂逅多位佳人，在初唐掀起属于谪仙少年的传奇浪潮。</x:v>
+      </x:c>
+      <x:c r="I70" s="10" t="str">
+        <x:v>89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「咪漫剧场」</x:v>
+      </x:c>
+      <x:c r="J70" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -5756,28 +5916,31 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
+        <x:v>荒岛逆袭：我成了荒岛之王</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G71" s="10" t="str">
-        <x:v>月亮与孤岛</x:v>
+        <x:v>庚庚</x:v>
       </x:c>
       <x:c r="H71" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I71" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>一场突发的海难，让公司员工陆鸣与总裁苏清寒等同事意外流落荒野孤岛。失去现代文明的庇护，习惯了优渥生活的苏清寒等人起初难以适应，依然带有职场上的刻板偏见，试图将荒野危机简单化。然而，陆鸣凭借过硬的野外求生知识与坚韧的意志，不仅成功获取了珍贵的食物和水源，还搭建起了安全的庇护所。为了整个团队的生存，陆鸣立下“按劳分配、互帮互助”的营地新规。在陆鸣的带领下，他们战胜了荒岛危机。</x:v>
+      </x:c>
+      <x:c r="I71" s="10" t="str">
+        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「庚庚」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J71" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -5785,28 +5948,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B72" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>剑定山河第一季</x:v>
+        <x:v>蓄意逐风：我在恋综称王称爸第二季</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>捷捷动漫馆</x:v>
+        <x:v>₊⁺水蜜陶🍑剧场</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I72" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>恋综游园会浪漫开启谢弥经助理刁茂巧手妆造一袭浅碧挂脖长裙惊艳全场绿毛龟轮椅依旧是她标志性座驾。沈爅卿一见盛装的谢弥眼底藏不住温柔轻声夸赞她夺目。二人扫荡美食摊位后，前去塔罗帐篷占卜谢弥一心惦记财运，顺势追问命定之人是不是沈爅卿，沈爅卿暗藏心事化身谜语人二人写下心愿纸船放入溪流，谢弥却抛下纸船直奔套圈摊位，沈爅卿含笑追赶。镜头曝光沈爅卿纸船秘密纸上赫然写着我的初恋是谢老师埋藏已久的心意悄然浮出水面。</x:v>
+      </x:c>
+      <x:c r="I72" s="10" t="str">
+        <x:v>119集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「₊⁺水蜜陶🍑剧场」</x:v>
+      </x:c>
+      <x:c r="J72" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -5814,28 +5980,31 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B73" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>反向养老：从出卖孙女到宠冠全村2</x:v>
+        <x:v>误惹京华第二季</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F73" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I73" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>面对婚姻背叛与有毒亲情，坚韧的女性姜辞忧毅然决然的断亲独立，凭实力职场逆袭的故事。在自我救赎路上，她与深情守护的真爱薄靳修携手击碎阴谋；更在历经千帆后与生母温馨和解，传递出当代女性自强不息、温暖治愈的硬核力量！</x:v>
+      </x:c>
+      <x:c r="I73" s="10" t="str">
+        <x:v>126集长剧集，符合起量主力区间；题材待验证；续季/系列续作，有前作热度背书；发布账号「星屿漫剧场」多次产出上榜剧</x:v>
+      </x:c>
+      <x:c r="J73" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -5843,28 +6012,31 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B74" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C74" s="10" t="str">
-        <x:v>一张照片传遍公司群我却因此重生了</x:v>
+        <x:v>68万存款，买了一场婚姻的真相第二季</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E74" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F74" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="G74" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>权策推剧</x:v>
       </x:c>
       <x:c r="H74" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I74" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>婚礼当天，吴子妍被丈夫一家逼签陪嫁房赠予协议，当众受辱。她当场撕毁协议、取消婚礼，却在离婚后遭遇周家霸占房产、伪造授权、私吞租金的无底线算计。从崩溃屈辱中站起，她冷静收集证据、诉诸法律，一步步追回房产与尊严。最终，周家付出代价，吴子妍拿回人生主动权，更将自己的经历化作对无数女性的边界提醒——守住底线，从不丢人。</x:v>
+      </x:c>
+      <x:c r="I74" s="10" t="str">
+        <x:v>135集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；续季/系列续作，有前作热度背书；发布账号「权策推剧」</x:v>
+      </x:c>
+      <x:c r="J74" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -5872,28 +6044,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B75" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C75" s="10" t="str">
-        <x:v>一纸通知书，丈夫托我赴前程</x:v>
+        <x:v>林国强的故事，重生80年带妻女翻身第二季</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E75" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F75" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G75" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>每日沙雕推荐</x:v>
       </x:c>
       <x:c r="H75" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I75" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>林国强重生回到八零年代，开国强饭店创业起家，分家脱离原生家庭，避开前世悲剧。第二季主线事业持续扩张，处理原生家庭一堆烂摊子，妹妹遭遇家暴悲剧，兄弟姐妹各自的命运走向，拓展大棚、养鸡场、鱼塘多条产业线，同时伴随亲戚算计、婚恋风波，铺垫县城大饭庄的新事业。</x:v>
+      </x:c>
+      <x:c r="I75" s="10" t="str">
+        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+      </x:c>
+      <x:c r="J75" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -5901,28 +6076,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B76" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C76" s="10" t="str">
-        <x:v>一顿饭算清</x:v>
+        <x:v>重生觉醒，这次我不做恋爱脑第六季</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E76" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F76" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="G76" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>桃汁夭夭</x:v>
       </x:c>
       <x:c r="H76" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I76" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>重活一世，林雾终于看清自己的心，坚定走向始终默默守护她的徐京妄。她用一场精心准备的生日惊喜，陪他回望成长岁月，也许下长久相伴的承诺。此后，两人的感情愈发甜蜜坚定。面对家人的关注，林雾坦然表达心意，徐京妄也以真诚回应她的偏爱。林雾也在彼此陪伴与守护中不断成长，与他携手奔向明亮温暖的未来。</x:v>
+      </x:c>
+      <x:c r="I76" s="10" t="str">
+        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「桃汁夭夭」</x:v>
+      </x:c>
+      <x:c r="J76" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -5930,28 +6108,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B77" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C77" s="10" t="str">
-        <x:v>一顿香锅断前缘</x:v>
+        <x:v>人是诡异幼崽第二季</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E77" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F77" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="G77" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>悦禾剧场</x:v>
       </x:c>
       <x:c r="H77" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I77" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>穿越者任逸一直以为自己生活在人类社会，直到毕业觉醒，才发现联盟里根本没有人类，而自己竟是披着人皮的诡异幼崽。觉醒幻术规则后，他与陆子涵进入副本实习，在一次次规则博弈中疯狂收割情绪、提升实力。随特别收割预案启动，任逸主动伪装成人类参与者潜入“陆家小院”，借直播扩大能力收益。然而瓜田、药园规则层层升级，浓雾深处的诡异梧桐与致命限制逐渐显现，一场更危险的猎杀正式开始。</x:v>
+      </x:c>
+      <x:c r="I77" s="10" t="str">
+        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈）；续季/系列续作，有前作热度背书；发布账号「悦禾剧场」</x:v>
+      </x:c>
+      <x:c r="J77" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -5959,28 +6140,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B78" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>仙尊归来，四大家族慌了</x:v>
+        <x:v>修仙归来护家人第二季</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
         <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>夏十七</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；发布账号「西瑶短剧」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I78" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
+      </x:c>
+      <x:c r="I78" s="10" t="str">
+        <x:v>72集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「夏十七」</x:v>
+      </x:c>
+      <x:c r="J78" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -5988,28 +6172,29 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B79" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>嫁妆被抢那天我亮明了身份</x:v>
+        <x:v>凡人仙鱼，混沌灵根逆袭仙途</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="G79" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str"/>
       <x:c r="H79" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I79" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>天玄宗杂役弟子许时安，因混沌废灵根被视为消耗资源的无底洞，只能在后山清理淤泥。意外之下，他在丹田中得到一只神秘黑鱼！神鱼吞吃废丹废符后，竟能吐出完美品阶的丹药符箓！自此，许时安从底层杂役逆袭，拜入仙子苏眠门下，习得上古剑法典籍《道剑十三》。秘境历练中，神鱼经历第三次进化，化为鲲之形态。面对仇人截杀与七魔将的血祭大阵，许时安以道剑十三破阵，祭出上古磨盘镇压万魔，一战封神，震惊整个天玄宗！</x:v>
+      </x:c>
+      <x:c r="I79" s="10" t="str">
+        <x:v>77集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J79" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -6017,28 +6202,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B80" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>带男友回大山继承家产</x:v>
+        <x:v>凡人修仙开局捡到聚宝仙鼎第四季</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>蜗牛漫剧剧场</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I80" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>全仙宗都笑凡人许长生五行杂灵根，注定困死废丹房！许长生得云瑶仙子引仙门，却沦为最低废丹房杂役，日日遭管事压榨羞辱。山洪濒死之际，天降聚宝仙鼎，废丹炼极品、残书化顶级道藏，万物经鼎皆能升华！他暗藏底牌隐忍发育，打脸欺辱自己的杂役与管事，大比惊艳全场，一跃成为内门弟子，凭一鼎之力逆转凡人身，踏破长生大道。</x:v>
+      </x:c>
+      <x:c r="I80" s="10" t="str">
+        <x:v>158集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「蜗牛漫剧剧场」</x:v>
+      </x:c>
+      <x:c r="J80" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -6046,28 +6234,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B81" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>末世，带着修改器重生，我无敌了2</x:v>
+        <x:v>别拿猪婆龙不当神兽第二季</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>机甲熊</x:v>
+        <x:v>与情箓</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I81" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>别拿猪婆龙不当神兽第二季来袭！渡劫失败的虞柏柏被天雷劈成了一条猪婆龙（扬子鳄），在高冷影帝家里当宠物蹭吃蹭喝蹭雪饼。影帝抱着鳄鱼形态的她殷切期盼，如果你能变成虞柏柏那样的美人该有多好啊！某一天，虞柏柏实在憋不住了，在影帝怀里现出了人形，她转头看向了高冷影帝，眼神魅惑，还满意你看到的吗？没想到，高冷影帝当场垮起了脸——变回去！</x:v>
+      </x:c>
+      <x:c r="I81" s="10" t="str">
+        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「与情箓」</x:v>
+      </x:c>
+      <x:c r="J81" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -6075,28 +6266,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B82" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>错写红封，终断婚约</x:v>
+        <x:v>发配充军，战神系统宁九才镇守边关第三季</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>灵梦剧场</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」多次产出上榜剧</x:v>
-      </x:c>
-      <x:c r="I82" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>宁川重回盛京，深知大晋皇室底蕴深厚。他借力邀月公主的夺嫡之争，接连拔除多方敌对势力，依靠特殊流水线能力快速提升自身修为。尘封数百年的宁家旧仇真相大白，宁川成功为家族洗刷冤屈，扶持妹妹宁婉儿建立宁国，登临帝位。外部危机却接连爆发，柳如烟、南海海族、葬土死灵纷纷发难。宁川不断突破境界，力克强敌，收获珍贵仙种，意外寻得离开绝灵之地的线索，一场席卷天下的大乱局徐徐拉开。</x:v>
+      </x:c>
+      <x:c r="I82" s="10" t="str">
+        <x:v>111集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+      </x:c>
+      <x:c r="J82" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -6104,28 +6298,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B83" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>一井见人心</x:v>
+        <x:v>咱们你听心声我吃瓜，换嫁夫妻笑哈哈第二季</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F83" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>云间予安</x:v>
+        <x:v>每日沙雕速递</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
-      </x:c>
-      <x:c r="I83" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>现代穿越者裴辞镜绑定吃瓜系统，娶了拥有读心能力的沈柠欢。裴辞镜表面咸鱼，内心疯狂吃瓜吐槽，沈柠欢看破他的心声，夫妻二人默契十足。恰逢太子发动宫变，二人携手化解危机，揪出八皇子的谋划。之后裴辞镜参加科举，高中探花，入朝任职翰林院编修。侯府内部恩怨逐渐化解，沈柠悦幡然悔悟。裴辞镜入职后接到修订水利典籍的差事，还意外发现前人疑似穿越者的线索，故事暂告一段落。</x:v>
+      </x:c>
+      <x:c r="I83" s="10" t="str">
+        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈）；续季/系列续作，有前作热度背书；发布账号「每日沙雕速递」</x:v>
+      </x:c>
+      <x:c r="J83" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -6133,28 +6330,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>一渠清水见人心</x:v>
+        <x:v>婚宴厅被抢，我反手告倒百亿公司</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F84" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>心痕剧场</x:v>
+        <x:v>妙手看剧</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
-      </x:c>
-      <x:c r="I84" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>许知夏筹备多年的婚宴当天，场地方突然毁约，替梁书瑶腾出主舞台。未婚夫陆远舟不仅没有替她说话，反而站到梁书瑶身边，逼她识相离场。梁家仗着百亿公司撑腰，封锁证据、操控舆论，想让她带着耻辱退场。许知夏却撕下婚纱上的花，保全合同、录音与资金记录，将婚宴变成反击的起点。她解除婚约，反手起诉梁家企业，让抢走她婚礼的人，为这场精心设计的羞辱付出代价。</x:v>
+      </x:c>
+      <x:c r="I84" s="10" t="str">
+        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转）；发布账号「妙手看剧」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J84" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -6162,28 +6362,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B85" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>七天照见人心</x:v>
+        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>倩倩短剧</x:v>
+        <x:v>云朵邮递员</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
-      </x:c>
-      <x:c r="I85" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
+      </x:c>
+      <x:c r="I85" s="10" t="str">
+        <x:v>131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；续季/系列续作，有前作热度背书；发布账号「云朵邮递员」</x:v>
+      </x:c>
+      <x:c r="J85" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -6191,28 +6394,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B86" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
+        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
+        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>溪溪剧场</x:v>
+        <x:v>平川动画</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I86" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
+      </x:c>
+      <x:c r="I86" s="10" t="str">
+        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 萌宝治愈 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「平川动画」</x:v>
+      </x:c>
+      <x:c r="J86" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -6220,28 +6426,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B87" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>假面羁绊：极客先生的秘密</x:v>
+        <x:v>小满混江湖第一季</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>北极熊短剧</x:v>
+        <x:v>两把刷子剧场</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
-      </x:c>
-      <x:c r="I87" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>底层客栈孤女姜小满为求生存，意外卷入烬月教阴谋，被迫顶替失踪多年的青梧派掌门义女林阿照，就此踏入一场蛰伏十六年的朝堂死局。在门派中她与心思深沉的大师兄沈砚舟步步周旋，又凭借儿时一张平安符，攀附腹黑的魔教教主谢无咎。随着旧案揭开，假身份之下牵扯出真公主的过往，侯府灭口、妃嫔算计、双生皇子秘闻接连浮现。市井孤女凭着狡黠与傲骨，游走于江湖朝堂，以袖中薄刃，搅动整片天下棋局。</x:v>
+      </x:c>
+      <x:c r="I87" s="10" t="str">
+        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「两把刷子剧场」</x:v>
+      </x:c>
+      <x:c r="J87" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -6249,28 +6458,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B88" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
+        <x:v>小邪爱空姐之欢喜对头误撞心动第二季</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>浪客剧场</x:v>
+        <x:v>天才黄小邪</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
-      </x:c>
-      <x:c r="I88" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>妇科医生陈北在航班上俯身帮男孩捡东西时，不慎误碰空姐陈诗瑶，被对方误会耍流氓，还闹到了警局，但最终警方证实了他的清白。这场飞机上的意外乌龙，本以为他们再无交集，可陈诗瑶却发现新租房子的房东竟然是陈北。于是两人开始同居，欢喜冤家同住一屋，从针锋相对到渐生情愫，最终甜蜜相恋、幸福相守。</x:v>
+      </x:c>
+      <x:c r="I88" s="10" t="str">
+        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「天才黄小邪」</x:v>
+      </x:c>
+      <x:c r="J88" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -6278,28 +6490,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B89" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>农村兽神第五季</x:v>
+        <x:v>开局成废后我反手养出十万御林军</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F89" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>每日欢乐漫剧</x:v>
+        <x:v>天桥热血剧场</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I89" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
+      </x:c>
+      <x:c r="I89" s="10" t="str">
+        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「天桥热血剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J89" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -6307,28 +6522,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>匠心逆袭：我为行业立规矩</x:v>
+        <x:v>心愿昭昭，神明有应第一季</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>五碗说漫</x:v>
+        <x:v>文妃儿</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
-      </x:c>
-      <x:c r="I90" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>雾禾最大的心愿，是寻一位模样俊朗、性情体贴的夫君，陪她守着小院安稳度日。于是，她跑到山中神像前认真许愿。没过多久，风离昭便来到她身边。他会洗衣做饭，会亲手添置家用，也会把她随口说过的话放在心上，只是偶尔傲娇炸毛，格外需要人哄。雾禾以为自己只是运气好，却渐渐发现，这位夫君似乎与山中的古老传说关系匪浅。一个愿望牵起一段奇缘，两个原本孤单的人，在欢笑与陪伴中学会信任，也把平凡光景过成了温暖明亮的好日子。</x:v>
+      </x:c>
+      <x:c r="I90" s="10" t="str">
+        <x:v>120集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文妃儿」</x:v>
+      </x:c>
+      <x:c r="J90" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -6336,28 +6554,31 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>囤货逆袭大佬末世之归途</x:v>
+        <x:v>我的别墅通两界，摆摊的我赚了亿点点第三季</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>种田囤货 / 逆袭打脸</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>逐梦剧场</x:v>
+        <x:v>灵梦剧场</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
-      </x:c>
-      <x:c r="I91" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>陆沉玉穿梭现代与异界，壮大石牙部落，完善城防、推行识字与岗位竞选，部落蒸蒸日上。白头部落举兵进犯，被陆沉玉击溃，俘虏纳入劳动力，吴志也归降部落。陆沉玉组建华夏商队，携盐、陶器等物资远征参加部落大集，沿路收服孤山、青山等部族，收获煤炭、蜂蜜、香草荚等资源。抵达大集后，华夏部落凭借精良物资震慑各方势力，神殿假意示好，企图套取制盐、烧瓷技术，陆沉玉将计就计，带着暗藏阴谋的神殿随从踏上归途。</x:v>
+      </x:c>
+      <x:c r="I91" s="10" t="str">
+        <x:v>104集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+      </x:c>
+      <x:c r="J91" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -6365,28 +6586,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
+        <x:v>我的渔船通龙宫第一季</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>小奶团动画</x:v>
+        <x:v>六翼动漫</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I92" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
+      </x:c>
+      <x:c r="I92" s="10" t="str">
+        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「六翼动漫」</x:v>
+      </x:c>
+      <x:c r="J92" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -6394,28 +6618,671 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B93" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
+        <x:v>我竟是道祖之狩猎气运之子第五季</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>闲人一坤</x:v>
+        <x:v>玖月说漫</x:v>
       </x:c>
       <x:c r="H93" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I93" s="11" t="n">
+        <x:v>三千道州与神魔大陆相连，古族之主古乾立于时代潮头，带领族中强者踏入更广阔天地。一次跨界之行，让魅魔族迎来全新归宿，也让古族与各大道统的联系愈发紧密。古乾一边安置新族地、汇聚各方资源，一边放眼界域天骄盛会与更高层次的古洪荒。随着古雄彪等新一代天骄崭露锋芒，古族气运日盛，新的伙伴、机缘与广阔天地接连出现。</x:v>
+      </x:c>
+      <x:c r="I93" s="10" t="str">
+        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书；发布账号「玖月说漫」</x:v>
+      </x:c>
+      <x:c r="J93" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B94" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C94" s="10" t="str">
+        <x:v>亲戚聚会他摆阔，我爸不结账了</x:v>
+      </x:c>
+      <x:c r="D94" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E94" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F94" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G94" s="10" t="str">
+        <x:v>屿风漫剧</x:v>
+      </x:c>
+      <x:c r="H94" s="10" t="str">
+        <x:v>家族聚会上，陈国梁借哥哥陈国栋的钱买车摆阔，又多次把宴请账单推给哥哥。陈昭为保护父亲，推动聚会各自结算，并逐步揭开叔叔冒用昭源名义、组织亲友参与虚假项目的真相。身份公开后，她妥善退还款项、安排分期偿还。陈国栋学会拒绝，陈国梁放下虚荣，家族重新认识本分与担当的价值。</x:v>
+      </x:c>
+      <x:c r="I94" s="10" t="str">
+        <x:v>58集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「屿风漫剧」多次产出上榜剧</x:v>
+      </x:c>
+      <x:c r="J94" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B95" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C95" s="10" t="str">
+        <x:v>回乡种田，手握灵泉养全家</x:v>
+      </x:c>
+      <x:c r="D95" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E95" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F95" s="10" t="str">
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="G95" s="10" t="str">
+        <x:v>星屿漫剧场</x:v>
+      </x:c>
+      <x:c r="H95" s="10" t="str">
+        <x:v>家破、失业、母亲癌症晚期——安南暖以为，回到团山村老家，只是陪家人熬过人生最黑的一段日子。可谁也没想到，一滴鲜血唤醒了床头那盆沉睡多年的枯木，从此，悄然改变了整个安家老宅的命运。破败的院子长出满园生机，病重的母亲重燃希望，沉寂多年的山村，也在她手中一点点苏醒。可灵泉带来的，从来不只是馈赠。秘密、因果、病痛、欲望，接踵而至。安南暖原本只想守住一个家，却一步步把老家打造成了人人向往的桃花源。</x:v>
+      </x:c>
+      <x:c r="I95" s="10" t="str">
+        <x:v>96集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；发布账号「星屿漫剧场」多次产出上榜剧</x:v>
+      </x:c>
+      <x:c r="J95" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B96" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C96" s="10" t="str">
+        <x:v>人到中年我逆袭成百草圣手</x:v>
+      </x:c>
+      <x:c r="D96" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E96" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F96" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G96" s="10" t="str">
+        <x:v>极剧-热血剧场</x:v>
+      </x:c>
+      <x:c r="H96" s="10" t="str">
+        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
+      </x:c>
+      <x:c r="I96" s="10" t="str">
+        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「极剧-热血剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J96" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B97" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C97" s="10" t="str">
+        <x:v>十灵根短命鬼？我手搓废丹成仙第九季</x:v>
+      </x:c>
+      <x:c r="D97" s="11" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E97" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F97" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G97" s="10" t="str">
+        <x:v>点云动漫剧场</x:v>
+      </x:c>
+      <x:c r="H97" s="10" t="str">
+        <x:v>他叫叶星辰，开局只剩一个人。别人靠灵根，他靠一口破鼎。废丹炼成宝丹，废矿炼出灵脉，垃圾残卷自己补全成绝世神功。所有人都笑他活不过三集，他却把死局炼成大道。为追查长辈遗案，他被踩进泥里，几乎身死道消。别人靠天赋，他靠压榨自己，从绝境榨出生机，废墟炼出神通。宿命拦路，一鼎砸碎。必死之局，炼成通天。那口鼎还在震，他骨头里钉着一个谜。看他如何用一口气，掀翻整个天下。</x:v>
+      </x:c>
+      <x:c r="I97" s="10" t="str">
+        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「点云动漫剧场」</x:v>
+      </x:c>
+      <x:c r="J97" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B98" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C98" s="10" t="str">
+        <x:v>御兽大陆：我的猫狗是神兽第一季</x:v>
+      </x:c>
+      <x:c r="D98" s="11" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E98" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F98" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G98" s="10" t="str">
+        <x:v>文心动漫</x:v>
+      </x:c>
+      <x:c r="H98" s="10" t="str">
+        <x:v>铲屎官林霜本和自己的一猫一狗和和美美，却意外穿越御兽大陆，成为一个废材御兽师，但没人想到，她的宠物居然都穿成了上古神兽。林霜带着自己的一猫一狗，混迹宗门，众人惊异于林霜的实力，也在林霜的带领下，领悟了御兽师和兽宠之间深厚的羁绊，最终，林霜带领宗门，抵御黑暗，一切尘埃落定，带着自己的一猫一狗，在御兽大陆有了属于自己的天地。</x:v>
+      </x:c>
+      <x:c r="I98" s="10" t="str">
+        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文心动漫」</x:v>
+      </x:c>
+      <x:c r="J98" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C99" s="10" t="str">
+        <x:v>微光知遇，包子铺的逆袭</x:v>
+      </x:c>
+      <x:c r="D99" s="11" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E99" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F99" s="10" t="str">
+        <x:v>美食治愈 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G99" s="10" t="str">
+        <x:v>潮汐互娱-爽剧社</x:v>
+      </x:c>
+      <x:c r="H99" s="10" t="str">
+        <x:v>十年前大雪天，落难的林夜得到苏晴赠予的热包子，心怀感恩。多年后事业有成的林夜找到饱受亲戚欺压、生活困顿的苏晴，隐瞒身份以合伙人身份帮她重振苏记包子铺。二人携手应对经营路上的重重阻碍，，守住食品本心，把传统包子手艺做成全国连锁品牌，妹妹苏念也实现艺术理想。</x:v>
+      </x:c>
+      <x:c r="I99" s="10" t="str">
+        <x:v>94集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 逆袭打脸）；发布账号「潮汐互娱-爽剧社」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J99" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="11" t="n">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="B100" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C100" s="10" t="str">
+        <x:v>我在工地当瓦工，反手掀了采购黑幕</x:v>
+      </x:c>
+      <x:c r="D100" s="11" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E100" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F100" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G100" s="10" t="str">
+        <x:v>云端漫剧场</x:v>
+      </x:c>
+      <x:c r="H100" s="10" t="str">
+        <x:v>瓦工出身的王大力深耕工程材料领域，不慕私利，坚守质量底线。面对职场倾轧、对手伪造证据、材料贪腐圈套，他依托完整证据链揭穿阴谋，完善采购验收制度。摒弃人情救火模式，建立权责清晰的工程管理体系，守护项目安全，维护从业者正当权益，诠释基建从业者的责任与担当。</x:v>
+      </x:c>
+      <x:c r="I100" s="10" t="str">
+        <x:v>88集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「云端漫剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J100" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B101" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C101" s="10" t="str">
+        <x:v>最后一个剑仙第二季</x:v>
+      </x:c>
+      <x:c r="D101" s="11" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E101" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F101" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G101" s="10" t="str">
+        <x:v>好个秋剧场</x:v>
+      </x:c>
+      <x:c r="H101" s="10" t="str">
+        <x:v>坦尔文明主力舰队大举入侵蓝星复仇。陈帅先以莲藕分身迎战陨灭，随即夺舍外星躯体的本尊现身，硬闯太阳核心拆解戴森球，覆灭敌舰。坦尔首领赫炎引来破军文明血狼佣兵团，陈帅不敌之际召请二郎神显圣，一枪覆灭破军文明。经此一役蓝星威震银河，灵汐女帝登门邀约陈帅代表灵汐文明，参加千年一度的银河盛会。</x:v>
+      </x:c>
+      <x:c r="I101" s="10" t="str">
+        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「好个秋剧场」</x:v>
+      </x:c>
+      <x:c r="J101" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B102" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C102" s="10" t="str">
+        <x:v>F级屠夫，我刀刀暴击斩神</x:v>
+      </x:c>
+      <x:c r="D102" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E102" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F102" s="10" t="str">
+        <x:v>婚姻情感 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G102" s="10" t="str">
+        <x:v>寒冰剧场</x:v>
+      </x:c>
+      <x:c r="H102" s="10" t="str">
+        <x:v>当整个世界都依靠转职决定未来，作为优等生的我，却觉醒最低阶的F级屠夫。流言与质疑扑面而来，唯有苏婉晴坚定站在我的身旁。意外解锁暴击天赋，让我拥有突破常规的力量。我既要守护相依为命的妹妹，又要应付各方势力对自身特殊血脉的窥探。穿梭各大危险秘境，寻找上古灵药，在重重危机之下，探寻命运埋藏的真相。</x:v>
+      </x:c>
+      <x:c r="I102" s="10" t="str">
+        <x:v>51集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；发布账号「寒冰剧场」</x:v>
+      </x:c>
+      <x:c r="J102" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B103" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C103" s="10" t="str">
+        <x:v>三年，我不装了</x:v>
+      </x:c>
+      <x:c r="D103" s="11" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E103" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F103" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G103" s="10" t="str">
+        <x:v>布噜布噜剧场</x:v>
+      </x:c>
+      <x:c r="H103" s="10" t="str">
+        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+      </x:c>
+      <x:c r="I103" s="10" t="str">
+        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「布噜布噜剧场」</x:v>
+      </x:c>
+      <x:c r="J103" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B104" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C104" s="10" t="str">
+        <x:v>下山，从一纸婚约开始</x:v>
+      </x:c>
+      <x:c r="D104" s="11" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E104" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F104" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G104" s="10" t="str">
+        <x:v>洛白剧场</x:v>
+      </x:c>
+      <x:c r="H104" s="10" t="str">
+        <x:v>鬼门传人陆凡受师娘逼迫下山，需找到天凤体女子成婚化解自身劫数。他在酒吧偶遇婚约对象苏若涵，救下遭人下药的她。陆凡前往苏家打算退婚，可苏若涵为抗拒家族安排的联姻，执意和陆凡领结婚证假结婚。苏若涵带陆凡去见另一位天凤体秦怡，两女为陆凡展开竞争。恰逢秦老爷子病危，一众名医束手无策，陆凡施展失传的鬼门十三针将其救活，展露高超医术。秦怡对陆凡心生好感，苏若涵也渐渐对陆凡动了真情，几人之间的情感拉扯就此展开。</x:v>
+      </x:c>
+      <x:c r="I104" s="10" t="str">
+        <x:v>151集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「洛白剧场」</x:v>
+      </x:c>
+      <x:c r="J104" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B105" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C105" s="10" t="str">
+        <x:v>不寄人间半尺光</x:v>
+      </x:c>
+      <x:c r="D105" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E105" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F105" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G105" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H105" s="10" t="str">
+        <x:v>苏晚剖腹产坐月子期间，婆婆孙淑芬装病博同情，丈夫郭鹏程愚孝偏袒。苏晚因照顾假摔的婆婆导致刀口崩裂，看清真相后毅然提出离婚。在好友协助下，她搜集证据揭穿婆婆伪装，并果断结束婚姻。随后苏晚投身职场，为助爱人傅时衍化解公司危机，不惜抵押资产、签署苛刻合同筹措资金，最终在董事会力挽狂澜，收获事业与爱情。</x:v>
+      </x:c>
+      <x:c r="I105" s="10" t="str">
+        <x:v>73集长剧集，符合起量主力区间；题材待验证；发布账号「幻境大剧场」多次产出上榜剧</x:v>
+      </x:c>
+      <x:c r="J105" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B106" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C106" s="10" t="str">
+        <x:v>九零绝境潮汐系统护我</x:v>
+      </x:c>
+      <x:c r="D106" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E106" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F106" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G106" s="10" t="str">
+        <x:v>杨桃剧院</x:v>
+      </x:c>
+      <x:c r="H106" s="10" t="str">
+        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+      </x:c>
+      <x:c r="I106" s="10" t="str">
+        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「杨桃剧院」</x:v>
+      </x:c>
+      <x:c r="J106" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B107" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C107" s="10" t="str">
+        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
+      </x:c>
+      <x:c r="D107" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E107" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F107" s="10" t="str">
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G107" s="10" t="str">
+        <x:v>AI便利店</x:v>
+      </x:c>
+      <x:c r="H107" s="10" t="str">
+        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
+      </x:c>
+      <x:c r="I107" s="10" t="str">
+        <x:v>96集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「AI便利店」</x:v>
+      </x:c>
+      <x:c r="J107" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B108" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C108" s="10" t="str">
+        <x:v>予你情深，岁岁相守</x:v>
+      </x:c>
+      <x:c r="D108" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E108" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F108" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G108" s="10" t="str">
+        <x:v>啾啾说漫</x:v>
+      </x:c>
+      <x:c r="H108" s="10" t="str">
+        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+      </x:c>
+      <x:c r="I108" s="10" t="str">
+        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「啾啾说漫」</x:v>
+      </x:c>
+      <x:c r="J108" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B109" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C109" s="10" t="str">
+        <x:v>二十八块麻辣烫，相亲男逼我领证</x:v>
+      </x:c>
+      <x:c r="D109" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E109" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F109" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G109" s="10" t="str">
+        <x:v>壹琚影视</x:v>
+      </x:c>
+      <x:c r="H109" s="10" t="str">
+        <x:v>单亲姐姐林小圆相亲时被抠门相亲男王浩以二十八块麻辣烫为饵逼婚，王浩携母姐堵门索要钱财房产，林小圆冷静周旋，戳穿王浩临时工身份谎言，面对辱骂报警维权，最终在民警与邻居帮助下逼退男方，守护了弟弟与自己的尊严。</x:v>
+      </x:c>
+      <x:c r="I109" s="10" t="str">
+        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「壹琚影视」</x:v>
+      </x:c>
+      <x:c r="J109" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B110" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C110" s="10" t="str">
+        <x:v>五十岁扮穷相亲，我试出了真心</x:v>
+      </x:c>
+      <x:c r="D110" s="11" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E110" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F110" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G110" s="10" t="str">
+        <x:v>不惧剧场</x:v>
+      </x:c>
+      <x:c r="H110" s="10" t="str">
+        <x:v>尝尽冷暖的陈牧远，为寻一份不掺杂质的真心，选择以平凡身份踏入烟火人间。风风火火的餐馆老板李珺月，以为他只是个潦倒大叔，却用她最大的真诚与善意，将“无家可归”的他热情收留。一个守护秘密，一个守护温暖，两个在尘世中各自坚韧的灵魂，在寻常日子的炊烟与暖阳里，找到了最安心的依靠。当一切真相大白，他们才明白，这世间最奢侈的幸福，从来不是财富的堆砌，而是抛开所有身份标签后，依然愿意为彼此撑伞、相守一生的真心。</x:v>
+      </x:c>
+      <x:c r="I110" s="10" t="str">
+        <x:v>99集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「不惧剧场」</x:v>
+      </x:c>
+      <x:c r="J110" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B111" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C111" s="10" t="str">
+        <x:v>京航婚事：战爷他超护短</x:v>
+      </x:c>
+      <x:c r="D111" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E111" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F111" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>漫剧时代</x:v>
+      </x:c>
+      <x:c r="H111" s="10" t="str">
+        <x:v>沈家突遭变故，姐妹为保家业卷入战家联姻。沈昭昭阴差阳错与“叔叔”战北渊结下隐秘婚约，沈清瓷则嫁与浪荡二少战司航。面对家族猜忌、职场倾轧与旧情纠葛，昭昭以机敏与武力护姐闯关，清瓷以魄力执掌航运。战北渊隐忍深情，暗藏“千浔”身份；昭昭步步为营，在危机中揭开幕后黑手，姐妹携手于豪门漩涡中逆风成长，守护彼此与家族。</x:v>
+      </x:c>
+      <x:c r="I111" s="10" t="str">
+        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「漫剧时代」</x:v>
+      </x:c>
+      <x:c r="J111" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B112" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C112" s="10" t="str">
+        <x:v>仙界老祖非要当我哥</x:v>
+      </x:c>
+      <x:c r="D112" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E112" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F112" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G112" s="10" t="str">
+        <x:v>青青漫剧</x:v>
+      </x:c>
+      <x:c r="H112" s="10" t="str">
+        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+      </x:c>
+      <x:c r="I112" s="10" t="str">
+        <x:v>61集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；发布账号「青青漫剧」</x:v>
+      </x:c>
+      <x:c r="J112" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B113" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C113" s="10" t="str">
+        <x:v>保姆的亲情陷阱</x:v>
+      </x:c>
+      <x:c r="D113" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E113" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F113" s="10" t="str">
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G113" s="10" t="str">
+        <x:v>鸡腿剧场</x:v>
+      </x:c>
+      <x:c r="H113" s="10" t="str">
+        <x:v>女总裁林夏夏因工作忙碌，为残疾父亲林强聘请了保姆王小梅，然而一次临时回家取文件，让她在无意中听见王小梅正在哄父亲买六千块的假药，还劝说父亲瞒着自己，林夏夏当即决定辞退王小梅。但由于父亲长期孤寂中得到王小梅的陪伴，反而对女儿恶语相向，坚称王小梅才是真心对他好的人</x:v>
+      </x:c>
+      <x:c r="I113" s="10" t="str">
+        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 婚姻情感）；发布账号「鸡腿剧场」</x:v>
+      </x:c>
+      <x:c r="J113" s="11" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6434,8 +7301,9 @@
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="70" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="50" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="70" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -6461,9 +7329,12 @@
         <x:v>发布账号</x:v>
       </x:c>
       <x:c r="H1" t="str">
+        <x:v>简介</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
         <x:v>推荐依据</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="J1" t="str">
         <x:v>综合评分</x:v>
       </x:c>
     </x:row>
@@ -6489,10 +7360,11 @@
       <x:c r="G2" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="H2" s="10" t="str"/>
+      <x:c r="I2" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I2" s="11" t="n">
+      <x:c r="J2" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -6518,10 +7390,11 @@
       <x:c r="G3" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H3" s="10" t="str">
+      <x:c r="H3" s="10" t="str"/>
+      <x:c r="I3" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；84集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="n">
+      <x:c r="J3" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -6547,10 +7420,11 @@
       <x:c r="G4" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H4" s="10" t="str">
+      <x:c r="H4" s="10" t="str"/>
+      <x:c r="I4" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="n">
+      <x:c r="J4" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -6576,10 +7450,11 @@
       <x:c r="G5" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="str">
+      <x:c r="H5" s="10" t="str"/>
+      <x:c r="I5" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="n">
+      <x:c r="J5" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6605,10 +7480,11 @@
       <x:c r="G6" s="10" t="str">
         <x:v>西瑶短剧</x:v>
       </x:c>
-      <x:c r="H6" s="10" t="str">
+      <x:c r="H6" s="10" t="str"/>
+      <x:c r="I6" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「西瑶短剧」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="n">
+      <x:c r="J6" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6634,10 +7510,11 @@
       <x:c r="G7" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="str">
+      <x:c r="H7" s="10" t="str"/>
+      <x:c r="I7" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="n">
+      <x:c r="J7" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6663,10 +7540,11 @@
       <x:c r="G8" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H8" s="10" t="str">
+      <x:c r="H8" s="10" t="str"/>
+      <x:c r="I8" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I8" s="11" t="n">
+      <x:c r="J8" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6692,10 +7570,11 @@
       <x:c r="G9" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H9" s="10" t="str">
+      <x:c r="H9" s="10" t="str"/>
+      <x:c r="I9" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6721,10 +7600,11 @@
       <x:c r="G10" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H10" s="10" t="str">
+      <x:c r="H10" s="10" t="str"/>
+      <x:c r="I10" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="n">
+      <x:c r="J10" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6750,10 +7630,11 @@
       <x:c r="G11" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H11" s="10" t="str">
+      <x:c r="H11" s="10" t="str"/>
+      <x:c r="I11" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I11" s="11" t="n">
+      <x:c r="J11" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6779,10 +7660,11 @@
       <x:c r="G12" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H12" s="10" t="str">
+      <x:c r="H12" s="10" t="str"/>
+      <x:c r="I12" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；68集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I12" s="11" t="n">
+      <x:c r="J12" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6808,10 +7690,11 @@
       <x:c r="G13" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H13" s="10" t="str">
+      <x:c r="H13" s="10" t="str"/>
+      <x:c r="I13" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="n">
+      <x:c r="J13" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6837,10 +7720,11 @@
       <x:c r="G14" s="10" t="str">
         <x:v>丽娟影视</x:v>
       </x:c>
-      <x:c r="H14" s="10" t="str">
+      <x:c r="H14" s="10" t="str"/>
+      <x:c r="I14" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；100集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="n">
+      <x:c r="J14" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6866,10 +7750,11 @@
       <x:c r="G15" s="10" t="str">
         <x:v>鲸喜漫剧🐳</x:v>
       </x:c>
-      <x:c r="H15" s="10" t="str">
+      <x:c r="H15" s="10" t="str"/>
+      <x:c r="I15" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="n">
+      <x:c r="J15" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6895,10 +7780,11 @@
       <x:c r="G16" s="10" t="str">
         <x:v>朝霞看剧</x:v>
       </x:c>
-      <x:c r="H16" s="10" t="str">
+      <x:c r="H16" s="10" t="str"/>
+      <x:c r="I16" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；118集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="n">
+      <x:c r="J16" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6924,10 +7810,11 @@
       <x:c r="G17" s="10" t="str">
         <x:v>上官格格</x:v>
       </x:c>
-      <x:c r="H17" s="10" t="str">
+      <x:c r="H17" s="10" t="str"/>
+      <x:c r="I17" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；161集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I17" s="11" t="n">
+      <x:c r="J17" s="11" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -6953,10 +7840,11 @@
       <x:c r="G18" s="10" t="str">
         <x:v>龙小五剧场</x:v>
       </x:c>
-      <x:c r="H18" s="10" t="str">
+      <x:c r="H18" s="10" t="str"/>
+      <x:c r="I18" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；74集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I18" s="11" t="n">
+      <x:c r="J18" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -6982,10 +7870,11 @@
       <x:c r="G19" s="10" t="str">
         <x:v>骏乐夜航船AIGC剧场</x:v>
       </x:c>
-      <x:c r="H19" s="10" t="str">
+      <x:c r="H19" s="10" t="str"/>
+      <x:c r="I19" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「骏乐夜航船AIGC剧场」</x:v>
       </x:c>
-      <x:c r="I19" s="11" t="n">
+      <x:c r="J19" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7011,10 +7900,11 @@
       <x:c r="G20" s="10" t="str">
         <x:v>排尚漫屋</x:v>
       </x:c>
-      <x:c r="H20" s="10" t="str">
+      <x:c r="H20" s="10" t="str"/>
+      <x:c r="I20" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I20" s="11" t="n">
+      <x:c r="J20" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7040,10 +7930,11 @@
       <x:c r="G21" s="10" t="str">
         <x:v>云腾剧场</x:v>
       </x:c>
-      <x:c r="H21" s="10" t="str">
+      <x:c r="H21" s="10" t="str"/>
+      <x:c r="I21" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；95集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I21" s="11" t="n">
+      <x:c r="J21" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7069,10 +7960,11 @@
       <x:c r="G22" s="10" t="str">
         <x:v>西子是个演员</x:v>
       </x:c>
-      <x:c r="H22" s="10" t="str">
+      <x:c r="H22" s="10" t="str"/>
+      <x:c r="I22" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧 / 古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I22" s="11" t="n">
+      <x:c r="J22" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7098,10 +7990,11 @@
       <x:c r="G23" s="10" t="str">
         <x:v>澜溪剧场</x:v>
       </x:c>
-      <x:c r="H23" s="10" t="str">
+      <x:c r="H23" s="10" t="str"/>
+      <x:c r="I23" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I23" s="11" t="n">
+      <x:c r="J23" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7127,10 +8020,11 @@
       <x:c r="G24" s="10" t="str">
         <x:v>文心动漫</x:v>
       </x:c>
-      <x:c r="H24" s="10" t="str">
+      <x:c r="H24" s="10" t="str"/>
+      <x:c r="I24" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I24" s="11" t="n">
+      <x:c r="J24" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7156,10 +8050,11 @@
       <x:c r="G25" s="10" t="str">
         <x:v>彩云动画</x:v>
       </x:c>
-      <x:c r="H25" s="10" t="str">
+      <x:c r="H25" s="10" t="str"/>
+      <x:c r="I25" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；117集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「彩云动画」</x:v>
       </x:c>
-      <x:c r="I25" s="11" t="n">
+      <x:c r="J25" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7185,10 +8080,11 @@
       <x:c r="G26" s="10" t="str">
         <x:v>灯下漫剧</x:v>
       </x:c>
-      <x:c r="H26" s="10" t="str">
+      <x:c r="H26" s="10" t="str"/>
+      <x:c r="I26" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；82集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 战神异能）；发布账号「灯下漫剧」</x:v>
       </x:c>
-      <x:c r="I26" s="11" t="n">
+      <x:c r="J26" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7214,10 +8110,11 @@
       <x:c r="G27" s="10" t="str">
         <x:v>优文疯漫</x:v>
       </x:c>
-      <x:c r="H27" s="10" t="str">
+      <x:c r="H27" s="10" t="str"/>
+      <x:c r="I27" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「优文疯漫」</x:v>
       </x:c>
-      <x:c r="I27" s="11" t="n">
+      <x:c r="J27" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7243,10 +8140,11 @@
       <x:c r="G28" s="10" t="str">
         <x:v>智帧剧场</x:v>
       </x:c>
-      <x:c r="H28" s="10" t="str">
+      <x:c r="H28" s="10" t="str"/>
+      <x:c r="I28" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I28" s="11" t="n">
+      <x:c r="J28" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7272,10 +8170,11 @@
       <x:c r="G29" s="10" t="str">
         <x:v>灵漫好剧</x:v>
       </x:c>
-      <x:c r="H29" s="10" t="str">
+      <x:c r="H29" s="10" t="str"/>
+      <x:c r="I29" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I29" s="11" t="n">
+      <x:c r="J29" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7301,10 +8200,11 @@
       <x:c r="G30" s="10" t="str">
         <x:v>灵漫剧场</x:v>
       </x:c>
-      <x:c r="H30" s="10" t="str">
+      <x:c r="H30" s="10" t="str"/>
+      <x:c r="I30" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I30" s="11" t="n">
+      <x:c r="J30" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7330,10 +8230,11 @@
       <x:c r="G31" s="10" t="str">
         <x:v>梦启剧场</x:v>
       </x:c>
-      <x:c r="H31" s="10" t="str">
+      <x:c r="H31" s="10" t="str"/>
+      <x:c r="I31" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「梦启剧场」</x:v>
       </x:c>
-      <x:c r="I31" s="11" t="n">
+      <x:c r="J31" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7359,10 +8260,11 @@
       <x:c r="G32" s="10" t="str">
         <x:v>云间漫剧-丸子</x:v>
       </x:c>
-      <x:c r="H32" s="10" t="str">
+      <x:c r="H32" s="10" t="str"/>
+      <x:c r="I32" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；121集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I32" s="11" t="n">
+      <x:c r="J32" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7388,10 +8290,11 @@
       <x:c r="G33" s="10" t="str">
         <x:v>星梦好剧</x:v>
       </x:c>
-      <x:c r="H33" s="10" t="str">
+      <x:c r="H33" s="10" t="str"/>
+      <x:c r="I33" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；发布账号「星梦好剧」</x:v>
       </x:c>
-      <x:c r="I33" s="11" t="n">
+      <x:c r="J33" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7417,10 +8320,11 @@
       <x:c r="G34" s="10" t="str">
         <x:v>陈柯</x:v>
       </x:c>
-      <x:c r="H34" s="10" t="str">
+      <x:c r="H34" s="10" t="str"/>
+      <x:c r="I34" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；200集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I34" s="11" t="n">
+      <x:c r="J34" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7446,10 +8350,11 @@
       <x:c r="G35" s="10" t="str">
         <x:v>九鲤动漫</x:v>
       </x:c>
-      <x:c r="H35" s="10" t="str">
+      <x:c r="H35" s="10" t="str"/>
+      <x:c r="I35" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「九鲤动漫」</x:v>
       </x:c>
-      <x:c r="I35" s="11" t="n">
+      <x:c r="J35" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7475,10 +8380,11 @@
       <x:c r="G36" s="10" t="str">
         <x:v>浮绘剧场</x:v>
       </x:c>
-      <x:c r="H36" s="10" t="str">
+      <x:c r="H36" s="10" t="str"/>
+      <x:c r="I36" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；120集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I36" s="11" t="n">
+      <x:c r="J36" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7504,10 +8410,11 @@
       <x:c r="G37" s="10" t="str">
         <x:v>幻境大剧场</x:v>
       </x:c>
-      <x:c r="H37" s="10" t="str">
+      <x:c r="H37" s="10" t="str"/>
+      <x:c r="I37" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「幻境大剧场」曾产出榜单常客</x:v>
       </x:c>
-      <x:c r="I37" s="11" t="n">
+      <x:c r="J37" s="11" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -7533,10 +8440,11 @@
       <x:c r="G38" s="10" t="str">
         <x:v>漫文</x:v>
       </x:c>
-      <x:c r="H38" s="10" t="str">
+      <x:c r="H38" s="10" t="str"/>
+      <x:c r="I38" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；79集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I38" s="11" t="n">
+      <x:c r="J38" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7562,10 +8470,11 @@
       <x:c r="G39" s="10" t="str">
         <x:v>闪闪动漫社</x:v>
       </x:c>
-      <x:c r="H39" s="10" t="str">
+      <x:c r="H39" s="10" t="str"/>
+      <x:c r="I39" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「闪闪动漫社」</x:v>
       </x:c>
-      <x:c r="I39" s="11" t="n">
+      <x:c r="J39" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7591,10 +8500,11 @@
       <x:c r="G40" s="10" t="str">
         <x:v>卿读剧场</x:v>
       </x:c>
-      <x:c r="H40" s="10" t="str">
+      <x:c r="H40" s="10" t="str"/>
+      <x:c r="I40" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「卿读剧场」</x:v>
       </x:c>
-      <x:c r="I40" s="11" t="n">
+      <x:c r="J40" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7620,10 +8530,11 @@
       <x:c r="G41" s="10" t="str">
         <x:v>次元佳思剧场</x:v>
       </x:c>
-      <x:c r="H41" s="10" t="str">
+      <x:c r="H41" s="10" t="str"/>
+      <x:c r="I41" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 逆袭打脸）；发布账号「次元佳思剧场」</x:v>
       </x:c>
-      <x:c r="I41" s="11" t="n">
+      <x:c r="J41" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7649,10 +8560,11 @@
       <x:c r="G42" s="10" t="str">
         <x:v>青禾短剧</x:v>
       </x:c>
-      <x:c r="H42" s="10" t="str">
+      <x:c r="H42" s="10" t="str"/>
+      <x:c r="I42" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；发布账号「青禾短剧」</x:v>
       </x:c>
-      <x:c r="I42" s="11" t="n">
+      <x:c r="J42" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7678,10 +8590,11 @@
       <x:c r="G43" s="10" t="str">
         <x:v>新美漫剧场</x:v>
       </x:c>
-      <x:c r="H43" s="10" t="str">
+      <x:c r="H43" s="10" t="str"/>
+      <x:c r="I43" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；78集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能）；发布账号「新美漫剧场」</x:v>
       </x:c>
-      <x:c r="I43" s="11" t="n">
+      <x:c r="J43" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7707,10 +8620,11 @@
       <x:c r="G44" s="10" t="str">
         <x:v>凛冬短剧</x:v>
       </x:c>
-      <x:c r="H44" s="10" t="str">
+      <x:c r="H44" s="10" t="str"/>
+      <x:c r="I44" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸）；发布账号「凛冬短剧」</x:v>
       </x:c>
-      <x:c r="I44" s="11" t="n">
+      <x:c r="J44" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7736,10 +8650,11 @@
       <x:c r="G45" s="10" t="str">
         <x:v>红豆剧场</x:v>
       </x:c>
-      <x:c r="H45" s="10" t="str">
+      <x:c r="H45" s="10" t="str"/>
+      <x:c r="I45" s="10" t="str">
         <x:v>经典3D制作，与主流爆款画风一致；80集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「红豆剧场」</x:v>
       </x:c>
-      <x:c r="I45" s="11" t="n">
+      <x:c r="J45" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7765,10 +8680,11 @@
       <x:c r="G46" s="10" t="str">
         <x:v>次元心动剧场</x:v>
       </x:c>
-      <x:c r="H46" s="10" t="str">
+      <x:c r="H46" s="10" t="str"/>
+      <x:c r="I46" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；55集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；发布账号「次元心动剧场」</x:v>
       </x:c>
-      <x:c r="I46" s="11" t="n">
+      <x:c r="J46" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7794,10 +8710,11 @@
       <x:c r="G47" s="10" t="str">
         <x:v>阳光微剧</x:v>
       </x:c>
-      <x:c r="H47" s="10" t="str">
+      <x:c r="H47" s="10" t="str"/>
+      <x:c r="I47" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材待验证；发布账号「阳光微剧」</x:v>
       </x:c>
-      <x:c r="I47" s="11" t="n">
+      <x:c r="J47" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -7823,10 +8740,11 @@
       <x:c r="G48" s="10" t="str">
         <x:v>漫恋小剧场</x:v>
       </x:c>
-      <x:c r="H48" s="10" t="str">
+      <x:c r="H48" s="10" t="str"/>
+      <x:c r="I48" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；45集，中等长度；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「漫恋小剧场」</x:v>
       </x:c>
-      <x:c r="I48" s="11" t="n">
+      <x:c r="J48" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -7852,10 +8770,11 @@
       <x:c r="G49" s="10" t="str">
         <x:v>漫语剧场</x:v>
       </x:c>
-      <x:c r="H49" s="10" t="str">
+      <x:c r="H49" s="10" t="str"/>
+      <x:c r="I49" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；46集，中等长度；题材契合爆款主线（家庭伦理）；发布账号「漫语剧场」</x:v>
       </x:c>
-      <x:c r="I49" s="11" t="n">
+      <x:c r="J49" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -7881,10 +8800,11 @@
       <x:c r="G50" s="10" t="str">
         <x:v>漫文传媒</x:v>
       </x:c>
-      <x:c r="H50" s="10" t="str">
+      <x:c r="H50" s="10" t="str"/>
+      <x:c r="I50" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；69集长剧集，符合起量主力区间；题材待验证；续季/系列续作，有前作热度背书</x:v>
       </x:c>
-      <x:c r="I50" s="11" t="n">
+      <x:c r="J50" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -7910,10 +8830,11 @@
       <x:c r="G51" s="10" t="str">
         <x:v>月光短剧</x:v>
       </x:c>
-      <x:c r="H51" s="10" t="str">
+      <x:c r="H51" s="10" t="str"/>
+      <x:c r="I51" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材待验证；发布账号「月光短剧」</x:v>
       </x:c>
-      <x:c r="I51" s="11" t="n">
+      <x:c r="J51" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -7939,10 +8860,11 @@
       <x:c r="G52" s="10" t="str">
         <x:v>凛冬短剧</x:v>
       </x:c>
-      <x:c r="H52" s="10" t="str">
+      <x:c r="H52" s="10" t="str"/>
+      <x:c r="I52" s="10" t="str">
         <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材待验证；发布账号「凛冬短剧」</x:v>
       </x:c>
-      <x:c r="I52" s="11" t="n">
+      <x:c r="J52" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -7968,10 +8890,11 @@
       <x:c r="G53" s="10" t="str">
         <x:v>恐龙粑粑小百科</x:v>
       </x:c>
-      <x:c r="H53" s="10" t="str">
+      <x:c r="H53" s="10" t="str"/>
+      <x:c r="I53" s="10" t="str">
         <x:v>83集长剧集，符合起量主力区间；题材待验证；发布账号「恐龙粑粑小百科」</x:v>
       </x:c>
-      <x:c r="I53" s="11" t="n">
+      <x:c r="J53" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -7980,28 +8903,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B54" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>重生归来，我把爸爸捧上神坛</x:v>
+        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G54" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
-      </x:c>
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str"/>
       <x:c r="H54" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；66集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 逆袭打脸 / 战神异能）；发布账号「闪闪动漫社」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I54" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
+      </x:c>
+      <x:c r="I54" s="10" t="str">
+        <x:v>57集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J54" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -8009,28 +8933,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B55" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>1977山猎重生，我以余生偿前错第三季</x:v>
+        <x:v>重生：回到1983当富翁之路第一季</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>307</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>阿水漫画</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；307集，集数偏短/超长需关注；题材契合爆款主线（年代怀旧 / 种田囤货）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I55" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>上市公司执行总裁周于峰意外重回1983年。面对尚未改善的家庭关系、生活拮据的弟弟妹妹，以及处处充满机遇与挑战的时代环境。凭借多年积累的商业经验与判断力，周于峰从小生意做起，在坚守原则与规则的同时抓住时代机遇，一步步改善家人的生活，也重新审视婚姻与亲情。在改革浪潮中，他与身边的人共同成长，用一次次选择改变人生轨迹，走出属于自己的创业之路。</x:v>
+      </x:c>
+      <x:c r="I55" s="10" t="str">
+        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「阿水漫画」</x:v>
+      </x:c>
+      <x:c r="J55" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -8038,28 +8965,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>丈夫坑娃，我绝不认输</x:v>
+        <x:v>1970重生岁岁，不负韶华</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F56" s="10" t="str">
-        <x:v>萌宝治愈 / 婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>星文文化</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈 / 婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I56" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
+      </x:c>
+      <x:c r="I56" s="10" t="str">
+        <x:v>86集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「星文文化」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J56" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -8067,28 +8997,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B57" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>五十再嫁，裴先生马甲藏不住了</x:v>
+        <x:v>全校笑我铁匠，我反手锻剑娘</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>榴莲漫剧</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I57" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>故事讲述英雄遗孤陆渊在转职仪式上觉醒最低级生活职业“铁匠”，遭受众人嘲笑，却意外激活隐藏职业“神级器灵师”。他以锻造之力创造出拥有灵智的强大器灵，一路打造剑娘、刀灵、盾灵，凭借隐藏实力横扫秘境、打破纪录、反击天才与权贵，从被轻视的废物铁匠成长为震撼世界的顶级强者。</x:v>
+      </x:c>
+      <x:c r="I57" s="10" t="str">
+        <x:v>142集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「榴莲漫剧」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J57" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -8096,28 +9029,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>从炼气到称霸，我只靠两块灵石逆袭第四季</x:v>
+        <x:v>八十年代：铁娘子的缝纫机逆袭路</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>107</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G58" s="10" t="str">
-        <x:v>初八漫剧</x:v>
+        <x:v>漫剧场小管家</x:v>
       </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；107集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I58" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>八十年代改革开放初期，金枝丈夫去世后，一直与婆家同住，带着女儿过日子。面对婆家的偏心与冷眼，她从不低头，靠着一手裁缝好手艺，从走街串巷给人缝补做起。一针一线，把日子缝得踏实。从为人代工到盘下门面，金枝凭手中针线和不认输的劲头，挣出尊严，也闯出了属于自己的裁缝铺子与人生。</x:v>
+      </x:c>
+      <x:c r="I58" s="10" t="str">
+        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「漫剧场小管家」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J58" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -8125,28 +9061,31 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B59" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>同频心动</x:v>
+        <x:v>反派大佬成了女儿奴第一季</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>戏众生</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I59" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>为了糖果奖励，薄珠珠接下系统任务，要让薄宴州认下自己。她顺着纸箱空降薄氏集团。薄宴州十分抗拒，故意逗弄珠珠。可糖果的吸引力让薄珠珠不肯放弃，折返回来状况百出，系统疯狂报错，薄宴州看着古灵精怪的小团子满心审视。</x:v>
+      </x:c>
+      <x:c r="I59" s="10" t="str">
+        <x:v>144集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；续季/系列续作，有前作热度背书；发布账号「戏众生」</x:v>
+      </x:c>
+      <x:c r="J59" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -8154,28 +9093,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>婚礼前夜，我换了新郎</x:v>
+        <x:v>后娘逆袭</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>1649世界</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I60" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
+      </x:c>
+      <x:c r="I60" s="10" t="str">
+        <x:v>74集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「1649世界」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J60" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -8183,28 +9125,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B61" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>玻璃钻戒终结七年错爱</x:v>
+        <x:v>带着仓库回七零第一季</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>无极动画</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I61" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>1976年，沈牧野含恨重生，回到与周翠兰离婚当天。他凭穿越而来的现代仓库和前世厨艺进入钢铁厂食堂，从被刁难到凭西餐接待外宾一战成名。他先救下二姐母女，再治大姐的腿、还三姐的债，把家人一个个从苦日子里拉出来。期间，厂办秘书苏婉清一次次替他解围，两人在烟火与患难中越走越近。最后全家搬进厂区小院，枣树下，悸动暗生。</x:v>
+      </x:c>
+      <x:c r="I61" s="10" t="str">
+        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「无极动画」</x:v>
+      </x:c>
+      <x:c r="J61" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -8212,28 +9157,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B62" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>丈夫掏空家底，被我撕破骗局</x:v>
+        <x:v>异能赶海：从失业到海洋女王第二季</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>保温虾虾</x:v>
+        <x:v>每日沙雕推荐</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；54集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；发布账号「保温虾虾」</x:v>
-      </x:c>
-      <x:c r="I62" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>北漂失意的苏蕴舟回乡后，觉醒能看透水下的特殊能力，靠收获珍贵海产快速积累财富，买下独栋别墅，改善全家生活。她救下遭遇意外的少年陆星辰，结识商界的霍铮，二人从试探发展为合作伙伴。苏蕴舟从容应对前男友、同学带来的人际纠葛。家里日子蒸蒸日上，父亲开办海产加工坊。苏蕴舟将一批珍珠交由霍氏处理，收到拍卖会邀约，在与大海相伴的日子里，完成自我成长与人生蜕变。</x:v>
+      </x:c>
+      <x:c r="I62" s="10" t="str">
+        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+      </x:c>
+      <x:c r="J62" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -8241,28 +9189,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B63" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>下午的早餐店第五季</x:v>
+        <x:v>彩运照人心，第一季</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>97</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
-        <x:v>盐系少女社</x:v>
+        <x:v>文之江影视</x:v>
       </x:c>
       <x:c r="H63" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；97集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I63" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>胡帕喜中巨额彩票，领奖当天却惨遭相恋四年的女友分手，昔日温情瞬间化为泡影。他斩断过往纠葛，毅然离职，奔赴郑州探望勤工俭学的妹妹，也因此结识了善良坚韧的梁池，两人渐生情愫。清明返乡，他冷眼看透势利亲戚的虚伪嘴脸，手握财富却选择低调行事，一心照料家人。在这冷暖交织的人情世故里，他褪去浮华，终与梁池携手，收获了一份纯粹真挚的缘分。</x:v>
+      </x:c>
+      <x:c r="I63" s="10" t="str">
+        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书；发布账号「文之江影视」</x:v>
+      </x:c>
+      <x:c r="J63" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -8270,28 +9221,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B64" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>不朽仙秦！第三季</x:v>
+        <x:v>恋上心通第一季</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>190</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
-        <x:v>虾仁白白</x:v>
+        <x:v>益阳动漫</x:v>
       </x:c>
       <x:c r="H64" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；190集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I64" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>快穿大佬叶聆刚退休就穿成恋综恶毒原配，绑定系统后惩罚竟全劈在冷漠老公谢淮舟身上，还附带感官通感！为了保命，高岭之花谢淮舟当众崩人设抢牵手、爆金币、求贴贴，全网惊呆说好的塑料夫妻呢？叶聆反骨杀疯恋综，手撕绿茶、暴揍前任、扫地出门全家奇葩。</x:v>
+      </x:c>
+      <x:c r="I64" s="10" t="str">
+        <x:v>129集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「益阳动漫」</x:v>
+      </x:c>
+      <x:c r="J64" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -8299,28 +9253,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B65" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>五十保姆觉醒，遗产见人心</x:v>
+        <x:v>收租精神小妹！第二季</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>家庭伦理 / 战神异能 / 现实反转</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
-        <x:v>剑心动漫</x:v>
+        <x:v>心悦漫剪</x:v>
       </x:c>
       <x:c r="H65" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 战神异能 / 现实反转）；发布账号「剑心动漫」</x:v>
-      </x:c>
-      <x:c r="I65" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>大厂十年，一朝被裁。林野拿着两百万补偿金回到县城，全款买了套别墅，只想安静活着。系统不让。收租万倍返还系统已激活。他盯着空荡荡的五个房间，开始琢磨怎么找租客。第一个上门的，是三个流浪到江城的精神小妹。从这天起，他的别墅再也没安静过。精神小妹、落魄富二代、跑路网红，各路奇人排着队住进来。</x:v>
+      </x:c>
+      <x:c r="I65" s="10" t="str">
+        <x:v>124集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「心悦漫剪」</x:v>
+      </x:c>
+      <x:c r="J65" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -8328,28 +9285,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>亿单提成仅百块，一顿炸鸡见人心</x:v>
+        <x:v>无心攀比，假千金重生后成团宠了</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
-        <x:v>晟樊影视</x:v>
+        <x:v>鲸跃AI剧场</x:v>
       </x:c>
       <x:c r="H66" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「晟樊影视」</x:v>
-      </x:c>
-      <x:c r="I66" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
+      </x:c>
+      <x:c r="I66" s="10" t="str">
+        <x:v>100集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「鲸跃AI剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J66" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -8357,28 +9317,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>全民御兽：神级鉴兽师第二季</x:v>
+        <x:v>死对头校花竟是我网恋女友第二季</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
-        <x:v>漫川动漫剧场</x:v>
+        <x:v>长鹿漫漫</x:v>
       </x:c>
       <x:c r="H67" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I67" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>网络里的温柔陪伴，与现实中的针锋相对形成奇妙反差。相识四年，他们一直是彼此最熟悉的网友，却从未想过对方就在身边。从最初的误会，到一次次相处中逐渐卸下防备，两人慢慢发现彼此不为人知的温柔一面。当四年网聊终于迎来奔现，他们才发现，那个一直陪伴自己的人，竟是现实中最意想不到的存在。一场甜蜜、欢乐又充满惊喜的青春恋爱，就此开始。</x:v>
+      </x:c>
+      <x:c r="I67" s="10" t="str">
+        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「长鹿漫漫」</x:v>
+      </x:c>
+      <x:c r="J67" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -8386,28 +9349,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>全蓝星都在抢的大佬是SSS级怪第一季</x:v>
+        <x:v>浴火重生，我撕碎前夫的美梦</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>竹蜻蜓剧场</x:v>
+        <x:v>云阅真人漫剧</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；59集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I68" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>家庭主妇林晚遭丈夫陈世杰与情人苏曼背叛，更被设计坠崖毁容。死里逃生后，她继承遗产、改头换面，以资本新贵身份重返陈世杰身边，步步引他暴露贪婪与罪行。最终真相大白，林晚在顾言守护下夺回属于她的一切，迎来新生。</x:v>
+      </x:c>
+      <x:c r="I68" s="10" t="str">
+        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「云阅真人漫剧」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J68" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -8415,28 +9381,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B69" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>农场萌宠！第六季</x:v>
+        <x:v>破窑洞飞出金凤凰第一季</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>种田囤货 / 婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>惜惜动漫</x:v>
+        <x:v>定边同城帮</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；67集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 婚姻情感）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I69" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>李根出身贫寒，大学时与富家女苏婉晴相恋，却在订婚宴上被当众退婚羞辱。他落魄返乡，在荒山上发现野生酸枣的商机，立志创业。从承包荒山、改土育苗，到历经暴雨毁林、父亲病倒、资金断裂等重重打击，他凭一股不服输的韧劲咬牙坚持。在贵人相助和全村人的支持下，他成功将荒山变成千亩枣园，成立合作社，带领黄土坡村脱贫致富。事业有成后，他赢得真诚爱情，拒绝资本诱惑，创办农业大学，用一生诠释了什么是坚守初心，扎根土地。</x:v>
+      </x:c>
+      <x:c r="I69" s="10" t="str">
+        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「定边同城帮」</x:v>
+      </x:c>
+      <x:c r="J69" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -8444,28 +9413,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B70" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>农门悍妻：病弱相公把我宠坏了第二季</x:v>
+        <x:v>纨绔穿越古代成就百万诗仙第一季</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>枕月漫影</x:v>
+        <x:v>咪漫剧场</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；63集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I70" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>现代纨绔魂穿贞观十年，成为军神李靖之孙李景安。开局揭皇榜医治长孙皇后，凭抄录千古诗词惊艳长安，诗会碾压对手一战封神。解锁硝石制冰、马蹄铁等黑科技搅动朝堂。一边当摆烂纨绔，一边搅动大唐风云，周旋世家权贵，邂逅多位佳人，在初唐掀起属于谪仙少年的传奇浪潮。</x:v>
+      </x:c>
+      <x:c r="I70" s="10" t="str">
+        <x:v>89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「咪漫剧场」</x:v>
+      </x:c>
+      <x:c r="J70" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -8473,28 +9445,31 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>利益照见人心</x:v>
+        <x:v>荒岛逆袭：我成了荒岛之王</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G71" s="10" t="str">
-        <x:v>天天爱看剧</x:v>
+        <x:v>庚庚</x:v>
       </x:c>
       <x:c r="H71" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；94集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「天天爱看剧」</x:v>
-      </x:c>
-      <x:c r="I71" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>一场突发的海难，让公司员工陆鸣与总裁苏清寒等同事意外流落荒野孤岛。失去现代文明的庇护，习惯了优渥生活的苏清寒等人起初难以适应，依然带有职场上的刻板偏见，试图将荒野危机简单化。然而，陆鸣凭借过硬的野外求生知识与坚韧的意志，不仅成功获取了珍贵的食物和水源，还搭建起了安全的庇护所。为了整个团队的生存，陆鸣立下“按劳分配、互帮互助”的营地新规。在陆鸣的带领下，他们战胜了荒岛危机。</x:v>
+      </x:c>
+      <x:c r="I71" s="10" t="str">
+        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「庚庚」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J71" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -8502,28 +9477,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B72" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>别追了霍总，太太想和你离婚很久了第五季</x:v>
+        <x:v>蓄意逐风：我在恋综称王称爸第二季</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>月亮与孤岛</x:v>
+        <x:v>₊⁺水蜜陶🍑剧场</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I72" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>恋综游园会浪漫开启谢弥经助理刁茂巧手妆造一袭浅碧挂脖长裙惊艳全场绿毛龟轮椅依旧是她标志性座驾。沈爅卿一见盛装的谢弥眼底藏不住温柔轻声夸赞她夺目。二人扫荡美食摊位后，前去塔罗帐篷占卜谢弥一心惦记财运，顺势追问命定之人是不是沈爅卿，沈爅卿暗藏心事化身谜语人二人写下心愿纸船放入溪流，谢弥却抛下纸船直奔套圈摊位，沈爅卿含笑追赶。镜头曝光沈爅卿纸船秘密纸上赫然写着我的初恋是谢老师埋藏已久的心意悄然浮出水面。</x:v>
+      </x:c>
+      <x:c r="I72" s="10" t="str">
+        <x:v>119集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「₊⁺水蜜陶🍑剧场」</x:v>
+      </x:c>
+      <x:c r="J72" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -8531,28 +9509,31 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B73" s="11" t="str">
-        <x:v>09·02</x:v>
+        <x:v>09·03</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>剑定山河第一季</x:v>
+        <x:v>跨万界穿梭！第四季</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F73" s="10" t="str">
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>捷捷动漫馆</x:v>
+        <x:v>二三漫剧</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I73" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>大夏探索小队在冰封星球发现已灭绝的奥斯塔文明及其AI“小烛”。为获取领先百年的科技遗产，他们深入怪物巢穴夺回权限密钥，解除了AI的限制。在得知该文明因太阳被夺而毁灭后，小队决心帮助小烛延续文明火种，并带着完整的科技树返回大夏，开启了蓝星科技飞跃的新篇章。</x:v>
+      </x:c>
+      <x:c r="I73" s="10" t="str">
+        <x:v>168集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「二三漫剧」</x:v>
+      </x:c>
+      <x:c r="J73" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -8560,28 +9541,31 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B74" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C74" s="10" t="str">
-        <x:v>一张照片传遍公司群我却因此重生了</x:v>
+        <x:v>68万存款，买了一场婚姻的真相第二季</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E74" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F74" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="G74" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>权策推剧</x:v>
       </x:c>
       <x:c r="H74" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；57集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I74" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>婚礼当天，吴子妍被丈夫一家逼签陪嫁房赠予协议，当众受辱。她当场撕毁协议、取消婚礼，却在离婚后遭遇周家霸占房产、伪造授权、私吞租金的无底线算计。从崩溃屈辱中站起，她冷静收集证据、诉诸法律，一步步追回房产与尊严。最终，周家付出代价，吴子妍拿回人生主动权，更将自己的经历化作对无数女性的边界提醒——守住底线，从不丢人。</x:v>
+      </x:c>
+      <x:c r="I74" s="10" t="str">
+        <x:v>135集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；续季/系列续作，有前作热度背书；发布账号「权策推剧」</x:v>
+      </x:c>
+      <x:c r="J74" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -8589,28 +9573,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B75" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C75" s="10" t="str">
-        <x:v>一纸通知书，丈夫托我赴前程</x:v>
+        <x:v>林国强的故事，重生80年带妻女翻身第二季</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E75" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F75" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G75" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>每日沙雕推荐</x:v>
       </x:c>
       <x:c r="H75" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；64集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I75" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>林国强重生回到八零年代，开国强饭店创业起家，分家脱离原生家庭，避开前世悲剧。第二季主线事业持续扩张，处理原生家庭一堆烂摊子，妹妹遭遇家暴悲剧，兄弟姐妹各自的命运走向，拓展大棚、养鸡场、鱼塘多条产业线，同时伴随亲戚算计、婚恋风波，铺垫县城大饭庄的新事业。</x:v>
+      </x:c>
+      <x:c r="I75" s="10" t="str">
+        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+      </x:c>
+      <x:c r="J75" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -8618,28 +9605,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B76" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C76" s="10" t="str">
-        <x:v>一顿饭算清</x:v>
+        <x:v>重生觉醒，这次我不做恋爱脑第六季</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E76" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F76" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="G76" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>桃汁夭夭</x:v>
       </x:c>
       <x:c r="H76" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；83集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I76" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>重活一世，林雾终于看清自己的心，坚定走向始终默默守护她的徐京妄。她用一场精心准备的生日惊喜，陪他回望成长岁月，也许下长久相伴的承诺。此后，两人的感情愈发甜蜜坚定。面对家人的关注，林雾坦然表达心意，徐京妄也以真诚回应她的偏爱。林雾也在彼此陪伴与守护中不断成长，与他携手奔向明亮温暖的未来。</x:v>
+      </x:c>
+      <x:c r="I76" s="10" t="str">
+        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「桃汁夭夭」</x:v>
+      </x:c>
+      <x:c r="J76" s="11" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -8647,28 +9637,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B77" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C77" s="10" t="str">
-        <x:v>一顿香锅断前缘</x:v>
+        <x:v>人是诡异幼崽第二季</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E77" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F77" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="G77" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>悦禾剧场</x:v>
       </x:c>
       <x:c r="H77" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；62集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I77" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>穿越者任逸一直以为自己生活在人类社会，直到毕业觉醒，才发现联盟里根本没有人类，而自己竟是披着人皮的诡异幼崽。觉醒幻术规则后，他与陆子涵进入副本实习，在一次次规则博弈中疯狂收割情绪、提升实力。随特别收割预案启动，任逸主动伪装成人类参与者潜入“陆家小院”，借直播扩大能力收益。然而瓜田、药园规则层层升级，浓雾深处的诡异梧桐与致命限制逐渐显现，一场更危险的猎杀正式开始。</x:v>
+      </x:c>
+      <x:c r="I77" s="10" t="str">
+        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈）；续季/系列续作，有前作热度背书；发布账号「悦禾剧场」</x:v>
+      </x:c>
+      <x:c r="J77" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -8676,28 +9669,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B78" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>嫁妆被抢那天我亮明了身份</x:v>
+        <x:v>修仙归来护家人第二季</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>夏十七</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I78" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
+      </x:c>
+      <x:c r="I78" s="10" t="str">
+        <x:v>72集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「夏十七」</x:v>
+      </x:c>
+      <x:c r="J78" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -8705,28 +9701,29 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B79" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>带男友回大山继承家产</x:v>
+        <x:v>凡人仙鱼，混沌灵根逆袭仙途</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="G79" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str"/>
       <x:c r="H79" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I79" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>天玄宗杂役弟子许时安，因混沌废灵根被视为消耗资源的无底洞，只能在后山清理淤泥。意外之下，他在丹田中得到一只神秘黑鱼！神鱼吞吃废丹废符后，竟能吐出完美品阶的丹药符箓！自此，许时安从底层杂役逆袭，拜入仙子苏眠门下，习得上古剑法典籍《道剑十三》。秘境历练中，神鱼经历第三次进化，化为鲲之形态。面对仇人截杀与七魔将的血祭大阵，许时安以道剑十三破阵，祭出上古磨盘镇压万魔，一战封神，震惊整个天玄宗！</x:v>
+      </x:c>
+      <x:c r="I79" s="10" t="str">
+        <x:v>77集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J79" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -8734,28 +9731,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B80" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>末世，带着修改器重生，我无敌了2</x:v>
+        <x:v>凡人修仙开局捡到聚宝仙鼎第四季</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>机甲熊</x:v>
+        <x:v>蜗牛漫剧剧场</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；73集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I80" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>全仙宗都笑凡人许长生五行杂灵根，注定困死废丹房！许长生得云瑶仙子引仙门，却沦为最低废丹房杂役，日日遭管事压榨羞辱。山洪濒死之际，天降聚宝仙鼎，废丹炼极品、残书化顶级道藏，万物经鼎皆能升华！他暗藏底牌隐忍发育，打脸欺辱自己的杂役与管事，大比惊艳全场，一跃成为内门弟子，凭一鼎之力逆转凡人身，踏破长生大道。</x:v>
+      </x:c>
+      <x:c r="I80" s="10" t="str">
+        <x:v>158集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「蜗牛漫剧剧场」</x:v>
+      </x:c>
+      <x:c r="J80" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -8763,28 +9763,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B81" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>错写红封，终断婚约</x:v>
+        <x:v>别拿猪婆龙不当神兽第二季</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>与情箓</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；61集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「幻境大剧场」上榜次数居前</x:v>
-      </x:c>
-      <x:c r="I81" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>别拿猪婆龙不当神兽第二季来袭！渡劫失败的虞柏柏被天雷劈成了一条猪婆龙（扬子鳄），在高冷影帝家里当宠物蹭吃蹭喝蹭雪饼。影帝抱着鳄鱼形态的她殷切期盼，如果你能变成虞柏柏那样的美人该有多好啊！某一天，虞柏柏实在憋不住了，在影帝怀里现出了人形，她转头看向了高冷影帝，眼神魅惑，还满意你看到的吗？没想到，高冷影帝当场垮起了脸——变回去！</x:v>
+      </x:c>
+      <x:c r="I81" s="10" t="str">
+        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「与情箓」</x:v>
+      </x:c>
+      <x:c r="J81" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -8792,28 +9795,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B82" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>一井见人心</x:v>
+        <x:v>发配充军，战神系统宁九才镇守边关第三季</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>云间予安</x:v>
+        <x:v>灵梦剧场</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；85集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「云间予安」</x:v>
-      </x:c>
-      <x:c r="I82" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>宁川重回盛京，深知大晋皇室底蕴深厚。他借力邀月公主的夺嫡之争，接连拔除多方敌对势力，依靠特殊流水线能力快速提升自身修为。尘封数百年的宁家旧仇真相大白，宁川成功为家族洗刷冤屈，扶持妹妹宁婉儿建立宁国，登临帝位。外部危机却接连爆发，柳如烟、南海海族、葬土死灵纷纷发难。宁川不断突破境界，力克强敌，收获珍贵仙种，意外寻得离开绝灵之地的线索，一场席卷天下的大乱局徐徐拉开。</x:v>
+      </x:c>
+      <x:c r="I82" s="10" t="str">
+        <x:v>111集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+      </x:c>
+      <x:c r="J82" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -8821,28 +9827,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B83" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>一渠清水见人心</x:v>
+        <x:v>咱们你听心声我吃瓜，换嫁夫妻笑哈哈第二季</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F83" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>心痕剧场</x:v>
+        <x:v>每日沙雕速递</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「心痕剧场」</x:v>
-      </x:c>
-      <x:c r="I83" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>现代穿越者裴辞镜绑定吃瓜系统，娶了拥有读心能力的沈柠欢。裴辞镜表面咸鱼，内心疯狂吃瓜吐槽，沈柠欢看破他的心声，夫妻二人默契十足。恰逢太子发动宫变，二人携手化解危机，揪出八皇子的谋划。之后裴辞镜参加科举，高中探花，入朝任职翰林院编修。侯府内部恩怨逐渐化解，沈柠悦幡然悔悟。裴辞镜入职后接到修订水利典籍的差事，还意外发现前人疑似穿越者的线索，故事暂告一段落。</x:v>
+      </x:c>
+      <x:c r="I83" s="10" t="str">
+        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈）；续季/系列续作，有前作热度背书；发布账号「每日沙雕速递」</x:v>
+      </x:c>
+      <x:c r="J83" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -8850,28 +9859,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>七天照见人心</x:v>
+        <x:v>婚宴厅被抢，我反手告倒百亿公司</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F84" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>倩倩短剧</x:v>
+        <x:v>妙手看剧</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；51集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「倩倩短剧」</x:v>
-      </x:c>
-      <x:c r="I84" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>许知夏筹备多年的婚宴当天，场地方突然毁约，替梁书瑶腾出主舞台。未婚夫陆远舟不仅没有替她说话，反而站到梁书瑶身边，逼她识相离场。梁家仗着百亿公司撑腰，封锁证据、操控舆论，想让她带着耻辱退场。许知夏却撕下婚纱上的花，保全合同、录音与资金记录，将婚宴变成反击的起点。她解除婚约，反手起诉梁家企业，让抢走她婚礼的人，为这场精心设计的羞辱付出代价。</x:v>
+      </x:c>
+      <x:c r="I84" s="10" t="str">
+        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转）；发布账号「妙手看剧」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J84" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -8879,28 +9891,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B85" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>书院后街摆吃摊，皇帝咋也来排队第四季</x:v>
+        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>古装宫廷 / 都市职场 / 美食治愈</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>溪溪剧场</x:v>
+        <x:v>云朵邮递员</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；124集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 都市职场 / 美食治愈）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I85" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
+      </x:c>
+      <x:c r="I85" s="10" t="str">
+        <x:v>131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；续季/系列续作，有前作热度背书；发布账号「云朵邮递员」</x:v>
+      </x:c>
+      <x:c r="J85" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -8908,28 +9923,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B86" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>假面羁绊：极客先生的秘密</x:v>
+        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>北极熊短剧</x:v>
+        <x:v>平川动画</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；50集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 现实反转）；发布账号「北极熊短剧」</x:v>
-      </x:c>
-      <x:c r="I86" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
+      </x:c>
+      <x:c r="I86" s="10" t="str">
+        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 萌宝治愈 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「平川动画」</x:v>
+      </x:c>
+      <x:c r="J86" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -8937,28 +9955,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B87" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>全球魔怪复苏：沙雕少爷的逆袭封神路</x:v>
+        <x:v>小满混江湖第一季</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>浪客剧场</x:v>
+        <x:v>两把刷子剧场</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；87集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「浪客剧场」</x:v>
-      </x:c>
-      <x:c r="I87" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>底层客栈孤女姜小满为求生存，意外卷入烬月教阴谋，被迫顶替失踪多年的青梧派掌门义女林阿照，就此踏入一场蛰伏十六年的朝堂死局。在门派中她与心思深沉的大师兄沈砚舟步步周旋，又凭借儿时一张平安符，攀附腹黑的魔教教主谢无咎。随着旧案揭开，假身份之下牵扯出真公主的过往，侯府灭口、妃嫔算计、双生皇子秘闻接连浮现。市井孤女凭着狡黠与傲骨，游走于江湖朝堂，以袖中薄刃，搅动整片天下棋局。</x:v>
+      </x:c>
+      <x:c r="I87" s="10" t="str">
+        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「两把刷子剧场」</x:v>
+      </x:c>
+      <x:c r="J87" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -8966,28 +9987,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B88" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>农村兽神第五季</x:v>
+        <x:v>小邪爱空姐之欢喜对头误撞心动第二季</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>每日欢乐漫剧</x:v>
+        <x:v>天才黄小邪</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I88" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>妇科医生陈北在航班上俯身帮男孩捡东西时，不慎误碰空姐陈诗瑶，被对方误会耍流氓，还闹到了警局，但最终警方证实了他的清白。这场飞机上的意外乌龙，本以为他们再无交集，可陈诗瑶却发现新租房子的房东竟然是陈北。于是两人开始同居，欢喜冤家同住一屋，从针锋相对到渐生情愫，最终甜蜜相恋、幸福相守。</x:v>
+      </x:c>
+      <x:c r="I88" s="10" t="str">
+        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「天才黄小邪」</x:v>
+      </x:c>
+      <x:c r="J88" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -8995,28 +10019,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B89" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>匠心逆袭：我为行业立规矩</x:v>
+        <x:v>开局成废后我反手养出十万御林军</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F89" s="10" t="str">
         <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>五碗说漫</x:v>
+        <x:v>天桥热血剧场</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；75集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「五碗说漫」</x:v>
-      </x:c>
-      <x:c r="I89" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
+      </x:c>
+      <x:c r="I89" s="10" t="str">
+        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「天桥热血剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J89" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -9024,28 +10051,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>囤货逆袭大佬末世之归途</x:v>
+        <x:v>心愿昭昭，神明有应第一季</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>种田囤货 / 逆袭打脸</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>逐梦剧场</x:v>
+        <x:v>文妃儿</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；130集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 逆袭打脸）；发布账号「逐梦剧场」</x:v>
-      </x:c>
-      <x:c r="I90" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>雾禾最大的心愿，是寻一位模样俊朗、性情体贴的夫君，陪她守着小院安稳度日。于是，她跑到山中神像前认真许愿。没过多久，风离昭便来到她身边。他会洗衣做饭，会亲手添置家用，也会把她随口说过的话放在心上，只是偶尔傲娇炸毛，格外需要人哄。雾禾以为自己只是运气好，却渐渐发现，这位夫君似乎与山中的古老传说关系匪浅。一个愿望牵起一段奇缘，两个原本孤单的人，在欢笑与陪伴中学会信任，也把平凡光景过成了温暖明亮的好日子。</x:v>
+      </x:c>
+      <x:c r="I90" s="10" t="str">
+        <x:v>120集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文妃儿」</x:v>
+      </x:c>
+      <x:c r="J90" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -9053,28 +10083,31 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>地府归来的大佬她巨沙雕第一季</x:v>
+        <x:v>我的别墅通两界，摆摊的我赚了亿点点第三季</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>小奶团动画</x:v>
+        <x:v>灵梦剧场</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>经典3D制作，与主流爆款画风一致；91集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I91" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>陆沉玉穿梭现代与异界，壮大石牙部落，完善城防、推行识字与岗位竞选，部落蒸蒸日上。白头部落举兵进犯，被陆沉玉击溃，俘虏纳入劳动力，吴志也归降部落。陆沉玉组建华夏商队，携盐、陶器等物资远征参加部落大集，沿路收服孤山、青山等部族，收获煤炭、蜂蜜、香草荚等资源。抵达大集后，华夏部落凭借精良物资震慑各方势力，神殿假意示好，企图套取制盐、烧瓷技术，陆沉玉将计就计，带着暗藏阴谋的神殿随从踏上归途。</x:v>
+      </x:c>
+      <x:c r="I91" s="10" t="str">
+        <x:v>104集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+      </x:c>
+      <x:c r="J91" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -9082,28 +10115,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>太太她不装了第一季：傲娇沈总追妻3</x:v>
+        <x:v>我的渔船通龙宫第一季</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>闲人一坤</x:v>
+        <x:v>六翼动漫</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；81集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书</x:v>
-      </x:c>
-      <x:c r="I92" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
+      </x:c>
+      <x:c r="I92" s="10" t="str">
+        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「六翼动漫」</x:v>
+      </x:c>
+      <x:c r="J92" s="11" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -9111,28 +10147,671 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B93" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09·04</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>家庭主妇的逆袭：亲手送他入狱</x:v>
+        <x:v>我竟是道祖之狩猎气运之子第五季</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E93" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F93" s="10" t="str">
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="G93" s="10" t="str">
+        <x:v>玖月说漫</x:v>
+      </x:c>
+      <x:c r="H93" s="10" t="str">
+        <x:v>三千道州与神魔大陆相连，古族之主古乾立于时代潮头，带领族中强者踏入更广阔天地。一次跨界之行，让魅魔族迎来全新归宿，也让古族与各大道统的联系愈发紧密。古乾一边安置新族地、汇聚各方资源，一边放眼界域天骄盛会与更高层次的古洪荒。随着古雄彪等新一代天骄崭露锋芒，古族气运日盛，新的伙伴、机缘与广阔天地接连出现。</x:v>
+      </x:c>
+      <x:c r="I93" s="10" t="str">
+        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书；发布账号「玖月说漫」</x:v>
+      </x:c>
+      <x:c r="J93" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B94" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C94" s="10" t="str">
+        <x:v>人到中年我逆袭成百草圣手</x:v>
+      </x:c>
+      <x:c r="D94" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E94" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F94" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G94" s="10" t="str">
+        <x:v>极剧-热血剧场</x:v>
+      </x:c>
+      <x:c r="H94" s="10" t="str">
+        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
+      </x:c>
+      <x:c r="I94" s="10" t="str">
+        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「极剧-热血剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J94" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B95" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C95" s="10" t="str">
+        <x:v>十灵根短命鬼？我手搓废丹成仙第九季</x:v>
+      </x:c>
+      <x:c r="D95" s="11" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E95" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F95" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G95" s="10" t="str">
+        <x:v>点云动漫剧场</x:v>
+      </x:c>
+      <x:c r="H95" s="10" t="str">
+        <x:v>他叫叶星辰，开局只剩一个人。别人靠灵根，他靠一口破鼎。废丹炼成宝丹，废矿炼出灵脉，垃圾残卷自己补全成绝世神功。所有人都笑他活不过三集，他却把死局炼成大道。为追查长辈遗案，他被踩进泥里，几乎身死道消。别人靠天赋，他靠压榨自己，从绝境榨出生机，废墟炼出神通。宿命拦路，一鼎砸碎。必死之局，炼成通天。那口鼎还在震，他骨头里钉着一个谜。看他如何用一口气，掀翻整个天下。</x:v>
+      </x:c>
+      <x:c r="I95" s="10" t="str">
+        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「点云动漫剧场」</x:v>
+      </x:c>
+      <x:c r="J95" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B96" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C96" s="10" t="str">
+        <x:v>御兽大陆：我的猫狗是神兽第一季</x:v>
+      </x:c>
+      <x:c r="D96" s="11" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E96" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F96" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G96" s="10" t="str">
+        <x:v>文心动漫</x:v>
+      </x:c>
+      <x:c r="H96" s="10" t="str">
+        <x:v>铲屎官林霜本和自己的一猫一狗和和美美，却意外穿越御兽大陆，成为一个废材御兽师，但没人想到，她的宠物居然都穿成了上古神兽。林霜带着自己的一猫一狗，混迹宗门，众人惊异于林霜的实力，也在林霜的带领下，领悟了御兽师和兽宠之间深厚的羁绊，最终，林霜带领宗门，抵御黑暗，一切尘埃落定，带着自己的一猫一狗，在御兽大陆有了属于自己的天地。</x:v>
+      </x:c>
+      <x:c r="I96" s="10" t="str">
+        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文心动漫」</x:v>
+      </x:c>
+      <x:c r="J96" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B97" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C97" s="10" t="str">
+        <x:v>微光知遇，包子铺的逆袭</x:v>
+      </x:c>
+      <x:c r="D97" s="11" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E97" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F97" s="10" t="str">
+        <x:v>美食治愈 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G97" s="10" t="str">
+        <x:v>潮汐互娱-爽剧社</x:v>
+      </x:c>
+      <x:c r="H97" s="10" t="str">
+        <x:v>十年前大雪天，落难的林夜得到苏晴赠予的热包子，心怀感恩。多年后事业有成的林夜找到饱受亲戚欺压、生活困顿的苏晴，隐瞒身份以合伙人身份帮她重振苏记包子铺。二人携手应对经营路上的重重阻碍，，守住食品本心，把传统包子手艺做成全国连锁品牌，妹妹苏念也实现艺术理想。</x:v>
+      </x:c>
+      <x:c r="I97" s="10" t="str">
+        <x:v>94集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 逆袭打脸）；发布账号「潮汐互娱-爽剧社」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J97" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B98" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C98" s="10" t="str">
+        <x:v>我在工地当瓦工，反手掀了采购黑幕</x:v>
+      </x:c>
+      <x:c r="D98" s="11" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E98" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F98" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G98" s="10" t="str">
+        <x:v>云端漫剧场</x:v>
+      </x:c>
+      <x:c r="H98" s="10" t="str">
+        <x:v>瓦工出身的王大力深耕工程材料领域，不慕私利，坚守质量底线。面对职场倾轧、对手伪造证据、材料贪腐圈套，他依托完整证据链揭穿阴谋，完善采购验收制度。摒弃人情救火模式，建立权责清晰的工程管理体系，守护项目安全，维护从业者正当权益，诠释基建从业者的责任与担当。</x:v>
+      </x:c>
+      <x:c r="I98" s="10" t="str">
+        <x:v>88集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「云端漫剧场」；剧名冲突前置、钩子强</x:v>
+      </x:c>
+      <x:c r="J98" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B99" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C99" s="10" t="str">
+        <x:v>最后一个剑仙第二季</x:v>
+      </x:c>
+      <x:c r="D99" s="11" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E99" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F99" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G99" s="10" t="str">
+        <x:v>好个秋剧场</x:v>
+      </x:c>
+      <x:c r="H99" s="10" t="str">
+        <x:v>坦尔文明主力舰队大举入侵蓝星复仇。陈帅先以莲藕分身迎战陨灭，随即夺舍外星躯体的本尊现身，硬闯太阳核心拆解戴森球，覆灭敌舰。坦尔首领赫炎引来破军文明血狼佣兵团，陈帅不敌之际召请二郎神显圣，一枪覆灭破军文明。经此一役蓝星威震银河，灵汐女帝登门邀约陈帅代表灵汐文明，参加千年一度的银河盛会。</x:v>
+      </x:c>
+      <x:c r="I99" s="10" t="str">
+        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「好个秋剧场」</x:v>
+      </x:c>
+      <x:c r="J99" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B100" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C100" s="10" t="str">
+        <x:v>F级屠夫，我刀刀暴击斩神</x:v>
+      </x:c>
+      <x:c r="D100" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E100" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F100" s="10" t="str">
+        <x:v>婚姻情感 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G100" s="10" t="str">
+        <x:v>寒冰剧场</x:v>
+      </x:c>
+      <x:c r="H100" s="10" t="str">
+        <x:v>当整个世界都依靠转职决定未来，作为优等生的我，却觉醒最低阶的F级屠夫。流言与质疑扑面而来，唯有苏婉晴坚定站在我的身旁。意外解锁暴击天赋，让我拥有突破常规的力量。我既要守护相依为命的妹妹，又要应付各方势力对自身特殊血脉的窥探。穿梭各大危险秘境，寻找上古灵药，在重重危机之下，探寻命运埋藏的真相。</x:v>
+      </x:c>
+      <x:c r="I100" s="10" t="str">
+        <x:v>51集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；发布账号「寒冰剧场」</x:v>
+      </x:c>
+      <x:c r="J100" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B101" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C101" s="10" t="str">
+        <x:v>三年，我不装了</x:v>
+      </x:c>
+      <x:c r="D101" s="11" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E101" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F101" s="10" t="str">
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G101" s="10" t="str">
+        <x:v>布噜布噜剧场</x:v>
+      </x:c>
+      <x:c r="H101" s="10" t="str">
+        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+      </x:c>
+      <x:c r="I101" s="10" t="str">
+        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「布噜布噜剧场」</x:v>
+      </x:c>
+      <x:c r="J101" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B102" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C102" s="10" t="str">
+        <x:v>下山，从一纸婚约开始</x:v>
+      </x:c>
+      <x:c r="D102" s="11" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="E102" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F102" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G102" s="10" t="str">
+        <x:v>洛白剧场</x:v>
+      </x:c>
+      <x:c r="H102" s="10" t="str">
+        <x:v>鬼门传人陆凡受师娘逼迫下山，需找到天凤体女子成婚化解自身劫数。他在酒吧偶遇婚约对象苏若涵，救下遭人下药的她。陆凡前往苏家打算退婚，可苏若涵为抗拒家族安排的联姻，执意和陆凡领结婚证假结婚。苏若涵带陆凡去见另一位天凤体秦怡，两女为陆凡展开竞争。恰逢秦老爷子病危，一众名医束手无策，陆凡施展失传的鬼门十三针将其救活，展露高超医术。秦怡对陆凡心生好感，苏若涵也渐渐对陆凡动了真情，几人之间的情感拉扯就此展开。</x:v>
+      </x:c>
+      <x:c r="I102" s="10" t="str">
+        <x:v>151集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「洛白剧场」</x:v>
+      </x:c>
+      <x:c r="J102" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B103" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C103" s="10" t="str">
+        <x:v>不寄人间半尺光</x:v>
+      </x:c>
+      <x:c r="D103" s="11" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E103" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F103" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G103" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H103" s="10" t="str">
+        <x:v>苏晚剖腹产坐月子期间，婆婆孙淑芬装病博同情，丈夫郭鹏程愚孝偏袒。苏晚因照顾假摔的婆婆导致刀口崩裂，看清真相后毅然提出离婚。在好友协助下，她搜集证据揭穿婆婆伪装，并果断结束婚姻。随后苏晚投身职场，为助爱人傅时衍化解公司危机，不惜抵押资产、签署苛刻合同筹措资金，最终在董事会力挽狂澜，收获事业与爱情。</x:v>
+      </x:c>
+      <x:c r="I103" s="10" t="str">
+        <x:v>73集长剧集，符合起量主力区间；题材待验证；发布账号「幻境大剧场」上榜次数居前</x:v>
+      </x:c>
+      <x:c r="J103" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B104" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C104" s="10" t="str">
+        <x:v>九零绝境潮汐系统护我</x:v>
+      </x:c>
+      <x:c r="D104" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E104" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F104" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G104" s="10" t="str">
+        <x:v>杨桃剧院</x:v>
+      </x:c>
+      <x:c r="H104" s="10" t="str">
+        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+      </x:c>
+      <x:c r="I104" s="10" t="str">
+        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「杨桃剧院」</x:v>
+      </x:c>
+      <x:c r="J104" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B105" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C105" s="10" t="str">
+        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
+      </x:c>
+      <x:c r="D105" s="11" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E105" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F105" s="10" t="str">
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G105" s="10" t="str">
+        <x:v>AI便利店</x:v>
+      </x:c>
+      <x:c r="H105" s="10" t="str">
+        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
+      </x:c>
+      <x:c r="I105" s="10" t="str">
+        <x:v>96集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「AI便利店」</x:v>
+      </x:c>
+      <x:c r="J105" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B106" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C106" s="10" t="str">
+        <x:v>予你情深，岁岁相守</x:v>
+      </x:c>
+      <x:c r="D106" s="11" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E93" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="F93" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G93" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
-      </x:c>
-      <x:c r="H93" s="10" t="str">
-        <x:v>仿真人制作，与主流爆款画风一致；60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「九鲤动漫」</x:v>
-      </x:c>
-      <x:c r="I93" s="11" t="n">
-        <x:v>7</x:v>
+      <x:c r="E106" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F106" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G106" s="10" t="str">
+        <x:v>啾啾说漫</x:v>
+      </x:c>
+      <x:c r="H106" s="10" t="str">
+        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+      </x:c>
+      <x:c r="I106" s="10" t="str">
+        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「啾啾说漫」</x:v>
+      </x:c>
+      <x:c r="J106" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B107" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C107" s="10" t="str">
+        <x:v>二十八块麻辣烫，相亲男逼我领证</x:v>
+      </x:c>
+      <x:c r="D107" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E107" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F107" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G107" s="10" t="str">
+        <x:v>壹琚影视</x:v>
+      </x:c>
+      <x:c r="H107" s="10" t="str">
+        <x:v>单亲姐姐林小圆相亲时被抠门相亲男王浩以二十八块麻辣烫为饵逼婚，王浩携母姐堵门索要钱财房产，林小圆冷静周旋，戳穿王浩临时工身份谎言，面对辱骂报警维权，最终在民警与邻居帮助下逼退男方，守护了弟弟与自己的尊严。</x:v>
+      </x:c>
+      <x:c r="I107" s="10" t="str">
+        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「壹琚影视」</x:v>
+      </x:c>
+      <x:c r="J107" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B108" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C108" s="10" t="str">
+        <x:v>五十岁扮穷相亲，我试出了真心</x:v>
+      </x:c>
+      <x:c r="D108" s="11" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E108" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F108" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G108" s="10" t="str">
+        <x:v>不惧剧场</x:v>
+      </x:c>
+      <x:c r="H108" s="10" t="str">
+        <x:v>尝尽冷暖的陈牧远，为寻一份不掺杂质的真心，选择以平凡身份踏入烟火人间。风风火火的餐馆老板李珺月，以为他只是个潦倒大叔，却用她最大的真诚与善意，将“无家可归”的他热情收留。一个守护秘密，一个守护温暖，两个在尘世中各自坚韧的灵魂，在寻常日子的炊烟与暖阳里，找到了最安心的依靠。当一切真相大白，他们才明白，这世间最奢侈的幸福，从来不是财富的堆砌，而是抛开所有身份标签后，依然愿意为彼此撑伞、相守一生的真心。</x:v>
+      </x:c>
+      <x:c r="I108" s="10" t="str">
+        <x:v>99集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「不惧剧场」</x:v>
+      </x:c>
+      <x:c r="J108" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B109" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C109" s="10" t="str">
+        <x:v>京航婚事：战爷他超护短</x:v>
+      </x:c>
+      <x:c r="D109" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E109" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F109" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G109" s="10" t="str">
+        <x:v>漫剧时代</x:v>
+      </x:c>
+      <x:c r="H109" s="10" t="str">
+        <x:v>沈家突遭变故，姐妹为保家业卷入战家联姻。沈昭昭阴差阳错与“叔叔”战北渊结下隐秘婚约，沈清瓷则嫁与浪荡二少战司航。面对家族猜忌、职场倾轧与旧情纠葛，昭昭以机敏与武力护姐闯关，清瓷以魄力执掌航运。战北渊隐忍深情，暗藏“千浔”身份；昭昭步步为营，在危机中揭开幕后黑手，姐妹携手于豪门漩涡中逆风成长，守护彼此与家族。</x:v>
+      </x:c>
+      <x:c r="I109" s="10" t="str">
+        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「漫剧时代」</x:v>
+      </x:c>
+      <x:c r="J109" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B110" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C110" s="10" t="str">
+        <x:v>亲戚聚会他摆阔，我爸不结账了</x:v>
+      </x:c>
+      <x:c r="D110" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E110" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F110" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="G110" s="10" t="str">
+        <x:v>屿风漫剧</x:v>
+      </x:c>
+      <x:c r="H110" s="10" t="str">
+        <x:v>家族聚会上，陈国梁借哥哥陈国栋的钱买车摆阔，又多次把宴请账单推给哥哥。陈昭为保护父亲，推动聚会各自结算，并逐步揭开叔叔冒用昭源名义、组织亲友参与虚假项目的真相。身份公开后，她妥善退还款项、安排分期偿还。陈国栋学会拒绝，陈国梁放下虚荣，家族重新认识本分与担当的价值。</x:v>
+      </x:c>
+      <x:c r="I110" s="10" t="str">
+        <x:v>58集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「屿风漫剧」</x:v>
+      </x:c>
+      <x:c r="J110" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B111" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C111" s="10" t="str">
+        <x:v>仙界老祖非要当我哥</x:v>
+      </x:c>
+      <x:c r="D111" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E111" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F111" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>青青漫剧</x:v>
+      </x:c>
+      <x:c r="H111" s="10" t="str">
+        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+      </x:c>
+      <x:c r="I111" s="10" t="str">
+        <x:v>61集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；发布账号「青青漫剧」</x:v>
+      </x:c>
+      <x:c r="J111" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B112" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C112" s="10" t="str">
+        <x:v>保姆的亲情陷阱</x:v>
+      </x:c>
+      <x:c r="D112" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E112" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F112" s="10" t="str">
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G112" s="10" t="str">
+        <x:v>鸡腿剧场</x:v>
+      </x:c>
+      <x:c r="H112" s="10" t="str">
+        <x:v>女总裁林夏夏因工作忙碌，为残疾父亲林强聘请了保姆王小梅，然而一次临时回家取文件，让她在无意中听见王小梅正在哄父亲买六千块的假药，还劝说父亲瞒着自己，林夏夏当即决定辞退王小梅。但由于父亲长期孤寂中得到王小梅的陪伴，反而对女儿恶语相向，坚称王小梅才是真心对他好的人</x:v>
+      </x:c>
+      <x:c r="I112" s="10" t="str">
+        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 婚姻情感）；发布账号「鸡腿剧场」</x:v>
+      </x:c>
+      <x:c r="J112" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B113" s="11" t="str">
+        <x:v>09·05</x:v>
+      </x:c>
+      <x:c r="C113" s="10" t="str">
+        <x:v>入朝当女官不料皇帝喊我娘</x:v>
+      </x:c>
+      <x:c r="D113" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E113" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F113" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G113" s="10" t="str">
+        <x:v>浮生观影</x:v>
+      </x:c>
+      <x:c r="H113" s="10" t="str">
+        <x:v>十八年前夏雨兰诞下皇子遭太后狸猫换太子死里逃生。她化身女官入宫护儿媳，意外发现当今皇帝是自己亲儿。夏雨兰联手暗恋她十八年的摄政王萧凛，一边化解后宫刁难，一边深挖换子与私盐走私案。历经重重危机搜集完整证据，朝堂之上母子当众相认，反派悉数伏法。尘埃落定，夏雨兰放下皇宫荣华，与萧凛出宫共度余生。</x:v>
+      </x:c>
+      <x:c r="I113" s="10" t="str">
+        <x:v>63集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；发布账号「浮生观影」</x:v>
+      </x:c>
+      <x:c r="J113" s="11" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9181,10 +10860,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>30.5%</x:v>
+        <x:v>30.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -9192,10 +10871,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>26.1%</x:v>
+        <x:v>26.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -9230,7 +10909,7 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
         <x:v>43.4%</x:v>
@@ -9630,10 +11309,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>858</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>98.7%</x:v>
+        <x:v>98.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -9652,10 +11331,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R5c81280e1e464689"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R185a7586c3ec4143"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R2ab6c17dc3ab41eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R9247f74579db41a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R8b3a454492c24903"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="Rc55ad0f341b04510"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R2fbbe031d06a4b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R6c03259b9b6342ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Radb6a72ce97346ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R1f030e7e461b4b5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="Ra096e0650d664a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R90f5bdae88e44017"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5377,26 +5377,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
+        <x:v>重生之我飒爆了！第二季</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G54" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str">
+        <x:v>罗曼蒂克-海豹分镜【AI短剧】</x:v>
+      </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
+        <x:v>重生归来的林雨汐，在涉外饭店当众揭穿辱华者，拒绝用尊严换投资；她一路守护家人、揭开身世、创办药厂。与陆逸领证成婚后，空间因果降临，两人被送往末世求生。回归现实，她带着异能和新生命，却遭遇婴儿被盗，危机再起。</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
-        <x:v>57集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J54" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -5407,28 +5409,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>重生：回到1983当富翁之路第一季</x:v>
+        <x:v>后娘逆袭</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>阿水漫画</x:v>
+        <x:v>1649世界</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>上市公司执行总裁周于峰意外重回1983年。面对尚未改善的家庭关系、生活拮据的弟弟妹妹，以及处处充满机遇与挑战的时代环境。凭借多年积累的商业经验与判断力，周于峰从小生意做起，在坚守原则与规则的同时抓住时代机遇，一步步改善家人的生活，也重新审视婚姻与亲情。在改革浪潮中，他与身边的人共同成长，用一次次选择改变人生轨迹，走出属于自己的创业之路。</x:v>
+        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
-        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「阿水漫画」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；74集，主力长度；发布账号「1649世界」</x:v>
       </x:c>
       <x:c r="J55" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -5439,10 +5441,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>1970重生岁岁，不负韶华</x:v>
+        <x:v>重生八零：直上青天展宏图</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
         <x:v>其他</x:v>
@@ -5451,16 +5453,16 @@
         <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
-        <x:v>星文文化</x:v>
+        <x:v>八哥剧场</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
+        <x:v>林振东前世倾尽所有娶妻养家，辛苦半生，却发现妻子早已变心，三个养子皆是旁人骨肉。他被白眼狼子女榨干家产、狠心害死，连累至亲落得凄惨下场。带着无尽悔恨，他重生回到送彩礼定亲当天！这一世他当众怒退婚约，守护家人、斩断孽缘，凭借超前眼光，踏实创业搞钱，逆袭改写全家悲惨命运！</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str">
-        <x:v>86集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「星文文化」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；95集，主力长度；发布账号「八哥剧场」</x:v>
       </x:c>
       <x:c r="J56" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9.5</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -5471,28 +5473,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>全校笑我铁匠，我反手锻剑娘</x:v>
+        <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
-        <x:v>榴莲漫剧</x:v>
+        <x:v>芸光剧场</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>故事讲述英雄遗孤陆渊在转职仪式上觉醒最低级生活职业“铁匠”，遭受众人嘲笑，却意外激活隐藏职业“神级器灵师”。他以锻造之力创造出拥有灵智的强大器灵，一路打造剑娘、刀灵、盾灵，凭借隐藏实力横扫秘境、打破纪录、反击天才与权贵，从被轻视的废物铁匠成长为震撼世界的顶级强者。</x:v>
+        <x:v>现代中医天才林薇遭遇意外，穿越到八零年代，成为嫌贫爱富的炮灰媳妇。觉醒药圃空间，靠着药灵产出的药材食材改善生活。原本的丈夫顾深是有学识的潜力青年，林薇一改原主态度，用心经营家庭。她摆摊卖药材，抓住机遇搞大棚中草药育苗，攻克育苗难题。一边化解林蕊、孙大勇等人的不断陷害，一边带领家人奔好日子。她无私分享种植技术，获得荣誉，和顾深双向奔赴，事业爱情家庭三丰收。</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str">
-        <x:v>142集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「榴莲漫剧」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「芸光剧场」</x:v>
       </x:c>
       <x:c r="J57" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -5503,28 +5505,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>八十年代：铁娘子的缝纫机逆袭路</x:v>
+        <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G58" s="10" t="str">
-        <x:v>漫剧场小管家</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str"/>
       <x:c r="H58" s="10" t="str">
-        <x:v>八十年代改革开放初期，金枝丈夫去世后，一直与婆家同住，带着女儿过日子。面对婆家的偏心与冷眼，她从不低头，靠着一手裁缝好手艺，从走街串巷给人缝补做起。一针一线，把日子缝得踏实。从为人代工到盘下门面，金枝凭手中针线和不认输的劲头，挣出尊严，也闯出了属于自己的裁缝铺子与人生。</x:v>
+        <x:v>顾诚意外穿越至妖魔横行的乱世，开局惨遭叛徒出卖，沦为猪妖的口粮。绝境中他觉醒“氪命系统”，消耗寿元即可瞬间将武学推演至圆满境界，斩杀妖魔邪修更能夺取寿元无限续航！凭借此逆天金手指，顾诚从镇魔司底层小吏起步，一路狂斩内鬼、手撕破凡大妖、血战魔道余孽。在女修徐念雪与未婚妻林青燕的相伴下，顾诚以命为引，融合极道武学，誓要杀穿这妖邪乱世，登顶巅峰！</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str">
-        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「漫剧场小管家」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J58" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -5535,28 +5535,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>反派大佬成了女儿奴第一季</x:v>
+        <x:v>穿越古代，我靠军火建立王朝</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
-        <x:v>戏众生</x:v>
+        <x:v>热雪Ai漫剧场</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>为了糖果奖励，薄珠珠接下系统任务，要让薄宴州认下自己。她顺着纸箱空降薄氏集团。薄宴州十分抗拒，故意逗弄珠珠。可糖果的吸引力让薄珠珠不肯放弃，折返回来状况百出，系统疯狂报错，薄宴州看着古灵精怪的小团子满心审视。</x:v>
+        <x:v>现代退伍老兵陈楠意外穿越异世，开局便成杀虎口死囚。身陷绝境，他凭借随身空间、现代军备与作战经验，从牢房杀出重围，在边境战场一路崛起。当世家权贵视人命如草芥，他不再替旧秩序卖命，带领追随者建立陈家军、夺下黑石崖。冷兵器时代撞上现代火力，一介死囚，誓要重建大乾，建立属于自己的王朝！</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str">
-        <x:v>144集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；续季/系列续作，有前作热度背书；发布账号「戏众生」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「热雪Ai漫剧场」</x:v>
       </x:c>
       <x:c r="J59" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -5567,28 +5567,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>后娘逆袭</x:v>
+        <x:v>穿越王妃美又飒</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
-        <x:v>1649世界</x:v>
+        <x:v>羚羊AI剧场</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
+        <x:v>别人宅斗用心机，她宅斗直接掏手枪！堂堂现代蛊医传人，竟穿成任人欺凌的傻子王妃，开局就被恶毒侧妃扔进乱葬岗灭口。叶南希冷笑，空间戒指觉醒，直接掏出沙漠之鹰突突了恶奴！顺手还拿下了权倾朝野的战神镇北王。面对绿茶顶替、下人欺凌、皇家算计，她一手银针一手枪，神挡杀神！</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str">
-        <x:v>74集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「1649世界」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「羚羊AI剧场」</x:v>
       </x:c>
       <x:c r="J60" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -5599,28 +5599,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>带着仓库回七零第一季</x:v>
+        <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>无极动画</x:v>
+        <x:v>购嗨漫剧</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>1976年，沈牧野含恨重生，回到与周翠兰离婚当天。他凭穿越而来的现代仓库和前世厨艺进入钢铁厂食堂，从被刁难到凭西餐接待外宾一战成名。他先救下二姐母女，再治大姐的腿、还三姐的债，把家人一个个从苦日子里拉出来。期间，厂办秘书苏婉清一次次替他解围，两人在烟火与患难中越走越近。最后全家搬进厂区小院，枣树下，悸动暗生。</x:v>
+        <x:v>孤儿少女凌昭本是四项满S的百年天才，脑内神秘芯片吞噬她的精神力，令她沦为被众人嘲讽的废柴学员。绝境之际，她解锁脑内秘境万国狩猎场，通过试炼积攒信仰币突破变强。在异兽与强者林立的残酷竞技中，凌昭逆势翻盘，携手高冷天才萧含雪、孤勇幸存者夏明桑，冲破层层封印。她觉醒SS级天赋，执掌神剑神谕，屡破赛场纪录，打脸天骄，对抗帝国黑暗势力，从底层逆袭成最年轻战神，毅然奔赴凶险边境守护万家灯火。</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str">
-        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「无极动画」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「购嗨漫剧」</x:v>
       </x:c>
       <x:c r="J61" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -5631,28 +5631,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>异能赶海：从失业到海洋女王第二季</x:v>
+        <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 现实反转</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>每日沙雕推荐</x:v>
+        <x:v>熊猫热剧</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>北漂失意的苏蕴舟回乡后，觉醒能看透水下的特殊能力，靠收获珍贵海产快速积累财富，买下独栋别墅，改善全家生活。她救下遭遇意外的少年陆星辰，结识商界的霍铮，二人从试探发展为合作伙伴。苏蕴舟从容应对前男友、同学带来的人际纠葛。家里日子蒸蒸日上，父亲开办海产加工坊。苏蕴舟将一批珍珠交由霍氏处理，收到拍卖会邀约，在与大海相伴的日子里，完成自我成长与人生蜕变。</x:v>
+        <x:v>沈南星意外绑定高温末世预警系统，识破闺蜜白薇谎称极寒末日、联合男友骗取她物资的圈套。在河狸系统的陪伴与协助下，她反手变卖房产囤定制冷设备与生存物资，在半山腰打造避暑堡垒，储备充足物资，搭建起净水、制冷与无土种植系统，一人一系统携手并肩安稳度过极热危机，山庄成为灾后重建核心基地，沈南星与河狸系统也结下了深厚的伙伴情谊，而背叛者也为自身的贪念与过错承担了相应的后果。</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str">
-        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；68集，主力长度；发布账号「熊猫热剧」</x:v>
       </x:c>
       <x:c r="J62" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -5663,28 +5663,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>彩运照人心，第一季</x:v>
+        <x:v>误惹京华第二季</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
-        <x:v>文之江影视</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="H63" s="10" t="str">
-        <x:v>胡帕喜中巨额彩票，领奖当天却惨遭相恋四年的女友分手，昔日温情瞬间化为泡影。他斩断过往纠葛，毅然离职，奔赴郑州探望勤工俭学的妹妹，也因此结识了善良坚韧的梁池，两人渐生情愫。清明返乡，他冷眼看透势利亲戚的虚伪嘴脸，手握财富却选择低调行事，一心照料家人。在这冷暖交织的人情世故里，他褪去浮华，终与梁池携手，收获了一份纯粹真挚的缘分。</x:v>
+        <x:v>面对婚姻背叛与有毒亲情，坚韧的女性姜辞忧毅然决然的断亲独立，凭实力职场逆袭的故事。在自我救赎路上，她与深情守护的真爱薄靳修携手击碎阴谋；更在历经千帆后与生母温馨和解，传递出当代女性自强不息、温暖治愈的硬核力量！</x:v>
       </x:c>
       <x:c r="I63" s="10" t="str">
-        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书；发布账号「文之江影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；126集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J63" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -5695,28 +5695,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>恋上心通第一季</x:v>
+        <x:v>借势逢生</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
-        <x:v>益阳动漫</x:v>
+        <x:v>虾华看漫剧</x:v>
       </x:c>
       <x:c r="H64" s="10" t="str">
-        <x:v>快穿大佬叶聆刚退休就穿成恋综恶毒原配，绑定系统后惩罚竟全劈在冷漠老公谢淮舟身上，还附带感官通感！为了保命，高岭之花谢淮舟当众崩人设抢牵手、爆金币、求贴贴，全网惊呆说好的塑料夫妻呢？叶聆反骨杀疯恋综，手撕绿茶、暴揍前任、扫地出门全家奇葩。</x:v>
+        <x:v>青苍城天才少主陆轩惨遭仇家暗算，丹田被毁沦为废人，婚约也遭林家强行逼迫退婚。绝境之中，他意外觉醒葬天坠秘境，邂逅上古强者，习得至尊剑道与不死丹神传承。陆轩借秘境机缘逆天重修，一路越级逆袭、横扫仇家，破绝境、战群雄，强势守护挚爱与家人，登顶武道巅峰！</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str">
-        <x:v>129集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「益阳动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；发布账号「虾华看漫剧」</x:v>
       </x:c>
       <x:c r="J64" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -5727,28 +5727,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>收租精神小妹！第二季</x:v>
+        <x:v>反派老爹不好惹</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G65" s="10" t="str">
-        <x:v>心悦漫剪</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G65" s="10" t="str"/>
       <x:c r="H65" s="10" t="str">
-        <x:v>大厂十年，一朝被裁。林野拿着两百万补偿金回到县城，全款买了套别墅，只想安静活着。系统不让。收租万倍返还系统已激活。他盯着空荡荡的五个房间，开始琢磨怎么找租客。第一个上门的，是三个流浪到江城的精神小妹。从这天起，他的别墅再也没安静过。精神小妹、落魄富二代、跑路网红，各路奇人排着队住进来。</x:v>
+        <x:v>首富沈渡穿越都市爽文，觉醒家族气运系统，为避免家破人亡命运，反套路截胡气运之子叶凡机缘。他痛改纨绔儿子沈云，斗苏家、破赌石局，屡次粉碎叶凡崛起计划。叶凡黑化搬来宗师师兄雷虎复仇，依旧被沈渡父子强势碾压，最终叶凡气运耗尽陨落。世界线自我修复，新气运之子、海外佣兵之王陈枫降临，沈家与天命的博弈再度开启。</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str">
-        <x:v>124集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「心悦漫剪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；88集，主力长度</x:v>
       </x:c>
       <x:c r="J65" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -5759,28 +5757,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>无心攀比，假千金重生后成团宠了</x:v>
+        <x:v>女粉丝的救赎</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
-        <x:v>鲸跃AI剧场</x:v>
+        <x:v>栗栗动漫</x:v>
       </x:c>
       <x:c r="H66" s="10" t="str">
-        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
+        <x:v>女主林鹿一觉醒来，穿越到自己最爱的女明星沈清秋身上，得知原主早已惨死。偶像的死并非意外，她决定替她讨回公道。面对黑料、陷害与豪门阴谋，林鹿一路反击，逐渐查出原主之死竟牵扯权氏夺权。随着调查深入，幕后真相浮出水面——权斯年为了扳倒权延修，原主不过是他路上的一颗绊脚石。为了复仇，林鹿也一步步卷入这场危险的豪门棋局。</x:v>
       </x:c>
       <x:c r="I66" s="10" t="str">
-        <x:v>100集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「鲸跃AI剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；90集，主力长度；发布账号「栗栗动漫」</x:v>
       </x:c>
       <x:c r="J66" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -5791,28 +5789,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>死对头校花竟是我网恋女友第二季</x:v>
+        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="G67" s="10" t="str">
-        <x:v>长鹿漫漫</x:v>
-      </x:c>
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G67" s="10" t="str"/>
       <x:c r="H67" s="10" t="str">
-        <x:v>网络里的温柔陪伴，与现实中的针锋相对形成奇妙反差。相识四年，他们一直是彼此最熟悉的网友，却从未想过对方就在身边。从最初的误会，到一次次相处中逐渐卸下防备，两人慢慢发现彼此不为人知的温柔一面。当四年网聊终于迎来奔现，他们才发现，那个一直陪伴自己的人，竟是现实中最意想不到的存在。一场甜蜜、欢乐又充满惊喜的青春恋爱，就此开始。</x:v>
+        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
       </x:c>
       <x:c r="I67" s="10" t="str">
-        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「长鹿漫漫」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；57集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J67" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -5823,28 +5819,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>浴火重生，我撕碎前夫的美梦</x:v>
+        <x:v>彪悍后妈在八零</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>云阅真人漫剧</x:v>
+        <x:v>玫瑰短剧.</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>家庭主妇林晚遭丈夫陈世杰与情人苏曼背叛，更被设计坠崖毁容。死里逃生后，她继承遗产、改头换面，以资本新贵身份重返陈世杰身边，步步引他暴露贪婪与罪行。最终真相大白，林晚在顾言守护下夺回属于她的一切，迎来新生。</x:v>
+        <x:v>末世强者姜珠重生到1983年，替假千金嫁给乡下“拖油瓶”男人，进门就当后妈。她攥着三千块彩礼嫁入陆家，丈夫陆战竟是运输队大队长，两个继子女正遭极品亲戚虐待。她劈锁立威、铁腕掌家，凭卤味绝活逆袭省城。夫妻并肩创业，她真心焐热两个孩子，收拾贪心亲戚、揭穿假千金阴谋、打下万贯家业。穿越女强人把当好后妈活成了最飒的事业，还在烟火人间里意外收获了属于自己的小生命。</x:v>
       </x:c>
       <x:c r="I68" s="10" t="str">
-        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「云阅真人漫剧」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；43集，次优长度；发布账号「玫瑰短剧.」</x:v>
       </x:c>
       <x:c r="J68" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -5855,28 +5851,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>破窑洞飞出金凤凰第一季</x:v>
+        <x:v>无心攀比，假千金重生后成团宠了</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>定边同城帮</x:v>
+        <x:v>鲸跃AI剧场</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>李根出身贫寒，大学时与富家女苏婉晴相恋，却在订婚宴上被当众退婚羞辱。他落魄返乡，在荒山上发现野生酸枣的商机，立志创业。从承包荒山、改土育苗，到历经暴雨毁林、父亲病倒、资金断裂等重重打击，他凭一股不服输的韧劲咬牙坚持。在贵人相助和全村人的支持下，他成功将荒山变成千亩枣园，成立合作社，带领黄土坡村脱贫致富。事业有成后，他赢得真诚爱情，拒绝资本诱惑，创办农业大学，用一生诠释了什么是坚守初心，扎根土地。</x:v>
+        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
       </x:c>
       <x:c r="I69" s="10" t="str">
-        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「定边同城帮」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；发布账号「鲸跃AI剧场」</x:v>
       </x:c>
       <x:c r="J69" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -5887,28 +5883,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>纨绔穿越古代成就百万诗仙第一季</x:v>
+        <x:v>程家小媳不好惹第二季</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>咪漫剧场</x:v>
+        <x:v>莹莹漫剧</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>现代纨绔魂穿贞观十年，成为军神李靖之孙李景安。开局揭皇榜医治长孙皇后，凭抄录千古诗词惊艳长安，诗会碾压对手一战封神。解锁硝石制冰、马蹄铁等黑科技搅动朝堂。一边当摆烂纨绔，一边搅动大唐风云，周旋世家权贵，邂逅多位佳人，在初唐掀起属于谪仙少年的传奇浪潮。</x:v>
+        <x:v>现代建筑设计师意外穿越，成了古代乡村被娘家倒贴银子卖掉的傻姑娘。她被哥嫂强行塞给穷小子程风当媳妇，一睁眼就被困在破屋中无依无靠。面对贫寒的家境和未知的处境，她只能暂时装傻保命，心里却早已盘算好出路，只等程风归来揭开这场错位婚事的后续。</x:v>
       </x:c>
       <x:c r="I70" s="10" t="str">
-        <x:v>89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「咪漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；135集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J70" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -5919,7 +5915,7 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>荒岛逆袭：我成了荒岛之王</x:v>
+        <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
         <x:v>60</x:v>
@@ -5928,19 +5924,19 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>古装宫廷 / 美食治愈</x:v>
       </x:c>
       <x:c r="G71" s="10" t="str">
-        <x:v>庚庚</x:v>
+        <x:v>恒漫剧场</x:v>
       </x:c>
       <x:c r="H71" s="10" t="str">
-        <x:v>一场突发的海难，让公司员工陆鸣与总裁苏清寒等同事意外流落荒野孤岛。失去现代文明的庇护，习惯了优渥生活的苏清寒等人起初难以适应，依然带有职场上的刻板偏见，试图将荒野危机简单化。然而，陆鸣凭借过硬的野外求生知识与坚韧的意志，不仅成功获取了珍贵的食物和水源，还搭建起了安全的庇护所。为了整个团队的生存，陆鸣立下“按劳分配、互帮互助”的营地新规。在陆鸣的带领下，他们战胜了荒岛危机。</x:v>
+        <x:v>现代平凡女孩穿越成古代小商户女，靠美食系统古几位性格迥异的优质公子，在经营小吃铺的甜蜜日常中，一是微服私访的护国将军之子沈墨，表面是纨绔公子，实则武艺高强，因被奶茶惊艳而天天来蹭吃，二是当朝首辅的孙子、温润如玉的才子顾清寒，他正为招待海外使臣的宴席发愁，慕名前来求教点心，三是神秘商人裴云，看似普通富商，却总能拿出稀有食材与林小满交易，并对她展露异常执着的关心。</x:v>
       </x:c>
       <x:c r="I71" s="10" t="str">
-        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「庚庚」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「恒漫剧场」</x:v>
       </x:c>
       <x:c r="J71" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -5951,28 +5947,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>蓄意逐风：我在恋综称王称爸第二季</x:v>
+        <x:v>转生成鼠，气哭冷艳校花</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>119</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>₊⁺水蜜陶🍑剧场</x:v>
+        <x:v>长夜动漫剧场</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>恋综游园会浪漫开启谢弥经助理刁茂巧手妆造一袭浅碧挂脖长裙惊艳全场绿毛龟轮椅依旧是她标志性座驾。沈爅卿一见盛装的谢弥眼底藏不住温柔轻声夸赞她夺目。二人扫荡美食摊位后，前去塔罗帐篷占卜谢弥一心惦记财运，顺势追问命定之人是不是沈爅卿，沈爅卿暗藏心事化身谜语人二人写下心愿纸船放入溪流，谢弥却抛下纸船直奔套圈摊位，沈爅卿含笑追赶。镜头曝光沈爅卿纸船秘密纸上赫然写着我的初恋是谢老师埋藏已久的心意悄然浮出水面。</x:v>
+        <x:v>林一穿越成花枝鼠，觉醒吞噬进化系统，偷吃重生女帝郑依云的贡品意外被契约。他靠吞噬灵物极速进化，认赤炎神凤为义母，携手女主横扫校园、征战万国大比，一路逆袭登顶。转生老鼠，开局偷吃校花贡品的命运新局继续展开。转生老鼠，开局偷吃校花贡品的命运新局继续展开。</x:v>
       </x:c>
       <x:c r="I72" s="10" t="str">
-        <x:v>119集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「₊⁺水蜜陶🍑剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「长夜动漫剧场」</x:v>
       </x:c>
       <x:c r="J72" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -5983,10 +5979,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>误惹京华第二季</x:v>
+        <x:v>魂穿百岁老太，零零后整顿全村</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
         <x:v>其他</x:v>
@@ -5995,16 +5991,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>筑创Ai漫剧</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>面对婚姻背叛与有毒亲情，坚韧的女性姜辞忧毅然决然的断亲独立，凭实力职场逆袭的故事。在自我救赎路上，她与深情守护的真爱薄靳修携手击碎阴谋；更在历经千帆后与生母温馨和解，传递出当代女性自强不息、温暖治愈的硬核力量！</x:v>
+        <x:v>24岁社畜林晚猝死后，穿越成顾家百岁老太太。面对极品亲戚争产、懦弱儿孙受欺、重男轻女旧俗、熟人骗局陷害、宗族道德绑架等重重困境，她以现代清醒头脑和通透智慧，一一化解危机、整顿家风，护住家人安稳。在带领全家逆袭翻身的过程中，她意外发现原主尘封半生的骨肉离别之痛。历经寻亲无果、善恶和解、遗憾释然，她最终领悟，人生无需圆满，带憾前行、温柔生活，便是重生最大的意义。</x:v>
       </x:c>
       <x:c r="I73" s="10" t="str">
-        <x:v>126集长剧集，符合起量主力区间；题材待验证；续季/系列续作，有前作热度背书；发布账号「星屿漫剧场」多次产出上榜剧</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；40集，次优长度；发布账号「筑创Ai漫剧」</x:v>
       </x:c>
       <x:c r="J73" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -6015,28 +6011,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C74" s="10" t="str">
-        <x:v>68万存款，买了一场婚姻的真相第二季</x:v>
+        <x:v>原来她从未输过</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E74" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F74" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G74" s="10" t="str">
-        <x:v>权策推剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H74" s="10" t="str">
-        <x:v>婚礼当天，吴子妍被丈夫一家逼签陪嫁房赠予协议，当众受辱。她当场撕毁协议、取消婚礼，却在离婚后遭遇周家霸占房产、伪造授权、私吞租金的无底线算计。从崩溃屈辱中站起，她冷静收集证据、诉诸法律，一步步追回房产与尊严。最终，周家付出代价，吴子妍拿回人生主动权，更将自己的经历化作对无数女性的边界提醒——守住底线，从不丢人。</x:v>
+        <x:v>丈夫临终将巨额股份赠予初恋，原配沈瑾看似隐忍退让，实则早已布局。在董事会关键时刻，她拿出公证遗嘱与录像证据，揭露丈夫生前设局试探真相。随着幕后黑手陆敬堂落网，沈瑾不仅守住家业，更助女儿林然顺利接班，最终母女二人迎来真正的新生与安宁。</x:v>
       </x:c>
       <x:c r="I74" s="10" t="str">
-        <x:v>135集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；续季/系列续作，有前作热度背书；发布账号「权策推剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度；发布账号「幻境大剧场」双口径都产爆款；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J74" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -6047,28 +6043,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C75" s="10" t="str">
-        <x:v>林国强的故事，重生80年带妻女翻身第二季</x:v>
+        <x:v>重生七零辣媳不好惹</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E75" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F75" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G75" s="10" t="str">
-        <x:v>每日沙雕推荐</x:v>
+        <x:v>长安漫剧社</x:v>
       </x:c>
       <x:c r="H75" s="10" t="str">
-        <x:v>林国强重生回到八零年代，开国强饭店创业起家，分家脱离原生家庭，避开前世悲剧。第二季主线事业持续扩张，处理原生家庭一堆烂摊子，妹妹遭遇家暴悲剧，兄弟姐妹各自的命运走向，拓展大棚、养鸡场、鱼塘多条产业线，同时伴随亲戚算计、婚恋风波，铺垫县城大饭庄的新事业。</x:v>
+        <x:v>现代女医生魂穿七零，成为全村唾弃的坏媳妇！醒来直接地狱开局——名声败坏，婆家刁难，还有个一心惦记的渣男前男友，丈夫周时勋对她满心嫌隙。既然占了这副身子，她绝不重蹈覆辙！怼极品、撕渣男、破流言，辣媳强势上线！高冷铁血军人周时勋，从冷眼旁观到步步沦陷，把小媳妇护在身后。贫瘠七十年代，没有开挂金手指，看盛安宁如何扭转恶名，撩动硬汉丈夫，斗渣逆袭，把苦日子过得热气腾腾！</x:v>
       </x:c>
       <x:c r="I75" s="10" t="str">
-        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；68集，主力长度；发布账号「长安漫剧社」</x:v>
       </x:c>
       <x:c r="J75" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -6079,28 +6075,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C76" s="10" t="str">
-        <x:v>重生觉醒，这次我不做恋爱脑第六季</x:v>
+        <x:v>初初处处藏不住</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E76" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F76" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G76" s="10" t="str">
-        <x:v>桃汁夭夭</x:v>
+        <x:v>漫小陆</x:v>
       </x:c>
       <x:c r="H76" s="10" t="str">
-        <x:v>重活一世，林雾终于看清自己的心，坚定走向始终默默守护她的徐京妄。她用一场精心准备的生日惊喜，陪他回望成长岁月，也许下长久相伴的承诺。此后，两人的感情愈发甜蜜坚定。面对家人的关注，林雾坦然表达心意，徐京妄也以真诚回应她的偏爱。林雾也在彼此陪伴与守护中不断成长，与他携手奔向明亮温暖的未来。</x:v>
+        <x:v>开局即地狱！她刚穿越就被毒哑，像牲口一样被抬去沉井！叶初初绑定吃瓜系统，却因穷得买不起道具，只能靠求生本能反杀恶奴。幸好将军哥哥及时赶到，然而她发现自己心里吐槽的心声，竟然能被特定人物听见？于是公堂之上，她一边吃瓜，一边靠心声疯狂输出信息差，全员震惊！继母丑事败露、杀母仇人当场现形</x:v>
       </x:c>
       <x:c r="I76" s="10" t="str">
-        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「桃汁夭夭」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「漫小陆」</x:v>
       </x:c>
       <x:c r="J76" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -6111,28 +6107,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C77" s="10" t="str">
-        <x:v>人是诡异幼崽第二季</x:v>
+        <x:v>号外号外，团宠小师妹她又开挂了</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>116</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E77" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F77" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G77" s="10" t="str">
-        <x:v>悦禾剧场</x:v>
+        <x:v>朵粒猫AI</x:v>
       </x:c>
       <x:c r="H77" s="10" t="str">
-        <x:v>穿越者任逸一直以为自己生活在人类社会，直到毕业觉醒，才发现联盟里根本没有人类，而自己竟是披着人皮的诡异幼崽。觉醒幻术规则后，他与陆子涵进入副本实习，在一次次规则博弈中疯狂收割情绪、提升实力。随特别收割预案启动，任逸主动伪装成人类参与者潜入“陆家小院”，借直播扩大能力收益。然而瓜田、药园规则层层升级，浓雾深处的诡异梧桐与致命限制逐渐显现，一场更危险的猎杀正式开始。</x:v>
+        <x:v>现代博士蓝玥穿越成被虐的蓝府大小姐，她本想躺平当咸鱼，却被上古手镯绑定，觉醒全属性八灵根。入沧澜宗后，她凭学霸思维和嘴炮神功一路逆袭，成为全宗团宠。大师兄萧玦表面清冷实则暗中护她周全，二师兄温润如玉、四师兄阳光开朗、三师兄御兽有方，轮流为她撑腰。面对庶姐蓝舞和玄天宗的百般构陷，蓝玥用实力告诉所有人，她不是废物，是整个大陆惹不起的存在。</x:v>
       </x:c>
       <x:c r="I77" s="10" t="str">
-        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈）；续季/系列续作，有前作热度背书；发布账号「悦禾剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「朵粒猫AI」</x:v>
       </x:c>
       <x:c r="J77" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -6143,28 +6139,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>修仙归来护家人第二季</x:v>
+        <x:v>山里来的小丫头，专治都市不服第三季</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>夏十七</x:v>
+        <x:v>动了个漫剧场</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
+        <x:v>被豪门未婚夫当众退婚，山里来的莫清舞却反手捏碎大劳，吓蒙全场！她不认银行卡，只认烤肠，5块救活京城首富，顺手压制顾家掌权人顾夜寒体内寒毒。从被嘲村姑到人人争抢的小神医，她靠天生神力、望气奇术一路打脸豪门、横扫黑市、硬闯秘境。七块混沌圣宝碎片背后，藏着能救心上人、也能毁灭苍生的惊天秘密。为了救顾夜寒和冷霄，她要把都市、古武、玄武大陆统统掀翻！</x:v>
       </x:c>
       <x:c r="I78" s="10" t="str">
-        <x:v>72集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「夏十七」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J78" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -6175,26 +6171,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>凡人仙鱼，混沌灵根逆袭仙途</x:v>
+        <x:v>开局成废后我反手养出十万御林军</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G79" s="10" t="str"/>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str">
+        <x:v>天桥热血剧场</x:v>
+      </x:c>
       <x:c r="H79" s="10" t="str">
-        <x:v>天玄宗杂役弟子许时安，因混沌废灵根被视为消耗资源的无底洞，只能在后山清理淤泥。意外之下，他在丹田中得到一只神秘黑鱼！神鱼吞吃废丹废符后，竟能吐出完美品阶的丹药符箓！自此，许时安从底层杂役逆袭，拜入仙子苏眠门下，习得上古剑法典籍《道剑十三》。秘境历练中，神鱼经历第三次进化，化为鲲之形态。面对仇人截杀与七魔将的血祭大阵，许时安以道剑十三破阵，祭出上古磨盘镇压万魔，一战封神，震惊整个天玄宗！</x:v>
+        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
       </x:c>
       <x:c r="I79" s="10" t="str">
-        <x:v>77集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「天桥热血剧场」</x:v>
       </x:c>
       <x:c r="J79" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -6205,28 +6203,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>凡人修仙开局捡到聚宝仙鼎第四季</x:v>
+        <x:v>捡到女帝，逆命双生第三季</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>蜗牛漫剧剧场</x:v>
+        <x:v>每日欢乐漫剧</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>全仙宗都笑凡人许长生五行杂灵根，注定困死废丹房！许长生得云瑶仙子引仙门，却沦为最低废丹房杂役，日日遭管事压榨羞辱。山洪濒死之际，天降聚宝仙鼎，废丹炼极品、残书化顶级道藏，万物经鼎皆能升华！他暗藏底牌隐忍发育，打脸欺辱自己的杂役与管事，大比惊艳全场，一跃成为内门弟子，凭一鼎之力逆转凡人身，踏破长生大道。</x:v>
+        <x:v>大夏废太子王腾落难之际觉醒签到系统，凭腹黑智谋与系统外挂扮猪吃虎，收服妖兽宗门，集结羊老头、鬼谷子、九尾天后等一众助力，和野心阴鸷的三皇子夏尤阵营展开权谋与实力的层层博弈。女主柳颜汐是瑶池女帝转世，兼具软萌娇羞与杀伐果断的极致反差，与王腾生死相伴、双向护持。最终二人携手君临天下，以世纪婚礼与天降祥瑞宣告真龙归位，全程密集打脸爽点、高甜宠妻与玄幻战斗名场面。</x:v>
       </x:c>
       <x:c r="I80" s="10" t="str">
-        <x:v>158集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「蜗牛漫剧剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；91集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J80" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -6237,28 +6235,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>别拿猪婆龙不当神兽第二季</x:v>
+        <x:v>穿回八零我凭厨艺旺翻全家</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>年代怀旧 / 美食治愈</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>与情箓</x:v>
+        <x:v>红颜剧场</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>别拿猪婆龙不当神兽第二季来袭！渡劫失败的虞柏柏被天雷劈成了一条猪婆龙（扬子鳄），在高冷影帝家里当宠物蹭吃蹭喝蹭雪饼。影帝抱着鳄鱼形态的她殷切期盼，如果你能变成虞柏柏那样的美人该有多好啊！某一天，虞柏柏实在憋不住了，在影帝怀里现出了人形，她转头看向了高冷影帝，眼神魅惑，还满意你看到的吗？没想到，高冷影帝当场垮起了脸——变回去！</x:v>
+        <x:v>现代女厨师穿越成80年代恶婆婆张桂芬，绑定灵泉空间系统，面对家徒四壁、儿媳垂危、孙女被卖的烂摊子，凭借出神入化的厨艺与灵泉水，救儿媳、赎孙女、治儿子、斗恶霸，带领全家从乡镇集市摆摊卖卤味，一路逆袭至县城开店，最终让宋家从穷困潦倒走向富足兴旺，彻底扭转恶婆之名。</x:v>
       </x:c>
       <x:c r="I81" s="10" t="str">
-        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「与情箓」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；发布账号「红颜剧场」</x:v>
       </x:c>
       <x:c r="J81" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -6269,28 +6267,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>发配充军，战神系统宁九才镇守边关第三季</x:v>
+        <x:v>重生六零之护妻猎王</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>年代怀旧 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
+        <x:v>静剧社</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>宁川重回盛京，深知大晋皇室底蕴深厚。他借力邀月公主的夺嫡之争，接连拔除多方敌对势力，依靠特殊流水线能力快速提升自身修为。尘封数百年的宁家旧仇真相大白，宁川成功为家族洗刷冤屈，扶持妹妹宁婉儿建立宁国，登临帝位。外部危机却接连爆发，柳如烟、南海海族、葬土死灵纷纷发难。宁川不断突破境界，力克强敌，收获珍贵仙种，意外寻得离开绝灵之地的线索，一场席卷天下的大乱局徐徐拉开。</x:v>
+        <x:v>顶级战神陆峥重生六零，沦为村里遭人唾弃的烂赌废物。开局债主登门，妻子沈知宁受尽欺凌、饥寒交迫。他闯风雪岭猎兽采参，凭本事碾压恶霸，靠灵芝换取身份。斗恶护妻，带领村民开荒拓路，盘活山村，逆袭过上红火安稳日子。</x:v>
       </x:c>
       <x:c r="I82" s="10" t="str">
-        <x:v>111集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；63集，主力长度；发布账号「静剧社」</x:v>
       </x:c>
       <x:c r="J82" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -6301,28 +6299,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>咱们你听心声我吃瓜，换嫁夫妻笑哈哈第二季</x:v>
+        <x:v>重生后我靠鉴宝慧眼翻身</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F83" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>每日沙雕速递</x:v>
+        <x:v>意欢剧场</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>现代穿越者裴辞镜绑定吃瓜系统，娶了拥有读心能力的沈柠欢。裴辞镜表面咸鱼，内心疯狂吃瓜吐槽，沈柠欢看破他的心声，夫妻二人默契十足。恰逢太子发动宫变，二人携手化解危机，揪出八皇子的谋划。之后裴辞镜参加科举，高中探花，入朝任职翰林院编修。侯府内部恩怨逐渐化解，沈柠悦幡然悔悟。裴辞镜入职后接到修订水利典籍的差事，还意外发现前人疑似穿越者的线索，故事暂告一段落。</x:v>
+        <x:v>孤儿林晚晚前世花光五百万装名媛，被揭穿后负债坠桥。重生回十八岁，她决心用真本事逆袭，积累资本，创立晚星珠宝鉴定工作室，招募被陷害的顶尖人才安沛，打造自主高定品牌。面对前世仇敌与同行打压，她冷静设局，在顶级晚宴上揭穿阴谋，最终收获事业、友情与自我认可。</x:v>
       </x:c>
       <x:c r="I83" s="10" t="str">
-        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈）；续季/系列续作，有前作热度背书；发布账号「每日沙雕速递」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「意欢剧场」</x:v>
       </x:c>
       <x:c r="J83" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -6333,28 +6331,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>婚宴厅被抢，我反手告倒百亿公司</x:v>
+        <x:v>长姐归来，以爱托举全家！</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F84" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>妙手看剧</x:v>
+        <x:v>一支喵</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>许知夏筹备多年的婚宴当天，场地方突然毁约，替梁书瑶腾出主舞台。未婚夫陆远舟不仅没有替她说话，反而站到梁书瑶身边，逼她识相离场。梁家仗着百亿公司撑腰，封锁证据、操控舆论，想让她带着耻辱退场。许知夏却撕下婚纱上的花，保全合同、录音与资金记录，将婚宴变成反击的起点。她解除婚约，反手起诉梁家企业，让抢走她婚礼的人，为这场精心设计的羞辱付出代价。</x:v>
+        <x:v>现代强者叶青萝意外穿越，成为被苏家无情驱逐的假千金，一朝跌落泥泞。幸而她重回清贫的亲生叶家，解锁随身空间逆袭开挂。面对破败家境、负债困境与邻里非议，叶青萝凭借精湛厨艺、出众文笔经商创收，踏实打拼。她温柔护佑父母幼弟，化解周遭纷争，步步深耕、稳步致富，带领平凡叶家摆脱贫苦，安家立业，阖家奔赴圆满红火的人生巅峰。</x:v>
       </x:c>
       <x:c r="I84" s="10" t="str">
-        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转）；发布账号「妙手看剧」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「一支喵」</x:v>
       </x:c>
       <x:c r="J84" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -6365,28 +6363,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
+        <x:v>为了活命我拼命整活</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>云朵邮递员</x:v>
+        <x:v>留阿布</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
+        <x:v>62岁骚男主播吴耐意外穿越，成了重病缠身的孤寡老大爷。手握三百万存款与四套房产，却叠满肝癌晚期、重度糖尿病、脑血栓等病痛buff，生命仅剩十四天！危急时刻，惊讶系统激活只要让自家三名美女租客惊讶，就能兑换寿命续命。温柔小护士、飒爽女刑警、风情女租户轮番登场。为了活下去，吴耐花式搞事，免房租、豪掷消费、秀逆天游戏操作，不断制造名场面，一边对抗病痛，一边疯狂刷惊讶值，开启爆笑续命逆袭生活。</x:v>
       </x:c>
       <x:c r="I85" s="10" t="str">
-        <x:v>131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；续季/系列续作，有前作热度背书；发布账号「云朵邮递员」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「留阿布」</x:v>
       </x:c>
       <x:c r="J85" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -6397,28 +6395,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
+        <x:v>婴语大师</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>平川动画</x:v>
+        <x:v>小天短剧</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
+        <x:v>18岁少女陆星辰意外觉醒“婴语翻译”系统，能听懂婴儿的每一次啼哭与呢喃。凭借这份独特天赋，她从一个普通大学生成长为京城顶级育儿专家，用爱与耐心呵护着豪门继承人们的健康成长。在数十年的守护中，陆星辰不仅用真心赢得了孩子们的依赖和全城大佬的敬重，更将这些孩子培养成三观正、有担当的栋梁之才。故事传递了“用心倾听、用爱陪伴”的育儿真谛，展现了平凡女孩凭借善良与专业逆袭人生的正能量。</x:v>
       </x:c>
       <x:c r="I86" s="10" t="str">
-        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 萌宝治愈 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「平川动画」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；65集，主力长度；发布账号「小天短剧」</x:v>
       </x:c>
       <x:c r="J86" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -6429,28 +6427,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>小满混江湖第一季</x:v>
+        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>两把刷子剧场</x:v>
+        <x:v>平川动画</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>底层客栈孤女姜小满为求生存，意外卷入烬月教阴谋，被迫顶替失踪多年的青梧派掌门义女林阿照，就此踏入一场蛰伏十六年的朝堂死局。在门派中她与心思深沉的大师兄沈砚舟步步周旋，又凭借儿时一张平安符，攀附腹黑的魔教教主谢无咎。随着旧案揭开，假身份之下牵扯出真公主的过往，侯府灭口、妃嫔算计、双生皇子秘闻接连浮现。市井孤女凭着狡黠与傲骨，游走于江湖朝堂，以袖中薄刃，搅动整片天下棋局。</x:v>
+        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
       </x:c>
       <x:c r="I87" s="10" t="str">
-        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「两把刷子剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；108集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J87" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -6461,28 +6459,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>小邪爱空姐之欢喜对头误撞心动第二季</x:v>
+        <x:v>我养的小兽怎么都成大佬了第二季</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>天才黄小邪</x:v>
+        <x:v>迷声漫剧</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>妇科医生陈北在航班上俯身帮男孩捡东西时，不慎误碰空姐陈诗瑶，被对方误会耍流氓，还闹到了警局，但最终警方证实了他的清白。这场飞机上的意外乌龙，本以为他们再无交集，可陈诗瑶却发现新租房子的房东竟然是陈北。于是两人开始同居，欢喜冤家同住一屋，从针锋相对到渐生情愫，最终甜蜜相恋、幸福相守。</x:v>
+        <x:v>赵橙知穿越星际兽世，百年前曾在废土星救下并养大五只幼兽，再睁眼却成了黑市待拍卖的F级废雌。危急关头，她唤出当年那只红狐幼崽——如今战功赫赫的归墟星将军千折意，被他强势救下护在身侧。随着校园风波迭起，白虎族首领庄九牧也认出了她的身份。昔日温顺小兽已成执掌一方的顶级大佬，百年执念与偏执守护尽数爆发，双强大佬开启极致修罗场</x:v>
       </x:c>
       <x:c r="I88" s="10" t="str">
-        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「天才黄小邪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；78集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J88" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -6493,28 +6491,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>开局成废后我反手养出十万御林军</x:v>
+        <x:v>烟火年代：我有灵泉空间第一季</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F89" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>天桥热血剧场</x:v>
+        <x:v>哒哒哒剧场</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
+        <x:v>七零年代，现代青年林墨穿越到被家人压榨迫害的知青身上，觉醒1元秒杀系统，开局秒杀储物戒。他手撕吸血原生家庭，拿到下乡名额前往极北大岭屯。一路凭借系统、念力与神级医术化解危机，结识王建军、方家姐妹。在乡村治病救人、打猎建功，周旋各方势力，对抗官场反派，积累财富与人脉，在七十年代的时代浪潮中闯出自己的一番天地。</x:v>
       </x:c>
       <x:c r="I89" s="10" t="str">
-        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「天桥热血剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J89" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -6525,28 +6523,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>心愿昭昭，神明有应第一季</x:v>
+        <x:v>修仙归来护家人第二季</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>文妃儿</x:v>
+        <x:v>夏十七</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>雾禾最大的心愿，是寻一位模样俊朗、性情体贴的夫君，陪她守着小院安稳度日。于是，她跑到山中神像前认真许愿。没过多久，风离昭便来到她身边。他会洗衣做饭，会亲手添置家用，也会把她随口说过的话放在心上，只是偶尔傲娇炸毛，格外需要人哄。雾禾以为自己只是运气好，却渐渐发现，这位夫君似乎与山中的古老传说关系匪浅。一个愿望牵起一段奇缘，两个原本孤单的人，在欢笑与陪伴中学会信任，也把平凡光景过成了温暖明亮的好日子。</x:v>
+        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
       </x:c>
       <x:c r="I90" s="10" t="str">
-        <x:v>120集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文妃儿」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；72集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J90" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -6557,28 +6555,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>我的别墅通两界，摆摊的我赚了亿点点第三季</x:v>
+        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>104</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
+        <x:v>云朵邮递员</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>陆沉玉穿梭现代与异界，壮大石牙部落，完善城防、推行识字与岗位竞选，部落蒸蒸日上。白头部落举兵进犯，被陆沉玉击溃，俘虏纳入劳动力，吴志也归降部落。陆沉玉组建华夏商队，携盐、陶器等物资远征参加部落大集，沿路收服孤山、青山等部族，收获煤炭、蜂蜜、香草荚等资源。抵达大集后，华夏部落凭借精良物资震慑各方势力，神殿假意示好，企图套取制盐、烧瓷技术，陆沉玉将计就计，带着暗藏阴谋的神殿随从踏上归途。</x:v>
+        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
       </x:c>
       <x:c r="I91" s="10" t="str">
-        <x:v>104集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；131集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J91" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -6589,28 +6587,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>我的渔船通龙宫第一季</x:v>
+        <x:v>小五替我择良缘</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>六翼动漫</x:v>
+        <x:v>一碗猫酱</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
+        <x:v>兄长出征前，留下鹦鹉小五陪伴姜疏萤。寿宴之上，养女阿娇觊觎小五，未婚夫裴渊偏帮外人，肆意放走鸟儿。姜疏萤心死决然退婚，却发现小五落入逍遥王陆砚卿手中，还提出以人换鸟。侯府内宅步步构陷，继母与父亲的阴谋层层揭开，姜疏萤携鹦鹉，在王爷相助之下，撕破虚伪假面，复仇逆袭，觅得良缘。</x:v>
       </x:c>
       <x:c r="I92" s="10" t="str">
-        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「六翼动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；53集，次优长度；发布账号「一碗猫酱」</x:v>
       </x:c>
       <x:c r="J92" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -6621,28 +6619,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>我竟是道祖之狩猎气运之子第五季</x:v>
+        <x:v>我的渔船通龙宫第一季</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>116</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>玖月说漫</x:v>
+        <x:v>六翼动漫</x:v>
       </x:c>
       <x:c r="H93" s="10" t="str">
-        <x:v>三千道州与神魔大陆相连，古族之主古乾立于时代潮头，带领族中强者踏入更广阔天地。一次跨界之行，让魅魔族迎来全新归宿，也让古族与各大道统的联系愈发紧密。古乾一边安置新族地、汇聚各方资源，一边放眼界域天骄盛会与更高层次的古洪荒。随着古雄彪等新一代天骄崭露锋芒，古族气运日盛，新的伙伴、机缘与广阔天地接连出现。</x:v>
+        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
       </x:c>
       <x:c r="I93" s="10" t="str">
-        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书；发布账号「玖月说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；65集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J93" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -6653,28 +6651,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C94" s="10" t="str">
-        <x:v>亲戚聚会他摆阔，我爸不结账了</x:v>
+        <x:v>不寄人间半尺光</x:v>
       </x:c>
       <x:c r="D94" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E94" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F94" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G94" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H94" s="10" t="str">
-        <x:v>家族聚会上，陈国梁借哥哥陈国栋的钱买车摆阔，又多次把宴请账单推给哥哥。陈昭为保护父亲，推动聚会各自结算，并逐步揭开叔叔冒用昭源名义、组织亲友参与虚假项目的真相。身份公开后，她妥善退还款项、安排分期偿还。陈国栋学会拒绝，陈国梁放下虚荣，家族重新认识本分与担当的价值。</x:v>
+        <x:v>苏晚剖腹产坐月子期间，婆婆孙淑芬装病博同情，丈夫郭鹏程愚孝偏袒。苏晚因照顾假摔的婆婆导致刀口崩裂，看清真相后毅然提出离婚。在好友协助下，她搜集证据揭穿婆婆伪装，并果断结束婚姻。随后苏晚投身职场，为助爱人傅时衍化解公司危机，不惜抵押资产、签署苛刻合同筹措资金，最终在董事会力挽狂澜，收获事业与爱情。</x:v>
       </x:c>
       <x:c r="I94" s="10" t="str">
-        <x:v>58集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「屿风漫剧」多次产出上榜剧</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；73集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
       </x:c>
       <x:c r="J94" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -6703,10 +6701,10 @@
         <x:v>家破、失业、母亲癌症晚期——安南暖以为，回到团山村老家，只是陪家人熬过人生最黑的一段日子。可谁也没想到，一滴鲜血唤醒了床头那盆沉睡多年的枯木，从此，悄然改变了整个安家老宅的命运。破败的院子长出满园生机，病重的母亲重燃希望，沉寂多年的山村，也在她手中一点点苏醒。可灵泉带来的，从来不只是馈赠。秘密、因果、病痛、欲望，接踵而至。安南暖原本只想守住一个家，却一步步把老家打造成了人人向往的桃花源。</x:v>
       </x:c>
       <x:c r="I95" s="10" t="str">
-        <x:v>96集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；发布账号「星屿漫剧场」多次产出上榜剧</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；96集，主力长度；发布账号「星屿漫剧场」按上榜剧数入榜</x:v>
       </x:c>
       <x:c r="J95" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -6717,28 +6715,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
-        <x:v>人到中年我逆袭成百草圣手</x:v>
+        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
       </x:c>
       <x:c r="D96" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E96" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F96" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G96" s="10" t="str">
-        <x:v>极剧-热血剧场</x:v>
+        <x:v>AI便利店</x:v>
       </x:c>
       <x:c r="H96" s="10" t="str">
-        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
+        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
       </x:c>
       <x:c r="I96" s="10" t="str">
-        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「极剧-热血剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「AI便利店」</x:v>
       </x:c>
       <x:c r="J96" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -6749,28 +6747,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
-        <x:v>十灵根短命鬼？我手搓废丹成仙第九季</x:v>
+        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F97" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G97" s="10" t="str">
-        <x:v>点云动漫剧场</x:v>
+        <x:v>饭饭剧场</x:v>
       </x:c>
       <x:c r="H97" s="10" t="str">
-        <x:v>他叫叶星辰，开局只剩一个人。别人靠灵根，他靠一口破鼎。废丹炼成宝丹，废矿炼出灵脉，垃圾残卷自己补全成绝世神功。所有人都笑他活不过三集，他却把死局炼成大道。为追查长辈遗案，他被踩进泥里，几乎身死道消。别人靠天赋，他靠压榨自己，从绝境榨出生机，废墟炼出神通。宿命拦路，一鼎砸碎。必死之局，炼成通天。那口鼎还在震，他骨头里钉着一个谜。看他如何用一口气，掀翻整个天下。</x:v>
+        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「点云动漫剧场」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「饭饭剧场」</x:v>
       </x:c>
       <x:c r="J97" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -6781,28 +6779,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>御兽大陆：我的猫狗是神兽第一季</x:v>
+        <x:v>我救的父女成了我的靠山第二季</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>110</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>文心动漫</x:v>
+        <x:v>潮汐心动放映厅</x:v>
       </x:c>
       <x:c r="H98" s="10" t="str">
-        <x:v>铲屎官林霜本和自己的一猫一狗和和美美，却意外穿越御兽大陆，成为一个废材御兽师，但没人想到，她的宠物居然都穿成了上古神兽。林霜带着自己的一猫一狗，混迹宗门，众人惊异于林霜的实力，也在林霜的带领下，领悟了御兽师和兽宠之间深厚的羁绊，最终，林霜带领宗门，抵御黑暗，一切尘埃落定，带着自己的一猫一狗，在御兽大陆有了属于自己的天地。</x:v>
+        <x:v>十八年前苏云出手救下困境中的林野与女儿林诗诗。十八年后苏云挣脱险境，与已是财团董事长的林野重逢。一桩意外揭开身世秘密，林诗诗并非林野骨肉，她的生父为护林野不幸离世，生母与妹妹正深陷生活困境。林诗诗得知身世大受震动，为救治病重生母毅然捐献肝脏。历经生死磨难，她和欢喜冤家陆时宇互生爱慕。众人揭穿包工头讨回公道，抚平旧日伤痕，苏云喜得龙凤胎，两代人在烟火生活里收获圆满团圆。</x:v>
       </x:c>
       <x:c r="I98" s="10" t="str">
-        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文心动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；78集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J98" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -6813,28 +6811,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>微光知遇，包子铺的逆袭</x:v>
+        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E99" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
+        <x:v>家庭伦理 / 现实反转</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>潮汐互娱-爽剧社</x:v>
+        <x:v>云间漫剧-玉川</x:v>
       </x:c>
       <x:c r="H99" s="10" t="str">
-        <x:v>十年前大雪天，落难的林夜得到苏晴赠予的热包子，心怀感恩。多年后事业有成的林夜找到饱受亲戚欺压、生活困顿的苏晴，隐瞒身份以合伙人身份帮她重振苏记包子铺。二人携手应对经营路上的重重阻碍，，守住食品本心，把传统包子手艺做成全国连锁品牌，妹妹苏念也实现艺术理想。</x:v>
+        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
       </x:c>
       <x:c r="I99" s="10" t="str">
-        <x:v>94集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 逆袭打脸）；发布账号「潮汐互娱-爽剧社」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
       </x:c>
       <x:c r="J99" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -6845,10 +6843,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>我在工地当瓦工，反手掀了采购黑幕</x:v>
+        <x:v>三年，我不装了</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>其他</x:v>
@@ -6857,16 +6855,16 @@
         <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>云端漫剧场</x:v>
+        <x:v>布噜布噜剧场</x:v>
       </x:c>
       <x:c r="H100" s="10" t="str">
-        <x:v>瓦工出身的王大力深耕工程材料领域，不慕私利，坚守质量底线。面对职场倾轧、对手伪造证据、材料贪腐圈套，他依托完整证据链揭穿阴谋，完善采购验收制度。摒弃人情救火模式，建立权责清晰的工程管理体系，守护项目安全，维护从业者正当权益，诠释基建从业者的责任与担当。</x:v>
+        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
       </x:c>
       <x:c r="I100" s="10" t="str">
-        <x:v>88集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「云端漫剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
       </x:c>
       <x:c r="J100" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -6877,28 +6875,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>最后一个剑仙第二季</x:v>
+        <x:v>沙县厨神</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>美食治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>好个秋剧场</x:v>
+        <x:v>新视觉漫剧心动剧场</x:v>
       </x:c>
       <x:c r="H101" s="10" t="str">
-        <x:v>坦尔文明主力舰队大举入侵蓝星复仇。陈帅先以莲藕分身迎战陨灭，随即夺舍外星躯体的本尊现身，硬闯太阳核心拆解戴森球，覆灭敌舰。坦尔首领赫炎引来破军文明血狼佣兵团，陈帅不敌之际召请二郎神显圣，一枪覆灭破军文明。经此一役蓝星威震银河，灵汐女帝登门邀约陈帅代表灵汐文明，参加千年一度的银河盛会。</x:v>
+        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
       </x:c>
       <x:c r="I101" s="10" t="str">
-        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「好个秋剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
       </x:c>
       <x:c r="J101" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -6909,28 +6907,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>F级屠夫，我刀刀暴击斩神</x:v>
+        <x:v>九零绝境潮汐系统护我</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F102" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G102" s="10" t="str">
-        <x:v>寒冰剧场</x:v>
+        <x:v>杨桃剧院</x:v>
       </x:c>
       <x:c r="H102" s="10" t="str">
-        <x:v>当整个世界都依靠转职决定未来，作为优等生的我，却觉醒最低阶的F级屠夫。流言与质疑扑面而来，唯有苏婉晴坚定站在我的身旁。意外解锁暴击天赋，让我拥有突破常规的力量。我既要守护相依为命的妹妹，又要应付各方势力对自身特殊血脉的窥探。穿梭各大危险秘境，寻找上古灵药，在重重危机之下，探寻命运埋藏的真相。</x:v>
+        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
       </x:c>
       <x:c r="I102" s="10" t="str">
-        <x:v>51集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；发布账号「寒冰剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
       </x:c>
       <x:c r="J102" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -6941,28 +6939,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>三年，我不装了</x:v>
+        <x:v>予你情深，岁岁相守</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F103" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>布噜布噜剧场</x:v>
+        <x:v>啾啾说漫</x:v>
       </x:c>
       <x:c r="H103" s="10" t="str">
-        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
       </x:c>
       <x:c r="I103" s="10" t="str">
-        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「布噜布噜剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
       </x:c>
       <x:c r="J103" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -6973,28 +6971,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>下山，从一纸婚约开始</x:v>
+        <x:v>仙界老祖非要当我哥</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F104" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>洛白剧场</x:v>
+        <x:v>青青漫剧</x:v>
       </x:c>
       <x:c r="H104" s="10" t="str">
-        <x:v>鬼门传人陆凡受师娘逼迫下山，需找到天凤体女子成婚化解自身劫数。他在酒吧偶遇婚约对象苏若涵，救下遭人下药的她。陆凡前往苏家打算退婚，可苏若涵为抗拒家族安排的联姻，执意和陆凡领结婚证假结婚。苏若涵带陆凡去见另一位天凤体秦怡，两女为陆凡展开竞争。恰逢秦老爷子病危，一众名医束手无策，陆凡施展失传的鬼门十三针将其救活，展露高超医术。秦怡对陆凡心生好感，苏若涵也渐渐对陆凡动了真情，几人之间的情感拉扯就此展开。</x:v>
+        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
       </x:c>
       <x:c r="I104" s="10" t="str">
-        <x:v>151集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「洛白剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
       </x:c>
       <x:c r="J104" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -7005,10 +7003,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>不寄人间半尺光</x:v>
+        <x:v>农家穗安：饼香满镇</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>其他</x:v>
@@ -7017,16 +7015,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>奇趣漫剧场</x:v>
       </x:c>
       <x:c r="H105" s="10" t="str">
-        <x:v>苏晚剖腹产坐月子期间，婆婆孙淑芬装病博同情，丈夫郭鹏程愚孝偏袒。苏晚因照顾假摔的婆婆导致刀口崩裂，看清真相后毅然提出离婚。在好友协助下，她搜集证据揭穿婆婆伪装，并果断结束婚姻。随后苏晚投身职场，为助爱人傅时衍化解公司危机，不惜抵押资产、签署苛刻合同筹措资金，最终在董事会力挽狂澜，收获事业与爱情。</x:v>
+        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
       </x:c>
       <x:c r="I105" s="10" t="str">
-        <x:v>73集长剧集，符合起量主力区间；题材待验证；发布账号「幻境大剧场」多次产出上榜剧</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
       </x:c>
       <x:c r="J105" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -7037,28 +7035,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>九零绝境潮汐系统护我</x:v>
+        <x:v>嫡女归来，厨香撼京华</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>杨桃剧院</x:v>
+        <x:v>锦书映年华</x:v>
       </x:c>
       <x:c r="H106" s="10" t="str">
-        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
       </x:c>
       <x:c r="I106" s="10" t="str">
-        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「杨桃剧院」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
       </x:c>
       <x:c r="J106" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -7069,28 +7067,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
+        <x:v>山野新婚暖光阴</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>AI便利店</x:v>
+        <x:v>小尘剧场</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
+        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>96集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「AI便利店」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -7101,28 +7099,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>予你情深，岁岁相守</x:v>
+        <x:v>我的小土狗竟有大帝之姿</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>啾啾说漫</x:v>
+        <x:v>嘉午纪</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「啾啾说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -7133,10 +7131,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>二十八块麻辣烫，相亲男逼我领证</x:v>
+        <x:v>替嫁棺妃</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
@@ -7145,16 +7143,16 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>壹琚影视</x:v>
+        <x:v>诗婳影视</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>单亲姐姐林小圆相亲时被抠门相亲男王浩以二十八块麻辣烫为饵逼婚，王浩携母姐堵门索要钱财房产，林小圆冷静周旋，戳穿王浩临时工身份谎言，面对辱骂报警维权，最终在民警与邻居帮助下逼退男方，守护了弟弟与自己的尊严。</x:v>
+        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「壹琚影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -7165,28 +7163,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>五十岁扮穷相亲，我试出了真心</x:v>
+        <x:v>末世的最后一餐</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F110" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G110" s="10" t="str">
-        <x:v>不惧剧场</x:v>
+        <x:v>团子动漫</x:v>
       </x:c>
       <x:c r="H110" s="10" t="str">
-        <x:v>尝尽冷暖的陈牧远，为寻一份不掺杂质的真心，选择以平凡身份踏入烟火人间。风风火火的餐馆老板李珺月，以为他只是个潦倒大叔，却用她最大的真诚与善意，将“无家可归”的他热情收留。一个守护秘密，一个守护温暖，两个在尘世中各自坚韧的灵魂，在寻常日子的炊烟与暖阳里，找到了最安心的依靠。当一切真相大白，他们才明白，这世间最奢侈的幸福，从来不是财富的堆砌，而是抛开所有身份标签后，依然愿意为彼此撑伞、相守一生的真心。</x:v>
+        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>99集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「不惧剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -7197,7 +7195,7 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>京航婚事：战爷他超护短</x:v>
+        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
         <x:v>80</x:v>
@@ -7206,19 +7204,17 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str">
-        <x:v>漫剧时代</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str"/>
       <x:c r="H111" s="10" t="str">
-        <x:v>沈家突遭变故，姐妹为保家业卷入战家联姻。沈昭昭阴差阳错与“叔叔”战北渊结下隐秘婚约，沈清瓷则嫁与浪荡二少战司航。面对家族猜忌、职场倾轧与旧情纠葛，昭昭以机敏与武力护姐闯关，清瓷以魄力执掌航运。战北渊隐忍深情，暗藏“千浔”身份；昭昭步步为营，在危机中揭开幕后黑手，姐妹携手于豪门漩涡中逆风成长，守护彼此与家族。</x:v>
+        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「漫剧时代」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -7229,28 +7225,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>仙界老祖非要当我哥</x:v>
+        <x:v>被赶走的保姆，竟是真夫人</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>青青漫剧</x:v>
+        <x:v>九鲤动漫</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>61集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；发布账号「青青漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7261,28 +7257,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>保姆的亲情陷阱</x:v>
+        <x:v>七旬老太，勇闯惊悚游戏第一季</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>鸡腿剧场</x:v>
+        <x:v>新娱剧场</x:v>
       </x:c>
       <x:c r="H113" s="10" t="str">
-        <x:v>女总裁林夏夏因工作忙碌，为残疾父亲林强聘请了保姆王小梅，然而一次临时回家取文件，让她在无意中听见王小梅正在哄父亲买六千块的假药，还劝说父亲瞒着自己，林夏夏当即决定辞退王小梅。但由于父亲长期孤寂中得到王小梅的陪伴，反而对女儿恶语相向，坚称王小梅才是真心对他好的人</x:v>
+        <x:v>七十岁农村老太李树英为救孙女主动报名进入惊悚游戏，获“老当益壮”与“隔代亲光环”技能。C级副本《伯爵庄园》中，她揭穿邪神永生阴谋，终结红衣侍女。B级副本《疯镇》里，她化身李阿婆暗中助人，协助消灭疯狂源头。完美通关后声名渐起，却被总系统盯上，新副本正等待她破解。</x:v>
       </x:c>
       <x:c r="I113" s="10" t="str">
-        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 婚姻情感）；发布账号「鸡腿剧场」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J113" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8906,26 +8902,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
+        <x:v>重生之我飒爆了！第二季</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G54" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str">
+        <x:v>罗曼蒂克-海豹分镜【AI短剧】</x:v>
+      </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
+        <x:v>重生归来的林雨汐，在涉外饭店当众揭穿辱华者，拒绝用尊严换投资；她一路守护家人、揭开身世、创办药厂。与陆逸领证成婚后，空间因果降临，两人被送往末世求生。回归现实，她带着异能和新生命，却遭遇婴儿被盗，危机再起。</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
-        <x:v>57集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J54" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -8936,28 +8934,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>重生：回到1983当富翁之路第一季</x:v>
+        <x:v>后娘逆袭</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>阿水漫画</x:v>
+        <x:v>1649世界</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>上市公司执行总裁周于峰意外重回1983年。面对尚未改善的家庭关系、生活拮据的弟弟妹妹，以及处处充满机遇与挑战的时代环境。凭借多年积累的商业经验与判断力，周于峰从小生意做起，在坚守原则与规则的同时抓住时代机遇，一步步改善家人的生活，也重新审视婚姻与亲情。在改革浪潮中，他与身边的人共同成长，用一次次选择改变人生轨迹，走出属于自己的创业之路。</x:v>
+        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
-        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「阿水漫画」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；74集，主力长度；发布账号「1649世界」</x:v>
       </x:c>
       <x:c r="J55" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -8968,10 +8966,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>1970重生岁岁，不负韶华</x:v>
+        <x:v>重生八零：直上青天展宏图</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
         <x:v>其他</x:v>
@@ -8980,16 +8978,16 @@
         <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
-        <x:v>星文文化</x:v>
+        <x:v>八哥剧场</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
+        <x:v>林振东前世倾尽所有娶妻养家，辛苦半生，却发现妻子早已变心，三个养子皆是旁人骨肉。他被白眼狼子女榨干家产、狠心害死，连累至亲落得凄惨下场。带着无尽悔恨，他重生回到送彩礼定亲当天！这一世他当众怒退婚约，守护家人、斩断孽缘，凭借超前眼光，踏实创业搞钱，逆袭改写全家悲惨命运！</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str">
-        <x:v>86集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；发布账号「星文文化」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；95集，主力长度；发布账号「八哥剧场」</x:v>
       </x:c>
       <x:c r="J56" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9.5</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -9000,28 +8998,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>全校笑我铁匠，我反手锻剑娘</x:v>
+        <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>142</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G57" s="10" t="str">
-        <x:v>榴莲漫剧</x:v>
+        <x:v>芸光剧场</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>故事讲述英雄遗孤陆渊在转职仪式上觉醒最低级生活职业“铁匠”，遭受众人嘲笑，却意外激活隐藏职业“神级器灵师”。他以锻造之力创造出拥有灵智的强大器灵，一路打造剑娘、刀灵、盾灵，凭借隐藏实力横扫秘境、打破纪录、反击天才与权贵，从被轻视的废物铁匠成长为震撼世界的顶级强者。</x:v>
+        <x:v>现代中医天才林薇遭遇意外，穿越到八零年代，成为嫌贫爱富的炮灰媳妇。觉醒药圃空间，靠着药灵产出的药材食材改善生活。原本的丈夫顾深是有学识的潜力青年，林薇一改原主态度，用心经营家庭。她摆摊卖药材，抓住机遇搞大棚中草药育苗，攻克育苗难题。一边化解林蕊、孙大勇等人的不断陷害，一边带领家人奔好日子。她无私分享种植技术，获得荣誉，和顾深双向奔赴，事业爱情家庭三丰收。</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str">
-        <x:v>142集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸）；发布账号「榴莲漫剧」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「芸光剧场」</x:v>
       </x:c>
       <x:c r="J57" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -9032,28 +9030,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>八十年代：铁娘子的缝纫机逆袭路</x:v>
+        <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="G58" s="10" t="str">
-        <x:v>漫剧场小管家</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str"/>
       <x:c r="H58" s="10" t="str">
-        <x:v>八十年代改革开放初期，金枝丈夫去世后，一直与婆家同住，带着女儿过日子。面对婆家的偏心与冷眼，她从不低头，靠着一手裁缝好手艺，从走街串巷给人缝补做起。一针一线，把日子缝得踏实。从为人代工到盘下门面，金枝凭手中针线和不认输的劲头，挣出尊严，也闯出了属于自己的裁缝铺子与人生。</x:v>
+        <x:v>顾诚意外穿越至妖魔横行的乱世，开局惨遭叛徒出卖，沦为猪妖的口粮。绝境中他觉醒“氪命系统”，消耗寿元即可瞬间将武学推演至圆满境界，斩杀妖魔邪修更能夺取寿元无限续航！凭借此逆天金手指，顾诚从镇魔司底层小吏起步，一路狂斩内鬼、手撕破凡大妖、血战魔道余孽。在女修徐念雪与未婚妻林青燕的相伴下，顾诚以命为引，融合极道武学，誓要杀穿这妖邪乱世，登顶巅峰！</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str">
-        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「漫剧场小管家」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J58" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -9064,28 +9060,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>反派大佬成了女儿奴第一季</x:v>
+        <x:v>穿越古代，我靠军火建立王朝</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
-        <x:v>戏众生</x:v>
+        <x:v>热雪Ai漫剧场</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>为了糖果奖励，薄珠珠接下系统任务，要让薄宴州认下自己。她顺着纸箱空降薄氏集团。薄宴州十分抗拒，故意逗弄珠珠。可糖果的吸引力让薄珠珠不肯放弃，折返回来状况百出，系统疯狂报错，薄宴州看着古灵精怪的小团子满心审视。</x:v>
+        <x:v>现代退伍老兵陈楠意外穿越异世，开局便成杀虎口死囚。身陷绝境，他凭借随身空间、现代军备与作战经验，从牢房杀出重围，在边境战场一路崛起。当世家权贵视人命如草芥，他不再替旧秩序卖命，带领追随者建立陈家军、夺下黑石崖。冷兵器时代撞上现代火力，一介死囚，誓要重建大乾，建立属于自己的王朝！</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str">
-        <x:v>144集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理）；续季/系列续作，有前作热度背书；发布账号「戏众生」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「热雪Ai漫剧场」</x:v>
       </x:c>
       <x:c r="J59" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -9096,28 +9092,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>后娘逆袭</x:v>
+        <x:v>穿越王妃美又飒</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
-        <x:v>1649世界</x:v>
+        <x:v>羚羊AI剧场</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
+        <x:v>别人宅斗用心机，她宅斗直接掏手枪！堂堂现代蛊医传人，竟穿成任人欺凌的傻子王妃，开局就被恶毒侧妃扔进乱葬岗灭口。叶南希冷笑，空间戒指觉醒，直接掏出沙漠之鹰突突了恶奴！顺手还拿下了权倾朝野的战神镇北王。面对绿茶顶替、下人欺凌、皇家算计，她一手银针一手枪，神挡杀神！</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str">
-        <x:v>74集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「1649世界」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「羚羊AI剧场」</x:v>
       </x:c>
       <x:c r="J60" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -9128,28 +9124,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>带着仓库回七零第一季</x:v>
+        <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>无极动画</x:v>
+        <x:v>购嗨漫剧</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>1976年，沈牧野含恨重生，回到与周翠兰离婚当天。他凭穿越而来的现代仓库和前世厨艺进入钢铁厂食堂，从被刁难到凭西餐接待外宾一战成名。他先救下二姐母女，再治大姐的腿、还三姐的债，把家人一个个从苦日子里拉出来。期间，厂办秘书苏婉清一次次替他解围，两人在烟火与患难中越走越近。最后全家搬进厂区小院，枣树下，悸动暗生。</x:v>
+        <x:v>孤儿少女凌昭本是四项满S的百年天才，脑内神秘芯片吞噬她的精神力，令她沦为被众人嘲讽的废柴学员。绝境之际，她解锁脑内秘境万国狩猎场，通过试炼积攒信仰币突破变强。在异兽与强者林立的残酷竞技中，凌昭逆势翻盘，携手高冷天才萧含雪、孤勇幸存者夏明桑，冲破层层封印。她觉醒SS级天赋，执掌神剑神谕，屡破赛场纪录，打脸天骄，对抗帝国黑暗势力，从底层逆袭成最年轻战神，毅然奔赴凶险边境守护万家灯火。</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str">
-        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（年代怀旧）；续季/系列续作，有前作热度背书；发布账号「无极动画」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「购嗨漫剧」</x:v>
       </x:c>
       <x:c r="J61" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -9160,28 +9156,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>异能赶海：从失业到海洋女王第二季</x:v>
+        <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 现实反转</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>每日沙雕推荐</x:v>
+        <x:v>熊猫热剧</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>北漂失意的苏蕴舟回乡后，觉醒能看透水下的特殊能力，靠收获珍贵海产快速积累财富，买下独栋别墅，改善全家生活。她救下遭遇意外的少年陆星辰，结识商界的霍铮，二人从试探发展为合作伙伴。苏蕴舟从容应对前男友、同学带来的人际纠葛。家里日子蒸蒸日上，父亲开办海产加工坊。苏蕴舟将一批珍珠交由霍氏处理，收到拍卖会邀约，在与大海相伴的日子里，完成自我成长与人生蜕变。</x:v>
+        <x:v>沈南星意外绑定高温末世预警系统，识破闺蜜白薇谎称极寒末日、联合男友骗取她物资的圈套。在河狸系统的陪伴与协助下，她反手变卖房产囤定制冷设备与生存物资，在半山腰打造避暑堡垒，储备充足物资，搭建起净水、制冷与无土种植系统，一人一系统携手并肩安稳度过极热危机，山庄成为灾后重建核心基地，沈南星与河狸系统也结下了深厚的伙伴情谊，而背叛者也为自身的贪念与过错承担了相应的后果。</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str">
-        <x:v>122集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；68集，主力长度；发布账号「熊猫热剧」</x:v>
       </x:c>
       <x:c r="J62" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -9192,28 +9188,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>彩运照人心，第一季</x:v>
+        <x:v>借势逢生</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G63" s="10" t="str">
-        <x:v>文之江影视</x:v>
+        <x:v>虾华看漫剧</x:v>
       </x:c>
       <x:c r="H63" s="10" t="str">
-        <x:v>胡帕喜中巨额彩票，领奖当天却惨遭相恋四年的女友分手，昔日温情瞬间化为泡影。他斩断过往纠葛，毅然离职，奔赴郑州探望勤工俭学的妹妹，也因此结识了善良坚韧的梁池，两人渐生情愫。清明返乡，他冷眼看透势利亲戚的虚伪嘴脸，手握财富却选择低调行事，一心照料家人。在这冷暖交织的人情世故里，他褪去浮华，终与梁池携手，收获了一份纯粹真挚的缘分。</x:v>
+        <x:v>青苍城天才少主陆轩惨遭仇家暗算，丹田被毁沦为废人，婚约也遭林家强行逼迫退婚。绝境之中，他意外觉醒葬天坠秘境，邂逅上古强者，习得至尊剑道与不死丹神传承。陆轩借秘境机缘逆天重修，一路越级逆袭、横扫仇家，破绝境、战群雄，强势守护挚爱与家人，登顶武道巅峰！</x:v>
       </x:c>
       <x:c r="I63" s="10" t="str">
-        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；续季/系列续作，有前作热度背书；发布账号「文之江影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；发布账号「虾华看漫剧」</x:v>
       </x:c>
       <x:c r="J63" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -9224,28 +9220,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>恋上心通第一季</x:v>
+        <x:v>反派老爹不好惹</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="G64" s="10" t="str">
-        <x:v>益阳动漫</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G64" s="10" t="str"/>
       <x:c r="H64" s="10" t="str">
-        <x:v>快穿大佬叶聆刚退休就穿成恋综恶毒原配，绑定系统后惩罚竟全劈在冷漠老公谢淮舟身上，还附带感官通感！为了保命，高岭之花谢淮舟当众崩人设抢牵手、爆金币、求贴贴，全网惊呆说好的塑料夫妻呢？叶聆反骨杀疯恋综，手撕绿茶、暴揍前任、扫地出门全家奇葩。</x:v>
+        <x:v>首富沈渡穿越都市爽文，觉醒家族气运系统，为避免家破人亡命运，反套路截胡气运之子叶凡机缘。他痛改纨绔儿子沈云，斗苏家、破赌石局，屡次粉碎叶凡崛起计划。叶凡黑化搬来宗师师兄雷虎复仇，依旧被沈渡父子强势碾压，最终叶凡气运耗尽陨落。世界线自我修复，新气运之子、海外佣兵之王陈枫降临，沈家与天命的博弈再度开启。</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str">
-        <x:v>129集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「益阳动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；88集，主力长度</x:v>
       </x:c>
       <x:c r="J64" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -9256,28 +9250,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>收租精神小妹！第二季</x:v>
+        <x:v>女粉丝的救赎</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
-        <x:v>心悦漫剪</x:v>
+        <x:v>栗栗动漫</x:v>
       </x:c>
       <x:c r="H65" s="10" t="str">
-        <x:v>大厂十年，一朝被裁。林野拿着两百万补偿金回到县城，全款买了套别墅，只想安静活着。系统不让。收租万倍返还系统已激活。他盯着空荡荡的五个房间，开始琢磨怎么找租客。第一个上门的，是三个流浪到江城的精神小妹。从这天起，他的别墅再也没安静过。精神小妹、落魄富二代、跑路网红，各路奇人排着队住进来。</x:v>
+        <x:v>女主林鹿一觉醒来，穿越到自己最爱的女明星沈清秋身上，得知原主早已惨死。偶像的死并非意外，她决定替她讨回公道。面对黑料、陷害与豪门阴谋，林鹿一路反击，逐渐查出原主之死竟牵扯权氏夺权。随着调查深入，幕后真相浮出水面——权斯年为了扳倒权延修，原主不过是他路上的一颗绊脚石。为了复仇，林鹿也一步步卷入这场危险的豪门棋局。</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str">
-        <x:v>124集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「心悦漫剪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；90集，主力长度；发布账号「栗栗动漫」</x:v>
       </x:c>
       <x:c r="J65" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -9288,28 +9282,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>无心攀比，假千金重生后成团宠了</x:v>
+        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="G66" s="10" t="str">
-        <x:v>鲸跃AI剧场</x:v>
-      </x:c>
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G66" s="10" t="str"/>
       <x:c r="H66" s="10" t="str">
-        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
+        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
       </x:c>
       <x:c r="I66" s="10" t="str">
-        <x:v>100集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「鲸跃AI剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；57集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J66" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -9320,28 +9312,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>死对头校花竟是我网恋女友第二季</x:v>
+        <x:v>彪悍后妈在八零</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
-        <x:v>长鹿漫漫</x:v>
+        <x:v>玫瑰短剧.</x:v>
       </x:c>
       <x:c r="H67" s="10" t="str">
-        <x:v>网络里的温柔陪伴，与现实中的针锋相对形成奇妙反差。相识四年，他们一直是彼此最熟悉的网友，却从未想过对方就在身边。从最初的误会，到一次次相处中逐渐卸下防备，两人慢慢发现彼此不为人知的温柔一面。当四年网聊终于迎来奔现，他们才发现，那个一直陪伴自己的人，竟是现实中最意想不到的存在。一场甜蜜、欢乐又充满惊喜的青春恋爱，就此开始。</x:v>
+        <x:v>末世强者姜珠重生到1983年，替假千金嫁给乡下“拖油瓶”男人，进门就当后妈。她攥着三千块彩礼嫁入陆家，丈夫陆战竟是运输队大队长，两个继子女正遭极品亲戚虐待。她劈锁立威、铁腕掌家，凭卤味绝活逆袭省城。夫妻并肩创业，她真心焐热两个孩子，收拾贪心亲戚、揭穿假千金阴谋、打下万贯家业。穿越女强人把当好后妈活成了最飒的事业，还在烟火人间里意外收获了属于自己的小生命。</x:v>
       </x:c>
       <x:c r="I67" s="10" t="str">
-        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「长鹿漫漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；43集，次优长度；发布账号「玫瑰短剧.」</x:v>
       </x:c>
       <x:c r="J67" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -9352,10 +9344,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>浴火重生，我撕碎前夫的美梦</x:v>
+        <x:v>无心攀比，假千金重生后成团宠了</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
         <x:v>其他</x:v>
@@ -9364,16 +9356,16 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>云阅真人漫剧</x:v>
+        <x:v>鲸跃AI剧场</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>家庭主妇林晚遭丈夫陈世杰与情人苏曼背叛，更被设计坠崖毁容。死里逃生后，她继承遗产、改头换面，以资本新贵身份重返陈世杰身边，步步引他暴露贪婪与罪行。最终真相大白，林晚在顾言守护下夺回属于她的一切，迎来新生。</x:v>
+        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
       </x:c>
       <x:c r="I68" s="10" t="str">
-        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「云阅真人漫剧」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；发布账号「鲸跃AI剧场」</x:v>
       </x:c>
       <x:c r="J68" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -9384,28 +9376,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>破窑洞飞出金凤凰第一季</x:v>
+        <x:v>程家小媳不好惹第二季</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>定边同城帮</x:v>
+        <x:v>莹莹漫剧</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>李根出身贫寒，大学时与富家女苏婉晴相恋，却在订婚宴上被当众退婚羞辱。他落魄返乡，在荒山上发现野生酸枣的商机，立志创业。从承包荒山、改土育苗，到历经暴雨毁林、父亲病倒、资金断裂等重重打击，他凭一股不服输的韧劲咬牙坚持。在贵人相助和全村人的支持下，他成功将荒山变成千亩枣园，成立合作社，带领黄土坡村脱贫致富。事业有成后，他赢得真诚爱情，拒绝资本诱惑，创办农业大学，用一生诠释了什么是坚守初心，扎根土地。</x:v>
+        <x:v>现代建筑设计师意外穿越，成了古代乡村被娘家倒贴银子卖掉的傻姑娘。她被哥嫂强行塞给穷小子程风当媳妇，一睁眼就被困在破屋中无依无靠。面对贫寒的家境和未知的处境，她只能暂时装傻保命，心里却早已盘算好出路，只等程风归来揭开这场错位婚事的后续。</x:v>
       </x:c>
       <x:c r="I69" s="10" t="str">
-        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「定边同城帮」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；135集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J69" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -9416,28 +9408,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>纨绔穿越古代成就百万诗仙第一季</x:v>
+        <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>89</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>古装宫廷 / 美食治愈</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>咪漫剧场</x:v>
+        <x:v>恒漫剧场</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>现代纨绔魂穿贞观十年，成为军神李靖之孙李景安。开局揭皇榜医治长孙皇后，凭抄录千古诗词惊艳长安，诗会碾压对手一战封神。解锁硝石制冰、马蹄铁等黑科技搅动朝堂。一边当摆烂纨绔，一边搅动大唐风云，周旋世家权贵，邂逅多位佳人，在初唐掀起属于谪仙少年的传奇浪潮。</x:v>
+        <x:v>现代平凡女孩穿越成古代小商户女，靠美食系统古几位性格迥异的优质公子，在经营小吃铺的甜蜜日常中，一是微服私访的护国将军之子沈墨，表面是纨绔公子，实则武艺高强，因被奶茶惊艳而天天来蹭吃，二是当朝首辅的孙子、温润如玉的才子顾清寒，他正为招待海外使臣的宴席发愁，慕名前来求教点心，三是神秘商人裴云，看似普通富商，却总能拿出稀有食材与林小满交易，并对她展露异常执着的关心。</x:v>
       </x:c>
       <x:c r="I70" s="10" t="str">
-        <x:v>89集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「咪漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「恒漫剧场」</x:v>
       </x:c>
       <x:c r="J70" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -9448,28 +9440,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>荒岛逆袭：我成了荒岛之王</x:v>
+        <x:v>转生成鼠，气哭冷艳校花</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G71" s="10" t="str">
-        <x:v>庚庚</x:v>
+        <x:v>长夜动漫剧场</x:v>
       </x:c>
       <x:c r="H71" s="10" t="str">
-        <x:v>一场突发的海难，让公司员工陆鸣与总裁苏清寒等同事意外流落荒野孤岛。失去现代文明的庇护，习惯了优渥生活的苏清寒等人起初难以适应，依然带有职场上的刻板偏见，试图将荒野危机简单化。然而，陆鸣凭借过硬的野外求生知识与坚韧的意志，不仅成功获取了珍贵的食物和水源，还搭建起了安全的庇护所。为了整个团队的生存，陆鸣立下“按劳分配、互帮互助”的营地新规。在陆鸣的带领下，他们战胜了荒岛危机。</x:v>
+        <x:v>林一穿越成花枝鼠，觉醒吞噬进化系统，偷吃重生女帝郑依云的贡品意外被契约。他靠吞噬灵物极速进化，认赤炎神凤为义母，携手女主横扫校园、征战万国大比，一路逆袭登顶。转生老鼠，开局偷吃校花贡品的命运新局继续展开。转生老鼠，开局偷吃校花贡品的命运新局继续展开。</x:v>
       </x:c>
       <x:c r="I71" s="10" t="str">
-        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「庚庚」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「长夜动漫剧场」</x:v>
       </x:c>
       <x:c r="J71" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -9480,28 +9472,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>蓄意逐风：我在恋综称王称爸第二季</x:v>
+        <x:v>魂穿百岁老太，零零后整顿全村</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>119</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>₊⁺水蜜陶🍑剧场</x:v>
+        <x:v>筑创Ai漫剧</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>恋综游园会浪漫开启谢弥经助理刁茂巧手妆造一袭浅碧挂脖长裙惊艳全场绿毛龟轮椅依旧是她标志性座驾。沈爅卿一见盛装的谢弥眼底藏不住温柔轻声夸赞她夺目。二人扫荡美食摊位后，前去塔罗帐篷占卜谢弥一心惦记财运，顺势追问命定之人是不是沈爅卿，沈爅卿暗藏心事化身谜语人二人写下心愿纸船放入溪流，谢弥却抛下纸船直奔套圈摊位，沈爅卿含笑追赶。镜头曝光沈爅卿纸船秘密纸上赫然写着我的初恋是谢老师埋藏已久的心意悄然浮出水面。</x:v>
+        <x:v>24岁社畜林晚猝死后，穿越成顾家百岁老太太。面对极品亲戚争产、懦弱儿孙受欺、重男轻女旧俗、熟人骗局陷害、宗族道德绑架等重重困境，她以现代清醒头脑和通透智慧，一一化解危机、整顿家风，护住家人安稳。在带领全家逆袭翻身的过程中，她意外发现原主尘封半生的骨肉离别之痛。历经寻亲无果、善恶和解、遗憾释然，她最终领悟，人生无需圆满，带憾前行、温柔生活，便是重生最大的意义。</x:v>
       </x:c>
       <x:c r="I72" s="10" t="str">
-        <x:v>119集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「₊⁺水蜜陶🍑剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；40集，次优长度；发布账号「筑创Ai漫剧」</x:v>
       </x:c>
       <x:c r="J72" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -9512,28 +9504,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>跨万界穿梭！第四季</x:v>
+        <x:v>1970重生岁岁，不负韶华</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F73" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>二三漫剧</x:v>
+        <x:v>星文文化</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>大夏探索小队在冰封星球发现已灭绝的奥斯塔文明及其AI“小烛”。为获取领先百年的科技遗产，他们深入怪物巢穴夺回权限密钥，解除了AI的限制。在得知该文明因太阳被夺而毁灭后，小队决心帮助小烛延续文明火种，并带着完整的科技树返回大夏，开启了蓝星科技飞跃的新篇章。</x:v>
+        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
       </x:c>
       <x:c r="I73" s="10" t="str">
-        <x:v>168集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「二三漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；86集，主力长度；发布账号「星文文化」</x:v>
       </x:c>
       <x:c r="J73" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -9544,28 +9536,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C74" s="10" t="str">
-        <x:v>68万存款，买了一场婚姻的真相第二季</x:v>
+        <x:v>原来她从未输过</x:v>
       </x:c>
       <x:c r="D74" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E74" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F74" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G74" s="10" t="str">
-        <x:v>权策推剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H74" s="10" t="str">
-        <x:v>婚礼当天，吴子妍被丈夫一家逼签陪嫁房赠予协议，当众受辱。她当场撕毁协议、取消婚礼，却在离婚后遭遇周家霸占房产、伪造授权、私吞租金的无底线算计。从崩溃屈辱中站起，她冷静收集证据、诉诸法律，一步步追回房产与尊严。最终，周家付出代价，吴子妍拿回人生主动权，更将自己的经历化作对无数女性的边界提醒——守住底线，从不丢人。</x:v>
+        <x:v>丈夫临终将巨额股份赠予初恋，原配沈瑾看似隐忍退让，实则早已布局。在董事会关键时刻，她拿出公证遗嘱与录像证据，揭露丈夫生前设局试探真相。随着幕后黑手陆敬堂落网，沈瑾不仅守住家业，更助女儿林然顺利接班，最终母女二人迎来真正的新生与安宁。</x:v>
       </x:c>
       <x:c r="I74" s="10" t="str">
-        <x:v>135集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 现实反转）；续季/系列续作，有前作热度背书；发布账号「权策推剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度；发布账号「幻境大剧场」双口径都产爆款；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J74" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -9576,28 +9568,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C75" s="10" t="str">
-        <x:v>林国强的故事，重生80年带妻女翻身第二季</x:v>
+        <x:v>重生七零辣媳不好惹</x:v>
       </x:c>
       <x:c r="D75" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E75" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F75" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G75" s="10" t="str">
-        <x:v>每日沙雕推荐</x:v>
+        <x:v>长安漫剧社</x:v>
       </x:c>
       <x:c r="H75" s="10" t="str">
-        <x:v>林国强重生回到八零年代，开国强饭店创业起家，分家脱离原生家庭，避开前世悲剧。第二季主线事业持续扩张，处理原生家庭一堆烂摊子，妹妹遭遇家暴悲剧，兄弟姐妹各自的命运走向，拓展大棚、养鸡场、鱼塘多条产业线，同时伴随亲戚算计、婚恋风波，铺垫县城大饭庄的新事业。</x:v>
+        <x:v>现代女医生魂穿七零，成为全村唾弃的坏媳妇！醒来直接地狱开局——名声败坏，婆家刁难，还有个一心惦记的渣男前男友，丈夫周时勋对她满心嫌隙。既然占了这副身子，她绝不重蹈覆辙！怼极品、撕渣男、破流言，辣媳强势上线！高冷铁血军人周时勋，从冷眼旁观到步步沦陷，把小媳妇护在身后。贫瘠七十年代，没有开挂金手指，看盛安宁如何扭转恶名，撩动硬汉丈夫，斗渣逆袭，把苦日子过得热气腾腾！</x:v>
       </x:c>
       <x:c r="I75" s="10" t="str">
-        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 逆袭打脸）；续季/系列续作，有前作热度背书；发布账号「每日沙雕推荐」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；68集，主力长度；发布账号「长安漫剧社」</x:v>
       </x:c>
       <x:c r="J75" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -9608,28 +9600,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C76" s="10" t="str">
-        <x:v>重生觉醒，这次我不做恋爱脑第六季</x:v>
+        <x:v>初初处处藏不住</x:v>
       </x:c>
       <x:c r="D76" s="11" t="n">
-        <x:v>101</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E76" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F76" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G76" s="10" t="str">
-        <x:v>桃汁夭夭</x:v>
+        <x:v>漫小陆</x:v>
       </x:c>
       <x:c r="H76" s="10" t="str">
-        <x:v>重活一世，林雾终于看清自己的心，坚定走向始终默默守护她的徐京妄。她用一场精心准备的生日惊喜，陪他回望成长岁月，也许下长久相伴的承诺。此后，两人的感情愈发甜蜜坚定。面对家人的关注，林雾坦然表达心意，徐京妄也以真诚回应她的偏爱。林雾也在彼此陪伴与守护中不断成长，与他携手奔向明亮温暖的未来。</x:v>
+        <x:v>开局即地狱！她刚穿越就被毒哑，像牲口一样被抬去沉井！叶初初绑定吃瓜系统，却因穷得买不起道具，只能靠求生本能反杀恶奴。幸好将军哥哥及时赶到，然而她发现自己心里吐槽的心声，竟然能被特定人物听见？于是公堂之上，她一边吃瓜，一边靠心声疯狂输出信息差，全员震惊！继母丑事败露、杀母仇人当场现形</x:v>
       </x:c>
       <x:c r="I76" s="10" t="str">
-        <x:v>101集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「桃汁夭夭」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「漫小陆」</x:v>
       </x:c>
       <x:c r="J76" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -9640,28 +9632,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C77" s="10" t="str">
-        <x:v>人是诡异幼崽第二季</x:v>
+        <x:v>号外号外，团宠小师妹她又开挂了</x:v>
       </x:c>
       <x:c r="D77" s="11" t="n">
-        <x:v>116</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E77" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F77" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G77" s="10" t="str">
-        <x:v>悦禾剧场</x:v>
+        <x:v>朵粒猫AI</x:v>
       </x:c>
       <x:c r="H77" s="10" t="str">
-        <x:v>穿越者任逸一直以为自己生活在人类社会，直到毕业觉醒，才发现联盟里根本没有人类，而自己竟是披着人皮的诡异幼崽。觉醒幻术规则后，他与陆子涵进入副本实习，在一次次规则博弈中疯狂收割情绪、提升实力。随特别收割预案启动，任逸主动伪装成人类参与者潜入“陆家小院”，借直播扩大能力收益。然而瓜田、药园规则层层升级，浓雾深处的诡异梧桐与致命限制逐渐显现，一场更危险的猎杀正式开始。</x:v>
+        <x:v>现代博士蓝玥穿越成被虐的蓝府大小姐，她本想躺平当咸鱼，却被上古手镯绑定，觉醒全属性八灵根。入沧澜宗后，她凭学霸思维和嘴炮神功一路逆袭，成为全宗团宠。大师兄萧玦表面清冷实则暗中护她周全，二师兄温润如玉、四师兄阳光开朗、三师兄御兽有方，轮流为她撑腰。面对庶姐蓝舞和玄天宗的百般构陷，蓝玥用实力告诉所有人，她不是废物，是整个大陆惹不起的存在。</x:v>
       </x:c>
       <x:c r="I77" s="10" t="str">
-        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（萌宝治愈）；续季/系列续作，有前作热度背书；发布账号「悦禾剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「朵粒猫AI」</x:v>
       </x:c>
       <x:c r="J77" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -9672,28 +9664,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>修仙归来护家人第二季</x:v>
+        <x:v>山里来的小丫头，专治都市不服第三季</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>夏十七</x:v>
+        <x:v>动了个漫剧场</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
+        <x:v>被豪门未婚夫当众退婚，山里来的莫清舞却反手捏碎大劳，吓蒙全场！她不认银行卡，只认烤肠，5块救活京城首富，顺手压制顾家掌权人顾夜寒体内寒毒。从被嘲村姑到人人争抢的小神医，她靠天生神力、望气奇术一路打脸豪门、横扫黑市、硬闯秘境。七块混沌圣宝碎片背后，藏着能救心上人、也能毁灭苍生的惊天秘密。为了救顾夜寒和冷霄，她要把都市、古武、玄武大陆统统掀翻！</x:v>
       </x:c>
       <x:c r="I78" s="10" t="str">
-        <x:v>72集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「夏十七」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J78" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -9704,26 +9696,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>凡人仙鱼，混沌灵根逆袭仙途</x:v>
+        <x:v>开局成废后我反手养出十万御林军</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E79" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G79" s="10" t="str"/>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="G79" s="10" t="str">
+        <x:v>天桥热血剧场</x:v>
+      </x:c>
       <x:c r="H79" s="10" t="str">
-        <x:v>天玄宗杂役弟子许时安，因混沌废灵根被视为消耗资源的无底洞，只能在后山清理淤泥。意外之下，他在丹田中得到一只神秘黑鱼！神鱼吞吃废丹废符后，竟能吐出完美品阶的丹药符箓！自此，许时安从底层杂役逆袭，拜入仙子苏眠门下，习得上古剑法典籍《道剑十三》。秘境历练中，神鱼经历第三次进化，化为鲲之形态。面对仇人截杀与七魔将的血祭大阵，许时安以道剑十三破阵，祭出上古磨盘镇压万魔，一战封神，震惊整个天玄宗！</x:v>
+        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
       </x:c>
       <x:c r="I79" s="10" t="str">
-        <x:v>77集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 逆袭打脸 / 战神异能）；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「天桥热血剧场」</x:v>
       </x:c>
       <x:c r="J79" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -9734,28 +9728,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>凡人修仙开局捡到聚宝仙鼎第四季</x:v>
+        <x:v>捡到女帝，逆命双生第三季</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>158</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>蜗牛漫剧剧场</x:v>
+        <x:v>每日欢乐漫剧</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>全仙宗都笑凡人许长生五行杂灵根，注定困死废丹房！许长生得云瑶仙子引仙门，却沦为最低废丹房杂役，日日遭管事压榨羞辱。山洪濒死之际，天降聚宝仙鼎，废丹炼极品、残书化顶级道藏，万物经鼎皆能升华！他暗藏底牌隐忍发育，打脸欺辱自己的杂役与管事，大比惊艳全场，一跃成为内门弟子，凭一鼎之力逆转凡人身，踏破长生大道。</x:v>
+        <x:v>大夏废太子王腾落难之际觉醒签到系统，凭腹黑智谋与系统外挂扮猪吃虎，收服妖兽宗门，集结羊老头、鬼谷子、九尾天后等一众助力，和野心阴鸷的三皇子夏尤阵营展开权谋与实力的层层博弈。女主柳颜汐是瑶池女帝转世，兼具软萌娇羞与杀伐果断的极致反差，与王腾生死相伴、双向护持。最终二人携手君临天下，以世纪婚礼与天降祥瑞宣告真龙归位，全程密集打脸爽点、高甜宠妻与玄幻战斗名场面。</x:v>
       </x:c>
       <x:c r="I80" s="10" t="str">
-        <x:v>158集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「蜗牛漫剧剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；91集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J80" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -9766,28 +9760,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>别拿猪婆龙不当神兽第二季</x:v>
+        <x:v>穿回八零我凭厨艺旺翻全家</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>年代怀旧 / 美食治愈</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>与情箓</x:v>
+        <x:v>红颜剧场</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>别拿猪婆龙不当神兽第二季来袭！渡劫失败的虞柏柏被天雷劈成了一条猪婆龙（扬子鳄），在高冷影帝家里当宠物蹭吃蹭喝蹭雪饼。影帝抱着鳄鱼形态的她殷切期盼，如果你能变成虞柏柏那样的美人该有多好啊！某一天，虞柏柏实在憋不住了，在影帝怀里现出了人形，她转头看向了高冷影帝，眼神魅惑，还满意你看到的吗？没想到，高冷影帝当场垮起了脸——变回去！</x:v>
+        <x:v>现代女厨师穿越成80年代恶婆婆张桂芬，绑定灵泉空间系统，面对家徒四壁、儿媳垂危、孙女被卖的烂摊子，凭借出神入化的厨艺与灵泉水，救儿媳、赎孙女、治儿子、斗恶霸，带领全家从乡镇集市摆摊卖卤味，一路逆袭至县城开店，最终让宋家从穷困潦倒走向富足兴旺，彻底扭转恶婆之名。</x:v>
       </x:c>
       <x:c r="I81" s="10" t="str">
-        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「与情箓」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；发布账号「红颜剧场」</x:v>
       </x:c>
       <x:c r="J81" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -9798,28 +9792,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>发配充军，战神系统宁九才镇守边关第三季</x:v>
+        <x:v>重生六零之护妻猎王</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>111</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>年代怀旧 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
+        <x:v>静剧社</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>宁川重回盛京，深知大晋皇室底蕴深厚。他借力邀月公主的夺嫡之争，接连拔除多方敌对势力，依靠特殊流水线能力快速提升自身修为。尘封数百年的宁家旧仇真相大白，宁川成功为家族洗刷冤屈，扶持妹妹宁婉儿建立宁国，登临帝位。外部危机却接连爆发，柳如烟、南海海族、葬土死灵纷纷发难。宁川不断突破境界，力克强敌，收获珍贵仙种，意外寻得离开绝灵之地的线索，一场席卷天下的大乱局徐徐拉开。</x:v>
+        <x:v>顶级战神陆峥重生六零，沦为村里遭人唾弃的烂赌废物。开局债主登门，妻子沈知宁受尽欺凌、饥寒交迫。他闯风雪岭猎兽采参，凭本事碾压恶霸，靠灵芝换取身份。斗恶护妻，带领村民开荒拓路，盘活山村，逆袭过上红火安稳日子。</x:v>
       </x:c>
       <x:c r="I82" s="10" t="str">
-        <x:v>111集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；63集，主力长度；发布账号「静剧社」</x:v>
       </x:c>
       <x:c r="J82" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -9830,28 +9824,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>咱们你听心声我吃瓜，换嫁夫妻笑哈哈第二季</x:v>
+        <x:v>重生后我靠鉴宝慧眼翻身</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F83" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>每日沙雕速递</x:v>
+        <x:v>意欢剧场</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>现代穿越者裴辞镜绑定吃瓜系统，娶了拥有读心能力的沈柠欢。裴辞镜表面咸鱼，内心疯狂吃瓜吐槽，沈柠欢看破他的心声，夫妻二人默契十足。恰逢太子发动宫变，二人携手化解危机，揪出八皇子的谋划。之后裴辞镜参加科举，高中探花，入朝任职翰林院编修。侯府内部恩怨逐渐化解，沈柠悦幡然悔悟。裴辞镜入职后接到修订水利典籍的差事，还意外发现前人疑似穿越者的线索，故事暂告一段落。</x:v>
+        <x:v>孤儿林晚晚前世花光五百万装名媛，被揭穿后负债坠桥。重生回十八岁，她决心用真本事逆袭，积累资本，创立晚星珠宝鉴定工作室，招募被陷害的顶尖人才安沛，打造自主高定品牌。面对前世仇敌与同行打压，她冷静设局，在顶级晚宴上揭穿阴谋，最终收获事业、友情与自我认可。</x:v>
       </x:c>
       <x:c r="I83" s="10" t="str">
-        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 美食治愈）；续季/系列续作，有前作热度背书；发布账号「每日沙雕速递」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「意欢剧场」</x:v>
       </x:c>
       <x:c r="J83" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -9862,28 +9856,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>婚宴厅被抢，我反手告倒百亿公司</x:v>
+        <x:v>长姐归来，以爱托举全家！</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F84" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>妙手看剧</x:v>
+        <x:v>一支喵</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>许知夏筹备多年的婚宴当天，场地方突然毁约，替梁书瑶腾出主舞台。未婚夫陆远舟不仅没有替她说话，反而站到梁书瑶身边，逼她识相离场。梁家仗着百亿公司撑腰，封锁证据、操控舆论，想让她带着耻辱退场。许知夏却撕下婚纱上的花，保全合同、录音与资金记录，将婚宴变成反击的起点。她解除婚约，反手起诉梁家企业，让抢走她婚礼的人，为这场精心设计的羞辱付出代价。</x:v>
+        <x:v>现代强者叶青萝意外穿越，成为被苏家无情驱逐的假千金，一朝跌落泥泞。幸而她重回清贫的亲生叶家，解锁随身空间逆袭开挂。面对破败家境、负债困境与邻里非议，叶青萝凭借精湛厨艺、出众文笔经商创收，踏实打拼。她温柔护佑父母幼弟，化解周遭纷争，步步深耕、稳步致富，带领平凡叶家摆脱贫苦，安家立业，阖家奔赴圆满红火的人生巅峰。</x:v>
       </x:c>
       <x:c r="I84" s="10" t="str">
-        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（都市职场 / 婚姻情感 / 逆袭打脸 / 现实反转）；发布账号「妙手看剧」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「一支喵」</x:v>
       </x:c>
       <x:c r="J84" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -9894,28 +9888,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
+        <x:v>为了活命我拼命整活</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>云朵邮递员</x:v>
+        <x:v>留阿布</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
+        <x:v>62岁骚男主播吴耐意外穿越，成了重病缠身的孤寡老大爷。手握三百万存款与四套房产，却叠满肝癌晚期、重度糖尿病、脑血栓等病痛buff，生命仅剩十四天！危急时刻，惊讶系统激活只要让自家三名美女租客惊讶，就能兑换寿命续命。温柔小护士、飒爽女刑警、风情女租户轮番登场。为了活下去，吴耐花式搞事，免房租、豪掷消费、秀逆天游戏操作，不断制造名场面，一边对抗病痛，一边疯狂刷惊讶值，开启爆笑续命逆袭生活。</x:v>
       </x:c>
       <x:c r="I85" s="10" t="str">
-        <x:v>131集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 婚姻情感）；续季/系列续作，有前作热度背书；发布账号「云朵邮递员」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「留阿布」</x:v>
       </x:c>
       <x:c r="J85" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -9926,28 +9920,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
+        <x:v>婴语大师</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>平川动画</x:v>
+        <x:v>小天短剧</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
+        <x:v>18岁少女陆星辰意外觉醒“婴语翻译”系统，能听懂婴儿的每一次啼哭与呢喃。凭借这份独特天赋，她从一个普通大学生成长为京城顶级育儿专家，用爱与耐心呵护着豪门继承人们的健康成长。在数十年的守护中，陆星辰不仅用真心赢得了孩子们的依赖和全城大佬的敬重，更将这些孩子培养成三观正、有担当的栋梁之才。故事传递了“用心倾听、用爱陪伴”的育儿真谛，展现了平凡女孩凭借善良与专业逆袭人生的正能量。</x:v>
       </x:c>
       <x:c r="I86" s="10" t="str">
-        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 萌宝治愈 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「平川动画」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；65集，主力长度；发布账号「小天短剧」</x:v>
       </x:c>
       <x:c r="J86" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -9958,28 +9952,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>小满混江湖第一季</x:v>
+        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>两把刷子剧场</x:v>
+        <x:v>平川动画</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>底层客栈孤女姜小满为求生存，意外卷入烬月教阴谋，被迫顶替失踪多年的青梧派掌门义女林阿照，就此踏入一场蛰伏十六年的朝堂死局。在门派中她与心思深沉的大师兄沈砚舟步步周旋，又凭借儿时一张平安符，攀附腹黑的魔教教主谢无咎。随着旧案揭开，假身份之下牵扯出真公主的过往，侯府灭口、妃嫔算计、双生皇子秘闻接连浮现。市井孤女凭着狡黠与傲骨，游走于江湖朝堂，以袖中薄刃，搅动整片天下棋局。</x:v>
+        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
       </x:c>
       <x:c r="I87" s="10" t="str">
-        <x:v>130集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；续季/系列续作，有前作热度背书；发布账号「两把刷子剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；108集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J87" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -9990,28 +9984,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>小邪爱空姐之欢喜对头误撞心动第二季</x:v>
+        <x:v>我养的小兽怎么都成大佬了第二季</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>115</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>天才黄小邪</x:v>
+        <x:v>迷声漫剧</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>妇科医生陈北在航班上俯身帮男孩捡东西时，不慎误碰空姐陈诗瑶，被对方误会耍流氓，还闹到了警局，但最终警方证实了他的清白。这场飞机上的意外乌龙，本以为他们再无交集，可陈诗瑶却发现新租房子的房东竟然是陈北。于是两人开始同居，欢喜冤家同住一屋，从针锋相对到渐生情愫，最终甜蜜相恋、幸福相守。</x:v>
+        <x:v>赵橙知穿越星际兽世，百年前曾在废土星救下并养大五只幼兽，再睁眼却成了黑市待拍卖的F级废雌。危急关头，她唤出当年那只红狐幼崽——如今战功赫赫的归墟星将军千折意，被他强势救下护在身侧。随着校园风波迭起，白虎族首领庄九牧也认出了她的身份。昔日温顺小兽已成执掌一方的顶级大佬，百年执念与偏执守护尽数爆发，双强大佬开启极致修罗场</x:v>
       </x:c>
       <x:c r="I88" s="10" t="str">
-        <x:v>115集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；续季/系列续作，有前作热度背书；发布账号「天才黄小邪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；78集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J88" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -10022,28 +10016,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>开局成废后我反手养出十万御林军</x:v>
+        <x:v>烟火年代：我有灵泉空间第一季</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F89" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>天桥热血剧场</x:v>
+        <x:v>哒哒哒剧场</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
+        <x:v>七零年代，现代青年林墨穿越到被家人压榨迫害的知青身上，觉醒1元秒杀系统，开局秒杀储物戒。他手撕吸血原生家庭，拿到下乡名额前往极北大岭屯。一路凭借系统、念力与神级医术化解危机，结识王建军、方家姐妹。在乡村治病救人、打猎建功，周旋各方势力，对抗官场反派，积累财富与人脉，在七十年代的时代浪潮中闯出自己的一番天地。</x:v>
       </x:c>
       <x:c r="I89" s="10" t="str">
-        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「天桥热血剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J89" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -10054,28 +10048,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>心愿昭昭，神明有应第一季</x:v>
+        <x:v>修仙归来护家人第二季</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>文妃儿</x:v>
+        <x:v>夏十七</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>雾禾最大的心愿，是寻一位模样俊朗、性情体贴的夫君，陪她守着小院安稳度日。于是，她跑到山中神像前认真许愿。没过多久，风离昭便来到她身边。他会洗衣做饭，会亲手添置家用，也会把她随口说过的话放在心上，只是偶尔傲娇炸毛，格外需要人哄。雾禾以为自己只是运气好，却渐渐发现，这位夫君似乎与山中的古老传说关系匪浅。一个愿望牵起一段奇缘，两个原本孤单的人，在欢笑与陪伴中学会信任，也把平凡光景过成了温暖明亮的好日子。</x:v>
+        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
       </x:c>
       <x:c r="I90" s="10" t="str">
-        <x:v>120集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文妃儿」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；72集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J90" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -10086,28 +10080,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>我的别墅通两界，摆摊的我赚了亿点点第三季</x:v>
+        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>104</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
+        <x:v>云朵邮递员</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>陆沉玉穿梭现代与异界，壮大石牙部落，完善城防、推行识字与岗位竞选，部落蒸蒸日上。白头部落举兵进犯，被陆沉玉击溃，俘虏纳入劳动力，吴志也归降部落。陆沉玉组建华夏商队，携盐、陶器等物资远征参加部落大集，沿路收服孤山、青山等部族，收获煤炭、蜂蜜、香草荚等资源。抵达大集后，华夏部落凭借精良物资震慑各方势力，神殿假意示好，企图套取制盐、烧瓷技术，陆沉玉将计就计，带着暗藏阴谋的神殿随从踏上归途。</x:v>
+        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
       </x:c>
       <x:c r="I91" s="10" t="str">
-        <x:v>104集长剧集，符合起量主力区间；题材契合爆款主线（都市职场）；续季/系列续作，有前作热度背书；发布账号「灵梦剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；131集，次优长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J91" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -10118,28 +10112,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>我的渔船通龙宫第一季</x:v>
+        <x:v>小五替我择良缘</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>六翼动漫</x:v>
+        <x:v>一碗猫酱</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
+        <x:v>兄长出征前，留下鹦鹉小五陪伴姜疏萤。寿宴之上，养女阿娇觊觎小五，未婚夫裴渊偏帮外人，肆意放走鸟儿。姜疏萤心死决然退婚，却发现小五落入逍遥王陆砚卿手中，还提出以人换鸟。侯府内宅步步构陷，继母与父亲的阴谋层层揭开，姜疏萤携鹦鹉，在王爷相助之下，撕破虚伪假面，复仇逆袭，觅得良缘。</x:v>
       </x:c>
       <x:c r="I92" s="10" t="str">
-        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「六翼动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；53集，次优长度；发布账号「一碗猫酱」</x:v>
       </x:c>
       <x:c r="J92" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -10150,28 +10144,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>我竟是道祖之狩猎气运之子第五季</x:v>
+        <x:v>我的渔船通龙宫第一季</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>116</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>玖月说漫</x:v>
+        <x:v>六翼动漫</x:v>
       </x:c>
       <x:c r="H93" s="10" t="str">
-        <x:v>三千道州与神魔大陆相连，古族之主古乾立于时代潮头，带领族中强者踏入更广阔天地。一次跨界之行，让魅魔族迎来全新归宿，也让古族与各大道统的联系愈发紧密。古乾一边安置新族地、汇聚各方资源，一边放眼界域天骄盛会与更高层次的古洪荒。随着古雄彪等新一代天骄崭露锋芒，古族气运日盛，新的伙伴、机缘与广阔天地接连出现。</x:v>
+        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
       </x:c>
       <x:c r="I93" s="10" t="str">
-        <x:v>116集长剧集，符合起量主力区间；题材契合爆款主线（种田囤货）；续季/系列续作，有前作热度背书；发布账号「玖月说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；65集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J93" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -10182,28 +10176,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C94" s="10" t="str">
-        <x:v>人到中年我逆袭成百草圣手</x:v>
+        <x:v>不寄人间半尺光</x:v>
       </x:c>
       <x:c r="D94" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E94" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F94" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G94" s="10" t="str">
-        <x:v>极剧-热血剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H94" s="10" t="str">
-        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
+        <x:v>苏晚剖腹产坐月子期间，婆婆孙淑芬装病博同情，丈夫郭鹏程愚孝偏袒。苏晚因照顾假摔的婆婆导致刀口崩裂，看清真相后毅然提出离婚。在好友协助下，她搜集证据揭穿婆婆伪装，并果断结束婚姻。随后苏晚投身职场，为助爱人傅时衍化解公司危机，不惜抵押资产、签署苛刻合同筹措资金，最终在董事会力挽狂澜，收获事业与爱情。</x:v>
       </x:c>
       <x:c r="I94" s="10" t="str">
-        <x:v>50集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「极剧-热血剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；73集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
       </x:c>
       <x:c r="J94" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -10214,28 +10208,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C95" s="10" t="str">
-        <x:v>十灵根短命鬼？我手搓废丹成仙第九季</x:v>
+        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
       </x:c>
       <x:c r="D95" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E95" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F95" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G95" s="10" t="str">
-        <x:v>点云动漫剧场</x:v>
+        <x:v>AI便利店</x:v>
       </x:c>
       <x:c r="H95" s="10" t="str">
-        <x:v>他叫叶星辰，开局只剩一个人。别人靠灵根，他靠一口破鼎。废丹炼成宝丹，废矿炼出灵脉，垃圾残卷自己补全成绝世神功。所有人都笑他活不过三集，他却把死局炼成大道。为追查长辈遗案，他被踩进泥里，几乎身死道消。别人靠天赋，他靠压榨自己，从绝境榨出生机，废墟炼出神通。宿命拦路，一鼎砸碎。必死之局，炼成通天。那口鼎还在震，他骨头里钉着一个谜。看他如何用一口气，掀翻整个天下。</x:v>
+        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
       </x:c>
       <x:c r="I95" s="10" t="str">
-        <x:v>108集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「点云动漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「AI便利店」</x:v>
       </x:c>
       <x:c r="J95" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -10246,28 +10240,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
-        <x:v>御兽大陆：我的猫狗是神兽第一季</x:v>
+        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
       </x:c>
       <x:c r="D96" s="11" t="n">
-        <x:v>110</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E96" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F96" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G96" s="10" t="str">
-        <x:v>文心动漫</x:v>
+        <x:v>饭饭剧场</x:v>
       </x:c>
       <x:c r="H96" s="10" t="str">
-        <x:v>铲屎官林霜本和自己的一猫一狗和和美美，却意外穿越御兽大陆，成为一个废材御兽师，但没人想到，她的宠物居然都穿成了上古神兽。林霜带着自己的一猫一狗，混迹宗门，众人惊异于林霜的实力，也在林霜的带领下，领悟了御兽师和兽宠之间深厚的羁绊，最终，林霜带领宗门，抵御黑暗，一切尘埃落定，带着自己的一猫一狗，在御兽大陆有了属于自己的天地。</x:v>
+        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
       </x:c>
       <x:c r="I96" s="10" t="str">
-        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；续季/系列续作，有前作热度背书；发布账号「文心动漫」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「饭饭剧场」</x:v>
       </x:c>
       <x:c r="J96" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -10278,28 +10272,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
-        <x:v>微光知遇，包子铺的逆袭</x:v>
+        <x:v>我救的父女成了我的靠山第二季</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>94</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F97" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G97" s="10" t="str">
-        <x:v>潮汐互娱-爽剧社</x:v>
+        <x:v>潮汐心动放映厅</x:v>
       </x:c>
       <x:c r="H97" s="10" t="str">
-        <x:v>十年前大雪天，落难的林夜得到苏晴赠予的热包子，心怀感恩。多年后事业有成的林夜找到饱受亲戚欺压、生活困顿的苏晴，隐瞒身份以合伙人身份帮她重振苏记包子铺。二人携手应对经营路上的重重阻碍，，守住食品本心，把传统包子手艺做成全国连锁品牌，妹妹苏念也实现艺术理想。</x:v>
+        <x:v>十八年前苏云出手救下困境中的林野与女儿林诗诗。十八年后苏云挣脱险境，与已是财团董事长的林野重逢。一桩意外揭开身世秘密，林诗诗并非林野骨肉，她的生父为护林野不幸离世，生母与妹妹正深陷生活困境。林诗诗得知身世大受震动，为救治病重生母毅然捐献肝脏。历经生死磨难，她和欢喜冤家陆时宇互生爱慕。众人揭穿包工头讨回公道，抚平旧日伤痕，苏云喜得龙凤胎，两代人在烟火生活里收获圆满团圆。</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>94集长剧集，符合起量主力区间；题材契合爆款主线（美食治愈 / 逆袭打脸）；发布账号「潮汐互娱-爽剧社」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；78集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J97" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -10310,28 +10304,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>我在工地当瓦工，反手掀了采购黑幕</x:v>
+        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>家庭伦理 / 现实反转</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>云端漫剧场</x:v>
+        <x:v>云间漫剧-玉川</x:v>
       </x:c>
       <x:c r="H98" s="10" t="str">
-        <x:v>瓦工出身的王大力深耕工程材料领域，不慕私利，坚守质量底线。面对职场倾轧、对手伪造证据、材料贪腐圈套，他依托完整证据链揭穿阴谋，完善采购验收制度。摒弃人情救火模式，建立权责清晰的工程管理体系，守护项目安全，维护从业者正当权益，诠释基建从业者的责任与担当。</x:v>
+        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
       </x:c>
       <x:c r="I98" s="10" t="str">
-        <x:v>88集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「云端漫剧场」；剧名冲突前置、钩子强</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
       </x:c>
       <x:c r="J98" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -10342,28 +10336,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>最后一个剑仙第二季</x:v>
+        <x:v>三年，我不装了</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>110</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E99" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>好个秋剧场</x:v>
+        <x:v>布噜布噜剧场</x:v>
       </x:c>
       <x:c r="H99" s="10" t="str">
-        <x:v>坦尔文明主力舰队大举入侵蓝星复仇。陈帅先以莲藕分身迎战陨灭，随即夺舍外星躯体的本尊现身，硬闯太阳核心拆解戴森球，覆灭敌舰。坦尔首领赫炎引来破军文明血狼佣兵团，陈帅不敌之际召请二郎神显圣，一枪覆灭破军文明。经此一役蓝星威震银河，灵汐女帝登门邀约陈帅代表灵汐文明，参加千年一度的银河盛会。</x:v>
+        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
       </x:c>
       <x:c r="I99" s="10" t="str">
-        <x:v>110集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；续季/系列续作，有前作热度背书；发布账号「好个秋剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
       </x:c>
       <x:c r="J99" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -10374,28 +10368,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>F级屠夫，我刀刀暴击斩神</x:v>
+        <x:v>沙县厨神</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F100" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
+        <x:v>美食治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>寒冰剧场</x:v>
+        <x:v>新视觉漫剧心动剧场</x:v>
       </x:c>
       <x:c r="H100" s="10" t="str">
-        <x:v>当整个世界都依靠转职决定未来，作为优等生的我，却觉醒最低阶的F级屠夫。流言与质疑扑面而来，唯有苏婉晴坚定站在我的身旁。意外解锁暴击天赋，让我拥有突破常规的力量。我既要守护相依为命的妹妹，又要应付各方势力对自身特殊血脉的窥探。穿梭各大危险秘境，寻找上古灵药，在重重危机之下，探寻命运埋藏的真相。</x:v>
+        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
       </x:c>
       <x:c r="I100" s="10" t="str">
-        <x:v>51集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感 / 战神异能）；发布账号「寒冰剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
       </x:c>
       <x:c r="J100" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -10406,28 +10400,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>三年，我不装了</x:v>
+        <x:v>九零绝境潮汐系统护我</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>布噜布噜剧场</x:v>
+        <x:v>杨桃剧院</x:v>
       </x:c>
       <x:c r="H101" s="10" t="str">
-        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
       </x:c>
       <x:c r="I101" s="10" t="str">
-        <x:v>52集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸）；发布账号「布噜布噜剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
       </x:c>
       <x:c r="J101" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -10438,10 +10432,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>下山，从一纸婚约开始</x:v>
+        <x:v>予你情深，岁岁相守</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>151</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>其他</x:v>
@@ -10450,16 +10444,16 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G102" s="10" t="str">
-        <x:v>洛白剧场</x:v>
+        <x:v>啾啾说漫</x:v>
       </x:c>
       <x:c r="H102" s="10" t="str">
-        <x:v>鬼门传人陆凡受师娘逼迫下山，需找到天凤体女子成婚化解自身劫数。他在酒吧偶遇婚约对象苏若涵，救下遭人下药的她。陆凡前往苏家打算退婚，可苏若涵为抗拒家族安排的联姻，执意和陆凡领结婚证假结婚。苏若涵带陆凡去见另一位天凤体秦怡，两女为陆凡展开竞争。恰逢秦老爷子病危，一众名医束手无策，陆凡施展失传的鬼门十三针将其救活，展露高超医术。秦怡对陆凡心生好感，苏若涵也渐渐对陆凡动了真情，几人之间的情感拉扯就此展开。</x:v>
+        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
       </x:c>
       <x:c r="I102" s="10" t="str">
-        <x:v>151集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「洛白剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
       </x:c>
       <x:c r="J102" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -10470,28 +10464,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>不寄人间半尺光</x:v>
+        <x:v>仙界老祖非要当我哥</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F103" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>青青漫剧</x:v>
       </x:c>
       <x:c r="H103" s="10" t="str">
-        <x:v>苏晚剖腹产坐月子期间，婆婆孙淑芬装病博同情，丈夫郭鹏程愚孝偏袒。苏晚因照顾假摔的婆婆导致刀口崩裂，看清真相后毅然提出离婚。在好友协助下，她搜集证据揭穿婆婆伪装，并果断结束婚姻。随后苏晚投身职场，为助爱人傅时衍化解公司危机，不惜抵押资产、签署苛刻合同筹措资金，最终在董事会力挽狂澜，收获事业与爱情。</x:v>
+        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
       </x:c>
       <x:c r="I103" s="10" t="str">
-        <x:v>73集长剧集，符合起量主力区间；题材待验证；发布账号「幻境大剧场」上榜次数居前</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
       </x:c>
       <x:c r="J103" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -10502,28 +10496,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>九零绝境潮汐系统护我</x:v>
+        <x:v>农家穗安：饼香满镇</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F104" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>杨桃剧院</x:v>
+        <x:v>奇趣漫剧场</x:v>
       </x:c>
       <x:c r="H104" s="10" t="str">
-        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
       </x:c>
       <x:c r="I104" s="10" t="str">
-        <x:v>70集长剧集，符合起量主力区间；题材契合爆款主线（战神异能）；发布账号「杨桃剧院」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
       </x:c>
       <x:c r="J104" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -10534,7 +10528,7 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
+        <x:v>回乡种田，手握灵泉养全家</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
         <x:v>96</x:v>
@@ -10543,19 +10537,19 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F105" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>AI便利店</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="H105" s="10" t="str">
-        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
+        <x:v>家破、失业、母亲癌症晚期——安南暖以为，回到团山村老家，只是陪家人熬过人生最黑的一段日子。可谁也没想到，一滴鲜血唤醒了床头那盆沉睡多年的枯木，从此，悄然改变了整个安家老宅的命运。破败的院子长出满园生机，病重的母亲重燃希望，沉寂多年的山村，也在她手中一点点苏醒。可灵泉带来的，从来不只是馈赠。秘密、因果、病痛、欲望，接踵而至。安南暖原本只想守住一个家，却一步步把老家打造成了人人向往的桃花源。</x:v>
       </x:c>
       <x:c r="I105" s="10" t="str">
-        <x:v>96集长剧集，符合起量主力区间；题材契合爆款主线（逆袭打脸 / 战神异能）；发布账号「AI便利店」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；96集，主力长度；发布账号「星屿漫剧场」</x:v>
       </x:c>
       <x:c r="J105" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -10566,28 +10560,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>予你情深，岁岁相守</x:v>
+        <x:v>嫡女归来，厨香撼京华</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>啾啾说漫</x:v>
+        <x:v>锦书映年华</x:v>
       </x:c>
       <x:c r="H106" s="10" t="str">
-        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
       </x:c>
       <x:c r="I106" s="10" t="str">
-        <x:v>60集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「啾啾说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
       </x:c>
       <x:c r="J106" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -10598,7 +10592,7 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>二十八块麻辣烫，相亲男逼我领证</x:v>
+        <x:v>山野新婚暖光阴</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
         <x:v>65</x:v>
@@ -10610,16 +10604,16 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>壹琚影视</x:v>
+        <x:v>小尘剧场</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>单亲姐姐林小圆相亲时被抠门相亲男王浩以二十八块麻辣烫为饵逼婚，王浩携母姐堵门索要钱财房产，林小圆冷静周旋，戳穿王浩临时工身份谎言，面对辱骂报警维权，最终在民警与邻居帮助下逼退男方，守护了弟弟与自己的尊严。</x:v>
+        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>65集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「壹琚影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -10630,28 +10624,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>五十岁扮穷相亲，我试出了真心</x:v>
+        <x:v>我的小土狗竟有大帝之姿</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>不惧剧场</x:v>
+        <x:v>嘉午纪</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>尝尽冷暖的陈牧远，为寻一份不掺杂质的真心，选择以平凡身份踏入烟火人间。风风火火的餐馆老板李珺月，以为他只是个潦倒大叔，却用她最大的真诚与善意，将“无家可归”的他热情收留。一个守护秘密，一个守护温暖，两个在尘世中各自坚韧的灵魂，在寻常日子的炊烟与暖阳里，找到了最安心的依靠。当一切真相大白，他们才明白，这世间最奢侈的幸福，从来不是财富的堆砌，而是抛开所有身份标签后，依然愿意为彼此撑伞、相守一生的真心。</x:v>
+        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>99集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「不惧剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -10662,10 +10656,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>京航婚事：战爷他超护短</x:v>
+        <x:v>替嫁棺妃</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
@@ -10674,16 +10668,16 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>漫剧时代</x:v>
+        <x:v>诗婳影视</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>沈家突遭变故，姐妹为保家业卷入战家联姻。沈昭昭阴差阳错与“叔叔”战北渊结下隐秘婚约，沈清瓷则嫁与浪荡二少战司航。面对家族猜忌、职场倾轧与旧情纠葛，昭昭以机敏与武力护姐闯关，清瓷以魄力执掌航运。战北渊隐忍深情，暗藏“千浔”身份；昭昭步步为营，在危机中揭开幕后黑手，姐妹携手于豪门漩涡中逆风成长，守护彼此与家族。</x:v>
+        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（婚姻情感）；发布账号「漫剧时代」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -10694,28 +10688,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>亲戚聚会他摆阔，我爸不结账了</x:v>
+        <x:v>末世的最后一餐</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F110" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G110" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>团子动漫</x:v>
       </x:c>
       <x:c r="H110" s="10" t="str">
-        <x:v>家族聚会上，陈国梁借哥哥陈国栋的钱买车摆阔，又多次把宴请账单推给哥哥。陈昭为保护父亲，推动聚会各自结算，并逐步揭开叔叔冒用昭源名义、组织亲友参与虚假项目的真相。身份公开后，她妥善退还款项、安排分期偿还。陈国栋学会拒绝，陈国梁放下虚荣，家族重新认识本分与担当的价值。</x:v>
+        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>58集长剧集，符合起量主力区间；题材契合爆款主线（现实反转）；发布账号「屿风漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -10726,28 +10720,26 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>仙界老祖非要当我哥</x:v>
+        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str">
-        <x:v>青青漫剧</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str"/>
       <x:c r="H111" s="10" t="str">
-        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>61集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷 / 战神异能）；发布账号「青青漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -10758,10 +10750,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>保姆的亲情陷阱</x:v>
+        <x:v>被赶走的保姆，竟是真夫人</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
@@ -10770,16 +10762,16 @@
         <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>鸡腿剧场</x:v>
+        <x:v>九鲤动漫</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>女总裁林夏夏因工作忙碌，为残疾父亲林强聘请了保姆王小梅，然而一次临时回家取文件，让她在无意中听见王小梅正在哄父亲买六千块的假药，还劝说父亲瞒着自己，林夏夏当即决定辞退王小梅。但由于父亲长期孤寂中得到王小梅的陪伴，反而对女儿恶语相向，坚称王小梅才是真心对他好的人</x:v>
+        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>80集长剧集，符合起量主力区间；题材契合爆款主线（家庭伦理 / 婚姻情感）；发布账号「鸡腿剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -10790,28 +10782,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>入朝当女官不料皇帝喊我娘</x:v>
+        <x:v>七旬老太，勇闯惊悚游戏第一季</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>浮生观影</x:v>
+        <x:v>新娱剧场</x:v>
       </x:c>
       <x:c r="H113" s="10" t="str">
-        <x:v>十八年前夏雨兰诞下皇子遭太后狸猫换太子死里逃生。她化身女官入宫护儿媳，意外发现当今皇帝是自己亲儿。夏雨兰联手暗恋她十八年的摄政王萧凛，一边化解后宫刁难，一边深挖换子与私盐走私案。历经重重危机搜集完整证据，朝堂之上母子当众相认，反派悉数伏法。尘埃落定，夏雨兰放下皇宫荣华，与萧凛出宫共度余生。</x:v>
+        <x:v>七十岁农村老太李树英为救孙女主动报名进入惊悚游戏，获“老当益壮”与“隔代亲光环”技能。C级副本《伯爵庄园》中，她揭穿邪神永生阴谋，终结红衣侍女。B级副本《疯镇》里，她化身李阿婆暗中助人，协助消灭疯狂源头。完美通关后声名渐起，却被总系统盯上，新副本正等待她破解。</x:v>
       </x:c>
       <x:c r="I113" s="10" t="str">
-        <x:v>63集长剧集，符合起量主力区间；题材契合爆款主线（古装宫廷）；发布账号「浮生观影」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；续季/系列续作</x:v>
       </x:c>
       <x:c r="J113" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R2fbbe031d06a4b84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R6c03259b9b6342ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Radb6a72ce97346ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R1f030e7e461b4b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="Ra096e0650d664a5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R90f5bdae88e44017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R3b65405495044fa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R200d2ea7cd09440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rad738c6f8c4f4e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Raf5b4c23d7a54802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R0bbb6f95b9c44c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R486c3a9960bc4055"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5377,28 +5377,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>重生之我飒爆了！第二季</x:v>
+        <x:v>后娘逆袭</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G54" s="10" t="str">
-        <x:v>罗曼蒂克-海豹分镜【AI短剧】</x:v>
+        <x:v>1649世界</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>重生归来的林雨汐，在涉外饭店当众揭穿辱华者，拒绝用尊严换投资；她一路守护家人、揭开身世、创办药厂。与陆逸领证成婚后，空间因果降临，两人被送往末世求生。回归现实，她带着异能和新生命，却遭遇婴儿被盗，危机再起。</x:v>
+        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；74集，主力长度；发布账号「1649世界」</x:v>
       </x:c>
       <x:c r="J54" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -5409,28 +5409,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>后娘逆袭</x:v>
+        <x:v>重生八零：直上青天展宏图</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>1649世界</x:v>
+        <x:v>八哥剧场</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
+        <x:v>林振东前世倾尽所有娶妻养家，辛苦半生，却发现妻子早已变心，三个养子皆是旁人骨肉。他被白眼狼子女榨干家产、狠心害死，连累至亲落得凄惨下场。带着无尽悔恨，他重生回到送彩礼定亲当天！这一世他当众怒退婚约，守护家人、斩断孽缘，凭借超前眼光，踏实创业搞钱，逆袭改写全家悲惨命运！</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；74集，主力长度；发布账号「1649世界」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；95集，主力长度；发布账号「八哥剧场」</x:v>
       </x:c>
       <x:c r="J55" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9.5</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -5441,10 +5441,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>重生八零：直上青天展宏图</x:v>
+        <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
         <x:v>其他</x:v>
@@ -5453,16 +5453,16 @@
         <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
-        <x:v>八哥剧场</x:v>
+        <x:v>芸光剧场</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>林振东前世倾尽所有娶妻养家，辛苦半生，却发现妻子早已变心，三个养子皆是旁人骨肉。他被白眼狼子女榨干家产、狠心害死，连累至亲落得凄惨下场。带着无尽悔恨，他重生回到送彩礼定亲当天！这一世他当众怒退婚约，守护家人、斩断孽缘，凭借超前眼光，踏实创业搞钱，逆袭改写全家悲惨命运！</x:v>
+        <x:v>现代中医天才林薇遭遇意外，穿越到八零年代，成为嫌贫爱富的炮灰媳妇。觉醒药圃空间，靠着药灵产出的药材食材改善生活。原本的丈夫顾深是有学识的潜力青年，林薇一改原主态度，用心经营家庭。她摆摊卖药材，抓住机遇搞大棚中草药育苗，攻克育苗难题。一边化解林蕊、孙大勇等人的不断陷害，一边带领家人奔好日子。她无私分享种植技术，获得荣誉，和顾深双向奔赴，事业爱情家庭三丰收。</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；95集，主力长度；发布账号「八哥剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「芸光剧场」</x:v>
       </x:c>
       <x:c r="J56" s="11" t="n">
-        <x:v>9.5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -5473,25 +5473,23 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
+        <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="G57" s="10" t="str">
-        <x:v>芸光剧场</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G57" s="10" t="str"/>
       <x:c r="H57" s="10" t="str">
-        <x:v>现代中医天才林薇遭遇意外，穿越到八零年代，成为嫌贫爱富的炮灰媳妇。觉醒药圃空间，靠着药灵产出的药材食材改善生活。原本的丈夫顾深是有学识的潜力青年，林薇一改原主态度，用心经营家庭。她摆摊卖药材，抓住机遇搞大棚中草药育苗，攻克育苗难题。一边化解林蕊、孙大勇等人的不断陷害，一边带领家人奔好日子。她无私分享种植技术，获得荣誉，和顾深双向奔赴，事业爱情家庭三丰收。</x:v>
+        <x:v>顾诚意外穿越至妖魔横行的乱世，开局惨遭叛徒出卖，沦为猪妖的口粮。绝境中他觉醒“氪命系统”，消耗寿元即可瞬间将武学推演至圆满境界，斩杀妖魔邪修更能夺取寿元无限续航！凭借此逆天金手指，顾诚从镇魔司底层小吏起步，一路狂斩内鬼、手撕破凡大妖、血战魔道余孽。在女修徐念雪与未婚妻林青燕的相伴下，顾诚以命为引，融合极道武学，誓要杀穿这妖邪乱世，登顶巅峰！</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「芸光剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J57" s="11" t="n">
         <x:v>9</x:v>
@@ -5505,23 +5503,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
+        <x:v>穿越古代，我靠军火建立王朝</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G58" s="10" t="str"/>
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str">
+        <x:v>热雪Ai漫剧场</x:v>
+      </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>顾诚意外穿越至妖魔横行的乱世，开局惨遭叛徒出卖，沦为猪妖的口粮。绝境中他觉醒“氪命系统”，消耗寿元即可瞬间将武学推演至圆满境界，斩杀妖魔邪修更能夺取寿元无限续航！凭借此逆天金手指，顾诚从镇魔司底层小吏起步，一路狂斩内鬼、手撕破凡大妖、血战魔道余孽。在女修徐念雪与未婚妻林青燕的相伴下，顾诚以命为引，融合极道武学，誓要杀穿这妖邪乱世，登顶巅峰！</x:v>
+        <x:v>现代退伍老兵陈楠意外穿越异世，开局便成杀虎口死囚。身陷绝境，他凭借随身空间、现代军备与作战经验，从牢房杀出重围，在边境战场一路崛起。当世家权贵视人命如草芥，他不再替旧秩序卖命，带领追随者建立陈家军、夺下黑石崖。冷兵器时代撞上现代火力，一介死囚，誓要重建大乾，建立属于自己的王朝！</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「热雪Ai漫剧场」</x:v>
       </x:c>
       <x:c r="J58" s="11" t="n">
         <x:v>9</x:v>
@@ -5535,25 +5535,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>穿越古代，我靠军火建立王朝</x:v>
+        <x:v>穿越王妃美又飒</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
-        <x:v>热雪Ai漫剧场</x:v>
+        <x:v>羚羊AI剧场</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>现代退伍老兵陈楠意外穿越异世，开局便成杀虎口死囚。身陷绝境，他凭借随身空间、现代军备与作战经验，从牢房杀出重围，在边境战场一路崛起。当世家权贵视人命如草芥，他不再替旧秩序卖命，带领追随者建立陈家军、夺下黑石崖。冷兵器时代撞上现代火力，一介死囚，誓要重建大乾，建立属于自己的王朝！</x:v>
+        <x:v>别人宅斗用心机，她宅斗直接掏手枪！堂堂现代蛊医传人，竟穿成任人欺凌的傻子王妃，开局就被恶毒侧妃扔进乱葬岗灭口。叶南希冷笑，空间戒指觉醒，直接掏出沙漠之鹰突突了恶奴！顺手还拿下了权倾朝野的战神镇北王。面对绿茶顶替、下人欺凌、皇家算计，她一手银针一手枪，神挡杀神！</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「热雪Ai漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「羚羊AI剧场」</x:v>
       </x:c>
       <x:c r="J59" s="11" t="n">
         <x:v>9</x:v>
@@ -5567,25 +5567,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>穿越王妃美又飒</x:v>
+        <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
-        <x:v>羚羊AI剧场</x:v>
+        <x:v>购嗨漫剧</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>别人宅斗用心机，她宅斗直接掏手枪！堂堂现代蛊医传人，竟穿成任人欺凌的傻子王妃，开局就被恶毒侧妃扔进乱葬岗灭口。叶南希冷笑，空间戒指觉醒，直接掏出沙漠之鹰突突了恶奴！顺手还拿下了权倾朝野的战神镇北王。面对绿茶顶替、下人欺凌、皇家算计，她一手银针一手枪，神挡杀神！</x:v>
+        <x:v>孤儿少女凌昭本是四项满S的百年天才，脑内神秘芯片吞噬她的精神力，令她沦为被众人嘲讽的废柴学员。绝境之际，她解锁脑内秘境万国狩猎场，通过试炼积攒信仰币突破变强。在异兽与强者林立的残酷竞技中，凌昭逆势翻盘，携手高冷天才萧含雪、孤勇幸存者夏明桑，冲破层层封印。她觉醒SS级天赋，执掌神剑神谕，屡破赛场纪录，打脸天骄，对抗帝国黑暗势力，从底层逆袭成最年轻战神，毅然奔赴凶险边境守护万家灯火。</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「羚羊AI剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「购嗨漫剧」</x:v>
       </x:c>
       <x:c r="J60" s="11" t="n">
         <x:v>9</x:v>
@@ -5599,25 +5599,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
+        <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 现实反转</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>购嗨漫剧</x:v>
+        <x:v>熊猫热剧</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>孤儿少女凌昭本是四项满S的百年天才，脑内神秘芯片吞噬她的精神力，令她沦为被众人嘲讽的废柴学员。绝境之际，她解锁脑内秘境万国狩猎场，通过试炼积攒信仰币突破变强。在异兽与强者林立的残酷竞技中，凌昭逆势翻盘，携手高冷天才萧含雪、孤勇幸存者夏明桑，冲破层层封印。她觉醒SS级天赋，执掌神剑神谕，屡破赛场纪录，打脸天骄，对抗帝国黑暗势力，从底层逆袭成最年轻战神，毅然奔赴凶险边境守护万家灯火。</x:v>
+        <x:v>沈南星意外绑定高温末世预警系统，识破闺蜜白薇谎称极寒末日、联合男友骗取她物资的圈套。在河狸系统的陪伴与协助下，她反手变卖房产囤定制冷设备与生存物资，在半山腰打造避暑堡垒，储备充足物资，搭建起净水、制冷与无土种植系统，一人一系统携手并肩安稳度过极热危机，山庄成为灾后重建核心基地，沈南星与河狸系统也结下了深厚的伙伴情谊，而背叛者也为自身的贪念与过错承担了相应的后果。</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「购嗨漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；68集，主力长度；发布账号「熊猫热剧」</x:v>
       </x:c>
       <x:c r="J61" s="11" t="n">
         <x:v>9</x:v>
@@ -5631,28 +5631,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
+        <x:v>借势逢生</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>逆袭打脸 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>熊猫热剧</x:v>
+        <x:v>虾华看漫剧</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>沈南星意外绑定高温末世预警系统，识破闺蜜白薇谎称极寒末日、联合男友骗取她物资的圈套。在河狸系统的陪伴与协助下，她反手变卖房产囤定制冷设备与生存物资，在半山腰打造避暑堡垒，储备充足物资，搭建起净水、制冷与无土种植系统，一人一系统携手并肩安稳度过极热危机，山庄成为灾后重建核心基地，沈南星与河狸系统也结下了深厚的伙伴情谊，而背叛者也为自身的贪念与过错承担了相应的后果。</x:v>
+        <x:v>青苍城天才少主陆轩惨遭仇家暗算，丹田被毁沦为废人，婚约也遭林家强行逼迫退婚。绝境之中，他意外觉醒葬天坠秘境，邂逅上古强者，习得至尊剑道与不死丹神传承。陆轩借秘境机缘逆天重修，一路越级逆袭、横扫仇家，破绝境、战群雄，强势守护挚爱与家人，登顶武道巅峰！</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；68集，主力长度；发布账号「熊猫热剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；发布账号「虾华看漫剧」</x:v>
       </x:c>
       <x:c r="J62" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -5663,28 +5663,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>误惹京华第二季</x:v>
+        <x:v>反派老爹不好惹</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G63" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G63" s="10" t="str"/>
       <x:c r="H63" s="10" t="str">
-        <x:v>面对婚姻背叛与有毒亲情，坚韧的女性姜辞忧毅然决然的断亲独立，凭实力职场逆袭的故事。在自我救赎路上，她与深情守护的真爱薄靳修携手击碎阴谋；更在历经千帆后与生母温馨和解，传递出当代女性自强不息、温暖治愈的硬核力量！</x:v>
+        <x:v>首富沈渡穿越都市爽文，觉醒家族气运系统，为避免家破人亡命运，反套路截胡气运之子叶凡机缘。他痛改纨绔儿子沈云，斗苏家、破赌石局，屡次粉碎叶凡崛起计划。叶凡黑化搬来宗师师兄雷虎复仇，依旧被沈渡父子强势碾压，最终叶凡气运耗尽陨落。世界线自我修复，新气运之子、海外佣兵之王陈枫降临，沈家与天命的博弈再度开启。</x:v>
       </x:c>
       <x:c r="I63" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；126集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；88集，主力长度</x:v>
       </x:c>
       <x:c r="J63" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -5695,10 +5693,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>借势逢生</x:v>
+        <x:v>女粉丝的救赎</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
         <x:v>其他</x:v>
@@ -5707,13 +5705,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G64" s="10" t="str">
-        <x:v>虾华看漫剧</x:v>
+        <x:v>栗栗动漫</x:v>
       </x:c>
       <x:c r="H64" s="10" t="str">
-        <x:v>青苍城天才少主陆轩惨遭仇家暗算，丹田被毁沦为废人，婚约也遭林家强行逼迫退婚。绝境之中，他意外觉醒葬天坠秘境，邂逅上古强者，习得至尊剑道与不死丹神传承。陆轩借秘境机缘逆天重修，一路越级逆袭、横扫仇家，破绝境、战群雄，强势守护挚爱与家人，登顶武道巅峰！</x:v>
+        <x:v>女主林鹿一觉醒来，穿越到自己最爱的女明星沈清秋身上，得知原主早已惨死。偶像的死并非意外，她决定替她讨回公道。面对黑料、陷害与豪门阴谋，林鹿一路反击，逐渐查出原主之死竟牵扯权氏夺权。随着调查深入，幕后真相浮出水面——权斯年为了扳倒权延修，原主不过是他路上的一颗绊脚石。为了复仇，林鹿也一步步卷入这场危险的豪门棋局。</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；发布账号「虾华看漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；90集，主力长度；发布账号「栗栗动漫」</x:v>
       </x:c>
       <x:c r="J64" s="11" t="n">
         <x:v>8</x:v>
@@ -5727,23 +5725,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>反派老爹不好惹</x:v>
+        <x:v>彪悍后妈在八零</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="G65" s="10" t="str"/>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
+      </x:c>
+      <x:c r="G65" s="10" t="str">
+        <x:v>玫瑰短剧.</x:v>
+      </x:c>
       <x:c r="H65" s="10" t="str">
-        <x:v>首富沈渡穿越都市爽文，觉醒家族气运系统，为避免家破人亡命运，反套路截胡气运之子叶凡机缘。他痛改纨绔儿子沈云，斗苏家、破赌石局，屡次粉碎叶凡崛起计划。叶凡黑化搬来宗师师兄雷虎复仇，依旧被沈渡父子强势碾压，最终叶凡气运耗尽陨落。世界线自我修复，新气运之子、海外佣兵之王陈枫降临，沈家与天命的博弈再度开启。</x:v>
+        <x:v>末世强者姜珠重生到1983年，替假千金嫁给乡下“拖油瓶”男人，进门就当后妈。她攥着三千块彩礼嫁入陆家，丈夫陆战竟是运输队大队长，两个继子女正遭极品亲戚虐待。她劈锁立威、铁腕掌家，凭卤味绝活逆袭省城。夫妻并肩创业，她真心焐热两个孩子，收拾贪心亲戚、揭穿假千金阴谋、打下万贯家业。穿越女强人把当好后妈活成了最飒的事业，还在烟火人间里意外收获了属于自己的小生命。</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；88集，主力长度</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；43集，次优长度；发布账号「玫瑰短剧.」</x:v>
       </x:c>
       <x:c r="J65" s="11" t="n">
         <x:v>8</x:v>
@@ -5757,25 +5757,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>女粉丝的救赎</x:v>
+        <x:v>无心攀比，假千金重生后成团宠了</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G66" s="10" t="str">
-        <x:v>栗栗动漫</x:v>
+        <x:v>鲸跃AI剧场</x:v>
       </x:c>
       <x:c r="H66" s="10" t="str">
-        <x:v>女主林鹿一觉醒来，穿越到自己最爱的女明星沈清秋身上，得知原主早已惨死。偶像的死并非意外，她决定替她讨回公道。面对黑料、陷害与豪门阴谋，林鹿一路反击，逐渐查出原主之死竟牵扯权氏夺权。随着调查深入，幕后真相浮出水面——权斯年为了扳倒权延修，原主不过是他路上的一颗绊脚石。为了复仇，林鹿也一步步卷入这场危险的豪门棋局。</x:v>
+        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
       </x:c>
       <x:c r="I66" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；90集，主力长度；发布账号「栗栗动漫」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；发布账号「鲸跃AI剧场」</x:v>
       </x:c>
       <x:c r="J66" s="11" t="n">
         <x:v>8</x:v>
@@ -5789,23 +5789,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
+        <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G67" s="10" t="str"/>
+        <x:v>古装宫廷 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="G67" s="10" t="str">
+        <x:v>恒漫剧场</x:v>
+      </x:c>
       <x:c r="H67" s="10" t="str">
-        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
+        <x:v>现代平凡女孩穿越成古代小商户女，靠美食系统古几位性格迥异的优质公子，在经营小吃铺的甜蜜日常中，一是微服私访的护国将军之子沈墨，表面是纨绔公子，实则武艺高强，因被奶茶惊艳而天天来蹭吃，二是当朝首辅的孙子、温润如玉的才子顾清寒，他正为招待海外使臣的宴席发愁，慕名前来求教点心，三是神秘商人裴云，看似普通富商，却总能拿出稀有食材与林小满交易，并对她展露异常执着的关心。</x:v>
       </x:c>
       <x:c r="I67" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；57集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「恒漫剧场」</x:v>
       </x:c>
       <x:c r="J67" s="11" t="n">
         <x:v>8</x:v>
@@ -5819,25 +5821,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>彪悍后妈在八零</x:v>
+        <x:v>转生成鼠，气哭冷艳校花</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>年代怀旧 / 家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>玫瑰短剧.</x:v>
+        <x:v>长夜动漫剧场</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>末世强者姜珠重生到1983年，替假千金嫁给乡下“拖油瓶”男人，进门就当后妈。她攥着三千块彩礼嫁入陆家，丈夫陆战竟是运输队大队长，两个继子女正遭极品亲戚虐待。她劈锁立威、铁腕掌家，凭卤味绝活逆袭省城。夫妻并肩创业，她真心焐热两个孩子，收拾贪心亲戚、揭穿假千金阴谋、打下万贯家业。穿越女强人把当好后妈活成了最飒的事业，还在烟火人间里意外收获了属于自己的小生命。</x:v>
+        <x:v>林一穿越成花枝鼠，觉醒吞噬进化系统，偷吃重生女帝郑依云的贡品意外被契约。他靠吞噬灵物极速进化，认赤炎神凤为义母，携手女主横扫校园、征战万国大比，一路逆袭登顶。转生老鼠，开局偷吃校花贡品的命运新局继续展开。转生老鼠，开局偷吃校花贡品的命运新局继续展开。</x:v>
       </x:c>
       <x:c r="I68" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；43集，次优长度；发布账号「玫瑰短剧.」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「长夜动漫剧场」</x:v>
       </x:c>
       <x:c r="J68" s="11" t="n">
         <x:v>8</x:v>
@@ -5851,25 +5853,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>无心攀比，假千金重生后成团宠了</x:v>
+        <x:v>魂穿百岁老太，零零后整顿全村</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F69" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>鲸跃AI剧场</x:v>
+        <x:v>筑创Ai漫剧</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
+        <x:v>24岁社畜林晚猝死后，穿越成顾家百岁老太太。面对极品亲戚争产、懦弱儿孙受欺、重男轻女旧俗、熟人骗局陷害、宗族道德绑架等重重困境，她以现代清醒头脑和通透智慧，一一化解危机、整顿家风，护住家人安稳。在带领全家逆袭翻身的过程中，她意外发现原主尘封半生的骨肉离别之痛。历经寻亲无果、善恶和解、遗憾释然，她最终领悟，人生无需圆满，带憾前行、温柔生活，便是重生最大的意义。</x:v>
       </x:c>
       <x:c r="I69" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；发布账号「鲸跃AI剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；40集，次优长度；发布账号「筑创Ai漫剧」</x:v>
       </x:c>
       <x:c r="J69" s="11" t="n">
         <x:v>8</x:v>
@@ -5883,28 +5885,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>程家小媳不好惹第二季</x:v>
+        <x:v>1970重生岁岁，不负韶华</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>莹莹漫剧</x:v>
+        <x:v>星文文化</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>现代建筑设计师意外穿越，成了古代乡村被娘家倒贴银子卖掉的傻姑娘。她被哥嫂强行塞给穷小子程风当媳妇，一睁眼就被困在破屋中无依无靠。面对贫寒的家境和未知的处境，她只能暂时装傻保命，心里却早已盘算好出路，只等程风归来揭开这场错位婚事的后续。</x:v>
+        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
       </x:c>
       <x:c r="I70" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；135集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；86集，主力长度；发布账号「星文文化」</x:v>
       </x:c>
       <x:c r="J70" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -5915,28 +5917,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
+        <x:v>剑心被夺后，我神魔同体！</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>古装宫廷 / 美食治愈</x:v>
-      </x:c>
-      <x:c r="G71" s="10" t="str">
-        <x:v>恒漫剧场</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G71" s="10" t="str"/>
       <x:c r="H71" s="10" t="str">
-        <x:v>现代平凡女孩穿越成古代小商户女，靠美食系统古几位性格迥异的优质公子，在经营小吃铺的甜蜜日常中，一是微服私访的护国将军之子沈墨，表面是纨绔公子，实则武艺高强，因被奶茶惊艳而天天来蹭吃，二是当朝首辅的孙子、温润如玉的才子顾清寒，他正为招待海外使臣的宴席发愁，慕名前来求教点心，三是神秘商人裴云，看似普通富商，却总能拿出稀有食材与林小满交易，并对她展露异常执着的关心。</x:v>
+        <x:v>太虚宫首席云青瑶遭未婚夫林修远、师妹白芷焉联手背叛，被夺玲珑剑心、废丹田弃尸葬神崖。她饮万毒蚀骨汤，修成万古毒体，化名凌瑶强势归来。一路打脸渣男贱女，夺回剑心，觉醒魔尊血脉，神魔同体举世无敌。昔日欺她负她者，皆被她狠狠清算，宗门跪求原谅她不屑一顾。最终她平定天魔浩劫，以身补天，受万宗朝拜，与常渊大婚飞升，谱写万古传奇。</x:v>
       </x:c>
       <x:c r="I71" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「恒漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；58集，次优长度；通用受众</x:v>
       </x:c>
       <x:c r="J71" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -5947,28 +5947,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>转生成鼠，气哭冷艳校花</x:v>
+        <x:v>哥哥争宠我富家天下兄妹绑错系统爆红了</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 古装宫廷 / 婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>长夜动漫剧场</x:v>
+        <x:v>虾饭桶</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>林一穿越成花枝鼠，觉醒吞噬进化系统，偷吃重生女帝郑依云的贡品意外被契约。他靠吞噬灵物极速进化，认赤炎神凤为义母，携手女主横扫校园、征战万国大比，一路逆袭登顶。转生老鼠，开局偷吃校花贡品的命运新局继续展开。转生老鼠，开局偷吃校花贡品的命运新局继续展开。</x:v>
+        <x:v>女总裁虾明月和她亲哥虾明理，穿越成大雍国巨贪丞相的儿女。最离谱的是，兄妹俩绑错了系统。她哥虾明理被绑定了女频宫斗系统，而虾明月则绑定男频败家系统，要求散尽贪官爹的小金库，护国安民。看兄妹联手，如何挽回口碑震惊满朝文武。</x:v>
       </x:c>
       <x:c r="I72" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「长夜动漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；130集，次优长度；发布账号「虾饭桶」</x:v>
       </x:c>
       <x:c r="J72" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -5979,10 +5979,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>魂穿百岁老太，零零后整顿全村</x:v>
+        <x:v>祖传铜勺，我靠火锅干翻联盟</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
         <x:v>其他</x:v>
@@ -5991,16 +5991,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>筑创Ai漫剧</x:v>
+        <x:v>趣创短剧</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>24岁社畜林晚猝死后，穿越成顾家百岁老太太。面对极品亲戚争产、懦弱儿孙受欺、重男轻女旧俗、熟人骗局陷害、宗族道德绑架等重重困境，她以现代清醒头脑和通透智慧，一一化解危机、整顿家风，护住家人安稳。在带领全家逆袭翻身的过程中，她意外发现原主尘封半生的骨肉离别之痛。历经寻亲无果、善恶和解、遗憾释然，她最终领悟，人生无需圆满，带憾前行、温柔生活，便是重生最大的意义。</x:v>
+        <x:v>90年代，陈川订婚当日被未婚妻当众退婚，火锅店面临关店危机。绝境下，铜勺里的熊猫精被唤醒，将古法火锅秘方传给陈川，前来寻衅的混混刀哥被火锅美味所折服，归顺为陈川的小弟。熊猫精告知陈川，老店镇守美食龙脉，极恶联盟靠化工调料摧毁本土风味，他父亲更是遭联盟暗害，唯有集齐九大绝世食材才能修复龙脉。陈川带着温夕、刀哥踏上寻找食材之路，一路对抗联盟设下的毒瘴等陷阱，集齐食材，赢得厨艺比赛，将中华美食发扬光大。</x:v>
       </x:c>
       <x:c r="I73" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；40集，次优长度；发布账号「筑创Ai漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；79集，主力长度；发布账号「趣创短剧」</x:v>
       </x:c>
       <x:c r="J73" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -6139,25 +6139,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>山里来的小丫头，专治都市不服第三季</x:v>
+        <x:v>开局成废后我反手养出十万御林军</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>动了个漫剧场</x:v>
+        <x:v>天桥热血剧场</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>被豪门未婚夫当众退婚，山里来的莫清舞却反手捏碎大劳，吓蒙全场！她不认银行卡，只认烤肠，5块救活京城首富，顺手压制顾家掌权人顾夜寒体内寒毒。从被嘲村姑到人人争抢的小神医，她靠天生神力、望气奇术一路打脸豪门、横扫黑市、硬闯秘境。七块混沌圣宝碎片背后，藏着能救心上人、也能毁灭苍生的惊天秘密。为了救顾夜寒和冷霄，她要把都市、古武、玄武大陆统统掀翻！</x:v>
+        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
       </x:c>
       <x:c r="I78" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「天桥热血剧场」</x:v>
       </x:c>
       <x:c r="J78" s="11" t="n">
         <x:v>9</x:v>
@@ -6171,7 +6171,7 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>开局成废后我反手养出十万御林军</x:v>
+        <x:v>穿回八零我凭厨艺旺翻全家</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
         <x:v>70</x:v>
@@ -6180,16 +6180,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>年代怀旧 / 美食治愈</x:v>
       </x:c>
       <x:c r="G79" s="10" t="str">
-        <x:v>天桥热血剧场</x:v>
+        <x:v>红颜剧场</x:v>
       </x:c>
       <x:c r="H79" s="10" t="str">
-        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
+        <x:v>现代女厨师穿越成80年代恶婆婆张桂芬，绑定灵泉空间系统，面对家徒四壁、儿媳垂危、孙女被卖的烂摊子，凭借出神入化的厨艺与灵泉水，救儿媳、赎孙女、治儿子、斗恶霸，带领全家从乡镇集市摆摊卖卤味，一路逆袭至县城开店，最终让宋家从穷困潦倒走向富足兴旺，彻底扭转恶婆之名。</x:v>
       </x:c>
       <x:c r="I79" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「天桥热血剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；发布账号「红颜剧场」</x:v>
       </x:c>
       <x:c r="J79" s="11" t="n">
         <x:v>9</x:v>
@@ -6203,25 +6203,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>捡到女帝，逆命双生第三季</x:v>
+        <x:v>重生六零之护妻猎王</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>年代怀旧 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>每日欢乐漫剧</x:v>
+        <x:v>静剧社</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>大夏废太子王腾落难之际觉醒签到系统，凭腹黑智谋与系统外挂扮猪吃虎，收服妖兽宗门，集结羊老头、鬼谷子、九尾天后等一众助力，和野心阴鸷的三皇子夏尤阵营展开权谋与实力的层层博弈。女主柳颜汐是瑶池女帝转世，兼具软萌娇羞与杀伐果断的极致反差，与王腾生死相伴、双向护持。最终二人携手君临天下，以世纪婚礼与天降祥瑞宣告真龙归位，全程密集打脸爽点、高甜宠妻与玄幻战斗名场面。</x:v>
+        <x:v>顶级战神陆峥重生六零，沦为村里遭人唾弃的烂赌废物。开局债主登门，妻子沈知宁受尽欺凌、饥寒交迫。他闯风雪岭猎兽采参，凭本事碾压恶霸，靠灵芝换取身份。斗恶护妻，带领村民开荒拓路，盘活山村，逆袭过上红火安稳日子。</x:v>
       </x:c>
       <x:c r="I80" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；91集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；63集，主力长度；发布账号「静剧社」</x:v>
       </x:c>
       <x:c r="J80" s="11" t="n">
         <x:v>9</x:v>
@@ -6235,7 +6235,7 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>穿回八零我凭厨艺旺翻全家</x:v>
+        <x:v>重生后我靠鉴宝慧眼翻身</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
         <x:v>70</x:v>
@@ -6244,16 +6244,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>年代怀旧 / 美食治愈</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>红颜剧场</x:v>
+        <x:v>意欢剧场</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>现代女厨师穿越成80年代恶婆婆张桂芬，绑定灵泉空间系统，面对家徒四壁、儿媳垂危、孙女被卖的烂摊子，凭借出神入化的厨艺与灵泉水，救儿媳、赎孙女、治儿子、斗恶霸，带领全家从乡镇集市摆摊卖卤味，一路逆袭至县城开店，最终让宋家从穷困潦倒走向富足兴旺，彻底扭转恶婆之名。</x:v>
+        <x:v>孤儿林晚晚前世花光五百万装名媛，被揭穿后负债坠桥。重生回十八岁，她决心用真本事逆袭，积累资本，创立晚星珠宝鉴定工作室，招募被陷害的顶尖人才安沛，打造自主高定品牌。面对前世仇敌与同行打压，她冷静设局，在顶级晚宴上揭穿阴谋，最终收获事业、友情与自我认可。</x:v>
       </x:c>
       <x:c r="I81" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；发布账号「红颜剧场」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「意欢剧场」</x:v>
       </x:c>
       <x:c r="J81" s="11" t="n">
         <x:v>9</x:v>
@@ -6267,25 +6267,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>重生六零之护妻猎王</x:v>
+        <x:v>长姐归来，以爱托举全家！</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>年代怀旧 / 婚姻情感</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>静剧社</x:v>
+        <x:v>一支喵</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>顶级战神陆峥重生六零，沦为村里遭人唾弃的烂赌废物。开局债主登门，妻子沈知宁受尽欺凌、饥寒交迫。他闯风雪岭猎兽采参，凭本事碾压恶霸，靠灵芝换取身份。斗恶护妻，带领村民开荒拓路，盘活山村，逆袭过上红火安稳日子。</x:v>
+        <x:v>现代强者叶青萝意外穿越，成为被苏家无情驱逐的假千金，一朝跌落泥泞。幸而她重回清贫的亲生叶家，解锁随身空间逆袭开挂。面对破败家境、负债困境与邻里非议，叶青萝凭借精湛厨艺、出众文笔经商创收，踏实打拼。她温柔护佑父母幼弟，化解周遭纷争，步步深耕、稳步致富，带领平凡叶家摆脱贫苦，安家立业，阖家奔赴圆满红火的人生巅峰。</x:v>
       </x:c>
       <x:c r="I82" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；63集，主力长度；发布账号「静剧社」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「一支喵」</x:v>
       </x:c>
       <x:c r="J82" s="11" t="n">
         <x:v>9</x:v>
@@ -6299,28 +6299,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>重生后我靠鉴宝慧眼翻身</x:v>
+        <x:v>为了活命我拼命整活</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F83" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>意欢剧场</x:v>
+        <x:v>留阿布</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>孤儿林晚晚前世花光五百万装名媛，被揭穿后负债坠桥。重生回十八岁，她决心用真本事逆袭，积累资本，创立晚星珠宝鉴定工作室，招募被陷害的顶尖人才安沛，打造自主高定品牌。面对前世仇敌与同行打压，她冷静设局，在顶级晚宴上揭穿阴谋，最终收获事业、友情与自我认可。</x:v>
+        <x:v>62岁骚男主播吴耐意外穿越，成了重病缠身的孤寡老大爷。手握三百万存款与四套房产，却叠满肝癌晚期、重度糖尿病、脑血栓等病痛buff，生命仅剩十四天！危急时刻，惊讶系统激活只要让自家三名美女租客惊讶，就能兑换寿命续命。温柔小护士、飒爽女刑警、风情女租户轮番登场。为了活下去，吴耐花式搞事，免房租、豪掷消费、秀逆天游戏操作，不断制造名场面，一边对抗病痛，一边疯狂刷惊讶值，开启爆笑续命逆袭生活。</x:v>
       </x:c>
       <x:c r="I83" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「意欢剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「留阿布」</x:v>
       </x:c>
       <x:c r="J83" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -6331,28 +6331,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>长姐归来，以爱托举全家！</x:v>
+        <x:v>婴语大师</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F84" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>一支喵</x:v>
+        <x:v>小天短剧</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>现代强者叶青萝意外穿越，成为被苏家无情驱逐的假千金，一朝跌落泥泞。幸而她重回清贫的亲生叶家，解锁随身空间逆袭开挂。面对破败家境、负债困境与邻里非议，叶青萝凭借精湛厨艺、出众文笔经商创收，踏实打拼。她温柔护佑父母幼弟，化解周遭纷争，步步深耕、稳步致富，带领平凡叶家摆脱贫苦，安家立业，阖家奔赴圆满红火的人生巅峰。</x:v>
+        <x:v>18岁少女陆星辰意外觉醒“婴语翻译”系统，能听懂婴儿的每一次啼哭与呢喃。凭借这份独特天赋，她从一个普通大学生成长为京城顶级育儿专家，用爱与耐心呵护着豪门继承人们的健康成长。在数十年的守护中，陆星辰不仅用真心赢得了孩子们的依赖和全城大佬的敬重，更将这些孩子培养成三观正、有担当的栋梁之才。故事传递了“用心倾听、用爱陪伴”的育儿真谛，展现了平凡女孩凭借善良与专业逆袭人生的正能量。</x:v>
       </x:c>
       <x:c r="I84" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「一支喵」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；65集，主力长度；发布账号「小天短剧」</x:v>
       </x:c>
       <x:c r="J84" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -6363,28 +6363,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>为了活命我拼命整活</x:v>
+        <x:v>小五替我择良缘</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>留阿布</x:v>
+        <x:v>一碗猫酱</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>62岁骚男主播吴耐意外穿越，成了重病缠身的孤寡老大爷。手握三百万存款与四套房产，却叠满肝癌晚期、重度糖尿病、脑血栓等病痛buff，生命仅剩十四天！危急时刻，惊讶系统激活只要让自家三名美女租客惊讶，就能兑换寿命续命。温柔小护士、飒爽女刑警、风情女租户轮番登场。为了活下去，吴耐花式搞事，免房租、豪掷消费、秀逆天游戏操作，不断制造名场面，一边对抗病痛，一边疯狂刷惊讶值，开启爆笑续命逆袭生活。</x:v>
+        <x:v>兄长出征前，留下鹦鹉小五陪伴姜疏萤。寿宴之上，养女阿娇觊觎小五，未婚夫裴渊偏帮外人，肆意放走鸟儿。姜疏萤心死决然退婚，却发现小五落入逍遥王陆砚卿手中，还提出以人换鸟。侯府内宅步步构陷，继母与父亲的阴谋层层揭开，姜疏萤携鹦鹉，在王爷相助之下，撕破虚伪假面，复仇逆袭，觅得良缘。</x:v>
       </x:c>
       <x:c r="I85" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「留阿布」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；53集，次优长度；发布账号「一碗猫酱」</x:v>
       </x:c>
       <x:c r="J85" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -6395,28 +6395,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>婴语大师</x:v>
+        <x:v>穿越乱世：每天一份拼好饭</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>小天短剧</x:v>
+        <x:v>西西漫剧（求关注）</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>18岁少女陆星辰意外觉醒“婴语翻译”系统，能听懂婴儿的每一次啼哭与呢喃。凭借这份独特天赋，她从一个普通大学生成长为京城顶级育儿专家，用爱与耐心呵护着豪门继承人们的健康成长。在数十年的守护中，陆星辰不仅用真心赢得了孩子们的依赖和全城大佬的敬重，更将这些孩子培养成三观正、有担当的栋梁之才。故事传递了“用心倾听、用爱陪伴”的育儿真谛，展现了平凡女孩凭借善良与专业逆袭人生的正能量。</x:v>
+        <x:v>林渊一觉睡醒，穿越回乱世，正当他快饿晕的时候，手机上跳出一个拼好饭系统，余额19块8毛，每天一份外卖续命。他反手把珍珠奶茶兑水当回力汤卖出爆价，用一碗工业香精熬的糊糊引爆全城疯抢！就凭这点余额，他硬生生从饿殍堆里杀出血路。开局一副烂牌？19块8，照样把这乱世玩翻天！</x:v>
       </x:c>
       <x:c r="I86" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；65集，主力长度；发布账号「小天短剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；60集，主力长度；发布账号「西西漫剧（求关注）」</x:v>
       </x:c>
       <x:c r="J86" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -6427,28 +6427,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
+        <x:v>萌小宝寻爹记</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>平川动画</x:v>
+        <x:v>小火短剧</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
+        <x:v>社恐编剧苏念带五岁儿子躲了五年，儿子却在红毯上当众抱住顶流影帝喊爹地！心机女配设局陷害、全网黑料铺天盖地，萌宝化身最强助攻替妈撕碎伪装。当结婚证曝光、影帝跪地求婚——原来这五年，他找她找疯了。迟来的告白，甜到爆炸。</x:v>
       </x:c>
       <x:c r="I87" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；108集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；62集，主力长度；发布账号「小火短剧」</x:v>
       </x:c>
       <x:c r="J87" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -6459,28 +6459,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>我养的小兽怎么都成大佬了第二季</x:v>
+        <x:v>转夫运</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>迷声漫剧</x:v>
+        <x:v>饼花</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>赵橙知穿越星际兽世，百年前曾在废土星救下并养大五只幼兽，再睁眼却成了黑市待拍卖的F级废雌。危急关头，她唤出当年那只红狐幼崽——如今战功赫赫的归墟星将军千折意，被他强势救下护在身侧。随着校园风波迭起，白虎族首领庄九牧也认出了她的身份。昔日温顺小兽已成执掌一方的顶级大佬，百年执念与偏执守护尽数爆发，双强大佬开启极致修罗场</x:v>
+        <x:v>李媛带着两个女儿离开旧日困境，意外获得随身空间，在流云县从一碗热气腾腾的面开始，重新经营人生。重生归来的王灿带着对未来的记忆，与她并肩摆摊、种菜、囤粮，把清苦日子过得越来越有盼头。常年诸事不顺的秀才谢砚之，因吃到李媛亲手做的饭重获好运，也走进她们的生活。面对异常天候和未知前路，李媛、王灿、谢砚之与亲友彼此扶持，学盘炕、备物资、办婚事、护家人，在寒冬到来前守住烟火与温暖，也在一路相伴中找到新的生活。</x:v>
       </x:c>
       <x:c r="I88" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；78集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；104集，次优长度；发布账号「饼花」</x:v>
       </x:c>
       <x:c r="J88" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -6491,10 +6491,10 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>烟火年代：我有灵泉空间第一季</x:v>
+        <x:v>这一世，换我走向你</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
         <x:v>其他</x:v>
@@ -6503,16 +6503,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>哒哒哒剧场</x:v>
+        <x:v>棋鸿信息</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>七零年代，现代青年林墨穿越到被家人压榨迫害的知青身上，觉醒1元秒杀系统，开局秒杀储物戒。他手撕吸血原生家庭，拿到下乡名额前往极北大岭屯。一路凭借系统、念力与神级医术化解危机，结识王建军、方家姐妹。在乡村治病救人、打猎建功，周旋各方势力，对抗官场反派，积累财富与人脉，在七十年代的时代浪潮中闯出自己的一番天地。</x:v>
+        <x:v>梁琪琪前世被丈夫赵添算计，被夺走家产、毁掉身体，含恨离世。重生回到赵添向她求婚现场，她假意答应求婚，收起爱意冷静复仇。她冻结赵添权限，收集赵添与杨雪的阴谋证据，在订婚宴当众揭穿二人的丑恶算计。前世葬礼上，她知晓顾深多年默默的深情与少年约定。洗清过往伤害后，梁琪琪放下伤痛，奔赴一直守候自己的顾深，这一世换她主动走向爱人。</x:v>
       </x:c>
       <x:c r="I89" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；72集，主力长度；发布账号「棋鸿信息」</x:v>
       </x:c>
       <x:c r="J89" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -6523,25 +6523,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>修仙归来护家人第二季</x:v>
+        <x:v>魂归处：不待帝王悔</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>夏十七</x:v>
+        <x:v>片单挖掘机</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
+        <x:v>皇后沈知微的父兄戍守边关重伤待援，她苦苦恳求帝王萧景珩下旨救人，却因贵妃柳如烟从中作梗，圣旨被一再搁置。父亲战死、兄长残伤归来，沈知微心死，借助系统开启假死程序，纵火焚毁坤宁宫。她灵魂滞留世间见证因果清算，萧景珩查清全部真相，严惩柳氏一族，对沈家百般补偿，深陷无尽悔恨。面对帝王迟来的忏悔，沈知微选择绝不原谅，了结全部羁绊，终于得以脱离这个世界，为自己重获新生。</x:v>
       </x:c>
       <x:c r="I90" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；72集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；43集，次优长度；发布账号「片单挖掘机」</x:v>
       </x:c>
       <x:c r="J90" s="11" t="n">
         <x:v>8</x:v>
@@ -6555,28 +6555,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
+        <x:v>太学废柴班拯救计划</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>云朵邮递员</x:v>
+        <x:v>小曲动漫</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
+        <x:v>林非晚穿成尚书府不受宠的嫡长女，嫁给了镇国将军霍云霆。她以现代商战智慧执掌公府财政，把太学废柴三害调教成科举前三甲，更带领他们揪出赈灾粮贪腐黑幕。诈死的战神丈夫现身，与她并肩作战、步步为营揭开惊天大案，最终朝堂清明，夫妻情深，昔日纨绔皆成治国栋梁。</x:v>
       </x:c>
       <x:c r="I91" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；131集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；84集，主力长度；发布账号「小曲动漫」</x:v>
       </x:c>
       <x:c r="J91" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -6587,28 +6587,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>小五替我择良缘</x:v>
+        <x:v>携手千里渡荒年</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>一碗猫酱</x:v>
+        <x:v>逗小包</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>兄长出征前，留下鹦鹉小五陪伴姜疏萤。寿宴之上，养女阿娇觊觎小五，未婚夫裴渊偏帮外人，肆意放走鸟儿。姜疏萤心死决然退婚，却发现小五落入逍遥王陆砚卿手中，还提出以人换鸟。侯府内宅步步构陷，继母与父亲的阴谋层层揭开，姜疏萤携鹦鹉，在王爷相助之下，撕破虚伪假面，复仇逆袭，觅得良缘。</x:v>
+        <x:v>现代女主意外穿越荒年，成为温四月，身陷逃荒绝境。危难之际，憨厚赤诚的夫君厉青山始终护她周全，为她遮风挡雨。绝境之中，温四月意外觉醒灵泉空间，手握求生底牌。逃亡路上，她褪去怯懦，凭借智慧与异能，习得炼盐之术、寻觅山野食粮，带领同行众人绝境求生。她心怀善意，坚守本心，与厉青山相互扶持、并肩前行，在乱世绝境中扎根希望，于颠沛流离里守护烟火与温情，一步步奔赴生机与新生。</x:v>
       </x:c>
       <x:c r="I92" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；53集，次优长度；发布账号「一碗猫酱」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；117集，次优长度；发布账号「逗小包」</x:v>
       </x:c>
       <x:c r="J92" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -6619,28 +6619,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>我的渔船通龙宫第一季</x:v>
+        <x:v>虾仁穿成驸马爷，公主谁爱娶谁娶！</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>六翼动漫</x:v>
+        <x:v>虾扯蛋动画</x:v>
       </x:c>
       <x:c r="H93" s="10" t="str">
-        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
+        <x:v>你，名为虾仁！穿越到一个架空世界，名为大乾王朝！无系统！而你，正是开国大将军虾国公之子，虾仁！当继承原主的记忆后，原本想当个纨绔，每天溜溜鸟，斗蝈蝈，潇洒过一生！可是，老爹你确告诉我，家里已经家徒四壁，而我，还有一个大乾嫡长公主的未婚妻？为了活下去，只能想办法做生意，而做生意的第一天就碰见隐藏身份的未婚妻，从此，故事由此展开！</x:v>
       </x:c>
       <x:c r="I93" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；65集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；91集，主力长度；发布账号「虾扯蛋动画」</x:v>
       </x:c>
       <x:c r="J93" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -6779,25 +6779,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>我救的父女成了我的靠山第二季</x:v>
+        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 现实反转</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>潮汐心动放映厅</x:v>
+        <x:v>云间漫剧-玉川</x:v>
       </x:c>
       <x:c r="H98" s="10" t="str">
-        <x:v>十八年前苏云出手救下困境中的林野与女儿林诗诗。十八年后苏云挣脱险境，与已是财团董事长的林野重逢。一桩意外揭开身世秘密，林诗诗并非林野骨肉，她的生父为护林野不幸离世，生母与妹妹正深陷生活困境。林诗诗得知身世大受震动，为救治病重生母毅然捐献肝脏。历经生死磨难，她和欢喜冤家陆时宇互生爱慕。众人揭穿包工头讨回公道，抚平旧日伤痕，苏云喜得龙凤胎，两代人在烟火生活里收获圆满团圆。</x:v>
+        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
       </x:c>
       <x:c r="I98" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；78集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
       </x:c>
       <x:c r="J98" s="11" t="n">
         <x:v>8</x:v>
@@ -6811,28 +6811,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
+        <x:v>三年，我不装了</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E99" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>家庭伦理 / 现实反转</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
+        <x:v>布噜布噜剧场</x:v>
       </x:c>
       <x:c r="H99" s="10" t="str">
-        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
+        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
       </x:c>
       <x:c r="I99" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
       </x:c>
       <x:c r="J99" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -6843,25 +6843,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>三年，我不装了</x:v>
+        <x:v>沙县厨神</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F100" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>美食治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>布噜布噜剧场</x:v>
+        <x:v>新视觉漫剧心动剧场</x:v>
       </x:c>
       <x:c r="H100" s="10" t="str">
-        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
       </x:c>
       <x:c r="I100" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
       </x:c>
       <x:c r="J100" s="11" t="n">
         <x:v>7.5</x:v>
@@ -6875,28 +6875,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>沙县厨神</x:v>
+        <x:v>九零绝境潮汐系统护我</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>113</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
-        <x:v>美食治愈 / 战神异能</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>新视觉漫剧心动剧场</x:v>
+        <x:v>杨桃剧院</x:v>
       </x:c>
       <x:c r="H101" s="10" t="str">
-        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
+        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
       </x:c>
       <x:c r="I101" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
       </x:c>
       <x:c r="J101" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -6907,25 +6907,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>九零绝境潮汐系统护我</x:v>
+        <x:v>予你情深，岁岁相守</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F102" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G102" s="10" t="str">
-        <x:v>杨桃剧院</x:v>
+        <x:v>啾啾说漫</x:v>
       </x:c>
       <x:c r="H102" s="10" t="str">
-        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
       </x:c>
       <x:c r="I102" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
       </x:c>
       <x:c r="J102" s="11" t="n">
         <x:v>7</x:v>
@@ -6939,25 +6939,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>予你情深，岁岁相守</x:v>
+        <x:v>仙界老祖非要当我哥</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F103" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>啾啾说漫</x:v>
+        <x:v>青青漫剧</x:v>
       </x:c>
       <x:c r="H103" s="10" t="str">
-        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
       </x:c>
       <x:c r="I103" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
       </x:c>
       <x:c r="J103" s="11" t="n">
         <x:v>7</x:v>
@@ -6971,25 +6971,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>仙界老祖非要当我哥</x:v>
+        <x:v>农家穗安：饼香满镇</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F104" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>青青漫剧</x:v>
+        <x:v>奇趣漫剧场</x:v>
       </x:c>
       <x:c r="H104" s="10" t="str">
-        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
       </x:c>
       <x:c r="I104" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
       </x:c>
       <x:c r="J104" s="11" t="n">
         <x:v>7</x:v>
@@ -7003,25 +7003,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>农家穗安：饼香满镇</x:v>
+        <x:v>嫡女归来，厨香撼京华</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F105" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>奇趣漫剧场</x:v>
+        <x:v>锦书映年华</x:v>
       </x:c>
       <x:c r="H105" s="10" t="str">
-        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
+        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
       </x:c>
       <x:c r="I105" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
       </x:c>
       <x:c r="J105" s="11" t="n">
         <x:v>7</x:v>
@@ -7035,25 +7035,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>嫡女归来，厨香撼京华</x:v>
+        <x:v>山野新婚暖光阴</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>小尘剧场</x:v>
       </x:c>
       <x:c r="H106" s="10" t="str">
-        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
+        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
       </x:c>
       <x:c r="I106" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
       </x:c>
       <x:c r="J106" s="11" t="n">
         <x:v>7</x:v>
@@ -7067,25 +7067,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>山野新婚暖光阴</x:v>
+        <x:v>我的小土狗竟有大帝之姿</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>小尘剧场</x:v>
+        <x:v>嘉午纪</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
+        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
         <x:v>7</x:v>
@@ -7099,25 +7099,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>我的小土狗竟有大帝之姿</x:v>
+        <x:v>替嫁棺妃</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>嘉午纪</x:v>
+        <x:v>诗婳影视</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
+        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
         <x:v>7</x:v>
@@ -7131,25 +7131,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>替嫁棺妃</x:v>
+        <x:v>末世的最后一餐</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F109" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>诗婳影视</x:v>
+        <x:v>团子动漫</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
+        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
         <x:v>7</x:v>
@@ -7163,10 +7163,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>末世的最后一餐</x:v>
+        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
@@ -7174,14 +7174,12 @@
       <x:c r="F110" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G110" s="10" t="str">
-        <x:v>团子动漫</x:v>
-      </x:c>
+      <x:c r="G110" s="10" t="str"/>
       <x:c r="H110" s="10" t="str">
-        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
+        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
         <x:v>7</x:v>
@@ -7195,23 +7193,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
+        <x:v>被赶走的保姆，竟是真夫人</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str"/>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>九鲤动漫</x:v>
+      </x:c>
       <x:c r="H111" s="10" t="str">
-        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
+        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
         <x:v>7</x:v>
@@ -7225,28 +7225,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>被赶走的保姆，竟是真夫人</x:v>
+        <x:v>新婚的羔羊</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
+        <x:v>战神漫剧</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
+        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6.5</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7257,28 +7257,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>七旬老太，勇闯惊悚游戏第一季</x:v>
+        <x:v>人到中年我逆袭成百草圣手</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>新娱剧场</x:v>
+        <x:v>极剧-热血剧场</x:v>
       </x:c>
       <x:c r="H113" s="10" t="str">
-        <x:v>七十岁农村老太李树英为救孙女主动报名进入惊悚游戏，获“老当益壮”与“隔代亲光环”技能。C级副本《伯爵庄园》中，她揭穿邪神永生阴谋，终结红衣侍女。B级副本《疯镇》里，她化身李阿婆暗中助人，协助消灭疯狂源头。完美通关后声名渐起，却被总系统盯上，新副本正等待她破解。</x:v>
+        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
       </x:c>
       <x:c r="I113" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；50集，次优长度；发布账号「极剧-热血剧场」</x:v>
       </x:c>
       <x:c r="J113" s="11" t="n">
-        <x:v>6.5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8902,28 +8902,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>重生之我飒爆了！第二季</x:v>
+        <x:v>后娘逆袭</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F54" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G54" s="10" t="str">
-        <x:v>罗曼蒂克-海豹分镜【AI短剧】</x:v>
+        <x:v>1649世界</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>重生归来的林雨汐，在涉外饭店当众揭穿辱华者，拒绝用尊严换投资；她一路守护家人、揭开身世、创办药厂。与陆逸领证成婚后，空间因果降临，两人被送往末世求生。回归现实，她带着异能和新生命，却遭遇婴儿被盗，危机再起。</x:v>
+        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；74集，主力长度；发布账号「1649世界」</x:v>
       </x:c>
       <x:c r="J54" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -8934,28 +8934,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>后娘逆袭</x:v>
+        <x:v>重生八零：直上青天展宏图</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F55" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G55" s="10" t="str">
-        <x:v>1649世界</x:v>
+        <x:v>八哥剧场</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>女主从现代职场人穿越成古代被贱卖的村姑，开局家徒四壁，还喜当两个五岁娃的后娘。面对极品亲戚算计、村民闲言，她凭现代智慧与一身厨艺绝地翻盘——熬蚝油、卖烤生蚝、建房兴业，带着孩子们读书致富，活出古代独立女性的精彩。表面冷硬的猎户夫君，实则身份成谜，从给休书到暗戳戳宠妻护短，反差萌十足。小日常里斗极品、搞事业、养萌娃，甜爽交织。当神秘身世逐渐揭开，这对“合约夫妻”能否携手逆袭，共赴锦绣前程？</x:v>
+        <x:v>林振东前世倾尽所有娶妻养家，辛苦半生，却发现妻子早已变心，三个养子皆是旁人骨肉。他被白眼狼子女榨干家产、狠心害死，连累至亲落得凄惨下场。带着无尽悔恨，他重生回到送彩礼定亲当天！这一世他当众怒退婚约，守护家人、斩断孽缘，凭借超前眼光，踏实创业搞钱，逆袭改写全家悲惨命运！</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；74集，主力长度；发布账号「1649世界」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；95集，主力长度；发布账号「八哥剧场」</x:v>
       </x:c>
       <x:c r="J55" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>9.5</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -8966,10 +8966,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>重生八零：直上青天展宏图</x:v>
+        <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
       </x:c>
       <x:c r="D56" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E56" s="11" t="str">
         <x:v>其他</x:v>
@@ -8978,16 +8978,16 @@
         <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G56" s="10" t="str">
-        <x:v>八哥剧场</x:v>
+        <x:v>芸光剧场</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>林振东前世倾尽所有娶妻养家，辛苦半生，却发现妻子早已变心，三个养子皆是旁人骨肉。他被白眼狼子女榨干家产、狠心害死，连累至亲落得凄惨下场。带着无尽悔恨，他重生回到送彩礼定亲当天！这一世他当众怒退婚约，守护家人、斩断孽缘，凭借超前眼光，踏实创业搞钱，逆袭改写全家悲惨命运！</x:v>
+        <x:v>现代中医天才林薇遭遇意外，穿越到八零年代，成为嫌贫爱富的炮灰媳妇。觉醒药圃空间，靠着药灵产出的药材食材改善生活。原本的丈夫顾深是有学识的潜力青年，林薇一改原主态度，用心经营家庭。她摆摊卖药材，抓住机遇搞大棚中草药育苗，攻克育苗难题。一边化解林蕊、孙大勇等人的不断陷害，一边带领家人奔好日子。她无私分享种植技术，获得荣誉，和顾深双向奔赴，事业爱情家庭三丰收。</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；95集，主力长度；发布账号「八哥剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「芸光剧场」</x:v>
       </x:c>
       <x:c r="J56" s="11" t="n">
-        <x:v>9.5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -8998,25 +8998,23 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
+        <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
       </x:c>
       <x:c r="D57" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F57" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="G57" s="10" t="str">
-        <x:v>芸光剧场</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G57" s="10" t="str"/>
       <x:c r="H57" s="10" t="str">
-        <x:v>现代中医天才林薇遭遇意外，穿越到八零年代，成为嫌贫爱富的炮灰媳妇。觉醒药圃空间，靠着药灵产出的药材食材改善生活。原本的丈夫顾深是有学识的潜力青年，林薇一改原主态度，用心经营家庭。她摆摊卖药材，抓住机遇搞大棚中草药育苗，攻克育苗难题。一边化解林蕊、孙大勇等人的不断陷害，一边带领家人奔好日子。她无私分享种植技术，获得荣誉，和顾深双向奔赴，事业爱情家庭三丰收。</x:v>
+        <x:v>顾诚意外穿越至妖魔横行的乱世，开局惨遭叛徒出卖，沦为猪妖的口粮。绝境中他觉醒“氪命系统”，消耗寿元即可瞬间将武学推演至圆满境界，斩杀妖魔邪修更能夺取寿元无限续航！凭借此逆天金手指，顾诚从镇魔司底层小吏起步，一路狂斩内鬼、手撕破凡大妖、血战魔道余孽。在女修徐念雪与未婚妻林青燕的相伴下，顾诚以命为引，融合极道武学，誓要杀穿这妖邪乱世，登顶巅峰！</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「芸光剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J57" s="11" t="n">
         <x:v>9</x:v>
@@ -9030,23 +9028,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
-        <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
+        <x:v>穿越古代，我靠军火建立王朝</x:v>
       </x:c>
       <x:c r="D58" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F58" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G58" s="10" t="str"/>
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str">
+        <x:v>热雪Ai漫剧场</x:v>
+      </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>顾诚意外穿越至妖魔横行的乱世，开局惨遭叛徒出卖，沦为猪妖的口粮。绝境中他觉醒“氪命系统”，消耗寿元即可瞬间将武学推演至圆满境界，斩杀妖魔邪修更能夺取寿元无限续航！凭借此逆天金手指，顾诚从镇魔司底层小吏起步，一路狂斩内鬼、手撕破凡大妖、血战魔道余孽。在女修徐念雪与未婚妻林青燕的相伴下，顾诚以命为引，融合极道武学，誓要杀穿这妖邪乱世，登顶巅峰！</x:v>
+        <x:v>现代退伍老兵陈楠意外穿越异世，开局便成杀虎口死囚。身陷绝境，他凭借随身空间、现代军备与作战经验，从牢房杀出重围，在边境战场一路崛起。当世家权贵视人命如草芥，他不再替旧秩序卖命，带领追随者建立陈家军、夺下黑石崖。冷兵器时代撞上现代火力，一介死囚，誓要重建大乾，建立属于自己的王朝！</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「热雪Ai漫剧场」</x:v>
       </x:c>
       <x:c r="J58" s="11" t="n">
         <x:v>9</x:v>
@@ -9060,25 +9060,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
-        <x:v>穿越古代，我靠军火建立王朝</x:v>
+        <x:v>穿越王妃美又飒</x:v>
       </x:c>
       <x:c r="D59" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E59" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F59" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G59" s="10" t="str">
-        <x:v>热雪Ai漫剧场</x:v>
+        <x:v>羚羊AI剧场</x:v>
       </x:c>
       <x:c r="H59" s="10" t="str">
-        <x:v>现代退伍老兵陈楠意外穿越异世，开局便成杀虎口死囚。身陷绝境，他凭借随身空间、现代军备与作战经验，从牢房杀出重围，在边境战场一路崛起。当世家权贵视人命如草芥，他不再替旧秩序卖命，带领追随者建立陈家军、夺下黑石崖。冷兵器时代撞上现代火力，一介死囚，誓要重建大乾，建立属于自己的王朝！</x:v>
+        <x:v>别人宅斗用心机，她宅斗直接掏手枪！堂堂现代蛊医传人，竟穿成任人欺凌的傻子王妃，开局就被恶毒侧妃扔进乱葬岗灭口。叶南希冷笑，空间戒指觉醒，直接掏出沙漠之鹰突突了恶奴！顺手还拿下了权倾朝野的战神镇北王。面对绿茶顶替、下人欺凌、皇家算计，她一手银针一手枪，神挡杀神！</x:v>
       </x:c>
       <x:c r="I59" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「热雪Ai漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「羚羊AI剧场」</x:v>
       </x:c>
       <x:c r="J59" s="11" t="n">
         <x:v>9</x:v>
@@ -9092,25 +9092,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
-        <x:v>穿越王妃美又飒</x:v>
+        <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
       </x:c>
       <x:c r="D60" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E60" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F60" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G60" s="10" t="str">
-        <x:v>羚羊AI剧场</x:v>
+        <x:v>购嗨漫剧</x:v>
       </x:c>
       <x:c r="H60" s="10" t="str">
-        <x:v>别人宅斗用心机，她宅斗直接掏手枪！堂堂现代蛊医传人，竟穿成任人欺凌的傻子王妃，开局就被恶毒侧妃扔进乱葬岗灭口。叶南希冷笑，空间戒指觉醒，直接掏出沙漠之鹰突突了恶奴！顺手还拿下了权倾朝野的战神镇北王。面对绿茶顶替、下人欺凌、皇家算计，她一手银针一手枪，神挡杀神！</x:v>
+        <x:v>孤儿少女凌昭本是四项满S的百年天才，脑内神秘芯片吞噬她的精神力，令她沦为被众人嘲讽的废柴学员。绝境之际，她解锁脑内秘境万国狩猎场，通过试炼积攒信仰币突破变强。在异兽与强者林立的残酷竞技中，凌昭逆势翻盘，携手高冷天才萧含雪、孤勇幸存者夏明桑，冲破层层封印。她觉醒SS级天赋，执掌神剑神谕，屡破赛场纪录，打脸天骄，对抗帝国黑暗势力，从底层逆袭成最年轻战神，毅然奔赴凶险边境守护万家灯火。</x:v>
       </x:c>
       <x:c r="I60" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「羚羊AI剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「购嗨漫剧」</x:v>
       </x:c>
       <x:c r="J60" s="11" t="n">
         <x:v>9</x:v>
@@ -9124,25 +9124,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
-        <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
+        <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
       </x:c>
       <x:c r="D61" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E61" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F61" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 现实反转</x:v>
       </x:c>
       <x:c r="G61" s="10" t="str">
-        <x:v>购嗨漫剧</x:v>
+        <x:v>熊猫热剧</x:v>
       </x:c>
       <x:c r="H61" s="10" t="str">
-        <x:v>孤儿少女凌昭本是四项满S的百年天才，脑内神秘芯片吞噬她的精神力，令她沦为被众人嘲讽的废柴学员。绝境之际，她解锁脑内秘境万国狩猎场，通过试炼积攒信仰币突破变强。在异兽与强者林立的残酷竞技中，凌昭逆势翻盘，携手高冷天才萧含雪、孤勇幸存者夏明桑，冲破层层封印。她觉醒SS级天赋，执掌神剑神谕，屡破赛场纪录，打脸天骄，对抗帝国黑暗势力，从底层逆袭成最年轻战神，毅然奔赴凶险边境守护万家灯火。</x:v>
+        <x:v>沈南星意外绑定高温末世预警系统，识破闺蜜白薇谎称极寒末日、联合男友骗取她物资的圈套。在河狸系统的陪伴与协助下，她反手变卖房产囤定制冷设备与生存物资，在半山腰打造避暑堡垒，储备充足物资，搭建起净水、制冷与无土种植系统，一人一系统携手并肩安稳度过极热危机，山庄成为灾后重建核心基地，沈南星与河狸系统也结下了深厚的伙伴情谊，而背叛者也为自身的贪念与过错承担了相应的后果。</x:v>
       </x:c>
       <x:c r="I61" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「购嗨漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；68集，主力长度；发布账号「熊猫热剧」</x:v>
       </x:c>
       <x:c r="J61" s="11" t="n">
         <x:v>9</x:v>
@@ -9156,28 +9156,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
-        <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
+        <x:v>借势逢生</x:v>
       </x:c>
       <x:c r="D62" s="11" t="n">
-        <x:v>68</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E62" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F62" s="10" t="str">
-        <x:v>逆袭打脸 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G62" s="10" t="str">
-        <x:v>熊猫热剧</x:v>
+        <x:v>虾华看漫剧</x:v>
       </x:c>
       <x:c r="H62" s="10" t="str">
-        <x:v>沈南星意外绑定高温末世预警系统，识破闺蜜白薇谎称极寒末日、联合男友骗取她物资的圈套。在河狸系统的陪伴与协助下，她反手变卖房产囤定制冷设备与生存物资，在半山腰打造避暑堡垒，储备充足物资，搭建起净水、制冷与无土种植系统，一人一系统携手并肩安稳度过极热危机，山庄成为灾后重建核心基地，沈南星与河狸系统也结下了深厚的伙伴情谊，而背叛者也为自身的贪念与过错承担了相应的后果。</x:v>
+        <x:v>青苍城天才少主陆轩惨遭仇家暗算，丹田被毁沦为废人，婚约也遭林家强行逼迫退婚。绝境之中，他意外觉醒葬天坠秘境，邂逅上古强者，习得至尊剑道与不死丹神传承。陆轩借秘境机缘逆天重修，一路越级逆袭、横扫仇家，破绝境、战群雄，强势守护挚爱与家人，登顶武道巅峰！</x:v>
       </x:c>
       <x:c r="I62" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；68集，主力长度；发布账号「熊猫热剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；发布账号「虾华看漫剧」</x:v>
       </x:c>
       <x:c r="J62" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -9188,25 +9188,23 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
-        <x:v>借势逢生</x:v>
+        <x:v>反派老爹不好惹</x:v>
       </x:c>
       <x:c r="D63" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E63" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F63" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G63" s="10" t="str">
-        <x:v>虾华看漫剧</x:v>
-      </x:c>
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="G63" s="10" t="str"/>
       <x:c r="H63" s="10" t="str">
-        <x:v>青苍城天才少主陆轩惨遭仇家暗算，丹田被毁沦为废人，婚约也遭林家强行逼迫退婚。绝境之中，他意外觉醒葬天坠秘境，邂逅上古强者，习得至尊剑道与不死丹神传承。陆轩借秘境机缘逆天重修，一路越级逆袭、横扫仇家，破绝境、战群雄，强势守护挚爱与家人，登顶武道巅峰！</x:v>
+        <x:v>首富沈渡穿越都市爽文，觉醒家族气运系统，为避免家破人亡命运，反套路截胡气运之子叶凡机缘。他痛改纨绔儿子沈云，斗苏家、破赌石局，屡次粉碎叶凡崛起计划。叶凡黑化搬来宗师师兄雷虎复仇，依旧被沈渡父子强势碾压，最终叶凡气运耗尽陨落。世界线自我修复，新气运之子、海外佣兵之王陈枫降临，沈家与天命的博弈再度开启。</x:v>
       </x:c>
       <x:c r="I63" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；100集，主力长度；发布账号「虾华看漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；88集，主力长度</x:v>
       </x:c>
       <x:c r="J63" s="11" t="n">
         <x:v>8</x:v>
@@ -9220,23 +9218,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
-        <x:v>反派老爹不好惹</x:v>
+        <x:v>女粉丝的救赎</x:v>
       </x:c>
       <x:c r="D64" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E64" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F64" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="G64" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G64" s="10" t="str">
+        <x:v>栗栗动漫</x:v>
+      </x:c>
       <x:c r="H64" s="10" t="str">
-        <x:v>首富沈渡穿越都市爽文，觉醒家族气运系统，为避免家破人亡命运，反套路截胡气运之子叶凡机缘。他痛改纨绔儿子沈云，斗苏家、破赌石局，屡次粉碎叶凡崛起计划。叶凡黑化搬来宗师师兄雷虎复仇，依旧被沈渡父子强势碾压，最终叶凡气运耗尽陨落。世界线自我修复，新气运之子、海外佣兵之王陈枫降临，沈家与天命的博弈再度开启。</x:v>
+        <x:v>女主林鹿一觉醒来，穿越到自己最爱的女明星沈清秋身上，得知原主早已惨死。偶像的死并非意外，她决定替她讨回公道。面对黑料、陷害与豪门阴谋，林鹿一路反击，逐渐查出原主之死竟牵扯权氏夺权。随着调查深入，幕后真相浮出水面——权斯年为了扳倒权延修，原主不过是他路上的一颗绊脚石。为了复仇，林鹿也一步步卷入这场危险的豪门棋局。</x:v>
       </x:c>
       <x:c r="I64" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；88集，主力长度</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；90集，主力长度；发布账号「栗栗动漫」</x:v>
       </x:c>
       <x:c r="J64" s="11" t="n">
         <x:v>8</x:v>
@@ -9250,25 +9250,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
-        <x:v>女粉丝的救赎</x:v>
+        <x:v>彪悍后妈在八零</x:v>
       </x:c>
       <x:c r="D65" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F65" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 家庭伦理</x:v>
       </x:c>
       <x:c r="G65" s="10" t="str">
-        <x:v>栗栗动漫</x:v>
+        <x:v>玫瑰短剧.</x:v>
       </x:c>
       <x:c r="H65" s="10" t="str">
-        <x:v>女主林鹿一觉醒来，穿越到自己最爱的女明星沈清秋身上，得知原主早已惨死。偶像的死并非意外，她决定替她讨回公道。面对黑料、陷害与豪门阴谋，林鹿一路反击，逐渐查出原主之死竟牵扯权氏夺权。随着调查深入，幕后真相浮出水面——权斯年为了扳倒权延修，原主不过是他路上的一颗绊脚石。为了复仇，林鹿也一步步卷入这场危险的豪门棋局。</x:v>
+        <x:v>末世强者姜珠重生到1983年，替假千金嫁给乡下“拖油瓶”男人，进门就当后妈。她攥着三千块彩礼嫁入陆家，丈夫陆战竟是运输队大队长，两个继子女正遭极品亲戚虐待。她劈锁立威、铁腕掌家，凭卤味绝活逆袭省城。夫妻并肩创业，她真心焐热两个孩子，收拾贪心亲戚、揭穿假千金阴谋、打下万贯家业。穿越女强人把当好后妈活成了最飒的事业，还在烟火人间里意外收获了属于自己的小生命。</x:v>
       </x:c>
       <x:c r="I65" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；90集，主力长度；发布账号「栗栗动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；43集，次优长度；发布账号「玫瑰短剧.」</x:v>
       </x:c>
       <x:c r="J65" s="11" t="n">
         <x:v>8</x:v>
@@ -9282,23 +9282,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
-        <x:v>开局获得融合系统从凡人逆袭成神第一季</x:v>
+        <x:v>无心攀比，假千金重生后成团宠了</x:v>
       </x:c>
       <x:c r="D66" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F66" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G66" s="10" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G66" s="10" t="str">
+        <x:v>鲸跃AI剧场</x:v>
+      </x:c>
       <x:c r="H66" s="10" t="str">
-        <x:v>讲述主角林尘本是底层凡人，意外获得融合系统，从小镇宗门杂役起步，融合低阶功法与灵根妖兽血脉快速变强。他接连打脸欺压自己的本土天才，拿下宗门小比第一，解决新手村邪修入侵危机，了结家族仇怨，筑基成功后离开故土，前往更大的修真城闯荡。</x:v>
+        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
       </x:c>
       <x:c r="I66" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；57集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；发布账号「鲸跃AI剧场」</x:v>
       </x:c>
       <x:c r="J66" s="11" t="n">
         <x:v>8</x:v>
@@ -9312,25 +9314,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
-        <x:v>彪悍后妈在八零</x:v>
+        <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
       </x:c>
       <x:c r="D67" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E67" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F67" s="10" t="str">
-        <x:v>年代怀旧 / 家庭伦理</x:v>
+        <x:v>古装宫廷 / 美食治愈</x:v>
       </x:c>
       <x:c r="G67" s="10" t="str">
-        <x:v>玫瑰短剧.</x:v>
+        <x:v>恒漫剧场</x:v>
       </x:c>
       <x:c r="H67" s="10" t="str">
-        <x:v>末世强者姜珠重生到1983年，替假千金嫁给乡下“拖油瓶”男人，进门就当后妈。她攥着三千块彩礼嫁入陆家，丈夫陆战竟是运输队大队长，两个继子女正遭极品亲戚虐待。她劈锁立威、铁腕掌家，凭卤味绝活逆袭省城。夫妻并肩创业，她真心焐热两个孩子，收拾贪心亲戚、揭穿假千金阴谋、打下万贯家业。穿越女强人把当好后妈活成了最飒的事业，还在烟火人间里意外收获了属于自己的小生命。</x:v>
+        <x:v>现代平凡女孩穿越成古代小商户女，靠美食系统古几位性格迥异的优质公子，在经营小吃铺的甜蜜日常中，一是微服私访的护国将军之子沈墨，表面是纨绔公子，实则武艺高强，因被奶茶惊艳而天天来蹭吃，二是当朝首辅的孙子、温润如玉的才子顾清寒，他正为招待海外使臣的宴席发愁，慕名前来求教点心，三是神秘商人裴云，看似普通富商，却总能拿出稀有食材与林小满交易，并对她展露异常执着的关心。</x:v>
       </x:c>
       <x:c r="I67" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；43集，次优长度；发布账号「玫瑰短剧.」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「恒漫剧场」</x:v>
       </x:c>
       <x:c r="J67" s="11" t="n">
         <x:v>8</x:v>
@@ -9344,25 +9346,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
-        <x:v>无心攀比，假千金重生后成团宠了</x:v>
+        <x:v>转生成鼠，气哭冷艳校花</x:v>
       </x:c>
       <x:c r="D68" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E68" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F68" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G68" s="10" t="str">
-        <x:v>鲸跃AI剧场</x:v>
+        <x:v>长夜动漫剧场</x:v>
       </x:c>
       <x:c r="H68" s="10" t="str">
-        <x:v>虞夏星重生回了家产争夺赛开始的那天，上一世她拼死拼活争第一，结果最后被扫地出门，净身出户！重活一世，虞夏星悟了，只要我把项目干倒闭，就能拿一千万遣散费光速跑路！于是，她果断接手了全校垫底、连亏十年的圣德大学，本以为稳亏，可为什么，她越想搞垮，学校越火？越想摆烂，越是团宠？全员反套路，越想输越躺赢。这个假千金，注定要赢到她不想赢。</x:v>
+        <x:v>林一穿越成花枝鼠，觉醒吞噬进化系统，偷吃重生女帝郑依云的贡品意外被契约。他靠吞噬灵物极速进化，认赤炎神凤为义母，携手女主横扫校园、征战万国大比，一路逆袭登顶。转生老鼠，开局偷吃校花贡品的命运新局继续展开。转生老鼠，开局偷吃校花贡品的命运新局继续展开。</x:v>
       </x:c>
       <x:c r="I68" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；100集，主力长度；发布账号「鲸跃AI剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「长夜动漫剧场」</x:v>
       </x:c>
       <x:c r="J68" s="11" t="n">
         <x:v>8</x:v>
@@ -9376,10 +9378,10 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
-        <x:v>程家小媳不好惹第二季</x:v>
+        <x:v>魂穿百岁老太，零零后整顿全村</x:v>
       </x:c>
       <x:c r="D69" s="11" t="n">
-        <x:v>135</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E69" s="11" t="str">
         <x:v>其他</x:v>
@@ -9388,13 +9390,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G69" s="10" t="str">
-        <x:v>莹莹漫剧</x:v>
+        <x:v>筑创Ai漫剧</x:v>
       </x:c>
       <x:c r="H69" s="10" t="str">
-        <x:v>现代建筑设计师意外穿越，成了古代乡村被娘家倒贴银子卖掉的傻姑娘。她被哥嫂强行塞给穷小子程风当媳妇，一睁眼就被困在破屋中无依无靠。面对贫寒的家境和未知的处境，她只能暂时装傻保命，心里却早已盘算好出路，只等程风归来揭开这场错位婚事的后续。</x:v>
+        <x:v>24岁社畜林晚猝死后，穿越成顾家百岁老太太。面对极品亲戚争产、懦弱儿孙受欺、重男轻女旧俗、熟人骗局陷害、宗族道德绑架等重重困境，她以现代清醒头脑和通透智慧，一一化解危机、整顿家风，护住家人安稳。在带领全家逆袭翻身的过程中，她意外发现原主尘封半生的骨肉离别之痛。历经寻亲无果、善恶和解、遗憾释然，她最终领悟，人生无需圆满，带憾前行、温柔生活，便是重生最大的意义。</x:v>
       </x:c>
       <x:c r="I69" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；135集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；40集，次优长度；发布账号「筑创Ai漫剧」</x:v>
       </x:c>
       <x:c r="J69" s="11" t="n">
         <x:v>8</x:v>
@@ -9408,28 +9410,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
-        <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
+        <x:v>1970重生岁岁，不负韶华</x:v>
       </x:c>
       <x:c r="D70" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E70" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F70" s="10" t="str">
-        <x:v>古装宫廷 / 美食治愈</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G70" s="10" t="str">
-        <x:v>恒漫剧场</x:v>
+        <x:v>星文文化</x:v>
       </x:c>
       <x:c r="H70" s="10" t="str">
-        <x:v>现代平凡女孩穿越成古代小商户女，靠美食系统古几位性格迥异的优质公子，在经营小吃铺的甜蜜日常中，一是微服私访的护国将军之子沈墨，表面是纨绔公子，实则武艺高强，因被奶茶惊艳而天天来蹭吃，二是当朝首辅的孙子、温润如玉的才子顾清寒，他正为招待海外使臣的宴席发愁，慕名前来求教点心，三是神秘商人裴云，看似普通富商，却总能拿出稀有食材与林小满交易，并对她展露异常执着的关心。</x:v>
+        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
       </x:c>
       <x:c r="I70" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「恒漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；86集，主力长度；发布账号「星文文化」</x:v>
       </x:c>
       <x:c r="J70" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -9440,28 +9442,26 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
-        <x:v>转生成鼠，气哭冷艳校花</x:v>
+        <x:v>剑心被夺后，我神魔同体！</x:v>
       </x:c>
       <x:c r="D71" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E71" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F71" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G71" s="10" t="str">
-        <x:v>长夜动漫剧场</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G71" s="10" t="str"/>
       <x:c r="H71" s="10" t="str">
-        <x:v>林一穿越成花枝鼠，觉醒吞噬进化系统，偷吃重生女帝郑依云的贡品意外被契约。他靠吞噬灵物极速进化，认赤炎神凤为义母，携手女主横扫校园、征战万国大比，一路逆袭登顶。转生老鼠，开局偷吃校花贡品的命运新局继续展开。转生老鼠，开局偷吃校花贡品的命运新局继续展开。</x:v>
+        <x:v>太虚宫首席云青瑶遭未婚夫林修远、师妹白芷焉联手背叛，被夺玲珑剑心、废丹田弃尸葬神崖。她饮万毒蚀骨汤，修成万古毒体，化名凌瑶强势归来。一路打脸渣男贱女，夺回剑心，觉醒魔尊血脉，神魔同体举世无敌。昔日欺她负她者，皆被她狠狠清算，宗门跪求原谅她不屑一顾。最终她平定天魔浩劫，以身补天，受万宗朝拜，与常渊大婚飞升，谱写万古传奇。</x:v>
       </x:c>
       <x:c r="I71" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；83集，主力长度；发布账号「长夜动漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；58集，次优长度；通用受众</x:v>
       </x:c>
       <x:c r="J71" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -9472,28 +9472,28 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
-        <x:v>魂穿百岁老太，零零后整顿全村</x:v>
+        <x:v>哥哥争宠我富家天下兄妹绑错系统爆红了</x:v>
       </x:c>
       <x:c r="D72" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E72" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F72" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 古装宫廷 / 婚姻情感 / 战神异能</x:v>
       </x:c>
       <x:c r="G72" s="10" t="str">
-        <x:v>筑创Ai漫剧</x:v>
+        <x:v>虾饭桶</x:v>
       </x:c>
       <x:c r="H72" s="10" t="str">
-        <x:v>24岁社畜林晚猝死后，穿越成顾家百岁老太太。面对极品亲戚争产、懦弱儿孙受欺、重男轻女旧俗、熟人骗局陷害、宗族道德绑架等重重困境，她以现代清醒头脑和通透智慧，一一化解危机、整顿家风，护住家人安稳。在带领全家逆袭翻身的过程中，她意外发现原主尘封半生的骨肉离别之痛。历经寻亲无果、善恶和解、遗憾释然，她最终领悟，人生无需圆满，带憾前行、温柔生活，便是重生最大的意义。</x:v>
+        <x:v>女总裁虾明月和她亲哥虾明理，穿越成大雍国巨贪丞相的儿女。最离谱的是，兄妹俩绑错了系统。她哥虾明理被绑定了女频宫斗系统，而虾明月则绑定男频败家系统，要求散尽贪官爹的小金库，护国安民。看兄妹联手，如何挽回口碑震惊满朝文武。</x:v>
       </x:c>
       <x:c r="I72" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；40集，次优长度；发布账号「筑创Ai漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；130集，次优长度；发布账号「虾饭桶」</x:v>
       </x:c>
       <x:c r="J72" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -9504,25 +9504,25 @@
         <x:v>09·03</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
-        <x:v>1970重生岁岁，不负韶华</x:v>
+        <x:v>祖传铜勺，我靠火锅干翻联盟</x:v>
       </x:c>
       <x:c r="D73" s="11" t="n">
-        <x:v>86</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F73" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G73" s="10" t="str">
-        <x:v>星文文化</x:v>
+        <x:v>趣创短剧</x:v>
       </x:c>
       <x:c r="H73" s="10" t="str">
-        <x:v>前世林秀禾掏心掏肺活了一辈子，铁饭碗让给弟弟，工资全数贴补娘家，升学名额拱手送人。她伺候二老、帮弟弟成家、供养侄子，熬得一身病痛。弥留之际躺在病床上，账户里只剩七块三毛钱。父母理所当然，你是姐姐，就该帮衬弟弟。弟弟冷眼旁观，姐，你别想拖累我。一朝重生，她回到1977年。</x:v>
+        <x:v>90年代，陈川订婚当日被未婚妻当众退婚，火锅店面临关店危机。绝境下，铜勺里的熊猫精被唤醒，将古法火锅秘方传给陈川，前来寻衅的混混刀哥被火锅美味所折服，归顺为陈川的小弟。熊猫精告知陈川，老店镇守美食龙脉，极恶联盟靠化工调料摧毁本土风味，他父亲更是遭联盟暗害，唯有集齐九大绝世食材才能修复龙脉。陈川带着温夕、刀哥踏上寻找食材之路，一路对抗联盟设下的毒瘴等陷阱，集齐食材，赢得厨艺比赛，将中华美食发扬光大。</x:v>
       </x:c>
       <x:c r="I73" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；86集，主力长度；发布账号「星文文化」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；79集，主力长度；发布账号「趣创短剧」</x:v>
       </x:c>
       <x:c r="J73" s="11" t="n">
         <x:v>7.5</x:v>
@@ -9664,25 +9664,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
-        <x:v>山里来的小丫头，专治都市不服第三季</x:v>
+        <x:v>开局成废后我反手养出十万御林军</x:v>
       </x:c>
       <x:c r="D78" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E78" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F78" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G78" s="10" t="str">
-        <x:v>动了个漫剧场</x:v>
+        <x:v>天桥热血剧场</x:v>
       </x:c>
       <x:c r="H78" s="10" t="str">
-        <x:v>被豪门未婚夫当众退婚，山里来的莫清舞却反手捏碎大劳，吓蒙全场！她不认银行卡，只认烤肠，5块救活京城首富，顺手压制顾家掌权人顾夜寒体内寒毒。从被嘲村姑到人人争抢的小神医，她靠天生神力、望气奇术一路打脸豪门、横扫黑市、硬闯秘境。七块混沌圣宝碎片背后，藏着能救心上人、也能毁灭苍生的惊天秘密。为了救顾夜寒和冷霄，她要把都市、古武、玄武大陆统统掀翻！</x:v>
+        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
       </x:c>
       <x:c r="I78" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「天桥热血剧场」</x:v>
       </x:c>
       <x:c r="J78" s="11" t="n">
         <x:v>9</x:v>
@@ -9696,7 +9696,7 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
-        <x:v>开局成废后我反手养出十万御林军</x:v>
+        <x:v>穿回八零我凭厨艺旺翻全家</x:v>
       </x:c>
       <x:c r="D79" s="11" t="n">
         <x:v>70</x:v>
@@ -9705,16 +9705,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F79" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>年代怀旧 / 美食治愈</x:v>
       </x:c>
       <x:c r="G79" s="10" t="str">
-        <x:v>天桥热血剧场</x:v>
+        <x:v>红颜剧场</x:v>
       </x:c>
       <x:c r="H79" s="10" t="str">
-        <x:v>现代边防军医沈清辞穿越大周，沦为遭诬陷通敌、受罚贬至大营的罪奴。她绑定系统，驯马王、查办贪腐、防控疫病，揪出外敌密探。依托西郊军营，整合边军、旧部与义勇，历经战事整编大军。班师回朝后，面对帝王猜忌加害，她公示罪证，发布檄文，另建大章王朝，登上女帝之位。</x:v>
+        <x:v>现代女厨师穿越成80年代恶婆婆张桂芬，绑定灵泉空间系统，面对家徒四壁、儿媳垂危、孙女被卖的烂摊子，凭借出神入化的厨艺与灵泉水，救儿媳、赎孙女、治儿子、斗恶霸，带领全家从乡镇集市摆摊卖卤味，一路逆袭至县城开店，最终让宋家从穷困潦倒走向富足兴旺，彻底扭转恶婆之名。</x:v>
       </x:c>
       <x:c r="I79" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「天桥热血剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；发布账号「红颜剧场」</x:v>
       </x:c>
       <x:c r="J79" s="11" t="n">
         <x:v>9</x:v>
@@ -9728,25 +9728,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
-        <x:v>捡到女帝，逆命双生第三季</x:v>
+        <x:v>重生六零之护妻猎王</x:v>
       </x:c>
       <x:c r="D80" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E80" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F80" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>年代怀旧 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G80" s="10" t="str">
-        <x:v>每日欢乐漫剧</x:v>
+        <x:v>静剧社</x:v>
       </x:c>
       <x:c r="H80" s="10" t="str">
-        <x:v>大夏废太子王腾落难之际觉醒签到系统，凭腹黑智谋与系统外挂扮猪吃虎，收服妖兽宗门，集结羊老头、鬼谷子、九尾天后等一众助力，和野心阴鸷的三皇子夏尤阵营展开权谋与实力的层层博弈。女主柳颜汐是瑶池女帝转世，兼具软萌娇羞与杀伐果断的极致反差，与王腾生死相伴、双向护持。最终二人携手君临天下，以世纪婚礼与天降祥瑞宣告真龙归位，全程密集打脸爽点、高甜宠妻与玄幻战斗名场面。</x:v>
+        <x:v>顶级战神陆峥重生六零，沦为村里遭人唾弃的烂赌废物。开局债主登门，妻子沈知宁受尽欺凌、饥寒交迫。他闯风雪岭猎兽采参，凭本事碾压恶霸，靠灵芝换取身份。斗恶护妻，带领村民开荒拓路，盘活山村，逆袭过上红火安稳日子。</x:v>
       </x:c>
       <x:c r="I80" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；91集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；63集，主力长度；发布账号「静剧社」</x:v>
       </x:c>
       <x:c r="J80" s="11" t="n">
         <x:v>9</x:v>
@@ -9760,7 +9760,7 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
-        <x:v>穿回八零我凭厨艺旺翻全家</x:v>
+        <x:v>重生后我靠鉴宝慧眼翻身</x:v>
       </x:c>
       <x:c r="D81" s="11" t="n">
         <x:v>70</x:v>
@@ -9769,16 +9769,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F81" s="10" t="str">
-        <x:v>年代怀旧 / 美食治愈</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G81" s="10" t="str">
-        <x:v>红颜剧场</x:v>
+        <x:v>意欢剧场</x:v>
       </x:c>
       <x:c r="H81" s="10" t="str">
-        <x:v>现代女厨师穿越成80年代恶婆婆张桂芬，绑定灵泉空间系统，面对家徒四壁、儿媳垂危、孙女被卖的烂摊子，凭借出神入化的厨艺与灵泉水，救儿媳、赎孙女、治儿子、斗恶霸，带领全家从乡镇集市摆摊卖卤味，一路逆袭至县城开店，最终让宋家从穷困潦倒走向富足兴旺，彻底扭转恶婆之名。</x:v>
+        <x:v>孤儿林晚晚前世花光五百万装名媛，被揭穿后负债坠桥。重生回十八岁，她决心用真本事逆袭，积累资本，创立晚星珠宝鉴定工作室，招募被陷害的顶尖人才安沛，打造自主高定品牌。面对前世仇敌与同行打压，她冷静设局，在顶级晚宴上揭穿阴谋，最终收获事业、友情与自我认可。</x:v>
       </x:c>
       <x:c r="I81" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；发布账号「红颜剧场」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「意欢剧场」</x:v>
       </x:c>
       <x:c r="J81" s="11" t="n">
         <x:v>9</x:v>
@@ -9792,25 +9792,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
-        <x:v>重生六零之护妻猎王</x:v>
+        <x:v>长姐归来，以爱托举全家！</x:v>
       </x:c>
       <x:c r="D82" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F82" s="10" t="str">
-        <x:v>年代怀旧 / 婚姻情感</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G82" s="10" t="str">
-        <x:v>静剧社</x:v>
+        <x:v>一支喵</x:v>
       </x:c>
       <x:c r="H82" s="10" t="str">
-        <x:v>顶级战神陆峥重生六零，沦为村里遭人唾弃的烂赌废物。开局债主登门，妻子沈知宁受尽欺凌、饥寒交迫。他闯风雪岭猎兽采参，凭本事碾压恶霸，靠灵芝换取身份。斗恶护妻，带领村民开荒拓路，盘活山村，逆袭过上红火安稳日子。</x:v>
+        <x:v>现代强者叶青萝意外穿越，成为被苏家无情驱逐的假千金，一朝跌落泥泞。幸而她重回清贫的亲生叶家，解锁随身空间逆袭开挂。面对破败家境、负债困境与邻里非议，叶青萝凭借精湛厨艺、出众文笔经商创收，踏实打拼。她温柔护佑父母幼弟，化解周遭纷争，步步深耕、稳步致富，带领平凡叶家摆脱贫苦，安家立业，阖家奔赴圆满红火的人生巅峰。</x:v>
       </x:c>
       <x:c r="I82" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；63集，主力长度；发布账号「静剧社」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「一支喵」</x:v>
       </x:c>
       <x:c r="J82" s="11" t="n">
         <x:v>9</x:v>
@@ -9824,28 +9824,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
-        <x:v>重生后我靠鉴宝慧眼翻身</x:v>
+        <x:v>为了活命我拼命整活</x:v>
       </x:c>
       <x:c r="D83" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E83" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F83" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G83" s="10" t="str">
-        <x:v>意欢剧场</x:v>
+        <x:v>留阿布</x:v>
       </x:c>
       <x:c r="H83" s="10" t="str">
-        <x:v>孤儿林晚晚前世花光五百万装名媛，被揭穿后负债坠桥。重生回十八岁，她决心用真本事逆袭，积累资本，创立晚星珠宝鉴定工作室，招募被陷害的顶尖人才安沛，打造自主高定品牌。面对前世仇敌与同行打压，她冷静设局，在顶级晚宴上揭穿阴谋，最终收获事业、友情与自我认可。</x:v>
+        <x:v>62岁骚男主播吴耐意外穿越，成了重病缠身的孤寡老大爷。手握三百万存款与四套房产，却叠满肝癌晚期、重度糖尿病、脑血栓等病痛buff，生命仅剩十四天！危急时刻，惊讶系统激活只要让自家三名美女租客惊讶，就能兑换寿命续命。温柔小护士、飒爽女刑警、风情女租户轮番登场。为了活下去，吴耐花式搞事，免房租、豪掷消费、秀逆天游戏操作，不断制造名场面，一边对抗病痛，一边疯狂刷惊讶值，开启爆笑续命逆袭生活。</x:v>
       </x:c>
       <x:c r="I83" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×2；70集，主力长度；发布账号「意欢剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「留阿布」</x:v>
       </x:c>
       <x:c r="J83" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -9856,28 +9856,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
-        <x:v>长姐归来，以爱托举全家！</x:v>
+        <x:v>婴语大师</x:v>
       </x:c>
       <x:c r="D84" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E84" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F84" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G84" s="10" t="str">
-        <x:v>一支喵</x:v>
+        <x:v>小天短剧</x:v>
       </x:c>
       <x:c r="H84" s="10" t="str">
-        <x:v>现代强者叶青萝意外穿越，成为被苏家无情驱逐的假千金，一朝跌落泥泞。幸而她重回清贫的亲生叶家，解锁随身空间逆袭开挂。面对破败家境、负债困境与邻里非议，叶青萝凭借精湛厨艺、出众文笔经商创收，踏实打拼。她温柔护佑父母幼弟，化解周遭纷争，步步深耕、稳步致富，带领平凡叶家摆脱贫苦，安家立业，阖家奔赴圆满红火的人生巅峰。</x:v>
+        <x:v>18岁少女陆星辰意外觉醒“婴语翻译”系统，能听懂婴儿的每一次啼哭与呢喃。凭借这份独特天赋，她从一个普通大学生成长为京城顶级育儿专家，用爱与耐心呵护着豪门继承人们的健康成长。在数十年的守护中，陆星辰不仅用真心赢得了孩子们的依赖和全城大佬的敬重，更将这些孩子培养成三观正、有担当的栋梁之才。故事传递了“用心倾听、用爱陪伴”的育儿真谛，展现了平凡女孩凭借善良与专业逆袭人生的正能量。</x:v>
       </x:c>
       <x:c r="I84" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；75集，主力长度；发布账号「一支喵」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；65集，主力长度；发布账号「小天短剧」</x:v>
       </x:c>
       <x:c r="J84" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -9888,28 +9888,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
-        <x:v>为了活命我拼命整活</x:v>
+        <x:v>小五替我择良缘</x:v>
       </x:c>
       <x:c r="D85" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E85" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F85" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G85" s="10" t="str">
-        <x:v>留阿布</x:v>
+        <x:v>一碗猫酱</x:v>
       </x:c>
       <x:c r="H85" s="10" t="str">
-        <x:v>62岁骚男主播吴耐意外穿越，成了重病缠身的孤寡老大爷。手握三百万存款与四套房产，却叠满肝癌晚期、重度糖尿病、脑血栓等病痛buff，生命仅剩十四天！危急时刻，惊讶系统激活只要让自家三名美女租客惊讶，就能兑换寿命续命。温柔小护士、飒爽女刑警、风情女租户轮番登场。为了活下去，吴耐花式搞事，免房租、豪掷消费、秀逆天游戏操作，不断制造名场面，一边对抗病痛，一边疯狂刷惊讶值，开启爆笑续命逆袭生活。</x:v>
+        <x:v>兄长出征前，留下鹦鹉小五陪伴姜疏萤。寿宴之上，养女阿娇觊觎小五，未婚夫裴渊偏帮外人，肆意放走鸟儿。姜疏萤心死决然退婚，却发现小五落入逍遥王陆砚卿手中，还提出以人换鸟。侯府内宅步步构陷，继母与父亲的阴谋层层揭开，姜疏萤携鹦鹉，在王爷相助之下，撕破虚伪假面，复仇逆袭，觅得良缘。</x:v>
       </x:c>
       <x:c r="I85" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「留阿布」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；53集，次优长度；发布账号「一碗猫酱」</x:v>
       </x:c>
       <x:c r="J85" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -9920,28 +9920,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
-        <x:v>婴语大师</x:v>
+        <x:v>穿越乱世：每天一份拼好饭</x:v>
       </x:c>
       <x:c r="D86" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E86" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F86" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G86" s="10" t="str">
-        <x:v>小天短剧</x:v>
+        <x:v>西西漫剧（求关注）</x:v>
       </x:c>
       <x:c r="H86" s="10" t="str">
-        <x:v>18岁少女陆星辰意外觉醒“婴语翻译”系统，能听懂婴儿的每一次啼哭与呢喃。凭借这份独特天赋，她从一个普通大学生成长为京城顶级育儿专家，用爱与耐心呵护着豪门继承人们的健康成长。在数十年的守护中，陆星辰不仅用真心赢得了孩子们的依赖和全城大佬的敬重，更将这些孩子培养成三观正、有担当的栋梁之才。故事传递了“用心倾听、用爱陪伴”的育儿真谛，展现了平凡女孩凭借善良与专业逆袭人生的正能量。</x:v>
+        <x:v>林渊一觉睡醒，穿越回乱世，正当他快饿晕的时候，手机上跳出一个拼好饭系统，余额19块8毛，每天一份外卖续命。他反手把珍珠奶茶兑水当回力汤卖出爆价，用一碗工业香精熬的糊糊引爆全城疯抢！就凭这点余额，他硬生生从饿殍堆里杀出血路。开局一副烂牌？19块8，照样把这乱世玩翻天！</x:v>
       </x:c>
       <x:c r="I86" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；65集，主力长度；发布账号「小天短剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；60集，主力长度；发布账号「西西漫剧（求关注）」</x:v>
       </x:c>
       <x:c r="J86" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -9952,28 +9952,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
-        <x:v>小小萌娃，神瞳赶海带家人致富第二季</x:v>
+        <x:v>萌小宝寻爹记</x:v>
       </x:c>
       <x:c r="D87" s="11" t="n">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E87" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F87" s="10" t="str">
-        <x:v>种田囤货 / 萌宝治愈 / 战神异能</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="G87" s="10" t="str">
-        <x:v>平川动画</x:v>
+        <x:v>小火短剧</x:v>
       </x:c>
       <x:c r="H87" s="10" t="str">
-        <x:v>一觉醒来，秦放绑定了赶海系统。面对城市的快节奏和无尽压力，秦放决定直接回到小时候生活的渔村当渔民。看着开局就获得的两个神级技能，秦放知道他轻松赚钱的日子就要来了！赶海提示，直接将藏匿在沙滩海水下的海货位置标记出来！不仅如此提示还可以提前预测出极品海货出现的区域。每次赶海都能收获满满！而且还有资源翻倍去进一步扩大收益！</x:v>
+        <x:v>社恐编剧苏念带五岁儿子躲了五年，儿子却在红毯上当众抱住顶流影帝喊爹地！心机女配设局陷害、全网黑料铺天盖地，萌宝化身最强助攻替妈撕碎伪装。当结婚证曝光、影帝跪地求婚——原来这五年，他找她找疯了。迟来的告白，甜到爆炸。</x:v>
       </x:c>
       <x:c r="I87" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；108集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；62集，主力长度；发布账号「小火短剧」</x:v>
       </x:c>
       <x:c r="J87" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -9984,28 +9984,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
-        <x:v>我养的小兽怎么都成大佬了第二季</x:v>
+        <x:v>转夫运</x:v>
       </x:c>
       <x:c r="D88" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E88" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F88" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G88" s="10" t="str">
-        <x:v>迷声漫剧</x:v>
+        <x:v>饼花</x:v>
       </x:c>
       <x:c r="H88" s="10" t="str">
-        <x:v>赵橙知穿越星际兽世，百年前曾在废土星救下并养大五只幼兽，再睁眼却成了黑市待拍卖的F级废雌。危急关头，她唤出当年那只红狐幼崽——如今战功赫赫的归墟星将军千折意，被他强势救下护在身侧。随着校园风波迭起，白虎族首领庄九牧也认出了她的身份。昔日温顺小兽已成执掌一方的顶级大佬，百年执念与偏执守护尽数爆发，双强大佬开启极致修罗场</x:v>
+        <x:v>李媛带着两个女儿离开旧日困境，意外获得随身空间，在流云县从一碗热气腾腾的面开始，重新经营人生。重生归来的王灿带着对未来的记忆，与她并肩摆摊、种菜、囤粮，把清苦日子过得越来越有盼头。常年诸事不顺的秀才谢砚之，因吃到李媛亲手做的饭重获好运，也走进她们的生活。面对异常天候和未知前路，李媛、王灿、谢砚之与亲友彼此扶持，学盘炕、备物资、办婚事、护家人，在寒冬到来前守住烟火与温暖，也在一路相伴中找到新的生活。</x:v>
       </x:c>
       <x:c r="I88" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；78集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；104集，次优长度；发布账号「饼花」</x:v>
       </x:c>
       <x:c r="J88" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -10016,10 +10016,10 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
-        <x:v>烟火年代：我有灵泉空间第一季</x:v>
+        <x:v>这一世，换我走向你</x:v>
       </x:c>
       <x:c r="D89" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
         <x:v>其他</x:v>
@@ -10028,16 +10028,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G89" s="10" t="str">
-        <x:v>哒哒哒剧场</x:v>
+        <x:v>棋鸿信息</x:v>
       </x:c>
       <x:c r="H89" s="10" t="str">
-        <x:v>七零年代，现代青年林墨穿越到被家人压榨迫害的知青身上，觉醒1元秒杀系统，开局秒杀储物戒。他手撕吸血原生家庭，拿到下乡名额前往极北大岭屯。一路凭借系统、念力与神级医术化解危机，结识王建军、方家姐妹。在乡村治病救人、打猎建功，周旋各方势力，对抗官场反派，积累财富与人脉，在七十年代的时代浪潮中闯出自己的一番天地。</x:v>
+        <x:v>梁琪琪前世被丈夫赵添算计，被夺走家产、毁掉身体，含恨离世。重生回到赵添向她求婚现场，她假意答应求婚，收起爱意冷静复仇。她冻结赵添权限，收集赵添与杨雪的阴谋证据，在订婚宴当众揭穿二人的丑恶算计。前世葬礼上，她知晓顾深多年默默的深情与少年约定。洗清过往伤害后，梁琪琪放下伤痛，奔赴一直守候自己的顾深，这一世换她主动走向爱人。</x:v>
       </x:c>
       <x:c r="I89" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；131集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；72集，主力长度；发布账号「棋鸿信息」</x:v>
       </x:c>
       <x:c r="J89" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -10048,25 +10048,25 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>修仙归来护家人第二季</x:v>
+        <x:v>魂归处：不待帝王悔</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸 / 战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>夏十七</x:v>
+        <x:v>片单挖掘机</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>男人修仙六百年后，正在渡劫飞升之时，陨落在雷劫中，回到了他原本穿越前的世界，意外发现已经过去了四十年。而他从未见过的好大儿已经给自己生了三个孙子。从此以后，他利用自己的能力，不仅带着家人过上好日子，还成为各个大佬最尊敬的人。</x:v>
+        <x:v>皇后沈知微的父兄戍守边关重伤待援，她苦苦恳求帝王萧景珩下旨救人，却因贵妃柳如烟从中作梗，圣旨被一再搁置。父亲战死、兄长残伤归来，沈知微心死，借助系统开启假死程序，纵火焚毁坤宁宫。她灵魂滞留世间见证因果清算，萧景珩查清全部真相，严惩柳氏一族，对沈家百般补偿，深陷无尽悔恨。面对帝王迟来的忏悔，沈知微选择绝不原谅，了结全部羁绊，终于得以脱离这个世界，为自己重获新生。</x:v>
       </x:c>
       <x:c r="I90" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；72集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；43集，次优长度；发布账号「片单挖掘机」</x:v>
       </x:c>
       <x:c r="J90" s="11" t="n">
         <x:v>8</x:v>
@@ -10080,28 +10080,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>嫁将军卑微时躺赢人生第二季</x:v>
+        <x:v>太学废柴班拯救计划</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>131</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F91" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>云朵邮递员</x:v>
+        <x:v>小曲动漫</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>荒年乱世，林润润携空间与弟弟穿越而来，与顾清止携手脱离顾家，建立清林村。凭借空间物资与现代知识，他们推行工分制，发展养殖、种植、香皂等产业，让百姓逐渐吃饱穿暖、安居乐业。与此同时，顾清止查明母亲被害真相，与林润润共同对抗柳荷花及背后的侯府。清林村不断扩张、招纳流民、训练村民、修筑高墙，在危机中壮大。众人还救下励王世子，获得王府支持。最终，清林村拥有土地、产业、人口和武装，乱世中的桃源初具雏形。</x:v>
+        <x:v>林非晚穿成尚书府不受宠的嫡长女，嫁给了镇国将军霍云霆。她以现代商战智慧执掌公府财政，把太学废柴三害调教成科举前三甲，更带领他们揪出赈灾粮贪腐黑幕。诈死的战神丈夫现身，与她并肩作战、步步为营揭开惊天大案，最终朝堂清明，夫妻情深，昔日纨绔皆成治国栋梁。</x:v>
       </x:c>
       <x:c r="I91" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；131集，次优长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；84集，主力长度；发布账号「小曲动漫」</x:v>
       </x:c>
       <x:c r="J91" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -10112,28 +10112,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>小五替我择良缘</x:v>
+        <x:v>携手千里渡荒年</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F92" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>一碗猫酱</x:v>
+        <x:v>逗小包</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>兄长出征前，留下鹦鹉小五陪伴姜疏萤。寿宴之上，养女阿娇觊觎小五，未婚夫裴渊偏帮外人，肆意放走鸟儿。姜疏萤心死决然退婚，却发现小五落入逍遥王陆砚卿手中，还提出以人换鸟。侯府内宅步步构陷，继母与父亲的阴谋层层揭开，姜疏萤携鹦鹉，在王爷相助之下，撕破虚伪假面，复仇逆袭，觅得良缘。</x:v>
+        <x:v>现代女主意外穿越荒年，成为温四月，身陷逃荒绝境。危难之际，憨厚赤诚的夫君厉青山始终护她周全，为她遮风挡雨。绝境之中，温四月意外觉醒灵泉空间，手握求生底牌。逃亡路上，她褪去怯懦，凭借智慧与异能，习得炼盐之术、寻觅山野食粮，带领同行众人绝境求生。她心怀善意，坚守本心，与厉青山相互扶持、并肩前行，在乱世绝境中扎根希望，于颠沛流离里守护烟火与温情，一步步奔赴生机与新生。</x:v>
       </x:c>
       <x:c r="I92" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；53集，次优长度；发布账号「一碗猫酱」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；117集，次优长度；发布账号「逗小包」</x:v>
       </x:c>
       <x:c r="J92" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -10144,28 +10144,28 @@
         <x:v>09·04</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
-        <x:v>我的渔船通龙宫第一季</x:v>
+        <x:v>虾仁穿成驸马爷，公主谁爱娶谁娶！</x:v>
       </x:c>
       <x:c r="D93" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E93" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F93" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G93" s="10" t="str">
-        <x:v>六翼动漫</x:v>
+        <x:v>虾扯蛋动画</x:v>
       </x:c>
       <x:c r="H93" s="10" t="str">
-        <x:v>被兄弟坑走祖宅以及女友背弃夺走金镯的张屿，为了给妹妹治病，以及报复兄弟和女友，拿回祖宅和金镯，凭借“海洋雷达”系统，捕获珍稀海产品卖钱和治病，还与海底龙宫龙王结交，实现预期目标，并成为海产大亨，迎娶白富美。</x:v>
+        <x:v>你，名为虾仁！穿越到一个架空世界，名为大乾王朝！无系统！而你，正是开国大将军虾国公之子，虾仁！当继承原主的记忆后，原本想当个纨绔，每天溜溜鸟，斗蝈蝈，潇洒过一生！可是，老爹你确告诉我，家里已经家徒四壁，而我，还有一个大乾嫡长公主的未婚妻？为了活下去，只能想办法做生意，而做生意的第一天就碰见隐藏身份的未婚妻，从此，故事由此展开！</x:v>
       </x:c>
       <x:c r="I93" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；65集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；91集，主力长度；发布账号「虾扯蛋动画」</x:v>
       </x:c>
       <x:c r="J93" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -10272,25 +10272,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
-        <x:v>我救的父女成了我的靠山第二季</x:v>
+        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F97" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 现实反转</x:v>
       </x:c>
       <x:c r="G97" s="10" t="str">
-        <x:v>潮汐心动放映厅</x:v>
+        <x:v>云间漫剧-玉川</x:v>
       </x:c>
       <x:c r="H97" s="10" t="str">
-        <x:v>十八年前苏云出手救下困境中的林野与女儿林诗诗。十八年后苏云挣脱险境，与已是财团董事长的林野重逢。一桩意外揭开身世秘密，林诗诗并非林野骨肉，她的生父为护林野不幸离世，生母与妹妹正深陷生活困境。林诗诗得知身世大受震动，为救治病重生母毅然捐献肝脏。历经生死磨难，她和欢喜冤家陆时宇互生爱慕。众人揭穿包工头讨回公道，抚平旧日伤痕，苏云喜得龙凤胎，两代人在烟火生活里收获圆满团圆。</x:v>
+        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；78集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
       </x:c>
       <x:c r="J97" s="11" t="n">
         <x:v>8</x:v>
@@ -10304,28 +10304,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
+        <x:v>三年，我不装了</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>家庭伦理 / 现实反转</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
+        <x:v>布噜布噜剧场</x:v>
       </x:c>
       <x:c r="H98" s="10" t="str">
-        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
+        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
       </x:c>
       <x:c r="I98" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
       </x:c>
       <x:c r="J98" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -10336,25 +10336,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>三年，我不装了</x:v>
+        <x:v>沙县厨神</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E99" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>美食治愈 / 战神异能</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>布噜布噜剧场</x:v>
+        <x:v>新视觉漫剧心动剧场</x:v>
       </x:c>
       <x:c r="H99" s="10" t="str">
-        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
       </x:c>
       <x:c r="I99" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
       </x:c>
       <x:c r="J99" s="11" t="n">
         <x:v>7.5</x:v>
@@ -10368,28 +10368,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>沙县厨神</x:v>
+        <x:v>九零绝境潮汐系统护我</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>113</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F100" s="10" t="str">
-        <x:v>美食治愈 / 战神异能</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>新视觉漫剧心动剧场</x:v>
+        <x:v>杨桃剧院</x:v>
       </x:c>
       <x:c r="H100" s="10" t="str">
-        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
+        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
       </x:c>
       <x:c r="I100" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
       </x:c>
       <x:c r="J100" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -10400,25 +10400,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>九零绝境潮汐系统护我</x:v>
+        <x:v>予你情深，岁岁相守</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>杨桃剧院</x:v>
+        <x:v>啾啾说漫</x:v>
       </x:c>
       <x:c r="H101" s="10" t="str">
-        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
       </x:c>
       <x:c r="I101" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
       </x:c>
       <x:c r="J101" s="11" t="n">
         <x:v>7</x:v>
@@ -10432,25 +10432,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>予你情深，岁岁相守</x:v>
+        <x:v>仙界老祖非要当我哥</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F102" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="G102" s="10" t="str">
-        <x:v>啾啾说漫</x:v>
+        <x:v>青青漫剧</x:v>
       </x:c>
       <x:c r="H102" s="10" t="str">
-        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
       </x:c>
       <x:c r="I102" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
       </x:c>
       <x:c r="J102" s="11" t="n">
         <x:v>7</x:v>
@@ -10464,25 +10464,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>仙界老祖非要当我哥</x:v>
+        <x:v>农家穗安：饼香满镇</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F103" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>青青漫剧</x:v>
+        <x:v>奇趣漫剧场</x:v>
       </x:c>
       <x:c r="H103" s="10" t="str">
-        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
       </x:c>
       <x:c r="I103" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
       </x:c>
       <x:c r="J103" s="11" t="n">
         <x:v>7</x:v>
@@ -10496,25 +10496,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>农家穗安：饼香满镇</x:v>
+        <x:v>回乡种田，手握灵泉养全家</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F104" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>种田囤货</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>奇趣漫剧场</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="H104" s="10" t="str">
-        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
+        <x:v>家破、失业、母亲癌症晚期——安南暖以为，回到团山村老家，只是陪家人熬过人生最黑的一段日子。可谁也没想到，一滴鲜血唤醒了床头那盆沉睡多年的枯木，从此，悄然改变了整个安家老宅的命运。破败的院子长出满园生机，病重的母亲重燃希望，沉寂多年的山村，也在她手中一点点苏醒。可灵泉带来的，从来不只是馈赠。秘密、因果、病痛、欲望，接踵而至。安南暖原本只想守住一个家，却一步步把老家打造成了人人向往的桃花源。</x:v>
       </x:c>
       <x:c r="I104" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；96集，主力长度；发布账号「星屿漫剧场」</x:v>
       </x:c>
       <x:c r="J104" s="11" t="n">
         <x:v>7</x:v>
@@ -10528,25 +10528,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>回乡种田，手握灵泉养全家</x:v>
+        <x:v>嫡女归来，厨香撼京华</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F105" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>锦书映年华</x:v>
       </x:c>
       <x:c r="H105" s="10" t="str">
-        <x:v>家破、失业、母亲癌症晚期——安南暖以为，回到团山村老家，只是陪家人熬过人生最黑的一段日子。可谁也没想到，一滴鲜血唤醒了床头那盆沉睡多年的枯木，从此，悄然改变了整个安家老宅的命运。破败的院子长出满园生机，病重的母亲重燃希望，沉寂多年的山村，也在她手中一点点苏醒。可灵泉带来的，从来不只是馈赠。秘密、因果、病痛、欲望，接踵而至。安南暖原本只想守住一个家，却一步步把老家打造成了人人向往的桃花源。</x:v>
+        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
       </x:c>
       <x:c r="I105" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；96集，主力长度；发布账号「星屿漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
       </x:c>
       <x:c r="J105" s="11" t="n">
         <x:v>7</x:v>
@@ -10560,25 +10560,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>嫡女归来，厨香撼京华</x:v>
+        <x:v>山野新婚暖光阴</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>小尘剧场</x:v>
       </x:c>
       <x:c r="H106" s="10" t="str">
-        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
+        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
       </x:c>
       <x:c r="I106" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
       </x:c>
       <x:c r="J106" s="11" t="n">
         <x:v>7</x:v>
@@ -10592,25 +10592,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>山野新婚暖光阴</x:v>
+        <x:v>我的小土狗竟有大帝之姿</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>小尘剧场</x:v>
+        <x:v>嘉午纪</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
+        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
         <x:v>7</x:v>
@@ -10624,25 +10624,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>我的小土狗竟有大帝之姿</x:v>
+        <x:v>替嫁棺妃</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>嘉午纪</x:v>
+        <x:v>诗婳影视</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
+        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
         <x:v>7</x:v>
@@ -10656,25 +10656,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>替嫁棺妃</x:v>
+        <x:v>末世的最后一餐</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F109" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>诗婳影视</x:v>
+        <x:v>团子动漫</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
+        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
         <x:v>7</x:v>
@@ -10688,10 +10688,10 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>末世的最后一餐</x:v>
+        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
@@ -10699,14 +10699,12 @@
       <x:c r="F110" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G110" s="10" t="str">
-        <x:v>团子动漫</x:v>
-      </x:c>
+      <x:c r="G110" s="10" t="str"/>
       <x:c r="H110" s="10" t="str">
-        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
+        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
         <x:v>7</x:v>
@@ -10720,23 +10718,25 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
+        <x:v>被赶走的保姆，竟是真夫人</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str"/>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>九鲤动漫</x:v>
+      </x:c>
       <x:c r="H111" s="10" t="str">
-        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
+        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
         <x:v>7</x:v>
@@ -10750,28 +10750,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>被赶走的保姆，竟是真夫人</x:v>
+        <x:v>新婚的羔羊</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
+        <x:v>战神漫剧</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
+        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6.5</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -10782,28 +10782,28 @@
         <x:v>09·05</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>七旬老太，勇闯惊悚游戏第一季</x:v>
+        <x:v>人到中年我逆袭成百草圣手</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>新娱剧场</x:v>
+        <x:v>极剧-热血剧场</x:v>
       </x:c>
       <x:c r="H113" s="10" t="str">
-        <x:v>七十岁农村老太李树英为救孙女主动报名进入惊悚游戏，获“老当益壮”与“隔代亲光环”技能。C级副本《伯爵庄园》中，她揭穿邪神永生阴谋，终结红衣侍女。B级副本《疯镇》里，她化身李阿婆暗中助人，协助消灭疯狂源头。完美通关后声名渐起，却被总系统盯上，新副本正等待她破解。</x:v>
+        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
       </x:c>
       <x:c r="I113" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×1；67集，主力长度；续季/系列续作</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；50集，次优长度；发布账号「极剧-热血剧场」</x:v>
       </x:c>
       <x:c r="J113" s="11" t="n">
-        <x:v>6.5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R3b65405495044fa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R200d2ea7cd09440c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rad738c6f8c4f4e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Raf5b4c23d7a54802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R0bbb6f95b9c44c76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R486c3a9960bc4055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R62e3ed9389494ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R9e0638377cc442ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rb9b98004174d4b91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Rec6ad0c69bb94725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R562f24cff3c04a5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R4d55c6e57df44e8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -359,7 +359,7 @@
         <x:v>08-10 20:00</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E2" s="10" t="n">
         <x:v>375</x:v>
@@ -372,7 +372,7 @@
       </x:c>
       <x:c r="H2" s="11" t="str"/>
       <x:c r="I2" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -386,7 +386,7 @@
         <x:v>08-08 17:00</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E3" s="10" t="n">
         <x:v>66</x:v>
@@ -401,7 +401,7 @@
         <x:v>4289</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -442,7 +442,7 @@
         <x:v>08-11 16:40</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E5" s="10" t="n">
         <x:v>82</x:v>
@@ -455,7 +455,7 @@
       </x:c>
       <x:c r="H5" s="11" t="str"/>
       <x:c r="I5" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -469,7 +469,7 @@
         <x:v>08-14 09:00</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="10" t="n">
         <x:v>788</x:v>
@@ -484,7 +484,7 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
+        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -521,28 +521,28 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>天灾囤货录，善恶见人心</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>08-10 16:30</x:v>
+        <x:v>06-29 17:30</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
-        <x:v>151</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>种田囤货 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>852</x:v>
+        <x:v>1834</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -550,25 +550,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>收租老汉</x:v>
+        <x:v>天灾囤货录，善恶见人心</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>08-10 06:00</x:v>
+        <x:v>08-10 16:30</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
-        <x:v>121</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>种田囤货 / 现实反转</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>8368</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
@@ -579,26 +579,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>重回八零，赶山狩猎养妻女</x:v>
+        <x:v>收租老汉</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>07-17 18:30</x:v>
+        <x:v>08-10 06:00</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="10" t="n">
-        <x:v>108</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G10" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="str"/>
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="n">
+        <x:v>8368</x:v>
+      </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -606,28 +608,26 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>06-29 17:30</x:v>
+        <x:v>07-17 18:30</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
-        <x:v>67</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F11" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G11" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="n">
-        <x:v>1834</x:v>
-      </x:c>
+        <x:v>年代怀旧 / 种田囤货 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str"/>
       <x:c r="I11" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-29</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -635,26 +635,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>重生归来，四小姐她不装了</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>08-10 15:00</x:v>
+        <x:v>07-31 00:30</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F12" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G12" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="H12" s="11" t="str"/>
+        <x:v>逆袭打脸</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="n">
+        <x:v>371</x:v>
+      </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -662,28 +664,26 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>重生归来，四小姐她不装了</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>07-31 00:30</x:v>
+        <x:v>08-10 15:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:v>115</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="n">
-        <x:v>371</x:v>
-      </x:c>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-27、2026-08-28、2026-08-29、2026-08-30</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -745,28 +745,26 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>垃圾桶里的寻人启事</x:v>
+        <x:v>半梦半醒半清欢</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>08-08 18:00</x:v>
+        <x:v>07-20 10:00</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E16" s="10" t="n">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="n">
-        <x:v>4442</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -774,26 +772,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>孤城照山河第一季</x:v>
+        <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-10 17:13</x:v>
+        <x:v>08-08 18:00</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
-        <x:v>185</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F17" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G17" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="str"/>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>4442</x:v>
+      </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25、2026-08-28、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-21、2026-08-22、2026-08-23</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -801,26 +801,26 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>山王传奇</x:v>
+        <x:v>孤城照山河第一季</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-15 10:00</x:v>
+        <x:v>08-10 17:13</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E18" s="10" t="n">
-        <x:v>95</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F18" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str"/>
       <x:c r="I18" s="10" t="str">
-        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-22、2026-08-23、2026-08-25、2026-08-28、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -828,26 +828,26 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>我将恩人一家捡回村</x:v>
+        <x:v>山王传奇</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>08-13 10:00</x:v>
+        <x:v>08-15 10:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E19" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F19" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G19" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str"/>
       <x:c r="I19" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -855,26 +855,26 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>我将恩人一家捡回村</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>06-30 18:00</x:v>
+        <x:v>08-13 10:00</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E20" s="10" t="n">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F20" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G20" s="10" t="str">
-        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str"/>
       <x:c r="I20" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -882,26 +882,26 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>半梦半醒半清欢</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>07-20 10:00</x:v>
+        <x:v>06-30 18:00</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E21" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -936,28 +936,26 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>菌香深处见人心</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>07-13 14:00</x:v>
+        <x:v>08-21 17:00</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="H23" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -965,26 +963,26 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>一瓶奶走过两个清晨</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-10 09:00</x:v>
+        <x:v>08-18 15:11</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>136</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
+        <x:v>2026-08-19、2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -992,26 +990,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-21 10:00</x:v>
+        <x:v>07-13 14:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>169</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="I25" s="10" t="str">
-        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1019,26 +1019,26 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>07-20 14:00</x:v>
+        <x:v>08-10 09:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>196</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1104,28 +1104,28 @@
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="10" t="str">
-        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
+        <x:v>重生80：十斤大米娶媳妇</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>07-27 11:00</x:v>
+        <x:v>09-01 06:30</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>暖夏短剧</x:v>
+        <x:v>白尘</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str"/>
     </x:row>
@@ -1135,28 +1135,28 @@
       </x:c>
       <x:c r="B3" s="11"/>
       <x:c r="C3" s="10" t="str">
-        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
+        <x:v>这辆车，我不伺候了</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>08-31 20:00</x:v>
+        <x:v>09-01 18:07</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str"/>
     </x:row>
@@ -1166,28 +1166,28 @@
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="10" t="str">
-        <x:v>大婚当日立规矩，这婚我不结了</x:v>
+        <x:v>当妈妈开始较真的时候</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>08-31 17:00</x:v>
+        <x:v>09-01 09:00</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>云影漫剧</x:v>
+        <x:v>小圆子剧场</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str"/>
     </x:row>
@@ -1197,28 +1197,28 @@
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="10" t="str">
-        <x:v>假千金归来，全家后悔莫及</x:v>
+        <x:v>我有六个黄毛爹</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>08-30 18:42</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>100</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>小桃红动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str"/>
     </x:row>
@@ -1228,28 +1228,28 @@
       </x:c>
       <x:c r="B6" s="11"/>
       <x:c r="C6" s="10" t="str">
-        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
+        <x:v>烫嘴的免费午饭</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>08-29 16:15</x:v>
+        <x:v>09-01 11:00</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>156</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>漫漫画丫头</x:v>
+        <x:v>夏安安</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str"/>
     </x:row>
@@ -1259,29 +1259,23 @@
       </x:c>
       <x:c r="B7" s="11"/>
       <x:c r="C7" s="10" t="str">
-        <x:v>和媳妇离家出走，享受幸福人生</x:v>
+        <x:v>乱世繁花入君怀</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>08-31 15:58</x:v>
-      </x:c>
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="n">
-        <x:v>40</x:v>
-      </x:c>
+      <x:c r="G7" s="11" t="str"/>
       <x:c r="H7" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="str">
-        <x:v>小尘剧场</x:v>
-      </x:c>
+      <x:c r="J7" s="10" t="str"/>
       <x:c r="K7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
@@ -1290,28 +1284,28 @@
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="10" t="str">
-        <x:v>闻心：京华稚园录</x:v>
+        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>08-31 19:00</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>106</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
-        <x:v>阿云剧场</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str"/>
     </x:row>
@@ -1321,28 +1315,28 @@
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="10" t="str">
-        <x:v>猪场风起</x:v>
+        <x:v>这一次，换我保护妈妈</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>08-28 21:37</x:v>
+        <x:v>09-01 08:00</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>栗子说漫</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str"/>
     </x:row>
@@ -1352,28 +1346,28 @@
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="10" t="str">
-        <x:v>胡同走出的真少爷</x:v>
+        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>08-29 11:03</x:v>
+        <x:v>08-31 18:00</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>二里清风</x:v>
+        <x:v>江屿动漫</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str"/>
     </x:row>
@@ -1383,28 +1377,28 @@
       </x:c>
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="10" t="str">
-        <x:v>赘婿逆袭：我的亿万人生</x:v>
+        <x:v>一纸微光赴君归</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>08-31 11:45</x:v>
+        <x:v>08-27 21:48</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
-        <x:v>古装宫廷 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>清欢古风剧场</x:v>
+        <x:v>二里清风</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str"/>
     </x:row>
@@ -1414,28 +1408,28 @@
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="10" t="str">
-        <x:v>我住帐篷那天，整个豪宅区慌了</x:v>
+        <x:v>后厨藏真爱，中年遇良缘</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>08-31 11:00</x:v>
+        <x:v>08-24 08:00</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>95漫画</x:v>
+        <x:v>鲤鲤短剧</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str"/>
     </x:row>
@@ -1445,30 +1439,32 @@
       </x:c>
       <x:c r="B13" s="11"/>
       <x:c r="C13" s="10" t="str">
-        <x:v>万界轮回，我有亿万神话词条加身</x:v>
+        <x:v>梦醒八零年</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>08-31 13:17</x:v>
+        <x:v>09-01 17:28</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>195</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>云间漫剧-零七</x:v>
-      </x:c>
-      <x:c r="K13" s="10" t="str"/>
+        <x:v>阿釉说漫</x:v>
+      </x:c>
+      <x:c r="K13" s="10" t="str">
+        <x:v>方鹤安从一场预示悲剧的旧梦里醒来，回到八十年代。知晓前世遭遇的他，断然拒绝了夏妍菲的提亲，决心夺回求学的机会。面对夏妍菲处处偏袒青梅竹马的种种行为，方鹤安不再一味迁就忍让，守住自己的底线。几番波折过后，他如愿走进大学校园，结识了品性真诚的顾清依。他彻底放下过往的情感执念，认真经营当下的生活，两人互相理解扶持，跨过岁月里的重重阻碍，最终收获安稳又甜蜜的幸福。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -1476,28 +1472,28 @@
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="10" t="str">
-        <x:v>姐姐不买单我慌了</x:v>
+        <x:v>没去团建，却背上三十四万欠款</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>08-31 19:10</x:v>
+        <x:v>08-28 09:00</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>表妹剧场</x:v>
+        <x:v>会火短剧场</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str"/>
     </x:row>
@@ -1507,28 +1503,28 @@
       </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="10" t="str">
-        <x:v>烟火与匠心</x:v>
+        <x:v>镇北少帅</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>08-31 20:07</x:v>
+        <x:v>08-26 16:06</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>馆长玉先生剧场</x:v>
+        <x:v>灵梦剧场</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str"/>
     </x:row>
@@ -1538,28 +1534,28 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="10" t="str">
-        <x:v>她契约的都是星际大佬</x:v>
+        <x:v>当爸爸终于看见我</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>08-31 10:00</x:v>
+        <x:v>09-01 06:16</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>141</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>小何故事会</x:v>
       </x:c>
       <x:c r="K16" s="10" t="str"/>
     </x:row>
@@ -1569,28 +1565,28 @@
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="10" t="str">
-        <x:v>空间雷异能：废墟求生录</x:v>
+        <x:v>诸天拍卖行，我好物倾销万域崛起</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>08-31 20:00</x:v>
+        <x:v>08-31 07:27</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>杰瑞剧场</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str"/>
     </x:row>
@@ -1600,28 +1596,28 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="10" t="str">
-        <x:v>跨物种相亲，我连夜扛着冰山跑路</x:v>
+        <x:v>月月归梨</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>08-30 15:07</x:v>
+        <x:v>09-01 16:30</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
-        <x:v>菁禾</x:v>
+        <x:v>月下知棠</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str"/>
     </x:row>
@@ -1631,28 +1627,28 @@
       </x:c>
       <x:c r="B19" s="11"/>
       <x:c r="C19" s="10" t="str">
-        <x:v>疯丫头与花薄少：六宝助功</x:v>
+        <x:v>满堂寿宴皆虚情</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>08-28 19:07</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
-        <x:v>AI梦</x:v>
+        <x:v>饺子动画</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str"/>
     </x:row>
@@ -1662,28 +1658,28 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="10" t="str">
-        <x:v>礼金局中局</x:v>
+        <x:v>五年归期：我的崽成了团宠</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>08-29 11:00</x:v>
+        <x:v>09-01 09:00</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
-        <x:v>AI 风华</x:v>
+        <x:v>言安剧场</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str"/>
     </x:row>
@@ -1693,28 +1689,28 @@
       </x:c>
       <x:c r="B21" s="11"/>
       <x:c r="C21" s="10" t="str">
-        <x:v>看我赶山养家第三季两情相悦</x:v>
+        <x:v>星光落在身边</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>08-16 11:00</x:v>
+        <x:v>09-01 14:30</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>600</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
-        <x:v>种田囤货 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
-        <x:v>知夏短剧</x:v>
+        <x:v>熬夜视界</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str"/>
     </x:row>
@@ -1724,28 +1720,28 @@
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="10" t="str">
-        <x:v>颠婆穿书：我在年代文里当德华</x:v>
+        <x:v>重生70猎户带妻女吃香喝辣</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>09-01 00:06</x:v>
+        <x:v>08-24 17:19</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>武汉卡看漫剧场</x:v>
+        <x:v>_凌凌柒</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str"/>
     </x:row>
@@ -1755,28 +1751,28 @@
       </x:c>
       <x:c r="B23" s="11"/>
       <x:c r="C23" s="10" t="str">
-        <x:v>八零姊妹破局新生</x:v>
+        <x:v>我自杀猪匠登圣</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>08-29 10:00</x:v>
+        <x:v>08-31 21:08</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>162</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>年代怀旧 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>朝夕影堂</x:v>
+        <x:v>布夭莲_</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str"/>
     </x:row>
@@ -1786,28 +1782,28 @@
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="10" t="str">
-        <x:v>比武招亲，我竟成了女王爷的夫婿</x:v>
+        <x:v>兽世第一废柴：靠实力啃三代</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>08-30 07:10</x:v>
+        <x:v>08-28 15:00</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>315</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H24" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
-        <x:v>诺威剧场</x:v>
+        <x:v>小风漫剧</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str"/>
     </x:row>
@@ -1817,28 +1813,28 @@
       </x:c>
       <x:c r="B25" s="11"/>
       <x:c r="C25" s="10" t="str">
-        <x:v>清风不渡旧时寒</x:v>
+        <x:v>细雨如春，替嫁得良缘</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>08-31 09:58</x:v>
+        <x:v>09-02 08:00</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>蜜糖次元社</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str"/>
     </x:row>
@@ -1848,50 +1844,50 @@
       </x:c>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="10" t="str">
-        <x:v>灶边的规矩</x:v>
+        <x:v>深宫重华录</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>08-30 16:31</x:v>
+        <x:v>09-01 17:45</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H26" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
-        <x:v>空白漫</x:v>
+        <x:v>蓝语</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="10" t="str">
-        <x:v>神女归途</x:v>
+        <x:v>我穿越寒门书生一路封神</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>08-29 19:20</x:v>
+        <x:v>08-30 18:20</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>169</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
         <x:v>未标注</x:v>
@@ -1900,162 +1896,162 @@
         <x:v>战神异能</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>河虾动漫</x:v>
+        <x:v>小团子动画</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="10" t="str">
-        <x:v>团宠驾到：督军府的满级小锦鲤</x:v>
+        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>08-26 10:00</x:v>
+        <x:v>09-01 10:54</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>254</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>婚姻情感 / 战神异能</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
-        <x:v>每日沙雕速递</x:v>
+        <x:v>一漳动漫</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="10" t="str">
-        <x:v>我大华第一逍遥王</x:v>
+        <x:v>高考落榜去搬砖，遇良人提点勤学上岸985</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>08-21 19:24</x:v>
+        <x:v>07-14 09:30</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>510</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H29" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
-        <x:v>口水显眼包</x:v>
+        <x:v>龙影剧院</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="10" t="str">
-        <x:v>月子第一天，婆婆离世了</x:v>
+        <x:v>滚烫的铁门</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>08-28 17:55</x:v>
+        <x:v>09-01 11:00</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
-        <x:v>锋芒映剧</x:v>
+        <x:v>锦书AI映画</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="10" t="str">
-        <x:v>择日复婚</x:v>
+        <x:v>龙赐神鉴：渔村少年驭沧海</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>08-29 20:30</x:v>
+        <x:v>08-31 19:00</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>153</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>种田囤货 / 战神异能</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>森森动画</x:v>
+        <x:v>拾光漫漫</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="10" t="str">
-        <x:v>王府小祖宗，捡啥啥是宝</x:v>
+        <x:v>嫡女锦杀第一季</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>08-29 10:00</x:v>
+        <x:v>09-01 16:00</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="11" t="n">
-        <x:v>120</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
-        <x:v>诗婳-君懿看剧</x:v>
+        <x:v>桃桃漫剧</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str"/>
     </x:row>
@@ -2065,19 +2061,19 @@
       </x:c>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="10" t="str">
-        <x:v>铺子空了，房东慌了</x:v>
+        <x:v>方寸宅院见公道</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>08-29 16:49</x:v>
+        <x:v>08-30 10:00</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G33" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
         <x:v>未标注</x:v>
@@ -2086,7 +2082,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
-        <x:v>林帧漫剧</x:v>
+        <x:v>豆豆动漫</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str"/>
     </x:row>
@@ -2096,19 +2092,19 @@
       </x:c>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="10" t="str">
-        <x:v>我在急诊室摸鱼，全院跪求出手！</x:v>
+        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>08-29 18:00</x:v>
+        <x:v>08-31 20:00</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G34" s="11" t="n">
-        <x:v>130</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -2117,7 +2113,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
-        <x:v>追更漫剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str"/>
     </x:row>
@@ -2127,28 +2123,28 @@
       </x:c>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="10" t="str">
-        <x:v>小小力量大，从家属院开始当家</x:v>
+        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>08-29 16:13</x:v>
+        <x:v>07-27 11:00</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G35" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>绿豆儿</x:v>
+        <x:v>暖夏短剧</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str"/>
     </x:row>
@@ -2158,28 +2154,28 @@
       </x:c>
       <x:c r="B36" s="11"/>
       <x:c r="C36" s="10" t="str">
-        <x:v>八零：盒饭女王从小摊开始</x:v>
+        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>08-30 10:00</x:v>
+        <x:v>08-29 16:15</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G36" s="11" t="n">
-        <x:v>133</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>年代怀旧 / 都市职场 / 美食治愈</x:v>
+        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
-        <x:v>东瓜剧场</x:v>
+        <x:v>漫漫画丫头</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str"/>
     </x:row>
@@ -2189,19 +2185,19 @@
       </x:c>
       <x:c r="B37" s="11"/>
       <x:c r="C37" s="10" t="str">
-        <x:v>大婚当天，前任坐在我的婚床</x:v>
+        <x:v>大婚当日立规矩，这婚我不结了</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E37" s="11" t="str">
-        <x:v>08-30 00:45</x:v>
+        <x:v>08-31 17:00</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H37" s="10" t="str">
         <x:v>仿真人</x:v>
@@ -2210,7 +2206,7 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
-        <x:v>星漫世界</x:v>
+        <x:v>云影漫剧</x:v>
       </x:c>
       <x:c r="K37" s="10" t="str"/>
     </x:row>
@@ -2220,28 +2216,28 @@
       </x:c>
       <x:c r="B38" s="11"/>
       <x:c r="C38" s="10" t="str">
-        <x:v>福宝治愈全世界，家有萌娃岁岁安第二季</x:v>
+        <x:v>颠婆穿书：我在年代文里当德华</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
-        <x:v>08-29 20:00</x:v>
+        <x:v>09-01 00:06</x:v>
       </x:c>
       <x:c r="F38" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G38" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H38" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
-        <x:v>萌宝治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J38" s="10" t="str">
-        <x:v>紫怡漫剧场</x:v>
+        <x:v>武汉卡看漫剧场</x:v>
       </x:c>
       <x:c r="K38" s="10" t="str"/>
     </x:row>
@@ -2251,19 +2247,19 @@
       </x:c>
       <x:c r="B39" s="11"/>
       <x:c r="C39" s="10" t="str">
-        <x:v>方寸宅院见公道</x:v>
+        <x:v>闻心：京华稚园录</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>08-30 10:00</x:v>
+        <x:v>08-31 19:00</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G39" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
         <x:v>未标注</x:v>
@@ -2272,7 +2268,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
-        <x:v>豆豆动漫</x:v>
+        <x:v>阿云剧场</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str"/>
     </x:row>
@@ -2282,216 +2278,30 @@
       </x:c>
       <x:c r="B40" s="11"/>
       <x:c r="C40" s="10" t="str">
-        <x:v>重生摊牌身份，众人惊了</x:v>
+        <x:v>烟火与匠心</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>08-29 18:00</x:v>
+        <x:v>08-31 20:07</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="11" t="n">
-        <x:v>139</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
-        <x:v>都市职场 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str">
-        <x:v>小清书漫</x:v>
+        <x:v>馆长玉先生剧场</x:v>
       </x:c>
       <x:c r="K40" s="10" t="str"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B41" s="11"/>
-      <x:c r="C41" s="10" t="str">
-        <x:v>我拿五万去扶贫，男友家却有三片海</x:v>
-      </x:c>
-      <x:c r="D41" s="11" t="str">
-        <x:v>2026-08-31</x:v>
-      </x:c>
-      <x:c r="E41" s="11" t="str">
-        <x:v>08-30 17:30</x:v>
-      </x:c>
-      <x:c r="F41" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G41" s="11" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H41" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I41" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J41" s="10" t="str">
-        <x:v>小菲菲动画</x:v>
-      </x:c>
-      <x:c r="K41" s="10" t="str"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B42" s="11"/>
-      <x:c r="C42" s="10" t="str">
-        <x:v>恩与仇之间的距离</x:v>
-      </x:c>
-      <x:c r="D42" s="11" t="str">
-        <x:v>2026-08-31</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="str">
-        <x:v>08-29 19:57</x:v>
-      </x:c>
-      <x:c r="F42" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G42" s="11" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H42" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I42" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J42" s="10" t="str">
-        <x:v>艾微动画剧场</x:v>
-      </x:c>
-      <x:c r="K42" s="10" t="str"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B43" s="11"/>
-      <x:c r="C43" s="10" t="str">
-        <x:v>前妻逼我献血，我转身离开</x:v>
-      </x:c>
-      <x:c r="D43" s="11" t="str">
-        <x:v>2026-08-31</x:v>
-      </x:c>
-      <x:c r="E43" s="11" t="str">
-        <x:v>08-30 16:50</x:v>
-      </x:c>
-      <x:c r="F43" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G43" s="11" t="n">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H43" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I43" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="J43" s="10" t="str">
-        <x:v>榴莲漫剧</x:v>
-      </x:c>
-      <x:c r="K43" s="10" t="str"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B44" s="11"/>
-      <x:c r="C44" s="10" t="str">
-        <x:v>一顾见晚星</x:v>
-      </x:c>
-      <x:c r="D44" s="11" t="str">
-        <x:v>2026-08-31</x:v>
-      </x:c>
-      <x:c r="E44" s="11" t="str">
-        <x:v>08-30 20:07</x:v>
-      </x:c>
-      <x:c r="F44" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G44" s="11" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H44" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I44" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J44" s="10" t="str">
-        <x:v>三针剧场</x:v>
-      </x:c>
-      <x:c r="K44" s="10" t="str"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B45" s="11"/>
-      <x:c r="C45" s="10" t="str">
-        <x:v>相亲坐错桌，陆总他追着不放</x:v>
-      </x:c>
-      <x:c r="D45" s="11" t="str">
-        <x:v>2026-08-30</x:v>
-      </x:c>
-      <x:c r="E45" s="11" t="str">
-        <x:v>08-26 11:28</x:v>
-      </x:c>
-      <x:c r="F45" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G45" s="11" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H45" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I45" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J45" s="10" t="str">
-        <x:v>喵琪琪追剧</x:v>
-      </x:c>
-      <x:c r="K45" s="10" t="str"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B46" s="11"/>
-      <x:c r="C46" s="10" t="str">
-        <x:v>相亲当天，未婚妻的男助理抢我车位</x:v>
-      </x:c>
-      <x:c r="D46" s="11" t="str">
-        <x:v>2026-08-31</x:v>
-      </x:c>
-      <x:c r="E46" s="11" t="str">
-        <x:v>08-30 12:50</x:v>
-      </x:c>
-      <x:c r="F46" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G46" s="11" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H46" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I46" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="J46" s="10" t="str">
-        <x:v>小丘剧场</x:v>
-      </x:c>
-      <x:c r="K46" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2575,7 +2385,7 @@
         <x:v>7514</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2607,7 +2417,7 @@
         <x:v>852</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2639,7 +2449,7 @@
         <x:v>8368</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2669,7 +2479,7 @@
       </x:c>
       <x:c r="I5" s="11" t="str"/>
       <x:c r="J5" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2699,7 +2509,7 @@
       </x:c>
       <x:c r="I6" s="11" t="str"/>
       <x:c r="J6" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2729,7 +2539,7 @@
       </x:c>
       <x:c r="I7" s="11" t="str"/>
       <x:c r="J7" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜7次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2737,29 +2547,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
+        <x:v>逆流年代：从1970开始种田养家</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>08-12 15:35</x:v>
+        <x:v>08-15 10:00</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str"/>
       <x:c r="J8" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计7次，起量能力已被验证；仿真人制作；110集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2789,7 +2599,7 @@
       </x:c>
       <x:c r="I9" s="11" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜6次、累计15次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计15次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2821,7 +2631,7 @@
         <x:v>4442</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜6次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2829,29 +2639,29 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>姜猎娶妻之知青良缘</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>08-10 09:00</x:v>
+        <x:v>08-17 09:38</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>136</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str"/>
       <x:c r="J11" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜6次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计10次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2881,7 +2691,7 @@
       </x:c>
       <x:c r="I12" s="11" t="str"/>
       <x:c r="J12" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2889,29 +2699,29 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>分家只给破枪，我听兽语富全屯</x:v>
+        <x:v>暴雪见人心</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>08-13 09:02</x:v>
+        <x:v>08-16 08:21</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="G13" s="10" t="n">
-        <x:v>79</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2919,29 +2729,29 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>这门婚我不嫁了</x:v>
+        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>08-15 09:00</x:v>
+        <x:v>08-11 10:41</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G14" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str"/>
       <x:c r="J14" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2949,29 +2759,29 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>逆流年代：从1970开始种田养家</x:v>
+        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>08-15 10:00</x:v>
+        <x:v>08-12 15:35</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="G15" s="10" t="n">
-        <x:v>110</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；110集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2979,29 +2789,29 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>这门婚我不嫁了</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>08-10 21:16</x:v>
+        <x:v>08-15 09:00</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="G16" s="10" t="n">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3009,29 +2819,29 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-17 09:38</x:v>
+        <x:v>08-10 09:00</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="G17" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I17" s="11" t="str"/>
       <x:c r="J17" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计10次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3039,29 +2849,29 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>悍妻替嫁，从前说</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-06 11:00</x:v>
+        <x:v>08-10 21:16</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G18" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3069,29 +2879,29 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>暴雪见人心</x:v>
+        <x:v>分家只给破枪，我听兽语富全屯</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>08-16 08:21</x:v>
+        <x:v>08-13 09:02</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="G19" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I19" s="11" t="str"/>
       <x:c r="J19" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3099,10 +2909,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
+        <x:v>重生凛冬跟随囤货</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>08-11 10:41</x:v>
+        <x:v>08-16 13:16</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
         <x:v>5</x:v>
@@ -3111,17 +2921,17 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="G20" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I20" s="11" t="str"/>
       <x:c r="J20" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；81集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3129,29 +2939,29 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>八零之老妈在厂长家当后妈</x:v>
+        <x:v>医风秩序线</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>08-14 09:08</x:v>
+        <x:v>08-17 11:00</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
         <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="G21" s="10" t="n">
-        <x:v>156</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；89集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3159,29 +2969,29 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>激活美食治愈系统,我靠摆摊火遍了整座城市</x:v>
+        <x:v>一墙之隔的求救声</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>08-14 17:00</x:v>
+        <x:v>08-15 09:18</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G22" s="10" t="n">
-        <x:v>177</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I22" s="11" t="str"/>
       <x:c r="J22" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计6次，起量能力已被验证；经典3D制作；177集长剧集；题材契合爆款主线（都市职场 / 美食治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；88集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3189,29 +2999,29 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>离婚那天我多了个董事长妈妈</x:v>
+        <x:v>五福临门，八方报喜</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>07-24 00:06</x:v>
+        <x:v>08-17 10:18</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G23" s="10" t="n">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3219,10 +3029,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
+        <x:v>芯骨藏锋</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-15 12:00</x:v>
+        <x:v>08-15 05:58</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>5</x:v>
@@ -3231,17 +3041,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="G24" s="10" t="n">
-        <x:v>95</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；仿真人制作；52集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3249,29 +3059,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>芯骨藏锋</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-15 05:58</x:v>
+        <x:v>08-11 00:26</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="G25" s="10" t="n">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜5次、累计5次，起量能力已被验证；仿真人制作；52集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3279,29 +3089,29 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-11 00:26</x:v>
+        <x:v>07-20 14:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="G26" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计11次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3309,31 +3119,29 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>悍妻替嫁，从前说</x:v>
       </x:c>
       <x:c r="C27" s="11" t="str">
-        <x:v>07-13 14:00</x:v>
+        <x:v>08-06 11:00</x:v>
       </x:c>
       <x:c r="D27" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="G27" s="10" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="H27" s="11" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I27" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="str"/>
       <x:c r="J27" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3341,29 +3149,29 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>八零之老妈在厂长家当后妈</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>07-20 14:00</x:v>
+        <x:v>08-14 09:08</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="G28" s="10" t="n">
-        <x:v>196</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I28" s="11" t="str"/>
       <x:c r="J28" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计11次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3371,29 +3179,29 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>这个姨娘不一般</x:v>
+        <x:v>东北阿姨：捡了个南方小土豆</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>07-12 11:00</x:v>
+        <x:v>08-19 07:40</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G29" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I29" s="11" t="str"/>
       <x:c r="J29" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；68集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3401,29 +3209,29 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>重生凛冬跟随囤货</x:v>
+        <x:v>冷宫开席：陛下又来蹭饭了</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>08-16 13:16</x:v>
+        <x:v>08-02 14:08</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G30" s="10" t="n">
-        <x:v>81</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I30" s="11" t="str"/>
       <x:c r="J30" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计8次，起量能力已被验证；81集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；122集长剧集；题材契合爆款主线（古装宫廷 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3431,29 +3239,29 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>九二年，他塞给我五百块</x:v>
+        <x:v>各生归途</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>08-09 13:57</x:v>
+        <x:v>08-17 17:50</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G31" s="10" t="n">
-        <x:v>64</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I31" s="11" t="str"/>
       <x:c r="J31" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；82集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3461,10 +3269,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>傻女重生记，睁眼后盖房发家</x:v>
+        <x:v>同事蹭了我三个月顺风车，把我当免费司机</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>07-10 17:00</x:v>
+        <x:v>08-19 06:00</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
         <x:v>4</x:v>
@@ -3473,17 +3281,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G32" s="10" t="n">
-        <x:v>102</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I32" s="11" t="str"/>
       <x:c r="J32" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3491,10 +3299,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>医风秩序线</x:v>
+        <x:v>激活美食治愈系统,我靠摆摊火遍了整座城市</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>08-17 11:00</x:v>
+        <x:v>08-14 17:00</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
         <x:v>4</x:v>
@@ -3503,17 +3311,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="G33" s="10" t="n">
-        <x:v>89</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I33" s="11" t="str"/>
       <x:c r="J33" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；89集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；177集长剧集；题材契合爆款主线（都市职场 / 美食治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3521,10 +3329,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>各生归途</x:v>
+        <x:v>离婚那天我多了个董事长妈妈</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>08-17 17:50</x:v>
+        <x:v>07-24 00:06</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
         <x:v>4</x:v>
@@ -3533,17 +3341,17 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="G34" s="10" t="n">
-        <x:v>82</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I34" s="11" t="str"/>
       <x:c r="J34" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；82集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3551,29 +3359,29 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
+        <x:v>寒途微光</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>08-13 06:00</x:v>
+        <x:v>07-25 10:00</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G35" s="10" t="n">
-        <x:v>119</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I35" s="11" t="str"/>
       <x:c r="J35" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3581,10 +3389,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>一墙之隔的求救声</x:v>
+        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>08-15 09:18</x:v>
+        <x:v>08-15 12:00</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
         <x:v>4</x:v>
@@ -3593,17 +3401,17 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="G36" s="10" t="n">
-        <x:v>88</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I36" s="11" t="str"/>
       <x:c r="J36" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；88集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3611,29 +3419,29 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>五福临门，八方报喜</x:v>
+        <x:v>一辆旧中巴奔向新生活</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>08-17 10:18</x:v>
+        <x:v>08-14 15:00</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="G37" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I37" s="11" t="str"/>
       <x:c r="J37" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；82集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3641,29 +3449,29 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>大唐：我真没想当国舅爷啊</x:v>
+        <x:v>不朽仙秦！</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>08-14 16:04</x:v>
+        <x:v>08-18 18:06</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G38" s="10" t="n">
-        <x:v>71</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I38" s="11" t="str"/>
       <x:c r="J38" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；71集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；200集长剧集；题材契合爆款主线（古装宫廷 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3671,29 +3479,29 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>捡到小蛇，我养出龙崽</x:v>
+        <x:v>烈焰护送：无人区突围</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>08-08 10:08</x:v>
+        <x:v>07-17 09:58</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G39" s="10" t="n">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I39" s="11" t="str"/>
       <x:c r="J39" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计5次，起量能力已被验证；61集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3701,10 +3509,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>一辆旧中巴奔向新生活</x:v>
+        <x:v>被休流放，我靠赶海养出战神</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>08-14 15:00</x:v>
+        <x:v>08-11 10:00</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
         <x:v>4</x:v>
@@ -3713,17 +3521,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G40" s="10" t="n">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="I40" s="11" t="str"/>
+      <x:c r="I40" s="11" t="n">
+        <x:v>57</x:v>
+      </x:c>
       <x:c r="J40" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计4次，起量能力已被验证；82集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；62集长剧集；题材契合爆款主线（种田囤货 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3731,10 +3541,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>老婆每月给别人一万五，离婚时她后悔了</x:v>
+        <x:v>锦鲤知恨</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>08-14 10:00</x:v>
+        <x:v>08-04 11:00</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
         <x:v>4</x:v>
@@ -3743,17 +3553,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>2026-08-18</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G41" s="10" t="n">
-        <x:v>113</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I41" s="11" t="str"/>
       <x:c r="J41" s="10" t="str">
-        <x:v>8-15~8-21两周期内上榜4次、累计4次，起量能力已被验证；仿真人制作；113集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10841,10 +10651,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>377</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>43.4%</x:v>
+        <x:v>43.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10852,10 +10662,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>264</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>30.4%</x:v>
+        <x:v>30.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -10863,10 +10673,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>228</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>26.2%</x:v>
+        <x:v>26.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -10890,10 +10700,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>12.4%</x:v>
+        <x:v>12.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -10901,10 +10711,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>376</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>43.4%</x:v>
+        <x:v>43.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -10912,10 +10722,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>11.3%</x:v>
+        <x:v>11%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -10923,10 +10733,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>284</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>32.8%</x:v>
+        <x:v>33.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -10950,10 +10760,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>344</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>39.6%</x:v>
+        <x:v>39.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -10961,10 +10771,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>163</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>18.8%</x:v>
+        <x:v>18.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -10972,10 +10782,10 @@
         <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>10.9%</x:v>
+        <x:v>10.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -10983,7 +10793,7 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
         <x:v>10.1%</x:v>
@@ -10991,24 +10801,24 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
-        <x:v>战神/异能/爽文</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.6%</x:v>
+        <x:v>8.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -11019,7 +10829,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>6.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -11027,10 +10837,10 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>6.3%</x:v>
+        <x:v>6.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -11041,7 +10851,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>5.3%</x:v>
+        <x:v>5.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -11049,10 +10859,10 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>5.1%</x:v>
+        <x:v>5.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -11073,7 +10883,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>上榜20次</x:v>
+        <x:v>上榜21次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
         <x:v>1</x:v>
@@ -11084,29 +10894,29 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="10" t="str">
-        <x:v>上榜19次</x:v>
+        <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="10" t="str">
-        <x:v>上榜18次</x:v>
+        <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10" t="str">
-        <x:v>上榜16次</x:v>
+        <x:v>上榜17次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
         <x:v>1</x:v>
@@ -11120,10 +10930,10 @@
         <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -11131,10 +10941,10 @@
         <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -11142,10 +10952,10 @@
         <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -11164,10 +10974,10 @@
         <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -11175,10 +10985,10 @@
         <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>1.0%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -11186,10 +10996,10 @@
         <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>1.3%</x:v>
+        <x:v>1.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -11197,10 +11007,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>2.2%</x:v>
+        <x:v>1.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -11208,10 +11018,10 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>1.8%</x:v>
+        <x:v>2.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -11219,10 +11029,10 @@
         <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>4.1%</x:v>
+        <x:v>4.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -11230,10 +11040,10 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>4.6%</x:v>
+        <x:v>4.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -11241,10 +11051,10 @@
         <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>5.4%</x:v>
+        <x:v>5.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -11252,10 +11062,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>9.2%</x:v>
+        <x:v>8.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -11263,10 +11073,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>17.6%</x:v>
+        <x:v>17.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -11274,10 +11084,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>432</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>49.7%</x:v>
+        <x:v>50.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="22" customHeight="1">
@@ -11301,15 +11111,15 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B51" s="11" t="n">
-        <x:v>859</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="C51" s="11" t="str">
-        <x:v>98.8%</x:v>
+        <x:v>98.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
         <x:v>5</x:v>
@@ -11320,13 +11130,13 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP托管</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -11361,7 +11171,7 @@
         <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B58" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C58" s="11" t="str">
         <x:v>1.5%</x:v>
@@ -11372,10 +11182,10 @@
         <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C59" s="11" t="str">
-        <x:v>1.3%</x:v>
+        <x:v>1.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -11383,7 +11193,7 @@
         <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
         <x:v>1%</x:v>
@@ -11402,21 +11212,21 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C63" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11424,10 +11234,10 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C64" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11435,7 +11245,7 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>咕咚剧场</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
         <x:v>20</x:v>
@@ -11446,10 +11256,10 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
-        <x:v>咕咚剧场</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C66" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11457,10 +11267,10 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>一样漫剧</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11468,7 +11278,7 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>一样漫剧</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
         <x:v>19</x:v>
@@ -11496,15 +11306,15 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="10" t="str">
-        <x:v>星漫剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -11512,10 +11322,10 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="str">
-        <x:v>周八宝</x:v>
+        <x:v>星漫剧场</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
         <x:v>0.6%</x:v>
@@ -11545,7 +11355,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C76" s="11" t="str">
-        <x:v>1.5%</x:v>
+        <x:v>1.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -11589,117 +11399,117 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C81" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B82" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C82" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="10" t="str">
-        <x:v>不兜</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B83" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C83" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="10" t="str">
-        <x:v>喵喵说书</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="B84" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C84" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>不兜</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C85" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10" t="str">
-        <x:v>取瘾书屋</x:v>
+        <x:v>喵喵说书</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C86" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10" t="str">
-        <x:v>清风短剧场</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C87" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>亦辰动漫</x:v>
+        <x:v>取瘾书屋</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C88" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>暖星追剧</x:v>
+        <x:v>清风短剧场</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C89" s="11" t="str">
-        <x:v>0.5%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>亦辰动漫</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C90" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="22" customHeight="1">

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R62e3ed9389494ea8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R9e0638377cc442ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rb9b98004174d4b91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Rec6ad0c69bb94725"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R562f24cff3c04a5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R4d55c6e57df44e8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R7e3580a2c9fc46bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R90dd60951966478a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R1023ccf0ca2e4841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Reedcbc1e68c24455"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R999882196cd7459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R9939112cc6564c5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3592,7 +3592,7 @@
         <x:v>排名</x:v>
       </x:c>
       <x:c r="B1" t="str">
-        <x:v>预计上线</x:v>
+        <x:v>预计发布时间</x:v>
       </x:c>
       <x:c r="C1" t="str">
         <x:v>剧名</x:v>
@@ -3624,7 +3624,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>假面恋人：三十八万撕开两年恋爱骗局</x:v>
@@ -3654,7 +3654,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
         <x:v>婚内骗局，我彻底粉碎前夫阴谋</x:v>
@@ -3684,7 +3684,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
         <x:v>闺蜜的谎言</x:v>
@@ -3714,7 +3714,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
         <x:v>一场蜜月，撕毁了我的婚姻</x:v>
@@ -3744,7 +3744,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
         <x:v>一庭兰香旧人归</x:v>
@@ -3774,7 +3774,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>姐姐不是提款机</x:v>
@@ -3804,7 +3804,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
         <x:v>婚礼当天，我拆穿了小姑子的假陪嫁房</x:v>
@@ -3834,7 +3834,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
         <x:v>归来吧，妈妈</x:v>
@@ -3864,7 +3864,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
         <x:v>情深不知晚</x:v>
@@ -3894,7 +3894,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
         <x:v>我养了三年的保姆，想夺走我的一切</x:v>
@@ -3924,7 +3924,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>我用一场退婚，换回了整个人生</x:v>
@@ -3954,7 +3954,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>我的座位，恕不奉陪</x:v>
@@ -3984,7 +3984,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
         <x:v>逆袭之通天财眼第7季</x:v>
@@ -4014,7 +4014,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>重生为蛇，投喂女帝反哺成龙第二季</x:v>
@@ -4044,7 +4044,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
         <x:v>重生猎户：杜鹃赶山屯满粮第二季</x:v>
@@ -4074,7 +4074,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>食香记：从一坛腌萝卜开始逆袭第一季完整版</x:v>
@@ -4104,7 +4104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
         <x:v>不死帝师上界篇第一季</x:v>
@@ -4134,7 +4134,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>五千块起家！卡车司机的逆袭人生</x:v>
@@ -4164,7 +4164,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
         <x:v>从前说：七零佳媳渡风尘第一季</x:v>
@@ -4194,7 +4194,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
         <x:v>从捡个仙子做老婆开始，凡血踏九天第二季</x:v>
@@ -4224,7 +4224,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
         <x:v>仙姝重回：我和魔尊带着宗门上大分第三季</x:v>
@@ -4254,7 +4254,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
         <x:v>公路求生卡进了古代，柳姨娘癫狂极了第三季</x:v>
@@ -4284,7 +4284,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
         <x:v>凤栖为臣，女扮男装搞基建第一季</x:v>
@@ -4314,7 +4314,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
         <x:v>刘一祖的故事之逆袭</x:v>
@@ -4344,7 +4344,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
         <x:v>刚毕业，离婚逆袭系统就来了</x:v>
@@ -4374,7 +4374,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
         <x:v>合伙人老婆夺我权我反手收购公司</x:v>
@@ -4404,7 +4404,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
         <x:v>商先生，婚后请热恋第三季</x:v>
@@ -4434,7 +4434,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
         <x:v>姑妈供我成状元，我用一生报她恩第一季</x:v>
@@ -4464,7 +4464,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
         <x:v>宠物急诊：自带病症词条天眼第一季</x:v>
@@ -4494,7 +4494,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
         <x:v>导航里的秘密！</x:v>
@@ -4524,7 +4524,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
         <x:v>彩运照人心第三季</x:v>
@@ -4554,7 +4554,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
         <x:v>穿成团宠后我靠读心逆袭</x:v>
@@ -4584,7 +4584,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
         <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
@@ -4614,7 +4614,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
         <x:v>藏在婚姻里的谎言</x:v>
@@ -4644,7 +4644,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
         <x:v>让你守边塞，你用汉堡养兵？第二季江南篇</x:v>
@@ -4674,7 +4674,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B37" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
         <x:v>撞破婚约骗局</x:v>
@@ -4704,7 +4704,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B38" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
         <x:v>下山归来，影后向我求婚第二季</x:v>
@@ -4734,7 +4734,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B39" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
         <x:v>免费荠菜见人心</x:v>
@@ -4764,7 +4764,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B40" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
         <x:v>毁我清白，我反手指认皇帝</x:v>
@@ -4794,7 +4794,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B41" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
         <x:v>丁克二十载，我摊牌了</x:v>
@@ -4824,7 +4824,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B42" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C42" s="10" t="str">
         <x:v>万界杂货铺：我靠倒卖物资赢麻了</x:v>
@@ -4854,7 +4854,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C43" s="10" t="str">
         <x:v>双生麒麟，神君爹爹傲娇娘</x:v>
@@ -4884,7 +4884,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C44" s="10" t="str">
         <x:v>捐躯失踪十八年，归来女儿去世了</x:v>
@@ -4914,7 +4914,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B45" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C45" s="10" t="str">
         <x:v>觉醒神级听劝系统，我成专听建议的校长</x:v>
@@ -4944,7 +4944,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C46" s="10" t="str">
         <x:v>退婚后我成了女帝</x:v>
@@ -4974,7 +4974,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B47" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C47" s="10" t="str">
         <x:v>1980：我重生后护她余生</x:v>
@@ -5004,7 +5004,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B48" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C48" s="10" t="str">
         <x:v>一担米嫁哑郎，他开口那天我哭了</x:v>
@@ -5034,7 +5034,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B49" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C49" s="10" t="str">
         <x:v>乖囡寻爹记</x:v>
@@ -5064,7 +5064,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B50" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C50" s="10" t="str">
         <x:v>山谷灵珠录第三季</x:v>
@@ -5094,7 +5094,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B51" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C51" s="10" t="str">
         <x:v>大促当天，我预言了一场爆炸</x:v>
@@ -5124,7 +5124,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C52" s="10" t="str">
         <x:v>盐弈</x:v>
@@ -5154,7 +5154,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B53" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C53" s="10" t="str">
         <x:v>九世相寻</x:v>
@@ -5184,7 +5184,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B54" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:50</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
         <x:v>后娘逆袭</x:v>
@@ -5216,7 +5216,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B55" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 19:40</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
         <x:v>重生八零：直上青天展宏图</x:v>
@@ -5248,7 +5248,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
         <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
@@ -5280,7 +5280,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B57" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
         <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
@@ -5310,7 +5310,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 21:00</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
         <x:v>穿越古代，我靠军火建立王朝</x:v>
@@ -5342,7 +5342,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B59" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
         <x:v>穿越王妃美又飒</x:v>
@@ -5374,7 +5374,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 18:00</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
         <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
@@ -5406,7 +5406,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B61" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
         <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
@@ -5438,7 +5438,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B62" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:01</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
         <x:v>借势逢生</x:v>
@@ -5470,7 +5470,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B63" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 09:00</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
         <x:v>反派老爹不好惹</x:v>
@@ -5500,7 +5500,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B64" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 18:44</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
         <x:v>女粉丝的救赎</x:v>
@@ -5532,7 +5532,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B65" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:00</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
         <x:v>彪悍后妈在八零</x:v>
@@ -5564,7 +5564,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 14:00</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
         <x:v>无心攀比，假千金重生后成团宠了</x:v>
@@ -5596,7 +5596,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 18:33</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
         <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
@@ -5628,7 +5628,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:00</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
         <x:v>转生成鼠，气哭冷艳校花</x:v>
@@ -5660,7 +5660,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B69" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:22</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
         <x:v>魂穿百岁老太，零零后整顿全村</x:v>
@@ -5692,7 +5692,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B70" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 17:53</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
         <x:v>1970重生岁岁，不负韶华</x:v>
@@ -5724,7 +5724,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 00:07</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
         <x:v>剑心被夺后，我神魔同体！</x:v>
@@ -5754,7 +5754,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B72" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 19:59</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
         <x:v>哥哥争宠我富家天下兄妹绑错系统爆红了</x:v>
@@ -5786,7 +5786,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B73" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:30</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
         <x:v>祖传铜勺，我靠火锅干翻联盟</x:v>
@@ -5818,7 +5818,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B74" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 00:19</x:v>
       </x:c>
       <x:c r="C74" s="10" t="str">
         <x:v>原来她从未输过</x:v>
@@ -5850,7 +5850,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B75" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 18:10</x:v>
       </x:c>
       <x:c r="C75" s="10" t="str">
         <x:v>重生七零辣媳不好惹</x:v>
@@ -5882,7 +5882,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B76" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 19:30</x:v>
       </x:c>
       <x:c r="C76" s="10" t="str">
         <x:v>初初处处藏不住</x:v>
@@ -5914,7 +5914,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B77" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 00:06</x:v>
       </x:c>
       <x:c r="C77" s="10" t="str">
         <x:v>号外号外，团宠小师妹她又开挂了</x:v>
@@ -5946,7 +5946,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B78" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:30</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
         <x:v>开局成废后我反手养出十万御林军</x:v>
@@ -5978,7 +5978,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B79" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:00</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
         <x:v>穿回八零我凭厨艺旺翻全家</x:v>
@@ -6010,7 +6010,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B80" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 11:00</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
         <x:v>重生六零之护妻猎王</x:v>
@@ -6042,7 +6042,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B81" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:00</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
         <x:v>重生后我靠鉴宝慧眼翻身</x:v>
@@ -6074,7 +6074,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B82" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 14:57</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
         <x:v>长姐归来，以爱托举全家！</x:v>
@@ -6106,7 +6106,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B83" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:37</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
         <x:v>为了活命我拼命整活</x:v>
@@ -6138,7 +6138,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 16:00</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
         <x:v>婴语大师</x:v>
@@ -6170,7 +6170,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B85" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 20:30</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
         <x:v>小五替我择良缘</x:v>
@@ -6202,7 +6202,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B86" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:30</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
         <x:v>穿越乱世：每天一份拼好饭</x:v>
@@ -6234,7 +6234,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B87" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 11:16</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
         <x:v>萌小宝寻爹记</x:v>
@@ -6266,7 +6266,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B88" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 17:00</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
         <x:v>转夫运</x:v>
@@ -6298,7 +6298,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B89" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 16:00</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
         <x:v>这一世，换我走向你</x:v>
@@ -6330,7 +6330,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 09:00</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
         <x:v>魂归处：不待帝王悔</x:v>
@@ -6362,7 +6362,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 10:05</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
         <x:v>太学废柴班拯救计划</x:v>
@@ -6394,7 +6394,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 17:00</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
         <x:v>携手千里渡荒年</x:v>
@@ -6426,7 +6426,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B93" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 09:47</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
         <x:v>虾仁穿成驸马爷，公主谁爱娶谁娶！</x:v>
@@ -6458,7 +6458,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B94" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:30</x:v>
       </x:c>
       <x:c r="C94" s="10" t="str">
         <x:v>不寄人间半尺光</x:v>
@@ -6490,7 +6490,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B95" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C95" s="10" t="str">
         <x:v>回乡种田，手握灵泉养全家</x:v>
@@ -6522,7 +6522,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B96" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
         <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
@@ -6554,7 +6554,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
         <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
@@ -6586,7 +6586,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
         <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
@@ -6618,7 +6618,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
         <x:v>三年，我不装了</x:v>
@@ -6650,7 +6650,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:08</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
         <x:v>沙县厨神</x:v>
@@ -6682,7 +6682,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B101" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:07</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
         <x:v>九零绝境潮汐系统护我</x:v>
@@ -6714,7 +6714,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B102" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
         <x:v>予你情深，岁岁相守</x:v>
@@ -6746,7 +6746,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B103" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:06</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
         <x:v>仙界老祖非要当我哥</x:v>
@@ -6778,7 +6778,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B104" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:45</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
         <x:v>农家穗安：饼香满镇</x:v>
@@ -6810,7 +6810,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B105" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
         <x:v>嫡女归来，厨香撼京华</x:v>
@@ -6842,7 +6842,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B106" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:58</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
         <x:v>山野新婚暖光阴</x:v>
@@ -6874,7 +6874,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
         <x:v>我的小土狗竟有大帝之姿</x:v>
@@ -6906,7 +6906,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
         <x:v>替嫁棺妃</x:v>
@@ -6938,7 +6938,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
         <x:v>末世的最后一餐</x:v>
@@ -6970,7 +6970,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
         <x:v>穿成纨绔，我靠诗词当文圣</x:v>
@@ -7000,7 +7000,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B111" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:06</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
         <x:v>被赶走的保姆，竟是真夫人</x:v>
@@ -7032,7 +7032,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
         <x:v>新婚的羔羊</x:v>
@@ -7064,7 +7064,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B113" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
         <x:v>人到中年我逆袭成百草圣手</x:v>
@@ -7117,7 +7117,7 @@
         <x:v>排名</x:v>
       </x:c>
       <x:c r="B1" t="str">
-        <x:v>预计上线</x:v>
+        <x:v>预计发布时间</x:v>
       </x:c>
       <x:c r="C1" t="str">
         <x:v>剧名</x:v>
@@ -7149,7 +7149,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>假面恋人：三十八万撕开两年恋爱骗局</x:v>
@@ -7179,7 +7179,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
         <x:v>婚内骗局，我彻底粉碎前夫阴谋</x:v>
@@ -7209,7 +7209,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
         <x:v>闺蜜的谎言</x:v>
@@ -7239,7 +7239,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
         <x:v>一场蜜月，撕毁了我的婚姻</x:v>
@@ -7269,7 +7269,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
         <x:v>一庭兰香旧人归</x:v>
@@ -7299,7 +7299,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>姐姐不是提款机</x:v>
@@ -7329,7 +7329,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
         <x:v>婚礼当天，我拆穿了小姑子的假陪嫁房</x:v>
@@ -7359,7 +7359,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
         <x:v>归来吧，妈妈</x:v>
@@ -7389,7 +7389,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
         <x:v>情深不知晚</x:v>
@@ -7419,7 +7419,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
         <x:v>我养了三年的保姆，想夺走我的一切</x:v>
@@ -7449,7 +7449,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
         <x:v>我用一场退婚，换回了整个人生</x:v>
@@ -7479,7 +7479,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
         <x:v>我的座位，恕不奉陪</x:v>
@@ -7509,7 +7509,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
         <x:v>逆袭之通天财眼第7季</x:v>
@@ -7539,7 +7539,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
         <x:v>重生为蛇，投喂女帝反哺成龙第二季</x:v>
@@ -7569,7 +7569,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
         <x:v>重生猎户：杜鹃赶山屯满粮第二季</x:v>
@@ -7599,7 +7599,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>食香记：从一坛腌萝卜开始逆袭第一季完整版</x:v>
@@ -7629,7 +7629,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
         <x:v>不死帝师上界篇第一季</x:v>
@@ -7659,7 +7659,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>五千块起家！卡车司机的逆袭人生</x:v>
@@ -7689,7 +7689,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
         <x:v>从前说：七零佳媳渡风尘第一季</x:v>
@@ -7719,7 +7719,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
         <x:v>从捡个仙子做老婆开始，凡血踏九天第二季</x:v>
@@ -7749,7 +7749,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
         <x:v>仙姝重回：我和魔尊带着宗门上大分第三季</x:v>
@@ -7779,7 +7779,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
         <x:v>公路求生卡进了古代，柳姨娘癫狂极了第三季</x:v>
@@ -7809,7 +7809,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C24" s="10" t="str">
         <x:v>凤栖为臣，女扮男装搞基建第一季</x:v>
@@ -7839,7 +7839,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
         <x:v>刘一祖的故事之逆袭</x:v>
@@ -7869,7 +7869,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
         <x:v>刚毕业，离婚逆袭系统就来了</x:v>
@@ -7899,7 +7899,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
         <x:v>合伙人老婆夺我权我反手收购公司</x:v>
@@ -7929,7 +7929,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
         <x:v>商先生，婚后请热恋第三季</x:v>
@@ -7959,7 +7959,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
         <x:v>姑妈供我成状元，我用一生报她恩第一季</x:v>
@@ -7989,7 +7989,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
         <x:v>宠物急诊：自带病症词条天眼第一季</x:v>
@@ -8019,7 +8019,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
         <x:v>导航里的秘密！</x:v>
@@ -8049,7 +8049,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
         <x:v>彩运照人心第三季</x:v>
@@ -8079,7 +8079,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
         <x:v>穿成团宠后我靠读心逆袭</x:v>
@@ -8109,7 +8109,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
         <x:v>聚宝仙盆之杂灵根才是真BOSS第十季</x:v>
@@ -8139,7 +8139,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
         <x:v>藏在婚姻里的谎言</x:v>
@@ -8169,7 +8169,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="11" t="str">
-        <x:v>08·29</x:v>
+        <x:v>08-29</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
         <x:v>让你守边塞，你用汉堡养兵？第二季江南篇</x:v>
@@ -8199,7 +8199,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B37" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
         <x:v>撞破婚约骗局</x:v>
@@ -8229,7 +8229,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B38" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
         <x:v>下山归来，影后向我求婚第二季</x:v>
@@ -8259,7 +8259,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B39" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
         <x:v>免费荠菜见人心</x:v>
@@ -8289,7 +8289,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B40" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
         <x:v>毁我清白，我反手指认皇帝</x:v>
@@ -8319,7 +8319,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B41" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
         <x:v>丁克二十载，我摊牌了</x:v>
@@ -8349,7 +8349,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B42" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C42" s="10" t="str">
         <x:v>万界杂货铺：我靠倒卖物资赢麻了</x:v>
@@ -8379,7 +8379,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C43" s="10" t="str">
         <x:v>双生麒麟，神君爹爹傲娇娘</x:v>
@@ -8409,7 +8409,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C44" s="10" t="str">
         <x:v>捐躯失踪十八年，归来女儿去世了</x:v>
@@ -8439,7 +8439,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B45" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C45" s="10" t="str">
         <x:v>觉醒神级听劝系统，我成专听建议的校长</x:v>
@@ -8469,7 +8469,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C46" s="10" t="str">
         <x:v>退婚后我成了女帝</x:v>
@@ -8499,7 +8499,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B47" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C47" s="10" t="str">
         <x:v>1980：我重生后护她余生</x:v>
@@ -8529,7 +8529,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B48" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C48" s="10" t="str">
         <x:v>一担米嫁哑郎，他开口那天我哭了</x:v>
@@ -8559,7 +8559,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B49" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C49" s="10" t="str">
         <x:v>乖囡寻爹记</x:v>
@@ -8589,7 +8589,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B50" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C50" s="10" t="str">
         <x:v>山谷灵珠录第三季</x:v>
@@ -8619,7 +8619,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B51" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C51" s="10" t="str">
         <x:v>大促当天，我预言了一场爆炸</x:v>
@@ -8649,7 +8649,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C52" s="10" t="str">
         <x:v>盐弈</x:v>
@@ -8679,7 +8679,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B53" s="11" t="str">
-        <x:v>08·30</x:v>
+        <x:v>08-30</x:v>
       </x:c>
       <x:c r="C53" s="10" t="str">
         <x:v>九世相寻</x:v>
@@ -8709,7 +8709,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B54" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:50</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
         <x:v>后娘逆袭</x:v>
@@ -8741,7 +8741,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B55" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 19:40</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
         <x:v>重生八零：直上青天展宏图</x:v>
@@ -8773,7 +8773,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
         <x:v>小手一背穿八零，搞事赚钱样样行</x:v>
@@ -8805,7 +8805,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B57" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
         <x:v>氪命镇魔：我靠寿元杀穿妖魔乱世</x:v>
@@ -8835,7 +8835,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B58" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 21:00</x:v>
       </x:c>
       <x:c r="C58" s="10" t="str">
         <x:v>穿越古代，我靠军火建立王朝</x:v>
@@ -8867,7 +8867,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B59" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C59" s="10" t="str">
         <x:v>穿越王妃美又飒</x:v>
@@ -8899,7 +8899,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 18:00</x:v>
       </x:c>
       <x:c r="C60" s="10" t="str">
         <x:v>落难公主，从孤儿院到万国之巅战神凌昭</x:v>
@@ -8931,7 +8931,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B61" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 10:00</x:v>
       </x:c>
       <x:c r="C61" s="10" t="str">
         <x:v>闺蜜骗我极寒末日，可我反手囤了制冷机</x:v>
@@ -8963,7 +8963,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B62" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:01</x:v>
       </x:c>
       <x:c r="C62" s="10" t="str">
         <x:v>借势逢生</x:v>
@@ -8995,7 +8995,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B63" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 09:00</x:v>
       </x:c>
       <x:c r="C63" s="10" t="str">
         <x:v>反派老爹不好惹</x:v>
@@ -9025,7 +9025,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B64" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 18:44</x:v>
       </x:c>
       <x:c r="C64" s="10" t="str">
         <x:v>女粉丝的救赎</x:v>
@@ -9057,7 +9057,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B65" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:00</x:v>
       </x:c>
       <x:c r="C65" s="10" t="str">
         <x:v>彪悍后妈在八零</x:v>
@@ -9089,7 +9089,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 14:00</x:v>
       </x:c>
       <x:c r="C66" s="10" t="str">
         <x:v>无心攀比，假千金重生后成团宠了</x:v>
@@ -9121,7 +9121,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 18:33</x:v>
       </x:c>
       <x:c r="C67" s="10" t="str">
         <x:v>穿越后古代贵公子因美食为我倾倒</x:v>
@@ -9153,7 +9153,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:00</x:v>
       </x:c>
       <x:c r="C68" s="10" t="str">
         <x:v>转生成鼠，气哭冷艳校花</x:v>
@@ -9185,7 +9185,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B69" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:22</x:v>
       </x:c>
       <x:c r="C69" s="10" t="str">
         <x:v>魂穿百岁老太，零零后整顿全村</x:v>
@@ -9217,7 +9217,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B70" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 17:53</x:v>
       </x:c>
       <x:c r="C70" s="10" t="str">
         <x:v>1970重生岁岁，不负韶华</x:v>
@@ -9249,7 +9249,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B71" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 00:07</x:v>
       </x:c>
       <x:c r="C71" s="10" t="str">
         <x:v>剑心被夺后，我神魔同体！</x:v>
@@ -9279,7 +9279,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B72" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 19:59</x:v>
       </x:c>
       <x:c r="C72" s="10" t="str">
         <x:v>哥哥争宠我富家天下兄妹绑错系统爆红了</x:v>
@@ -9311,7 +9311,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B73" s="11" t="str">
-        <x:v>09·03</x:v>
+        <x:v>09-03 16:30</x:v>
       </x:c>
       <x:c r="C73" s="10" t="str">
         <x:v>祖传铜勺，我靠火锅干翻联盟</x:v>
@@ -9343,7 +9343,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B74" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 00:19</x:v>
       </x:c>
       <x:c r="C74" s="10" t="str">
         <x:v>原来她从未输过</x:v>
@@ -9375,7 +9375,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B75" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 18:10</x:v>
       </x:c>
       <x:c r="C75" s="10" t="str">
         <x:v>重生七零辣媳不好惹</x:v>
@@ -9407,7 +9407,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B76" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 19:30</x:v>
       </x:c>
       <x:c r="C76" s="10" t="str">
         <x:v>初初处处藏不住</x:v>
@@ -9439,7 +9439,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B77" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 00:06</x:v>
       </x:c>
       <x:c r="C77" s="10" t="str">
         <x:v>号外号外，团宠小师妹她又开挂了</x:v>
@@ -9471,7 +9471,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B78" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:30</x:v>
       </x:c>
       <x:c r="C78" s="10" t="str">
         <x:v>开局成废后我反手养出十万御林军</x:v>
@@ -9503,7 +9503,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B79" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:00</x:v>
       </x:c>
       <x:c r="C79" s="10" t="str">
         <x:v>穿回八零我凭厨艺旺翻全家</x:v>
@@ -9535,7 +9535,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B80" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 11:00</x:v>
       </x:c>
       <x:c r="C80" s="10" t="str">
         <x:v>重生六零之护妻猎王</x:v>
@@ -9567,7 +9567,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B81" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:00</x:v>
       </x:c>
       <x:c r="C81" s="10" t="str">
         <x:v>重生后我靠鉴宝慧眼翻身</x:v>
@@ -9599,7 +9599,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B82" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 14:57</x:v>
       </x:c>
       <x:c r="C82" s="10" t="str">
         <x:v>长姐归来，以爱托举全家！</x:v>
@@ -9631,7 +9631,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B83" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:37</x:v>
       </x:c>
       <x:c r="C83" s="10" t="str">
         <x:v>为了活命我拼命整活</x:v>
@@ -9663,7 +9663,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B84" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 16:00</x:v>
       </x:c>
       <x:c r="C84" s="10" t="str">
         <x:v>婴语大师</x:v>
@@ -9695,7 +9695,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B85" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 20:30</x:v>
       </x:c>
       <x:c r="C85" s="10" t="str">
         <x:v>小五替我择良缘</x:v>
@@ -9727,7 +9727,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B86" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 08:30</x:v>
       </x:c>
       <x:c r="C86" s="10" t="str">
         <x:v>穿越乱世：每天一份拼好饭</x:v>
@@ -9759,7 +9759,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B87" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 11:16</x:v>
       </x:c>
       <x:c r="C87" s="10" t="str">
         <x:v>萌小宝寻爹记</x:v>
@@ -9791,7 +9791,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B88" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 17:00</x:v>
       </x:c>
       <x:c r="C88" s="10" t="str">
         <x:v>转夫运</x:v>
@@ -9823,7 +9823,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B89" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 16:00</x:v>
       </x:c>
       <x:c r="C89" s="10" t="str">
         <x:v>这一世，换我走向你</x:v>
@@ -9855,7 +9855,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 09:00</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
         <x:v>魂归处：不待帝王悔</x:v>
@@ -9887,7 +9887,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 10:05</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
         <x:v>太学废柴班拯救计划</x:v>
@@ -9919,7 +9919,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 17:00</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
         <x:v>携手千里渡荒年</x:v>
@@ -9951,7 +9951,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B93" s="11" t="str">
-        <x:v>09·04</x:v>
+        <x:v>09-04 09:47</x:v>
       </x:c>
       <x:c r="C93" s="10" t="str">
         <x:v>虾仁穿成驸马爷，公主谁爱娶谁娶！</x:v>
@@ -9983,7 +9983,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B94" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:30</x:v>
       </x:c>
       <x:c r="C94" s="10" t="str">
         <x:v>不寄人间半尺光</x:v>
@@ -10015,7 +10015,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B95" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C95" s="10" t="str">
         <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
@@ -10047,7 +10047,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B96" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
         <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
@@ -10079,7 +10079,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
         <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
@@ -10111,7 +10111,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
         <x:v>三年，我不装了</x:v>
@@ -10143,7 +10143,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:08</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
         <x:v>沙县厨神</x:v>
@@ -10175,7 +10175,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:07</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
         <x:v>九零绝境潮汐系统护我</x:v>
@@ -10207,7 +10207,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B101" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
         <x:v>予你情深，岁岁相守</x:v>
@@ -10239,7 +10239,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B102" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:06</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
         <x:v>仙界老祖非要当我哥</x:v>
@@ -10271,7 +10271,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B103" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:45</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
         <x:v>农家穗安：饼香满镇</x:v>
@@ -10303,7 +10303,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B104" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
         <x:v>回乡种田，手握灵泉养全家</x:v>
@@ -10335,7 +10335,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B105" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
         <x:v>嫡女归来，厨香撼京华</x:v>
@@ -10367,7 +10367,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B106" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 09:58</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
         <x:v>山野新婚暖光阴</x:v>
@@ -10399,7 +10399,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
         <x:v>我的小土狗竟有大帝之姿</x:v>
@@ -10431,7 +10431,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
         <x:v>替嫁棺妃</x:v>
@@ -10463,7 +10463,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
         <x:v>末世的最后一餐</x:v>
@@ -10495,7 +10495,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
         <x:v>穿成纨绔，我靠诗词当文圣</x:v>
@@ -10525,7 +10525,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B111" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 00:06</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
         <x:v>被赶走的保姆，竟是真夫人</x:v>
@@ -10557,7 +10557,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
         <x:v>新婚的羔羊</x:v>
@@ -10589,7 +10589,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B113" s="11" t="str">
-        <x:v>09·05</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
         <x:v>人到中年我逆袭成百草圣手</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R7e3580a2c9fc46bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R90dd60951966478a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R1023ccf0ca2e4841"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Reedcbc1e68c24455"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R999882196cd7459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R9939112cc6564c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R0ac77d9f57ec4e3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R68479af133dd4f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rf0a722207f2a43fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R3c9eca9d48c340a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R9e493397da8c41a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="Rc33ad09738f24d10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5842,7 +5842,7 @@
         <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度；发布账号「幻境大剧场」双口径都产爆款；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J74" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -6330,31 +6330,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
-        <x:v>09-04 09:00</x:v>
+        <x:v>09-04 10:05</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>魂归处：不待帝王悔</x:v>
+        <x:v>太学废柴班拯救计划</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>片单挖掘机</x:v>
+        <x:v>小曲动漫</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>皇后沈知微的父兄戍守边关重伤待援，她苦苦恳求帝王萧景珩下旨救人，却因贵妃柳如烟从中作梗，圣旨被一再搁置。父亲战死、兄长残伤归来，沈知微心死，借助系统开启假死程序，纵火焚毁坤宁宫。她灵魂滞留世间见证因果清算，萧景珩查清全部真相，严惩柳氏一族，对沈家百般补偿，深陷无尽悔恨。面对帝王迟来的忏悔，沈知微选择绝不原谅，了结全部羁绊，终于得以脱离这个世界，为自己重获新生。</x:v>
+        <x:v>林非晚穿成尚书府不受宠的嫡长女，嫁给了镇国将军霍云霆。她以现代商战智慧执掌公府财政，把太学废柴三害调教成科举前三甲，更带领他们揪出赈灾粮贪腐黑幕。诈死的战神丈夫现身，与她并肩作战、步步为营揭开惊天大案，最终朝堂清明，夫妻情深，昔日纨绔皆成治国栋梁。</x:v>
       </x:c>
       <x:c r="I90" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；43集，次优长度；发布账号「片单挖掘机」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；84集，主力长度；发布账号「小曲动漫」</x:v>
       </x:c>
       <x:c r="J90" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -6362,13 +6362,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>09-04 10:05</x:v>
+        <x:v>09-04 17:00</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>太学废柴班拯救计划</x:v>
+        <x:v>携手千里渡荒年</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>其他</x:v>
@@ -6377,13 +6377,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>小曲动漫</x:v>
+        <x:v>逗小包</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>林非晚穿成尚书府不受宠的嫡长女，嫁给了镇国将军霍云霆。她以现代商战智慧执掌公府财政，把太学废柴三害调教成科举前三甲，更带领他们揪出赈灾粮贪腐黑幕。诈死的战神丈夫现身，与她并肩作战、步步为营揭开惊天大案，最终朝堂清明，夫妻情深，昔日纨绔皆成治国栋梁。</x:v>
+        <x:v>现代女主意外穿越荒年，成为温四月，身陷逃荒绝境。危难之际，憨厚赤诚的夫君厉青山始终护她周全，为她遮风挡雨。绝境之中，温四月意外觉醒灵泉空间，手握求生底牌。逃亡路上，她褪去怯懦，凭借智慧与异能，习得炼盐之术、寻觅山野食粮，带领同行众人绝境求生。她心怀善意，坚守本心，与厉青山相互扶持、并肩前行，在乱世绝境中扎根希望，于颠沛流离里守护烟火与温情，一步步奔赴生机与新生。</x:v>
       </x:c>
       <x:c r="I91" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；84集，主力长度；发布账号「小曲动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；117集，次优长度；发布账号「逗小包」</x:v>
       </x:c>
       <x:c r="J91" s="11" t="n">
         <x:v>7.5</x:v>
@@ -6394,13 +6394,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>09-04 17:00</x:v>
+        <x:v>09-04 09:00</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>携手千里渡荒年</x:v>
+        <x:v>毒士：千古第三阳谋</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>117</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
         <x:v>其他</x:v>
@@ -6409,13 +6409,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>逗小包</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>现代女主意外穿越荒年，成为温四月，身陷逃荒绝境。危难之际，憨厚赤诚的夫君厉青山始终护她周全，为她遮风挡雨。绝境之中，温四月意外觉醒灵泉空间，手握求生底牌。逃亡路上，她褪去怯懦，凭借智慧与异能，习得炼盐之术、寻觅山野食粮，带领同行众人绝境求生。她心怀善意，坚守本心，与厉青山相互扶持、并肩前行，在乱世绝境中扎根希望，于颠沛流离里守护烟火与温情，一步步奔赴生机与新生。</x:v>
+        <x:v>高阳意外穿越大乾，成了长安臭名昭著的纨绔子弟。一次揭榜入宫，他凭狠辣刁钻的谋略得到女帝武曌赏识，从平粮价、赈灾救民，到朝堂斗法、兵战争锋、削藩定策，步步算尽人心。面对权臣、世家与藩王，高阳以毒计破局，逐渐成为女帝身边最危险、也最不可或缺的第一毒士。</x:v>
       </x:c>
       <x:c r="I92" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；117集，次优长度；发布账号「逗小包」</x:v>
+        <x:v>题材契合爆款主线×1（剧名/分类/简介三路识别）；简介爽点词×1；819集，长度需关注；发布账号「孤灵剧场」双口径都产爆款</x:v>
       </x:c>
       <x:c r="J92" s="11" t="n">
         <x:v>7.5</x:v>
@@ -6482,7 +6482,7 @@
         <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；73集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
       </x:c>
       <x:c r="J94" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -6514,7 +6514,7 @@
         <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；96集，主力长度；发布账号「星屿漫剧场」按上榜剧数入榜</x:v>
       </x:c>
       <x:c r="J95" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>9.5</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -6874,28 +6874,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 07:12</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>我的小土狗竟有大帝之姿</x:v>
+        <x:v>山间破晓路</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>嘉午纪</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
+        <x:v>青山村菜农王桂芳遭黑车欺压，252路司机张桂林违规接送菜农引发争议。面对黑车报复与内部排挤，二人坚守初心。在经理李建国支持下，他们克服扎胎、诬陷等阻碍，最终推动惠农专线正式落地，带领村民成立合作社，实现共同致富。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
+        <x:v>题材待验证；127集，次优长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
         <x:v>7</x:v>
@@ -6906,28 +6906,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>替嫁棺妃</x:v>
+        <x:v>我的小土狗竟有大帝之姿</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>诗婳影视</x:v>
+        <x:v>嘉午纪</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
+        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
         <x:v>7</x:v>
@@ -6938,28 +6938,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>末世的最后一餐</x:v>
+        <x:v>替嫁棺妃</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F109" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>团子动漫</x:v>
+        <x:v>诗婳影视</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
+        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
         <x:v>7</x:v>
@@ -6970,13 +6970,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
+        <x:v>末世的最后一餐</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
@@ -6984,12 +6984,14 @@
       <x:c r="F110" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G110" s="10" t="str"/>
+      <x:c r="G110" s="10" t="str">
+        <x:v>团子动漫</x:v>
+      </x:c>
       <x:c r="H110" s="10" t="str">
-        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
+        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
         <x:v>7</x:v>
@@ -7000,28 +7002,26 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B111" s="11" t="str">
-        <x:v>09-05 00:06</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>被赶走的保姆，竟是真夫人</x:v>
+        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str"/>
       <x:c r="H111" s="10" t="str">
-        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
+        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
         <x:v>7</x:v>
@@ -7032,31 +7032,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 00:06</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>新婚的羔羊</x:v>
+        <x:v>被赶走的保姆，竟是真夫人</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>战神漫剧</x:v>
+        <x:v>九鲤动漫</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
+        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>6.5</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7067,28 +7067,28 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>人到中年我逆袭成百草圣手</x:v>
+        <x:v>新婚的羔羊</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>极剧-热血剧场</x:v>
+        <x:v>战神漫剧</x:v>
       </x:c>
       <x:c r="H113" s="10" t="str">
-        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
+        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
       </x:c>
       <x:c r="I113" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；50集，次优长度；发布账号「极剧-热血剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
       </x:c>
       <x:c r="J113" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>6.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9367,7 +9367,7 @@
         <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度；发布账号「幻境大剧场」双口径都产爆款；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J74" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -9855,31 +9855,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="11" t="str">
-        <x:v>09-04 09:00</x:v>
+        <x:v>09-04 10:05</x:v>
       </x:c>
       <x:c r="C90" s="10" t="str">
-        <x:v>魂归处：不待帝王悔</x:v>
+        <x:v>太学废柴班拯救计划</x:v>
       </x:c>
       <x:c r="D90" s="11" t="n">
-        <x:v>43</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F90" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G90" s="10" t="str">
-        <x:v>片单挖掘机</x:v>
+        <x:v>小曲动漫</x:v>
       </x:c>
       <x:c r="H90" s="10" t="str">
-        <x:v>皇后沈知微的父兄戍守边关重伤待援，她苦苦恳求帝王萧景珩下旨救人，却因贵妃柳如烟从中作梗，圣旨被一再搁置。父亲战死、兄长残伤归来，沈知微心死，借助系统开启假死程序，纵火焚毁坤宁宫。她灵魂滞留世间见证因果清算，萧景珩查清全部真相，严惩柳氏一族，对沈家百般补偿，深陷无尽悔恨。面对帝王迟来的忏悔，沈知微选择绝不原谅，了结全部羁绊，终于得以脱离这个世界，为自己重获新生。</x:v>
+        <x:v>林非晚穿成尚书府不受宠的嫡长女，嫁给了镇国将军霍云霆。她以现代商战智慧执掌公府财政，把太学废柴三害调教成科举前三甲，更带领他们揪出赈灾粮贪腐黑幕。诈死的战神丈夫现身，与她并肩作战、步步为营揭开惊天大案，最终朝堂清明，夫妻情深，昔日纨绔皆成治国栋梁。</x:v>
       </x:c>
       <x:c r="I90" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；43集，次优长度；发布账号「片单挖掘机」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；84集，主力长度；发布账号「小曲动漫」</x:v>
       </x:c>
       <x:c r="J90" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7.5</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -9887,13 +9887,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B91" s="11" t="str">
-        <x:v>09-04 10:05</x:v>
+        <x:v>09-04 17:00</x:v>
       </x:c>
       <x:c r="C91" s="10" t="str">
-        <x:v>太学废柴班拯救计划</x:v>
+        <x:v>携手千里渡荒年</x:v>
       </x:c>
       <x:c r="D91" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E91" s="11" t="str">
         <x:v>其他</x:v>
@@ -9902,13 +9902,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G91" s="10" t="str">
-        <x:v>小曲动漫</x:v>
+        <x:v>逗小包</x:v>
       </x:c>
       <x:c r="H91" s="10" t="str">
-        <x:v>林非晚穿成尚书府不受宠的嫡长女，嫁给了镇国将军霍云霆。她以现代商战智慧执掌公府财政，把太学废柴三害调教成科举前三甲，更带领他们揪出赈灾粮贪腐黑幕。诈死的战神丈夫现身，与她并肩作战、步步为营揭开惊天大案，最终朝堂清明，夫妻情深，昔日纨绔皆成治国栋梁。</x:v>
+        <x:v>现代女主意外穿越荒年，成为温四月，身陷逃荒绝境。危难之际，憨厚赤诚的夫君厉青山始终护她周全，为她遮风挡雨。绝境之中，温四月意外觉醒灵泉空间，手握求生底牌。逃亡路上，她褪去怯懦，凭借智慧与异能，习得炼盐之术、寻觅山野食粮，带领同行众人绝境求生。她心怀善意，坚守本心，与厉青山相互扶持、并肩前行，在乱世绝境中扎根希望，于颠沛流离里守护烟火与温情，一步步奔赴生机与新生。</x:v>
       </x:c>
       <x:c r="I91" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；84集，主力长度；发布账号「小曲动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；117集，次优长度；发布账号「逗小包」</x:v>
       </x:c>
       <x:c r="J91" s="11" t="n">
         <x:v>7.5</x:v>
@@ -9919,13 +9919,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="11" t="str">
-        <x:v>09-04 17:00</x:v>
+        <x:v>09-04 09:00</x:v>
       </x:c>
       <x:c r="C92" s="10" t="str">
-        <x:v>携手千里渡荒年</x:v>
+        <x:v>毒士：千古第三阳谋</x:v>
       </x:c>
       <x:c r="D92" s="11" t="n">
-        <x:v>117</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="E92" s="11" t="str">
         <x:v>其他</x:v>
@@ -9934,13 +9934,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G92" s="10" t="str">
-        <x:v>逗小包</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="H92" s="10" t="str">
-        <x:v>现代女主意外穿越荒年，成为温四月，身陷逃荒绝境。危难之际，憨厚赤诚的夫君厉青山始终护她周全，为她遮风挡雨。绝境之中，温四月意外觉醒灵泉空间，手握求生底牌。逃亡路上，她褪去怯懦，凭借智慧与异能，习得炼盐之术、寻觅山野食粮，带领同行众人绝境求生。她心怀善意，坚守本心，与厉青山相互扶持、并肩前行，在乱世绝境中扎根希望，于颠沛流离里守护烟火与温情，一步步奔赴生机与新生。</x:v>
+        <x:v>高阳意外穿越大乾，成了长安臭名昭著的纨绔子弟。一次揭榜入宫，他凭狠辣刁钻的谋略得到女帝武曌赏识，从平粮价、赈灾救民，到朝堂斗法、兵战争锋、削藩定策，步步算尽人心。面对权臣、世家与藩王，高阳以毒计破局，逐渐成为女帝身边最危险、也最不可或缺的第一毒士。</x:v>
       </x:c>
       <x:c r="I92" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；117集，次优长度；发布账号「逗小包」</x:v>
+        <x:v>题材契合爆款主线×1（剧名/分类/简介三路识别）；简介爽点词×1；819集，长度需关注；发布账号「孤灵剧场」双口径都产爆款</x:v>
       </x:c>
       <x:c r="J92" s="11" t="n">
         <x:v>7.5</x:v>
@@ -10007,7 +10007,7 @@
         <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；73集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
       </x:c>
       <x:c r="J94" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -10399,28 +10399,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 07:12</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>我的小土狗竟有大帝之姿</x:v>
+        <x:v>山间破晓路</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>嘉午纪</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
+        <x:v>青山村菜农王桂芳遭黑车欺压，252路司机张桂林违规接送菜农引发争议。面对黑车报复与内部排挤，二人坚守初心。在经理李建国支持下，他们克服扎胎、诬陷等阻碍，最终推动惠农专线正式落地，带领村民成立合作社，实现共同致富。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
+        <x:v>题材待验证；127集，次优长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
         <x:v>7</x:v>
@@ -10431,28 +10431,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>替嫁棺妃</x:v>
+        <x:v>我的小土狗竟有大帝之姿</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>诗婳影视</x:v>
+        <x:v>嘉午纪</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
+        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
         <x:v>7</x:v>
@@ -10463,28 +10463,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>末世的最后一餐</x:v>
+        <x:v>替嫁棺妃</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F109" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>团子动漫</x:v>
+        <x:v>诗婳影视</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
+        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
         <x:v>7</x:v>
@@ -10495,13 +10495,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
+        <x:v>末世的最后一餐</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
@@ -10509,12 +10509,14 @@
       <x:c r="F110" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G110" s="10" t="str"/>
+      <x:c r="G110" s="10" t="str">
+        <x:v>团子动漫</x:v>
+      </x:c>
       <x:c r="H110" s="10" t="str">
-        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
+        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
         <x:v>7</x:v>
@@ -10525,28 +10527,26 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B111" s="11" t="str">
-        <x:v>09-05 00:06</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>被赶走的保姆，竟是真夫人</x:v>
+        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str"/>
       <x:c r="H111" s="10" t="str">
-        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
+        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
         <x:v>7</x:v>
@@ -10557,31 +10557,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 00:06</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>新婚的羔羊</x:v>
+        <x:v>被赶走的保姆，竟是真夫人</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>战神漫剧</x:v>
+        <x:v>九鲤动漫</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
+        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>6.5</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -10592,28 +10592,28 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>人到中年我逆袭成百草圣手</x:v>
+        <x:v>新婚的羔羊</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>极剧-热血剧场</x:v>
+        <x:v>战神漫剧</x:v>
       </x:c>
       <x:c r="H113" s="10" t="str">
-        <x:v>江承远被儿媳嫌弃、被迫离家，回山村靠辨药本领采药谋生，途中救了凌氏董事长凌玥，获其赏识入职凌氏。他从保安做起，凭过人眼力接连识破百年首乌、千年紫芝等名贵药材，屡次为公司挽回损失，一路逆袭为中药研发总监。儿媳张萍与高管陈舟勾结掉包药材、偷换雪灵芝，江承远与凌玥联手揭穿阴谋，儿子江泽看清张萍真面目与其离婚。江承远在药材交流会上大展身手，获行业贡献奖，与凌玥发展出真挚黄昏恋，带着儿子活出光彩人生。</x:v>
+        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
       </x:c>
       <x:c r="I113" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；50集，次优长度；发布账号「极剧-热血剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
       </x:c>
       <x:c r="J113" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>6.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R0ac77d9f57ec4e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R68479af133dd4f45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rf0a722207f2a43fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R3c9eca9d48c340a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R9e493397da8c41a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="Rc33ad09738f24d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R344b4674295c4beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R37c494d6aa794bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rb87fd09badde4265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R3e3e45043e7b4fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R00bfd88128db4aac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R9f7eef375b5147e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -359,7 +359,7 @@
         <x:v>08-10 20:00</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="10" t="n">
         <x:v>375</x:v>
@@ -372,7 +372,7 @@
       </x:c>
       <x:c r="H2" s="11" t="str"/>
       <x:c r="I2" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -415,7 +415,7 @@
         <x:v>08-09 11:00</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="10" t="n">
         <x:v>66</x:v>
@@ -428,7 +428,7 @@
       </x:c>
       <x:c r="H4" s="11" t="str"/>
       <x:c r="I4" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-29、2026-08-30、2026-08-31、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -469,7 +469,7 @@
         <x:v>08-14 09:00</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="10" t="n">
         <x:v>788</x:v>
@@ -484,7 +484,7 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
+        <x:v>2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -492,28 +492,28 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>包子里的真心</x:v>
+        <x:v>县令哭穷五年，李世民进城懵了</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>08-07 17:29</x:v>
+        <x:v>06-29 17:30</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="10" t="n">
-        <x:v>41</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>7514</x:v>
+        <x:v>1834</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -521,28 +521,28 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>县令哭穷五年，李世民进城懵了</x:v>
+        <x:v>天灾囤货录，善恶见人心</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>06-29 17:30</x:v>
+        <x:v>08-10 16:30</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
-        <x:v>67</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F8" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>种田囤货 / 现实反转</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>1834</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -550,25 +550,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>天灾囤货录，善恶见人心</x:v>
+        <x:v>包子里的真心</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>08-10 16:30</x:v>
+        <x:v>08-07 17:29</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
-        <x:v>151</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F9" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G9" s="10" t="str">
-        <x:v>种田囤货 / 现实反转</x:v>
+        <x:v>婚姻情感 / 美食治愈</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>852</x:v>
+        <x:v>7514</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24</x:v>
@@ -664,26 +664,26 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>半梦半醒半清欢</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>08-10 15:00</x:v>
+        <x:v>07-20 10:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F13" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G13" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str"/>
       <x:c r="I13" s="10" t="str">
-        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
+        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -691,26 +691,26 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>08-11 08:00</x:v>
+        <x:v>08-10 15:00</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G14" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str"/>
       <x:c r="I14" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
+        <x:v>2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -718,26 +718,26 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>08-11 00:26</x:v>
+        <x:v>08-11 08:00</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E15" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F15" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G15" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str"/>
       <x:c r="I15" s="10" t="str">
-        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20、2026-08-21、2026-08-22、2026-08-24</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -745,26 +745,26 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>半梦半醒半清欢</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>07-20 10:00</x:v>
+        <x:v>08-11 00:26</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E16" s="10" t="n">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F16" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str"/>
       <x:c r="I16" s="10" t="str">
-        <x:v>2026-08-19、2026-08-20、2026-08-21、2026-08-23、2026-08-24、2026-08-25、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
+        <x:v>2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-19、2026-08-20、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-28</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -882,26 +882,26 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>菌香深处见人心</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>06-30 18:00</x:v>
+        <x:v>08-21 17:00</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E21" s="10" t="n">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F21" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G21" s="10" t="str">
-        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str"/>
       <x:c r="I21" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -909,26 +909,26 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>商场收回档口我成了全城的供应商</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>08-19 20:22</x:v>
+        <x:v>06-30 18:00</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E22" s="10" t="n">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str">
-        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-01</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -936,26 +936,26 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>菌香深处见人心</x:v>
+        <x:v>商场收回档口我成了全城的供应商</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>08-21 17:00</x:v>
+        <x:v>08-19 20:22</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str">
-        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
+        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -963,26 +963,26 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>一瓶奶走过两个清晨</x:v>
+        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-18 15:11</x:v>
+        <x:v>08-24 08:00</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>63</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>2026-08-19、2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -990,28 +990,26 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>余生逢玉伴心安</x:v>
+        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>07-13 14:00</x:v>
+        <x:v>07-20 14:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="H25" s="11" t="n">
-        <x:v>785</x:v>
-      </x:c>
+        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-24、2026-08-26</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1019,26 +1017,26 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>一瓶奶走过两个清晨</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-10 09:00</x:v>
+        <x:v>08-18 15:11</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>136</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-19、2026-08-20</x:v>
+        <x:v>2026-08-19、2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1104,28 +1102,28 @@
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="10" t="str">
-        <x:v>重生80：十斤大米娶媳妇</x:v>
+        <x:v>六万不到账，五十桌不开席</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>09-01 06:30</x:v>
+        <x:v>09-02 19:00</x:v>
       </x:c>
       <x:c r="F2" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>208</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H2" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I2" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="J2" s="10" t="str">
-        <x:v>白尘</x:v>
+        <x:v>云起剧场</x:v>
       </x:c>
       <x:c r="K2" s="10" t="str"/>
     </x:row>
@@ -1135,19 +1133,19 @@
       </x:c>
       <x:c r="B3" s="11"/>
       <x:c r="C3" s="10" t="str">
-        <x:v>这辆车，我不伺候了</x:v>
+        <x:v>宴席终散人归远</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>09-01 18:07</x:v>
+        <x:v>09-01 20:18</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
         <x:v>仿真人</x:v>
@@ -1156,7 +1154,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>柚子吖</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str"/>
     </x:row>
@@ -1166,30 +1164,32 @@
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="10" t="str">
-        <x:v>当妈妈开始较真的时候</x:v>
+        <x:v>靠山屯纪事</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
+        <x:v>09-02 15:00</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>小圆子剧场</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="str"/>
+        <x:v>小小动画</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str">
+        <x:v>穿越到七十年代的花昭，重生在肥胖的少女身上。她凭借一身胆识与偶然得到的宝物，改变自身境遇，巧妙化解亲戚的算计纠缠。抓住时代机遇带动村里发展副业，改善一家人的生活。与军人叶深结缘，意外迎来新的小生命。面对原生家庭的复杂纠葛，她保持清醒，护住爷爷与至亲，在艰苦的年代里脚踏实地，靠着智慧和韧性，一步步打拼出属于自己的安稳人生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -1197,28 +1197,28 @@
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="10" t="str">
-        <x:v>我有六个黄毛爹</x:v>
+        <x:v>你让我出海：我一船货卖二十万你慌什么</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
+        <x:v>09-02 09:05</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>呼哈短剧</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str"/>
     </x:row>
@@ -1228,28 +1228,28 @@
       </x:c>
       <x:c r="B6" s="11"/>
       <x:c r="C6" s="10" t="str">
-        <x:v>烫嘴的免费午饭</x:v>
+        <x:v>我什么都没干，却成了大功臣</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>09-01 11:00</x:v>
+        <x:v>09-01 17:32</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>夏安安</x:v>
+        <x:v>小姐姐追漫画</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str"/>
     </x:row>
@@ -1259,23 +1259,29 @@
       </x:c>
       <x:c r="B7" s="11"/>
       <x:c r="C7" s="10" t="str">
-        <x:v>乱世繁花入君怀</x:v>
+        <x:v>扣我三十万，我收购你公司</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="str"/>
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>08-08 10:00</x:v>
+      </x:c>
       <x:c r="F7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="str"/>
+      <x:c r="G7" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J7" s="10" t="str"/>
+        <x:v>都市职场</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="str">
+        <x:v>闪闪动漫社</x:v>
+      </x:c>
       <x:c r="K7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
@@ -1284,30 +1290,32 @@
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="10" t="str">
-        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
+        <x:v>盛海风云</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
+        <x:v>09-02 09:58</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
-        <x:v>白桃剧场</x:v>
-      </x:c>
-      <x:c r="K8" s="10" t="str"/>
+        <x:v>星间漫步</x:v>
+      </x:c>
+      <x:c r="K8" s="10" t="str">
+        <x:v>八十岁的千亿级盛海财团创始人林晚秋重生回到董事会召开前夕，当场罢免为私情撕毁百亿合作协议的嫡孙顾景辰，召回蛰伏非洲的铁血庶孙顾景深，布下代码陷阱精准反制宿敌耀星科技的商业间谍阴谋，以铁血手腕守护集团基业，顺利完成新老权力交接。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -1315,28 +1323,28 @@
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="10" t="str">
-        <x:v>这一次，换我保护妈妈</x:v>
+        <x:v>一块钱买来的妈妈</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>09-01 08:00</x:v>
+        <x:v>09-02 01:57</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>阿南影视</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str"/>
     </x:row>
@@ -1346,28 +1354,28 @@
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="10" t="str">
-        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
+        <x:v>外婆的小心思</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>08-31 18:00</x:v>
+        <x:v>09-01 11:22</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>457</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>江屿动漫</x:v>
+        <x:v>奇境剧场</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str"/>
     </x:row>
@@ -1377,19 +1385,19 @@
       </x:c>
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="10" t="str">
-        <x:v>一纸微光赴君归</x:v>
+        <x:v>月薪四千，我手握亿级底牌</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>08-27 21:48</x:v>
+        <x:v>07-24 11:00</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
         <x:v>仿真人</x:v>
@@ -1398,7 +1406,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>二里清风</x:v>
+        <x:v>治愈 AI 恋</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str"/>
     </x:row>
@@ -1408,28 +1416,28 @@
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="10" t="str">
-        <x:v>后厨藏真爱，中年遇良缘</x:v>
+        <x:v>商场涨租，我连夜带走所有商户</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>08-24 08:00</x:v>
+        <x:v>09-02 10:20</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>鲤鲤短剧</x:v>
+        <x:v>奈斯动画</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str"/>
     </x:row>
@@ -1439,32 +1447,30 @@
       </x:c>
       <x:c r="B13" s="11"/>
       <x:c r="C13" s="10" t="str">
-        <x:v>梦醒八零年</x:v>
+        <x:v>两个儿子护我归家</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>09-01 17:28</x:v>
+        <x:v>08-31 18:24</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>阿釉说漫</x:v>
-      </x:c>
-      <x:c r="K13" s="10" t="str">
-        <x:v>方鹤安从一场预示悲剧的旧梦里醒来，回到八十年代。知晓前世遭遇的他，断然拒绝了夏妍菲的提亲，决心夺回求学的机会。面对夏妍菲处处偏袒青梅竹马的种种行为，方鹤安不再一味迁就忍让，守住自己的底线。几番波折过后，他如愿走进大学校园，结识了品性真诚的顾清依。他彻底放下过往的情感执念，认真经营当下的生活，两人互相理解扶持，跨过岁月里的重重阻碍，最终收获安稳又甜蜜的幸福。</x:v>
-      </x:c>
+        <x:v>桑园小剧场</x:v>
+      </x:c>
+      <x:c r="K13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -1472,28 +1478,28 @@
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="10" t="str">
-        <x:v>没去团建，却背上三十四万欠款</x:v>
+        <x:v>遗落在村口的春天</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>08-28 09:00</x:v>
+        <x:v>09-02 10:37</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>会火短剧场</x:v>
+        <x:v>奇迹短剧</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str"/>
     </x:row>
@@ -1503,28 +1509,28 @@
       </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="10" t="str">
-        <x:v>镇北少帅</x:v>
+        <x:v>狂枭归来</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>08-26 16:06</x:v>
+        <x:v>08-30 00:06</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
+        <x:v>漫界剧场</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str"/>
     </x:row>
@@ -1534,30 +1540,32 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="10" t="str">
-        <x:v>当爸爸终于看见我</x:v>
+        <x:v>爹爹入赘我暴富啦</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>09-01 06:16</x:v>
+        <x:v>09-02 00:20</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>小何故事会</x:v>
-      </x:c>
-      <x:c r="K16" s="10" t="str"/>
+        <x:v>每日沙雕推荐</x:v>
+      </x:c>
+      <x:c r="K16" s="10" t="str">
+        <x:v>沈明珠看着母亲决绝离去，姐姐执意奔赴城里。她灵机一动，主动给父亲说媒，让父亲入赘彪悍女猎户钱三妞。她凭借前世记忆得到祖传的灵泉玉佩，和三位性格迥异的继兄相处融洽。一家人齐心对抗难缠的街坊对手，揭穿坏人的伪装，齐心协力把小日子过得红火安稳。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -1565,28 +1573,28 @@
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="10" t="str">
-        <x:v>诸天拍卖行，我好物倾销万域崛起</x:v>
+        <x:v>洋媳妇勇闯东北老家</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>08-31 07:27</x:v>
+        <x:v>09-02 16:00</x:v>
       </x:c>
       <x:c r="F17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H17" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J17" s="10" t="str">
-        <x:v>杰瑞剧场</x:v>
+        <x:v>云间漫剧-十六</x:v>
       </x:c>
       <x:c r="K17" s="10" t="str"/>
     </x:row>
@@ -1596,28 +1604,28 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="10" t="str">
-        <x:v>月月归梨</x:v>
+        <x:v>我没有爸，但有三个妈</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>09-01 16:30</x:v>
+        <x:v>09-02 08:00</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>149</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
-        <x:v>月下知棠</x:v>
+        <x:v>魔力大世界</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str"/>
     </x:row>
@@ -1627,28 +1635,28 @@
       </x:c>
       <x:c r="B19" s="11"/>
       <x:c r="C19" s="10" t="str">
-        <x:v>满堂寿宴皆虚情</x:v>
+        <x:v>布衣成圣</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
+        <x:v>09-01 18:30</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
-        <x:v>饺子动画</x:v>
+        <x:v>南小离</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str"/>
     </x:row>
@@ -1658,28 +1666,28 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="10" t="str">
-        <x:v>五年归期：我的崽成了团宠</x:v>
+        <x:v>十八年后再掌天远</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
+        <x:v>08-29 20:00</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
-        <x:v>言安剧场</x:v>
+        <x:v>小雅说漫</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str"/>
     </x:row>
@@ -1689,19 +1697,19 @@
       </x:c>
       <x:c r="B21" s="11"/>
       <x:c r="C21" s="10" t="str">
-        <x:v>星光落在身边</x:v>
+        <x:v>分房名单没有他</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>09-01 14:30</x:v>
+        <x:v>08-09 17:18</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
         <x:v>未标注</x:v>
@@ -1710,7 +1718,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
-        <x:v>熬夜视界</x:v>
+        <x:v>一身傲骨</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str"/>
     </x:row>
@@ -1720,28 +1728,28 @@
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="10" t="str">
-        <x:v>重生70猎户带妻女吃香喝辣</x:v>
+        <x:v>陈丰的故事！</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>08-24 17:19</x:v>
+        <x:v>09-01 19:41</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>婚姻情感 / 美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>_凌凌柒</x:v>
+        <x:v>小土豆动画</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str"/>
     </x:row>
@@ -1751,28 +1759,28 @@
       </x:c>
       <x:c r="B23" s="11"/>
       <x:c r="C23" s="10" t="str">
-        <x:v>我自杀猪匠登圣</x:v>
+        <x:v>守尺不负匠人心</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>08-31 21:08</x:v>
+        <x:v>09-02 00:10</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>201</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>布夭莲_</x:v>
+        <x:v>新漫剧场</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str"/>
     </x:row>
@@ -1782,13 +1790,13 @@
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="10" t="str">
-        <x:v>兽世第一废柴：靠实力啃三代</x:v>
+        <x:v>一碗牛肉板面的良心账</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>08-28 15:00</x:v>
+        <x:v>08-31 08:18</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:v>1</x:v>
@@ -1797,13 +1805,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="H24" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
-        <x:v>小风漫剧</x:v>
+        <x:v>朵朵漫</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str"/>
     </x:row>
@@ -1813,28 +1821,28 @@
       </x:c>
       <x:c r="B25" s="11"/>
       <x:c r="C25" s="10" t="str">
-        <x:v>细雨如春，替嫁得良缘</x:v>
+        <x:v>装穷三年，我和大小姐双双掉马</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>09-02 08:00</x:v>
+        <x:v>09-02 00:15</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str"/>
     </x:row>
@@ -1844,29 +1852,23 @@
       </x:c>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="10" t="str">
-        <x:v>深宫重华录</x:v>
+        <x:v>六零年代重组家庭实录</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="str">
-        <x:v>09-01 17:45</x:v>
-      </x:c>
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str"/>
       <x:c r="F26" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="n">
-        <x:v>141</x:v>
-      </x:c>
+      <x:c r="G26" s="11" t="str"/>
       <x:c r="H26" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J26" s="10" t="str">
-        <x:v>蓝语</x:v>
-      </x:c>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="J26" s="10" t="str"/>
       <x:c r="K26" s="10" t="str"/>
     </x:row>
     <x:row r="27">
@@ -1875,28 +1877,28 @@
       </x:c>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="10" t="str">
-        <x:v>我穿越寒门书生一路封神</x:v>
+        <x:v>玉碎双姝错</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>08-30 18:20</x:v>
+        <x:v>09-02 17:00</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>125</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>小团子动画</x:v>
+        <x:v>观月剧场</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str"/>
     </x:row>
@@ -1906,28 +1908,28 @@
       </x:c>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="10" t="str">
-        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
+        <x:v>洪伟的故事</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>09-01 10:54</x:v>
+        <x:v>09-02 09:53</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
-        <x:v>一漳动漫</x:v>
+        <x:v>淑芬动画</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str"/>
     </x:row>
@@ -1937,28 +1939,28 @@
       </x:c>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="10" t="str">
-        <x:v>高考落榜去搬砖，遇良人提点勤学上岸985</x:v>
+        <x:v>她为爱上岸，我们送她回海</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>07-14 09:30</x:v>
+        <x:v>09-02 17:08</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H29" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
-        <x:v>龙影剧院</x:v>
+        <x:v>悦也系</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str"/>
     </x:row>
@@ -1968,90 +1970,90 @@
       </x:c>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="10" t="str">
-        <x:v>滚烫的铁门</x:v>
+        <x:v>陷落京霓：错认大佬他心动了</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>09-01 11:00</x:v>
+        <x:v>08-30 18:00</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
-        <x:v>锦书AI映画</x:v>
+        <x:v>心动小剧场</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="10" t="str">
-        <x:v>龙赐神鉴：渔村少年驭沧海</x:v>
+        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>08-31 19:00</x:v>
+        <x:v>07-27 11:00</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>163</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>种田囤货 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>拾光漫漫</x:v>
+        <x:v>暖夏短剧</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
-        <x:v>新剧</x:v>
+        <x:v>次新剧</x:v>
       </x:c>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="10" t="str">
-        <x:v>嫡女锦杀第一季</x:v>
+        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>09-01 16:00</x:v>
+        <x:v>08-29 16:15</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G32" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
-        <x:v>桃桃漫剧</x:v>
+        <x:v>漫漫画丫头</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str"/>
     </x:row>
@@ -2061,28 +2063,28 @@
       </x:c>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="10" t="str">
-        <x:v>方寸宅院见公道</x:v>
+        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>08-30 10:00</x:v>
+        <x:v>08-31 20:00</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G33" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
-        <x:v>豆豆动漫</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str"/>
     </x:row>
@@ -2092,28 +2094,28 @@
       </x:c>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="10" t="str">
-        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
+        <x:v>闻心：京华稚园录</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>08-31 20:00</x:v>
+        <x:v>08-31 19:00</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G34" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>阿云剧场</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str"/>
     </x:row>
@@ -2123,28 +2125,28 @@
       </x:c>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="10" t="str">
-        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
+        <x:v>这辆车，我不伺候了</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>07-27 11:00</x:v>
+        <x:v>09-01 18:07</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G35" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>暖夏短剧</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str"/>
     </x:row>
@@ -2154,28 +2156,28 @@
       </x:c>
       <x:c r="B36" s="11"/>
       <x:c r="C36" s="10" t="str">
-        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
+        <x:v>重生80：十斤大米娶媳妇</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>08-29 16:15</x:v>
+        <x:v>09-01 06:30</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G36" s="11" t="n">
-        <x:v>156</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
-        <x:v>漫漫画丫头</x:v>
+        <x:v>白尘</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str"/>
     </x:row>
@@ -2185,28 +2187,28 @@
       </x:c>
       <x:c r="B37" s="11"/>
       <x:c r="C37" s="10" t="str">
-        <x:v>大婚当日立规矩，这婚我不结了</x:v>
+        <x:v>我有六个黄毛爹</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E37" s="11" t="str">
-        <x:v>08-31 17:00</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="F37" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H37" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
-        <x:v>云影漫剧</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="K37" s="10" t="str"/>
     </x:row>
@@ -2216,29 +2218,23 @@
       </x:c>
       <x:c r="B38" s="11"/>
       <x:c r="C38" s="10" t="str">
-        <x:v>颠婆穿书：我在年代文里当德华</x:v>
+        <x:v>乱世繁花入君怀</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E38" s="11" t="str">
-        <x:v>09-01 00:06</x:v>
-      </x:c>
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="str"/>
       <x:c r="F38" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G38" s="11" t="n">
-        <x:v>85</x:v>
-      </x:c>
+      <x:c r="G38" s="11" t="str"/>
       <x:c r="H38" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="J38" s="10" t="str">
-        <x:v>武汉卡看漫剧场</x:v>
-      </x:c>
+      <x:c r="J38" s="10" t="str"/>
       <x:c r="K38" s="10" t="str"/>
     </x:row>
     <x:row r="39">
@@ -2247,28 +2243,28 @@
       </x:c>
       <x:c r="B39" s="11"/>
       <x:c r="C39" s="10" t="str">
-        <x:v>闻心：京华稚园录</x:v>
+        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>08-31 19:00</x:v>
+        <x:v>08-31 18:00</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G39" s="11" t="n">
-        <x:v>106</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
-        <x:v>阿云剧场</x:v>
+        <x:v>江屿动漫</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str"/>
     </x:row>
@@ -2278,30 +2274,497 @@
       </x:c>
       <x:c r="B40" s="11"/>
       <x:c r="C40" s="10" t="str">
-        <x:v>烟火与匠心</x:v>
+        <x:v>烫嘴的免费午饭</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>08-31 20:07</x:v>
+        <x:v>09-01 11:00</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I40" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="J40" s="10" t="str">
+        <x:v>夏安安</x:v>
+      </x:c>
+      <x:c r="K40" s="10" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B41" s="11"/>
+      <x:c r="C41" s="10" t="str">
+        <x:v>五年归期：我的崽成了团宠</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E41" s="11" t="str">
+        <x:v>09-01 09:00</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H41" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I41" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="J41" s="10" t="str">
+        <x:v>言安剧场</x:v>
+      </x:c>
+      <x:c r="K41" s="10" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B42" s="11"/>
+      <x:c r="C42" s="10" t="str">
+        <x:v>跨物种相亲，我连夜扛着冰山跑路</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="str">
+        <x:v>08-30 15:07</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G42" s="11" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H42" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="I40" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J40" s="10" t="str">
-        <x:v>馆长玉先生剧场</x:v>
-      </x:c>
-      <x:c r="K40" s="10" t="str"/>
+      <x:c r="I42" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J42" s="10" t="str">
+        <x:v>菁禾</x:v>
+      </x:c>
+      <x:c r="K42" s="10" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B43" s="11"/>
+      <x:c r="C43" s="10" t="str">
+        <x:v>当妈妈开始较真的时候</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="str">
+        <x:v>09-01 09:00</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G43" s="11" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H43" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I43" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="J43" s="10" t="str">
+        <x:v>小圆子剧场</x:v>
+      </x:c>
+      <x:c r="K43" s="10" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B44" s="11"/>
+      <x:c r="C44" s="10" t="str">
+        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="str">
+        <x:v>09-01 10:54</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G44" s="11" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H44" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I44" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="J44" s="10" t="str">
+        <x:v>一漳动漫</x:v>
+      </x:c>
+      <x:c r="K44" s="10" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B45" s="11"/>
+      <x:c r="C45" s="10" t="str">
+        <x:v>满堂寿宴皆虚情</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="str">
+        <x:v>09-01 10:00</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G45" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H45" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I45" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="J45" s="10" t="str">
+        <x:v>饺子动画</x:v>
+      </x:c>
+      <x:c r="K45" s="10" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B46" s="11"/>
+      <x:c r="C46" s="10" t="str">
+        <x:v>细雨如春，替嫁得良缘</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="str">
+        <x:v>09-02 08:00</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G46" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H46" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I46" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="J46" s="10" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
+      <x:c r="K46" s="10" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B47" s="11"/>
+      <x:c r="C47" s="10" t="str">
+        <x:v>深宫重华录</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="str">
+        <x:v>09-01 17:45</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G47" s="11" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H47" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I47" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J47" s="10" t="str">
+        <x:v>蓝语</x:v>
+      </x:c>
+      <x:c r="K47" s="10" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B48" s="11"/>
+      <x:c r="C48" s="10" t="str">
+        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="str">
+        <x:v>09-01 10:00</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G48" s="11" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H48" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I48" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="J48" s="10" t="str">
+        <x:v>白桃剧场</x:v>
+      </x:c>
+      <x:c r="K48" s="10" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B49" s="11"/>
+      <x:c r="C49" s="10" t="str">
+        <x:v>梦醒八零年</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="str">
+        <x:v>09-01 17:28</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G49" s="11" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H49" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="I49" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="J49" s="10" t="str">
+        <x:v>阿釉说漫</x:v>
+      </x:c>
+      <x:c r="K49" s="10" t="str">
+        <x:v>方鹤安从一场预示悲剧的旧梦里醒来，回到八十年代。知晓前世遭遇的他，断然拒绝了夏妍菲的提亲，决心夺回求学的机会。面对夏妍菲处处偏袒青梅竹马的种种行为，方鹤安不再一味迁就忍让，守住自己的底线。几番波折过后，他如愿走进大学校园，结识了品性真诚的顾清依。他彻底放下过往的情感执念，认真经营当下的生活，两人互相理解扶持，跨过岁月里的重重阻碍，最终收获安稳又甜蜜的幸福。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B50" s="11"/>
+      <x:c r="C50" s="10" t="str">
+        <x:v>我自杀猪匠登圣</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="str">
+        <x:v>08-31 21:08</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G50" s="11" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H50" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I50" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J50" s="10" t="str">
+        <x:v>布夭莲_</x:v>
+      </x:c>
+      <x:c r="K50" s="10" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B51" s="11"/>
+      <x:c r="C51" s="10" t="str">
+        <x:v>万界轮回，我有亿万神话词条加身</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="str">
+        <x:v>08-31 13:17</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G51" s="11" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H51" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I51" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="J51" s="10" t="str">
+        <x:v>云间漫剧-零七</x:v>
+      </x:c>
+      <x:c r="K51" s="10" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B52" s="11"/>
+      <x:c r="C52" s="10" t="str">
+        <x:v>这一次，换我保护妈妈</x:v>
+      </x:c>
+      <x:c r="D52" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E52" s="11" t="str">
+        <x:v>09-01 08:00</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G52" s="11" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H52" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I52" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="J52" s="10" t="str">
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
+      <x:c r="K52" s="10" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B53" s="11"/>
+      <x:c r="C53" s="10" t="str">
+        <x:v>比武招亲，我竟成了女王爷的夫婿</x:v>
+      </x:c>
+      <x:c r="D53" s="11" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="E53" s="11" t="str">
+        <x:v>08-30 07:10</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G53" s="11" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="H53" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I53" s="10" t="str">
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="J53" s="10" t="str">
+        <x:v>诺威剧场</x:v>
+      </x:c>
+      <x:c r="K53" s="10" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B54" s="11"/>
+      <x:c r="C54" s="10" t="str">
+        <x:v>她契约的都是星际大佬</x:v>
+      </x:c>
+      <x:c r="D54" s="11" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="E54" s="11" t="str">
+        <x:v>08-31 10:00</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G54" s="11" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H54" s="10" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I54" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J54" s="10" t="str">
+        <x:v>阅友动漫</x:v>
+      </x:c>
+      <x:c r="K54" s="10" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="11" t="str">
+        <x:v>次新剧</x:v>
+      </x:c>
+      <x:c r="B55" s="11"/>
+      <x:c r="C55" s="10" t="str">
+        <x:v>镇北少帅</x:v>
+      </x:c>
+      <x:c r="D55" s="11" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E55" s="11" t="str">
+        <x:v>08-26 16:06</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G55" s="11" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H55" s="10" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I55" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J55" s="10" t="str">
+        <x:v>灵梦剧场</x:v>
+      </x:c>
+      <x:c r="K55" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2393,10 +2856,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
-        <x:v>天灾囤货录，善恶见人心</x:v>
+        <x:v>收租老汉</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>08-10 16:30</x:v>
+        <x:v>08-10 06:00</x:v>
       </x:c>
       <x:c r="D3" s="11" t="n">
         <x:v>7</x:v>
@@ -2408,16 +2871,16 @@
         <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G3" s="10" t="n">
-        <x:v>151</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>852</x:v>
+        <x:v>8368</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；151集长剧集；题材契合爆款主线（种田囤货 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2425,10 +2888,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>收租老汉</x:v>
+        <x:v>重回八零，赶山狩猎养妻女</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>08-10 06:00</x:v>
+        <x:v>07-17 18:30</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
         <x:v>7</x:v>
@@ -2437,19 +2900,17 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-29</x:v>
       </x:c>
       <x:c r="G4" s="10" t="n">
-        <x:v>121</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I4" s="11" t="n">
-        <x:v>8368</x:v>
-      </x:c>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str"/>
       <x:c r="J4" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计15次，起量能力已被验证；经典3D制作；121集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计15次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2457,29 +2918,29 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>沉渊三年：老槐树下的传家宝</x:v>
+        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>08-10 15:00</x:v>
+        <x:v>08-11 08:00</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>2026-08-25</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G5" s="10" t="n">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str"/>
       <x:c r="J5" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2487,10 +2948,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>先帝将我赐婚将军，他当众降我为妾</x:v>
+        <x:v>垃圾桶里的寻人启事</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>08-11 08:00</x:v>
+        <x:v>08-08 18:00</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
         <x:v>7</x:v>
@@ -2499,17 +2960,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="G6" s="10" t="n">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="str"/>
+      <x:c r="I6" s="11" t="n">
+        <x:v>4442</x:v>
+      </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；题材契合爆款主线（古装宫廷 / 婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2517,10 +2980,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>山王传奇</x:v>
+        <x:v>孤城照山河第一季</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>08-15 10:00</x:v>
+        <x:v>08-10 17:13</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
         <x:v>7</x:v>
@@ -2529,17 +2992,17 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="G7" s="10" t="n">
-        <x:v>95</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str"/>
       <x:c r="J7" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；95集长剧集；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计13次，起量能力已被验证；185集长剧集；题材契合爆款主线（古装宫廷）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2547,29 +3010,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>逆流年代：从1970开始种田养家</x:v>
+        <x:v>余生逢玉伴心安</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>08-15 10:00</x:v>
+        <x:v>07-13 14:00</x:v>
       </x:c>
       <x:c r="D8" s="11" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="G8" s="10" t="n">
-        <x:v>110</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="n">
+        <x:v>785</x:v>
+      </x:c>
       <x:c r="J8" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜7次、累计7次，起量能力已被验证；仿真人制作；110集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计11次，起量能力已被验证；68集长剧集；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2577,29 +3042,29 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>重回八零，赶山狩猎养妻女</x:v>
+        <x:v>小溪的逆袭第一季</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>07-17 18:30</x:v>
+        <x:v>08-10 09:00</x:v>
       </x:c>
       <x:c r="D9" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E9" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="G9" s="10" t="n">
-        <x:v>108</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str"/>
       <x:c r="J9" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计15次，起量能力已被验证；108集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货 / 婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2607,31 +3072,29 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>垃圾桶里的寻人启事</x:v>
+        <x:v>一盏灯暖赶路人</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>08-08 18:00</x:v>
+        <x:v>08-10 21:16</x:v>
       </x:c>
       <x:c r="D10" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E10" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-22</x:v>
       </x:c>
       <x:c r="G10" s="10" t="n">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I10" s="11" t="n">
-        <x:v>4442</x:v>
-      </x:c>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str"/>
       <x:c r="J10" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计13次，起量能力已被验证；60集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2639,29 +3102,29 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>姜猎娶妻之知青良缘</x:v>
+        <x:v>云岭藏金，真心为聘</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>08-17 09:38</x:v>
+        <x:v>07-17 19:00</x:v>
       </x:c>
       <x:c r="D11" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E11" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G11" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str"/>
       <x:c r="J11" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计10次，起量能力已被验证；经典3D制作；62集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2669,29 +3132,29 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>我妈装穷来认我</x:v>
+        <x:v>魔力情谊之我一个人来的</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>08-14 10:00</x:v>
+        <x:v>08-08 16:07</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G12" s="10" t="n">
-        <x:v>54</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str"/>
       <x:c r="J12" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜7次、累计8次，起量能力已被验证；经典3D制作；108集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2699,29 +3162,29 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
-        <x:v>暴雪见人心</x:v>
+        <x:v>沉渊三年：老槐树下的传家宝</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>08-16 08:21</x:v>
+        <x:v>08-10 15:00</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="G13" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str"/>
       <x:c r="J13" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计14次，起量能力已被验证；经典3D制作；53集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2729,29 +3192,29 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
-        <x:v>团建忘带我，我一觉睡塌了整个公司！</x:v>
+        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>08-11 10:41</x:v>
+        <x:v>08-11 00:26</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-28</x:v>
       </x:c>
       <x:c r="G14" s="10" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str"/>
       <x:c r="J14" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计8次，起量能力已被验证；55集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2759,29 +3222,29 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
-        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>08-12 15:35</x:v>
+        <x:v>06-30 18:00</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="G15" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计12次，起量能力已被验证；56集长剧集；题材契合爆款主线（种田囤货 / 美食治愈 / 逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2789,19 +3252,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
-        <x:v>这门婚我不嫁了</x:v>
+        <x:v>悍妻替嫁，从前说</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>08-15 09:00</x:v>
+        <x:v>08-06 11:00</x:v>
       </x:c>
       <x:c r="D16" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="G16" s="10" t="n">
         <x:v>68</x:v>
@@ -2811,7 +3274,7 @@
       </x:c>
       <x:c r="I16" s="11" t="str"/>
       <x:c r="J16" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2819,29 +3282,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
-        <x:v>小溪的逆袭第一季</x:v>
+        <x:v>爷爷不请七遍不动筷</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>08-10 09:00</x:v>
+        <x:v>07-17 10:00</x:v>
       </x:c>
       <x:c r="D17" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="G17" s="10" t="n">
-        <x:v>136</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H17" s="11" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I17" s="11" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:v>490</x:v>
+      </x:c>
       <x:c r="J17" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计11次，起量能力已被验证；136集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计9次，起量能力已被验证；仿真人制作；50集长剧集；题材契合爆款主线（家庭伦理）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2849,29 +3314,29 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
-        <x:v>一盏灯暖赶路人</x:v>
+        <x:v>轮回：别惹这个外卖员他活了一万年</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>08-10 21:16</x:v>
+        <x:v>08-09 13:30</x:v>
       </x:c>
       <x:c r="D18" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="G18" s="10" t="n">
-        <x:v>69</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H18" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I18" s="11" t="str"/>
       <x:c r="J18" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计10次，起量能力已被验证；仿真人制作；69集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计8次，起量能力已被验证；经典3D制作；122集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2879,29 +3344,29 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>分家只给破枪，我听兽语富全屯</x:v>
+        <x:v>三百块的信任，九十万的真相</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>08-13 09:02</x:v>
+        <x:v>08-11 17:00</x:v>
       </x:c>
       <x:c r="D19" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="G19" s="10" t="n">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H19" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I19" s="11" t="str"/>
       <x:c r="J19" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计7次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2909,29 +3374,29 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
-        <x:v>重生凛冬跟随囤货</x:v>
+        <x:v>我哥四个全是宠妹狂魔</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>08-16 13:16</x:v>
+        <x:v>08-07 10:59</x:v>
       </x:c>
       <x:c r="D20" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="G20" s="10" t="n">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H20" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I20" s="11" t="str"/>
       <x:c r="J20" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；81集长剧集；题材契合爆款主线（种田囤货）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计7次，起量能力已被验证；仿真人制作；100集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2939,29 +3404,29 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
-        <x:v>医风秩序线</x:v>
+        <x:v>大力幼崽到处捡爹</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>08-17 11:00</x:v>
+        <x:v>08-12 16:10</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G21" s="10" t="n">
-        <x:v>89</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H21" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I21" s="11" t="str"/>
       <x:c r="J21" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；89集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；200集长剧集；题材契合爆款主线（家庭伦理 / 萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2969,29 +3434,29 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>一墙之隔的求救声</x:v>
+        <x:v>馋哭！陆总该吃饭了</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>08-15 09:18</x:v>
+        <x:v>07-20 15:00</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F22" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G22" s="10" t="n">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I22" s="11" t="str"/>
       <x:c r="J22" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；88集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜6次、累计6次，起量能力已被验证；经典3D制作；98集长剧集；题材契合爆款主线（美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2999,29 +3464,29 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>五福临门，八方报喜</x:v>
+        <x:v>分家只给破枪，我听兽语富全屯</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>08-17 10:18</x:v>
+        <x:v>08-13 09:02</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F23" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="G23" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I23" s="11" t="str"/>
       <x:c r="J23" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；经典3D制作；79集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3029,29 +3494,29 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>芯骨藏锋</x:v>
+        <x:v>这个姨娘不一般</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-15 05:58</x:v>
+        <x:v>07-12 11:00</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F24" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G24" s="10" t="n">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H24" s="11" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I24" s="11" t="str"/>
       <x:c r="J24" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；仿真人制作；52集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；仿真人制作；62集长剧集；题材契合爆款主线（古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3059,29 +3524,29 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>全世界都吃不下，只有我吃到服务器瘫痪</x:v>
+        <x:v>重回千禧我靠赶海养活家人</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>08-11 00:26</x:v>
+        <x:v>07-19 17:18</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F25" s="11" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="G25" s="10" t="n">
-        <x:v>50</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I25" s="11" t="str"/>
       <x:c r="J25" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计13次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计8次，起量能力已被验证；183集长剧集；题材契合爆款主线（年代怀旧 / 种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3089,29 +3554,29 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>九二年，他塞给我五百块</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>07-20 14:00</x:v>
+        <x:v>08-09 13:57</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F26" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="G26" s="10" t="n">
-        <x:v>196</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str"/>
       <x:c r="J26" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计11次，起量能力已被验证；196集长剧集；题材契合爆款主线（萌宝治愈 / 都市职场 / 美食治愈）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计7次，起量能力已被验证；仿真人制作；64集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3119,29 +3584,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
-        <x:v>悍妻替嫁，从前说</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="str">
-        <x:v>08-06 11:00</x:v>
-      </x:c>
+        <x:v>学习暴富后，我孤立了整个豪门</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str"/>
       <x:c r="D27" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>2026-08-19</x:v>
-      </x:c>
-      <x:c r="G27" s="10" t="n">
-        <x:v>68</x:v>
-      </x:c>
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="G27" s="10" t="str"/>
       <x:c r="H27" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str"/>
       <x:c r="J27" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计9次，起量能力已被验证；经典3D制作；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计7次，起量能力已被验证；题材契合爆款主线（逆袭打脸）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3149,29 +3610,29 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
-        <x:v>八零之老妈在厂长家当后妈</x:v>
+        <x:v>199的排场，48万的账</x:v>
       </x:c>
       <x:c r="C28" s="11" t="str">
-        <x:v>08-14 09:08</x:v>
+        <x:v>08-08 18:00</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>2026-08-23</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G28" s="10" t="n">
-        <x:v>156</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H28" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I28" s="11" t="str"/>
       <x:c r="J28" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3179,29 +3640,29 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
-        <x:v>东北阿姨：捡了个南方小土豆</x:v>
+        <x:v>疯娘翻身，穿越宠崽</x:v>
       </x:c>
       <x:c r="C29" s="11" t="str">
-        <x:v>08-19 07:40</x:v>
+        <x:v>08-01 17:00</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G29" s="10" t="n">
-        <x:v>68</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H29" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I29" s="11" t="str"/>
       <x:c r="J29" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；68集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；200集长剧集；题材契合爆款主线（婚姻情感 / 逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3209,29 +3670,29 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
-        <x:v>冷宫开席：陛下又来蹭饭了</x:v>
+        <x:v>空间萌宝两岁半，小奶娃治愈全家</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>08-02 14:08</x:v>
+        <x:v>08-13 06:00</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="G30" s="10" t="n">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H30" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I30" s="11" t="str"/>
       <x:c r="J30" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；122集长剧集；题材契合爆款主线（古装宫廷 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；119集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -3239,29 +3700,29 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>各生归途</x:v>
+        <x:v>被总经理针对后，我只按菜单做菜</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>08-17 17:50</x:v>
+        <x:v>06-12 14:06</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G31" s="10" t="n">
-        <x:v>82</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H31" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I31" s="11" t="str"/>
       <x:c r="J31" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；82集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3269,29 +3730,29 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>同事蹭了我三个月顺风车，把我当免费司机</x:v>
+        <x:v>一塘清水鉴人心</x:v>
       </x:c>
       <x:c r="C32" s="11" t="str">
-        <x:v>08-19 06:00</x:v>
+        <x:v>08-11 17:06</x:v>
       </x:c>
       <x:c r="D32" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-15</x:v>
       </x:c>
       <x:c r="G32" s="10" t="n">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H32" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I32" s="11" t="str"/>
       <x:c r="J32" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；经典3D制作；56集长剧集；题材契合爆款主线（现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -3299,29 +3760,29 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>激活美食治愈系统,我靠摆摊火遍了整座城市</x:v>
+        <x:v>寒庭有犬鸣</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>08-14 17:00</x:v>
+        <x:v>08-12 19:43</x:v>
       </x:c>
       <x:c r="D33" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>2026-08-29</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="G33" s="10" t="n">
-        <x:v>177</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H33" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I33" s="11" t="str"/>
       <x:c r="J33" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；经典3D制作；177集长剧集；题材契合爆款主线（都市职场 / 美食治愈 / 战神异能）；回落时间短、热度余温仍在</x:v>
+        <x:v>8-16~8-22两周期内上榜5次、累计5次，起量能力已被验证；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -3329,29 +3790,29 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>离婚那天我多了个董事长妈妈</x:v>
+        <x:v>我妈装穷来认我</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>07-24 00:06</x:v>
+        <x:v>08-14 10:00</x:v>
       </x:c>
       <x:c r="D34" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F34" s="11" t="str">
-        <x:v>2026-08-19</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="G34" s="10" t="n">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H34" s="11" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I34" s="11" t="str"/>
       <x:c r="J34" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；60集长剧集；题材契合爆款主线（家庭伦理 / 婚姻情感 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计9次，起量能力已被验证；经典3D制作；54集长剧集；题材契合爆款主线（家庭伦理 / 现实反转）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -3359,29 +3820,29 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>寒途微光</x:v>
+        <x:v>天生怪力女主，被傅家捧在心尖</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>07-25 10:00</x:v>
+        <x:v>08-12 15:35</x:v>
       </x:c>
       <x:c r="D35" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F35" s="11" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-08-21</x:v>
       </x:c>
       <x:c r="G35" s="10" t="n">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H35" s="11" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I35" s="11" t="str"/>
       <x:c r="J35" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计8次，起量能力已被验证；经典3D制作；50集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -3389,29 +3850,29 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>撞大运后我在县城买了个院，开启悠哉人生</x:v>
+        <x:v>八零之老妈在厂长家当后妈</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>08-15 12:00</x:v>
+        <x:v>08-14 09:08</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F36" s="11" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="G36" s="10" t="n">
-        <x:v>95</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H36" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I36" s="11" t="str"/>
       <x:c r="J36" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；经典3D制作；95集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计7次，起量能力已被验证；156集长剧集；题材契合爆款主线（年代怀旧 / 家庭伦理）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3419,29 +3880,29 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>一辆旧中巴奔向新生活</x:v>
+        <x:v>守着灶台，守住本心</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>08-14 15:00</x:v>
+        <x:v>06-18 16:16</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F37" s="11" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="G37" s="10" t="n">
-        <x:v>82</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H37" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I37" s="11" t="str"/>
       <x:c r="J37" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；82集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计7次，起量能力已被验证；仿真人制作；52集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3449,29 +3910,29 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>不朽仙秦！</x:v>
+        <x:v>傅总，您的三岁小债主上门了</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>08-18 18:06</x:v>
+        <x:v>07-23 00:06</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F38" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="G38" s="10" t="n">
-        <x:v>200</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H38" s="11" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I38" s="11" t="str"/>
       <x:c r="J38" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；200集长剧集；题材契合爆款主线（古装宫廷 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；仿真人制作；97集长剧集；题材契合爆款主线（萌宝治愈）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3479,29 +3940,29 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>烈焰护送：无人区突围</x:v>
+        <x:v>傻女重生记，睁眼后盖房发家</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>07-17 09:58</x:v>
+        <x:v>07-10 17:00</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F39" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-23</x:v>
       </x:c>
       <x:c r="G39" s="10" t="n">
-        <x:v>49</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H39" s="11" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I39" s="11" t="str"/>
       <x:c r="J39" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；102集长剧集；题材契合爆款主线（逆袭打脸 / 现实反转）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3509,31 +3970,29 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>被休流放，我靠赶海养出战神</x:v>
+        <x:v>撞大运后我在县城买了个院</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>08-11 10:00</x:v>
+        <x:v>08-13 10:00</x:v>
       </x:c>
       <x:c r="D40" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F40" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="G40" s="10" t="n">
-        <x:v>62</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H40" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="I40" s="11" t="n">
-        <x:v>57</x:v>
-      </x:c>
+      <x:c r="I40" s="11" t="str"/>
       <x:c r="J40" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；62集长剧集；题材契合爆款主线（种田囤货 / 战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计6次，起量能力已被验证；120集长剧集；题材契合爆款主线（年代怀旧）；回落时间短、热度余温仍在</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3541,29 +4000,329 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>锦鲤知恨</x:v>
+        <x:v>八零媳妇富农家</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>08-04 11:00</x:v>
+        <x:v>07-25 19:59</x:v>
       </x:c>
       <x:c r="D41" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F41" s="11" t="str">
-        <x:v>2026-08-22</x:v>
+        <x:v>2026-08-18</x:v>
       </x:c>
       <x:c r="G41" s="10" t="n">
-        <x:v>45</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H41" s="11" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I41" s="11" t="str"/>
       <x:c r="J41" s="10" t="str">
-        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；105集长剧集；题材契合爆款主线（年代怀旧）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="11" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="10" t="str">
+        <x:v>半熟沦陷</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="str">
+        <x:v>08-08 11:00</x:v>
+      </x:c>
+      <x:c r="D42" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E42" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="G42" s="10" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H42" s="11" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I42" s="11" t="str"/>
+      <x:c r="J42" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；68集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="10" t="str">
+        <x:v>小火归山</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>08-05 10:29</x:v>
+      </x:c>
+      <x:c r="D43" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E43" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F43" s="11" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="G43" s="10" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H43" s="11" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I43" s="11" t="str"/>
+      <x:c r="J43" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；50集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="11" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="10" t="str">
+        <x:v>恶妇翻身一锅烟火养全家第一季</x:v>
+      </x:c>
+      <x:c r="C44" s="11" t="str">
+        <x:v>08-07 09:00</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E44" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F44" s="11" t="str">
+        <x:v>2026-08-15</x:v>
+      </x:c>
+      <x:c r="G44" s="10" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H44" s="11" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I44" s="11" t="str"/>
+      <x:c r="J44" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；174集长剧集；题材契合爆款主线（逆袭打脸）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="11" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="10" t="str">
+        <x:v>我家成了别人的婚房</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>08-11 10:00</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E45" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>2026-08-18</x:v>
+      </x:c>
+      <x:c r="G45" s="10" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H45" s="11" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I45" s="11" t="str"/>
+      <x:c r="J45" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；71集长剧集；题材契合爆款主线（婚姻情感）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="10" t="str">
+        <x:v>我的订婚宴上，闯进来两个要饭的</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="str">
+        <x:v>07-16 18:00</x:v>
+      </x:c>
+      <x:c r="D46" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E46" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="G46" s="10" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H46" s="11" t="str">
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="I46" s="11" t="str"/>
+      <x:c r="J46" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；仿真人制作；66集长剧集；题材契合爆款主线（婚姻情感 / 美食治愈）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="11" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" s="10" t="str">
+        <x:v>青礁潮起，鲛人归</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>07-18 18:12</x:v>
+      </x:c>
+      <x:c r="D47" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E47" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="G47" s="10" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H47" s="11" t="str">
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="I47" s="11" t="str"/>
+      <x:c r="J47" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计5次，起量能力已被验证；51集长剧集；题材契合爆款主线（战神异能）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="11" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" s="10" t="str">
+        <x:v>别人养鱼，我养水</x:v>
+      </x:c>
+      <x:c r="C48" s="11" t="str">
+        <x:v>07-02 10:28</x:v>
+      </x:c>
+      <x:c r="D48" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E48" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="str">
+        <x:v>2026-08-15</x:v>
+      </x:c>
+      <x:c r="G48" s="10" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H48" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I48" s="11" t="str"/>
+      <x:c r="J48" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；62集长剧集；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="11" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" s="10" t="str">
+        <x:v>我的车间不养闲人</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="str">
+        <x:v>06-10 14:30</x:v>
+      </x:c>
+      <x:c r="D49" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E49" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="G49" s="10" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H49" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I49" s="11" t="str"/>
+      <x:c r="J49" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；52集长剧集；题材契合爆款主线（都市职场）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="11" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B50" s="10" t="str">
+        <x:v>携手八零，与君同赴山河</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="str">
+        <x:v>08-13 12:57</x:v>
+      </x:c>
+      <x:c r="D50" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E50" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F50" s="11" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="G50" s="10" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H50" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I50" s="11" t="str"/>
+      <x:c r="J50" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；124集长剧集；题材契合爆款主线（年代怀旧 / 古装宫廷）；热度已回落，进入约两周的复投窗口期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B51" s="10" t="str">
+        <x:v>灵泉姑娘，分家后富甲一方第一季</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="str">
+        <x:v>08-11 04:00</x:v>
+      </x:c>
+      <x:c r="D51" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E51" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F51" s="11" t="str">
+        <x:v>2026-08-15</x:v>
+      </x:c>
+      <x:c r="G51" s="10" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H51" s="11" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="I51" s="11" t="str"/>
+      <x:c r="J51" s="10" t="str">
+        <x:v>8-16~8-22两周期内上榜4次、累计4次，起量能力已被验证；经典3D制作；152集长剧集；题材契合爆款主线（种田囤货）；热度已回落，进入约两周的复投窗口期</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10651,10 +11410,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>387</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>43.0%</x:v>
+        <x:v>42.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10662,7 +11421,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>278</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>30.9%</x:v>
@@ -10673,10 +11432,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>235</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>26.1%</x:v>
+        <x:v>26.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -10700,10 +11459,10 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>12.5%</x:v>
+        <x:v>12.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -10711,10 +11470,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>386</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>43.1%</x:v>
+        <x:v>43.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -10722,10 +11481,10 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>11%</x:v>
+        <x:v>11.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -10733,10 +11492,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>298</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33.3%</x:v>
+        <x:v>33%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -10760,10 +11519,10 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>358</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>39.8%</x:v>
+        <x:v>40.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -10771,10 +11530,10 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
-        <x:v>18.7%</x:v>
+        <x:v>18.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -10785,7 +11544,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>10.8%</x:v>
+        <x:v>10.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -10793,10 +11552,10 @@
         <x:v>年代怀旧/种田囤货</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>10.1%</x:v>
+        <x:v>9.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -10804,10 +11563,10 @@
         <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>8.8%</x:v>
+        <x:v>8.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -10818,7 +11577,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>8.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -10826,10 +11585,10 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>6.8%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -10837,10 +11596,10 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>6.4%</x:v>
+        <x:v>6.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -10848,10 +11607,10 @@
         <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>5.1%</x:v>
+        <x:v>5.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -10859,7 +11618,7 @@
         <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
         <x:v>5.0%</x:v>
@@ -10883,7 +11642,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>上榜21次</x:v>
+        <x:v>上榜22次</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
         <x:v>1</x:v>
@@ -10897,10 +11656,10 @@
         <x:v>上榜20次</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C30" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -10908,15 +11667,15 @@
         <x:v>上榜19次</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="11" t="str">
-        <x:v>0.2%</x:v>
+        <x:v>0.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10" t="str">
-        <x:v>上榜17次</x:v>
+        <x:v>上榜18次</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
         <x:v>1</x:v>
@@ -10927,306 +11686,306 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>上榜15次</x:v>
+        <x:v>上榜16次</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C33" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>上榜14次</x:v>
+        <x:v>上榜15次</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
-        <x:v>0.1%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>上榜13次</x:v>
+        <x:v>上榜14次</x:v>
       </x:c>
       <x:c r="B35" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>上榜12次</x:v>
+        <x:v>上榜13次</x:v>
       </x:c>
       <x:c r="B36" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.3%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>上榜11次</x:v>
+        <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>1.0%</x:v>
+        <x:v>0.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>上榜10次</x:v>
+        <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>上榜9次</x:v>
+        <x:v>上榜10次</x:v>
       </x:c>
       <x:c r="B39" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>1.4%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>上榜8次</x:v>
+        <x:v>上榜9次</x:v>
       </x:c>
       <x:c r="B40" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C40" s="11" t="str">
-        <x:v>1.9%</x:v>
+        <x:v>1.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>上榜7次</x:v>
+        <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>2.2%</x:v>
+        <x:v>1.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>上榜6次</x:v>
+        <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>4.3%</x:v>
+        <x:v>2.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>上榜5次</x:v>
+        <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
         <x:v>38</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
-        <x:v>4.2%</x:v>
+        <x:v>4.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>上榜4次</x:v>
+        <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>5.3%</x:v>
+        <x:v>4.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>上榜3次</x:v>
+        <x:v>上榜4次</x:v>
       </x:c>
       <x:c r="B45" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C45" s="11" t="str">
-        <x:v>8.8%</x:v>
+        <x:v>4.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>上榜2次</x:v>
+        <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>157</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>17.4%</x:v>
+        <x:v>8.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
+        <x:v>上榜2次</x:v>
+      </x:c>
+      <x:c r="B47" s="11" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>18.9%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="10" t="str">
         <x:v>上榜1次</x:v>
       </x:c>
-      <x:c r="B47" s="11" t="n">
-        <x:v>452</x:v>
-      </x:c>
-      <x:c r="C47" s="11" t="str">
-        <x:v>50.2%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="22" customHeight="1">
-      <x:c r="A49" s="14" t="str">
+      <x:c r="B48" s="11" t="n">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C48" s="11" t="str">
+        <x:v>49.2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="14" t="str">
         <x:v>版权类型分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="24" customHeight="1">
-      <x:c r="A50" s="5" t="str">
+    <x:row r="51" ht="24" customHeight="1">
+      <x:c r="A51" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B50" t="str">
+      <x:c r="B51" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C50" t="str">
+      <x:c r="C51" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="10" t="str">
-        <x:v>CP自营</x:v>
-      </x:c>
-      <x:c r="B51" s="11" t="n">
-        <x:v>888</x:v>
-      </x:c>
-      <x:c r="C51" s="11" t="str">
-        <x:v>98.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>98.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>CP托管</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
+        <x:v>CP托管</x:v>
+      </x:c>
+      <x:c r="B54" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C54" s="11" t="str">
+        <x:v>0.6%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="10" t="str">
         <x:v>番茄原创</x:v>
       </x:c>
-      <x:c r="B54" s="11" t="n">
+      <x:c r="B55" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C54" s="11" t="str">
+      <x:c r="C55" s="11" t="str">
         <x:v>0.2%</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="22" customHeight="1">
-      <x:c r="A56" s="14" t="str">
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜次数</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="24" customHeight="1">
-      <x:c r="A57" s="5" t="str">
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B57" t="str">
+      <x:c r="B58" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C57" t="str">
+      <x:c r="C58" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
-      </x:c>
-      <x:c r="B58" s="11" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C58" s="11" t="str">
-        <x:v>1.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B59" s="11" t="n">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C59" s="11" t="str">
-        <x:v>1.2%</x:v>
+        <x:v>1.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B60" s="11" t="n">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C60" s="11" t="str">
-        <x:v>1%</x:v>
+        <x:v>1.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B61" s="11" t="n">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C61" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>1%</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="10" t="str">
-        <x:v>茉冉漫影</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B62" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C62" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>茉冉漫影</x:v>
       </x:c>
       <x:c r="B63" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C63" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11234,10 +11993,10 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B64" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C64" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11245,10 +12004,10 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="10" t="str">
-        <x:v>咕咚剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B65" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C65" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11256,7 +12015,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="10" t="str">
-        <x:v>左手良画</x:v>
+        <x:v>咕咚剧场</x:v>
       </x:c>
       <x:c r="B66" s="11" t="n">
         <x:v>20</x:v>
@@ -11267,7 +12026,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="10" t="str">
-        <x:v>东山啊</x:v>
+        <x:v>一样漫剧</x:v>
       </x:c>
       <x:c r="B67" s="11" t="n">
         <x:v>20</x:v>
@@ -11278,10 +12037,10 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="10" t="str">
-        <x:v>一样漫剧</x:v>
+        <x:v>左手良画</x:v>
       </x:c>
       <x:c r="B68" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11289,10 +12048,10 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="10" t="str">
-        <x:v>一张不够花</x:v>
+        <x:v>东山啊</x:v>
       </x:c>
       <x:c r="B69" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C69" s="11" t="str">
         <x:v>0.8%</x:v>
@@ -11300,10 +12059,10 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>一张不够花</x:v>
       </x:c>
       <x:c r="B70" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C70" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -11314,7 +12073,7 @@
         <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="B71" s="11" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C71" s="11" t="str">
         <x:v>0.7%</x:v>
@@ -11322,100 +12081,100 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="10" t="str">
-        <x:v>星漫剧场</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B72" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C72" s="11" t="str">
-        <x:v>0.6%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="22" customHeight="1">
-      <x:c r="A74" s="14" t="str">
+        <x:v>0.7%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="10" t="str">
+        <x:v>每日沙雕速递</x:v>
+      </x:c>
+      <x:c r="B73" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C73" s="11" t="str">
+        <x:v>0.7%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="14" t="str">
         <x:v>发布抖音号TOP15·上榜剧数</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="24" customHeight="1">
-      <x:c r="A75" s="5" t="str">
+    <x:row r="76" ht="24" customHeight="1">
+      <x:c r="A76" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B75" t="str">
+      <x:c r="B76" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C75" t="str">
+      <x:c r="C76" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
-      </x:c>
-      <x:c r="B76" s="11" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C76" s="11" t="str">
-        <x:v>1.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="10" t="str">
-        <x:v>孤灵剧场</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="B77" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C77" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>1.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="10" t="str">
-        <x:v>番荔枝剧场</x:v>
+        <x:v>孤灵剧场</x:v>
       </x:c>
       <x:c r="B78" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C78" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="B79" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C79" s="11" t="str">
-        <x:v>0.6%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="10" t="str">
-        <x:v>渲渲动画</x:v>
+        <x:v>番荔枝剧场</x:v>
       </x:c>
       <x:c r="B80" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C80" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="B81" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C81" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>渲渲动画</x:v>
       </x:c>
       <x:c r="B82" s="11" t="n">
         <x:v>4</x:v>
@@ -11426,7 +12185,7 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="10" t="str">
-        <x:v>西瑶短剧</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="B83" s="11" t="n">
         <x:v>4</x:v>
@@ -11437,7 +12196,7 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="10" t="str">
-        <x:v>屿风漫剧</x:v>
+        <x:v>西瑶短剧</x:v>
       </x:c>
       <x:c r="B84" s="11" t="n">
         <x:v>4</x:v>
@@ -11448,7 +12207,7 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="10" t="str">
-        <x:v>不兜</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="B85" s="11" t="n">
         <x:v>4</x:v>
@@ -11459,7 +12218,7 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="10" t="str">
-        <x:v>喵喵说书</x:v>
+        <x:v>不兜</x:v>
       </x:c>
       <x:c r="B86" s="11" t="n">
         <x:v>4</x:v>
@@ -11470,7 +12229,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>喵喵说书</x:v>
       </x:c>
       <x:c r="B87" s="11" t="n">
         <x:v>4</x:v>
@@ -11481,7 +12240,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="10" t="str">
-        <x:v>取瘾书屋</x:v>
+        <x:v>星屿漫剧场</x:v>
       </x:c>
       <x:c r="B88" s="11" t="n">
         <x:v>4</x:v>
@@ -11492,7 +12251,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="10" t="str">
-        <x:v>清风短剧场</x:v>
+        <x:v>小小动画</x:v>
       </x:c>
       <x:c r="B89" s="11" t="n">
         <x:v>4</x:v>
@@ -11503,7 +12262,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="10" t="str">
-        <x:v>亦辰动漫</x:v>
+        <x:v>取瘾书屋</x:v>
       </x:c>
       <x:c r="B90" s="11" t="n">
         <x:v>4</x:v>
@@ -11512,91 +12271,91 @@
         <x:v>0.4%</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="22" customHeight="1">
-      <x:c r="A92" s="14" t="str">
+    <x:row r="91">
+      <x:c r="A91" s="10" t="str">
+        <x:v>清风短剧场</x:v>
+      </x:c>
+      <x:c r="B91" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C91" s="11" t="str">
+        <x:v>0.4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="14" t="str">
         <x:v>付费榜主题分布</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="24" customHeight="1">
-      <x:c r="A93" s="5" t="str">
+    <x:row r="94" ht="24" customHeight="1">
+      <x:c r="A94" s="5" t="str">
         <x:v>项目</x:v>
       </x:c>
-      <x:c r="B93" t="str">
+      <x:c r="B94" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="C93" t="str">
+      <x:c r="C94" t="str">
         <x:v>占比</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94">
-      <x:c r="A94" s="10" t="str">
-        <x:v>婚姻/情感</x:v>
-      </x:c>
-      <x:c r="B94" s="11" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C94" s="11" t="str">
-        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="10" t="str">
-        <x:v>家庭伦理/萌宝</x:v>
+        <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B95" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C95" s="11" t="str">
-        <x:v>15.0%</x:v>
+        <x:v>19.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>家庭伦理/萌宝</x:v>
       </x:c>
       <x:c r="B96" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C96" s="11" t="str">
-        <x:v>10.0%</x:v>
+        <x:v>15.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="B97" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C97" s="11" t="str">
-        <x:v>9.0%</x:v>
+        <x:v>10.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="10" t="str">
-        <x:v>年代怀旧/种田</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B98" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C98" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="10" t="str">
-        <x:v>现实反转/人性</x:v>
+        <x:v>年代怀旧/种田</x:v>
       </x:c>
       <x:c r="B99" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C99" s="11" t="str">
-        <x:v>6.0%</x:v>
+        <x:v>7.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="10" t="str">
-        <x:v>战神/异能</x:v>
+        <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B100" s="11" t="n">
         <x:v>6</x:v>
@@ -11607,12 +12366,23 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="10" t="str">
+        <x:v>战神/异能</x:v>
+      </x:c>
+      <x:c r="B101" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C101" s="11" t="str">
+        <x:v>6.0%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="10" t="str">
         <x:v>美食治愈</x:v>
       </x:c>
-      <x:c r="B101" s="11" t="n">
+      <x:c r="B102" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C101" s="11" t="str">
+      <x:c r="C102" s="11" t="str">
         <x:v>5.0%</x:v>
       </x:c>
     </x:row>
@@ -11622,10 +12392,10 @@
     <x:mergeCell ref="A7:C7"/>
     <x:mergeCell ref="A14:C14"/>
     <x:mergeCell ref="A27:C27"/>
-    <x:mergeCell ref="A49:C49"/>
-    <x:mergeCell ref="A56:C56"/>
-    <x:mergeCell ref="A74:C74"/>
-    <x:mergeCell ref="A92:C92"/>
+    <x:mergeCell ref="A50:C50"/>
+    <x:mergeCell ref="A57:C57"/>
+    <x:mergeCell ref="A75:C75"/>
+    <x:mergeCell ref="A93:C93"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R344b4674295c4beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R37c494d6aa794bcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rb87fd09badde4265"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R3e3e45043e7b4fe0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R00bfd88128db4aac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R9f7eef375b5147e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R28365ebbd9cd4486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R3b4902140bd1403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R5b31a9957d804232"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R2260025e0d134ae8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="Rf55baa58498c43e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R47b3b8c3f04b4cd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7284,28 +7284,26 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
-        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
+        <x:v>枯骨重生：我靠灵种逆修仙</x:v>
       </x:c>
       <x:c r="D96" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E96" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F96" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G96" s="10" t="str">
-        <x:v>AI便利店</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G96" s="10" t="str"/>
       <x:c r="H96" s="10" t="str">
-        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
+        <x:v>重生归来，叶长生携前世炼丹秘术蛰伏云渺宗。为报恩越级斩杀作恶同门，身陷死罪时被丹院秦无越破格保全，判三年流放域外。携苏千荷所赠天阶短剑踏入壶镇、云山城，借重生经验看破黑市暴利，以废丹炼宝变废为宝。途中救下百草阁顾清棠，破黑牙帮暗局，揪内鬼搅动风云。情义立心，智谋破局，于宗门纷争与域外黑暗中步步逆袭，开启三年崛起之路。</x:v>
       </x:c>
       <x:c r="I96" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「AI便利店」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×2</x:v>
       </x:c>
       <x:c r="J96" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -7316,10 +7314,10 @@
         <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
-        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
+        <x:v>草根逆袭成歌神</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>其他</x:v>
@@ -7328,16 +7326,16 @@
         <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G97" s="10" t="str">
-        <x:v>饭饭剧场</x:v>
+        <x:v>天桥桃花漫</x:v>
       </x:c>
       <x:c r="H97" s="10" t="str">
-        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
+        <x:v>八十年代工厂保安郭亮惨遭未婚妻张媚与陆海潮谋害，濒死重生回到婚礼当日。他当众退婚，迎娶暗恋自己的顾小薇，依靠前世记忆手握海量金曲闯荡乐坛。一路对抗对手的构陷打压，冲破抄袭诬陷、赛场黑幕等重重危机。顾小薇遭人暗算变成植物人，郭亮设局揪出真凶将仇人绳之以法。最终爱人苏醒，郭亮凭才华蜕变为一代传奇音乐人。</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「饭饭剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；99集，主力长度；发布账号「天桥桃花漫」</x:v>
       </x:c>
       <x:c r="J97" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -7345,31 +7343,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>09-05 09:00</x:v>
+        <x:v>09-05 17:19</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
+        <x:v>金牌读心护工</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>家庭伦理 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
+        <x:v>猜你们想看</x:v>
       </x:c>
       <x:c r="H98" s="10" t="str">
-        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
+        <x:v>前幼师苏澄为生计转行护工，意外获得读心技能，能听见失语老人的真实心声。在她尽心尽职的捍卫下，最终，她不仅帮老人守住尊严与财产，更用温柔与正直赢得信赖，从底层护工逆袭为被大佬团宠的金牌顾问。温暖治愈，诠释善良与担当的力量。</x:v>
       </x:c>
       <x:c r="I98" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「猜你们想看」</x:v>
       </x:c>
       <x:c r="J98" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -7377,31 +7375,31 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 01:32</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>三年，我不装了</x:v>
+        <x:v>远远儿童之重生婴儿</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E99" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>布噜布噜剧场</x:v>
+        <x:v>尧远漫漫</x:v>
       </x:c>
       <x:c r="H99" s="10" t="str">
-        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+        <x:v>重生回2005年，言秋发现自己变成了一个连翻身都费劲的婴儿。更离谱的是，隔壁床那个皱巴巴的小青梅，居然在发育速度上全方位碾压他这个重生者--她翻身比他快，独坐比他久，走路比他早，好在他有个签到系统，每年签一次，奖励不大但实用。从“语言精通”到“过目不忘”，言秋决定低调发育，暗中守护这个将来会闪闪发光的青梅。</x:v>
       </x:c>
       <x:c r="I99" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度；发布账号「尧远漫漫」</x:v>
       </x:c>
       <x:c r="J99" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -7409,31 +7407,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
-        <x:v>09-05 00:08</x:v>
+        <x:v>09-05 14:53</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>沙县厨神</x:v>
+        <x:v>一个馒头换来的首辅夫君</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>113</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F100" s="10" t="str">
-        <x:v>美食治愈 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>新视觉漫剧心动剧场</x:v>
+        <x:v>苏栎</x:v>
       </x:c>
       <x:c r="H100" s="10" t="str">
-        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
+        <x:v>现代女精英穿越成破茅屋里的小娘子，宋知禾用半个热馒头捡了个落魄病秧子当夫君，还逼他写下“卖身契”。谁料小赘婿一路逆袭，竟金榜题名官拜内阁首辅！面对权相构陷、千金夺夫，宋知禾手握现代商道，做连锁、平国库、调巨粮解大疫，一路获封天下皇商总督与一品诰命。金銮殿上，首辅大人手捧御赐金馒头奏请天下为聘“一个馒头换一生，我只要她一人。”</x:v>
       </x:c>
       <x:c r="I100" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；51集，次优长度；发布账号「苏栎」</x:v>
       </x:c>
       <x:c r="J100" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -7441,31 +7439,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B101" s="11" t="str">
-        <x:v>09-05 00:07</x:v>
+        <x:v>09-05 07:27</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>九零绝境潮汐系统护我</x:v>
+        <x:v>不做帝王枕边人</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>杨桃剧院</x:v>
+        <x:v>方士漫剧</x:v>
       </x:c>
       <x:c r="H101" s="10" t="str">
-        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+        <x:v>重生归来的沈知春，重回皇子分封之夜。前世她倾力抚育的三位亲子，最终辜负了她。今生三子同样重生，执着前程，对她满心戒备。沈知春放下执念，放弃出宫安稳，选择入宫自守。她善待孤苦无依的萧景澄，二人彼此扶持。面对深宫纷争与诸多误会，她挣脱宿命枷锁、坚守本心，最终与知恩笃行的萧景澄携手，奔赴坦荡自由的新生。</x:v>
       </x:c>
       <x:c r="I101" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；80集，主力长度；发布账号「方士漫剧」</x:v>
       </x:c>
       <x:c r="J101" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -7473,31 +7471,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B102" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 07:30</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>予你情深，岁岁相守</x:v>
+        <x:v>九零真千金我靠高考逆天改命</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F102" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G102" s="10" t="str">
-        <x:v>啾啾说漫</x:v>
+        <x:v>未央剧场</x:v>
       </x:c>
       <x:c r="H102" s="10" t="str">
-        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+        <x:v>乡下女孩林希从小与奶奶相依为命，最大的梦想是考上京大物理系、报效祖国。高考还有一年，生父苏志强突然找上门，将她接回苏家。然而苏家并非温暖港湾——养女苏柔柔处处算计，父母偏心冷漠，二哥冲动蛮横，唯有大哥苏承宇暗中相助。面对冒名顶替的身世真相、蓄意的刹车事故、保姆调包的惊天阴谋，林希始终冷静清醒，以高考为唯一目标，用满分的试卷、国家级物理竞赛冠军、高考状元一步步打脸所有人。</x:v>
       </x:c>
       <x:c r="I102" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；69集，主力长度；发布账号「未央剧场」</x:v>
       </x:c>
       <x:c r="J102" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -7505,31 +7503,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B103" s="11" t="str">
-        <x:v>09-05 00:06</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>仙界老祖非要当我哥</x:v>
+        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F103" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>青青漫剧</x:v>
+        <x:v>AI便利店</x:v>
       </x:c>
       <x:c r="H103" s="10" t="str">
-        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
       </x:c>
       <x:c r="I103" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「AI便利店」</x:v>
       </x:c>
       <x:c r="J103" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -7537,13 +7535,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B104" s="11" t="str">
-        <x:v>09-05 09:45</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>农家穗安：饼香满镇</x:v>
+        <x:v>假千金带领全家致富咯</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>其他</x:v>
@@ -7552,16 +7550,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>奇趣漫剧场</x:v>
+        <x:v>丫丫漫剧</x:v>
       </x:c>
       <x:c r="H104" s="10" t="str">
-        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
+        <x:v>假千金苏晚晚重生在真千金苏婉柔归门的晚宴，前世被陷害驱逐的噩梦历历在目。这一世她彻底觉醒，手撕虚伪豪门、断绝苏家关系，毅然回归清贫的原生家庭，奔赴三位低谷期的天才亲哥哥。面对村民的嘲讽、旁人的轻视，苏晚晚凭借前世记忆和超前思维，安抚自卑的哥哥们，发掘三人各自的天赋，带着一家人从零起步，试水短视频、做农家美食、搭建乡村土特产合作社。</x:v>
       </x:c>
       <x:c r="I104" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；73集，主力长度；发布账号「丫丫漫剧」</x:v>
       </x:c>
       <x:c r="J104" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -7569,31 +7567,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B105" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 02:51</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>嫡女归来，厨香撼京华</x:v>
+        <x:v>凤骨烬</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F105" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>宝可漫</x:v>
       </x:c>
       <x:c r="H105" s="10" t="str">
-        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
+        <x:v>烬羽台少主谢无烬遭心腹裴玄背叛惨死，浴火重生于宁远侯府受尽欺凌的病弱嫡女沈青鸾体内。为报两世血仇，她以病骨藏锋芒，步步设局，不仅反杀恶毒继母与庶妹、揭开生母被害真相，更与追查烬羽旧案的冷面摄政王萧砚辞强强联手。两人在诡谲朝局中寻得先帝密诏，一举扳倒权倾朝野的贺兰外戚。最终她召回旧部，誓要向伪善的裴玄讨回满门血债，上演了一场绝地反击的权谋复仇大戏。</x:v>
       </x:c>
       <x:c r="I105" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；77集，主力长度；发布账号「宝可漫」</x:v>
       </x:c>
       <x:c r="J105" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -7601,31 +7599,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B106" s="11" t="str">
-        <x:v>09-05 09:58</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>山野新婚暖光阴</x:v>
+        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>小尘剧场</x:v>
+        <x:v>饭饭剧场</x:v>
       </x:c>
       <x:c r="H106" s="10" t="str">
-        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
+        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
       </x:c>
       <x:c r="I106" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「饭饭剧场」</x:v>
       </x:c>
       <x:c r="J106" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -7633,31 +7631,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
-        <x:v>09-05 07:12</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>山间破晓路</x:v>
+        <x:v>发配充军，战神系统宁九才乱世称雄</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>127</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>牛奶剧场</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>青山村菜农王桂芳遭黑车欺压，252路司机张桂林违规接送菜农引发争议。面对黑车报复与内部排挤，二人坚守初心。在经理李建国支持下，他们克服扎胎、诬陷等阻碍，最终推动惠农专线正式落地，带领村民成立合作社，实现共同致富。</x:v>
+        <x:v>宁川本是盛京城才子，被未婚妻柳如烟伪造反诗构陷，抄家流放三千里充军黑铁城。濒死之际觉醒战神系统，获得满级箭术。抵御金帐汗国的战争中大放异彩，凭借箭术、制毒天赋立下赫赫战功，结识生死弟兄，与初云商会颜如玉产生羁绊。押送敌酋回盛京看清皇室凉薄，解救受难族人，得知柳如烟遁入羽化仙门。身陷敌国险境不断变强，等待时机复仇，图谋改变乱世格局。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>题材待验证；127集，次优长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「牛奶剧场」</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -7665,31 +7663,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 14:00</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>我的小土狗竟有大帝之姿</x:v>
+        <x:v>回京后嫁权臣，玄门嫡女震朝野</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>嘉午纪</x:v>
+        <x:v>诸云·青梅剧场</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
+        <x:v>现代守护灵传人沐幽月穿成丞相嫡女，被陆家掳走十年当续命血包，遭灭口时觉醒守护灵逃生，被权臣夜玄瑾所救。三年后她隐居山村做神医，偶遇陆家仇人，设计报复后认父回都。她身怀守护灵、手握赤血山势力，护着全家，一路清算陆家、黎家、魏太后等仇敌；同时和夜玄瑾渐生情愫，联手破阴谋，治好中蛊小皇帝，打脸一众权贵，最终所有仇人自食恶果，她与夜玄瑾相守。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；73集，主力长度；发布账号「诸云·青梅剧场」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -7697,13 +7695,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>替嫁棺妃</x:v>
+        <x:v>岁月迟来一段情</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
@@ -7712,16 +7710,16 @@
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>诗婳影视</x:v>
+        <x:v>鲸奇短剧新番</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
+        <x:v>保姆沈静娴不堪前夫纠缠，选择离婚。她结识了以护工身份相处的杨建华，二人中年相恋闪婚。这个看似平凡的护工丈夫，身上藏着不为人知的巨大马甲。杨建华暗中帮助沈静娴，直到身份被揭开。前夫与其相关人员承担了相应的后果，沈静娴摆脱内心自卑，释怀过往，与杨建华及其家人拥有了安稳幸福的晚年生活。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；69集，主力长度；发布账号「鲸奇短剧新番」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -7729,31 +7727,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 00:08</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>末世的最后一餐</x:v>
+        <x:v>弃妇带崽之我在古代开电动车逃荒</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F110" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G110" s="10" t="str">
-        <x:v>团子动漫</x:v>
+        <x:v>成都花花家剧场</x:v>
       </x:c>
       <x:c r="H110" s="10" t="str">
-        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
+        <x:v>现代女余思思车祸身亡后，意外穿越成古代被婆家踹出门的产后弃妇，绝境中她发现自己拥有随身空间——生前骑的粉色电动车及超市物资，且每日再生。她不做圣母，也懒得复仇，搜刮废弃村落的最后一口粮，把电动车塞满物资，背上女儿，骑着电动车一头扎进饥荒蔓延的乱世。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；122集，次优长度；发布账号「成都花花家剧场」</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -7764,7 +7762,7 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
+        <x:v>我是毒舌真千金之嘴炮小嫡主</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
         <x:v>80</x:v>
@@ -7775,15 +7773,17 @@
       <x:c r="F111" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="G111" s="10" t="str"/>
+      <x:c r="G111" s="10" t="str">
+        <x:v>贰拾叁楼漫剧</x:v>
+      </x:c>
       <x:c r="H111" s="10" t="str">
-        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
+        <x:v>温晚梨穿书成为原著里下场凄惨的恶毒女配，觉醒侯府真千金身份后，索性看淡纷争、随心摆烂。她初归府邸便遭假千金设计下药，危急关头，她翻墙跃至隔壁摄政王厉景珩的院落，脱口扬言要与他成婚，随即飘然离去，让清冷矜贵的厉景珩心生惦念。回归侯府后，温晚梨巧妙反击，逼假千金当众致歉，又对着父亲撒娇讨赏、灵动耍闹，轻松拿捏全府人心。摆烂通透千金邂逅高冷摄政王，一路打脸逆袭，活得肆意潇洒。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；80集，主力长度；发布账号「贰拾叁楼漫剧」</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -7791,31 +7791,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
-        <x:v>09-05 00:06</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>被赶走的保姆，竟是真夫人</x:v>
+        <x:v>挪车风波后我亮出总裁身份</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
+        <x:v>都市职场 / 现实反转</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
+        <x:v>微短剧中心</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
+        <x:v>陆氏集团继承人陆汐瑶低调归国，本欲与未婚夫沈沼完婚并接手公司，却发现代理总裁沈沼早已背叛自己，不仅挪用公款为管培生情人叶晓雨定制豪车，更纵容其在公司霸凌员工、大搞特权。从地下停车场的挪车冲突开始，陆汐瑶霸气摊牌真实身份，一边召回被排挤的骨干整顿公司，一边搜集证据以法律手段追责，最终将沈沼与叶晓雨绳之以法，肃清公司歪风，重建公平的职场秩序。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；76集，主力长度；发布账号「微短剧中心」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7826,27 +7826,667 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>新婚的羔羊</x:v>
+        <x:v>神级舅舅，培养七个天才外甥女</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="G113" s="10" t="str">
+        <x:v>糖糖动漫剧场</x:v>
+      </x:c>
+      <x:c r="H113" s="10" t="str">
+        <x:v>单身青年沈峰被姐姐“坑”来照顾七个外甥女，意外激活神级带娃系统。一个月内，七个零蛋女孩分别在语文、数学、外语、科学、音乐、美术、体育上展露天赋，从全县垫底逆袭为耀眼新星。沈峰在带娃与追梦的夹缝中，用责任与爱点亮了七个孩子的未来。</x:v>
+      </x:c>
+      <x:c r="I113" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；79集，主力长度；发布账号「糖糖动漫剧场」</x:v>
+      </x:c>
+      <x:c r="J113" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B114" s="11" t="str">
+        <x:v>09-06 00:37</x:v>
+      </x:c>
+      <x:c r="C114" s="10" t="str">
+        <x:v>阳阳正本磨豆腐</x:v>
+      </x:c>
+      <x:c r="D114" s="11" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E114" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F114" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G114" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H114" s="10" t="str">
+        <x:v>林桂香经营豆腐摊十五年，因成本上涨微调价格，遭邻居钱翠娥恶意砸摊、造谣。女儿林晓念为护母尊严，拒绝无理勒索并关店抗争。随着调查深入，当年丈夫工伤死亡的真相逐渐浮出水面，母女二人最终揭露黑幕，夺回公道，开启新生活。</x:v>
+      </x:c>
+      <x:c r="I114" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；76集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
+      </x:c>
+      <x:c r="J114" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B115" s="11" t="str">
+        <x:v>09-06 00:07</x:v>
+      </x:c>
+      <x:c r="C115" s="10" t="str">
+        <x:v>夫君假死化龙后本公主不装了</x:v>
+      </x:c>
+      <x:c r="D115" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E115" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F115" s="10" t="str">
+        <x:v>古装宫廷 / 婚姻情感 / 逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G115" s="10" t="str">
+        <x:v>长歌剧场</x:v>
+      </x:c>
+      <x:c r="H115" s="10" t="str">
+        <x:v>凤族嫡公主凤怜下凡历劫，惨遭夫君江淮清假意离世欺骗。对方飞升化龙之际，狠心终结了她的性命。一朝重生，她回到江淮清飞升前夕，特意打造精铁贴身护甲，破其裸身化龙的算计。她意外收留碰瓷白狐小白，实则是为她逆转时空的狐尊谢妄。这一世，凤怜手撕绿茶、打脸恶亲，揭穿天界冒牌真身，勇战魔域劲敌，逆袭登顶天界至尊。</x:v>
+      </x:c>
+      <x:c r="I115" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「长歌剧场」</x:v>
+      </x:c>
+      <x:c r="J115" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B116" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C116" s="10" t="str">
+        <x:v>爱意灼心，真千金她拒绝内耗</x:v>
+      </x:c>
+      <x:c r="D116" s="11" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E116" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F116" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="G113" s="10" t="str">
-        <x:v>战神漫剧</x:v>
-      </x:c>
-      <x:c r="H113" s="10" t="str">
-        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
-      </x:c>
-      <x:c r="I113" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
-      </x:c>
-      <x:c r="J113" s="11" t="n">
+      <x:c r="G116" s="10" t="str">
+        <x:v>每日沙雕推荐</x:v>
+      </x:c>
+      <x:c r="H116" s="10" t="str">
+        <x:v>真千金叶空回归，面对绿茶假千金与虚伪亲情，她拒绝内耗，靠毒舌与武力疯狂打脸整顿豪门！腹黑装残的大佬温璨与她一拍即合，订婚结盟。随着“天才画师”等神级马甲掉落，叶家人全员觉醒变妹控。看疯批千金与双面大佬强强联手，一路狂飙，爽翻全场！</x:v>
+      </x:c>
+      <x:c r="I116" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；77集，主力长度；发布账号「每日沙雕推荐」</x:v>
+      </x:c>
+      <x:c r="J116" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B117" s="11" t="str">
+        <x:v>09-06 00:25</x:v>
+      </x:c>
+      <x:c r="C117" s="10" t="str">
+        <x:v>嫡女不哑继母慌了</x:v>
+      </x:c>
+      <x:c r="D117" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E117" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F117" s="10" t="str">
+        <x:v>家庭伦理 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G117" s="10" t="str">
+        <x:v>魔力甜宠剧场</x:v>
+      </x:c>
+      <x:c r="H117" s="10" t="str">
+        <x:v>大苏嫡公主陆倾双为查母后死因，自毁声带装哑六年，受尽继母祁曼华欺凌。外邦使臣逼宫之际，她突然开口揭露阴谋，震惊朝堂。随后她步步为营，智斗奸臣崔延，救出被诬陷的舅舅顾义。为消除皇帝疑心，她主动交还兵权，在危机四伏的皇宫中独自开启复仇之路。</x:v>
+      </x:c>
+      <x:c r="I117" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；126集，次优长度；发布账号「魔力甜宠剧场」</x:v>
+      </x:c>
+      <x:c r="J117" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B118" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C118" s="10" t="str">
+        <x:v>晚来遇星辰</x:v>
+      </x:c>
+      <x:c r="D118" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E118" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F118" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G118" s="10" t="str">
+        <x:v>苞米花剧场</x:v>
+      </x:c>
+      <x:c r="H118" s="10" t="str">
+        <x:v>大学生林晚遭前男友顾言及其母亲逼退婚，绝境中却意外收到闺蜜苏倾倾转来的一亿元，从此彻底改写人生。她果断斩断旧情，在逆袭中与苏倾倾的哥哥苏辰相识相爱并闪婚。可甜蜜婚后，林晚却发现父亲当年车祸身亡竟与苏辰有关。随着神秘“双胞胎妹妹”现身，一场围绕爱情、亲情的阴谋逐渐揭开。</x:v>
+      </x:c>
+      <x:c r="I118" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；发布账号「苞米花剧场」</x:v>
+      </x:c>
+      <x:c r="J118" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B119" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C119" s="10" t="str">
+        <x:v>破屋藏空间，荒山变金山</x:v>
+      </x:c>
+      <x:c r="D119" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E119" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F119" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G119" s="10" t="str">
+        <x:v>小杰动漫</x:v>
+      </x:c>
+      <x:c r="H119" s="10" t="str">
+        <x:v>林峰意外重生回到分家断亲的这天，被刻薄母亲和自私大哥净身赶出家门，只分得一间破败茅草屋。绝境之中，他觉醒随身桃源空间，拥有灵泉沃土，洗髓强身还能催熟奇珍作物。面对家人的压榨算计、村民的冷眼嘲讽，林峰签下断亲书，携不离不弃的妻子周欣雨，靠着空间宝物打猎、卖参、培育珍稀果蔬，开荒荒山搞产业。他狠狠打脸贪婪的原生家庭，一路逆袭搞事业建庄园，在遍地荆棘的处境里，守护爱人，闯出属于自己的富贵人生。</x:v>
+      </x:c>
+      <x:c r="I119" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度；发布账号「小杰动漫」</x:v>
+      </x:c>
+      <x:c r="J119" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B120" s="11" t="str">
+        <x:v>09-06 00:06</x:v>
+      </x:c>
+      <x:c r="C120" s="10" t="str">
+        <x:v>被赶出豪门，假千金马甲捂不住了</x:v>
+      </x:c>
+      <x:c r="D120" s="11" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E120" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F120" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G120" s="10" t="str">
+        <x:v>爱跳动1号剧场</x:v>
+      </x:c>
+      <x:c r="H120" s="10" t="str">
+        <x:v>叶浅被养父母赶出家门，却意外发现亲生父母竟是首富顾家，三个哥哥更是各自领域的翘楚。叶依依在婚礼上污蔑叶浅反被当场揭穿，又暗中布局设下陷阱，逼叶浅赴约，危急瞬间未婚夫霍司衍舍身相护，废墟下两人彼此依靠。危机解除后，志一的现身开始揭开惊天秘密——叶依依身上的“气运系统”似乎专为叶浅而来，二十二年的错位人生，究竟是阴差阳错还是背后隐藏玄机。</x:v>
+      </x:c>
+      <x:c r="I120" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；56集，次优长度；发布账号「爱跳动1号剧场」</x:v>
+      </x:c>
+      <x:c r="J120" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B121" s="11" t="str">
+        <x:v>09-06 00:30</x:v>
+      </x:c>
+      <x:c r="C121" s="10" t="str">
+        <x:v>错信女配后前夫他后悔了</x:v>
+      </x:c>
+      <x:c r="D121" s="11" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E121" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F121" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G121" s="10" t="str">
+        <x:v>大河剧场</x:v>
+      </x:c>
+      <x:c r="H121" s="10" t="str">
+        <x:v>恋爱三年结婚四年，七年感情，商时序偏信他人，将她送上审判庭。顾汐冉心如死灰，无罪释放那一刻，她说，“商时序，我们离婚吧。”“你别后悔！”被偏爱的有恃无恐，他以为她只是赌气，过几天就会回来。这次他等了很久，等到她成为与自己并肩的大律师，与他对簿公堂，他才慌了。“冉冉我还爱你，求你回来。”顾汐冉微微一笑，“商先生让一让，别挡着我去当你婶。”</x:v>
+      </x:c>
+      <x:c r="I121" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；76集，主力长度；发布账号「大河剧场」</x:v>
+      </x:c>
+      <x:c r="J121" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B122" s="11" t="str">
+        <x:v>09-06 09:00</x:v>
+      </x:c>
+      <x:c r="C122" s="10" t="str">
+        <x:v>七零悍妻当家</x:v>
+      </x:c>
+      <x:c r="D122" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E122" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F122" s="10" t="str">
+        <x:v>年代怀旧 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G122" s="10" t="str">
+        <x:v>忆想动漫</x:v>
+      </x:c>
+      <x:c r="H122" s="10" t="str">
+        <x:v>现代苏念安意外穿越到七十年代，成为命运凄惨的少女。她被迫替嫁残疾陆承轩，面对窘迫家境、体弱的丈夫和三个年幼的孩子，她一改原主懦弱性格，凭借精湛医术救治陆承轩，智斗极品亲戚、顺利分家立足。她用心呵护家人、踏实经营生活，一步步治愈彼此，带领小家摆脱困境，改写全员的悲惨命运。</x:v>
+      </x:c>
+      <x:c r="I122" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；66集，主力长度；发布账号「忆想动漫」</x:v>
+      </x:c>
+      <x:c r="J122" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B123" s="11" t="str">
+        <x:v>09-06 07:16</x:v>
+      </x:c>
+      <x:c r="C123" s="10" t="str">
+        <x:v>乱世携弟妹，我自荒野建帝朝</x:v>
+      </x:c>
+      <x:c r="D123" s="11" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E123" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F123" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G123" s="10" t="str">
+        <x:v>栖林</x:v>
+      </x:c>
+      <x:c r="H123" s="10" t="str">
+        <x:v>沈沫雪意外坠入大荒灾世，开局便是满目饥馑。父兄亡故，身后是尚年幼的弟妹，前路是盗匪、饥寒与生死逃亡。她不愿只顾自保，于流离荒野收留无数挣扎求生的流民，开荒筑垒，订立规矩，把四散难民凝聚成一股力量。于乱世夹缝之中步步鏖战，抗衡豪强，平定四方。没有天降金手指，仅凭智慧与万民拥戴，从一介逃难孤女，一步步开创属于女子的宏图基业。</x:v>
+      </x:c>
+      <x:c r="I123" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；129集，次优长度；发布账号「栖林」</x:v>
+      </x:c>
+      <x:c r="J123" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B124" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C124" s="10" t="str">
+        <x:v>八零重生烧琉璃</x:v>
+      </x:c>
+      <x:c r="D124" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E124" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F124" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="G124" s="10" t="str">
+        <x:v>仙舟免费剧场</x:v>
+      </x:c>
+      <x:c r="H124" s="10" t="str">
+        <x:v>1980年，林场病秧子陆川重生，带着前世材料学知识与沈家失传琉璃古法，摆脱退婚窘境，联合烧窑师傅王大勇、护林队长李铁牛等人，克服原料匮乏、对手赵志高与孙麻子百般刁难，攻克脱蜡琉璃工艺。他不仅治好肺病，助力沈清璃父女平反，建起琉璃车间拿下国礼订单，众人携手将林场逐步发展为琉璃小镇，书写年代逆袭的励志故事。</x:v>
+      </x:c>
+      <x:c r="I124" s="10" t="str">
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；发布账号「仙舟免费剧场」</x:v>
+      </x:c>
+      <x:c r="J124" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B125" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C125" s="10" t="str">
+        <x:v>国运求生，我的技能有亿点多</x:v>
+      </x:c>
+      <x:c r="D125" s="11" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E125" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F125" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G125" s="10" t="str">
+        <x:v>锦瑟书斋</x:v>
+      </x:c>
+      <x:c r="H125" s="10" t="str">
+        <x:v>冻土末日下，国运求生游戏降临，各国选手被传送至危机四伏的荒蛮界。代表炎国参赛的苏寒意外激活神级宗师系统，任何行动都能转化为技能并不断升级。他凭借智慧与强大动手能力，狩猎采集、建造地堡、驯养猛兽，接连触发万倍物资返还。面对荒野巨兽与各国挑战，苏寒一路逆袭，为炎国夺回国运，也从普通青年成长为令世界震撼的荒野战神。</x:v>
+      </x:c>
+      <x:c r="I125" s="10" t="str">
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；132集，次优长度；发布账号「锦瑟书斋」</x:v>
+      </x:c>
+      <x:c r="J125" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B126" s="11" t="str">
+        <x:v>09-06 11:30</x:v>
+      </x:c>
+      <x:c r="C126" s="10" t="str">
+        <x:v>异世界的美食家</x:v>
+      </x:c>
+      <x:c r="D126" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E126" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F126" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="G126" s="10" t="str">
+        <x:v>禹佗剧场</x:v>
+      </x:c>
+      <x:c r="H126" s="10" t="str">
+        <x:v>现代厨师步方穿越武者横行的玄幻世界，觉醒美食家系统，开了间不起眼小店。小店菜品用料皆是灵兽、灵材，售价高昂，食用还能提升修士修为，门口有十阶神兽看门、机械助手保驾护航。从第一位食客肖小龙开始，皇子、将军、世家子弟纷纷被美食折服，步方不断解锁蛋炒饭、酒糟鱼、药膳等各色灵食，坚守小店规矩，以厨艺征服各路强者，一步步朝着玄幻世界厨神之路前行。</x:v>
+      </x:c>
+      <x:c r="I126" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「禹佗剧场」</x:v>
+      </x:c>
+      <x:c r="J126" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B127" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C127" s="10" t="str">
+        <x:v>拆迁款到账那天，我签了离婚协议</x:v>
+      </x:c>
+      <x:c r="D127" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E127" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F127" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G127" s="10" t="str">
+        <x:v>诗婳-小林看剧</x:v>
+      </x:c>
+      <x:c r="H127" s="10" t="str">
+        <x:v>高价拆迁款竟让丈夫周凯以房产证有自己名字为由，逼妻子陈念拿十万净身出户。陈念心死签字，却意外发现父母留下的房产藏着神秘契约，周凯因贪婪反而背上巨债。与此同时，失踪十年的父亲陈建军神秘现身，陈念也在青梅竹马律师赵东的陪伴下，一步步揭开父亲假死、华月集团与幕后黑手洪万山的秘密。她彻底觉醒，继承父亲的事业，逆袭成为掌控集团的商业总裁。</x:v>
+      </x:c>
+      <x:c r="I127" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；发布账号「诗婳-小林看剧」</x:v>
+      </x:c>
+      <x:c r="J127" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B128" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C128" s="10" t="str">
+        <x:v>林莽猎枭：八零狩猎餐餐吃肉</x:v>
+      </x:c>
+      <x:c r="D128" s="11" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E128" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F128" s="10" t="str">
+        <x:v>年代怀旧 / 种田囤货 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="G128" s="10" t="str">
+        <x:v>悬疑藏结局</x:v>
+      </x:c>
+      <x:c r="H128" s="10" t="str">
+        <x:v>林阳重生回到1985年东北山村，带着前世记忆觉醒狩猎系统，凭借猎物锁定与自动瞄准能力在山林中屡获奇猎，快速积累财富与人脉。他打脸贪得无厌的孙家，摆脱错缘，守护家人，与青梅竹马李小婉相知相恋，还凭借猎熊功绩当上巡山员，带领伙伴闯事业，在白山黑水间逆天改命，活成顶天立地的汉子。</x:v>
+      </x:c>
+      <x:c r="I128" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；114集，次优长度；发布账号「悬疑藏结局」</x:v>
+      </x:c>
+      <x:c r="J128" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B129" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C129" s="10" t="str">
+        <x:v>落魄千金闪婚记，领证对象是总裁</x:v>
+      </x:c>
+      <x:c r="D129" s="11" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E129" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F129" s="10" t="str">
+        <x:v>都市职场 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G129" s="10" t="str">
+        <x:v>白日梦制造局</x:v>
+      </x:c>
+      <x:c r="H129" s="10" t="str">
+        <x:v>夏念安撞破男友秦少钰与表妹夏慕晴背叛后果断分手，却又被舅舅一家逼迫替嫁豪门。为夺回母亲留下的月华集团股权，她阴差阳错与裴氏继承人裴晋廷闪婚。原本只是一场各取所需的契约婚姻，却在一次次并肩反击中逐渐变成真心。面对渣男纠缠、表妹陷害、舅舅夺产及裴家继承权争斗，夏念安不断揭开神医、黑客等隐藏身份，与裴晋廷强强联手，打脸反派、守住家业，也收获了势均力敌的爱情。</x:v>
+      </x:c>
+      <x:c r="I129" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；219集，长度需关注；发布账号「白日梦制造局」</x:v>
+      </x:c>
+      <x:c r="J129" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B130" s="11" t="str">
+        <x:v>09-06 07:00</x:v>
+      </x:c>
+      <x:c r="C130" s="10" t="str">
+        <x:v>被净身出户后我亮出身份</x:v>
+      </x:c>
+      <x:c r="D130" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E130" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F130" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G130" s="10" t="str">
+        <x:v>魔力甜宠剧场</x:v>
+      </x:c>
+      <x:c r="H130" s="10" t="str">
+        <x:v>富家千金苏晚为爱情隐去家世，说服父亲拿出两千五百万支持丈夫陆川创业。六周年纪念日，陆川携白月光温如回家提出离婚，逼她放弃婚内财产。苏晚归家后查实陆川境外重婚、私自转移夫妻财产。她拒绝对方舆论施压与和解，在慈善晚宴展露苏家千金身份。庭审证据充分，法院判陆川与温如婚姻无效，返还财产股权，苏晚夺得孩子抚养权，放下过往接手家族事业开启新生。</x:v>
+      </x:c>
+      <x:c r="I130" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；发布账号「魔力甜宠剧场」；剧名钩子×1</x:v>
+      </x:c>
+      <x:c r="J130" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B131" s="11" t="str">
+        <x:v>09-06 08:00</x:v>
+      </x:c>
+      <x:c r="C131" s="10" t="str">
+        <x:v>重生后前夫抢着娶庶妹，却不知我才是真凤命</x:v>
+      </x:c>
+      <x:c r="D131" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E131" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F131" s="10" t="str">
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G131" s="10" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
+      <x:c r="H131" s="10" t="str">
+        <x:v>沈云归携前世记忆重生。前世辅萧承璟登基反遭猜忌，含恨而终。今世他抢先娶庶妹沈若莺称天命女，她入太庙静观其变，借治水案布棋，提前备粮固堤，随太子赈灾救民。天命假象败露，萧承璟悔悟被拒。祭天大典她以水纹证其失职，萧承璟流放染疫亡。她任水务女官，太子守于身侧。重生一世，她终立于日光之下，做回自己。</x:v>
+      </x:c>
+      <x:c r="I131" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；59集，次优长度；发布账号「心动漫剧场」</x:v>
+      </x:c>
+      <x:c r="J131" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B132" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C132" s="10" t="str">
+        <x:v>影帝偷听心声:穿成萌犬爆红娱乐圈</x:v>
+      </x:c>
+      <x:c r="D132" s="11" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E132" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F132" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G132" s="10" t="str">
+        <x:v>剧燃动漫</x:v>
+      </x:c>
+      <x:c r="H132" s="10" t="str">
+        <x:v>三线女演员黎昭领奖途中遭死对头设计车祸，魂穿为流浪狗“狗蛋”，被高冷影帝沈韫收养。二人意外达成“心声互通”，黎昭化身极具人性的爆笑萌宠，随沈韫开启温馨治愈的豪门与娱乐圈生活。在沈韫的守护与偏爱下，黎昭逐渐揭开当年车祸真相并惩治恶人，同时在欢喜互动中与沈韫互生情愫，上演了一场爆笑又甜蜜的萌宠逆袭之旅。</x:v>
+      </x:c>
+      <x:c r="I132" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；110集，次优长度；发布账号「剧燃动漫」</x:v>
+      </x:c>
+      <x:c r="J132" s="11" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B133" s="11" t="str">
+        <x:v>09-06 09:30</x:v>
+      </x:c>
+      <x:c r="C133" s="10" t="str">
+        <x:v>我在天才家庭拖后腿</x:v>
+      </x:c>
+      <x:c r="D133" s="11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E133" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F133" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G133" s="10" t="str">
+        <x:v>金龙动画</x:v>
+      </x:c>
+      <x:c r="H133" s="10" t="str">
+        <x:v>出身顶尖高知家庭的短视频博主陈默，父母分别是清华物理系教授与中科院研究员，姐姐更是CERN博士后。清华物理系学霸表妹沈薇前来借住，起初带着优越感，认定陈默是家族基因的短板。在这个处处讲究严谨与科学的家里，沈薇不断经受“高能暴击”，在相处与镜头记录下卸下天才光环，学会接纳失败，读懂热爱本身的意义，陈默也用真实的短片完成对天才与普通人的重新诠释。</x:v>
+      </x:c>
+      <x:c r="I133" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；74集，主力长度；发布账号「金龙动画」</x:v>
+      </x:c>
+      <x:c r="J133" s="11" t="n">
         <x:v>6.5</x:v>
       </x:c>
     </x:row>
@@ -10777,28 +11417,26 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C95" s="10" t="str">
-        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
+        <x:v>枯骨重生：我靠灵种逆修仙</x:v>
       </x:c>
       <x:c r="D95" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E95" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F95" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G95" s="10" t="str">
-        <x:v>AI便利店</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G95" s="10" t="str"/>
       <x:c r="H95" s="10" t="str">
-        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
+        <x:v>重生归来，叶长生携前世炼丹秘术蛰伏云渺宗。为报恩越级斩杀作恶同门，身陷死罪时被丹院秦无越破格保全，判三年流放域外。携苏千荷所赠天阶短剑踏入壶镇、云山城，借重生经验看破黑市暴利，以废丹炼宝变废为宝。途中救下百草阁顾清棠，破黑牙帮暗局，揪内鬼搅动风云。情义立心，智谋破局，于宗门纷争与域外黑暗中步步逆袭，开启三年崛起之路。</x:v>
       </x:c>
       <x:c r="I95" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「AI便利店」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×2</x:v>
       </x:c>
       <x:c r="J95" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -10809,10 +11447,10 @@
         <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
-        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
+        <x:v>草根逆袭成歌神</x:v>
       </x:c>
       <x:c r="D96" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E96" s="11" t="str">
         <x:v>其他</x:v>
@@ -10821,16 +11459,16 @@
         <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G96" s="10" t="str">
-        <x:v>饭饭剧场</x:v>
+        <x:v>天桥桃花漫</x:v>
       </x:c>
       <x:c r="H96" s="10" t="str">
-        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
+        <x:v>八十年代工厂保安郭亮惨遭未婚妻张媚与陆海潮谋害，濒死重生回到婚礼当日。他当众退婚，迎娶暗恋自己的顾小薇，依靠前世记忆手握海量金曲闯荡乐坛。一路对抗对手的构陷打压，冲破抄袭诬陷、赛场黑幕等重重危机。顾小薇遭人暗算变成植物人，郭亮设局揪出真凶将仇人绳之以法。最终爱人苏醒，郭亮凭才华蜕变为一代传奇音乐人。</x:v>
       </x:c>
       <x:c r="I96" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「饭饭剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；99集，主力长度；发布账号「天桥桃花漫」</x:v>
       </x:c>
       <x:c r="J96" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -10838,31 +11476,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
-        <x:v>09-05 09:00</x:v>
+        <x:v>09-05 17:19</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
-        <x:v>被停职那天，我抱着儿子闯进董事长办公室</x:v>
+        <x:v>金牌读心护工</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F97" s="10" t="str">
-        <x:v>家庭伦理 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G97" s="10" t="str">
-        <x:v>云间漫剧-玉川</x:v>
+        <x:v>猜你们想看</x:v>
       </x:c>
       <x:c r="H97" s="10" t="str">
-        <x:v>被停职那天，设计师纪言抱着高烧儿子走进董事长办公室，全场震惊，她竟是隐婚五年的集团少夫人，孩子是董事长亲孙子！面对丈夫长期缺位、职场打压和设计成果被侵占，她不再隐忍，凭专业实力当众还原真相，院士父亲出手为她正名。最终她结束错婚、夺回抚养权与事业，升任设计中心负责人。婚姻从不是女人的归宿，独立与实力才是。</x:v>
+        <x:v>前幼师苏澄为生计转行护工，意外获得读心技能，能听见失语老人的真实心声。在她尽心尽职的捍卫下，最终，她不仅帮老人守住尊严与财产，更用温柔与正直赢得信赖，从底层护工逆袭为被大佬团宠的金牌顾问。温暖治愈，诠释善良与担当的力量。</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；83集，主力长度；发布账号「云间漫剧-玉川」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「猜你们想看」</x:v>
       </x:c>
       <x:c r="J97" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -10870,31 +11508,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 01:32</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>三年，我不装了</x:v>
+        <x:v>远远儿童之重生婴儿</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>布噜布噜剧场</x:v>
+        <x:v>尧远漫漫</x:v>
       </x:c>
       <x:c r="H98" s="10" t="str">
-        <x:v>入赘沈家三年，萧尘受尽屈辱端茶倒水、跪地擦鞋、被逼离婚，所有人都以为他是个吃软饭的废物。直到十亿投资签约宴上，身份揭穿他竟是天衡集团董事长，而那个被沈家捧上天的少董，不过是他的下属。但这场逆袭不是为了打脸。萧尘隐姓埋名，只为查清恩师徐怀远被害的真相。当沈家跪求原谅时，他最在意的却是妻子沈清晚的目光她撕碎离婚协议，选择与他并肩。从被赶出家门到回家吃饭，三年赘婿终成丈夫。</x:v>
+        <x:v>重生回2005年，言秋发现自己变成了一个连翻身都费劲的婴儿。更离谱的是，隔壁床那个皱巴巴的小青梅，居然在发育速度上全方位碾压他这个重生者--她翻身比他快，独坐比他久，走路比他早，好在他有个签到系统，每年签一次，奖励不大但实用。从“语言精通”到“过目不忘”，言秋决定低调发育，暗中守护这个将来会闪闪发光的青梅。</x:v>
       </x:c>
       <x:c r="I98" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；52集，次优长度；发布账号「布噜布噜剧场」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度；发布账号「尧远漫漫」</x:v>
       </x:c>
       <x:c r="J98" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -10902,31 +11540,31 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
-        <x:v>09-05 00:08</x:v>
+        <x:v>09-05 14:53</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>沙县厨神</x:v>
+        <x:v>一个馒头换来的首辅夫君</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
-        <x:v>113</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E99" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>美食治愈 / 战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>新视觉漫剧心动剧场</x:v>
+        <x:v>苏栎</x:v>
       </x:c>
       <x:c r="H99" s="10" t="str">
-        <x:v>大学毕业的李知白遭好友坑骗，扛下六十万巨债接手金融街一家砂县小吃，因天价菜品定价被冠上“黑店”名号。绝望之际激活了厨神系统，凭一手神级厨艺把平价小吃做出顶级滋味。从路人嫌弃到食客真香，他用一碗碗热食熨帖失意职场人，也读懂了美食的烟火温度。最终还清债务、口碑逆袭，把人人吐槽的“黑店”打造成高端美食食材市场，成长为了金融街独一份的美食传奇。</x:v>
+        <x:v>现代女精英穿越成破茅屋里的小娘子，宋知禾用半个热馒头捡了个落魄病秧子当夫君，还逼他写下“卖身契”。谁料小赘婿一路逆袭，竟金榜题名官拜内阁首辅！面对权相构陷、千金夺夫，宋知禾手握现代商道，做连锁、平国库、调巨粮解大疫，一路获封天下皇商总督与一品诰命。金銮殿上，首辅大人手捧御赐金馒头奏请天下为聘“一个馒头换一生，我只要她一人。”</x:v>
       </x:c>
       <x:c r="I99" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；113集，次优长度；发布账号「新视觉漫剧心动剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；51集，次优长度；发布账号「苏栎」</x:v>
       </x:c>
       <x:c r="J99" s="11" t="n">
-        <x:v>7.5</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -10934,31 +11572,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
-        <x:v>09-05 00:07</x:v>
+        <x:v>09-05 07:27</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>九零绝境潮汐系统护我</x:v>
+        <x:v>不做帝王枕边人</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F100" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>杨桃剧院</x:v>
+        <x:v>方士漫剧</x:v>
       </x:c>
       <x:c r="H100" s="10" t="str">
-        <x:v>九十年代初，渔村少女沈晚为护弟弟与债主抗争，意外激活潮汐情报系统，能实时获取海域渔获信息。她从赶海起步，捕获珍稀海产还清八万债务，逐步组建船队、建立加工厂，带领全村渔民共同致富，最终成为区域渔业龙头，收获事业与爱情。</x:v>
+        <x:v>重生归来的沈知春，重回皇子分封之夜。前世她倾力抚育的三位亲子，最终辜负了她。今生三子同样重生，执着前程，对她满心戒备。沈知春放下执念，放弃出宫安稳，选择入宫自守。她善待孤苦无依的萧景澄，二人彼此扶持。面对深宫纷争与诸多误会，她挣脱宿命枷锁、坚守本心，最终与知恩笃行的萧景澄携手，奔赴坦荡自由的新生。</x:v>
       </x:c>
       <x:c r="I100" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「杨桃剧院」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；80集，主力长度；发布账号「方士漫剧」</x:v>
       </x:c>
       <x:c r="J100" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -10966,31 +11604,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B101" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 07:30</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>予你情深，岁岁相守</x:v>
+        <x:v>九零真千金我靠高考逆天改命</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>啾啾说漫</x:v>
+        <x:v>未央剧场</x:v>
       </x:c>
       <x:c r="H101" s="10" t="str">
-        <x:v>叛逆千金苏念夏一觉穿越到十年后，竟如愿嫁给暗恋的禁欲修行之人沈砚之，可这场婚姻只剩冷漠与算计。看清悲剧结局的她溺水重回婚礼当日，当众逃婚。一边是挣脱命运的自由人生，一边是为她逐渐破戒动心的沈砚之，她能否挣脱既定宿命，改写爱而不得的结局？</x:v>
+        <x:v>乡下女孩林希从小与奶奶相依为命，最大的梦想是考上京大物理系、报效祖国。高考还有一年，生父苏志强突然找上门，将她接回苏家。然而苏家并非温暖港湾——养女苏柔柔处处算计，父母偏心冷漠，二哥冲动蛮横，唯有大哥苏承宇暗中相助。面对冒名顶替的身世真相、蓄意的刹车事故、保姆调包的惊天阴谋，林希始终冷静清醒，以高考为唯一目标，用满分的试卷、国家级物理竞赛冠军、高考状元一步步打脸所有人。</x:v>
       </x:c>
       <x:c r="I101" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「啾啾说漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；69集，主力长度；发布账号「未央剧场」</x:v>
       </x:c>
       <x:c r="J101" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -10998,31 +11636,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B102" s="11" t="str">
-        <x:v>09-05 00:06</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>仙界老祖非要当我哥</x:v>
+        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F102" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G102" s="10" t="str">
-        <x:v>青青漫剧</x:v>
+        <x:v>AI便利店</x:v>
       </x:c>
       <x:c r="H102" s="10" t="str">
-        <x:v>修界第一人，玉华派太上老祖后池，修为深不可测，千载未逢敌手。因被魔尊戏称单身，他决心将对方视为珍宝的妹妹拐来，悉心照顾。他救下她，授以法术，精心照料，每日相伴，讲述奇闻异事，赠予奇珍异宝，自认已是完美兄长，她定会将旧事忘却。妹妹时夏心生疑窦这神色冷峻、夜夜伴她夜话的异人究竟意欲何为？兄长时冬竟已穿越至此？他此刻身在何方？这方世界又隐藏着何种玄机？她决心拨开迷雾，探寻一切真相。</x:v>
+        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
       </x:c>
       <x:c r="I102" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；61集，主力长度；发布账号「青青漫剧」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「AI便利店」</x:v>
       </x:c>
       <x:c r="J102" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -11030,13 +11668,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B103" s="11" t="str">
-        <x:v>09-05 09:45</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>农家穗安：饼香满镇</x:v>
+        <x:v>假千金带领全家致富咯</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>其他</x:v>
@@ -11045,16 +11683,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>奇趣漫剧场</x:v>
+        <x:v>丫丫漫剧</x:v>
       </x:c>
       <x:c r="H103" s="10" t="str">
-        <x:v>现代早餐铺打工的宋穗安意外穿越，成为宋家备受压榨的二房女儿。寿宴上她不甘母女受尽委屈，愤然分家，靠着一手烙饼手艺艰难求生。她顶着家族刁难、亲戚剽窃算计，守住“穗安粗粮饼”的招牌，和母亲周秀娘一起，凭双手挣得宅院与安稳生活。</x:v>
+        <x:v>假千金苏晚晚重生在真千金苏婉柔归门的晚宴，前世被陷害驱逐的噩梦历历在目。这一世她彻底觉醒，手撕虚伪豪门、断绝苏家关系，毅然回归清贫的原生家庭，奔赴三位低谷期的天才亲哥哥。面对村民的嘲讽、旁人的轻视，苏晚晚凭借前世记忆和超前思维，安抚自卑的哥哥们，发掘三人各自的天赋，带着一家人从零起步，试水短视频、做农家美食、搭建乡村土特产合作社。</x:v>
       </x:c>
       <x:c r="I103" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「奇趣漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；73集，主力长度；发布账号「丫丫漫剧」</x:v>
       </x:c>
       <x:c r="J103" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -11062,31 +11700,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B104" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 02:51</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>回乡种田，手握灵泉养全家</x:v>
+        <x:v>凤骨烬</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F104" s="10" t="str">
-        <x:v>种田囤货</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>星屿漫剧场</x:v>
+        <x:v>宝可漫</x:v>
       </x:c>
       <x:c r="H104" s="10" t="str">
-        <x:v>家破、失业、母亲癌症晚期——安南暖以为，回到团山村老家，只是陪家人熬过人生最黑的一段日子。可谁也没想到，一滴鲜血唤醒了床头那盆沉睡多年的枯木，从此，悄然改变了整个安家老宅的命运。破败的院子长出满园生机，病重的母亲重燃希望，沉寂多年的山村，也在她手中一点点苏醒。可灵泉带来的，从来不只是馈赠。秘密、因果、病痛、欲望，接踵而至。安南暖原本只想守住一个家，却一步步把老家打造成了人人向往的桃花源。</x:v>
+        <x:v>烬羽台少主谢无烬遭心腹裴玄背叛惨死，浴火重生于宁远侯府受尽欺凌的病弱嫡女沈青鸾体内。为报两世血仇，她以病骨藏锋芒，步步设局，不仅反杀恶毒继母与庶妹、揭开生母被害真相，更与追查烬羽旧案的冷面摄政王萧砚辞强强联手。两人在诡谲朝局中寻得先帝密诏，一举扳倒权倾朝野的贺兰外戚。最终她召回旧部，誓要向伪善的裴玄讨回满门血债，上演了一场绝地反击的权谋复仇大戏。</x:v>
       </x:c>
       <x:c r="I104" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；96集，主力长度；发布账号「星屿漫剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；77集，主力长度；发布账号「宝可漫」</x:v>
       </x:c>
       <x:c r="J104" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -11094,31 +11732,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B105" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>嫡女归来，厨香撼京华</x:v>
+        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F105" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>锦书映年华</x:v>
+        <x:v>饭饭剧场</x:v>
       </x:c>
       <x:c r="H105" s="10" t="str">
-        <x:v>现代猪脚饭传人楚莽意外穿越，成为大靖乡野的女屠户。一次上门送肉的机缘，她凭借身上的胎记与信物，和相府亲人相认。来到相府，楚莽不通琴棋书画，只精通祖传卤煮手艺，面对旁人的非议与试探，她用一锅鲜香的猪脚饭扭转众人看法。与苏知婉有婚约的二皇子心怀算计，布下圈套想要加害楚莽，还企图利用苏知婉达成自身图谋。楚莽与苏知婉解开过往误会，彼此信任，合力搜集证据，当众揭穿二皇子的阴谋楚莽凭借本事获得皇帝赏识。</x:v>
+        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
       </x:c>
       <x:c r="I105" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；73集，主力长度；发布账号「锦书映年华」</x:v>
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「饭饭剧场」</x:v>
       </x:c>
       <x:c r="J105" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -11126,31 +11764,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B106" s="11" t="str">
-        <x:v>09-05 09:58</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>山野新婚暖光阴</x:v>
+        <x:v>发配充军，战神系统宁九才乱世称雄</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>小尘剧场</x:v>
+        <x:v>牛奶剧场</x:v>
       </x:c>
       <x:c r="H106" s="10" t="str">
-        <x:v>秋清苒离婚当天赌气嫁给“俊傻子”林承煦，却在贫困新家获得婆婆和丈夫毫无保留的尊重。她带着母子俩做服装生意逆袭脱贫，亲手盖起小楼。前夫何启恒攀比挥霍落得人财两空，而林承煦回避亲密的背后，是家族欺凌造成的创伤。婆媳联手击退恶亲，夫妻解开多年心结，一家四口终得团圆。</x:v>
+        <x:v>宁川本是盛京城才子，被未婚妻柳如烟伪造反诗构陷，抄家流放三千里充军黑铁城。濒死之际觉醒战神系统，获得满级箭术。抵御金帐汗国的战争中大放异彩，凭借箭术、制毒天赋立下赫赫战功，结识生死弟兄，与初云商会颜如玉产生羁绊。押送敌酋回盛京看清皇室凉薄，解救受难族人，得知柳如烟遁入羽化仙门。身陷敌国险境不断变强，等待时机复仇，图谋改变乱世格局。</x:v>
       </x:c>
       <x:c r="I106" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；65集，主力长度；发布账号「小尘剧场」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「牛奶剧场」</x:v>
       </x:c>
       <x:c r="J106" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -11158,31 +11796,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
-        <x:v>09-05 07:12</x:v>
+        <x:v>09-05 14:00</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>山间破晓路</x:v>
+        <x:v>回京后嫁权臣，玄门嫡女震朝野</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>127</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>幻境大剧场</x:v>
+        <x:v>诸云·青梅剧场</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>青山村菜农王桂芳遭黑车欺压，252路司机张桂林违规接送菜农引发争议。面对黑车报复与内部排挤，二人坚守初心。在经理李建国支持下，他们克服扎胎、诬陷等阻碍，最终推动惠农专线正式落地，带领村民成立合作社，实现共同致富。</x:v>
+        <x:v>现代守护灵传人沐幽月穿成丞相嫡女，被陆家掳走十年当续命血包，遭灭口时觉醒守护灵逃生，被权臣夜玄瑾所救。三年后她隐居山村做神医，偶遇陆家仇人，设计报复后认父回都。她身怀守护灵、手握赤血山势力，护着全家，一路清算陆家、黎家、魏太后等仇敌；同时和夜玄瑾渐生情愫，联手破阴谋，治好中蛊小皇帝，打脸一众权贵，最终所有仇人自食恶果，她与夜玄瑾相守。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>题材待验证；127集，次优长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；73集，主力长度；发布账号「诸云·青梅剧场」</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -11190,31 +11828,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>我的小土狗竟有大帝之姿</x:v>
+        <x:v>岁月迟来一段情</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E108" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>嘉午纪</x:v>
+        <x:v>鲸奇短剧新番</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>社畜李穆与土狗旺财遭雷劈穿越修仙界，李穆凭现代格斗思路屡创越级胜绩一路逆袭。看似普通的旺财实为万年前渡劫失败的太虚宗仙尊秦无观，始终暗中护主。二人相认后联手平定魔道，最终李穆与江雪梧成婚，秦无观破境大乘，迎来圆满结局。</x:v>
+        <x:v>保姆沈静娴不堪前夫纠缠，选择离婚。她结识了以护工身份相处的杨建华，二人中年相恋闪婚。这个看似平凡的护工丈夫，身上藏着不为人知的巨大马甲。杨建华暗中帮助沈静娴，直到身份被揭开。前夫与其相关人员承担了相应的后果，沈静娴摆脱内心自卑，释怀过往，与杨建华及其家人拥有了安稳幸福的晚年生活。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；71集，主力长度；发布账号「嘉午纪」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；69集，主力长度；发布账号「鲸奇短剧新番」</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -11222,31 +11860,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 00:08</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>替嫁棺妃</x:v>
+        <x:v>弃妇带崽之我在古代开电动车逃荒</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F109" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>诗婳影视</x:v>
+        <x:v>成都花花家剧场</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>流浪医女梨棠被主家沈凝雪打成傻子，替其嫁入东宫为太子陪葬。棺中梨棠恢复神智，救下中毒未死的太子容昭。二人携手，一边疗伤，一边暗中追查下毒与谋反真相，复仇逆袭，最终梨棠褪去婢籍，成为太子妃，与容昭共享山河。</x:v>
+        <x:v>现代女余思思车祸身亡后，意外穿越成古代被婆家踹出门的产后弃妇，绝境中她发现自己拥有随身空间——生前骑的粉色电动车及超市物资，且每日再生。她不做圣母，也懒得复仇，搜刮废弃村落的最后一口粮，把电动车塞满物资，背上女儿，骑着电动车一头扎进饥荒蔓延的乱世。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；52集，次优长度；发布账号「诗婳影视」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；122集，次优长度；发布账号「成都花花家剧场」</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -11254,13 +11892,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>末世的最后一餐</x:v>
+        <x:v>我是毒舌真千金之嘴炮小嫡主</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
@@ -11269,16 +11907,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G110" s="10" t="str">
-        <x:v>团子动漫</x:v>
+        <x:v>贰拾叁楼漫剧</x:v>
       </x:c>
       <x:c r="H110" s="10" t="str">
-        <x:v>变异危机席卷城市，生存资源变得弥足珍贵。苏晴在上一世倾尽心力守护家人，却遭遇身边至亲的背叛，落得悲剧收场。当她带着过往的伤痛与记忆重回危机开端，这一次她不再一味付出。认清人性的复杂，守住属于自己的生存空间，在混乱的末世之中，努力为自己寻得一线生机。</x:v>
+        <x:v>温晚梨穿书成为原著里下场凄惨的恶毒女配，觉醒侯府真千金身份后，索性看淡纷争、随心摆烂。她初归府邸便遭假千金设计下药，危急关头，她翻墙跃至隔壁摄政王厉景珩的院落，脱口扬言要与他成婚，随即飘然离去，让清冷矜贵的厉景珩心生惦念。回归侯府后，温晚梨巧妙反击，逼假千金当众致歉，又对着父亲撒娇讨赏、灵动耍闹，轻松拿捏全府人心。摆烂通透千金邂逅高冷摄政王，一路打脸逆袭，活得肆意潇洒。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；70集，主力长度；发布账号「团子动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；80集，主力长度；发布账号「贰拾叁楼漫剧」</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -11289,26 +11927,28 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>穿成纨绔，我靠诗词当文圣</x:v>
+        <x:v>挪车风波后我亮出总裁身份</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="G111" s="10" t="str"/>
+        <x:v>都市职场 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G111" s="10" t="str">
+        <x:v>微短剧中心</x:v>
+      </x:c>
       <x:c r="H111" s="10" t="str">
-        <x:v>现代文科博士穿越，成大华纨绔世子江小白。父亲误会他花钱买状元，江小白洞悉功高震主的危机，打算以入赘自保。丞相诗会上，他凭传世诗作一鸣惊人，赢得才女李知微赏识，又以《师说》拜入大儒蔺奉朔门下。面对朝堂科举构陷，他金銮殿据理力争，步步拆解阴谋。临危接待北虞使团，他诗词谋略碾压对手。最终查获首辅孟修堂通敌罪证，扳倒巨奸，侯府得以晋封。可兄长战死的真相尚未完全揭开，朝堂暗流依旧涌动。</x:v>
+        <x:v>陆氏集团继承人陆汐瑶低调归国，本欲与未婚夫沈沼完婚并接手公司，却发现代理总裁沈沼早已背叛自己，不仅挪用公款为管培生情人叶晓雨定制豪车，更纵容其在公司霸凌员工、大搞特权。从地下停车场的挪车冲突开始，陆汐瑶霸气摊牌真实身份，一边召回被排挤的骨干整顿公司，一边搜集证据以法律手段追责，最终将沈沼与叶晓雨绳之以法，肃清公司歪风，重建公平的职场秩序。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；剧名钩子×1</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；76集，主力长度；发布账号「微短剧中心」</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -11316,31 +11956,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
-        <x:v>09-05 00:06</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>被赶走的保姆，竟是真夫人</x:v>
+        <x:v>神级舅舅，培养七个天才外甥女</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>家庭伦理 / 婚姻情感</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>九鲤动漫</x:v>
+        <x:v>糖糖动漫剧场</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>农村女孩唐小满考上海城211，为凑够学费到傅家当保姆，与总裁傅宴清一夜缠绵后逃跑，好友宋妍却冒名顶替成首富女主人。唐小满入设计部实习获总裁关照，宋妍人前温柔人后败光好感，眼看真相将揭、身份危机步步逼近。</x:v>
+        <x:v>单身青年沈峰被姐姐“坑”来照顾七个外甥女，意外激活神级带娃系统。一个月内，七个零蛋女孩分别在语文、数学、外语、科学、音乐、美术、体育上展露天赋，从全县垫底逆袭为耀眼新星。沈峰在带娃与追梦的夹缝中，用责任与爱点亮了七个孩子的未来。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；60集，主力长度；发布账号「九鲤动漫」</x:v>
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；79集，主力长度；发布账号「糖糖动漫剧场」</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -11348,30 +11988,670 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B113" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 11:00</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>新婚的羔羊</x:v>
+        <x:v>老祖宗显灵：我的心声全府都能听见</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G113" s="10" t="str">
+        <x:v>众乐漫剧</x:v>
+      </x:c>
+      <x:c r="H113" s="10" t="str">
+        <x:v>谢家老祖宗谢昭宁即将飞升，却被天雷劈进后代子孙体内，成了一个差点饿死的真千金！修为尽毁，只剩算命异能，更离谱的是她的心声全府都能听见！面对绿茶养女勾结皇子伪造密信、下毒手钏、构陷科考的连环杀局，谢家众人靠老祖宗心声疯狂剧透。老祖宗表面嫌弃后人愚蠢，实则嘴硬心软的心声把反派按地摩擦。当阴谋破产、养女入狱，谢家震惊发现，这丫头竟是他们苦寻十八年的亲骨肉。看着祠堂里被拜了百年的自己牌位，老祖宗傻眼了。</x:v>
+      </x:c>
+      <x:c r="I113" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；67集，主力长度；发布账号「众乐漫剧」</x:v>
+      </x:c>
+      <x:c r="J113" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B114" s="11" t="str">
+        <x:v>09-06 00:37</x:v>
+      </x:c>
+      <x:c r="C114" s="10" t="str">
+        <x:v>阳阳正本磨豆腐</x:v>
+      </x:c>
+      <x:c r="D114" s="11" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E114" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F114" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G114" s="10" t="str">
+        <x:v>幻境大剧场</x:v>
+      </x:c>
+      <x:c r="H114" s="10" t="str">
+        <x:v>林桂香经营豆腐摊十五年，因成本上涨微调价格，遭邻居钱翠娥恶意砸摊、造谣。女儿林晓念为护母尊严，拒绝无理勒索并关店抗争。随着调查深入，当年丈夫工伤死亡的真相逐渐浮出水面，母女二人最终揭露黑幕，夺回公道，开启新生活。</x:v>
+      </x:c>
+      <x:c r="I114" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；76集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
+      </x:c>
+      <x:c r="J114" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B115" s="11" t="str">
+        <x:v>09-06 00:07</x:v>
+      </x:c>
+      <x:c r="C115" s="10" t="str">
+        <x:v>夫君假死化龙后本公主不装了</x:v>
+      </x:c>
+      <x:c r="D115" s="11" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E115" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F115" s="10" t="str">
+        <x:v>古装宫廷 / 婚姻情感 / 逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G115" s="10" t="str">
+        <x:v>长歌剧场</x:v>
+      </x:c>
+      <x:c r="H115" s="10" t="str">
+        <x:v>凤族嫡公主凤怜下凡历劫，惨遭夫君江淮清假意离世欺骗。对方飞升化龙之际，狠心终结了她的性命。一朝重生，她回到江淮清飞升前夕，特意打造精铁贴身护甲，破其裸身化龙的算计。她意外收留碰瓷白狐小白，实则是为她逆转时空的狐尊谢妄。这一世，凤怜手撕绿茶、打脸恶亲，揭穿天界冒牌真身，勇战魔域劲敌，逆袭登顶天界至尊。</x:v>
+      </x:c>
+      <x:c r="I115" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「长歌剧场」</x:v>
+      </x:c>
+      <x:c r="J115" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B116" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C116" s="10" t="str">
+        <x:v>爱意灼心，真千金她拒绝内耗</x:v>
+      </x:c>
+      <x:c r="D116" s="11" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E116" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F116" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="G113" s="10" t="str">
-        <x:v>战神漫剧</x:v>
-      </x:c>
-      <x:c r="H113" s="10" t="str">
-        <x:v>普通花店店主宁芷嫁与完美丈夫靳驰寒，新婚夜饮交杯酒后离奇昏迷。婚后她频繁体虚乏力，手臂屡现隐秘针孔，察觉自己被暗中采血。她悄悄取证，惊觉丈夫为情人苏蔓图谋她的肾脏，亲生母亲也收受五百万巨款出卖她。宁芷假意顺从隐忍，联合靳家对手顾景阳深入追查，揭穿苏蔓装病侵吞家产、靳驰寒当年谋害其父等层层黑幕，集齐罪证将恶人绳之以法，挣脱任人宰割的命运，涅槃重生。</x:v>
-      </x:c>
-      <x:c r="I113" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；80集，主力长度；发布账号「战神漫剧」</x:v>
-      </x:c>
-      <x:c r="J113" s="11" t="n">
+      <x:c r="G116" s="10" t="str">
+        <x:v>每日沙雕推荐</x:v>
+      </x:c>
+      <x:c r="H116" s="10" t="str">
+        <x:v>真千金叶空回归，面对绿茶假千金与虚伪亲情，她拒绝内耗，靠毒舌与武力疯狂打脸整顿豪门！腹黑装残的大佬温璨与她一拍即合，订婚结盟。随着“天才画师”等神级马甲掉落，叶家人全员觉醒变妹控。看疯批千金与双面大佬强强联手，一路狂飙，爽翻全场！</x:v>
+      </x:c>
+      <x:c r="I116" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；77集，主力长度；发布账号「每日沙雕推荐」</x:v>
+      </x:c>
+      <x:c r="J116" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B117" s="11" t="str">
+        <x:v>09-06 00:25</x:v>
+      </x:c>
+      <x:c r="C117" s="10" t="str">
+        <x:v>嫡女不哑继母慌了</x:v>
+      </x:c>
+      <x:c r="D117" s="11" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E117" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F117" s="10" t="str">
+        <x:v>家庭伦理 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G117" s="10" t="str">
+        <x:v>魔力甜宠剧场</x:v>
+      </x:c>
+      <x:c r="H117" s="10" t="str">
+        <x:v>大苏嫡公主陆倾双为查母后死因，自毁声带装哑六年，受尽继母祁曼华欺凌。外邦使臣逼宫之际，她突然开口揭露阴谋，震惊朝堂。随后她步步为营，智斗奸臣崔延，救出被诬陷的舅舅顾义。为消除皇帝疑心，她主动交还兵权，在危机四伏的皇宫中独自开启复仇之路。</x:v>
+      </x:c>
+      <x:c r="I117" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；126集，次优长度；发布账号「魔力甜宠剧场」</x:v>
+      </x:c>
+      <x:c r="J117" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B118" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C118" s="10" t="str">
+        <x:v>晚来遇星辰</x:v>
+      </x:c>
+      <x:c r="D118" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E118" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F118" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G118" s="10" t="str">
+        <x:v>苞米花剧场</x:v>
+      </x:c>
+      <x:c r="H118" s="10" t="str">
+        <x:v>大学生林晚遭前男友顾言及其母亲逼退婚，绝境中却意外收到闺蜜苏倾倾转来的一亿元，从此彻底改写人生。她果断斩断旧情，在逆袭中与苏倾倾的哥哥苏辰相识相爱并闪婚。可甜蜜婚后，林晚却发现父亲当年车祸身亡竟与苏辰有关。随着神秘“双胞胎妹妹”现身，一场围绕爱情、亲情的阴谋逐渐揭开。</x:v>
+      </x:c>
+      <x:c r="I118" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；发布账号「苞米花剧场」</x:v>
+      </x:c>
+      <x:c r="J118" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B119" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C119" s="10" t="str">
+        <x:v>破屋藏空间，荒山变金山</x:v>
+      </x:c>
+      <x:c r="D119" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E119" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F119" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G119" s="10" t="str">
+        <x:v>小杰动漫</x:v>
+      </x:c>
+      <x:c r="H119" s="10" t="str">
+        <x:v>林峰意外重生回到分家断亲的这天，被刻薄母亲和自私大哥净身赶出家门，只分得一间破败茅草屋。绝境之中，他觉醒随身桃源空间，拥有灵泉沃土，洗髓强身还能催熟奇珍作物。面对家人的压榨算计、村民的冷眼嘲讽，林峰签下断亲书，携不离不弃的妻子周欣雨，靠着空间宝物打猎、卖参、培育珍稀果蔬，开荒荒山搞产业。他狠狠打脸贪婪的原生家庭，一路逆袭搞事业建庄园，在遍地荆棘的处境里，守护爱人，闯出属于自己的富贵人生。</x:v>
+      </x:c>
+      <x:c r="I119" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度；发布账号「小杰动漫」</x:v>
+      </x:c>
+      <x:c r="J119" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B120" s="11" t="str">
+        <x:v>09-06 00:06</x:v>
+      </x:c>
+      <x:c r="C120" s="10" t="str">
+        <x:v>被赶出豪门，假千金马甲捂不住了</x:v>
+      </x:c>
+      <x:c r="D120" s="11" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E120" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F120" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G120" s="10" t="str">
+        <x:v>爱跳动1号剧场</x:v>
+      </x:c>
+      <x:c r="H120" s="10" t="str">
+        <x:v>叶浅被养父母赶出家门，却意外发现亲生父母竟是首富顾家，三个哥哥更是各自领域的翘楚。叶依依在婚礼上污蔑叶浅反被当场揭穿，又暗中布局设下陷阱，逼叶浅赴约，危急瞬间未婚夫霍司衍舍身相护，废墟下两人彼此依靠。危机解除后，志一的现身开始揭开惊天秘密——叶依依身上的“气运系统”似乎专为叶浅而来，二十二年的错位人生，究竟是阴差阳错还是背后隐藏玄机。</x:v>
+      </x:c>
+      <x:c r="I120" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；56集，次优长度；发布账号「爱跳动1号剧场」</x:v>
+      </x:c>
+      <x:c r="J120" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B121" s="11" t="str">
+        <x:v>09-06 00:30</x:v>
+      </x:c>
+      <x:c r="C121" s="10" t="str">
+        <x:v>错信女配后前夫他后悔了</x:v>
+      </x:c>
+      <x:c r="D121" s="11" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E121" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F121" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="G121" s="10" t="str">
+        <x:v>大河剧场</x:v>
+      </x:c>
+      <x:c r="H121" s="10" t="str">
+        <x:v>恋爱三年结婚四年，七年感情，商时序偏信他人，将她送上审判庭。顾汐冉心如死灰，无罪释放那一刻，她说，“商时序，我们离婚吧。”“你别后悔！”被偏爱的有恃无恐，他以为她只是赌气，过几天就会回来。这次他等了很久，等到她成为与自己并肩的大律师，与他对簿公堂，他才慌了。“冉冉我还爱你，求你回来。”顾汐冉微微一笑，“商先生让一让，别挡着我去当你婶。”</x:v>
+      </x:c>
+      <x:c r="I121" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；76集，主力长度；发布账号「大河剧场」</x:v>
+      </x:c>
+      <x:c r="J121" s="11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B122" s="11" t="str">
+        <x:v>09-06 09:00</x:v>
+      </x:c>
+      <x:c r="C122" s="10" t="str">
+        <x:v>七零悍妻当家</x:v>
+      </x:c>
+      <x:c r="D122" s="11" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E122" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F122" s="10" t="str">
+        <x:v>年代怀旧 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G122" s="10" t="str">
+        <x:v>忆想动漫</x:v>
+      </x:c>
+      <x:c r="H122" s="10" t="str">
+        <x:v>现代苏念安意外穿越到七十年代，成为命运凄惨的少女。她被迫替嫁残疾陆承轩，面对窘迫家境、体弱的丈夫和三个年幼的孩子，她一改原主懦弱性格，凭借精湛医术救治陆承轩，智斗极品亲戚、顺利分家立足。她用心呵护家人、踏实经营生活，一步步治愈彼此，带领小家摆脱困境，改写全员的悲惨命运。</x:v>
+      </x:c>
+      <x:c r="I122" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；66集，主力长度；发布账号「忆想动漫」</x:v>
+      </x:c>
+      <x:c r="J122" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B123" s="11" t="str">
+        <x:v>09-06 07:16</x:v>
+      </x:c>
+      <x:c r="C123" s="10" t="str">
+        <x:v>乱世携弟妹，我自荒野建帝朝</x:v>
+      </x:c>
+      <x:c r="D123" s="11" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E123" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F123" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G123" s="10" t="str">
+        <x:v>栖林</x:v>
+      </x:c>
+      <x:c r="H123" s="10" t="str">
+        <x:v>沈沫雪意外坠入大荒灾世，开局便是满目饥馑。父兄亡故，身后是尚年幼的弟妹，前路是盗匪、饥寒与生死逃亡。她不愿只顾自保，于流离荒野收留无数挣扎求生的流民，开荒筑垒，订立规矩，把四散难民凝聚成一股力量。于乱世夹缝之中步步鏖战，抗衡豪强，平定四方。没有天降金手指，仅凭智慧与万民拥戴，从一介逃难孤女，一步步开创属于女子的宏图基业。</x:v>
+      </x:c>
+      <x:c r="I123" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；129集，次优长度；发布账号「栖林」</x:v>
+      </x:c>
+      <x:c r="J123" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="11" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B124" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C124" s="10" t="str">
+        <x:v>八零重生烧琉璃</x:v>
+      </x:c>
+      <x:c r="D124" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E124" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F124" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="G124" s="10" t="str">
+        <x:v>仙舟免费剧场</x:v>
+      </x:c>
+      <x:c r="H124" s="10" t="str">
+        <x:v>1980年，林场病秧子陆川重生，带着前世材料学知识与沈家失传琉璃古法，摆脱退婚窘境，联合烧窑师傅王大勇、护林队长李铁牛等人，克服原料匮乏、对手赵志高与孙麻子百般刁难，攻克脱蜡琉璃工艺。他不仅治好肺病，助力沈清璃父女平反，建起琉璃车间拿下国礼订单，众人携手将林场逐步发展为琉璃小镇，书写年代逆袭的励志故事。</x:v>
+      </x:c>
+      <x:c r="I124" s="10" t="str">
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；发布账号「仙舟免费剧场」</x:v>
+      </x:c>
+      <x:c r="J124" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="11" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B125" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C125" s="10" t="str">
+        <x:v>国运求生，我的技能有亿点多</x:v>
+      </x:c>
+      <x:c r="D125" s="11" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E125" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F125" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G125" s="10" t="str">
+        <x:v>锦瑟书斋</x:v>
+      </x:c>
+      <x:c r="H125" s="10" t="str">
+        <x:v>冻土末日下，国运求生游戏降临，各国选手被传送至危机四伏的荒蛮界。代表炎国参赛的苏寒意外激活神级宗师系统，任何行动都能转化为技能并不断升级。他凭借智慧与强大动手能力，狩猎采集、建造地堡、驯养猛兽，接连触发万倍物资返还。面对荒野巨兽与各国挑战，苏寒一路逆袭，为炎国夺回国运，也从普通青年成长为令世界震撼的荒野战神。</x:v>
+      </x:c>
+      <x:c r="I125" s="10" t="str">
+        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；132集，次优长度；发布账号「锦瑟书斋」</x:v>
+      </x:c>
+      <x:c r="J125" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B126" s="11" t="str">
+        <x:v>09-06 11:30</x:v>
+      </x:c>
+      <x:c r="C126" s="10" t="str">
+        <x:v>异世界的美食家</x:v>
+      </x:c>
+      <x:c r="D126" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E126" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F126" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="G126" s="10" t="str">
+        <x:v>禹佗剧场</x:v>
+      </x:c>
+      <x:c r="H126" s="10" t="str">
+        <x:v>现代厨师步方穿越武者横行的玄幻世界，觉醒美食家系统，开了间不起眼小店。小店菜品用料皆是灵兽、灵材，售价高昂，食用还能提升修士修为，门口有十阶神兽看门、机械助手保驾护航。从第一位食客肖小龙开始，皇子、将军、世家子弟纷纷被美食折服，步方不断解锁蛋炒饭、酒糟鱼、药膳等各色灵食，坚守小店规矩，以厨艺征服各路强者，一步步朝着玄幻世界厨神之路前行。</x:v>
+      </x:c>
+      <x:c r="I126" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「禹佗剧场」</x:v>
+      </x:c>
+      <x:c r="J126" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B127" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C127" s="10" t="str">
+        <x:v>拆迁款到账那天，我签了离婚协议</x:v>
+      </x:c>
+      <x:c r="D127" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E127" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F127" s="10" t="str">
+        <x:v>婚姻情感 / 现实反转</x:v>
+      </x:c>
+      <x:c r="G127" s="10" t="str">
+        <x:v>诗婳-小林看剧</x:v>
+      </x:c>
+      <x:c r="H127" s="10" t="str">
+        <x:v>高价拆迁款竟让丈夫周凯以房产证有自己名字为由，逼妻子陈念拿十万净身出户。陈念心死签字，却意外发现父母留下的房产藏着神秘契约，周凯因贪婪反而背上巨债。与此同时，失踪十年的父亲陈建军神秘现身，陈念也在青梅竹马律师赵东的陪伴下，一步步揭开父亲假死、华月集团与幕后黑手洪万山的秘密。她彻底觉醒，继承父亲的事业，逆袭成为掌控集团的商业总裁。</x:v>
+      </x:c>
+      <x:c r="I127" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；发布账号「诗婳-小林看剧」</x:v>
+      </x:c>
+      <x:c r="J127" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B128" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C128" s="10" t="str">
+        <x:v>林莽猎枭：八零狩猎餐餐吃肉</x:v>
+      </x:c>
+      <x:c r="D128" s="11" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E128" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F128" s="10" t="str">
+        <x:v>年代怀旧 / 种田囤货 / 美食治愈</x:v>
+      </x:c>
+      <x:c r="G128" s="10" t="str">
+        <x:v>悬疑藏结局</x:v>
+      </x:c>
+      <x:c r="H128" s="10" t="str">
+        <x:v>林阳重生回到1985年东北山村，带着前世记忆觉醒狩猎系统，凭借猎物锁定与自动瞄准能力在山林中屡获奇猎，快速积累财富与人脉。他打脸贪得无厌的孙家，摆脱错缘，守护家人，与青梅竹马李小婉相知相恋，还凭借猎熊功绩当上巡山员，带领伙伴闯事业，在白山黑水间逆天改命，活成顶天立地的汉子。</x:v>
+      </x:c>
+      <x:c r="I128" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；114集，次优长度；发布账号「悬疑藏结局」</x:v>
+      </x:c>
+      <x:c r="J128" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B129" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C129" s="10" t="str">
+        <x:v>落魄千金闪婚记，领证对象是总裁</x:v>
+      </x:c>
+      <x:c r="D129" s="11" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E129" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F129" s="10" t="str">
+        <x:v>都市职场 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G129" s="10" t="str">
+        <x:v>白日梦制造局</x:v>
+      </x:c>
+      <x:c r="H129" s="10" t="str">
+        <x:v>夏念安撞破男友秦少钰与表妹夏慕晴背叛后果断分手，却又被舅舅一家逼迫替嫁豪门。为夺回母亲留下的月华集团股权，她阴差阳错与裴氏继承人裴晋廷闪婚。原本只是一场各取所需的契约婚姻，却在一次次并肩反击中逐渐变成真心。面对渣男纠缠、表妹陷害、舅舅夺产及裴家继承权争斗，夏念安不断揭开神医、黑客等隐藏身份，与裴晋廷强强联手，打脸反派、守住家业，也收获了势均力敌的爱情。</x:v>
+      </x:c>
+      <x:c r="I129" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；219集，长度需关注；发布账号「白日梦制造局」</x:v>
+      </x:c>
+      <x:c r="J129" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="11" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B130" s="11" t="str">
+        <x:v>09-06 07:00</x:v>
+      </x:c>
+      <x:c r="C130" s="10" t="str">
+        <x:v>被净身出户后我亮出身份</x:v>
+      </x:c>
+      <x:c r="D130" s="11" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E130" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F130" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G130" s="10" t="str">
+        <x:v>魔力甜宠剧场</x:v>
+      </x:c>
+      <x:c r="H130" s="10" t="str">
+        <x:v>富家千金苏晚为爱情隐去家世，说服父亲拿出两千五百万支持丈夫陆川创业。六周年纪念日，陆川携白月光温如回家提出离婚，逼她放弃婚内财产。苏晚归家后查实陆川境外重婚、私自转移夫妻财产。她拒绝对方舆论施压与和解，在慈善晚宴展露苏家千金身份。庭审证据充分，法院判陆川与温如婚姻无效，返还财产股权，苏晚夺得孩子抚养权，放下过往接手家族事业开启新生。</x:v>
+      </x:c>
+      <x:c r="I130" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；发布账号「魔力甜宠剧场」；剧名钩子×1</x:v>
+      </x:c>
+      <x:c r="J130" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B131" s="11" t="str">
+        <x:v>09-06 08:00</x:v>
+      </x:c>
+      <x:c r="C131" s="10" t="str">
+        <x:v>重生后前夫抢着娶庶妹，却不知我才是真凤命</x:v>
+      </x:c>
+      <x:c r="D131" s="11" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E131" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F131" s="10" t="str">
+        <x:v>古装宫廷 / 婚姻情感</x:v>
+      </x:c>
+      <x:c r="G131" s="10" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
+      <x:c r="H131" s="10" t="str">
+        <x:v>沈云归携前世记忆重生。前世辅萧承璟登基反遭猜忌，含恨而终。今世他抢先娶庶妹沈若莺称天命女，她入太庙静观其变，借治水案布棋，提前备粮固堤，随太子赈灾救民。天命假象败露，萧承璟悔悟被拒。祭天大典她以水纹证其失职，萧承璟流放染疫亡。她任水务女官，太子守于身侧。重生一世，她终立于日光之下，做回自己。</x:v>
+      </x:c>
+      <x:c r="I131" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；59集，次优长度；发布账号「心动漫剧场」</x:v>
+      </x:c>
+      <x:c r="J131" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B132" s="11" t="str">
+        <x:v>09-06 10:00</x:v>
+      </x:c>
+      <x:c r="C132" s="10" t="str">
+        <x:v>影帝偷听心声:穿成萌犬爆红娱乐圈</x:v>
+      </x:c>
+      <x:c r="D132" s="11" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E132" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F132" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="G132" s="10" t="str">
+        <x:v>剧燃动漫</x:v>
+      </x:c>
+      <x:c r="H132" s="10" t="str">
+        <x:v>三线女演员黎昭领奖途中遭死对头设计车祸，魂穿为流浪狗“狗蛋”，被高冷影帝沈韫收养。二人意外达成“心声互通”，黎昭化身极具人性的爆笑萌宠，随沈韫开启温馨治愈的豪门与娱乐圈生活。在沈韫的守护与偏爱下，黎昭逐渐揭开当年车祸真相并惩治恶人，同时在欢喜互动中与沈韫互生情愫，上演了一场爆笑又甜蜜的萌宠逆袭之旅。</x:v>
+      </x:c>
+      <x:c r="I132" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；110集，次优长度；发布账号「剧燃动漫」</x:v>
+      </x:c>
+      <x:c r="J132" s="11" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B133" s="11" t="str">
+        <x:v>09-06 09:30</x:v>
+      </x:c>
+      <x:c r="C133" s="10" t="str">
+        <x:v>我在天才家庭拖后腿</x:v>
+      </x:c>
+      <x:c r="D133" s="11" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E133" s="11" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F133" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="G133" s="10" t="str">
+        <x:v>金龙动画</x:v>
+      </x:c>
+      <x:c r="H133" s="10" t="str">
+        <x:v>出身顶尖高知家庭的短视频博主陈默，父母分别是清华物理系教授与中科院研究员，姐姐更是CERN博士后。清华物理系学霸表妹沈薇前来借住，起初带着优越感，认定陈默是家族基因的短板。在这个处处讲究严谨与科学的家里，沈薇不断经受“高能暴击”，在相处与镜头记录下卸下天才光环，学会接纳失败，读懂热爱本身的意义，陈默也用真实的短片完成对天才与普通人的重新诠释。</x:v>
+      </x:c>
+      <x:c r="I133" s="10" t="str">
+        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；74集，主力长度；发布账号「金龙动画」</x:v>
+      </x:c>
+      <x:c r="J133" s="11" t="n">
         <x:v>6.5</x:v>
       </x:c>
     </x:row>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R28365ebbd9cd4486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R3b4902140bd1403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R5b31a9957d804232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R2260025e0d134ae8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="Rf55baa58498c43e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R47b3b8c3f04b4cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R00617be94309495a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R6fc82e2250734e6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rf0f49eb0e6894ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R935c7274774f4579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="Rb096208ccd7a4e55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R95a194d4abb548e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11403,10 +11403,10 @@
         <x:v>苏晚剖腹产坐月子期间，婆婆孙淑芬装病博同情，丈夫郭鹏程愚孝偏袒。苏晚因照顾假摔的婆婆导致刀口崩裂，看清真相后毅然提出离婚。在好友协助下，她搜集证据揭穿婆婆伪装，并果断结束婚姻。随后苏晚投身职场，为助爱人傅时衍化解公司危机，不惜抵押资产、签署苛刻合同筹措资金，最终在董事会力挽狂澜，收获事业与爱情。</x:v>
       </x:c>
       <x:c r="I94" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；73集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
+        <x:v>发布账号「幻境大剧场」双口径TOP12精品号，账号满分；题材契合爆款主线×3（剧名/分类/简介三路识别）；73集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J94" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -11417,26 +11417,28 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C95" s="10" t="str">
-        <x:v>枯骨重生：我靠灵种逆修仙</x:v>
+        <x:v>回乡种田，手握灵泉养全家</x:v>
       </x:c>
       <x:c r="D95" s="11" t="n">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E95" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F95" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G95" s="10" t="str"/>
+        <x:v>种田囤货</x:v>
+      </x:c>
+      <x:c r="G95" s="10" t="str">
+        <x:v>星屿漫剧场</x:v>
+      </x:c>
       <x:c r="H95" s="10" t="str">
-        <x:v>重生归来，叶长生携前世炼丹秘术蛰伏云渺宗。为报恩越级斩杀作恶同门，身陷死罪时被丹院秦无越破格保全，判三年流放域外。携苏千荷所赠天阶短剑踏入壶镇、云山城，借重生经验看破黑市暴利，以废丹炼宝变废为宝。途中救下百草阁顾清棠，破黑牙帮暗局，揪内鬼搅动风云。情义立心，智谋破局，于宗门纷争与域外黑暗中步步逆袭，开启三年崛起之路。</x:v>
+        <x:v>家破、失业、母亲癌症晚期——安南暖以为，回到团山村老家，只是陪家人熬过人生最黑的一段日子。可谁也没想到，一滴鲜血唤醒了床头那盆沉睡多年的枯木，从此，悄然改变了整个安家老宅的命运。破败的院子长出满园生机，病重的母亲重燃希望，沉寂多年的山村，也在她手中一点点苏醒。可灵泉带来的，从来不只是馈赠。秘密、因果、病痛、欲望，接踵而至。安南暖原本只想守住一个家，却一步步把老家打造成了人人向往的桃花源。</x:v>
       </x:c>
       <x:c r="I95" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×2</x:v>
+        <x:v>发布账号「星屿漫剧场」进入单口径TOP12，账号高分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；96集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J95" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -11444,31 +11446,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B96" s="11" t="str">
-        <x:v>09-05 09:00</x:v>
+        <x:v>09-05 07:12</x:v>
       </x:c>
       <x:c r="C96" s="10" t="str">
-        <x:v>草根逆袭成歌神</x:v>
+        <x:v>山间破晓路</x:v>
       </x:c>
       <x:c r="D96" s="11" t="n">
-        <x:v>99</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E96" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F96" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G96" s="10" t="str">
-        <x:v>天桥桃花漫</x:v>
+        <x:v>幻境大剧场</x:v>
       </x:c>
       <x:c r="H96" s="10" t="str">
-        <x:v>八十年代工厂保安郭亮惨遭未婚妻张媚与陆海潮谋害，濒死重生回到婚礼当日。他当众退婚，迎娶暗恋自己的顾小薇，依靠前世记忆手握海量金曲闯荡乐坛。一路对抗对手的构陷打压，冲破抄袭诬陷、赛场黑幕等重重危机。顾小薇遭人暗算变成植物人，郭亮设局揪出真凶将仇人绳之以法。最终爱人苏醒，郭亮凭才华蜕变为一代传奇音乐人。</x:v>
+        <x:v>青山村菜农王桂芳遭黑车欺压，252路司机张桂林违规接送菜农引发争议。面对黑车报复与内部排挤，二人坚守初心。在经理李建国支持下，他们克服扎胎、诬陷等阻碍，最终推动惠农专线正式落地，带领村民成立合作社，实现共同致富。</x:v>
       </x:c>
       <x:c r="I96" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；99集，主力长度；发布账号「天桥桃花漫」</x:v>
+        <x:v>发布账号「幻境大剧场」双口径TOP12精品号，账号满分；题材待验证；127集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="J96" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -11476,31 +11478,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B97" s="11" t="str">
-        <x:v>09-05 17:19</x:v>
+        <x:v>09-05 17:35</x:v>
       </x:c>
       <x:c r="C97" s="10" t="str">
-        <x:v>金牌读心护工</x:v>
+        <x:v>老宅之外，自有山河</x:v>
       </x:c>
       <x:c r="D97" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F97" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G97" s="10" t="str">
-        <x:v>猜你们想看</x:v>
+        <x:v>喵喵说书</x:v>
       </x:c>
       <x:c r="H97" s="10" t="str">
-        <x:v>前幼师苏澄为生计转行护工，意外获得读心技能，能听见失语老人的真实心声。在她尽心尽职的捍卫下，最终，她不仅帮老人守住尊严与财产，更用温柔与正直赢得信赖，从底层护工逆袭为被大佬团宠的金牌顾问。温暖治愈，诠释善良与担当的力量。</x:v>
+        <x:v>林晚棠倾尽心血将破败林家祖宅打造成网红民宿青溪旧院，生意红火后，亲戚却上门争抢经营权。她毅然交出老宅，带着团队另起炉灶开办归山茶宿。靠着用心的服务与成熟的活动运营，赢得老客信赖。老宅可以易主，但真心打磨的实力，才是立身真正的归处。</x:v>
       </x:c>
       <x:c r="I97" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；发布账号「猜你们想看」</x:v>
+        <x:v>发布账号「喵喵说书」进入单口径TOP12，账号高分；题材契合爆款主线×2（剧名/分类/简介三路识别）；63集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J97" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -11508,31 +11510,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>09-05 01:32</x:v>
+        <x:v>09-05 11:24</x:v>
       </x:c>
       <x:c r="C98" s="10" t="str">
-        <x:v>远远儿童之重生婴儿</x:v>
+        <x:v>重回1975，我家包子喂狗都不给他</x:v>
       </x:c>
       <x:c r="D98" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F98" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧 / 美食治愈</x:v>
       </x:c>
       <x:c r="G98" s="10" t="str">
-        <x:v>尧远漫漫</x:v>
+        <x:v>小野AI漫剧厂</x:v>
       </x:c>
       <x:c r="H98" s="10" t="str">
-        <x:v>重生回2005年，言秋发现自己变成了一个连翻身都费劲的婴儿。更离谱的是，隔壁床那个皱巴巴的小青梅，居然在发育速度上全方位碾压他这个重生者--她翻身比他快，独坐比他久，走路比他早，好在他有个签到系统，每年签一次，奖励不大但实用。从“语言精通”到“过目不忘”，言秋决定低调发育，暗中守护这个将来会闪闪发光的青梅。</x:v>
+        <x:v>1975年北方农村，被丈夫失手撞向灶台角的孟翠琴，一睁眼重回1975年，还没跳进那场毁了她一辈子的婚姻。前世十八年操劳，今生看着上门蹭饭的斯文知青沈耀安，她“哐当”扣死蒸笼，我家包子，喂狗都不给他。伪君子步步换梯攀高枝，她冷眼布长线，从不亲自动手，只等他自食恶果。一碗锅包肉闯进城，撞上个话少手实、递上存折的男人。重活一回，她能改写自己的命运吗？</x:v>
       </x:c>
       <x:c r="I98" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度；发布账号「尧远漫漫」</x:v>
+        <x:v>发布账号「小野AI漫剧厂」稳定产出（上榜14次/出过3部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；60集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J98" s="11" t="n">
-        <x:v>8.5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -11540,10 +11542,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
-        <x:v>09-05 14:53</x:v>
+        <x:v>09-05 14:51</x:v>
       </x:c>
       <x:c r="C99" s="10" t="str">
-        <x:v>一个馒头换来的首辅夫君</x:v>
+        <x:v>随手救个落难总裁</x:v>
       </x:c>
       <x:c r="D99" s="11" t="n">
         <x:v>51</x:v>
@@ -11552,19 +11554,19 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F99" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="G99" s="10" t="str">
-        <x:v>苏栎</x:v>
+        <x:v>小野AI漫剧厂</x:v>
       </x:c>
       <x:c r="H99" s="10" t="str">
-        <x:v>现代女精英穿越成破茅屋里的小娘子，宋知禾用半个热馒头捡了个落魄病秧子当夫君，还逼他写下“卖身契”。谁料小赘婿一路逆袭，竟金榜题名官拜内阁首辅！面对权相构陷、千金夺夫，宋知禾手握现代商道，做连锁、平国库、调巨粮解大疫，一路获封天下皇商总督与一品诰命。金銮殿上，首辅大人手捧御赐金馒头奏请天下为聘“一个馒头换一生，我只要她一人。”</x:v>
+        <x:v>隐退资本大佬顾长歌隐居渔村，偶然救下遭对手陆天恒迫害的宋氏总裁宋青舟。她出手帮助宋青舟化解商业危机，对抗恶意垄断。同时带动清湾村渔民成立合作社，谋求自主销路。二人携手搜集证据，将不法势力绳之以法。历经重重磨难，两人解开过往心结，并肩守护渔村与企业，收获双向奔赴的真挚感情，归于烟火生活。</x:v>
       </x:c>
       <x:c r="I99" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；51集，次优长度；发布账号「苏栎」</x:v>
+        <x:v>发布账号「小野AI漫剧厂」稳定产出（上榜14次/出过3部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；51集，次优长度；通用受众</x:v>
       </x:c>
       <x:c r="J99" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10.5</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -11572,31 +11574,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
-        <x:v>09-05 07:27</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C100" s="10" t="str">
-        <x:v>不做帝王枕边人</x:v>
+        <x:v>亲戚聚会他摆阔，我爸不结账了</x:v>
       </x:c>
       <x:c r="D100" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E100" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F100" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G100" s="10" t="str">
-        <x:v>方士漫剧</x:v>
+        <x:v>屿风漫剧</x:v>
       </x:c>
       <x:c r="H100" s="10" t="str">
-        <x:v>重生归来的沈知春，重回皇子分封之夜。前世她倾力抚育的三位亲子，最终辜负了她。今生三子同样重生，执着前程，对她满心戒备。沈知春放下执念，放弃出宫安稳，选择入宫自守。她善待孤苦无依的萧景澄，二人彼此扶持。面对深宫纷争与诸多误会，她挣脱宿命枷锁、坚守本心，最终与知恩笃行的萧景澄携手，奔赴坦荡自由的新生。</x:v>
+        <x:v>家族聚会上，陈国梁借哥哥陈国栋的钱买车摆阔，又多次把宴请账单推给哥哥。陈昭为保护父亲，推动聚会各自结算，并逐步揭开叔叔冒用昭源名义、组织亲友参与虚假项目的真相。身份公开后，她妥善退还款项、安排分期偿还。陈国栋学会拒绝，陈国梁放下虚荣，家族重新认识本分与担当的价值。</x:v>
       </x:c>
       <x:c r="I100" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；80集，主力长度；发布账号「方士漫剧」</x:v>
+        <x:v>发布账号「屿风漫剧」进入单口径TOP12，账号高分；题材契合爆款主线×1（剧名/分类/简介三路识别）；58集，次优长度</x:v>
       </x:c>
       <x:c r="J100" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -11604,31 +11606,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B101" s="11" t="str">
-        <x:v>09-05 07:30</x:v>
+        <x:v>09-05 17:00</x:v>
       </x:c>
       <x:c r="C101" s="10" t="str">
-        <x:v>九零真千金我靠高考逆天改命</x:v>
+        <x:v>出租车投诉风波</x:v>
       </x:c>
       <x:c r="D101" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E101" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F101" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="G101" s="10" t="str">
-        <x:v>未央剧场</x:v>
+        <x:v>燕子剧场</x:v>
       </x:c>
       <x:c r="H101" s="10" t="str">
-        <x:v>乡下女孩林希从小与奶奶相依为命，最大的梦想是考上京大物理系、报效祖国。高考还有一年，生父苏志强突然找上门，将她接回苏家。然而苏家并非温暖港湾——养女苏柔柔处处算计，父母偏心冷漠，二哥冲动蛮横，唯有大哥苏承宇暗中相助。面对冒名顶替的身世真相、蓄意的刹车事故、保姆调包的惊天阴谋，林希始终冷静清醒，以高考为唯一目标，用满分的试卷、国家级物理竞赛冠军、高考状元一步步打脸所有人。</x:v>
+        <x:v>暴雨天，何秋宜睡过头误了高铁、丢了工作，却把怒火全砸向司机许海庆，追加投诉到他账号冻结，还投诉威胁出租车公司领导要开除许海庆。许海庆为保饭碗低头认赔，却在平台写情况说明时错过了生病妻子的最后一面。后来何秋宜进了振华实业公司，发现许海庆给老板开车，又心声恶意，不仅改单做局、发黑函、剪辑录音想再次搞垮他。这一次，许海庆拿出全部证据当众清算，投诉是刀，但刀也会回旋。</x:v>
       </x:c>
       <x:c r="I101" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；69集，主力长度；发布账号「未央剧场」</x:v>
+        <x:v>发布账号「燕子剧场」稳定产出（上榜13次/出过1部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；55集，次优长度；通用受众</x:v>
       </x:c>
       <x:c r="J101" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9.5</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -11639,28 +11641,26 @@
         <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C102" s="10" t="str">
-        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
+        <x:v>枯骨重生：我靠灵种逆修仙</x:v>
       </x:c>
       <x:c r="D102" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E102" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F102" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
-      </x:c>
-      <x:c r="G102" s="10" t="str">
-        <x:v>AI便利店</x:v>
-      </x:c>
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="G102" s="10" t="str"/>
       <x:c r="H102" s="10" t="str">
-        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
+        <x:v>重生归来，叶长生携前世炼丹秘术蛰伏云渺宗。为报恩越级斩杀作恶同门，身陷死罪时被丹院秦无越破格保全，判三年流放域外。携苏千荷所赠天阶短剑踏入壶镇、云山城，借重生经验看破黑市暴利，以废丹炼宝变废为宝。途中救下百草阁顾清棠，破黑牙帮暗局，揪内鬼搅动风云。情义立心，智谋破局，于宗门纷争与域外黑暗中步步逆袭，开启三年崛起之路。</x:v>
       </x:c>
       <x:c r="I102" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「AI便利店」</x:v>
+        <x:v>无发布账号，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；70集，主力长度；剧名钩子×2</x:v>
       </x:c>
       <x:c r="J102" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -11668,31 +11668,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B103" s="11" t="str">
-        <x:v>09-05 10:30</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C103" s="10" t="str">
-        <x:v>假千金带领全家致富咯</x:v>
+        <x:v>草根逆袭成歌神</x:v>
       </x:c>
       <x:c r="D103" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E103" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F103" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G103" s="10" t="str">
-        <x:v>丫丫漫剧</x:v>
+        <x:v>天桥桃花漫</x:v>
       </x:c>
       <x:c r="H103" s="10" t="str">
-        <x:v>假千金苏晚晚重生在真千金苏婉柔归门的晚宴，前世被陷害驱逐的噩梦历历在目。这一世她彻底觉醒，手撕虚伪豪门、断绝苏家关系，毅然回归清贫的原生家庭，奔赴三位低谷期的天才亲哥哥。面对村民的嘲讽、旁人的轻视，苏晚晚凭借前世记忆和超前思维，安抚自卑的哥哥们，发掘三人各自的天赋，带着一家人从零起步，试水短视频、做农家美食、搭建乡村土特产合作社。</x:v>
+        <x:v>八十年代工厂保安郭亮惨遭未婚妻张媚与陆海潮谋害，濒死重生回到婚礼当日。他当众退婚，迎娶暗恋自己的顾小薇，依靠前世记忆手握海量金曲闯荡乐坛。一路对抗对手的构陷打压，冲破抄袭诬陷、赛场黑幕等重重危机。顾小薇遭人暗算变成植物人，郭亮设局揪出真凶将仇人绳之以法。最终爱人苏醒，郭亮凭才华蜕变为一代传奇音乐人。</x:v>
       </x:c>
       <x:c r="I103" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；73集，主力长度；发布账号「丫丫漫剧」</x:v>
+        <x:v>发布账号「天桥桃花漫」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；99集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J103" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -11700,31 +11700,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B104" s="11" t="str">
-        <x:v>09-05 02:51</x:v>
+        <x:v>09-05 17:19</x:v>
       </x:c>
       <x:c r="C104" s="10" t="str">
-        <x:v>凤骨烬</x:v>
+        <x:v>金牌读心护工</x:v>
       </x:c>
       <x:c r="D104" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E104" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F104" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G104" s="10" t="str">
-        <x:v>宝可漫</x:v>
+        <x:v>猜你们想看</x:v>
       </x:c>
       <x:c r="H104" s="10" t="str">
-        <x:v>烬羽台少主谢无烬遭心腹裴玄背叛惨死，浴火重生于宁远侯府受尽欺凌的病弱嫡女沈青鸾体内。为报两世血仇，她以病骨藏锋芒，步步设局，不仅反杀恶毒继母与庶妹、揭开生母被害真相，更与追查烬羽旧案的冷面摄政王萧砚辞强强联手。两人在诡谲朝局中寻得先帝密诏，一举扳倒权倾朝野的贺兰外戚。最终她召回旧部，誓要向伪善的裴玄讨回满门血债，上演了一场绝地反击的权谋复仇大戏。</x:v>
+        <x:v>前幼师苏澄为生计转行护工，意外获得读心技能，能听见失语老人的真实心声。在她尽心尽职的捍卫下，最终，她不仅帮老人守住尊严与财产，更用温柔与正直赢得信赖，从底层护工逆袭为被大佬团宠的金牌顾问。温暖治愈，诠释善良与担当的力量。</x:v>
       </x:c>
       <x:c r="I104" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；77集，主力长度；发布账号「宝可漫」</x:v>
+        <x:v>发布账号「猜你们想看」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；62集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J104" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -11732,31 +11732,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B105" s="11" t="str">
-        <x:v>09-05 09:00</x:v>
+        <x:v>09-05 01:32</x:v>
       </x:c>
       <x:c r="C105" s="10" t="str">
-        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
+        <x:v>远远儿童之重生婴儿</x:v>
       </x:c>
       <x:c r="D105" s="11" t="n">
-        <x:v>96</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F105" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G105" s="10" t="str">
-        <x:v>饭饭剧场</x:v>
+        <x:v>尧远漫漫</x:v>
       </x:c>
       <x:c r="H105" s="10" t="str">
-        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
+        <x:v>重生回2005年，言秋发现自己变成了一个连翻身都费劲的婴儿。更离谱的是，隔壁床那个皱巴巴的小青梅，居然在发育速度上全方位碾压他这个重生者--她翻身比他快，独坐比他久，走路比他早，好在他有个签到系统，每年签一次，奖励不大但实用。从“语言精通”到“过目不忘”，言秋决定低调发育，暗中守护这个将来会闪闪发光的青梅。</x:v>
       </x:c>
       <x:c r="I105" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；发布账号「饭饭剧场」</x:v>
+        <x:v>发布账号「尧远漫漫」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J105" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>8.5</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -11764,28 +11764,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B106" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 14:53</x:v>
       </x:c>
       <x:c r="C106" s="10" t="str">
-        <x:v>发配充军，战神系统宁九才乱世称雄</x:v>
+        <x:v>一个馒头换来的首辅夫君</x:v>
       </x:c>
       <x:c r="D106" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F106" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G106" s="10" t="str">
-        <x:v>牛奶剧场</x:v>
+        <x:v>苏栎</x:v>
       </x:c>
       <x:c r="H106" s="10" t="str">
-        <x:v>宁川本是盛京城才子，被未婚妻柳如烟伪造反诗构陷，抄家流放三千里充军黑铁城。濒死之际觉醒战神系统，获得满级箭术。抵御金帐汗国的战争中大放异彩，凭借箭术、制毒天赋立下赫赫战功，结识生死弟兄，与初云商会颜如玉产生羁绊。押送敌酋回盛京看清皇室凉薄，解救受难族人，得知柳如烟遁入羽化仙门。身陷敌国险境不断变强，等待时机复仇，图谋改变乱世格局。</x:v>
+        <x:v>现代女精英穿越成破茅屋里的小娘子，宋知禾用半个热馒头捡了个落魄病秧子当夫君，还逼他写下“卖身契”。谁料小赘婿一路逆袭，竟金榜题名官拜内阁首辅！面对权相构陷、千金夺夫，宋知禾手握现代商道，做连锁、平国库、调巨粮解大疫，一路获封天下皇商总督与一品诰命。金銮殿上，首辅大人手捧御赐金馒头奏请天下为聘“一个馒头换一生，我只要她一人。”</x:v>
       </x:c>
       <x:c r="I106" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度；发布账号「牛奶剧场」</x:v>
+        <x:v>发布账号「苏栎」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；51集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="J106" s="11" t="n">
         <x:v>8</x:v>
@@ -11796,28 +11796,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B107" s="11" t="str">
-        <x:v>09-05 14:00</x:v>
+        <x:v>09-05 07:27</x:v>
       </x:c>
       <x:c r="C107" s="10" t="str">
-        <x:v>回京后嫁权臣，玄门嫡女震朝野</x:v>
+        <x:v>不做帝王枕边人</x:v>
       </x:c>
       <x:c r="D107" s="11" t="n">
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E107" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F107" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G107" s="10" t="str">
-        <x:v>诸云·青梅剧场</x:v>
+        <x:v>方士漫剧</x:v>
       </x:c>
       <x:c r="H107" s="10" t="str">
-        <x:v>现代守护灵传人沐幽月穿成丞相嫡女，被陆家掳走十年当续命血包，遭灭口时觉醒守护灵逃生，被权臣夜玄瑾所救。三年后她隐居山村做神医，偶遇陆家仇人，设计报复后认父回都。她身怀守护灵、手握赤血山势力，护着全家，一路清算陆家、黎家、魏太后等仇敌；同时和夜玄瑾渐生情愫，联手破阴谋，治好中蛊小皇帝，打脸一众权贵，最终所有仇人自食恶果，她与夜玄瑾相守。</x:v>
+        <x:v>重生归来的沈知春，重回皇子分封之夜。前世她倾力抚育的三位亲子，最终辜负了她。今生三子同样重生，执着前程，对她满心戒备。沈知春放下执念，放弃出宫安稳，选择入宫自守。她善待孤苦无依的萧景澄，二人彼此扶持。面对深宫纷争与诸多误会，她挣脱宿命枷锁、坚守本心，最终与知恩笃行的萧景澄携手，奔赴坦荡自由的新生。</x:v>
       </x:c>
       <x:c r="I107" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；73集，主力长度；发布账号「诸云·青梅剧场」</x:v>
+        <x:v>发布账号「方士漫剧」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；80集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J107" s="11" t="n">
         <x:v>8</x:v>
@@ -11828,10 +11828,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 07:30</x:v>
       </x:c>
       <x:c r="C108" s="10" t="str">
-        <x:v>岁月迟来一段情</x:v>
+        <x:v>九零真千金我靠高考逆天改命</x:v>
       </x:c>
       <x:c r="D108" s="11" t="n">
         <x:v>69</x:v>
@@ -11840,16 +11840,16 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F108" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G108" s="10" t="str">
-        <x:v>鲸奇短剧新番</x:v>
+        <x:v>未央剧场</x:v>
       </x:c>
       <x:c r="H108" s="10" t="str">
-        <x:v>保姆沈静娴不堪前夫纠缠，选择离婚。她结识了以护工身份相处的杨建华，二人中年相恋闪婚。这个看似平凡的护工丈夫，身上藏着不为人知的巨大马甲。杨建华暗中帮助沈静娴，直到身份被揭开。前夫与其相关人员承担了相应的后果，沈静娴摆脱内心自卑，释怀过往，与杨建华及其家人拥有了安稳幸福的晚年生活。</x:v>
+        <x:v>乡下女孩林希从小与奶奶相依为命，最大的梦想是考上京大物理系、报效祖国。高考还有一年，生父苏志强突然找上门，将她接回苏家。然而苏家并非温暖港湾——养女苏柔柔处处算计，父母偏心冷漠，二哥冲动蛮横，唯有大哥苏承宇暗中相助。面对冒名顶替的身世真相、蓄意的刹车事故、保姆调包的惊天阴谋，林希始终冷静清醒，以高考为唯一目标，用满分的试卷、国家级物理竞赛冠军、高考状元一步步打脸所有人。</x:v>
       </x:c>
       <x:c r="I108" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；69集，主力长度；发布账号「鲸奇短剧新番」</x:v>
+        <x:v>发布账号「未央剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；69集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J108" s="11" t="n">
         <x:v>8</x:v>
@@ -11860,28 +11860,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B109" s="11" t="str">
-        <x:v>09-05 00:08</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C109" s="10" t="str">
-        <x:v>弃妇带崽之我在古代开电动车逃荒</x:v>
+        <x:v>乱世捉刀人，我以斩恶无敌世间</x:v>
       </x:c>
       <x:c r="D109" s="11" t="n">
-        <x:v>122</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E109" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F109" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G109" s="10" t="str">
-        <x:v>成都花花家剧场</x:v>
+        <x:v>AI便利店</x:v>
       </x:c>
       <x:c r="H109" s="10" t="str">
-        <x:v>现代女余思思车祸身亡后，意外穿越成古代被婆家踹出门的产后弃妇，绝境中她发现自己拥有随身空间——生前骑的粉色电动车及超市物资，且每日再生。她不做圣母，也懒得复仇，搜刮废弃村落的最后一口粮，把电动车塞满物资，背上女儿，骑着电动车一头扎进饥荒蔓延的乱世。</x:v>
+        <x:v>穿越者陆野绑定“悬赏系统”，以底层捉刀人身份开启硬核猎杀之路。他凭杀伐果断的作风，猎杀通缉犯换取修为，一路横推卧虎寨、平定长乐帮，在血腥江湖中冷眼看穿正邪虚伪。面对朝廷招安，他毅然拒绝，与苍云宗天骄夏侯凛音合力独闯恶人谷，血战七大恶人。最终，他在寒潭死斗中突破罡气境巅峰，悟出“宗师意境”并凝聚自我意象，从此背负修罗之名，踏上一段以杀止杀、打穿阶级枷锁的无敌游侠横推之路。</x:v>
       </x:c>
       <x:c r="I109" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；122集，次优长度；发布账号「成都花花家剧场」</x:v>
+        <x:v>发布账号「AI便利店」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度</x:v>
       </x:c>
       <x:c r="J109" s="11" t="n">
         <x:v>8</x:v>
@@ -11892,13 +11892,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B110" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 10:30</x:v>
       </x:c>
       <x:c r="C110" s="10" t="str">
-        <x:v>我是毒舌真千金之嘴炮小嫡主</x:v>
+        <x:v>假千金带领全家致富咯</x:v>
       </x:c>
       <x:c r="D110" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E110" s="11" t="str">
         <x:v>其他</x:v>
@@ -11907,13 +11907,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G110" s="10" t="str">
-        <x:v>贰拾叁楼漫剧</x:v>
+        <x:v>丫丫漫剧</x:v>
       </x:c>
       <x:c r="H110" s="10" t="str">
-        <x:v>温晚梨穿书成为原著里下场凄惨的恶毒女配，觉醒侯府真千金身份后，索性看淡纷争、随心摆烂。她初归府邸便遭假千金设计下药，危急关头，她翻墙跃至隔壁摄政王厉景珩的院落，脱口扬言要与他成婚，随即飘然离去，让清冷矜贵的厉景珩心生惦念。回归侯府后，温晚梨巧妙反击，逼假千金当众致歉，又对着父亲撒娇讨赏、灵动耍闹，轻松拿捏全府人心。摆烂通透千金邂逅高冷摄政王，一路打脸逆袭，活得肆意潇洒。</x:v>
+        <x:v>假千金苏晚晚重生在真千金苏婉柔归门的晚宴，前世被陷害驱逐的噩梦历历在目。这一世她彻底觉醒，手撕虚伪豪门、断绝苏家关系，毅然回归清贫的原生家庭，奔赴三位低谷期的天才亲哥哥。面对村民的嘲讽、旁人的轻视，苏晚晚凭借前世记忆和超前思维，安抚自卑的哥哥们，发掘三人各自的天赋，带着一家人从零起步，试水短视频、做农家美食、搭建乡村土特产合作社。</x:v>
       </x:c>
       <x:c r="I110" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；80集，主力长度；发布账号「贰拾叁楼漫剧」</x:v>
+        <x:v>发布账号「丫丫漫剧」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；73集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J110" s="11" t="n">
         <x:v>8</x:v>
@@ -11924,28 +11924,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B111" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 02:51</x:v>
       </x:c>
       <x:c r="C111" s="10" t="str">
-        <x:v>挪车风波后我亮出总裁身份</x:v>
+        <x:v>凤骨烬</x:v>
       </x:c>
       <x:c r="D111" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E111" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F111" s="10" t="str">
-        <x:v>都市职场 / 现实反转</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G111" s="10" t="str">
-        <x:v>微短剧中心</x:v>
+        <x:v>宝可漫</x:v>
       </x:c>
       <x:c r="H111" s="10" t="str">
-        <x:v>陆氏集团继承人陆汐瑶低调归国，本欲与未婚夫沈沼完婚并接手公司，却发现代理总裁沈沼早已背叛自己，不仅挪用公款为管培生情人叶晓雨定制豪车，更纵容其在公司霸凌员工、大搞特权。从地下停车场的挪车冲突开始，陆汐瑶霸气摊牌真实身份，一边召回被排挤的骨干整顿公司，一边搜集证据以法律手段追责，最终将沈沼与叶晓雨绳之以法，肃清公司歪风，重建公平的职场秩序。</x:v>
+        <x:v>烬羽台少主谢无烬遭心腹裴玄背叛惨死，浴火重生于宁远侯府受尽欺凌的病弱嫡女沈青鸾体内。为报两世血仇，她以病骨藏锋芒，步步设局，不仅反杀恶毒继母与庶妹、揭开生母被害真相，更与追查烬羽旧案的冷面摄政王萧砚辞强强联手。两人在诡谲朝局中寻得先帝密诏，一举扳倒权倾朝野的贺兰外戚。最终她召回旧部，誓要向伪善的裴玄讨回满门血债，上演了一场绝地反击的权谋复仇大戏。</x:v>
       </x:c>
       <x:c r="I111" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；76集，主力长度；发布账号「微短剧中心」</x:v>
+        <x:v>发布账号「宝可漫」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；77集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J111" s="11" t="n">
         <x:v>8</x:v>
@@ -11956,28 +11956,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B112" s="11" t="str">
-        <x:v>09-05 10:00</x:v>
+        <x:v>09-05 09:00</x:v>
       </x:c>
       <x:c r="C112" s="10" t="str">
-        <x:v>神级舅舅，培养七个天才外甥女</x:v>
+        <x:v>卡里三十七块，我靠神级课堂翻身</x:v>
       </x:c>
       <x:c r="D112" s="11" t="n">
-        <x:v>79</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E112" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F112" s="10" t="str">
-        <x:v>战神异能</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G112" s="10" t="str">
-        <x:v>糖糖动漫剧场</x:v>
+        <x:v>饭饭剧场</x:v>
       </x:c>
       <x:c r="H112" s="10" t="str">
-        <x:v>单身青年沈峰被姐姐“坑”来照顾七个外甥女，意外激活神级带娃系统。一个月内，七个零蛋女孩分别在语文、数学、外语、科学、音乐、美术、体育上展露天赋，从全县垫底逆袭为耀眼新星。沈峰在带娃与追梦的夹缝中，用责任与爱点亮了七个孩子的未来。</x:v>
+        <x:v>林宇穿成负债累累、名声烂透的大学讲师，开局只剩三十七块，还面临教学考核和学生举报。他放弃念PPT，用外卖、炒股、自我保护、校园贷、AI算法等真实问题讲透数学，意外激活超级教师系统。学生从厌恶到追随，国安从监控到重视，云澜科技和军方也因他的AI架构介入，林宇从烂讲师逆袭成国家核心资产。</x:v>
       </x:c>
       <x:c r="I112" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；79集，主力长度；发布账号「糖糖动漫剧场」</x:v>
+        <x:v>发布账号「饭饭剧场」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；96集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J112" s="11" t="n">
         <x:v>8</x:v>
@@ -11988,28 +11988,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B113" s="11" t="str">
-        <x:v>09-05 11:00</x:v>
+        <x:v>09-05 10:00</x:v>
       </x:c>
       <x:c r="C113" s="10" t="str">
-        <x:v>老祖宗显灵：我的心声全府都能听见</x:v>
+        <x:v>发配充军，战神系统宁九才乱世称雄</x:v>
       </x:c>
       <x:c r="D113" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F113" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="G113" s="10" t="str">
-        <x:v>众乐漫剧</x:v>
+        <x:v>牛奶剧场</x:v>
       </x:c>
       <x:c r="H113" s="10" t="str">
-        <x:v>谢家老祖宗谢昭宁即将飞升，却被天雷劈进后代子孙体内，成了一个差点饿死的真千金！修为尽毁，只剩算命异能，更离谱的是她的心声全府都能听见！面对绿茶养女勾结皇子伪造密信、下毒手钏、构陷科考的连环杀局，谢家众人靠老祖宗心声疯狂剧透。老祖宗表面嫌弃后人愚蠢，实则嘴硬心软的心声把反派按地摩擦。当阴谋破产、养女入狱，谢家震惊发现，这丫头竟是他们苦寻十八年的亲骨肉。看着祠堂里被拜了百年的自己牌位，老祖宗傻眼了。</x:v>
+        <x:v>宁川本是盛京城才子，被未婚妻柳如烟伪造反诗构陷，抄家流放三千里充军黑铁城。濒死之际觉醒战神系统，获得满级箭术。抵御金帐汗国的战争中大放异彩，凭借箭术、制毒天赋立下赫赫战功，结识生死弟兄，与初云商会颜如玉产生羁绊。押送敌酋回盛京看清皇室凉薄，解救受难族人，得知柳如烟遁入羽化仙门。身陷敌国险境不断变强，等待时机复仇，图谋改变乱世格局。</x:v>
       </x:c>
       <x:c r="I113" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；67集，主力长度；发布账号「众乐漫剧」</x:v>
+        <x:v>发布账号「牛奶剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；80集，主力长度</x:v>
       </x:c>
       <x:c r="J113" s="11" t="n">
         <x:v>8</x:v>
@@ -12041,10 +12041,10 @@
         <x:v>林桂香经营豆腐摊十五年，因成本上涨微调价格，遭邻居钱翠娥恶意砸摊、造谣。女儿林晓念为护母尊严，拒绝无理勒索并关店抗争。随着调查深入，当年丈夫工伤死亡的真相逐渐浮出水面，母女二人最终揭露黑幕，夺回公道，开启新生活。</x:v>
       </x:c>
       <x:c r="I114" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；76集，主力长度；发布账号「幻境大剧场」双口径都产爆款；女频受众</x:v>
+        <x:v>发布账号「幻境大剧场」双口径TOP12精品号，账号满分；题材契合爆款主线×3（剧名/分类/简介三路识别）；76集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J114" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -12052,31 +12052,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B115" s="11" t="str">
-        <x:v>09-06 00:07</x:v>
+        <x:v>09-06 08:00</x:v>
       </x:c>
       <x:c r="C115" s="10" t="str">
-        <x:v>夫君假死化龙后本公主不装了</x:v>
+        <x:v>重生后前夫抢着娶庶妹，却不知我才是真凤命</x:v>
       </x:c>
       <x:c r="D115" s="11" t="n">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E115" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F115" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感 / 逆袭打脸 / 战神异能</x:v>
+        <x:v>古装宫廷 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G115" s="10" t="str">
-        <x:v>长歌剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="H115" s="10" t="str">
-        <x:v>凤族嫡公主凤怜下凡历劫，惨遭夫君江淮清假意离世欺骗。对方飞升化龙之际，狠心终结了她的性命。一朝重生，她回到江淮清飞升前夕，特意打造精铁贴身护甲，破其裸身化龙的算计。她意外收留碰瓷白狐小白，实则是为她逆转时空的狐尊谢妄。这一世，凤怜手撕绿茶、打脸恶亲，揭穿天界冒牌真身，勇战魔域劲敌，逆袭登顶天界至尊。</x:v>
+        <x:v>沈云归携前世记忆重生。前世辅萧承璟登基反遭猜忌，含恨而终。今世他抢先娶庶妹沈若莺称天命女，她入太庙静观其变，借治水案布棋，提前备粮固堤，随太子赈灾救民。天命假象败露，萧承璟悔悟被拒。祭天大典她以水纹证其失职，萧承璟流放染疫亡。她任水务女官，太子守于身侧。重生一世，她终立于日光之下，做回自己。</x:v>
       </x:c>
       <x:c r="I115" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；发布账号「长歌剧场」</x:v>
+        <x:v>发布账号「心动漫剧场」稳定产出（上榜19次/出过3部），账号基础分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；59集，次优长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J115" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -12084,28 +12084,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B116" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-06 00:07</x:v>
       </x:c>
       <x:c r="C116" s="10" t="str">
-        <x:v>爱意灼心，真千金她拒绝内耗</x:v>
+        <x:v>夫君假死化龙后本公主不装了</x:v>
       </x:c>
       <x:c r="D116" s="11" t="n">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E116" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F116" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>古装宫廷 / 婚姻情感 / 逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="G116" s="10" t="str">
-        <x:v>每日沙雕推荐</x:v>
+        <x:v>长歌剧场</x:v>
       </x:c>
       <x:c r="H116" s="10" t="str">
-        <x:v>真千金叶空回归，面对绿茶假千金与虚伪亲情，她拒绝内耗，靠毒舌与武力疯狂打脸整顿豪门！腹黑装残的大佬温璨与她一拍即合，订婚结盟。随着“天才画师”等神级马甲掉落，叶家人全员觉醒变妹控。看疯批千金与双面大佬强强联手，一路狂飙，爽翻全场！</x:v>
+        <x:v>凤族嫡公主凤怜下凡历劫，惨遭夫君江淮清假意离世欺骗。对方飞升化龙之际，狠心终结了她的性命。一朝重生，她回到江淮清飞升前夕，特意打造精铁贴身护甲，破其裸身化龙的算计。她意外收留碰瓷白狐小白，实则是为她逆转时空的狐尊谢妄。这一世，凤怜手撕绿茶、打脸恶亲，揭穿天界冒牌真身，勇战魔域劲敌，逆袭登顶天界至尊。</x:v>
       </x:c>
       <x:c r="I116" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；77集，主力长度；发布账号「每日沙雕推荐」</x:v>
+        <x:v>发布账号「长歌剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；71集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J116" s="11" t="n">
         <x:v>9</x:v>
@@ -12116,31 +12116,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B117" s="11" t="str">
-        <x:v>09-06 00:25</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C117" s="10" t="str">
-        <x:v>嫡女不哑继母慌了</x:v>
+        <x:v>爱意灼心，真千金她拒绝内耗</x:v>
       </x:c>
       <x:c r="D117" s="11" t="n">
-        <x:v>126</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E117" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F117" s="10" t="str">
-        <x:v>家庭伦理 / 现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G117" s="10" t="str">
-        <x:v>魔力甜宠剧场</x:v>
+        <x:v>每日沙雕推荐</x:v>
       </x:c>
       <x:c r="H117" s="10" t="str">
-        <x:v>大苏嫡公主陆倾双为查母后死因，自毁声带装哑六年，受尽继母祁曼华欺凌。外邦使臣逼宫之际，她突然开口揭露阴谋，震惊朝堂。随后她步步为营，智斗奸臣崔延，救出被诬陷的舅舅顾义。为消除皇帝疑心，她主动交还兵权，在危机四伏的皇宫中独自开启复仇之路。</x:v>
+        <x:v>真千金叶空回归，面对绿茶假千金与虚伪亲情，她拒绝内耗，靠毒舌与武力疯狂打脸整顿豪门！腹黑装残的大佬温璨与她一拍即合，订婚结盟。随着“天才画师”等神级马甲掉落，叶家人全员觉醒变妹控。看疯批千金与双面大佬强强联手，一路狂飙，爽翻全场！</x:v>
       </x:c>
       <x:c r="I117" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；126集，次优长度；发布账号「魔力甜宠剧场」</x:v>
+        <x:v>发布账号「每日沙雕推荐」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；77集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J117" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -12148,28 +12148,28 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B118" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-06 00:25</x:v>
       </x:c>
       <x:c r="C118" s="10" t="str">
-        <x:v>晚来遇星辰</x:v>
+        <x:v>嫡女不哑继母慌了</x:v>
       </x:c>
       <x:c r="D118" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E118" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F118" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 现实反转</x:v>
       </x:c>
       <x:c r="G118" s="10" t="str">
-        <x:v>苞米花剧场</x:v>
+        <x:v>魔力甜宠剧场</x:v>
       </x:c>
       <x:c r="H118" s="10" t="str">
-        <x:v>大学生林晚遭前男友顾言及其母亲逼退婚，绝境中却意外收到闺蜜苏倾倾转来的一亿元，从此彻底改写人生。她果断斩断旧情，在逆袭中与苏倾倾的哥哥苏辰相识相爱并闪婚。可甜蜜婚后，林晚却发现父亲当年车祸身亡竟与苏辰有关。随着神秘“双胞胎妹妹”现身，一场围绕爱情、亲情的阴谋逐渐揭开。</x:v>
+        <x:v>大苏嫡公主陆倾双为查母后死因，自毁声带装哑六年，受尽继母祁曼华欺凌。外邦使臣逼宫之际，她突然开口揭露阴谋，震惊朝堂。随后她步步为营，智斗奸臣崔延，救出被诬陷的舅舅顾义。为消除皇帝疑心，她主动交还兵权，在危机四伏的皇宫中独自开启复仇之路。</x:v>
       </x:c>
       <x:c r="I118" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；发布账号「苞米花剧场」</x:v>
+        <x:v>发布账号「魔力甜宠剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；126集，次优长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J118" s="11" t="n">
         <x:v>8</x:v>
@@ -12183,10 +12183,10 @@
         <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C119" s="10" t="str">
-        <x:v>破屋藏空间，荒山变金山</x:v>
+        <x:v>晚来遇星辰</x:v>
       </x:c>
       <x:c r="D119" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E119" s="11" t="str">
         <x:v>其他</x:v>
@@ -12195,13 +12195,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G119" s="10" t="str">
-        <x:v>小杰动漫</x:v>
+        <x:v>苞米花剧场</x:v>
       </x:c>
       <x:c r="H119" s="10" t="str">
-        <x:v>林峰意外重生回到分家断亲的这天，被刻薄母亲和自私大哥净身赶出家门，只分得一间破败茅草屋。绝境之中，他觉醒随身桃源空间，拥有灵泉沃土，洗髓强身还能催熟奇珍作物。面对家人的压榨算计、村民的冷眼嘲讽，林峰签下断亲书，携不离不弃的妻子周欣雨，靠着空间宝物打猎、卖参、培育珍稀果蔬，开荒荒山搞产业。他狠狠打脸贪婪的原生家庭，一路逆袭搞事业建庄园，在遍地荆棘的处境里，守护爱人，闯出属于自己的富贵人生。</x:v>
+        <x:v>大学生林晚遭前男友顾言及其母亲逼退婚，绝境中却意外收到闺蜜苏倾倾转来的一亿元，从此彻底改写人生。她果断斩断旧情，在逆袭中与苏倾倾的哥哥苏辰相识相爱并闪婚。可甜蜜婚后，林晚却发现父亲当年车祸身亡竟与苏辰有关。随着神秘“双胞胎妹妹”现身，一场围绕爱情、亲情的阴谋逐渐揭开。</x:v>
       </x:c>
       <x:c r="I119" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度；发布账号「小杰动漫」</x:v>
+        <x:v>发布账号「苞米花剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="J119" s="11" t="n">
         <x:v>8</x:v>
@@ -12212,13 +12212,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B120" s="11" t="str">
-        <x:v>09-06 00:06</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C120" s="10" t="str">
-        <x:v>被赶出豪门，假千金马甲捂不住了</x:v>
+        <x:v>破屋藏空间，荒山变金山</x:v>
       </x:c>
       <x:c r="D120" s="11" t="n">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E120" s="11" t="str">
         <x:v>其他</x:v>
@@ -12227,13 +12227,13 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="G120" s="10" t="str">
-        <x:v>爱跳动1号剧场</x:v>
+        <x:v>小杰动漫</x:v>
       </x:c>
       <x:c r="H120" s="10" t="str">
-        <x:v>叶浅被养父母赶出家门，却意外发现亲生父母竟是首富顾家，三个哥哥更是各自领域的翘楚。叶依依在婚礼上污蔑叶浅反被当场揭穿，又暗中布局设下陷阱，逼叶浅赴约，危急瞬间未婚夫霍司衍舍身相护，废墟下两人彼此依靠。危机解除后，志一的现身开始揭开惊天秘密——叶依依身上的“气运系统”似乎专为叶浅而来，二十二年的错位人生，究竟是阴差阳错还是背后隐藏玄机。</x:v>
+        <x:v>林峰意外重生回到分家断亲的这天，被刻薄母亲和自私大哥净身赶出家门，只分得一间破败茅草屋。绝境之中，他觉醒随身桃源空间，拥有灵泉沃土，洗髓强身还能催熟奇珍作物。面对家人的压榨算计、村民的冷眼嘲讽，林峰签下断亲书，携不离不弃的妻子周欣雨，靠着空间宝物打猎、卖参、培育珍稀果蔬，开荒荒山搞产业。他狠狠打脸贪婪的原生家庭，一路逆袭搞事业建庄园，在遍地荆棘的处境里，守护爱人，闯出属于自己的富贵人生。</x:v>
       </x:c>
       <x:c r="I120" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；56集，次优长度；发布账号「爱跳动1号剧场」</x:v>
+        <x:v>发布账号「小杰动漫」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；66集，主力长度</x:v>
       </x:c>
       <x:c r="J120" s="11" t="n">
         <x:v>8</x:v>
@@ -12244,28 +12244,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B121" s="11" t="str">
-        <x:v>09-06 00:30</x:v>
+        <x:v>09-06 00:06</x:v>
       </x:c>
       <x:c r="C121" s="10" t="str">
-        <x:v>错信女配后前夫他后悔了</x:v>
+        <x:v>被赶出豪门，假千金马甲捂不住了</x:v>
       </x:c>
       <x:c r="D121" s="11" t="n">
-        <x:v>76</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E121" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F121" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G121" s="10" t="str">
-        <x:v>大河剧场</x:v>
+        <x:v>爱跳动1号剧场</x:v>
       </x:c>
       <x:c r="H121" s="10" t="str">
-        <x:v>恋爱三年结婚四年，七年感情，商时序偏信他人，将她送上审判庭。顾汐冉心如死灰，无罪释放那一刻，她说，“商时序，我们离婚吧。”“你别后悔！”被偏爱的有恃无恐，他以为她只是赌气，过几天就会回来。这次他等了很久，等到她成为与自己并肩的大律师，与他对簿公堂，他才慌了。“冉冉我还爱你，求你回来。”顾汐冉微微一笑，“商先生让一让，别挡着我去当你婶。”</x:v>
+        <x:v>叶浅被养父母赶出家门，却意外发现亲生父母竟是首富顾家，三个哥哥更是各自领域的翘楚。叶依依在婚礼上污蔑叶浅反被当场揭穿，又暗中布局设下陷阱，逼叶浅赴约，危急瞬间未婚夫霍司衍舍身相护，废墟下两人彼此依靠。危机解除后，志一的现身开始揭开惊天秘密——叶依依身上的“气运系统”似乎专为叶浅而来，二十二年的错位人生，究竟是阴差阳错还是背后隐藏玄机。</x:v>
       </x:c>
       <x:c r="I121" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；76集，主力长度；发布账号「大河剧场」</x:v>
+        <x:v>发布账号「爱跳动1号剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；56集，次优长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J121" s="11" t="n">
         <x:v>8</x:v>
@@ -12276,31 +12276,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B122" s="11" t="str">
-        <x:v>09-06 09:00</x:v>
+        <x:v>09-06 00:30</x:v>
       </x:c>
       <x:c r="C122" s="10" t="str">
-        <x:v>七零悍妻当家</x:v>
+        <x:v>错信女配后前夫他后悔了</x:v>
       </x:c>
       <x:c r="D122" s="11" t="n">
-        <x:v>66</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E122" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F122" s="10" t="str">
-        <x:v>年代怀旧 / 婚姻情感</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="G122" s="10" t="str">
-        <x:v>忆想动漫</x:v>
+        <x:v>大河剧场</x:v>
       </x:c>
       <x:c r="H122" s="10" t="str">
-        <x:v>现代苏念安意外穿越到七十年代，成为命运凄惨的少女。她被迫替嫁残疾陆承轩，面对窘迫家境、体弱的丈夫和三个年幼的孩子，她一改原主懦弱性格，凭借精湛医术救治陆承轩，智斗极品亲戚、顺利分家立足。她用心呵护家人、踏实经营生活，一步步治愈彼此，带领小家摆脱困境，改写全员的悲惨命运。</x:v>
+        <x:v>恋爱三年结婚四年，七年感情，商时序偏信他人，将她送上审判庭。顾汐冉心如死灰，无罪释放那一刻，她说，“商时序，我们离婚吧。”“你别后悔！”被偏爱的有恃无恐，他以为她只是赌气，过几天就会回来。这次他等了很久，等到她成为与自己并肩的大律师，与他对簿公堂，他才慌了。“冉冉我还爱你，求你回来。”顾汐冉微微一笑，“商先生让一让，别挡着我去当你婶。”</x:v>
       </x:c>
       <x:c r="I122" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；66集，主力长度；发布账号「忆想动漫」</x:v>
+        <x:v>发布账号「大河剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；76集，主力长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J122" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -12308,28 +12308,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B123" s="11" t="str">
-        <x:v>09-06 07:16</x:v>
+        <x:v>09-06 09:00</x:v>
       </x:c>
       <x:c r="C123" s="10" t="str">
-        <x:v>乱世携弟妹，我自荒野建帝朝</x:v>
+        <x:v>七零悍妻当家</x:v>
       </x:c>
       <x:c r="D123" s="11" t="n">
-        <x:v>129</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E123" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F123" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>年代怀旧 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G123" s="10" t="str">
-        <x:v>栖林</x:v>
+        <x:v>忆想动漫</x:v>
       </x:c>
       <x:c r="H123" s="10" t="str">
-        <x:v>沈沫雪意外坠入大荒灾世，开局便是满目饥馑。父兄亡故，身后是尚年幼的弟妹，前路是盗匪、饥寒与生死逃亡。她不愿只顾自保，于流离荒野收留无数挣扎求生的流民，开荒筑垒，订立规矩，把四散难民凝聚成一股力量。于乱世夹缝之中步步鏖战，抗衡豪强，平定四方。没有天降金手指，仅凭智慧与万民拥戴，从一介逃难孤女，一步步开创属于女子的宏图基业。</x:v>
+        <x:v>现代苏念安意外穿越到七十年代，成为命运凄惨的少女。她被迫替嫁残疾陆承轩，面对窘迫家境、体弱的丈夫和三个年幼的孩子，她一改原主懦弱性格，凭借精湛医术救治陆承轩，智斗极品亲戚、顺利分家立足。她用心呵护家人、踏实经营生活，一步步治愈彼此，带领小家摆脱困境，改写全员的悲惨命运。</x:v>
       </x:c>
       <x:c r="I123" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；129集，次优长度；发布账号「栖林」</x:v>
+        <x:v>发布账号「忆想动漫」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；66集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J123" s="11" t="n">
         <x:v>7</x:v>
@@ -12340,28 +12340,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B124" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-06 07:16</x:v>
       </x:c>
       <x:c r="C124" s="10" t="str">
-        <x:v>八零重生烧琉璃</x:v>
+        <x:v>乱世携弟妹，我自荒野建帝朝</x:v>
       </x:c>
       <x:c r="D124" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E124" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F124" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="G124" s="10" t="str">
-        <x:v>仙舟免费剧场</x:v>
+        <x:v>栖林</x:v>
       </x:c>
       <x:c r="H124" s="10" t="str">
-        <x:v>1980年，林场病秧子陆川重生，带着前世材料学知识与沈家失传琉璃古法，摆脱退婚窘境，联合烧窑师傅王大勇、护林队长李铁牛等人，克服原料匮乏、对手赵志高与孙麻子百般刁难，攻克脱蜡琉璃工艺。他不仅治好肺病，助力沈清璃父女平反，建起琉璃车间拿下国礼订单，众人携手将林场逐步发展为琉璃小镇，书写年代逆袭的励志故事。</x:v>
+        <x:v>沈沫雪意外坠入大荒灾世，开局便是满目饥馑。父兄亡故，身后是尚年幼的弟妹，前路是盗匪、饥寒与生死逃亡。她不愿只顾自保，于流离荒野收留无数挣扎求生的流民，开荒筑垒，订立规矩，把四散难民凝聚成一股力量。于乱世夹缝之中步步鏖战，抗衡豪强，平定四方。没有天降金手指，仅凭智慧与万民拥戴，从一介逃难孤女，一步步开创属于女子的宏图基业。</x:v>
       </x:c>
       <x:c r="I124" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；发布账号「仙舟免费剧场」</x:v>
+        <x:v>发布账号「栖林」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；129集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="J124" s="11" t="n">
         <x:v>7</x:v>
@@ -12375,25 +12375,25 @@
         <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C125" s="10" t="str">
-        <x:v>国运求生，我的技能有亿点多</x:v>
+        <x:v>八零重生烧琉璃</x:v>
       </x:c>
       <x:c r="D125" s="11" t="n">
-        <x:v>132</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E125" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F125" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="G125" s="10" t="str">
-        <x:v>锦瑟书斋</x:v>
+        <x:v>仙舟免费剧场</x:v>
       </x:c>
       <x:c r="H125" s="10" t="str">
-        <x:v>冻土末日下，国运求生游戏降临，各国选手被传送至危机四伏的荒蛮界。代表炎国参赛的苏寒意外激活神级宗师系统，任何行动都能转化为技能并不断升级。他凭借智慧与强大动手能力，狩猎采集、建造地堡、驯养猛兽，接连触发万倍物资返还。面对荒野巨兽与各国挑战，苏寒一路逆袭，为炎国夺回国运，也从普通青年成长为令世界震撼的荒野战神。</x:v>
+        <x:v>1980年，林场病秧子陆川重生，带着前世材料学知识与沈家失传琉璃古法，摆脱退婚窘境，联合烧窑师傅王大勇、护林队长李铁牛等人，克服原料匮乏、对手赵志高与孙麻子百般刁难，攻克脱蜡琉璃工艺。他不仅治好肺病，助力沈清璃父女平反，建起琉璃车间拿下国礼订单，众人携手将林场逐步发展为琉璃小镇，书写年代逆袭的励志故事。</x:v>
       </x:c>
       <x:c r="I125" s="10" t="str">
-        <x:v>题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；132集，次优长度；发布账号「锦瑟书斋」</x:v>
+        <x:v>发布账号「仙舟免费剧场」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；50集，次优长度；剧名钩子×1</x:v>
       </x:c>
       <x:c r="J125" s="11" t="n">
         <x:v>7</x:v>
@@ -12404,28 +12404,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B126" s="11" t="str">
-        <x:v>09-06 11:30</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C126" s="10" t="str">
-        <x:v>异世界的美食家</x:v>
+        <x:v>国运求生，我的技能有亿点多</x:v>
       </x:c>
       <x:c r="D126" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E126" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F126" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G126" s="10" t="str">
-        <x:v>禹佗剧场</x:v>
+        <x:v>锦瑟书斋</x:v>
       </x:c>
       <x:c r="H126" s="10" t="str">
-        <x:v>现代厨师步方穿越武者横行的玄幻世界，觉醒美食家系统，开了间不起眼小店。小店菜品用料皆是灵兽、灵材，售价高昂，食用还能提升修士修为，门口有十阶神兽看门、机械助手保驾护航。从第一位食客肖小龙开始，皇子、将军、世家子弟纷纷被美食折服，步方不断解锁蛋炒饭、酒糟鱼、药膳等各色灵食，坚守小店规矩，以厨艺征服各路强者，一步步朝着玄幻世界厨神之路前行。</x:v>
+        <x:v>冻土末日下，国运求生游戏降临，各国选手被传送至危机四伏的荒蛮界。代表炎国参赛的苏寒意外激活神级宗师系统，任何行动都能转化为技能并不断升级。他凭借智慧与强大动手能力，狩猎采集、建造地堡、驯养猛兽，接连触发万倍物资返还。面对荒野巨兽与各国挑战，苏寒一路逆袭，为炎国夺回国运，也从普通青年成长为令世界震撼的荒野战神。</x:v>
       </x:c>
       <x:c r="I126" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度；发布账号「禹佗剧场」</x:v>
+        <x:v>发布账号「锦瑟书斋」无榜单战绩，账号0分；题材契合爆款主线×2（剧名/分类/简介三路识别）；简介爽点词×3；132集，次优长度；女频受众</x:v>
       </x:c>
       <x:c r="J126" s="11" t="n">
         <x:v>7</x:v>
@@ -12436,28 +12436,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B127" s="11" t="str">
-        <x:v>09-06 10:00</x:v>
+        <x:v>09-06 11:30</x:v>
       </x:c>
       <x:c r="C127" s="10" t="str">
-        <x:v>拆迁款到账那天，我签了离婚协议</x:v>
+        <x:v>异世界的美食家</x:v>
       </x:c>
       <x:c r="D127" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E127" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F127" s="10" t="str">
-        <x:v>婚姻情感 / 现实反转</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="G127" s="10" t="str">
-        <x:v>诗婳-小林看剧</x:v>
+        <x:v>禹佗剧场</x:v>
       </x:c>
       <x:c r="H127" s="10" t="str">
-        <x:v>高价拆迁款竟让丈夫周凯以房产证有自己名字为由，逼妻子陈念拿十万净身出户。陈念心死签字，却意外发现父母留下的房产藏着神秘契约，周凯因贪婪反而背上巨债。与此同时，失踪十年的父亲陈建军神秘现身，陈念也在青梅竹马律师赵东的陪伴下，一步步揭开父亲假死、华月集团与幕后黑手洪万山的秘密。她彻底觉醒，继承父亲的事业，逆袭成为掌控集团的商业总裁。</x:v>
+        <x:v>现代厨师步方穿越武者横行的玄幻世界，觉醒美食家系统，开了间不起眼小店。小店菜品用料皆是灵兽、灵材，售价高昂，食用还能提升修士修为，门口有十阶神兽看门、机械助手保驾护航。从第一位食客肖小龙开始，皇子、将军、世家子弟纷纷被美食折服，步方不断解锁蛋炒饭、酒糟鱼、药膳等各色灵食，坚守小店规矩，以厨艺征服各路强者，一步步朝着玄幻世界厨神之路前行。</x:v>
       </x:c>
       <x:c r="I127" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；发布账号「诗婳-小林看剧」</x:v>
+        <x:v>发布账号「禹佗剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；60集，主力长度</x:v>
       </x:c>
       <x:c r="J127" s="11" t="n">
         <x:v>7</x:v>
@@ -12471,25 +12471,25 @@
         <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C128" s="10" t="str">
-        <x:v>林莽猎枭：八零狩猎餐餐吃肉</x:v>
+        <x:v>拆迁款到账那天，我签了离婚协议</x:v>
       </x:c>
       <x:c r="D128" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E128" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F128" s="10" t="str">
-        <x:v>年代怀旧 / 种田囤货 / 美食治愈</x:v>
+        <x:v>婚姻情感 / 现实反转</x:v>
       </x:c>
       <x:c r="G128" s="10" t="str">
-        <x:v>悬疑藏结局</x:v>
+        <x:v>诗婳-小林看剧</x:v>
       </x:c>
       <x:c r="H128" s="10" t="str">
-        <x:v>林阳重生回到1985年东北山村，带着前世记忆觉醒狩猎系统，凭借猎物锁定与自动瞄准能力在山林中屡获奇猎，快速积累财富与人脉。他打脸贪得无厌的孙家，摆脱错缘，守护家人，与青梅竹马李小婉相知相恋，还凭借猎熊功绩当上巡山员，带领伙伴闯事业，在白山黑水间逆天改命，活成顶天立地的汉子。</x:v>
+        <x:v>高价拆迁款竟让丈夫周凯以房产证有自己名字为由，逼妻子陈念拿十万净身出户。陈念心死签字，却意外发现父母留下的房产藏着神秘契约，周凯因贪婪反而背上巨债。与此同时，失踪十年的父亲陈建军神秘现身，陈念也在青梅竹马律师赵东的陪伴下，一步步揭开父亲假死、华月集团与幕后黑手洪万山的秘密。她彻底觉醒，继承父亲的事业，逆袭成为掌控集团的商业总裁。</x:v>
       </x:c>
       <x:c r="I128" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；114集，次优长度；发布账号「悬疑藏结局」</x:v>
+        <x:v>发布账号「诗婳-小林看剧」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；64集，主力长度；女频受众</x:v>
       </x:c>
       <x:c r="J128" s="11" t="n">
         <x:v>7</x:v>
@@ -12503,25 +12503,25 @@
         <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C129" s="10" t="str">
-        <x:v>落魄千金闪婚记，领证对象是总裁</x:v>
+        <x:v>林莽猎枭：八零狩猎餐餐吃肉</x:v>
       </x:c>
       <x:c r="D129" s="11" t="n">
-        <x:v>219</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E129" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F129" s="10" t="str">
-        <x:v>都市职场 / 婚姻情感</x:v>
+        <x:v>年代怀旧 / 种田囤货 / 美食治愈</x:v>
       </x:c>
       <x:c r="G129" s="10" t="str">
-        <x:v>白日梦制造局</x:v>
+        <x:v>悬疑藏结局</x:v>
       </x:c>
       <x:c r="H129" s="10" t="str">
-        <x:v>夏念安撞破男友秦少钰与表妹夏慕晴背叛后果断分手，却又被舅舅一家逼迫替嫁豪门。为夺回母亲留下的月华集团股权，她阴差阳错与裴氏继承人裴晋廷闪婚。原本只是一场各取所需的契约婚姻，却在一次次并肩反击中逐渐变成真心。面对渣男纠缠、表妹陷害、舅舅夺产及裴家继承权争斗，夏念安不断揭开神医、黑客等隐藏身份，与裴晋廷强强联手，打脸反派、守住家业，也收获了势均力敌的爱情。</x:v>
+        <x:v>林阳重生回到1985年东北山村，带着前世记忆觉醒狩猎系统，凭借猎物锁定与自动瞄准能力在山林中屡获奇猎，快速积累财富与人脉。他打脸贪得无厌的孙家，摆脱错缘，守护家人，与青梅竹马李小婉相知相恋，还凭借猎熊功绩当上巡山员，带领伙伴闯事业，在白山黑水间逆天改命，活成顶天立地的汉子。</x:v>
       </x:c>
       <x:c r="I129" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；219集，长度需关注；发布账号「白日梦制造局」</x:v>
+        <x:v>发布账号「悬疑藏结局」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；114集，次优长度</x:v>
       </x:c>
       <x:c r="J129" s="11" t="n">
         <x:v>7</x:v>
@@ -12532,28 +12532,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B130" s="11" t="str">
-        <x:v>09-06 07:00</x:v>
+        <x:v>09-06 10:00</x:v>
       </x:c>
       <x:c r="C130" s="10" t="str">
-        <x:v>被净身出户后我亮出身份</x:v>
+        <x:v>落魄千金闪婚记，领证对象是总裁</x:v>
       </x:c>
       <x:c r="D130" s="11" t="n">
-        <x:v>61</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E130" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F130" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场 / 婚姻情感</x:v>
       </x:c>
       <x:c r="G130" s="10" t="str">
-        <x:v>魔力甜宠剧场</x:v>
+        <x:v>白日梦制造局</x:v>
       </x:c>
       <x:c r="H130" s="10" t="str">
-        <x:v>富家千金苏晚为爱情隐去家世，说服父亲拿出两千五百万支持丈夫陆川创业。六周年纪念日，陆川携白月光温如回家提出离婚，逼她放弃婚内财产。苏晚归家后查实陆川境外重婚、私自转移夫妻财产。她拒绝对方舆论施压与和解，在慈善晚宴展露苏家千金身份。庭审证据充分，法院判陆川与温如婚姻无效，返还财产股权，苏晚夺得孩子抚养权，放下过往接手家族事业开启新生。</x:v>
+        <x:v>夏念安撞破男友秦少钰与表妹夏慕晴背叛后果断分手，却又被舅舅一家逼迫替嫁豪门。为夺回母亲留下的月华集团股权，她阴差阳错与裴氏继承人裴晋廷闪婚。原本只是一场各取所需的契约婚姻，却在一次次并肩反击中逐渐变成真心。面对渣男纠缠、表妹陷害、舅舅夺产及裴家继承权争斗，夏念安不断揭开神医、黑客等隐藏身份，与裴晋廷强强联手，打脸反派、守住家业，也收获了势均力敌的爱情。</x:v>
       </x:c>
       <x:c r="I130" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；发布账号「魔力甜宠剧场」；剧名钩子×1</x:v>
+        <x:v>发布账号「白日梦制造局」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×3；219集，长度需关注；女频受众</x:v>
       </x:c>
       <x:c r="J130" s="11" t="n">
         <x:v>7</x:v>
@@ -12564,28 +12564,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B131" s="11" t="str">
-        <x:v>09-06 08:00</x:v>
+        <x:v>09-06 07:00</x:v>
       </x:c>
       <x:c r="C131" s="10" t="str">
-        <x:v>重生后前夫抢着娶庶妹，却不知我才是真凤命</x:v>
+        <x:v>被净身出户后我亮出身份</x:v>
       </x:c>
       <x:c r="D131" s="11" t="n">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E131" s="11" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="F131" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="G131" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>魔力甜宠剧场</x:v>
       </x:c>
       <x:c r="H131" s="10" t="str">
-        <x:v>沈云归携前世记忆重生。前世辅萧承璟登基反遭猜忌，含恨而终。今世他抢先娶庶妹沈若莺称天命女，她入太庙静观其变，借治水案布棋，提前备粮固堤，随太子赈灾救民。天命假象败露，萧承璟悔悟被拒。祭天大典她以水纹证其失职，萧承璟流放染疫亡。她任水务女官，太子守于身侧。重生一世，她终立于日光之下，做回自己。</x:v>
+        <x:v>富家千金苏晚为爱情隐去家世，说服父亲拿出两千五百万支持丈夫陆川创业。六周年纪念日，陆川携白月光温如回家提出离婚，逼她放弃婚内财产。苏晚归家后查实陆川境外重婚、私自转移夫妻财产。她拒绝对方舆论施压与和解，在慈善晚宴展露苏家千金身份。庭审证据充分，法院判陆川与温如婚姻无效，返还财产股权，苏晚夺得孩子抚养权，放下过往接手家族事业开启新生。</x:v>
       </x:c>
       <x:c r="I131" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；59集，次优长度；发布账号「心动漫剧场」</x:v>
+        <x:v>发布账号「魔力甜宠剧场」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；61集，主力长度；剧名钩子×1；女频受众</x:v>
       </x:c>
       <x:c r="J131" s="11" t="n">
         <x:v>7</x:v>
@@ -12617,7 +12617,7 @@
         <x:v>三线女演员黎昭领奖途中遭死对头设计车祸，魂穿为流浪狗“狗蛋”，被高冷影帝沈韫收养。二人意外达成“心声互通”，黎昭化身极具人性的爆笑萌宠，随沈韫开启温馨治愈的豪门与娱乐圈生活。在沈韫的守护与偏爱下，黎昭逐渐揭开当年车祸真相并惩治恶人，同时在欢喜互动中与沈韫互生情愫，上演了一场爆笑又甜蜜的萌宠逆袭之旅。</x:v>
       </x:c>
       <x:c r="I132" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；110集，次优长度；发布账号「剧燃动漫」</x:v>
+        <x:v>发布账号「剧燃动漫」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×2；110集，次优长度；通用受众</x:v>
       </x:c>
       <x:c r="J132" s="11" t="n">
         <x:v>6.5</x:v>
@@ -12649,7 +12649,7 @@
         <x:v>出身顶尖高知家庭的短视频博主陈默，父母分别是清华物理系教授与中科院研究员，姐姐更是CERN博士后。清华物理系学霸表妹沈薇前来借住，起初带着优越感，认定陈默是家族基因的短板。在这个处处讲究严谨与科学的家里，沈薇不断经受“高能暴击”，在相处与镜头记录下卸下天才光环，学会接纳失败，读懂热爱本身的意义，陈默也用真实的短片完成对天才与普通人的重新诠释。</x:v>
       </x:c>
       <x:c r="I133" s="10" t="str">
-        <x:v>题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；74集，主力长度；发布账号「金龙动画」</x:v>
+        <x:v>发布账号「金龙动画」无榜单战绩，账号0分；题材契合爆款主线×3（剧名/分类/简介三路识别）；简介爽点词×1；74集，主力长度；通用受众</x:v>
       </x:c>
       <x:c r="J133" s="11" t="n">
         <x:v>6.5</x:v>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R00617be94309495a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧次新剧榜" sheetId="2" r:id="R6fc82e2250734e6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rf0f49eb0e6894ed3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R935c7274774f4579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="Rb096208ccd7a4e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R95a194d4abb548e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R0667ea9cb5ae4b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R590f90448f654e7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rc6c84dc6118d448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Rbec79490fd954556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R222a54788ad74f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R5e91c49289dd49a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -909,26 +909,26 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
-        <x:v>从鸡场开始的逆袭</x:v>
+        <x:v>一瓶奶走过两个清晨</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>06-30 18:00</x:v>
+        <x:v>08-18 15:11</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E22" s="10" t="n">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G22" s="10" t="str">
-        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="H22" s="11" t="str"/>
       <x:c r="I22" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
+        <x:v>2026-08-19、2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -936,26 +936,26 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
-        <x:v>商场收回档口我成了全城的供应商</x:v>
+        <x:v>从鸡场开始的逆袭</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>08-19 20:22</x:v>
+        <x:v>06-30 18:00</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F23" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G23" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>种田囤货 / 美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="H23" s="11" t="str"/>
       <x:c r="I23" s="10" t="str">
-        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-01</x:v>
+        <x:v>2026-08-10、2026-08-11、2026-08-12、2026-08-13、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-23、2026-08-24、2026-08-25、2026-08-31</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -963,16 +963,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
-        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
+        <x:v>商场收回档口我成了全城的供应商</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>08-24 08:00</x:v>
+        <x:v>08-19 20:22</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>77</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F24" s="10" t="str">
         <x:v>经典3D</x:v>
@@ -982,7 +982,7 @@
       </x:c>
       <x:c r="H24" s="11" t="str"/>
       <x:c r="I24" s="10" t="str">
-        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
+        <x:v>2026-08-20、2026-08-21、2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-30、2026-08-31、2026-09-01</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -990,26 +990,26 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
-        <x:v>福宝花卷致富：我的小吃店通古今</x:v>
+        <x:v>我年终奖80w降到1w9，领导却慌了</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>07-20 14:00</x:v>
+        <x:v>08-24 08:00</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>196</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F25" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="G25" s="10" t="str">
-        <x:v>萌宝治愈 / 都市职场 / 美食治愈</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="H25" s="11" t="str"/>
       <x:c r="I25" s="10" t="str">
-        <x:v>2026-08-10、2026-08-11、2026-08-13、2026-08-14、2026-08-15、2026-08-16、2026-08-17、2026-08-18、2026-08-22、2026-08-23、2026-08-29、2026-09-03</x:v>
+        <x:v>2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02、2026-09-03</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1017,26 +1017,26 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
-        <x:v>一瓶奶走过两个清晨</x:v>
+        <x:v>福宝治愈全世界，家有萌娃岁岁安</x:v>
       </x:c>
       <x:c r="C26" s="11" t="str">
-        <x:v>08-18 15:11</x:v>
+        <x:v>08-21 10:00</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>63</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F26" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="G26" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>萌宝治愈</x:v>
       </x:c>
       <x:c r="H26" s="11" t="str"/>
       <x:c r="I26" s="10" t="str">
-        <x:v>2026-08-19、2026-08-23、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-02</x:v>
+        <x:v>2026-08-22、2026-08-23、2026-08-24、2026-08-25、2026-08-26、2026-08-27、2026-08-28、2026-08-29、2026-08-30、2026-08-31、2026-09-01、2026-09-03</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1133,30 +1133,32 @@
       </x:c>
       <x:c r="B3" s="11"/>
       <x:c r="C3" s="10" t="str">
-        <x:v>宴席终散人归远</x:v>
+        <x:v>靠山屯纪事</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>09-01 20:18</x:v>
+        <x:v>09-02 15:00</x:v>
       </x:c>
       <x:c r="F3" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="H3" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I3" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>柚子吖</x:v>
-      </x:c>
-      <x:c r="K3" s="10" t="str"/>
+        <x:v>小小动画</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="str">
+        <x:v>穿越到七十年代的花昭，重生在肥胖的少女身上。她凭借一身胆识与偶然得到的宝物，改变自身境遇，巧妙化解亲戚的算计纠缠。抓住时代机遇带动村里发展副业，改善一家人的生活。与军人叶深结缘，意外迎来新的小生命。面对原生家庭的复杂纠葛，她保持清醒，护住爷爷与至亲，在艰苦的年代里脚踏实地，靠着智慧和韧性，一步步打拼出属于自己的安稳人生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -1164,32 +1166,30 @@
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="10" t="str">
-        <x:v>靠山屯纪事</x:v>
+        <x:v>你让我出海：我一船货卖二十万你慌什么</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>09-02 15:00</x:v>
+        <x:v>09-02 09:05</x:v>
       </x:c>
       <x:c r="F4" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I4" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>小小动画</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="str">
-        <x:v>穿越到七十年代的花昭，重生在肥胖的少女身上。她凭借一身胆识与偶然得到的宝物，改变自身境遇，巧妙化解亲戚的算计纠缠。抓住时代机遇带动村里发展副业，改善一家人的生活。与军人叶深结缘，意外迎来新的小生命。面对原生家庭的复杂纠葛，她保持清醒，护住爷爷与至亲，在艰苦的年代里脚踏实地，靠着智慧和韧性，一步步打拼出属于自己的安稳人生。</x:v>
-      </x:c>
+        <x:v>呼哈短剧</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -1197,28 +1197,28 @@
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="10" t="str">
-        <x:v>你让我出海：我一船货卖二十万你慌什么</x:v>
+        <x:v>一碗热饭暖人性</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>09-02 09:05</x:v>
+        <x:v>09-03 00:06</x:v>
       </x:c>
       <x:c r="F5" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>呼哈短剧</x:v>
+        <x:v>第九幕</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str"/>
     </x:row>
@@ -1228,30 +1228,32 @@
       </x:c>
       <x:c r="B6" s="11"/>
       <x:c r="C6" s="10" t="str">
-        <x:v>我什么都没干，却成了大功臣</x:v>
+        <x:v>盛海风云</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>09-01 17:32</x:v>
+        <x:v>09-02 09:58</x:v>
       </x:c>
       <x:c r="F6" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>小姐姐追漫画</x:v>
-      </x:c>
-      <x:c r="K6" s="10" t="str"/>
+        <x:v>星间漫步</x:v>
+      </x:c>
+      <x:c r="K6" s="10" t="str">
+        <x:v>八十岁的千亿级盛海财团创始人林晚秋重生回到董事会召开前夕，当场罢免为私情撕毁百亿合作协议的嫡孙顾景辰，召回蛰伏非洲的铁血庶孙顾景深，布下代码陷阱精准反制宿敌耀星科技的商业间谍阴谋，以铁血手腕守护集团基业，顺利完成新老权力交接。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -1259,28 +1261,28 @@
       </x:c>
       <x:c r="B7" s="11"/>
       <x:c r="C7" s="10" t="str">
-        <x:v>扣我三十万，我收购你公司</x:v>
+        <x:v>宴席终散人归远</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>08-08 10:00</x:v>
+        <x:v>09-01 20:18</x:v>
       </x:c>
       <x:c r="F7" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J7" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>柚子吖</x:v>
       </x:c>
       <x:c r="K7" s="10" t="str"/>
     </x:row>
@@ -1290,31 +1292,31 @@
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="10" t="str">
-        <x:v>盛海风云</x:v>
+        <x:v>爹爹入赘我暴富啦</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>09-02 09:58</x:v>
+        <x:v>09-02 00:20</x:v>
       </x:c>
       <x:c r="F8" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
-        <x:v>星间漫步</x:v>
+        <x:v>每日沙雕推荐</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>八十岁的千亿级盛海财团创始人林晚秋重生回到董事会召开前夕，当场罢免为私情撕毁百亿合作协议的嫡孙顾景辰，召回蛰伏非洲的铁血庶孙顾景深，布下代码陷阱精准反制宿敌耀星科技的商业间谍阴谋，以铁血手腕守护集团基业，顺利完成新老权力交接。</x:v>
+        <x:v>沈明珠看着母亲决绝离去，姐姐执意奔赴城里。她灵机一动，主动给父亲说媒，让父亲入赘彪悍女猎户钱三妞。她凭借前世记忆得到祖传的灵泉玉佩，和三位性格迥异的继兄相处融洽。一家人齐心对抗难缠的街坊对手，揭穿坏人的伪装，齐心协力把小日子过得红火安稳。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1323,28 +1325,28 @@
       </x:c>
       <x:c r="B9" s="11"/>
       <x:c r="C9" s="10" t="str">
-        <x:v>一块钱买来的妈妈</x:v>
+        <x:v>被遗忘的股票账户</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>09-02 01:57</x:v>
+        <x:v>09-02 06:17</x:v>
       </x:c>
       <x:c r="F9" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>阿南影视</x:v>
+        <x:v>新漫剧场</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str"/>
     </x:row>
@@ -1354,28 +1356,28 @@
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="10" t="str">
-        <x:v>外婆的小心思</x:v>
+        <x:v>洋媳妇勇闯东北老家</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>09-01 11:22</x:v>
+        <x:v>09-02 16:00</x:v>
       </x:c>
       <x:c r="F10" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>奇境剧场</x:v>
+        <x:v>云间漫剧-十六</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str"/>
     </x:row>
@@ -1385,28 +1387,28 @@
       </x:c>
       <x:c r="B11" s="11"/>
       <x:c r="C11" s="10" t="str">
-        <x:v>月薪四千，我手握亿级底牌</x:v>
+        <x:v>遗落在村口的春天</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>07-24 11:00</x:v>
+        <x:v>09-02 10:37</x:v>
       </x:c>
       <x:c r="F11" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>55</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>治愈 AI 恋</x:v>
+        <x:v>奇迹短剧</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str"/>
     </x:row>
@@ -1416,28 +1418,28 @@
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="10" t="str">
-        <x:v>商场涨租，我连夜带走所有商户</x:v>
+        <x:v>一碗牛肉板面的良心账</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>09-02 10:20</x:v>
+        <x:v>08-31 08:18</x:v>
       </x:c>
       <x:c r="F12" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>奈斯动画</x:v>
+        <x:v>朵朵漫</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str"/>
     </x:row>
@@ -1447,28 +1449,28 @@
       </x:c>
       <x:c r="B13" s="11"/>
       <x:c r="C13" s="10" t="str">
-        <x:v>两个儿子护我归家</x:v>
+        <x:v>雨天无敌之神也想过退休生活</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>08-31 18:24</x:v>
+        <x:v>09-02 15:00</x:v>
       </x:c>
       <x:c r="F13" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>83</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>桑园小剧场</x:v>
+        <x:v>晓晓的创作</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str"/>
     </x:row>
@@ -1478,28 +1480,28 @@
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="10" t="str">
-        <x:v>遗落在村口的春天</x:v>
+        <x:v>洪伟的故事</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>09-02 10:37</x:v>
+        <x:v>09-02 09:53</x:v>
       </x:c>
       <x:c r="F14" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J14" s="10" t="str">
-        <x:v>奇迹短剧</x:v>
+        <x:v>淑芬动画</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str"/>
     </x:row>
@@ -1509,28 +1511,28 @@
       </x:c>
       <x:c r="B15" s="11"/>
       <x:c r="C15" s="10" t="str">
-        <x:v>狂枭归来</x:v>
+        <x:v>一碟辣椒引出人心账</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>08-30 00:06</x:v>
+        <x:v>09-02 11:30</x:v>
       </x:c>
       <x:c r="F15" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
-        <x:v>逆袭打脸</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>漫界剧场</x:v>
+        <x:v>洛川漫剧</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str"/>
     </x:row>
@@ -1540,32 +1542,30 @@
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="10" t="str">
-        <x:v>爹爹入赘我暴富啦</x:v>
+        <x:v>外婆的小心思</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>09-02 00:20</x:v>
+        <x:v>09-01 11:22</x:v>
       </x:c>
       <x:c r="F16" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>121</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>每日沙雕推荐</x:v>
-      </x:c>
-      <x:c r="K16" s="10" t="str">
-        <x:v>沈明珠看着母亲决绝离去，姐姐执意奔赴城里。她灵机一动，主动给父亲说媒，让父亲入赘彪悍女猎户钱三妞。她凭借前世记忆得到祖传的灵泉玉佩，和三位性格迥异的继兄相处融洽。一家人齐心对抗难缠的街坊对手，揭穿坏人的伪装，齐心协力把小日子过得红火安稳。</x:v>
-      </x:c>
+        <x:v>奇境剧场</x:v>
+      </x:c>
+      <x:c r="K16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -1573,29 +1573,23 @@
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="10" t="str">
-        <x:v>洋媳妇勇闯东北老家</x:v>
+        <x:v>餐桌上的河豚</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="str">
-        <x:v>09-02 16:00</x:v>
-      </x:c>
+      <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="n">
-        <x:v>154</x:v>
-      </x:c>
+      <x:c r="G17" s="11" t="str"/>
       <x:c r="H17" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="J17" s="10" t="str">
-        <x:v>云间漫剧-十六</x:v>
-      </x:c>
+      <x:c r="J17" s="10" t="str"/>
       <x:c r="K17" s="10" t="str"/>
     </x:row>
     <x:row r="18">
@@ -1604,28 +1598,28 @@
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="10" t="str">
-        <x:v>我没有爸，但有三个妈</x:v>
+        <x:v>一块钱买来的妈妈</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>09-02 08:00</x:v>
+        <x:v>09-02 01:57</x:v>
       </x:c>
       <x:c r="F18" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>57</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
-        <x:v>魔力大世界</x:v>
+        <x:v>阿南影视</x:v>
       </x:c>
       <x:c r="K18" s="10" t="str"/>
     </x:row>
@@ -1635,28 +1629,28 @@
       </x:c>
       <x:c r="B19" s="11"/>
       <x:c r="C19" s="10" t="str">
-        <x:v>布衣成圣</x:v>
+        <x:v>神魔伴我镇北凉</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>09-01 18:30</x:v>
+        <x:v>09-02 10:00</x:v>
       </x:c>
       <x:c r="F19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>309</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>战神异能</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
-        <x:v>南小离</x:v>
+        <x:v>史小怪</x:v>
       </x:c>
       <x:c r="K19" s="10" t="str"/>
     </x:row>
@@ -1666,28 +1660,28 @@
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="10" t="str">
-        <x:v>十八年后再掌天远</x:v>
+        <x:v>谁动了我的成绩</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>08-29 20:00</x:v>
+        <x:v>09-02 18:06</x:v>
       </x:c>
       <x:c r="F20" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
-        <x:v>小雅说漫</x:v>
+        <x:v>故事里</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str"/>
     </x:row>
@@ -1697,13 +1691,13 @@
       </x:c>
       <x:c r="B21" s="11"/>
       <x:c r="C21" s="10" t="str">
-        <x:v>分房名单没有他</x:v>
+        <x:v>他们霸占我的房结婚，我反手卖掉</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>08-09 17:18</x:v>
+        <x:v>09-02 00:06</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
         <x:v>1</x:v>
@@ -1715,10 +1709,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
-        <x:v>一身傲骨</x:v>
+        <x:v>金秋剧场</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str"/>
     </x:row>
@@ -1728,28 +1722,28 @@
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="10" t="str">
-        <x:v>陈丰的故事！</x:v>
+        <x:v>两个儿子护我归家</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E22" s="11" t="str">
-        <x:v>09-01 19:41</x:v>
+        <x:v>08-31 18:24</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="11" t="n">
-        <x:v>112</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>小土豆动画</x:v>
+        <x:v>桑园小剧场</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str"/>
     </x:row>
@@ -1759,28 +1753,28 @@
       </x:c>
       <x:c r="B23" s="11"/>
       <x:c r="C23" s="10" t="str">
-        <x:v>守尺不负匠人心</x:v>
+        <x:v>一念清醒万山开</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E23" s="11" t="str">
-        <x:v>09-02 00:10</x:v>
+        <x:v>07-24 10:00</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="11" t="n">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>新漫剧场</x:v>
+        <x:v>必看短剧</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str"/>
     </x:row>
@@ -1790,28 +1784,28 @@
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="10" t="str">
-        <x:v>一碗牛肉板面的良心账</x:v>
+        <x:v>离婚后我万丈荣光</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>08-31 08:18</x:v>
+        <x:v>09-02 18:00</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H24" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
-        <x:v>朵朵漫</x:v>
+        <x:v>平阅漫漫看</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str"/>
     </x:row>
@@ -1821,28 +1815,28 @@
       </x:c>
       <x:c r="B25" s="11"/>
       <x:c r="C25" s="10" t="str">
-        <x:v>装穷三年，我和大小姐双双掉马</x:v>
+        <x:v>我什么都没干，却成了大功臣</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>09-02 00:15</x:v>
+        <x:v>09-01 17:32</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="11" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
+        <x:v>小姐姐追漫画</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str"/>
     </x:row>
@@ -1852,23 +1846,29 @@
       </x:c>
       <x:c r="B26" s="11"/>
       <x:c r="C26" s="10" t="str">
-        <x:v>六零年代重组家庭实录</x:v>
+        <x:v>退掉三十块水闸费，旱涝淹醒全村人</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
-      <x:c r="E26" s="11" t="str"/>
+      <x:c r="E26" s="11" t="str">
+        <x:v>08-22 17:49</x:v>
+      </x:c>
       <x:c r="F26" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G26" s="11" t="str"/>
+      <x:c r="G26" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="H26" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="J26" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J26" s="10" t="str">
+        <x:v>小林剧场</x:v>
+      </x:c>
       <x:c r="K26" s="10" t="str"/>
     </x:row>
     <x:row r="27">
@@ -1877,28 +1877,28 @@
       </x:c>
       <x:c r="B27" s="11"/>
       <x:c r="C27" s="10" t="str">
-        <x:v>玉碎双姝错</x:v>
+        <x:v>母亲的难题</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>09-02 17:00</x:v>
+        <x:v>07-08 10:00</x:v>
       </x:c>
       <x:c r="F27" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>观月剧场</x:v>
+        <x:v>久久剧场</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str"/>
     </x:row>
@@ -1908,28 +1908,28 @@
       </x:c>
       <x:c r="B28" s="11"/>
       <x:c r="C28" s="10" t="str">
-        <x:v>洪伟的故事</x:v>
+        <x:v>流放厨娘，我靠美食绝地翻盘记</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>09-02 09:53</x:v>
+        <x:v>08-31 10:00</x:v>
       </x:c>
       <x:c r="F28" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>美食治愈 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
-        <x:v>淑芬动画</x:v>
+        <x:v>大师兄说剧</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str"/>
     </x:row>
@@ -1939,28 +1939,28 @@
       </x:c>
       <x:c r="B29" s="11"/>
       <x:c r="C29" s="10" t="str">
-        <x:v>她为爱上岸，我们送她回海</x:v>
+        <x:v>前妻背叛，现任竟让我原谅她</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E29" s="11" t="str">
-        <x:v>09-02 17:08</x:v>
+        <x:v>08-29 13:33</x:v>
       </x:c>
       <x:c r="F29" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H29" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J29" s="10" t="str">
-        <x:v>悦也系</x:v>
+        <x:v>清禾精品剧场</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str"/>
     </x:row>
@@ -1970,90 +1970,90 @@
       </x:c>
       <x:c r="B30" s="11"/>
       <x:c r="C30" s="10" t="str">
-        <x:v>陷落京霓：错认大佬他心动了</x:v>
+        <x:v>七年退让到此为止</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E30" s="11" t="str">
-        <x:v>08-30 18:00</x:v>
+        <x:v>09-01 12:00</x:v>
       </x:c>
       <x:c r="F30" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="11" t="n">
-        <x:v>146</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
-        <x:v>心动小剧场</x:v>
+        <x:v>二妞.影视</x:v>
       </x:c>
       <x:c r="K30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B31" s="11"/>
       <x:c r="C31" s="10" t="str">
-        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
+        <x:v>装穷三年，我和大小姐双双掉马</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>07-27 11:00</x:v>
+        <x:v>09-02 00:15</x:v>
       </x:c>
       <x:c r="F31" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="11" t="n">
-        <x:v>196</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>暖夏短剧</x:v>
+        <x:v>星漫动漫剧场</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
-        <x:v>次新剧</x:v>
+        <x:v>新剧</x:v>
       </x:c>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="10" t="str">
-        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
+        <x:v>扣我三十万，我收购你公司</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>08-29 16:15</x:v>
+        <x:v>08-08 10:00</x:v>
       </x:c>
       <x:c r="F32" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="11" t="n">
-        <x:v>156</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
-        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
-        <x:v>漫漫画丫头</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str"/>
     </x:row>
@@ -2063,28 +2063,28 @@
       </x:c>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="10" t="str">
-        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
+        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>08-31 20:00</x:v>
+        <x:v>07-27 11:00</x:v>
       </x:c>
       <x:c r="F33" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G33" s="11" t="n">
-        <x:v>67</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
-        <x:v>马克动漫</x:v>
+        <x:v>暖夏短剧</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str"/>
     </x:row>
@@ -2094,28 +2094,28 @@
       </x:c>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="10" t="str">
-        <x:v>闻心：京华稚园录</x:v>
+        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>08-31 19:00</x:v>
+        <x:v>08-29 16:15</x:v>
       </x:c>
       <x:c r="F34" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G34" s="11" t="n">
-        <x:v>106</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="J34" s="10" t="str">
-        <x:v>阿云剧场</x:v>
+        <x:v>漫漫画丫头</x:v>
       </x:c>
       <x:c r="K34" s="10" t="str"/>
     </x:row>
@@ -2125,28 +2125,28 @@
       </x:c>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="10" t="str">
-        <x:v>这辆车，我不伺候了</x:v>
+        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>09-01 18:07</x:v>
+        <x:v>08-31 20:00</x:v>
       </x:c>
       <x:c r="F35" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G35" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>马克动漫</x:v>
       </x:c>
       <x:c r="K35" s="10" t="str"/>
     </x:row>
@@ -2156,28 +2156,28 @@
       </x:c>
       <x:c r="B36" s="11"/>
       <x:c r="C36" s="10" t="str">
-        <x:v>重生80：十斤大米娶媳妇</x:v>
+        <x:v>大婚当日立规矩，这婚我不结了</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E36" s="11" t="str">
-        <x:v>09-01 06:30</x:v>
+        <x:v>08-31 17:00</x:v>
       </x:c>
       <x:c r="F36" s="11" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G36" s="11" t="n">
-        <x:v>208</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
-        <x:v>白尘</x:v>
+        <x:v>云影漫剧</x:v>
       </x:c>
       <x:c r="K36" s="10" t="str"/>
     </x:row>
@@ -2187,7 +2187,7 @@
       </x:c>
       <x:c r="B37" s="11"/>
       <x:c r="C37" s="10" t="str">
-        <x:v>我有六个黄毛爹</x:v>
+        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
         <x:v>2026-09-02</x:v>
@@ -2199,16 +2199,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H37" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="K37" s="10" t="str"/>
     </x:row>
@@ -2218,23 +2218,29 @@
       </x:c>
       <x:c r="B38" s="11"/>
       <x:c r="C38" s="10" t="str">
-        <x:v>乱世繁花入君怀</x:v>
+        <x:v>烫嘴的免费午饭</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
-      <x:c r="E38" s="11" t="str"/>
+      <x:c r="E38" s="11" t="str">
+        <x:v>09-01 11:00</x:v>
+      </x:c>
       <x:c r="F38" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G38" s="11" t="str"/>
+      <x:c r="G38" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="H38" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J38" s="10" t="str"/>
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="J38" s="10" t="str">
+        <x:v>夏安安</x:v>
+      </x:c>
       <x:c r="K38" s="10" t="str"/>
     </x:row>
     <x:row r="39">
@@ -2243,28 +2249,28 @@
       </x:c>
       <x:c r="B39" s="11"/>
       <x:c r="C39" s="10" t="str">
-        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
+        <x:v>这辆车，我不伺候了</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>08-31 18:00</x:v>
+        <x:v>09-01 18:07</x:v>
       </x:c>
       <x:c r="F39" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G39" s="11" t="n">
-        <x:v>457</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
-        <x:v>江屿动漫</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="K39" s="10" t="str"/>
     </x:row>
@@ -2274,28 +2280,28 @@
       </x:c>
       <x:c r="B40" s="11"/>
       <x:c r="C40" s="10" t="str">
-        <x:v>烫嘴的免费午饭</x:v>
+        <x:v>重生80：十斤大米娶媳妇</x:v>
       </x:c>
       <x:c r="D40" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>09-01 11:00</x:v>
+        <x:v>09-01 06:30</x:v>
       </x:c>
       <x:c r="F40" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J40" s="10" t="str">
-        <x:v>夏安安</x:v>
+        <x:v>白尘</x:v>
       </x:c>
       <x:c r="K40" s="10" t="str"/>
     </x:row>
@@ -2305,28 +2311,28 @@
       </x:c>
       <x:c r="B41" s="11"/>
       <x:c r="C41" s="10" t="str">
-        <x:v>五年归期：我的崽成了团宠</x:v>
+        <x:v>我有六个黄毛爹</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="F41" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G41" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H41" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J41" s="10" t="str">
-        <x:v>言安剧场</x:v>
+        <x:v>闪闪动漫社</x:v>
       </x:c>
       <x:c r="K41" s="10" t="str"/>
     </x:row>
@@ -2336,28 +2342,28 @@
       </x:c>
       <x:c r="B42" s="11"/>
       <x:c r="C42" s="10" t="str">
-        <x:v>跨物种相亲，我连夜扛着冰山跑路</x:v>
+        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
-        <x:v>08-30 15:07</x:v>
+        <x:v>09-01 10:54</x:v>
       </x:c>
       <x:c r="F42" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G42" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H42" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="J42" s="10" t="str">
-        <x:v>菁禾</x:v>
+        <x:v>一漳动漫</x:v>
       </x:c>
       <x:c r="K42" s="10" t="str"/>
     </x:row>
@@ -2367,28 +2373,28 @@
       </x:c>
       <x:c r="B43" s="11"/>
       <x:c r="C43" s="10" t="str">
-        <x:v>当妈妈开始较真的时候</x:v>
+        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
       </x:c>
       <x:c r="D43" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E43" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
+        <x:v>08-31 18:00</x:v>
       </x:c>
       <x:c r="F43" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G43" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="H43" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="J43" s="10" t="str">
-        <x:v>小圆子剧场</x:v>
+        <x:v>江屿动漫</x:v>
       </x:c>
       <x:c r="K43" s="10" t="str"/>
     </x:row>
@@ -2398,28 +2404,28 @@
       </x:c>
       <x:c r="B44" s="11"/>
       <x:c r="C44" s="10" t="str">
-        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
+        <x:v>当妈妈开始较真的时候</x:v>
       </x:c>
       <x:c r="D44" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E44" s="11" t="str">
-        <x:v>09-01 10:54</x:v>
+        <x:v>09-01 09:00</x:v>
       </x:c>
       <x:c r="F44" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G44" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H44" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J44" s="10" t="str">
-        <x:v>一漳动漫</x:v>
+        <x:v>小圆子剧场</x:v>
       </x:c>
       <x:c r="K44" s="10" t="str"/>
     </x:row>
@@ -2429,28 +2435,28 @@
       </x:c>
       <x:c r="B45" s="11"/>
       <x:c r="C45" s="10" t="str">
-        <x:v>满堂寿宴皆虚情</x:v>
+        <x:v>深宫重华录</x:v>
       </x:c>
       <x:c r="D45" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
+        <x:v>09-01 17:45</x:v>
       </x:c>
       <x:c r="F45" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G45" s="11" t="n">
-        <x:v>90</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H45" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J45" s="10" t="str">
-        <x:v>饺子动画</x:v>
+        <x:v>蓝语</x:v>
       </x:c>
       <x:c r="K45" s="10" t="str"/>
     </x:row>
@@ -2491,28 +2497,28 @@
       </x:c>
       <x:c r="B47" s="11"/>
       <x:c r="C47" s="10" t="str">
-        <x:v>深宫重华录</x:v>
+        <x:v>五年归期：我的崽成了团宠</x:v>
       </x:c>
       <x:c r="D47" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E47" s="11" t="str">
-        <x:v>09-01 17:45</x:v>
+        <x:v>09-01 09:00</x:v>
       </x:c>
       <x:c r="F47" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G47" s="11" t="n">
-        <x:v>141</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H47" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J47" s="10" t="str">
-        <x:v>蓝语</x:v>
+        <x:v>言安剧场</x:v>
       </x:c>
       <x:c r="K47" s="10" t="str"/>
     </x:row>
@@ -2522,29 +2528,23 @@
       </x:c>
       <x:c r="B48" s="11"/>
       <x:c r="C48" s="10" t="str">
-        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
+        <x:v>乱世繁花入君怀</x:v>
       </x:c>
       <x:c r="D48" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
-      <x:c r="E48" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
-      </x:c>
+      <x:c r="E48" s="11" t="str"/>
       <x:c r="F48" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G48" s="11" t="n">
-        <x:v>52</x:v>
-      </x:c>
+      <x:c r="G48" s="11" t="str"/>
       <x:c r="H48" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="J48" s="10" t="str">
-        <x:v>白桃剧场</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="J48" s="10" t="str"/>
       <x:c r="K48" s="10" t="str"/>
     </x:row>
     <x:row r="49">
@@ -2553,32 +2553,30 @@
       </x:c>
       <x:c r="B49" s="11"/>
       <x:c r="C49" s="10" t="str">
-        <x:v>梦醒八零年</x:v>
+        <x:v>跨物种相亲，我连夜扛着冰山跑路</x:v>
       </x:c>
       <x:c r="D49" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E49" s="11" t="str">
-        <x:v>09-01 17:28</x:v>
+        <x:v>08-30 15:07</x:v>
       </x:c>
       <x:c r="F49" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G49" s="11" t="n">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H49" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I49" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J49" s="10" t="str">
-        <x:v>阿釉说漫</x:v>
-      </x:c>
-      <x:c r="K49" s="10" t="str">
-        <x:v>方鹤安从一场预示悲剧的旧梦里醒来，回到八十年代。知晓前世遭遇的他，断然拒绝了夏妍菲的提亲，决心夺回求学的机会。面对夏妍菲处处偏袒青梅竹马的种种行为，方鹤安不再一味迁就忍让，守住自己的底线。几番波折过后，他如愿走进大学校园，结识了品性真诚的顾清依。他彻底放下过往的情感执念，认真经营当下的生活，两人互相理解扶持，跨过岁月里的重重阻碍，最终收获安稳又甜蜜的幸福。</x:v>
-      </x:c>
+        <x:v>菁禾</x:v>
+      </x:c>
+      <x:c r="K49" s="10" t="str"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="11" t="str">
@@ -2586,28 +2584,28 @@
       </x:c>
       <x:c r="B50" s="11"/>
       <x:c r="C50" s="10" t="str">
-        <x:v>我自杀猪匠登圣</x:v>
+        <x:v>满堂寿宴皆虚情</x:v>
       </x:c>
       <x:c r="D50" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E50" s="11" t="str">
-        <x:v>08-31 21:08</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="F50" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G50" s="11" t="n">
-        <x:v>201</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H50" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="I50" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="J50" s="10" t="str">
-        <x:v>布夭莲_</x:v>
+        <x:v>饺子动画</x:v>
       </x:c>
       <x:c r="K50" s="10" t="str"/>
     </x:row>
@@ -2617,28 +2615,28 @@
       </x:c>
       <x:c r="B51" s="11"/>
       <x:c r="C51" s="10" t="str">
-        <x:v>万界轮回，我有亿万神话词条加身</x:v>
+        <x:v>当爸爸终于看见我</x:v>
       </x:c>
       <x:c r="D51" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E51" s="11" t="str">
-        <x:v>08-31 13:17</x:v>
+        <x:v>09-01 06:16</x:v>
       </x:c>
       <x:c r="F51" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G51" s="11" t="n">
-        <x:v>195</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H51" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="I51" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J51" s="10" t="str">
-        <x:v>云间漫剧-零七</x:v>
+        <x:v>小何故事会</x:v>
       </x:c>
       <x:c r="K51" s="10" t="str"/>
     </x:row>
@@ -2648,28 +2646,28 @@
       </x:c>
       <x:c r="B52" s="11"/>
       <x:c r="C52" s="10" t="str">
-        <x:v>这一次，换我保护妈妈</x:v>
+        <x:v>万界轮回，我有亿万神话词条加身</x:v>
       </x:c>
       <x:c r="D52" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E52" s="11" t="str">
-        <x:v>09-01 08:00</x:v>
+        <x:v>08-31 13:17</x:v>
       </x:c>
       <x:c r="F52" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G52" s="11" t="n">
-        <x:v>63</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H52" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I52" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷 / 战神异能</x:v>
       </x:c>
       <x:c r="J52" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
+        <x:v>云间漫剧-零七</x:v>
       </x:c>
       <x:c r="K52" s="10" t="str"/>
     </x:row>
@@ -2679,28 +2677,28 @@
       </x:c>
       <x:c r="B53" s="11"/>
       <x:c r="C53" s="10" t="str">
-        <x:v>比武招亲，我竟成了女王爷的夫婿</x:v>
+        <x:v>星光落在身边</x:v>
       </x:c>
       <x:c r="D53" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E53" s="11" t="str">
-        <x:v>08-30 07:10</x:v>
+        <x:v>09-01 14:30</x:v>
       </x:c>
       <x:c r="F53" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G53" s="11" t="n">
-        <x:v>315</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H53" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="I53" s="10" t="str">
-        <x:v>古装宫廷 / 婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="J53" s="10" t="str">
-        <x:v>诺威剧场</x:v>
+        <x:v>熬夜视界</x:v>
       </x:c>
       <x:c r="K53" s="10" t="str"/>
     </x:row>
@@ -2710,28 +2708,28 @@
       </x:c>
       <x:c r="B54" s="11"/>
       <x:c r="C54" s="10" t="str">
-        <x:v>她契约的都是星际大佬</x:v>
+        <x:v>这一次，换我保护妈妈</x:v>
       </x:c>
       <x:c r="D54" s="11" t="str">
-        <x:v>2026-09-01</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
-        <x:v>08-31 10:00</x:v>
+        <x:v>09-01 08:00</x:v>
       </x:c>
       <x:c r="F54" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G54" s="11" t="n">
-        <x:v>141</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="J54" s="10" t="str">
-        <x:v>阅友动漫</x:v>
+        <x:v>芙浚动漫短剧</x:v>
       </x:c>
       <x:c r="K54" s="10" t="str"/>
     </x:row>
@@ -2741,30 +2739,32 @@
       </x:c>
       <x:c r="B55" s="11"/>
       <x:c r="C55" s="10" t="str">
-        <x:v>镇北少帅</x:v>
+        <x:v>梦醒八零年</x:v>
       </x:c>
       <x:c r="D55" s="11" t="str">
         <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
-        <x:v>08-26 16:06</x:v>
+        <x:v>09-01 17:28</x:v>
       </x:c>
       <x:c r="F55" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G55" s="11" t="n">
-        <x:v>144</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>年代怀旧</x:v>
       </x:c>
       <x:c r="J55" s="10" t="str">
-        <x:v>灵梦剧场</x:v>
-      </x:c>
-      <x:c r="K55" s="10" t="str"/>
+        <x:v>阿釉说漫</x:v>
+      </x:c>
+      <x:c r="K55" s="10" t="str">
+        <x:v>方鹤安从一场预示悲剧的旧梦里醒来，回到八十年代。知晓前世遭遇的他，断然拒绝了夏妍菲的提亲，决心夺回求学的机会。面对夏妍菲处处偏袒青梅竹马的种种行为，方鹤安不再一味迁就忍让，守住自己的底线。几番波折过后，他如愿走进大学校园，结识了品性真诚的顾清依。他彻底放下过往的情感执念，认真经营当下的生活，两人互相理解扶持，跨过岁月里的重重阻碍，最终收获安稳又甜蜜的幸福。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12690,10 +12690,10 @@
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>42.7%</x:v>
+        <x:v>42.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -12701,7 +12701,7 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>287</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>30.9%</x:v>
@@ -12712,10 +12712,10 @@
         <x:v>仿真人</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>245</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>26.4%</x:v>
+        <x:v>26.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -12739,7 +12739,7 @@
         <x:v>30-49集</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
         <x:v>12.3%</x:v>
@@ -12750,10 +12750,10 @@
         <x:v>50-79集</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>399</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>43.2%</x:v>
+        <x:v>43.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -12761,7 +12761,7 @@
         <x:v>80-99集</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
         <x:v>11.4%</x:v>
@@ -12772,10 +12772,10 @@
         <x:v>100集以上</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>305</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>33%</x:v>
+        <x:v>32.9%</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -12799,7 +12799,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>375</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>40.4%</x:v>
@@ -12810,7 +12810,7 @@
         <x:v>婚姻/情感</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C17" s="11" t="str">
         <x:v>18.3%</x:v>
@@ -12824,7 +12824,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="11" t="str">
-        <x:v>10.4%</x:v>
+        <x:v>10.3%</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -12835,7 +12835,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="C19" s="11" t="str">
-        <x:v>9.9%</x:v>
+        <x:v>9.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -12846,7 +12846,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="C20" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>8.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -12854,10 +12854,10 @@
         <x:v>战神/异能/爽文</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C21" s="11" t="str">
-        <x:v>8.4%</x:v>
+        <x:v>8.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -12865,10 +12865,10 @@
         <x:v>现实反转/人性</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C22" s="11" t="str">
-        <x:v>7.0%</x:v>
+        <x:v>7.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -12876,32 +12876,32 @@
         <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C23" s="11" t="str">
-        <x:v>6.5%</x:v>
+        <x:v>6.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>逆袭/打脸</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="C24" s="11" t="str">
-        <x:v>5.2%</x:v>
+        <x:v>5.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="10" t="str">
-        <x:v>逆袭/打脸</x:v>
+        <x:v>都市职场</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C25" s="11" t="str">
-        <x:v>5.0%</x:v>
+        <x:v>5.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -13005,7 +13005,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
-        <x:v>0.8%</x:v>
+        <x:v>0.7%</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -13013,10 +13013,10 @@
         <x:v>上榜12次</x:v>
       </x:c>
       <x:c r="B37" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C37" s="11" t="str">
-        <x:v>0.4%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -13024,10 +13024,10 @@
         <x:v>上榜11次</x:v>
       </x:c>
       <x:c r="B38" s="11" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C38" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -13038,7 +13038,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="11" t="str">
-        <x:v>0.9%</x:v>
+        <x:v>0.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -13057,10 +13057,10 @@
         <x:v>上榜8次</x:v>
       </x:c>
       <x:c r="B41" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C41" s="11" t="str">
-        <x:v>1.7%</x:v>
+        <x:v>1.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -13068,10 +13068,10 @@
         <x:v>上榜7次</x:v>
       </x:c>
       <x:c r="B42" s="11" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C42" s="11" t="str">
-        <x:v>2.7%</x:v>
+        <x:v>2.5%</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -13079,7 +13079,7 @@
         <x:v>上榜6次</x:v>
       </x:c>
       <x:c r="B43" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C43" s="11" t="str">
         <x:v>4.1%</x:v>
@@ -13090,10 +13090,10 @@
         <x:v>上榜5次</x:v>
       </x:c>
       <x:c r="B44" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C44" s="11" t="str">
-        <x:v>4.3%</x:v>
+        <x:v>4.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -13112,10 +13112,10 @@
         <x:v>上榜3次</x:v>
       </x:c>
       <x:c r="B46" s="11" t="n">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C46" s="11" t="str">
-        <x:v>8.7%</x:v>
+        <x:v>9.0%</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -13123,10 +13123,10 @@
         <x:v>上榜2次</x:v>
       </x:c>
       <x:c r="B47" s="11" t="n">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C47" s="11" t="str">
-        <x:v>18.9%</x:v>
+        <x:v>18.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -13134,10 +13134,10 @@
         <x:v>上榜1次</x:v>
       </x:c>
       <x:c r="B48" s="11" t="n">
-        <x:v>457</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C48" s="11" t="str">
-        <x:v>49.2%</x:v>
+        <x:v>49.8%</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="22" customHeight="1">
@@ -13161,10 +13161,10 @@
         <x:v>CP自营</x:v>
       </x:c>
       <x:c r="B52" s="11" t="n">
-        <x:v>912</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="C52" s="11" t="str">
-        <x:v>98.2%</x:v>
+        <x:v>98.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -13172,10 +13172,10 @@
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="B53" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C53" s="11" t="str">
-        <x:v>1.0%</x:v>
+        <x:v>1.1%</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -13224,7 +13224,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C59" s="11" t="str">
-        <x:v>1.5%</x:v>
+        <x:v>1.4%</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -13378,7 +13378,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C73" s="11" t="str">
-        <x:v>0.7%</x:v>
+        <x:v>0.6%</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="22" customHeight="1">

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R0667ea9cb5ae4b34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R590f90448f654e7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Rc6c84dc6118d448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="Rbec79490fd954556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R222a54788ad74f8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R5e91c49289dd49a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R6427eba9ee594cf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R92d89996a19c4b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R2cc8082d821340cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R75f8d37f08b94dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R364ec8e940564798"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R0c6c52f32a974c40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1049,16 +1049,18 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="50" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="7" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -1066,1705 +1068,1359 @@
         <x:v>类型</x:v>
       </x:c>
       <x:c r="B1" t="str">
-        <x:v>排名</x:v>
+        <x:v>最新排名</x:v>
       </x:c>
       <x:c r="C1" t="str">
         <x:v>剧名</x:v>
       </x:c>
       <x:c r="D1" t="str">
-        <x:v>首次上榜</x:v>
+        <x:v>上线/首榜</x:v>
       </x:c>
       <x:c r="E1" t="str">
-        <x:v>预计上线</x:v>
+        <x:v>上期排名</x:v>
       </x:c>
       <x:c r="F1" t="str">
-        <x:v>上榜次数</x:v>
+        <x:v>变化</x:v>
       </x:c>
       <x:c r="G1" t="str">
+        <x:v>上榜期数</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>连续期数</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
         <x:v>集数</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="J1" t="str">
         <x:v>制作风格</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="K1" t="str">
         <x:v>主题分类</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="L1" t="str">
         <x:v>发布账号</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="M1" t="str">
         <x:v>简介</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B2" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
       <x:c r="C2" s="10" t="str">
-        <x:v>六万不到账，五十桌不开席</x:v>
+        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>09-02 19:00</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>08-31 20:00</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str"/>
+      <x:c r="F2" s="11" t="str"/>
       <x:c r="G2" s="11" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H2" s="10" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str">
-        <x:v>云起剧场</x:v>
-      </x:c>
-      <x:c r="K2" s="10" t="str"/>
+      <x:c r="K2" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="str">
+        <x:v>马克动漫</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B3" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>靠山屯纪事</x:v>
+        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="str">
-        <x:v>09-02 15:00</x:v>
-      </x:c>
-      <x:c r="F3" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 10:00</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str"/>
+      <x:c r="F3" s="11" t="str"/>
       <x:c r="G3" s="11" t="n">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H3" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I3" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="n">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
-        <x:v>小小动画</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>穿越到七十年代的花昭，重生在肥胖的少女身上。她凭借一身胆识与偶然得到的宝物，改变自身境遇，巧妙化解亲戚的算计纠缠。抓住时代机遇带动村里发展副业，改善一家人的生活。与军人叶深结缘，意外迎来新的小生命。面对原生家庭的复杂纠葛，她保持清醒，护住爷爷与至亲，在艰苦的年代里脚踏实地，靠着智慧和韧性，一步步打拼出属于自己的安稳人生。</x:v>
-      </x:c>
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="L3" s="11" t="str">
+        <x:v>白桃剧场</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B4" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>你让我出海：我一船货卖二十万你慌什么</x:v>
+        <x:v>烫嘴的免费午饭</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="str">
-        <x:v>09-02 09:05</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 11:00</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str"/>
+      <x:c r="F4" s="11" t="str"/>
       <x:c r="G4" s="11" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H4" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I4" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="n">
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
-        <x:v>呼哈短剧</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L4" s="11" t="str">
+        <x:v>夏安安</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B5" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>一碗热饭暖人性</x:v>
+        <x:v>这辆车，我不伺候了</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>09-03 00:06</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 18:07</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str"/>
+      <x:c r="F5" s="11" t="str"/>
       <x:c r="G5" s="11" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="n">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>第九幕</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L5" s="11" t="str">
+        <x:v>腿毛漫漫</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B6" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>盛海风云</x:v>
+        <x:v>重生80：十斤大米娶媳妇</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="str">
-        <x:v>09-02 09:58</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 06:30</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str"/>
+      <x:c r="F6" s="11" t="str"/>
       <x:c r="G6" s="11" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H6" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I6" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="n">
+        <x:v>208</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>星间漫步</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
-        <x:v>八十岁的千亿级盛海财团创始人林晚秋重生回到董事会召开前夕，当场罢免为私情撕毁百亿合作协议的嫡孙顾景辰，召回蛰伏非洲的铁血庶孙顾景深，布下代码陷阱精准反制宿敌耀星科技的商业间谍阴谋，以铁血手腕守护集团基业，顺利完成新老权力交接。</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="str">
+        <x:v>白尘</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B7" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="n">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>宴席终散人归远</x:v>
+        <x:v>我有六个黄毛爹</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>09-01 20:18</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 10:00</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str"/>
+      <x:c r="F7" s="11" t="str"/>
       <x:c r="G7" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H7" s="10" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J7" s="10" t="str">
-        <x:v>柚子吖</x:v>
-      </x:c>
-      <x:c r="K7" s="10" t="str"/>
+      <x:c r="K7" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L7" s="11" t="str">
+        <x:v>闪闪动漫社</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B8" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>爹爹入赘我暴富啦</x:v>
+        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>09-02 00:20</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 10:54</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str"/>
+      <x:c r="F8" s="11" t="str"/>
       <x:c r="G8" s="11" t="n">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H8" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I8" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="n">
+        <x:v>184</x:v>
       </x:c>
       <x:c r="J8" s="10" t="str">
-        <x:v>每日沙雕推荐</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K8" s="10" t="str">
-        <x:v>沈明珠看着母亲决绝离去，姐姐执意奔赴城里。她灵机一动，主动给父亲说媒，让父亲入赘彪悍女猎户钱三妞。她凭借前世记忆得到祖传的灵泉玉佩，和三位性格迥异的继兄相处融洽。一家人齐心对抗难缠的街坊对手，揭穿坏人的伪装，齐心协力把小日子过得红火安稳。</x:v>
-      </x:c>
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="L8" s="11" t="str">
+        <x:v>一漳动漫</x:v>
+      </x:c>
+      <x:c r="M8" s="10" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B9" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="n">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>被遗忘的股票账户</x:v>
+        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str">
-        <x:v>09-02 06:17</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>08-31 18:00</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str"/>
+      <x:c r="F9" s="11" t="str"/>
       <x:c r="G9" s="11" t="n">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H9" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I9" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="n">
+        <x:v>457</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>新漫剧场</x:v>
-      </x:c>
-      <x:c r="K9" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K9" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="str">
+        <x:v>江屿动漫</x:v>
+      </x:c>
+      <x:c r="M9" s="10" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B10" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="n">
+        <x:v>34</x:v>
+      </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>洋媳妇勇闯东北老家</x:v>
+        <x:v>当妈妈开始较真的时候</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="str">
-        <x:v>09-02 16:00</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 09:00</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="11" t="str"/>
       <x:c r="G10" s="11" t="n">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H10" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I10" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="n">
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>云间漫剧-十六</x:v>
-      </x:c>
-      <x:c r="K10" s="10" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K10" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="str">
+        <x:v>小圆子剧场</x:v>
+      </x:c>
+      <x:c r="M10" s="10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B11" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="n">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>遗落在村口的春天</x:v>
+        <x:v>深宫重华录</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="str">
-        <x:v>09-02 10:37</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 17:45</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str"/>
+      <x:c r="F11" s="11" t="str"/>
       <x:c r="G11" s="11" t="n">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H11" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="n">
+        <x:v>141</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>奇迹短剧</x:v>
-      </x:c>
-      <x:c r="K11" s="10" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K11" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L11" s="11" t="str">
+        <x:v>蓝语</x:v>
+      </x:c>
+      <x:c r="M11" s="10" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B12" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>一碗牛肉板面的良心账</x:v>
+        <x:v>细雨如春，替嫁得良缘</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="str">
-        <x:v>08-31 08:18</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-02 08:00</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str"/>
+      <x:c r="F12" s="11" t="str"/>
       <x:c r="G12" s="11" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H12" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I12" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>朵朵漫</x:v>
-      </x:c>
-      <x:c r="K12" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K12" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L12" s="11" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
+      <x:c r="M12" s="10" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B13" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="n">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>雨天无敌之神也想过退休生活</x:v>
+        <x:v>五年归期：我的崽成了团宠</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="str">
-        <x:v>09-02 15:00</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 09:00</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str"/>
+      <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H13" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I13" s="10" t="str">
-        <x:v>逆袭打脸 / 战神异能</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>晓晓的创作</x:v>
-      </x:c>
-      <x:c r="K13" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="K13" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="str">
+        <x:v>言安剧场</x:v>
+      </x:c>
+      <x:c r="M13" s="10" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B14" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="n">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>洪伟的故事</x:v>
+        <x:v>乱世繁花入君怀</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="str">
-        <x:v>09-02 09:53</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str"/>
+      <x:c r="F14" s="11" t="str"/>
       <x:c r="G14" s="11" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H14" s="10" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str"/>
+      <x:c r="J14" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="I14" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J14" s="10" t="str">
-        <x:v>淑芬动画</x:v>
-      </x:c>
-      <x:c r="K14" s="10" t="str"/>
+      <x:c r="K14" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="str"/>
+      <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B15" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>一碟辣椒引出人心账</x:v>
+        <x:v>满堂寿宴皆虚情</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="str">
-        <x:v>09-02 11:30</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 10:00</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str"/>
+      <x:c r="F15" s="11" t="str"/>
       <x:c r="G15" s="11" t="n">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H15" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I15" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="n">
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J15" s="10" t="str">
-        <x:v>洛川漫剧</x:v>
-      </x:c>
-      <x:c r="K15" s="10" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K15" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="str">
+        <x:v>饺子动画</x:v>
+      </x:c>
+      <x:c r="M15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B16" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="n">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>外婆的小心思</x:v>
+        <x:v>这一次，换我保护妈妈</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="str">
-        <x:v>09-01 11:22</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>09-01 08:00</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str"/>
+      <x:c r="F16" s="11" t="str"/>
       <x:c r="G16" s="11" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H16" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I16" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="n">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J16" s="10" t="str">
-        <x:v>奇境剧场</x:v>
-      </x:c>
-      <x:c r="K16" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K16" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="str">
+        <x:v>芙浚动漫短剧</x:v>
+      </x:c>
+      <x:c r="M16" s="10" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B17" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="n">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="C17" s="10" t="str">
-        <x:v>餐桌上的河豚</x:v>
+        <x:v>梦醒八零年</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>2026-09-03</x:v>
+        <x:v>09-01 17:28</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str"/>
-      <x:c r="F17" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="str"/>
-      <x:c r="H17" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I17" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J17" s="10" t="str"/>
-      <x:c r="K17" s="10" t="str"/>
+      <x:c r="F17" s="11" t="str"/>
+      <x:c r="G17" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="J17" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K17" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="L17" s="11" t="str">
+        <x:v>阿釉说漫</x:v>
+      </x:c>
+      <x:c r="M17" s="10" t="str">
+        <x:v>方鹤安从一场预示悲剧的旧梦里醒来，回到八十年代。知晓前世遭遇的他，断然拒绝了夏妍菲的提亲，决心夺回求学的机会。面对夏妍菲处处偏袒青梅竹马的种种行为，方鹤安不再一味迁就忍让，守住自己的底线。几番波折过后，他如愿走进大学校园，结识了品性真诚的顾清依。他彻底放下过往的情感执念，认真经营当下的生活，两人互相理解扶持，跨过岁月里的重重阻碍，最终收获安稳又甜蜜的幸福。</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B18" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="n">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="C18" s="10" t="str">
-        <x:v>一块钱买来的妈妈</x:v>
+        <x:v>万界轮回，我有亿万神话词条加身</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="str">
-        <x:v>09-02 01:57</x:v>
-      </x:c>
-      <x:c r="F18" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>08-31 13:17</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str"/>
+      <x:c r="F18" s="11" t="str"/>
       <x:c r="G18" s="11" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H18" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I18" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:v>195</x:v>
       </x:c>
       <x:c r="J18" s="10" t="str">
-        <x:v>阿南影视</x:v>
-      </x:c>
-      <x:c r="K18" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K18" s="10" t="str">
+        <x:v>古装宫廷 / 战神异能</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="str">
+        <x:v>云间漫剧-零七</x:v>
+      </x:c>
+      <x:c r="M18" s="10" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B19" s="11"/>
+        <x:v>持续在榜</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="n">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="C19" s="10" t="str">
-        <x:v>神魔伴我镇北凉</x:v>
+        <x:v>大婚当日立规矩，这婚我不结了</x:v>
       </x:c>
       <x:c r="D19" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="str">
-        <x:v>09-02 10:00</x:v>
-      </x:c>
-      <x:c r="F19" s="11" t="n">
+        <x:v>08-31 17:00</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="str"/>
+      <x:c r="F19" s="11" t="str"/>
+      <x:c r="G19" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="n">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H19" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I19" s="10" t="str">
-        <x:v>战神异能</x:v>
+      <x:c r="I19" s="11" t="n">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J19" s="10" t="str">
-        <x:v>史小怪</x:v>
-      </x:c>
-      <x:c r="K19" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="K19" s="10" t="str">
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L19" s="11" t="str">
+        <x:v>云影漫剧</x:v>
+      </x:c>
+      <x:c r="M19" s="10" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B20" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>谁动了我的成绩</x:v>
+        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="str">
-        <x:v>09-02 18:06</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H20" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I20" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>09-01 10:00</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="str">
+        <x:v>↑55位</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="str"/>
+      <x:c r="H20" s="11" t="str"/>
+      <x:c r="I20" s="11" t="n">
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
-        <x:v>故事里</x:v>
-      </x:c>
-      <x:c r="K20" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K20" s="10" t="str">
+        <x:v>古装宫廷</x:v>
+      </x:c>
+      <x:c r="L20" s="11" t="str">
+        <x:v>白桃剧场</x:v>
+      </x:c>
+      <x:c r="M20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B21" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="n">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>他们霸占我的房结婚，我反手卖掉</x:v>
+        <x:v>爹爹入赘我暴富啦</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="str">
-        <x:v>09-02 00:06</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H21" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I21" s="10" t="str">
-        <x:v>婚姻情感 / 逆袭打脸</x:v>
+        <x:v>09-02 00:20</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="str">
+        <x:v>↑44位</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="str"/>
+      <x:c r="H21" s="11" t="str"/>
+      <x:c r="I21" s="11" t="n">
+        <x:v>121</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
-        <x:v>金秋剧场</x:v>
-      </x:c>
-      <x:c r="K21" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K21" s="10" t="str">
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="str">
+        <x:v>每日沙雕推荐</x:v>
+      </x:c>
+      <x:c r="M21" s="10" t="str">
+        <x:v>沈明珠看着母亲决绝离去，姐姐执意奔赴城里。她灵机一动，主动给父亲说媒，让父亲入赘彪悍女猎户钱三妞。她凭借前世记忆得到祖传的灵泉玉佩，和三位性格迥异的继兄相处融洽。一家人齐心对抗难缠的街坊对手，揭穿坏人的伪装，齐心协力把小日子过得红火安稳。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B22" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="n">
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>两个儿子护我归家</x:v>
+        <x:v>洪伟的故事</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="str">
-        <x:v>08-31 18:24</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="n">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H22" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I22" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>09-02 09:53</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="str">
+        <x:v>↑41位</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="str"/>
+      <x:c r="H22" s="11" t="str"/>
+      <x:c r="I22" s="11" t="n">
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>桑园小剧场</x:v>
-      </x:c>
-      <x:c r="K22" s="10" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K22" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L22" s="11" t="str">
+        <x:v>淑芬动画</x:v>
+      </x:c>
+      <x:c r="M22" s="10" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B23" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="n">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>一念清醒万山开</x:v>
+        <x:v>洋媳妇勇闯东北老家</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="str">
-        <x:v>07-24 10:00</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H23" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I23" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>09-02 16:00</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="str">
+        <x:v>↑29位</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="str"/>
+      <x:c r="H23" s="11" t="str"/>
+      <x:c r="I23" s="11" t="n">
+        <x:v>154</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>必看短剧</x:v>
-      </x:c>
-      <x:c r="K23" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K23" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L23" s="11" t="str">
+        <x:v>云间漫剧-十六</x:v>
+      </x:c>
+      <x:c r="M23" s="10" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B24" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="C24" s="10" t="str">
-        <x:v>离婚后我万丈荣光</x:v>
+        <x:v>烫嘴的免费午饭</x:v>
       </x:c>
       <x:c r="D24" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="str">
-        <x:v>09-02 18:00</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G24" s="11" t="n">
+        <x:v>09-01 11:00</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>↑22位</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="str"/>
+      <x:c r="H24" s="11" t="str"/>
+      <x:c r="I24" s="11" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H24" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I24" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
       <x:c r="J24" s="10" t="str">
-        <x:v>平阅漫漫看</x:v>
-      </x:c>
-      <x:c r="K24" s="10" t="str"/>
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K24" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L24" s="11" t="str">
+        <x:v>夏安安</x:v>
+      </x:c>
+      <x:c r="M24" s="10" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B25" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="n">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>我什么都没干，却成了大功臣</x:v>
+        <x:v>遗落在村口的春天</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="str">
-        <x:v>09-01 17:32</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H25" s="10" t="str">
+        <x:v>09-02 10:37</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>↑21位</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="str"/>
+      <x:c r="H25" s="11" t="str"/>
+      <x:c r="I25" s="11" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="J25" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I25" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J25" s="10" t="str">
-        <x:v>小姐姐追漫画</x:v>
-      </x:c>
-      <x:c r="K25" s="10" t="str"/>
+      <x:c r="K25" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L25" s="11" t="str">
+        <x:v>奇迹短剧</x:v>
+      </x:c>
+      <x:c r="M25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B26" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B26" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>退掉三十块水闸费，旱涝淹醒全村人</x:v>
+        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="str">
-        <x:v>08-22 17:49</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H26" s="10" t="str">
+        <x:v>09-01 10:54</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>↑19位</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="str"/>
+      <x:c r="H26" s="11" t="str"/>
+      <x:c r="I26" s="11" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J26" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I26" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J26" s="10" t="str">
-        <x:v>小林剧场</x:v>
-      </x:c>
-      <x:c r="K26" s="10" t="str"/>
+      <x:c r="K26" s="10" t="str">
+        <x:v>年代怀旧</x:v>
+      </x:c>
+      <x:c r="L26" s="11" t="str">
+        <x:v>一漳动漫</x:v>
+      </x:c>
+      <x:c r="M26" s="10" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B27" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B27" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>母亲的难题</x:v>
+        <x:v>盛海风云</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E27" s="11" t="str">
-        <x:v>07-08 10:00</x:v>
-      </x:c>
-      <x:c r="F27" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G27" s="11" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H27" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>09-02 09:58</x:v>
+      </x:c>
+      <x:c r="E27" s="11" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>↑18位</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="str"/>
+      <x:c r="H27" s="11" t="str"/>
+      <x:c r="I27" s="11" t="n">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>久久剧场</x:v>
-      </x:c>
-      <x:c r="K27" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K27" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L27" s="11" t="str">
+        <x:v>星间漫步</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str">
+        <x:v>八十岁的千亿级盛海财团创始人林晚秋重生回到董事会召开前夕，当场罢免为私情撕毁百亿合作协议的嫡孙顾景辰，召回蛰伏非洲的铁血庶孙顾景深，布下代码陷阱精准反制宿敌耀星科技的商业间谍阴谋，以铁血手腕守护集团基业，顺利完成新老权力交接。</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B28" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B28" s="11" t="n">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>流放厨娘，我靠美食绝地翻盘记</x:v>
+        <x:v>深宫重华录</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E28" s="11" t="str">
-        <x:v>08-31 10:00</x:v>
-      </x:c>
-      <x:c r="F28" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G28" s="11" t="n">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H28" s="10" t="str">
+        <x:v>09-01 17:45</x:v>
+      </x:c>
+      <x:c r="E28" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>↑17位</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="str"/>
+      <x:c r="H28" s="11" t="str"/>
+      <x:c r="I28" s="11" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J28" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
-      <x:c r="I28" s="10" t="str">
-        <x:v>美食治愈 / 逆袭打脸</x:v>
-      </x:c>
-      <x:c r="J28" s="10" t="str">
-        <x:v>大师兄说剧</x:v>
-      </x:c>
-      <x:c r="K28" s="10" t="str"/>
+      <x:c r="K28" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L28" s="11" t="str">
+        <x:v>蓝语</x:v>
+      </x:c>
+      <x:c r="M28" s="10" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B29" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B29" s="11" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>前妻背叛，现任竟让我原谅她</x:v>
+        <x:v>细雨如春，替嫁得良缘</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E29" s="11" t="str">
-        <x:v>08-29 13:33</x:v>
-      </x:c>
-      <x:c r="F29" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H29" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I29" s="10" t="str">
+        <x:v>09-02 08:00</x:v>
+      </x:c>
+      <x:c r="E29" s="11" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F29" s="11" t="str">
+        <x:v>↑11位</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="str"/>
+      <x:c r="H29" s="11" t="str"/>
+      <x:c r="I29" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J29" s="10" t="str">
+        <x:v>经典3D</x:v>
+      </x:c>
+      <x:c r="K29" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
-      <x:c r="J29" s="10" t="str">
-        <x:v>清禾精品剧场</x:v>
-      </x:c>
-      <x:c r="K29" s="10" t="str"/>
+      <x:c r="L29" s="11" t="str">
+        <x:v>心动漫剧场</x:v>
+      </x:c>
+      <x:c r="M29" s="10" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B30" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B30" s="11" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>七年退让到此为止</x:v>
+        <x:v>你让我出海：我一船货卖二十万你慌什么</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E30" s="11" t="str">
-        <x:v>09-01 12:00</x:v>
-      </x:c>
-      <x:c r="F30" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G30" s="11" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H30" s="10" t="str">
+        <x:v>09-02 09:05</x:v>
+      </x:c>
+      <x:c r="E30" s="11" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F30" s="11" t="str">
+        <x:v>↑10位</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="str"/>
+      <x:c r="H30" s="11" t="str"/>
+      <x:c r="I30" s="11" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="J30" s="10" t="str">
         <x:v>仿真人</x:v>
       </x:c>
-      <x:c r="I30" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J30" s="10" t="str">
-        <x:v>二妞.影视</x:v>
-      </x:c>
-      <x:c r="K30" s="10" t="str"/>
+      <x:c r="K30" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L30" s="11" t="str">
+        <x:v>呼哈短剧</x:v>
+      </x:c>
+      <x:c r="M30" s="10" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B31" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B31" s="11" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>装穷三年，我和大小姐双双掉马</x:v>
+        <x:v>靠山屯纪事</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E31" s="11" t="str">
-        <x:v>09-02 00:15</x:v>
-      </x:c>
-      <x:c r="F31" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G31" s="11" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H31" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I31" s="10" t="str">
-        <x:v>现实反转</x:v>
+        <x:v>09-02 15:00</x:v>
+      </x:c>
+      <x:c r="E31" s="11" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>↑7位</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str"/>
+      <x:c r="H31" s="11" t="str"/>
+      <x:c r="I31" s="11" t="n">
+        <x:v>168</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>星漫动漫剧场</x:v>
-      </x:c>
-      <x:c r="K31" s="10" t="str"/>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="K31" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L31" s="11" t="str">
+        <x:v>小小动画</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="str">
+        <x:v>穿越到七十年代的花昭，重生在肥胖的少女身上。她凭借一身胆识与偶然得到的宝物，改变自身境遇，巧妙化解亲戚的算计纠缠。抓住时代机遇带动村里发展副业，改善一家人的生活。与军人叶深结缘，意外迎来新的小生命。面对原生家庭的复杂纠葛，她保持清醒，护住爷爷与至亲，在艰苦的年代里脚踏实地，靠着智慧和韧性，一步步打拼出属于自己的安稳人生。</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
-        <x:v>新剧</x:v>
-      </x:c>
-      <x:c r="B32" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="n">
+        <x:v>34</x:v>
+      </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>扣我三十万，我收购你公司</x:v>
+        <x:v>当妈妈开始较真的时候</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E32" s="11" t="str">
-        <x:v>08-08 10:00</x:v>
-      </x:c>
-      <x:c r="F32" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G32" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H32" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I32" s="10" t="str">
-        <x:v>都市职场</x:v>
+        <x:v>09-01 09:00</x:v>
+      </x:c>
+      <x:c r="E32" s="11" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>↑5位</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="str"/>
+      <x:c r="H32" s="11" t="str"/>
+      <x:c r="I32" s="11" t="n">
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
-      </x:c>
-      <x:c r="K32" s="10" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K32" s="10" t="str">
+        <x:v>家庭伦理</x:v>
+      </x:c>
+      <x:c r="L32" s="11" t="str">
+        <x:v>小圆子剧场</x:v>
+      </x:c>
+      <x:c r="M32" s="10" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B33" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>让你代写情书，你落笔惊哭大儒第一季</x:v>
+        <x:v>六万不到账，五十桌不开席</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E33" s="11" t="str">
-        <x:v>07-27 11:00</x:v>
-      </x:c>
-      <x:c r="F33" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G33" s="11" t="n">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H33" s="10" t="str">
+        <x:v>09-02 19:00</x:v>
+      </x:c>
+      <x:c r="E33" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>↑4位</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str"/>
+      <x:c r="H33" s="11" t="str"/>
+      <x:c r="I33" s="11" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J33" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I33" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="J33" s="10" t="str">
-        <x:v>暖夏短剧</x:v>
-      </x:c>
-      <x:c r="K33" s="10" t="str"/>
+      <x:c r="K33" s="10" t="str">
+        <x:v>美食治愈 / 现实反转</x:v>
+      </x:c>
+      <x:c r="L33" s="11" t="str">
+        <x:v>云起剧场</x:v>
+      </x:c>
+      <x:c r="M33" s="10" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B34" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>我请客吃饭变同事家庭宴结账后同事慌了</x:v>
+        <x:v>一碗热饭暖人性</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E34" s="11" t="str">
-        <x:v>08-29 16:15</x:v>
-      </x:c>
-      <x:c r="F34" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G34" s="11" t="n">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H34" s="10" t="str">
+        <x:v>09-03 00:06</x:v>
+      </x:c>
+      <x:c r="E34" s="11" t="str"/>
+      <x:c r="F34" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="str"/>
+      <x:c r="H34" s="11" t="str"/>
+      <x:c r="I34" s="11" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J34" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I34" s="10" t="str">
-        <x:v>都市职场 / 美食治愈 / 现实反转</x:v>
-      </x:c>
-      <x:c r="J34" s="10" t="str">
-        <x:v>漫漫画丫头</x:v>
-      </x:c>
-      <x:c r="K34" s="10" t="str"/>
+      <x:c r="K34" s="10" t="str">
+        <x:v>美食治愈</x:v>
+      </x:c>
+      <x:c r="L34" s="11" t="str">
+        <x:v>第九幕</x:v>
+      </x:c>
+      <x:c r="M34" s="10" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B35" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="n">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
+        <x:v>被遗忘的股票账户</x:v>
       </x:c>
       <x:c r="D35" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E35" s="11" t="str">
-        <x:v>08-31 20:00</x:v>
-      </x:c>
-      <x:c r="F35" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G35" s="11" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H35" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I35" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>09-02 06:17</x:v>
+      </x:c>
+      <x:c r="E35" s="11" t="str"/>
+      <x:c r="F35" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str"/>
+      <x:c r="H35" s="11" t="str"/>
+      <x:c r="I35" s="11" t="n">
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J35" s="10" t="str">
-        <x:v>马克动漫</x:v>
-      </x:c>
-      <x:c r="K35" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="K35" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L35" s="11" t="str">
+        <x:v>新漫剧场</x:v>
+      </x:c>
+      <x:c r="M35" s="10" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B36" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="n">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>大婚当日立规矩，这婚我不结了</x:v>
+        <x:v>雨天无敌之神也想过退休生活</x:v>
       </x:c>
       <x:c r="D36" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E36" s="11" t="str">
-        <x:v>08-31 17:00</x:v>
-      </x:c>
-      <x:c r="F36" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G36" s="11" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H36" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I36" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>09-02 15:00</x:v>
+      </x:c>
+      <x:c r="E36" s="11" t="str"/>
+      <x:c r="F36" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G36" s="11" t="str"/>
+      <x:c r="H36" s="11" t="str"/>
+      <x:c r="I36" s="11" t="n">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J36" s="10" t="str">
-        <x:v>云影漫剧</x:v>
-      </x:c>
-      <x:c r="K36" s="10" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K36" s="10" t="str">
+        <x:v>逆袭打脸 / 战神异能</x:v>
+      </x:c>
+      <x:c r="L36" s="11" t="str">
+        <x:v>晓晓的创作</x:v>
+      </x:c>
+      <x:c r="M36" s="10" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B37" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="n">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="C37" s="10" t="str">
-        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
+        <x:v>一碟辣椒引出人心账</x:v>
       </x:c>
       <x:c r="D37" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E37" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
-      </x:c>
-      <x:c r="F37" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G37" s="11" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H37" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I37" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>09-02 11:30</x:v>
+      </x:c>
+      <x:c r="E37" s="11" t="str"/>
+      <x:c r="F37" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="str"/>
+      <x:c r="H37" s="11" t="str"/>
+      <x:c r="I37" s="11" t="n">
+        <x:v>108</x:v>
       </x:c>
       <x:c r="J37" s="10" t="str">
-        <x:v>白桃剧场</x:v>
-      </x:c>
-      <x:c r="K37" s="10" t="str"/>
+        <x:v>仿真人</x:v>
+      </x:c>
+      <x:c r="K37" s="10" t="str">
+        <x:v>现实反转</x:v>
+      </x:c>
+      <x:c r="L37" s="11" t="str">
+        <x:v>洛川漫剧</x:v>
+      </x:c>
+      <x:c r="M37" s="10" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B38" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="n">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>烫嘴的免费午饭</x:v>
+        <x:v>餐桌上的河豚</x:v>
       </x:c>
       <x:c r="D38" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E38" s="11" t="str">
-        <x:v>09-01 11:00</x:v>
-      </x:c>
-      <x:c r="F38" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G38" s="11" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H38" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I38" s="10" t="str">
-        <x:v>美食治愈</x:v>
-      </x:c>
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E38" s="11" t="str"/>
+      <x:c r="F38" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="str"/>
+      <x:c r="H38" s="11" t="str"/>
+      <x:c r="I38" s="11" t="str"/>
       <x:c r="J38" s="10" t="str">
-        <x:v>夏安安</x:v>
-      </x:c>
-      <x:c r="K38" s="10" t="str"/>
+        <x:v>未标注</x:v>
+      </x:c>
+      <x:c r="K38" s="10" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L38" s="11" t="str"/>
+      <x:c r="M38" s="10" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B39" s="11"/>
+        <x:v>新剧上升</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="n">
+        <x:v>65</x:v>
+      </x:c>
       <x:c r="C39" s="10" t="str">
-        <x:v>这辆车，我不伺候了</x:v>
+        <x:v>神魔伴我镇北凉</x:v>
       </x:c>
       <x:c r="D39" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E39" s="11" t="str">
-        <x:v>09-01 18:07</x:v>
-      </x:c>
-      <x:c r="F39" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G39" s="11" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H39" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I39" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>09-02 10:00</x:v>
+      </x:c>
+      <x:c r="E39" s="11" t="str"/>
+      <x:c r="F39" s="11" t="str">
+        <x:v>新上榜</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="str"/>
+      <x:c r="H39" s="11" t="str"/>
+      <x:c r="I39" s="11" t="n">
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J39" s="10" t="str">
-        <x:v>腿毛漫漫</x:v>
-      </x:c>
-      <x:c r="K39" s="10" t="str"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B40" s="11"/>
-      <x:c r="C40" s="10" t="str">
-        <x:v>重生80：十斤大米娶媳妇</x:v>
-      </x:c>
-      <x:c r="D40" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E40" s="11" t="str">
-        <x:v>09-01 06:30</x:v>
-      </x:c>
-      <x:c r="F40" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G40" s="11" t="n">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H40" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I40" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J40" s="10" t="str">
-        <x:v>白尘</x:v>
-      </x:c>
-      <x:c r="K40" s="10" t="str"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B41" s="11"/>
-      <x:c r="C41" s="10" t="str">
-        <x:v>我有六个黄毛爹</x:v>
-      </x:c>
-      <x:c r="D41" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E41" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
-      </x:c>
-      <x:c r="F41" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G41" s="11" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H41" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I41" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="J41" s="10" t="str">
-        <x:v>闪闪动漫社</x:v>
-      </x:c>
-      <x:c r="K41" s="10" t="str"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B42" s="11"/>
-      <x:c r="C42" s="10" t="str">
-        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
-      </x:c>
-      <x:c r="D42" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E42" s="11" t="str">
-        <x:v>09-01 10:54</x:v>
-      </x:c>
-      <x:c r="F42" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G42" s="11" t="n">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H42" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
-      <x:c r="I42" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="J42" s="10" t="str">
-        <x:v>一漳动漫</x:v>
-      </x:c>
-      <x:c r="K42" s="10" t="str"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B43" s="11"/>
-      <x:c r="C43" s="10" t="str">
-        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
-      </x:c>
-      <x:c r="D43" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E43" s="11" t="str">
-        <x:v>08-31 18:00</x:v>
-      </x:c>
-      <x:c r="F43" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G43" s="11" t="n">
-        <x:v>457</x:v>
-      </x:c>
-      <x:c r="H43" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I43" s="10" t="str">
-        <x:v>古装宫廷</x:v>
-      </x:c>
-      <x:c r="J43" s="10" t="str">
-        <x:v>江屿动漫</x:v>
-      </x:c>
-      <x:c r="K43" s="10" t="str"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B44" s="11"/>
-      <x:c r="C44" s="10" t="str">
-        <x:v>当妈妈开始较真的时候</x:v>
-      </x:c>
-      <x:c r="D44" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E44" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
-      </x:c>
-      <x:c r="F44" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G44" s="11" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H44" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I44" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="J44" s="10" t="str">
-        <x:v>小圆子剧场</x:v>
-      </x:c>
-      <x:c r="K44" s="10" t="str"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B45" s="11"/>
-      <x:c r="C45" s="10" t="str">
-        <x:v>深宫重华录</x:v>
-      </x:c>
-      <x:c r="D45" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E45" s="11" t="str">
-        <x:v>09-01 17:45</x:v>
-      </x:c>
-      <x:c r="F45" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G45" s="11" t="n">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H45" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I45" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J45" s="10" t="str">
-        <x:v>蓝语</x:v>
-      </x:c>
-      <x:c r="K45" s="10" t="str"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B46" s="11"/>
-      <x:c r="C46" s="10" t="str">
-        <x:v>细雨如春，替嫁得良缘</x:v>
-      </x:c>
-      <x:c r="D46" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E46" s="11" t="str">
-        <x:v>09-02 08:00</x:v>
-      </x:c>
-      <x:c r="F46" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G46" s="11" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H46" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I46" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="J46" s="10" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
-      <x:c r="K46" s="10" t="str"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B47" s="11"/>
-      <x:c r="C47" s="10" t="str">
-        <x:v>五年归期：我的崽成了团宠</x:v>
-      </x:c>
-      <x:c r="D47" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E47" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
-      </x:c>
-      <x:c r="F47" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G47" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H47" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I47" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="J47" s="10" t="str">
-        <x:v>言安剧场</x:v>
-      </x:c>
-      <x:c r="K47" s="10" t="str"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B48" s="11"/>
-      <x:c r="C48" s="10" t="str">
-        <x:v>乱世繁花入君怀</x:v>
-      </x:c>
-      <x:c r="D48" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E48" s="11" t="str"/>
-      <x:c r="F48" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G48" s="11" t="str"/>
-      <x:c r="H48" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I48" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J48" s="10" t="str"/>
-      <x:c r="K48" s="10" t="str"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B49" s="11"/>
-      <x:c r="C49" s="10" t="str">
-        <x:v>跨物种相亲，我连夜扛着冰山跑路</x:v>
-      </x:c>
-      <x:c r="D49" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E49" s="11" t="str">
-        <x:v>08-30 15:07</x:v>
-      </x:c>
-      <x:c r="F49" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G49" s="11" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H49" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I49" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J49" s="10" t="str">
-        <x:v>菁禾</x:v>
-      </x:c>
-      <x:c r="K49" s="10" t="str"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B50" s="11"/>
-      <x:c r="C50" s="10" t="str">
-        <x:v>满堂寿宴皆虚情</x:v>
-      </x:c>
-      <x:c r="D50" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E50" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
-      </x:c>
-      <x:c r="F50" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G50" s="11" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H50" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I50" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="J50" s="10" t="str">
-        <x:v>饺子动画</x:v>
-      </x:c>
-      <x:c r="K50" s="10" t="str"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B51" s="11"/>
-      <x:c r="C51" s="10" t="str">
-        <x:v>当爸爸终于看见我</x:v>
-      </x:c>
-      <x:c r="D51" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E51" s="11" t="str">
-        <x:v>09-01 06:16</x:v>
-      </x:c>
-      <x:c r="F51" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G51" s="11" t="n">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H51" s="10" t="str">
-        <x:v>仿真人</x:v>
-      </x:c>
-      <x:c r="I51" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="J51" s="10" t="str">
-        <x:v>小何故事会</x:v>
-      </x:c>
-      <x:c r="K51" s="10" t="str"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B52" s="11"/>
-      <x:c r="C52" s="10" t="str">
-        <x:v>万界轮回，我有亿万神话词条加身</x:v>
-      </x:c>
-      <x:c r="D52" s="11" t="str">
-        <x:v>2026-09-01</x:v>
-      </x:c>
-      <x:c r="E52" s="11" t="str">
-        <x:v>08-31 13:17</x:v>
-      </x:c>
-      <x:c r="F52" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G52" s="11" t="n">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H52" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I52" s="10" t="str">
-        <x:v>古装宫廷 / 战神异能</x:v>
-      </x:c>
-      <x:c r="J52" s="10" t="str">
-        <x:v>云间漫剧-零七</x:v>
-      </x:c>
-      <x:c r="K52" s="10" t="str"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B53" s="11"/>
-      <x:c r="C53" s="10" t="str">
-        <x:v>星光落在身边</x:v>
-      </x:c>
-      <x:c r="D53" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E53" s="11" t="str">
-        <x:v>09-01 14:30</x:v>
-      </x:c>
-      <x:c r="F53" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G53" s="11" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H53" s="10" t="str">
-        <x:v>未标注</x:v>
-      </x:c>
-      <x:c r="I53" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="J53" s="10" t="str">
-        <x:v>熬夜视界</x:v>
-      </x:c>
-      <x:c r="K53" s="10" t="str"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B54" s="11"/>
-      <x:c r="C54" s="10" t="str">
-        <x:v>这一次，换我保护妈妈</x:v>
-      </x:c>
-      <x:c r="D54" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E54" s="11" t="str">
-        <x:v>09-01 08:00</x:v>
-      </x:c>
-      <x:c r="F54" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G54" s="11" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H54" s="10" t="str">
-        <x:v>经典3D</x:v>
-      </x:c>
-      <x:c r="I54" s="10" t="str">
-        <x:v>家庭伦理</x:v>
-      </x:c>
-      <x:c r="J54" s="10" t="str">
-        <x:v>芙浚动漫短剧</x:v>
-      </x:c>
-      <x:c r="K54" s="10" t="str"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="11" t="str">
-        <x:v>次新剧</x:v>
-      </x:c>
-      <x:c r="B55" s="11"/>
-      <x:c r="C55" s="10" t="str">
-        <x:v>梦醒八零年</x:v>
-      </x:c>
-      <x:c r="D55" s="11" t="str">
-        <x:v>2026-09-02</x:v>
-      </x:c>
-      <x:c r="E55" s="11" t="str">
-        <x:v>09-01 17:28</x:v>
-      </x:c>
-      <x:c r="F55" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G55" s="11" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H55" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="I55" s="10" t="str">
-        <x:v>年代怀旧</x:v>
-      </x:c>
-      <x:c r="J55" s="10" t="str">
-        <x:v>阿釉说漫</x:v>
-      </x:c>
-      <x:c r="K55" s="10" t="str">
-        <x:v>方鹤安从一场预示悲剧的旧梦里醒来，回到八十年代。知晓前世遭遇的他，断然拒绝了夏妍菲的提亲，决心夺回求学的机会。面对夏妍菲处处偏袒青梅竹马的种种行为，方鹤安不再一味迁就忍让，守住自己的底线。几番波折过后，他如愿走进大学校园，结识了品性真诚的顾清依。他彻底放下过往的情感执念，认真经营当下的生活，两人互相理解扶持，跨过岁月里的重重阻碍，最终收获安稳又甜蜜的幸福。</x:v>
-      </x:c>
+      <x:c r="K39" s="10" t="str">
+        <x:v>战神异能</x:v>
+      </x:c>
+      <x:c r="L39" s="11" t="str">
+        <x:v>史小怪</x:v>
+      </x:c>
+      <x:c r="M39" s="10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/榜单数据.xlsx
+++ b/榜单数据.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R6427eba9ee594cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="R92d89996a19c4b2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="R2cc8082d821340cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R75f8d37f08b94dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="R364ec8e940564798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R0c6c52f32a974c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="常青榜" sheetId="1" r:id="R4e640466fd234829"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上榜的新剧" sheetId="2" r:id="Rc6c5044cdb4a4736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="老剧复投榜" sheetId="3" r:id="Ra98106c6cd1f48f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜剧数" sheetId="4" r:id="R362c1cbe5ea0457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新剧推荐·上榜次数" sheetId="5" r:id="Rbfacd79f5ac34137"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="特点统计" sheetId="6" r:id="R027bb82851d14bf8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1109,7 +1109,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B2" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="10" t="str">
         <x:v>房东赌我四千员工搬不走，三天后整栋楼空了</x:v>
@@ -1120,10 +1120,10 @@
       <x:c r="E2" s="11" t="str"/>
       <x:c r="F2" s="11" t="str"/>
       <x:c r="G2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H2" s="11" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
         <x:v>67</x:v>
@@ -1147,30 +1147,30 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="10" t="str">
-        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
+        <x:v>烫嘴的免费午饭</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
+        <x:v>09-01 11:00</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str"/>
       <x:c r="F3" s="11" t="str"/>
       <x:c r="G3" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H3" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J3" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K3" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>美食治愈</x:v>
       </x:c>
       <x:c r="L3" s="11" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>夏安安</x:v>
       </x:c>
       <x:c r="M3" s="10" t="str"/>
     </x:row>
@@ -1179,33 +1179,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B4" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>烫嘴的免费午饭</x:v>
+        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>09-01 11:00</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str"/>
       <x:c r="F4" s="11" t="str"/>
       <x:c r="G4" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H4" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J4" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K4" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L4" s="11" t="str">
-        <x:v>夏安安</x:v>
+        <x:v>白桃剧场</x:v>
       </x:c>
       <x:c r="M4" s="10" t="str"/>
     </x:row>
@@ -1214,33 +1214,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B5" s="11" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>这辆车，我不伺候了</x:v>
+        <x:v>重生80：十斤大米娶媳妇</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>09-01 18:07</x:v>
+        <x:v>09-01 06:30</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str"/>
       <x:c r="F5" s="11" t="str"/>
       <x:c r="G5" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L5" s="11" t="str">
-        <x:v>腿毛漫漫</x:v>
+        <x:v>白尘</x:v>
       </x:c>
       <x:c r="M5" s="10" t="str"/>
     </x:row>
@@ -1249,33 +1249,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>重生80：十斤大米娶媳妇</x:v>
+        <x:v>这辆车，我不伺候了</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>09-01 06:30</x:v>
+        <x:v>09-01 18:07</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str"/>
       <x:c r="F6" s="11" t="str"/>
       <x:c r="G6" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H6" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>208</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J6" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="K6" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L6" s="11" t="str">
-        <x:v>白尘</x:v>
+        <x:v>腿毛漫漫</x:v>
       </x:c>
       <x:c r="M6" s="10" t="str"/>
     </x:row>
@@ -1284,7 +1284,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>我有六个黄毛爹</x:v>
@@ -1295,10 +1295,10 @@
       <x:c r="E7" s="11" t="str"/>
       <x:c r="F7" s="11" t="str"/>
       <x:c r="G7" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H7" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
         <x:v>72</x:v>
@@ -1319,7 +1319,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
         <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
@@ -1330,10 +1330,10 @@
       <x:c r="E8" s="11" t="str"/>
       <x:c r="F8" s="11" t="str"/>
       <x:c r="G8" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H8" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
         <x:v>184</x:v>
@@ -1354,33 +1354,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
+        <x:v>当妈妈开始较真的时候</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>08-31 18:00</x:v>
+        <x:v>09-01 09:00</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str"/>
       <x:c r="F9" s="11" t="str"/>
       <x:c r="G9" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H9" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>457</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J9" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K9" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>家庭伦理</x:v>
       </x:c>
       <x:c r="L9" s="11" t="str">
-        <x:v>江屿动漫</x:v>
+        <x:v>小圆子剧场</x:v>
       </x:c>
       <x:c r="M9" s="10" t="str"/>
     </x:row>
@@ -1389,33 +1389,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B10" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>当妈妈开始较真的时候</x:v>
+        <x:v>三天后穿越古代，我贷款搬空商城！</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
+        <x:v>08-31 18:00</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str"/>
       <x:c r="F10" s="11" t="str"/>
       <x:c r="G10" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H10" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="J10" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K10" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>古装宫廷</x:v>
       </x:c>
       <x:c r="L10" s="11" t="str">
-        <x:v>小圆子剧场</x:v>
+        <x:v>江屿动漫</x:v>
       </x:c>
       <x:c r="M10" s="10" t="str"/>
     </x:row>
@@ -1424,33 +1424,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B11" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>深宫重华录</x:v>
+        <x:v>五年归期：我的崽成了团宠</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>09-01 17:45</x:v>
+        <x:v>09-01 09:00</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str"/>
       <x:c r="F11" s="11" t="str"/>
       <x:c r="G11" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H11" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>141</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J11" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="K11" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L11" s="11" t="str">
-        <x:v>蓝语</x:v>
+        <x:v>言安剧场</x:v>
       </x:c>
       <x:c r="M11" s="10" t="str"/>
     </x:row>
@@ -1459,33 +1459,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B12" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>细雨如春，替嫁得良缘</x:v>
+        <x:v>深宫重华录</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>09-02 08:00</x:v>
+        <x:v>09-01 17:45</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str"/>
       <x:c r="F12" s="11" t="str"/>
       <x:c r="G12" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H12" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I12" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="J12" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K12" s="10" t="str">
-        <x:v>婚姻情感</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L12" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
+        <x:v>蓝语</x:v>
       </x:c>
       <x:c r="M12" s="10" t="str"/>
     </x:row>
@@ -1494,33 +1494,33 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B13" s="11" t="n">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C13" s="10" t="str">
-        <x:v>五年归期：我的崽成了团宠</x:v>
+        <x:v>细雨如春，替嫁得良缘</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
+        <x:v>09-02 08:00</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str"/>
       <x:c r="F13" s="11" t="str"/>
       <x:c r="G13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H13" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J13" s="10" t="str">
-        <x:v>仿真人</x:v>
+        <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K13" s="10" t="str">
         <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L13" s="11" t="str">
-        <x:v>言安剧场</x:v>
+        <x:v>心动漫剧场</x:v>
       </x:c>
       <x:c r="M13" s="10" t="str"/>
     </x:row>
@@ -1529,30 +1529,34 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B14" s="11" t="n">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>乱世繁花入君怀</x:v>
+        <x:v>满堂寿宴皆虚情</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>2026-09-02</x:v>
+        <x:v>09-01 10:00</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str"/>
       <x:c r="F14" s="11" t="str"/>
       <x:c r="G14" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H14" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I14" s="11" t="str"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="n">
+        <x:v>90</x:v>
+      </x:c>
       <x:c r="J14" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K14" s="10" t="str">
-        <x:v>其他</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="str"/>
+        <x:v>婚姻情感</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="str">
+        <x:v>饺子动画</x:v>
+      </x:c>
       <x:c r="M14" s="10" t="str"/>
     </x:row>
     <x:row r="15">
@@ -1560,34 +1564,30 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B15" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C15" s="10" t="str">
-        <x:v>满堂寿宴皆虚情</x:v>
+        <x:v>乱世繁花入君怀</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str"/>
       <x:c r="F15" s="11" t="str"/>
       <x:c r="G15" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="11" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I15" s="11" t="n">
-        <x:v>90</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str"/>
       <x:c r="J15" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K15" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L15" s="11" t="str">
-        <x:v>饺子动画</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="str"/>
       <x:c r="M15" s="10" t="str"/>
     </x:row>
     <x:row r="16">
@@ -1595,7 +1595,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B16" s="11" t="n">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
         <x:v>这一次，换我保护妈妈</x:v>
@@ -1606,10 +1606,10 @@
       <x:c r="E16" s="11" t="str"/>
       <x:c r="F16" s="11" t="str"/>
       <x:c r="G16" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H16" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
         <x:v>63</x:v>
@@ -1630,7 +1630,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B17" s="11" t="n">
-        <x:v>85</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C17" s="10" t="str">
         <x:v>梦醒八零年</x:v>
@@ -1641,10 +1641,10 @@
       <x:c r="E17" s="11" t="str"/>
       <x:c r="F17" s="11" t="str"/>
       <x:c r="G17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H17" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
         <x:v>48</x:v>
@@ -1667,7 +1667,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B18" s="11" t="n">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C18" s="10" t="str">
         <x:v>万界轮回，我有亿万神话词条加身</x:v>
@@ -1678,10 +1678,10 @@
       <x:c r="E18" s="11" t="str"/>
       <x:c r="F18" s="11" t="str"/>
       <x:c r="G18" s="11" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="H18" s="11" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
         <x:v>195</x:v>
@@ -1702,7 +1702,7 @@
         <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B19" s="11" t="n">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>大婚当日立规矩，这婚我不结了</x:v>
@@ -1713,10 +1713,10 @@
       <x:c r="E19" s="11" t="str"/>
       <x:c r="F19" s="11" t="str"/>
       <x:c r="G19" s="11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H19" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
         <x:v>46</x:v>
@@ -1734,248 +1734,252 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B20" s="11" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C20" s="10" t="str">
-        <x:v>乌鸦掉进凤凰窝，我成了冥凤小公主</x:v>
+        <x:v>六万不到账，五十桌不开席</x:v>
       </x:c>
       <x:c r="D20" s="11" t="str">
-        <x:v>09-01 10:00</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F20" s="11" t="str">
-        <x:v>↑55位</x:v>
-      </x:c>
-      <x:c r="G20" s="11" t="str"/>
-      <x:c r="H20" s="11" t="str"/>
+        <x:v>09-02 19:00</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="str"/>
+      <x:c r="F20" s="11" t="str"/>
+      <x:c r="G20" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H20" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J20" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K20" s="10" t="str">
-        <x:v>古装宫廷</x:v>
+        <x:v>美食治愈 / 现实反转</x:v>
       </x:c>
       <x:c r="L20" s="11" t="str">
-        <x:v>白桃剧场</x:v>
+        <x:v>云起剧场</x:v>
       </x:c>
       <x:c r="M20" s="10" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B21" s="11" t="n">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="10" t="str">
-        <x:v>爹爹入赘我暴富啦</x:v>
+        <x:v>靠山屯纪事</x:v>
       </x:c>
       <x:c r="D21" s="11" t="str">
-        <x:v>09-02 00:20</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F21" s="11" t="str">
-        <x:v>↑44位</x:v>
-      </x:c>
-      <x:c r="G21" s="11" t="str"/>
-      <x:c r="H21" s="11" t="str"/>
+        <x:v>09-02 15:00</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="str"/>
+      <x:c r="F21" s="11" t="str"/>
+      <x:c r="G21" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H21" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:v>121</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="J21" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="K21" s="10" t="str">
-        <x:v>家庭伦理 / 逆袭打脸</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L21" s="11" t="str">
-        <x:v>每日沙雕推荐</x:v>
+        <x:v>小小动画</x:v>
       </x:c>
       <x:c r="M21" s="10" t="str">
-        <x:v>沈明珠看着母亲决绝离去，姐姐执意奔赴城里。她灵机一动，主动给父亲说媒，让父亲入赘彪悍女猎户钱三妞。她凭借前世记忆得到祖传的灵泉玉佩，和三位性格迥异的继兄相处融洽。一家人齐心对抗难缠的街坊对手，揭穿坏人的伪装，齐心协力把小日子过得红火安稳。</x:v>
+        <x:v>穿越到七十年代的花昭，重生在肥胖的少女身上。她凭借一身胆识与偶然得到的宝物，改变自身境遇，巧妙化解亲戚的算计纠缠。抓住时代机遇带动村里发展副业，改善一家人的生活。与军人叶深结缘，意外迎来新的小生命。面对原生家庭的复杂纠葛，她保持清醒，护住爷爷与至亲，在艰苦的年代里脚踏实地，靠着智慧和韧性，一步步打拼出属于自己的安稳人生。</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B22" s="11" t="n">
-        <x:v>54</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" s="10" t="str">
-        <x:v>洪伟的故事</x:v>
+        <x:v>爹爹入赘我暴富啦</x:v>
       </x:c>
       <x:c r="D22" s="11" t="str">
-        <x:v>09-02 09:53</x:v>
-      </x:c>
-      <x:c r="E22" s="11" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F22" s="11" t="str">
-        <x:v>↑41位</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="str"/>
-      <x:c r="H22" s="11" t="str"/>
+        <x:v>09-02 00:20</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="str"/>
+      <x:c r="F22" s="11" t="str"/>
+      <x:c r="G22" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H22" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I22" s="11" t="n">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="J22" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K22" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>家庭伦理 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L22" s="11" t="str">
-        <x:v>淑芬动画</x:v>
-      </x:c>
-      <x:c r="M22" s="10" t="str"/>
+        <x:v>每日沙雕推荐</x:v>
+      </x:c>
+      <x:c r="M22" s="10" t="str">
+        <x:v>沈明珠看着母亲决绝离去，姐姐执意奔赴城里。她灵机一动，主动给父亲说媒，让父亲入赘彪悍女猎户钱三妞。她凭借前世记忆得到祖传的灵泉玉佩，和三位性格迥异的继兄相处融洽。一家人齐心对抗难缠的街坊对手，揭穿坏人的伪装，齐心协力把小日子过得红火安稳。</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B23" s="11" t="n">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C23" s="10" t="str">
-        <x:v>洋媳妇勇闯东北老家</x:v>
+        <x:v>盛海风云</x:v>
       </x:c>
       <x:c r="D23" s="11" t="str">
-        <x:v>09-02 16:00</x:v>
-      </x:c>
-      <x:c r="E23" s="11" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F23" s="11" t="str">
-        <x:v>↑29位</x:v>
-      </x:c>
-      <x:c r="G23" s="11" t="str"/>
-      <x:c r="H23" s="11" t="str"/>
+        <x:v>09-02 09:58</x:v>
+      </x:c>
+      <x:c r="E23" s="11" t="str"/>
+      <x:c r="F23" s="11" t="str"/>
+      <x:c r="G23" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H23" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I23" s="11" t="n">
-        <x:v>154</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J23" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="K23" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L23" s="11" t="str">
-        <x:v>云间漫剧-十六</x:v>
-      </x:c>
-      <x:c r="M23" s="10" t="str"/>
+        <x:v>星间漫步</x:v>
+      </x:c>
+      <x:c r="M23" s="10" t="str">
+        <x:v>八十岁的千亿级盛海财团创始人林晚秋重生回到董事会召开前夕，当场罢免为私情撕毁百亿合作协议的嫡孙顾景辰，召回蛰伏非洲的铁血庶孙顾景深，布下代码陷阱精准反制宿敌耀星科技的商业间谍阴谋，以铁血手腕守护集团基业，顺利完成新老权力交接。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B24" s="11" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="str">
+        <x:v>宴席终散人归远</x:v>
+      </x:c>
+      <x:c r="D24" s="11" t="str">
+        <x:v>09-01 20:18</x:v>
+      </x:c>
+      <x:c r="E24" s="11" t="str"/>
+      <x:c r="F24" s="11" t="str"/>
+      <x:c r="G24" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C24" s="10" t="str">
-        <x:v>烫嘴的免费午饭</x:v>
-      </x:c>
-      <x:c r="D24" s="11" t="str">
-        <x:v>09-01 11:00</x:v>
-      </x:c>
-      <x:c r="E24" s="11" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F24" s="11" t="str">
-        <x:v>↑22位</x:v>
-      </x:c>
-      <x:c r="G24" s="11" t="str"/>
-      <x:c r="H24" s="11" t="str"/>
+      <x:c r="H24" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I24" s="11" t="n">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J24" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="K24" s="10" t="str">
-        <x:v>美食治愈</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L24" s="11" t="str">
-        <x:v>夏安安</x:v>
+        <x:v>柚子吖</x:v>
       </x:c>
       <x:c r="M24" s="10" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B25" s="11" t="n">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="10" t="str">
-        <x:v>遗落在村口的春天</x:v>
+        <x:v>你让我出海：我一船货卖二十万你慌什么</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>09-02 10:37</x:v>
-      </x:c>
-      <x:c r="E25" s="11" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F25" s="11" t="str">
-        <x:v>↑21位</x:v>
-      </x:c>
-      <x:c r="G25" s="11" t="str"/>
-      <x:c r="H25" s="11" t="str"/>
+        <x:v>09-02 09:05</x:v>
+      </x:c>
+      <x:c r="E25" s="11" t="str"/>
+      <x:c r="F25" s="11" t="str"/>
+      <x:c r="G25" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H25" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I25" s="11" t="n">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J25" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="K25" s="10" t="str">
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L25" s="11" t="str">
-        <x:v>奇迹短剧</x:v>
+        <x:v>呼哈短剧</x:v>
       </x:c>
       <x:c r="M25" s="10" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
-        <x:v>新剧上升</x:v>
+        <x:v>持续在榜</x:v>
       </x:c>
       <x:c r="B26" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="10" t="str">
-        <x:v>浴火重生重回1984，怒掀桌子拒入赘</x:v>
+        <x:v>洋媳妇勇闯东北老家</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>09-01 10:54</x:v>
-      </x:c>
-      <x:c r="E26" s="11" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F26" s="11" t="str">
-        <x:v>↑19位</x:v>
-      </x:c>
-      <x:c r="G26" s="11" t="str"/>
-      <x:c r="H26" s="11" t="str"/>
+        <x:v>09-02 16:00</x:v>
+      </x:c>
+      <x:c r="E26" s="11" t="str"/>
+      <x:c r="F26" s="11" t="str"/>
+      <x:c r="G26" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H26" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I26" s="11" t="n">
-        <x:v>184</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="J26" s="10" t="str">
         <x:v>经典3D</x:v>
       </x:c>
       <x:c r="K26" s="10" t="str">
-        <x:v>年代怀旧</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L26" s="11" t="str">
-        <x:v>一漳动漫</x:v>
+        <x:v>云间漫剧-十六</x:v>
       </x:c>
       <x:c r="M26" s="10" t="str"/>
     </x:row>
@@ -1984,70 +1988,68 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B27" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C27" s="10" t="str">
-        <x:v>盛海风云</x:v>
+        <x:v>他们霸占我的房结婚，我反手卖掉</x:v>
       </x:c>
       <x:c r="D27" s="11" t="str">
-        <x:v>09-02 09:58</x:v>
+        <x:v>09-02 00:06</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:v>38</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F27" s="11" t="str">
-        <x:v>↑18位</x:v>
+        <x:v>↑38位</x:v>
       </x:c>
       <x:c r="G27" s="11" t="str"/>
       <x:c r="H27" s="11" t="str"/>
       <x:c r="I27" s="11" t="n">
-        <x:v>84</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K27" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感 / 逆袭打脸</x:v>
       </x:c>
       <x:c r="L27" s="11" t="str">
-        <x:v>星间漫步</x:v>
-      </x:c>
-      <x:c r="M27" s="10" t="str">
-        <x:v>八十岁的千亿级盛海财团创始人林晚秋重生回到董事会召开前夕，当场罢免为私情撕毁百亿合作协议的嫡孙顾景辰，召回蛰伏非洲的铁血庶孙顾景深，布下代码陷阱精准反制宿敌耀星科技的商业间谍阴谋，以铁血手腕守护集团基业，顺利完成新老权力交接。</x:v>
-      </x:c>
+        <x:v>金秋剧场</x:v>
+      </x:c>
+      <x:c r="M27" s="10" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B28" s="11" t="n">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="10" t="str">
-        <x:v>深宫重华录</x:v>
+        <x:v>离婚后我万丈荣光</x:v>
       </x:c>
       <x:c r="D28" s="11" t="str">
-        <x:v>09-01 17:45</x:v>
+        <x:v>09-02 18:00</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:v>53</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F28" s="11" t="str">
-        <x:v>↑17位</x:v>
+        <x:v>↑18位</x:v>
       </x:c>
       <x:c r="G28" s="11" t="str"/>
       <x:c r="H28" s="11" t="str"/>
       <x:c r="I28" s="11" t="n">
-        <x:v>141</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J28" s="10" t="str">
-        <x:v>未标注</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="K28" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>婚姻情感</x:v>
       </x:c>
       <x:c r="L28" s="11" t="str">
-        <x:v>蓝语</x:v>
+        <x:v>平阅漫漫看</x:v>
       </x:c>
       <x:c r="M28" s="10" t="str"/>
     </x:row>
@@ -2056,34 +2058,30 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B29" s="11" t="n">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="10" t="str">
-        <x:v>细雨如春，替嫁得良缘</x:v>
+        <x:v>餐桌上的河豚</x:v>
       </x:c>
       <x:c r="D29" s="11" t="str">
-        <x:v>09-02 08:00</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F29" s="11" t="str">
-        <x:v>↑11位</x:v>
+        <x:v>↑15位</x:v>
       </x:c>
       <x:c r="G29" s="11" t="str"/>
       <x:c r="H29" s="11" t="str"/>
-      <x:c r="I29" s="11" t="n">
-        <x:v>75</x:v>
-      </x:c>
+      <x:c r="I29" s="11" t="str"/>
       <x:c r="J29" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>未标注</x:v>
       </x:c>
       <x:c r="K29" s="10" t="str">
-        <x:v>婚姻情感</x:v>
-      </x:c>
-      <x:c r="L29" s="11" t="str">
-        <x:v>心动漫剧场</x:v>
-      </x:c>
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="L29" s="11" t="str"/>
       <x:c r="M29" s="10" t="str"/>
     </x:row>
     <x:row r="30">
@@ -2091,24 +2089,24 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B30" s="11" t="n">
-        <x:v>16</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C30" s="10" t="str">
-        <x:v>你让我出海：我一船货卖二十万你慌什么</x:v>
+        <x:v>七年退让到此为止</x:v>
       </x:c>
       <x:c r="D30" s="11" t="str">
-        <x:v>09-02 09:05</x:v>
+        <x:v>09-01 12:00</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:v>26</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F30" s="11" t="str">
-        <x:v>↑10位</x:v>
+        <x:v>↑13位</x:v>
       </x:c>
       <x:c r="G30" s="11" t="str"/>
       <x:c r="H30" s="11" t="str"/>
       <x:c r="I30" s="11" t="n">
-        <x:v>87</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J30" s="10" t="str">
         <x:v>仿真人</x:v>
@@ -2117,7 +2115,7 @@
         <x:v>其他</x:v>
       </x:c>
       <x:c r="L30" s="11" t="str">
-        <x:v>呼哈短剧</x:v>
+        <x:v>二妞.影视</x:v>
       </x:c>
       <x:c r="M30" s="10" t="str"/>
     </x:row>
@@ -2126,70 +2124,68 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B31" s="11" t="n">
-        <x:v>13</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>靠山屯纪事</x:v>
+        <x:v>一碟辣椒引出人心账</x:v>
       </x:c>
       <x:c r="D31" s="11" t="str">
-        <x:v>09-02 15:00</x:v>
+        <x:v>09-02 11:30</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:v>20</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F31" s="11" t="str">
-        <x:v>↑7位</x:v>
+        <x:v>↑10位</x:v>
       </x:c>
       <x:c r="G31" s="11" t="str"/>
       <x:c r="H31" s="11" t="str"/>
       <x:c r="I31" s="11" t="n">
-        <x:v>168</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="J31" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="K31" s="10" t="str">
-        <x:v>其他</x:v>
+        <x:v>现实反转</x:v>
       </x:c>
       <x:c r="L31" s="11" t="str">
-        <x:v>小小动画</x:v>
-      </x:c>
-      <x:c r="M31" s="10" t="str">
-        <x:v>穿越到七十年代的花昭，重生在肥胖的少女身上。她凭借一身胆识与偶然得到的宝物，改变自身境遇，巧妙化解亲戚的算计纠缠。抓住时代机遇带动村里发展副业，改善一家人的生活。与军人叶深结缘，意外迎来新的小生命。面对原生家庭的复杂纠葛，她保持清醒，护住爷爷与至亲，在艰苦的年代里脚踏实地，靠着智慧和韧性，一步步打拼出属于自己的安稳人生。</x:v>
-      </x:c>
+        <x:v>洛川漫剧</x:v>
+      </x:c>
+      <x:c r="M31" s="10" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="11" t="str">
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B32" s="11" t="n">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>当妈妈开始较真的时候</x:v>
+        <x:v>雨天无敌之神也想过退休生活</x:v>
       </x:c>
       <x:c r="D32" s="11" t="str">
-        <x:v>09-01 09:00</x:v>
+        <x:v>09-02 15:00</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:v>39</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F32" s="11" t="str">
-        <x:v>↑5位</x:v>
+        <x:v>↑8位</x:v>
       </x:c>
       <x:c r="G32" s="11" t="str"/>
       <x:c r="H32" s="11" t="str"/>
       <x:c r="I32" s="11" t="n">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J32" s="10" t="str">
         <x:v>未标注</x:v>
       </x:c>
       <x:c r="K32" s="10" t="str">
-        <x:v>家庭伦理</x:v>
+        <x:v>逆袭打脸 / 战神异能</x:v>
       </x:c>
       <x:c r="L32" s="11" t="str">
-        <x:v>小圆子剧场</x:v>
+        <x:v>晓晓的创作</x:v>
       </x:c>
       <x:c r="M32" s="10" t="str"/>
     </x:row>
@@ -2198,33 +2194,33 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B33" s="11" t="n">
-        <x:v>5</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>六万不到账，五十桌不开席</x:v>
+        <x:v>外婆的小心思</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>09-02 19:00</x:v>
+        <x:v>09-01 11:22</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:v>9</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F33" s="11" t="str">
-        <x:v>↑4位</x:v>
+        <x:v>↑8位</x:v>
       </x:c>
       <x:c r="G33" s="11" t="str"/>
       <x:c r="H33" s="11" t="str"/>
       <x:c r="I33" s="11" t="n">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J33" s="10" t="str">
-        <x:v>经典3D</x:v>
+        <x:v>仿真人</x:v>
       </x:c>
       <x:c r="K33" s="10" t="str">
-        <x:v>美食治愈 / 现实反转</x:v>
+        <x:v>其他</x:v>
       </x:c>
       <x:c r="L33" s="11" t="str">
-        <x:v>云起剧场</x:v>
+        <x:v>奇境剧场</x:v>
       </x:c>
       <x:c r="M33" s="10" t="str"/>
     </x:row>
@@ -2233,31 +2229,33 @@
         <x:v>新剧上升</x:v>
       </x:c>
       <x:c r="B34" s="11" t="n">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x: